--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="954" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD910A3B-836C-4E57-8E6A-A8933CF6C332}"/>
+  <xr:revisionPtr revIDLastSave="955" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D05CB1F8-ACEC-4794-9084-F5A1B54C5176}"/>
   <bookViews>
-    <workbookView xWindow="38420" yWindow="170" windowWidth="38380" windowHeight="20860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="327">
   <si>
     <t>Tijd</t>
   </si>
@@ -1327,33 +1327,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1719,99 +1719,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="38" t="s">
+      <c r="F1" s="40"/>
+      <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="36"/>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="37" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="36"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="37" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="36"/>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="37" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="36"/>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="37" t="s">
         <v>9</v>
       </c>
       <c r="P1" s="36"/>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="37" t="s">
         <v>10</v>
       </c>
       <c r="R1" s="36"/>
-      <c r="S1" s="38" t="s">
+      <c r="S1" s="37" t="s">
         <v>11</v>
       </c>
       <c r="T1" s="36"/>
-      <c r="U1" s="38" t="s">
+      <c r="U1" s="37" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="36"/>
-      <c r="W1" s="38" t="s">
+      <c r="W1" s="37" t="s">
         <v>13</v>
       </c>
       <c r="X1" s="36"/>
-      <c r="Y1" s="38" t="s">
+      <c r="Y1" s="37" t="s">
         <v>14</v>
       </c>
       <c r="Z1" s="36"/>
-      <c r="AA1" s="38" t="s">
+      <c r="AA1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="AB1" s="36"/>
-      <c r="AC1" s="38" t="s">
+      <c r="AC1" s="37" t="s">
         <v>16</v>
       </c>
       <c r="AD1" s="36"/>
-      <c r="AE1" s="38" t="s">
+      <c r="AE1" s="37" t="s">
         <v>17</v>
       </c>
       <c r="AF1" s="36"/>
-      <c r="AG1" s="38" t="s">
+      <c r="AG1" s="37" t="s">
         <v>18</v>
       </c>
       <c r="AH1" s="36"/>
-      <c r="AI1" s="38" t="s">
+      <c r="AI1" s="37" t="s">
         <v>19</v>
       </c>
       <c r="AJ1" s="36"/>
-      <c r="AK1" s="38" t="s">
+      <c r="AK1" s="37" t="s">
         <v>20</v>
       </c>
       <c r="AL1" s="36"/>
-      <c r="AM1" s="38" t="s">
+      <c r="AM1" s="37" t="s">
         <v>21</v>
       </c>
       <c r="AN1" s="36"/>
-      <c r="AO1" s="38" t="s">
+      <c r="AO1" s="37" t="s">
         <v>22</v>
       </c>
       <c r="AP1" s="36"/>
-      <c r="AQ1" s="38" t="s">
+      <c r="AQ1" s="37" t="s">
         <v>23</v>
       </c>
       <c r="AR1" s="36"/>
-      <c r="AS1" s="38" t="s">
+      <c r="AS1" s="37" t="s">
         <v>24</v>
       </c>
       <c r="AT1" s="36"/>
@@ -1823,10 +1823,10 @@
       </c>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A2" s="43"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="42"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
       </c>
@@ -1961,59 +1961,59 @@
       </c>
     </row>
     <row r="3" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="44"/>
       <c r="AU3" s="7"/>
       <c r="AV3" s="7"/>
     </row>
     <row r="4" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="34"/>
@@ -2071,164 +2071,166 @@
       <c r="B5" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="10"/>
+      <c r="C5" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="11" t="str">
+      <c r="F5" s="11">
         <f>IF(OR($C5="",E5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E5,FIND("-",E5)-1),"")=AU5,IFERROR(--MID(E5,FIND("-",E5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(E5,FIND("-",E5)-1),""))-(IFERROR(--MID(E5,FIND("-",E5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(E5,FIND("-",E5)-1),""))-(IFERROR(--MID(E5,FIND("-",E5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(E5,FIND("-",E5)-1),""))=(AU5))+2*((IFERROR(--MID(E5,FIND("-",E5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="11" t="str">
+      <c r="H5" s="11">
         <f>IF(OR($C5="",G5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G5,FIND("-",G5)-1),"")=AU5,IFERROR(--MID(G5,FIND("-",G5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(G5,FIND("-",G5)-1),""))-(IFERROR(--MID(G5,FIND("-",G5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(G5,FIND("-",G5)-1),""))-(IFERROR(--MID(G5,FIND("-",G5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(G5,FIND("-",G5)-1),""))=(AU5))+2*((IFERROR(--MID(G5,FIND("-",G5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="11" t="str">
+      <c r="J5" s="11">
         <f>IF(OR($C5="",I5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I5,FIND("-",I5)-1),"")=AU5,IFERROR(--MID(I5,FIND("-",I5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(I5,FIND("-",I5)-1),""))-(IFERROR(--MID(I5,FIND("-",I5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(I5,FIND("-",I5)-1),""))-(IFERROR(--MID(I5,FIND("-",I5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(I5,FIND("-",I5)-1),""))=(AU5))+2*((IFERROR(--MID(I5,FIND("-",I5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="11" t="str">
+      <c r="L5" s="11">
         <f>IF(OR($C5="",K5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K5,FIND("-",K5)-1),"")=AU5,IFERROR(--MID(K5,FIND("-",K5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(K5,FIND("-",K5)-1),""))-(IFERROR(--MID(K5,FIND("-",K5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(K5,FIND("-",K5)-1),""))-(IFERROR(--MID(K5,FIND("-",K5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(K5,FIND("-",K5)-1),""))=(AU5))+2*((IFERROR(--MID(K5,FIND("-",K5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N5" s="11" t="str">
+      <c r="N5" s="11">
         <f>IF(OR($C5="",M5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M5,FIND("-",M5)-1),"")=AU5,IFERROR(--MID(M5,FIND("-",M5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(M5,FIND("-",M5)-1),""))-(IFERROR(--MID(M5,FIND("-",M5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(M5,FIND("-",M5)-1),""))-(IFERROR(--MID(M5,FIND("-",M5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(M5,FIND("-",M5)-1),""))=(AU5))+2*((IFERROR(--MID(M5,FIND("-",M5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P5" s="11" t="str">
+      <c r="P5" s="11">
         <f>IF(OR($C5="",O5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O5,FIND("-",O5)-1),"")=AU5,IFERROR(--MID(O5,FIND("-",O5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(O5,FIND("-",O5)-1),""))-(IFERROR(--MID(O5,FIND("-",O5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(O5,FIND("-",O5)-1),""))-(IFERROR(--MID(O5,FIND("-",O5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(O5,FIND("-",O5)-1),""))=(AU5))+2*((IFERROR(--MID(O5,FIND("-",O5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="11" t="str">
+      <c r="R5" s="11">
         <f>IF(OR($C5="",Q5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q5,FIND("-",Q5)-1),"")=AU5,IFERROR(--MID(Q5,FIND("-",Q5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(Q5,FIND("-",Q5)-1),""))-(IFERROR(--MID(Q5,FIND("-",Q5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(Q5,FIND("-",Q5)-1),""))-(IFERROR(--MID(Q5,FIND("-",Q5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(Q5,FIND("-",Q5)-1),""))=(AU5))+2*((IFERROR(--MID(Q5,FIND("-",Q5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="11" t="str">
+      <c r="T5" s="11">
         <f>IF(OR($C5="",S5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S5,FIND("-",S5)-1),"")=AU5,IFERROR(--MID(S5,FIND("-",S5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(S5,FIND("-",S5)-1),""))-(IFERROR(--MID(S5,FIND("-",S5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(S5,FIND("-",S5)-1),""))-(IFERROR(--MID(S5,FIND("-",S5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(S5,FIND("-",S5)-1),""))=(AU5))+2*((IFERROR(--MID(S5,FIND("-",S5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V5" s="11" t="str">
+      <c r="V5" s="11">
         <f>IF(OR($C5="",U5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U5,FIND("-",U5)-1),"")=AU5,IFERROR(--MID(U5,FIND("-",U5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(U5,FIND("-",U5)-1),""))-(IFERROR(--MID(U5,FIND("-",U5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(U5,FIND("-",U5)-1),""))-(IFERROR(--MID(U5,FIND("-",U5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(U5,FIND("-",U5)-1),""))=(AU5))+2*((IFERROR(--MID(U5,FIND("-",U5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X5" s="11" t="str">
+      <c r="X5" s="11">
         <f>IF(OR($C5="",W5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W5,FIND("-",W5)-1),"")=AU5,IFERROR(--MID(W5,FIND("-",W5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(W5,FIND("-",W5)-1),""))-(IFERROR(--MID(W5,FIND("-",W5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(W5,FIND("-",W5)-1),""))-(IFERROR(--MID(W5,FIND("-",W5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(W5,FIND("-",W5)-1),""))=(AU5))+2*((IFERROR(--MID(W5,FIND("-",W5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Y5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z5" s="11" t="str">
+      <c r="Z5" s="11">
         <f>IF(OR($C5="",Y5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y5,FIND("-",Y5)-1),"")=AU5,IFERROR(--MID(Y5,FIND("-",Y5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(Y5,FIND("-",Y5)-1),""))-(IFERROR(--MID(Y5,FIND("-",Y5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(Y5,FIND("-",Y5)-1),""))-(IFERROR(--MID(Y5,FIND("-",Y5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(Y5,FIND("-",Y5)-1),""))=(AU5))+2*((IFERROR(--MID(Y5,FIND("-",Y5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AB5" s="11" t="str">
+      <c r="AB5" s="11">
         <f>IF(OR($C5="",AA5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA5,FIND("-",AA5)-1),"")=AU5,IFERROR(--MID(AA5,FIND("-",AA5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AA5,FIND("-",AA5)-1),""))-(IFERROR(--MID(AA5,FIND("-",AA5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AA5,FIND("-",AA5)-1),""))-(IFERROR(--MID(AA5,FIND("-",AA5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AA5,FIND("-",AA5)-1),""))=(AU5))+2*((IFERROR(--MID(AA5,FIND("-",AA5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD5" s="11" t="str">
+      <c r="AD5" s="11">
         <f>IF(OR($C5="",AC5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC5,FIND("-",AC5)-1),"")=AU5,IFERROR(--MID(AC5,FIND("-",AC5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AC5,FIND("-",AC5)-1),""))-(IFERROR(--MID(AC5,FIND("-",AC5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AC5,FIND("-",AC5)-1),""))-(IFERROR(--MID(AC5,FIND("-",AC5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AC5,FIND("-",AC5)-1),""))=(AU5))+2*((IFERROR(--MID(AC5,FIND("-",AC5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF5" s="11" t="str">
+      <c r="AF5" s="11">
         <f>IF(OR($C5="",AE5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE5,FIND("-",AE5)-1),"")=AU5,IFERROR(--MID(AE5,FIND("-",AE5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AE5,FIND("-",AE5)-1),""))-(IFERROR(--MID(AE5,FIND("-",AE5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AE5,FIND("-",AE5)-1),""))-(IFERROR(--MID(AE5,FIND("-",AE5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AE5,FIND("-",AE5)-1),""))=(AU5))+2*((IFERROR(--MID(AE5,FIND("-",AE5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH5" s="11" t="str">
+      <c r="AH5" s="11">
         <f>IF(OR($C5="",AG5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG5,FIND("-",AG5)-1),"")=AU5,IFERROR(--MID(AG5,FIND("-",AG5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AG5,FIND("-",AG5)-1),""))-(IFERROR(--MID(AG5,FIND("-",AG5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AG5,FIND("-",AG5)-1),""))-(IFERROR(--MID(AG5,FIND("-",AG5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AG5,FIND("-",AG5)-1),""))=(AU5))+2*((IFERROR(--MID(AG5,FIND("-",AG5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ5" s="11" t="str">
+      <c r="AJ5" s="11">
         <f>IF(OR($C5="",AI5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI5,FIND("-",AI5)-1),"")=AU5,IFERROR(--MID(AI5,FIND("-",AI5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AI5,FIND("-",AI5)-1),""))-(IFERROR(--MID(AI5,FIND("-",AI5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AI5,FIND("-",AI5)-1),""))-(IFERROR(--MID(AI5,FIND("-",AI5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AI5,FIND("-",AI5)-1),""))=(AU5))+2*((IFERROR(--MID(AI5,FIND("-",AI5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL5" s="11" t="str">
+      <c r="AL5" s="11">
         <f>IF(OR($C5="",AK5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK5,FIND("-",AK5)-1),"")=AU5,IFERROR(--MID(AK5,FIND("-",AK5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AK5,FIND("-",AK5)-1),""))-(IFERROR(--MID(AK5,FIND("-",AK5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AK5,FIND("-",AK5)-1),""))-(IFERROR(--MID(AK5,FIND("-",AK5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AK5,FIND("-",AK5)-1),""))=(AU5))+2*((IFERROR(--MID(AK5,FIND("-",AK5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AN5" s="11" t="str">
+      <c r="AN5" s="11">
         <f>IF(OR($C5="",AM5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM5,FIND("-",AM5)-1),"")=AU5,IFERROR(--MID(AM5,FIND("-",AM5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AM5,FIND("-",AM5)-1),""))-(IFERROR(--MID(AM5,FIND("-",AM5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AM5,FIND("-",AM5)-1),""))-(IFERROR(--MID(AM5,FIND("-",AM5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AM5,FIND("-",AM5)-1),""))=(AU5))+2*((IFERROR(--MID(AM5,FIND("-",AM5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AP5" s="11" t="str">
+      <c r="AP5" s="11">
         <f>IF(OR($C5="",AO5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO5,FIND("-",AO5)-1),"")=AU5,IFERROR(--MID(AO5,FIND("-",AO5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AO5,FIND("-",AO5)-1),""))-(IFERROR(--MID(AO5,FIND("-",AO5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AO5,FIND("-",AO5)-1),""))-(IFERROR(--MID(AO5,FIND("-",AO5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AO5,FIND("-",AO5)-1),""))=(AU5))+2*((IFERROR(--MID(AO5,FIND("-",AO5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AR5" s="11" t="str">
+      <c r="AR5" s="11">
         <f>IF(OR($C5="",AQ5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ5,FIND("-",AQ5)-1),"")=AU5,IFERROR(--MID(AQ5,FIND("-",AQ5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AQ5,FIND("-",AQ5)-1),""))-(IFERROR(--MID(AQ5,FIND("-",AQ5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AQ5,FIND("-",AQ5)-1),""))-(IFERROR(--MID(AQ5,FIND("-",AQ5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AQ5,FIND("-",AQ5)-1),""))=(AU5))+2*((IFERROR(--MID(AQ5,FIND("-",AQ5)+1,99),""))=(AV5))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AS5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT5" s="11" t="str">
+      <c r="AT5" s="11">
         <f>IF(OR($C5="",AS5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS5,FIND("-",AS5)-1),"")=AU5,IFERROR(--MID(AS5,FIND("-",AS5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AS5,FIND("-",AS5)-1),""))-(IFERROR(--MID(AS5,FIND("-",AS5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AS5,FIND("-",AS5)-1),""))-(IFERROR(--MID(AS5,FIND("-",AS5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AS5,FIND("-",AS5)-1),""))=(AU5))+2*((IFERROR(--MID(AS5,FIND("-",AS5)+1,99),""))=(AV5))),""))</f>
-        <v/>
-      </c>
-      <c r="AU5" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AU5" s="11">
         <f>IF($C5="","",IFERROR(--LEFT($C5,FIND("-",$C5)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AV5" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AV5" s="11">
         <f>IF($C5="","",IFERROR(--MID($C5,FIND("-",$C5)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:48" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -2285,7 +2287,7 @@
       <c r="AV6" s="12"/>
     </row>
     <row r="7" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="34"/>
@@ -2724,7 +2726,7 @@
       <c r="AV10" s="12"/>
     </row>
     <row r="11" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="34"/>
@@ -3163,7 +3165,7 @@
       <c r="AV14" s="12"/>
     </row>
     <row r="15" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
       <c r="B15" s="34"/>
@@ -4103,7 +4105,7 @@
       <c r="AV21" s="12"/>
     </row>
     <row r="22" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
       <c r="B22" s="34"/>
@@ -4876,7 +4878,7 @@
       <c r="AV27" s="12"/>
     </row>
     <row r="28" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
       <c r="B28" s="34"/>
@@ -5482,7 +5484,7 @@
       <c r="AV32" s="12"/>
     </row>
     <row r="33" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
       <c r="B33" s="34"/>
@@ -6422,7 +6424,7 @@
       <c r="AV39" s="12"/>
     </row>
     <row r="40" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="37" t="s">
+      <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
       <c r="B40" s="34"/>
@@ -7195,7 +7197,7 @@
       <c r="AV45" s="12"/>
     </row>
     <row r="46" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="37" t="s">
+      <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
       <c r="B46" s="34"/>
@@ -7801,7 +7803,7 @@
       <c r="AV50" s="12"/>
     </row>
     <row r="51" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="37" t="s">
+      <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
       <c r="B51" s="34"/>
@@ -8741,7 +8743,7 @@
       <c r="AV57" s="12"/>
     </row>
     <row r="58" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="37" t="s">
+      <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
       <c r="B58" s="34"/>
@@ -9514,7 +9516,7 @@
       <c r="AV63" s="12"/>
     </row>
     <row r="64" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="37" t="s">
+      <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
       <c r="B64" s="34"/>
@@ -10287,7 +10289,7 @@
       <c r="AV69" s="12"/>
     </row>
     <row r="70" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="37" t="s">
+      <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
       <c r="B70" s="34"/>
@@ -11060,7 +11062,7 @@
       <c r="AV75" s="12"/>
     </row>
     <row r="76" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="37" t="s">
+      <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
       <c r="B76" s="34"/>
@@ -11833,7 +11835,7 @@
       <c r="AV81" s="12"/>
     </row>
     <row r="82" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="37" t="s">
+      <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
       <c r="B82" s="34"/>
@@ -12940,7 +12942,7 @@
       <c r="AV89" s="12"/>
     </row>
     <row r="90" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="37" t="s">
+      <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
       <c r="B90" s="34"/>
@@ -14047,7 +14049,7 @@
       <c r="AV97" s="12"/>
     </row>
     <row r="98" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="37" t="s">
+      <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="34"/>
@@ -15154,7 +15156,7 @@
       <c r="AV105" s="12"/>
     </row>
     <row r="106" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="37" t="s">
+      <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
       <c r="B106" s="34"/>
@@ -15980,7 +15982,7 @@
       <c r="AV112" s="12"/>
     </row>
     <row r="113" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="33" t="s">
+      <c r="A113" s="42" t="s">
         <v>128</v>
       </c>
       <c r="B113" s="34"/>
@@ -16032,7 +16034,7 @@
       <c r="AV113" s="7"/>
     </row>
     <row r="114" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="37" t="s">
+      <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
       <c r="B114" s="34"/>
@@ -16262,7 +16264,7 @@
       <c r="AV116" s="12"/>
     </row>
     <row r="117" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="37" t="s">
+      <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
       <c r="B117" s="34"/>
@@ -16617,7 +16619,7 @@
       <c r="AV120" s="12"/>
     </row>
     <row r="121" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="37" t="s">
+      <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
       <c r="B121" s="34"/>
@@ -17097,7 +17099,7 @@
       <c r="AV125" s="12"/>
     </row>
     <row r="126" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="37" t="s">
+      <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
       <c r="B126" s="34"/>
@@ -17577,7 +17579,7 @@
       <c r="AV130" s="12"/>
     </row>
     <row r="131" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="37" t="s">
+      <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
       <c r="B131" s="34"/>
@@ -17932,7 +17934,7 @@
       <c r="AV134" s="12"/>
     </row>
     <row r="135" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="37" t="s">
+      <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
       <c r="B135" s="34"/>
@@ -18412,7 +18414,7 @@
       <c r="AV139" s="12"/>
     </row>
     <row r="140" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="37" t="s">
+      <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
       <c r="B140" s="34"/>
@@ -18820,7 +18822,7 @@
       <c r="AV144" s="12"/>
     </row>
     <row r="145" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="33" t="s">
+      <c r="A145" s="42" t="s">
         <v>167</v>
       </c>
       <c r="B145" s="34"/>
@@ -18872,7 +18874,7 @@
       <c r="AV145" s="7"/>
     </row>
     <row r="146" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="37" t="s">
+      <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
       <c r="B146" s="34"/>
@@ -19227,7 +19229,7 @@
       <c r="AV149" s="12"/>
     </row>
     <row r="150" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="37" t="s">
+      <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
       <c r="B150" s="34"/>
@@ -19457,7 +19459,7 @@
       <c r="AV152" s="12"/>
     </row>
     <row r="153" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="37" t="s">
+      <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
       <c r="B153" s="34"/>
@@ -19812,7 +19814,7 @@
       <c r="AV156" s="12"/>
     </row>
     <row r="157" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="37" t="s">
+      <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
       <c r="B157" s="34"/>
@@ -20345,7 +20347,7 @@
       <c r="AV162" s="12"/>
     </row>
     <row r="163" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="33" t="s">
+      <c r="A163" s="42" t="s">
         <v>187</v>
       </c>
       <c r="B163" s="34"/>
@@ -20397,7 +20399,7 @@
       <c r="AV163" s="7"/>
     </row>
     <row r="164" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="37" t="s">
+      <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
       <c r="B164" s="34"/>
@@ -20627,7 +20629,7 @@
       <c r="AV166" s="12"/>
     </row>
     <row r="167" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="37" t="s">
+      <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
       <c r="B167" s="34"/>
@@ -20857,7 +20859,7 @@
       <c r="AV169" s="12"/>
     </row>
     <row r="170" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="37" t="s">
+      <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
       <c r="B170" s="34"/>
@@ -21087,7 +21089,7 @@
       <c r="AV172" s="12"/>
     </row>
     <row r="173" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="37" t="s">
+      <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
       <c r="B173" s="34"/>
@@ -21370,7 +21372,7 @@
       <c r="AV176" s="12"/>
     </row>
     <row r="177" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="33" t="s">
+      <c r="A177" s="42" t="s">
         <v>200</v>
       </c>
       <c r="B177" s="34"/>
@@ -21422,7 +21424,7 @@
       <c r="AV177" s="7"/>
     </row>
     <row r="178" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="37" t="s">
+      <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
       <c r="B178" s="34"/>
@@ -21652,7 +21654,7 @@
       <c r="AV180" s="12"/>
     </row>
     <row r="181" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="37" t="s">
+      <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
       <c r="B181" s="34"/>
@@ -21935,7 +21937,7 @@
       <c r="AV184" s="12"/>
     </row>
     <row r="185" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="33" t="s">
+      <c r="A185" s="42" t="s">
         <v>207</v>
       </c>
       <c r="B185" s="34"/>
@@ -21987,7 +21989,7 @@
       <c r="AV185" s="7"/>
     </row>
     <row r="186" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="37" t="s">
+      <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
       <c r="B186" s="34"/>
@@ -22270,7 +22272,7 @@
       <c r="AV189" s="12"/>
     </row>
     <row r="190" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="33" t="s">
+      <c r="A190" s="42" t="s">
         <v>211</v>
       </c>
       <c r="B190" s="34"/>
@@ -22322,7 +22324,7 @@
       <c r="AV190" s="7"/>
     </row>
     <row r="191" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="37" t="s">
+      <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
       <c r="B191" s="34"/>
@@ -22606,6 +22608,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="A185:AT185"/>
+    <mergeCell ref="A40:AT40"/>
+    <mergeCell ref="A82:AT82"/>
+    <mergeCell ref="A4:AT4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AT3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AT33"/>
+    <mergeCell ref="A15:AT15"/>
+    <mergeCell ref="A191:AT191"/>
+    <mergeCell ref="A145:AT145"/>
+    <mergeCell ref="A163:AT163"/>
+    <mergeCell ref="A173:AT173"/>
+    <mergeCell ref="A114:AT114"/>
+    <mergeCell ref="A186:AT186"/>
+    <mergeCell ref="A167:AT167"/>
+    <mergeCell ref="A157:AT157"/>
+    <mergeCell ref="A181:AT181"/>
+    <mergeCell ref="A126:AT126"/>
+    <mergeCell ref="A140:AT140"/>
+    <mergeCell ref="A131:AT131"/>
+    <mergeCell ref="A190:AT190"/>
+    <mergeCell ref="A170:AT170"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A22:AT22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A178:AT178"/>
+    <mergeCell ref="A70:AT70"/>
+    <mergeCell ref="A153:AT153"/>
+    <mergeCell ref="A177:AT177"/>
+    <mergeCell ref="A113:AT113"/>
+    <mergeCell ref="A117:AT117"/>
+    <mergeCell ref="A146:AT146"/>
+    <mergeCell ref="A76:AT76"/>
+    <mergeCell ref="A164:AT164"/>
+    <mergeCell ref="A106:AT106"/>
+    <mergeCell ref="A150:AT150"/>
+    <mergeCell ref="A90:AT90"/>
+    <mergeCell ref="A98:AT98"/>
+    <mergeCell ref="A121:AT121"/>
+    <mergeCell ref="A135:AT135"/>
     <mergeCell ref="A51:AT51"/>
     <mergeCell ref="A58:AT58"/>
     <mergeCell ref="A64:AT64"/>
@@ -22622,59 +22677,6 @@
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="A28:AT28"/>
-    <mergeCell ref="A178:AT178"/>
-    <mergeCell ref="A70:AT70"/>
-    <mergeCell ref="A153:AT153"/>
-    <mergeCell ref="A177:AT177"/>
-    <mergeCell ref="A113:AT113"/>
-    <mergeCell ref="A117:AT117"/>
-    <mergeCell ref="A146:AT146"/>
-    <mergeCell ref="A76:AT76"/>
-    <mergeCell ref="A164:AT164"/>
-    <mergeCell ref="A106:AT106"/>
-    <mergeCell ref="A150:AT150"/>
-    <mergeCell ref="A90:AT90"/>
-    <mergeCell ref="A98:AT98"/>
-    <mergeCell ref="A121:AT121"/>
-    <mergeCell ref="A135:AT135"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A22:AT22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A33:AT33"/>
-    <mergeCell ref="A15:AT15"/>
-    <mergeCell ref="A191:AT191"/>
-    <mergeCell ref="A145:AT145"/>
-    <mergeCell ref="A163:AT163"/>
-    <mergeCell ref="A173:AT173"/>
-    <mergeCell ref="A114:AT114"/>
-    <mergeCell ref="A186:AT186"/>
-    <mergeCell ref="A167:AT167"/>
-    <mergeCell ref="A157:AT157"/>
-    <mergeCell ref="A181:AT181"/>
-    <mergeCell ref="A126:AT126"/>
-    <mergeCell ref="A140:AT140"/>
-    <mergeCell ref="A131:AT131"/>
-    <mergeCell ref="A190:AT190"/>
-    <mergeCell ref="A170:AT170"/>
-    <mergeCell ref="A185:AT185"/>
-    <mergeCell ref="A40:AT40"/>
-    <mergeCell ref="A82:AT82"/>
-    <mergeCell ref="A4:AT4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AT3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25274,6 +25276,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -25285,16 +25297,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -25352,7 +25354,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
@@ -25360,7 +25362,7 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" ref="E3:E23" si="1">C3+D3</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25374,7 +25376,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AK17</f>
@@ -25382,7 +25384,7 @@
       </c>
       <c r="E4" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25396,7 +25398,7 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!U17</f>
@@ -25404,7 +25406,7 @@
       </c>
       <c r="E5" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25418,7 +25420,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!W17</f>
@@ -25426,13 +25428,13 @@
       </c>
       <c r="E6" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="str">
         <f>Wedstrijden_beheer!S1</f>
@@ -25440,7 +25442,7 @@
       </c>
       <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7" s="11">
         <f>Bonus_beheer!S17</f>
@@ -25448,7 +25450,7 @@
       </c>
       <c r="E7" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25462,7 +25464,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!AG17</f>
@@ -25470,13 +25472,13 @@
       </c>
       <c r="E8" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -25484,7 +25486,7 @@
       </c>
       <c r="C9" s="11">
         <f>SUM(Wedstrijden_beheer!AT3:'Wedstrijden_beheer'!AT194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9" s="11">
         <f>Bonus_beheer!AS17</f>
@@ -25492,13 +25494,13 @@
       </c>
       <c r="E9" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>Wedstrijden_beheer!E1</f>
@@ -25506,7 +25508,7 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!E17</f>
@@ -25514,13 +25516,13 @@
       </c>
       <c r="E10" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>Wedstrijden_beheer!AO1</f>
@@ -25528,7 +25530,7 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -25536,7 +25538,7 @@
       </c>
       <c r="E11" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25550,7 +25552,7 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!K17</f>
@@ -25558,13 +25560,13 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -25572,7 +25574,7 @@
       </c>
       <c r="C13" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D13" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -25580,13 +25582,13 @@
       </c>
       <c r="E13" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -25594,7 +25596,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -25602,13 +25604,13 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
@@ -25616,7 +25618,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!AT4:'Wedstrijden_beheer'!AT195)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!AS18</f>
@@ -25624,7 +25626,7 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25638,7 +25640,7 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!Y17</f>
@@ -25646,13 +25648,13 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="str">
         <f>Wedstrijden_beheer!AA1</f>
@@ -25660,7 +25662,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -25668,13 +25670,13 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!M1</f>
@@ -25682,7 +25684,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!M17</f>
@@ -25690,13 +25692,13 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>Wedstrijden_beheer!AC1</f>
@@ -25704,7 +25706,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -25712,13 +25714,13 @@
       </c>
       <c r="E19" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1" t="str">
         <f>Wedstrijden_beheer!AE1</f>
@@ -25726,7 +25728,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -25734,13 +25736,13 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!G1</f>
@@ -25748,7 +25750,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!G17</f>
@@ -25756,13 +25758,13 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
@@ -25784,7 +25786,7 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -26161,26 +26163,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -26375,26 +26357,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26411,4 +26394,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="955" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D05CB1F8-ACEC-4794-9084-F5A1B54C5176}"/>
+  <xr:revisionPtr revIDLastSave="956" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{879FD0C0-2BF2-473B-BD9F-82F15C73270B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Stand!$E$2:$E$22</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="327">
   <si>
     <t>Tijd</t>
   </si>
@@ -1327,33 +1327,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1719,99 +1719,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="37" t="s">
+      <c r="F1" s="44"/>
+      <c r="G1" s="38" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="36"/>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="38" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="36"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="36"/>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="38" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="36"/>
-      <c r="O1" s="37" t="s">
+      <c r="O1" s="38" t="s">
         <v>9</v>
       </c>
       <c r="P1" s="36"/>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="38" t="s">
         <v>10</v>
       </c>
       <c r="R1" s="36"/>
-      <c r="S1" s="37" t="s">
+      <c r="S1" s="38" t="s">
         <v>11</v>
       </c>
       <c r="T1" s="36"/>
-      <c r="U1" s="37" t="s">
+      <c r="U1" s="38" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="36"/>
-      <c r="W1" s="37" t="s">
+      <c r="W1" s="38" t="s">
         <v>13</v>
       </c>
       <c r="X1" s="36"/>
-      <c r="Y1" s="37" t="s">
+      <c r="Y1" s="38" t="s">
         <v>14</v>
       </c>
       <c r="Z1" s="36"/>
-      <c r="AA1" s="37" t="s">
+      <c r="AA1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="AB1" s="36"/>
-      <c r="AC1" s="37" t="s">
+      <c r="AC1" s="38" t="s">
         <v>16</v>
       </c>
       <c r="AD1" s="36"/>
-      <c r="AE1" s="37" t="s">
+      <c r="AE1" s="38" t="s">
         <v>17</v>
       </c>
       <c r="AF1" s="36"/>
-      <c r="AG1" s="37" t="s">
+      <c r="AG1" s="38" t="s">
         <v>18</v>
       </c>
       <c r="AH1" s="36"/>
-      <c r="AI1" s="37" t="s">
+      <c r="AI1" s="38" t="s">
         <v>19</v>
       </c>
       <c r="AJ1" s="36"/>
-      <c r="AK1" s="37" t="s">
+      <c r="AK1" s="38" t="s">
         <v>20</v>
       </c>
       <c r="AL1" s="36"/>
-      <c r="AM1" s="37" t="s">
+      <c r="AM1" s="38" t="s">
         <v>21</v>
       </c>
       <c r="AN1" s="36"/>
-      <c r="AO1" s="37" t="s">
+      <c r="AO1" s="38" t="s">
         <v>22</v>
       </c>
       <c r="AP1" s="36"/>
-      <c r="AQ1" s="37" t="s">
+      <c r="AQ1" s="38" t="s">
         <v>23</v>
       </c>
       <c r="AR1" s="36"/>
-      <c r="AS1" s="37" t="s">
+      <c r="AS1" s="38" t="s">
         <v>24</v>
       </c>
       <c r="AT1" s="36"/>
@@ -1823,10 +1823,10 @@
       </c>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A2" s="39"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="41"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
       </c>
@@ -1961,59 +1961,59 @@
       </c>
     </row>
     <row r="3" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="40"/>
       <c r="AU3" s="7"/>
       <c r="AV3" s="7"/>
     </row>
     <row r="4" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="34"/>
@@ -2287,7 +2287,7 @@
       <c r="AV6" s="12"/>
     </row>
     <row r="7" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="37" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="34"/>
@@ -2345,164 +2345,166 @@
       <c r="B8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="10"/>
+      <c r="C8" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="11" t="str">
+      <c r="F8" s="11">
         <f>IF(OR($C8="",E8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E8,FIND("-",E8)-1),"")=AU8,IFERROR(--MID(E8,FIND("-",E8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(E8,FIND("-",E8)-1),""))-(IFERROR(--MID(E8,FIND("-",E8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(E8,FIND("-",E8)-1),""))-(IFERROR(--MID(E8,FIND("-",E8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(E8,FIND("-",E8)-1),""))=(AU8))+2*((IFERROR(--MID(E8,FIND("-",E8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="11" t="str">
+      <c r="H8" s="11">
         <f>IF(OR($C8="",G8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G8,FIND("-",G8)-1),"")=AU8,IFERROR(--MID(G8,FIND("-",G8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(G8,FIND("-",G8)-1),""))-(IFERROR(--MID(G8,FIND("-",G8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(G8,FIND("-",G8)-1),""))-(IFERROR(--MID(G8,FIND("-",G8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(G8,FIND("-",G8)-1),""))=(AU8))+2*((IFERROR(--MID(G8,FIND("-",G8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="11" t="str">
+      <c r="J8" s="11">
         <f>IF(OR($C8="",I8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I8,FIND("-",I8)-1),"")=AU8,IFERROR(--MID(I8,FIND("-",I8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(I8,FIND("-",I8)-1),""))-(IFERROR(--MID(I8,FIND("-",I8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(I8,FIND("-",I8)-1),""))-(IFERROR(--MID(I8,FIND("-",I8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(I8,FIND("-",I8)-1),""))=(AU8))+2*((IFERROR(--MID(I8,FIND("-",I8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="11" t="str">
+      <c r="L8" s="11">
         <f>IF(OR($C8="",K8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K8,FIND("-",K8)-1),"")=AU8,IFERROR(--MID(K8,FIND("-",K8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(K8,FIND("-",K8)-1),""))-(IFERROR(--MID(K8,FIND("-",K8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(K8,FIND("-",K8)-1),""))-(IFERROR(--MID(K8,FIND("-",K8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(K8,FIND("-",K8)-1),""))=(AU8))+2*((IFERROR(--MID(K8,FIND("-",K8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="11" t="str">
+      <c r="N8" s="11">
         <f>IF(OR($C8="",M8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M8,FIND("-",M8)-1),"")=AU8,IFERROR(--MID(M8,FIND("-",M8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(M8,FIND("-",M8)-1),""))-(IFERROR(--MID(M8,FIND("-",M8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(M8,FIND("-",M8)-1),""))-(IFERROR(--MID(M8,FIND("-",M8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(M8,FIND("-",M8)-1),""))=(AU8))+2*((IFERROR(--MID(M8,FIND("-",M8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P8" s="11" t="str">
+      <c r="P8" s="11">
         <f>IF(OR($C8="",O8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O8,FIND("-",O8)-1),"")=AU8,IFERROR(--MID(O8,FIND("-",O8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(O8,FIND("-",O8)-1),""))-(IFERROR(--MID(O8,FIND("-",O8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(O8,FIND("-",O8)-1),""))-(IFERROR(--MID(O8,FIND("-",O8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(O8,FIND("-",O8)-1),""))=(AU8))+2*((IFERROR(--MID(O8,FIND("-",O8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="R8" s="11" t="str">
+      <c r="R8" s="11">
         <f>IF(OR($C8="",Q8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q8,FIND("-",Q8)-1),"")=AU8,IFERROR(--MID(Q8,FIND("-",Q8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(Q8,FIND("-",Q8)-1),""))-(IFERROR(--MID(Q8,FIND("-",Q8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(Q8,FIND("-",Q8)-1),""))-(IFERROR(--MID(Q8,FIND("-",Q8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(Q8,FIND("-",Q8)-1),""))=(AU8))+2*((IFERROR(--MID(Q8,FIND("-",Q8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T8" s="11" t="str">
+      <c r="T8" s="11">
         <f>IF(OR($C8="",S8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S8,FIND("-",S8)-1),"")=AU8,IFERROR(--MID(S8,FIND("-",S8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(S8,FIND("-",S8)-1),""))-(IFERROR(--MID(S8,FIND("-",S8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(S8,FIND("-",S8)-1),""))-(IFERROR(--MID(S8,FIND("-",S8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(S8,FIND("-",S8)-1),""))=(AU8))+2*((IFERROR(--MID(S8,FIND("-",S8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V8" s="11" t="str">
+      <c r="V8" s="11">
         <f>IF(OR($C8="",U8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U8,FIND("-",U8)-1),"")=AU8,IFERROR(--MID(U8,FIND("-",U8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(U8,FIND("-",U8)-1),""))-(IFERROR(--MID(U8,FIND("-",U8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(U8,FIND("-",U8)-1),""))-(IFERROR(--MID(U8,FIND("-",U8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(U8,FIND("-",U8)-1),""))=(AU8))+2*((IFERROR(--MID(U8,FIND("-",U8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X8" s="11" t="str">
+      <c r="X8" s="11">
         <f>IF(OR($C8="",W8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W8,FIND("-",W8)-1),"")=AU8,IFERROR(--MID(W8,FIND("-",W8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(W8,FIND("-",W8)-1),""))-(IFERROR(--MID(W8,FIND("-",W8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(W8,FIND("-",W8)-1),""))-(IFERROR(--MID(W8,FIND("-",W8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(W8,FIND("-",W8)-1),""))=(AU8))+2*((IFERROR(--MID(W8,FIND("-",W8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z8" s="11" t="str">
+      <c r="Z8" s="11">
         <f>IF(OR($C8="",Y8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y8,FIND("-",Y8)-1),"")=AU8,IFERROR(--MID(Y8,FIND("-",Y8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(Y8,FIND("-",Y8)-1),""))-(IFERROR(--MID(Y8,FIND("-",Y8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(Y8,FIND("-",Y8)-1),""))-(IFERROR(--MID(Y8,FIND("-",Y8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(Y8,FIND("-",Y8)-1),""))=(AU8))+2*((IFERROR(--MID(Y8,FIND("-",Y8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AB8" s="11" t="str">
+      <c r="AB8" s="11">
         <f>IF(OR($C8="",AA8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA8,FIND("-",AA8)-1),"")=AU8,IFERROR(--MID(AA8,FIND("-",AA8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AA8,FIND("-",AA8)-1),""))-(IFERROR(--MID(AA8,FIND("-",AA8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AA8,FIND("-",AA8)-1),""))-(IFERROR(--MID(AA8,FIND("-",AA8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AA8,FIND("-",AA8)-1),""))=(AU8))+2*((IFERROR(--MID(AA8,FIND("-",AA8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AD8" s="11" t="str">
+      <c r="AD8" s="11">
         <f>IF(OR($C8="",AC8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC8,FIND("-",AC8)-1),"")=AU8,IFERROR(--MID(AC8,FIND("-",AC8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AC8,FIND("-",AC8)-1),""))-(IFERROR(--MID(AC8,FIND("-",AC8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AC8,FIND("-",AC8)-1),""))-(IFERROR(--MID(AC8,FIND("-",AC8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AC8,FIND("-",AC8)-1),""))=(AU8))+2*((IFERROR(--MID(AC8,FIND("-",AC8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AF8" s="11" t="str">
+      <c r="AF8" s="11">
         <f>IF(OR($C8="",AE8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE8,FIND("-",AE8)-1),"")=AU8,IFERROR(--MID(AE8,FIND("-",AE8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AE8,FIND("-",AE8)-1),""))-(IFERROR(--MID(AE8,FIND("-",AE8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AE8,FIND("-",AE8)-1),""))-(IFERROR(--MID(AE8,FIND("-",AE8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AE8,FIND("-",AE8)-1),""))=(AU8))+2*((IFERROR(--MID(AE8,FIND("-",AE8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AH8" s="11" t="str">
+      <c r="AH8" s="11">
         <f>IF(OR($C8="",AG8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG8,FIND("-",AG8)-1),"")=AU8,IFERROR(--MID(AG8,FIND("-",AG8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AG8,FIND("-",AG8)-1),""))-(IFERROR(--MID(AG8,FIND("-",AG8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AG8,FIND("-",AG8)-1),""))-(IFERROR(--MID(AG8,FIND("-",AG8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AG8,FIND("-",AG8)-1),""))=(AU8))+2*((IFERROR(--MID(AG8,FIND("-",AG8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AJ8" s="11" t="str">
+      <c r="AJ8" s="11">
         <f>IF(OR($C8="",AI8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI8,FIND("-",AI8)-1),"")=AU8,IFERROR(--MID(AI8,FIND("-",AI8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AI8,FIND("-",AI8)-1),""))-(IFERROR(--MID(AI8,FIND("-",AI8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AI8,FIND("-",AI8)-1),""))-(IFERROR(--MID(AI8,FIND("-",AI8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AI8,FIND("-",AI8)-1),""))=(AU8))+2*((IFERROR(--MID(AI8,FIND("-",AI8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AL8" s="11" t="str">
+      <c r="AL8" s="11">
         <f>IF(OR($C8="",AK8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK8,FIND("-",AK8)-1),"")=AU8,IFERROR(--MID(AK8,FIND("-",AK8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AK8,FIND("-",AK8)-1),""))-(IFERROR(--MID(AK8,FIND("-",AK8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AK8,FIND("-",AK8)-1),""))-(IFERROR(--MID(AK8,FIND("-",AK8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AK8,FIND("-",AK8)-1),""))=(AU8))+2*((IFERROR(--MID(AK8,FIND("-",AK8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AN8" s="11" t="str">
+      <c r="AN8" s="11">
         <f>IF(OR($C8="",AM8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM8,FIND("-",AM8)-1),"")=AU8,IFERROR(--MID(AM8,FIND("-",AM8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AM8,FIND("-",AM8)-1),""))-(IFERROR(--MID(AM8,FIND("-",AM8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AM8,FIND("-",AM8)-1),""))-(IFERROR(--MID(AM8,FIND("-",AM8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AM8,FIND("-",AM8)-1),""))=(AU8))+2*((IFERROR(--MID(AM8,FIND("-",AM8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP8" s="11" t="str">
+      <c r="AP8" s="11">
         <f>IF(OR($C8="",AO8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO8,FIND("-",AO8)-1),"")=AU8,IFERROR(--MID(AO8,FIND("-",AO8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AO8,FIND("-",AO8)-1),""))-(IFERROR(--MID(AO8,FIND("-",AO8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AO8,FIND("-",AO8)-1),""))-(IFERROR(--MID(AO8,FIND("-",AO8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AO8,FIND("-",AO8)-1),""))=(AU8))+2*((IFERROR(--MID(AO8,FIND("-",AO8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR8" s="11" t="str">
+      <c r="AR8" s="11">
         <f>IF(OR($C8="",AQ8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ8,FIND("-",AQ8)-1),"")=AU8,IFERROR(--MID(AQ8,FIND("-",AQ8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AQ8,FIND("-",AQ8)-1),""))-(IFERROR(--MID(AQ8,FIND("-",AQ8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AQ8,FIND("-",AQ8)-1),""))-(IFERROR(--MID(AQ8,FIND("-",AQ8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AQ8,FIND("-",AQ8)-1),""))=(AU8))+2*((IFERROR(--MID(AQ8,FIND("-",AQ8)+1,99),""))=(AV8))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT8" s="11" t="str">
+      <c r="AT8" s="11">
         <f>IF(OR($C8="",AS8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS8,FIND("-",AS8)-1),"")=AU8,IFERROR(--MID(AS8,FIND("-",AS8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AS8,FIND("-",AS8)-1),""))-(IFERROR(--MID(AS8,FIND("-",AS8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AS8,FIND("-",AS8)-1),""))-(IFERROR(--MID(AS8,FIND("-",AS8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AS8,FIND("-",AS8)-1),""))=(AU8))+2*((IFERROR(--MID(AS8,FIND("-",AS8)+1,99),""))=(AV8))),""))</f>
-        <v/>
-      </c>
-      <c r="AU8" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AU8" s="11">
         <f>IF($C8="","",IFERROR(--LEFT($C8,FIND("-",$C8)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AV8" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="11">
         <f>IF($C8="","",IFERROR(--MID($C8,FIND("-",$C8)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:48" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -2726,7 +2728,7 @@
       <c r="AV10" s="12"/>
     </row>
     <row r="11" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="37" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="34"/>
@@ -3165,7 +3167,7 @@
       <c r="AV14" s="12"/>
     </row>
     <row r="15" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="37" t="s">
         <v>58</v>
       </c>
       <c r="B15" s="34"/>
@@ -4105,7 +4107,7 @@
       <c r="AV21" s="12"/>
     </row>
     <row r="22" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="37" t="s">
         <v>75</v>
       </c>
       <c r="B22" s="34"/>
@@ -4878,7 +4880,7 @@
       <c r="AV27" s="12"/>
     </row>
     <row r="28" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="37" t="s">
         <v>84</v>
       </c>
       <c r="B28" s="34"/>
@@ -5484,7 +5486,7 @@
       <c r="AV32" s="12"/>
     </row>
     <row r="33" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="37" t="s">
         <v>92</v>
       </c>
       <c r="B33" s="34"/>
@@ -6424,7 +6426,7 @@
       <c r="AV39" s="12"/>
     </row>
     <row r="40" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="33" t="s">
+      <c r="A40" s="37" t="s">
         <v>103</v>
       </c>
       <c r="B40" s="34"/>
@@ -7197,7 +7199,7 @@
       <c r="AV45" s="12"/>
     </row>
     <row r="46" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="33" t="s">
+      <c r="A46" s="37" t="s">
         <v>110</v>
       </c>
       <c r="B46" s="34"/>
@@ -7803,7 +7805,7 @@
       <c r="AV50" s="12"/>
     </row>
     <row r="51" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="33" t="s">
+      <c r="A51" s="37" t="s">
         <v>111</v>
       </c>
       <c r="B51" s="34"/>
@@ -8743,7 +8745,7 @@
       <c r="AV57" s="12"/>
     </row>
     <row r="58" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="33" t="s">
+      <c r="A58" s="37" t="s">
         <v>114</v>
       </c>
       <c r="B58" s="34"/>
@@ -9516,7 +9518,7 @@
       <c r="AV63" s="12"/>
     </row>
     <row r="64" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="33" t="s">
+      <c r="A64" s="37" t="s">
         <v>116</v>
       </c>
       <c r="B64" s="34"/>
@@ -10289,7 +10291,7 @@
       <c r="AV69" s="12"/>
     </row>
     <row r="70" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="33" t="s">
+      <c r="A70" s="37" t="s">
         <v>117</v>
       </c>
       <c r="B70" s="34"/>
@@ -11062,7 +11064,7 @@
       <c r="AV75" s="12"/>
     </row>
     <row r="76" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="33" t="s">
+      <c r="A76" s="37" t="s">
         <v>118</v>
       </c>
       <c r="B76" s="34"/>
@@ -11835,7 +11837,7 @@
       <c r="AV81" s="12"/>
     </row>
     <row r="82" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="33" t="s">
+      <c r="A82" s="37" t="s">
         <v>119</v>
       </c>
       <c r="B82" s="34"/>
@@ -12942,7 +12944,7 @@
       <c r="AV89" s="12"/>
     </row>
     <row r="90" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="33" t="s">
+      <c r="A90" s="37" t="s">
         <v>122</v>
       </c>
       <c r="B90" s="34"/>
@@ -14049,7 +14051,7 @@
       <c r="AV97" s="12"/>
     </row>
     <row r="98" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="33" t="s">
+      <c r="A98" s="37" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="34"/>
@@ -15156,7 +15158,7 @@
       <c r="AV105" s="12"/>
     </row>
     <row r="106" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="33" t="s">
+      <c r="A106" s="37" t="s">
         <v>126</v>
       </c>
       <c r="B106" s="34"/>
@@ -15982,7 +15984,7 @@
       <c r="AV112" s="12"/>
     </row>
     <row r="113" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="42" t="s">
+      <c r="A113" s="33" t="s">
         <v>128</v>
       </c>
       <c r="B113" s="34"/>
@@ -16034,7 +16036,7 @@
       <c r="AV113" s="7"/>
     </row>
     <row r="114" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="33" t="s">
+      <c r="A114" s="37" t="s">
         <v>126</v>
       </c>
       <c r="B114" s="34"/>
@@ -16264,7 +16266,7 @@
       <c r="AV116" s="12"/>
     </row>
     <row r="117" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="33" t="s">
+      <c r="A117" s="37" t="s">
         <v>131</v>
       </c>
       <c r="B117" s="34"/>
@@ -16619,7 +16621,7 @@
       <c r="AV120" s="12"/>
     </row>
     <row r="121" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="33" t="s">
+      <c r="A121" s="37" t="s">
         <v>136</v>
       </c>
       <c r="B121" s="34"/>
@@ -17099,7 +17101,7 @@
       <c r="AV125" s="12"/>
     </row>
     <row r="126" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="33" t="s">
+      <c r="A126" s="37" t="s">
         <v>143</v>
       </c>
       <c r="B126" s="34"/>
@@ -17579,7 +17581,7 @@
       <c r="AV130" s="12"/>
     </row>
     <row r="131" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="33" t="s">
+      <c r="A131" s="37" t="s">
         <v>150</v>
       </c>
       <c r="B131" s="34"/>
@@ -17934,7 +17936,7 @@
       <c r="AV134" s="12"/>
     </row>
     <row r="135" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="33" t="s">
+      <c r="A135" s="37" t="s">
         <v>155</v>
       </c>
       <c r="B135" s="34"/>
@@ -18414,7 +18416,7 @@
       <c r="AV139" s="12"/>
     </row>
     <row r="140" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="33" t="s">
+      <c r="A140" s="37" t="s">
         <v>162</v>
       </c>
       <c r="B140" s="34"/>
@@ -18822,7 +18824,7 @@
       <c r="AV144" s="12"/>
     </row>
     <row r="145" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="42" t="s">
+      <c r="A145" s="33" t="s">
         <v>167</v>
       </c>
       <c r="B145" s="34"/>
@@ -18874,7 +18876,7 @@
       <c r="AV145" s="7"/>
     </row>
     <row r="146" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="33" t="s">
+      <c r="A146" s="37" t="s">
         <v>162</v>
       </c>
       <c r="B146" s="34"/>
@@ -19229,7 +19231,7 @@
       <c r="AV149" s="12"/>
     </row>
     <row r="150" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="33" t="s">
+      <c r="A150" s="37" t="s">
         <v>172</v>
       </c>
       <c r="B150" s="34"/>
@@ -19459,7 +19461,7 @@
       <c r="AV152" s="12"/>
     </row>
     <row r="153" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="33" t="s">
+      <c r="A153" s="37" t="s">
         <v>175</v>
       </c>
       <c r="B153" s="34"/>
@@ -19814,7 +19816,7 @@
       <c r="AV156" s="12"/>
     </row>
     <row r="157" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="33" t="s">
+      <c r="A157" s="37" t="s">
         <v>180</v>
       </c>
       <c r="B157" s="34"/>
@@ -20347,7 +20349,7 @@
       <c r="AV162" s="12"/>
     </row>
     <row r="163" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="42" t="s">
+      <c r="A163" s="33" t="s">
         <v>187</v>
       </c>
       <c r="B163" s="34"/>
@@ -20399,7 +20401,7 @@
       <c r="AV163" s="7"/>
     </row>
     <row r="164" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="33" t="s">
+      <c r="A164" s="37" t="s">
         <v>188</v>
       </c>
       <c r="B164" s="34"/>
@@ -20629,7 +20631,7 @@
       <c r="AV166" s="12"/>
     </row>
     <row r="167" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="33" t="s">
+      <c r="A167" s="37" t="s">
         <v>191</v>
       </c>
       <c r="B167" s="34"/>
@@ -20859,7 +20861,7 @@
       <c r="AV169" s="12"/>
     </row>
     <row r="170" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="33" t="s">
+      <c r="A170" s="37" t="s">
         <v>194</v>
       </c>
       <c r="B170" s="34"/>
@@ -21089,7 +21091,7 @@
       <c r="AV172" s="12"/>
     </row>
     <row r="173" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="33" t="s">
+      <c r="A173" s="37" t="s">
         <v>197</v>
       </c>
       <c r="B173" s="34"/>
@@ -21372,7 +21374,7 @@
       <c r="AV176" s="12"/>
     </row>
     <row r="177" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="42" t="s">
+      <c r="A177" s="33" t="s">
         <v>200</v>
       </c>
       <c r="B177" s="34"/>
@@ -21424,7 +21426,7 @@
       <c r="AV177" s="7"/>
     </row>
     <row r="178" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="33" t="s">
+      <c r="A178" s="37" t="s">
         <v>201</v>
       </c>
       <c r="B178" s="34"/>
@@ -21654,7 +21656,7 @@
       <c r="AV180" s="12"/>
     </row>
     <row r="181" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="33" t="s">
+      <c r="A181" s="37" t="s">
         <v>204</v>
       </c>
       <c r="B181" s="34"/>
@@ -21937,7 +21939,7 @@
       <c r="AV184" s="12"/>
     </row>
     <row r="185" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="42" t="s">
+      <c r="A185" s="33" t="s">
         <v>207</v>
       </c>
       <c r="B185" s="34"/>
@@ -21989,7 +21991,7 @@
       <c r="AV185" s="7"/>
     </row>
     <row r="186" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="33" t="s">
+      <c r="A186" s="37" t="s">
         <v>208</v>
       </c>
       <c r="B186" s="34"/>
@@ -22272,7 +22274,7 @@
       <c r="AV189" s="12"/>
     </row>
     <row r="190" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="42" t="s">
+      <c r="A190" s="33" t="s">
         <v>211</v>
       </c>
       <c r="B190" s="34"/>
@@ -22324,7 +22326,7 @@
       <c r="AV190" s="7"/>
     </row>
     <row r="191" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="33" t="s">
+      <c r="A191" s="37" t="s">
         <v>212</v>
       </c>
       <c r="B191" s="34"/>
@@ -22608,6 +22610,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="A51:AT51"/>
+    <mergeCell ref="A58:AT58"/>
+    <mergeCell ref="A64:AT64"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A7:AT7"/>
+    <mergeCell ref="A46:AT46"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AT11"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="A28:AT28"/>
+    <mergeCell ref="A178:AT178"/>
+    <mergeCell ref="A70:AT70"/>
+    <mergeCell ref="A153:AT153"/>
+    <mergeCell ref="A177:AT177"/>
+    <mergeCell ref="A113:AT113"/>
+    <mergeCell ref="A117:AT117"/>
+    <mergeCell ref="A146:AT146"/>
+    <mergeCell ref="A76:AT76"/>
+    <mergeCell ref="A164:AT164"/>
+    <mergeCell ref="A106:AT106"/>
+    <mergeCell ref="A150:AT150"/>
+    <mergeCell ref="A90:AT90"/>
+    <mergeCell ref="A98:AT98"/>
+    <mergeCell ref="A121:AT121"/>
+    <mergeCell ref="A135:AT135"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A22:AT22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A33:AT33"/>
+    <mergeCell ref="A15:AT15"/>
+    <mergeCell ref="A191:AT191"/>
+    <mergeCell ref="A145:AT145"/>
+    <mergeCell ref="A163:AT163"/>
+    <mergeCell ref="A173:AT173"/>
+    <mergeCell ref="A114:AT114"/>
+    <mergeCell ref="A186:AT186"/>
+    <mergeCell ref="A167:AT167"/>
+    <mergeCell ref="A157:AT157"/>
+    <mergeCell ref="A181:AT181"/>
+    <mergeCell ref="A126:AT126"/>
+    <mergeCell ref="A140:AT140"/>
+    <mergeCell ref="A131:AT131"/>
+    <mergeCell ref="A190:AT190"/>
+    <mergeCell ref="A170:AT170"/>
     <mergeCell ref="A185:AT185"/>
     <mergeCell ref="A40:AT40"/>
     <mergeCell ref="A82:AT82"/>
@@ -22624,59 +22679,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AT33"/>
-    <mergeCell ref="A15:AT15"/>
-    <mergeCell ref="A191:AT191"/>
-    <mergeCell ref="A145:AT145"/>
-    <mergeCell ref="A163:AT163"/>
-    <mergeCell ref="A173:AT173"/>
-    <mergeCell ref="A114:AT114"/>
-    <mergeCell ref="A186:AT186"/>
-    <mergeCell ref="A167:AT167"/>
-    <mergeCell ref="A157:AT157"/>
-    <mergeCell ref="A181:AT181"/>
-    <mergeCell ref="A126:AT126"/>
-    <mergeCell ref="A140:AT140"/>
-    <mergeCell ref="A131:AT131"/>
-    <mergeCell ref="A190:AT190"/>
-    <mergeCell ref="A170:AT170"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A22:AT22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A178:AT178"/>
-    <mergeCell ref="A70:AT70"/>
-    <mergeCell ref="A153:AT153"/>
-    <mergeCell ref="A177:AT177"/>
-    <mergeCell ref="A113:AT113"/>
-    <mergeCell ref="A117:AT117"/>
-    <mergeCell ref="A146:AT146"/>
-    <mergeCell ref="A76:AT76"/>
-    <mergeCell ref="A164:AT164"/>
-    <mergeCell ref="A106:AT106"/>
-    <mergeCell ref="A150:AT150"/>
-    <mergeCell ref="A90:AT90"/>
-    <mergeCell ref="A98:AT98"/>
-    <mergeCell ref="A121:AT121"/>
-    <mergeCell ref="A135:AT135"/>
-    <mergeCell ref="A51:AT51"/>
-    <mergeCell ref="A58:AT58"/>
-    <mergeCell ref="A64:AT64"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A7:AT7"/>
-    <mergeCell ref="A46:AT46"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AT11"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="A28:AT28"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25276,16 +25278,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -25297,6 +25289,16 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -25346,7 +25348,7 @@
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <f t="shared" ref="A3:A23" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="str">
         <f>Wedstrijden_beheer!O1</f>
@@ -25368,7 +25370,7 @@
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>Wedstrijden_beheer!AK1</f>
@@ -25390,7 +25392,7 @@
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="str">
         <f>Wedstrijden_beheer!U1</f>
@@ -25412,7 +25414,7 @@
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="str">
         <f>Wedstrijden_beheer!W1</f>
@@ -25434,7 +25436,7 @@
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="str">
         <f>Wedstrijden_beheer!S1</f>
@@ -25456,7 +25458,7 @@
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="str">
         <f>Wedstrijden_beheer!AG1</f>
@@ -25478,7 +25480,7 @@
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -25486,7 +25488,7 @@
       </c>
       <c r="C9" s="11">
         <f>SUM(Wedstrijden_beheer!AT3:'Wedstrijden_beheer'!AT194)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D9" s="11">
         <f>Bonus_beheer!AS17</f>
@@ -25494,13 +25496,13 @@
       </c>
       <c r="E9" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>Wedstrijden_beheer!E1</f>
@@ -25522,7 +25524,7 @@
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>Wedstrijden_beheer!AO1</f>
@@ -25544,7 +25546,7 @@
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1" t="str">
         <f>Wedstrijden_beheer!K1</f>
@@ -25566,7 +25568,7 @@
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -25574,7 +25576,7 @@
       </c>
       <c r="C13" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -25582,13 +25584,13 @@
       </c>
       <c r="E13" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B14" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -25596,7 +25598,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -25604,13 +25606,13 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
@@ -25618,7 +25620,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!AT4:'Wedstrijden_beheer'!AT195)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!AS18</f>
@@ -25626,13 +25628,13 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B16" s="1" t="str">
         <f>Wedstrijden_beheer!Y1</f>
@@ -25654,7 +25656,7 @@
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="str">
         <f>Wedstrijden_beheer!AA1</f>
@@ -25676,7 +25678,7 @@
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!M1</f>
@@ -25698,7 +25700,7 @@
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>Wedstrijden_beheer!AC1</f>
@@ -25720,7 +25722,7 @@
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="str">
         <f>Wedstrijden_beheer!AE1</f>
@@ -25742,7 +25744,7 @@
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!G1</f>
@@ -25750,7 +25752,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!G17</f>
@@ -25758,13 +25760,13 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
@@ -25772,7 +25774,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!I17</f>
@@ -25780,13 +25782,13 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -25794,7 +25796,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -25802,7 +25804,7 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -26163,6 +26165,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -26357,27 +26379,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26394,23 +26415,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="956" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{879FD0C0-2BF2-473B-BD9F-82F15C73270B}"/>
+  <xr:revisionPtr revIDLastSave="958" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18F2ECEE-2AA4-4ABE-93BB-F6849C20AFD9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="327">
   <si>
     <t>Tijd</t>
   </si>
@@ -1327,33 +1327,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1719,99 +1719,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="38" t="s">
+      <c r="F1" s="40"/>
+      <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="36"/>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="37" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="36"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="37" t="s">
         <v>7</v>
       </c>
       <c r="L1" s="36"/>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="37" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="36"/>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="37" t="s">
         <v>9</v>
       </c>
       <c r="P1" s="36"/>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="37" t="s">
         <v>10</v>
       </c>
       <c r="R1" s="36"/>
-      <c r="S1" s="38" t="s">
+      <c r="S1" s="37" t="s">
         <v>11</v>
       </c>
       <c r="T1" s="36"/>
-      <c r="U1" s="38" t="s">
+      <c r="U1" s="37" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="36"/>
-      <c r="W1" s="38" t="s">
+      <c r="W1" s="37" t="s">
         <v>13</v>
       </c>
       <c r="X1" s="36"/>
-      <c r="Y1" s="38" t="s">
+      <c r="Y1" s="37" t="s">
         <v>14</v>
       </c>
       <c r="Z1" s="36"/>
-      <c r="AA1" s="38" t="s">
+      <c r="AA1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="AB1" s="36"/>
-      <c r="AC1" s="38" t="s">
+      <c r="AC1" s="37" t="s">
         <v>16</v>
       </c>
       <c r="AD1" s="36"/>
-      <c r="AE1" s="38" t="s">
+      <c r="AE1" s="37" t="s">
         <v>17</v>
       </c>
       <c r="AF1" s="36"/>
-      <c r="AG1" s="38" t="s">
+      <c r="AG1" s="37" t="s">
         <v>18</v>
       </c>
       <c r="AH1" s="36"/>
-      <c r="AI1" s="38" t="s">
+      <c r="AI1" s="37" t="s">
         <v>19</v>
       </c>
       <c r="AJ1" s="36"/>
-      <c r="AK1" s="38" t="s">
+      <c r="AK1" s="37" t="s">
         <v>20</v>
       </c>
       <c r="AL1" s="36"/>
-      <c r="AM1" s="38" t="s">
+      <c r="AM1" s="37" t="s">
         <v>21</v>
       </c>
       <c r="AN1" s="36"/>
-      <c r="AO1" s="38" t="s">
+      <c r="AO1" s="37" t="s">
         <v>22</v>
       </c>
       <c r="AP1" s="36"/>
-      <c r="AQ1" s="38" t="s">
+      <c r="AQ1" s="37" t="s">
         <v>23</v>
       </c>
       <c r="AR1" s="36"/>
-      <c r="AS1" s="38" t="s">
+      <c r="AS1" s="37" t="s">
         <v>24</v>
       </c>
       <c r="AT1" s="36"/>
@@ -1823,10 +1823,10 @@
       </c>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.35">
-      <c r="A2" s="43"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="42"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
       </c>
@@ -1961,59 +1961,59 @@
       </c>
     </row>
     <row r="3" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="44"/>
       <c r="AU3" s="7"/>
       <c r="AV3" s="7"/>
     </row>
     <row r="4" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="34"/>
@@ -2071,166 +2071,164 @@
       <c r="B5" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="C5" s="10"/>
       <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="11" t="str">
         <f>IF(OR($C5="",E5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E5,FIND("-",E5)-1),"")=AU5,IFERROR(--MID(E5,FIND("-",E5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(E5,FIND("-",E5)-1),""))-(IFERROR(--MID(E5,FIND("-",E5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(E5,FIND("-",E5)-1),""))-(IFERROR(--MID(E5,FIND("-",E5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(E5,FIND("-",E5)-1),""))=(AU5))+2*((IFERROR(--MID(E5,FIND("-",E5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="G5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="11" t="str">
         <f>IF(OR($C5="",G5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G5,FIND("-",G5)-1),"")=AU5,IFERROR(--MID(G5,FIND("-",G5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(G5,FIND("-",G5)-1),""))-(IFERROR(--MID(G5,FIND("-",G5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(G5,FIND("-",G5)-1),""))-(IFERROR(--MID(G5,FIND("-",G5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(G5,FIND("-",G5)-1),""))=(AU5))+2*((IFERROR(--MID(G5,FIND("-",G5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="I5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="11" t="str">
         <f>IF(OR($C5="",I5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I5,FIND("-",I5)-1),"")=AU5,IFERROR(--MID(I5,FIND("-",I5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(I5,FIND("-",I5)-1),""))-(IFERROR(--MID(I5,FIND("-",I5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(I5,FIND("-",I5)-1),""))-(IFERROR(--MID(I5,FIND("-",I5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(I5,FIND("-",I5)-1),""))=(AU5))+2*((IFERROR(--MID(I5,FIND("-",I5)+1,99),""))=(AV5))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="11" t="str">
         <f>IF(OR($C5="",K5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K5,FIND("-",K5)-1),"")=AU5,IFERROR(--MID(K5,FIND("-",K5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(K5,FIND("-",K5)-1),""))-(IFERROR(--MID(K5,FIND("-",K5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(K5,FIND("-",K5)-1),""))-(IFERROR(--MID(K5,FIND("-",K5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(K5,FIND("-",K5)-1),""))=(AU5))+2*((IFERROR(--MID(K5,FIND("-",K5)+1,99),""))=(AV5))),""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="M5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="11" t="str">
         <f>IF(OR($C5="",M5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M5,FIND("-",M5)-1),"")=AU5,IFERROR(--MID(M5,FIND("-",M5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(M5,FIND("-",M5)-1),""))-(IFERROR(--MID(M5,FIND("-",M5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(M5,FIND("-",M5)-1),""))-(IFERROR(--MID(M5,FIND("-",M5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(M5,FIND("-",M5)-1),""))=(AU5))+2*((IFERROR(--MID(M5,FIND("-",M5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="O5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="11" t="str">
         <f>IF(OR($C5="",O5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O5,FIND("-",O5)-1),"")=AU5,IFERROR(--MID(O5,FIND("-",O5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(O5,FIND("-",O5)-1),""))-(IFERROR(--MID(O5,FIND("-",O5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(O5,FIND("-",O5)-1),""))-(IFERROR(--MID(O5,FIND("-",O5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(O5,FIND("-",O5)-1),""))=(AU5))+2*((IFERROR(--MID(O5,FIND("-",O5)+1,99),""))=(AV5))),""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="Q5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="11" t="str">
         <f>IF(OR($C5="",Q5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q5,FIND("-",Q5)-1),"")=AU5,IFERROR(--MID(Q5,FIND("-",Q5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(Q5,FIND("-",Q5)-1),""))-(IFERROR(--MID(Q5,FIND("-",Q5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(Q5,FIND("-",Q5)-1),""))-(IFERROR(--MID(Q5,FIND("-",Q5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(Q5,FIND("-",Q5)-1),""))=(AU5))+2*((IFERROR(--MID(Q5,FIND("-",Q5)+1,99),""))=(AV5))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="S5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="11" t="str">
         <f>IF(OR($C5="",S5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S5,FIND("-",S5)-1),"")=AU5,IFERROR(--MID(S5,FIND("-",S5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(S5,FIND("-",S5)-1),""))-(IFERROR(--MID(S5,FIND("-",S5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(S5,FIND("-",S5)-1),""))-(IFERROR(--MID(S5,FIND("-",S5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(S5,FIND("-",S5)-1),""))=(AU5))+2*((IFERROR(--MID(S5,FIND("-",S5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="U5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="11" t="str">
         <f>IF(OR($C5="",U5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U5,FIND("-",U5)-1),"")=AU5,IFERROR(--MID(U5,FIND("-",U5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(U5,FIND("-",U5)-1),""))-(IFERROR(--MID(U5,FIND("-",U5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(U5,FIND("-",U5)-1),""))-(IFERROR(--MID(U5,FIND("-",U5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(U5,FIND("-",U5)-1),""))=(AU5))+2*((IFERROR(--MID(U5,FIND("-",U5)+1,99),""))=(AV5))),""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="W5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X5" s="11">
+      <c r="X5" s="11" t="str">
         <f>IF(OR($C5="",W5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W5,FIND("-",W5)-1),"")=AU5,IFERROR(--MID(W5,FIND("-",W5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(W5,FIND("-",W5)-1),""))-(IFERROR(--MID(W5,FIND("-",W5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(W5,FIND("-",W5)-1),""))-(IFERROR(--MID(W5,FIND("-",W5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(W5,FIND("-",W5)-1),""))=(AU5))+2*((IFERROR(--MID(W5,FIND("-",W5)+1,99),""))=(AV5))),""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="Y5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z5" s="11">
+      <c r="Z5" s="11" t="str">
         <f>IF(OR($C5="",Y5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y5,FIND("-",Y5)-1),"")=AU5,IFERROR(--MID(Y5,FIND("-",Y5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(Y5,FIND("-",Y5)-1),""))-(IFERROR(--MID(Y5,FIND("-",Y5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(Y5,FIND("-",Y5)-1),""))-(IFERROR(--MID(Y5,FIND("-",Y5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(Y5,FIND("-",Y5)-1),""))=(AU5))+2*((IFERROR(--MID(Y5,FIND("-",Y5)+1,99),""))=(AV5))),""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AA5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AB5" s="11" t="str">
         <f>IF(OR($C5="",AA5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA5,FIND("-",AA5)-1),"")=AU5,IFERROR(--MID(AA5,FIND("-",AA5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AA5,FIND("-",AA5)-1),""))-(IFERROR(--MID(AA5,FIND("-",AA5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AA5,FIND("-",AA5)-1),""))-(IFERROR(--MID(AA5,FIND("-",AA5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AA5,FIND("-",AA5)-1),""))=(AU5))+2*((IFERROR(--MID(AA5,FIND("-",AA5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="AC5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AD5" s="11" t="str">
         <f>IF(OR($C5="",AC5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC5,FIND("-",AC5)-1),"")=AU5,IFERROR(--MID(AC5,FIND("-",AC5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AC5,FIND("-",AC5)-1),""))-(IFERROR(--MID(AC5,FIND("-",AC5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AC5,FIND("-",AC5)-1),""))-(IFERROR(--MID(AC5,FIND("-",AC5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AC5,FIND("-",AC5)-1),""))=(AU5))+2*((IFERROR(--MID(AC5,FIND("-",AC5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="AE5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF5" s="11">
+      <c r="AF5" s="11" t="str">
         <f>IF(OR($C5="",AE5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE5,FIND("-",AE5)-1),"")=AU5,IFERROR(--MID(AE5,FIND("-",AE5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AE5,FIND("-",AE5)-1),""))-(IFERROR(--MID(AE5,FIND("-",AE5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AE5,FIND("-",AE5)-1),""))-(IFERROR(--MID(AE5,FIND("-",AE5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AE5,FIND("-",AE5)-1),""))=(AU5))+2*((IFERROR(--MID(AE5,FIND("-",AE5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="AG5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH5" s="11">
+      <c r="AH5" s="11" t="str">
         <f>IF(OR($C5="",AG5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG5,FIND("-",AG5)-1),"")=AU5,IFERROR(--MID(AG5,FIND("-",AG5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AG5,FIND("-",AG5)-1),""))-(IFERROR(--MID(AG5,FIND("-",AG5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AG5,FIND("-",AG5)-1),""))-(IFERROR(--MID(AG5,FIND("-",AG5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AG5,FIND("-",AG5)-1),""))=(AU5))+2*((IFERROR(--MID(AG5,FIND("-",AG5)+1,99),""))=(AV5))),""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AI5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ5" s="11">
+      <c r="AJ5" s="11" t="str">
         <f>IF(OR($C5="",AI5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI5,FIND("-",AI5)-1),"")=AU5,IFERROR(--MID(AI5,FIND("-",AI5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AI5,FIND("-",AI5)-1),""))-(IFERROR(--MID(AI5,FIND("-",AI5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AI5,FIND("-",AI5)-1),""))-(IFERROR(--MID(AI5,FIND("-",AI5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AI5,FIND("-",AI5)-1),""))=(AU5))+2*((IFERROR(--MID(AI5,FIND("-",AI5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="AK5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL5" s="11">
+      <c r="AL5" s="11" t="str">
         <f>IF(OR($C5="",AK5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK5,FIND("-",AK5)-1),"")=AU5,IFERROR(--MID(AK5,FIND("-",AK5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AK5,FIND("-",AK5)-1),""))-(IFERROR(--MID(AK5,FIND("-",AK5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AK5,FIND("-",AK5)-1),""))-(IFERROR(--MID(AK5,FIND("-",AK5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AK5,FIND("-",AK5)-1),""))=(AU5))+2*((IFERROR(--MID(AK5,FIND("-",AK5)+1,99),""))=(AV5))),""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AM5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AN5" s="11">
+      <c r="AN5" s="11" t="str">
         <f>IF(OR($C5="",AM5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM5,FIND("-",AM5)-1),"")=AU5,IFERROR(--MID(AM5,FIND("-",AM5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AM5,FIND("-",AM5)-1),""))-(IFERROR(--MID(AM5,FIND("-",AM5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AM5,FIND("-",AM5)-1),""))-(IFERROR(--MID(AM5,FIND("-",AM5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AM5,FIND("-",AM5)-1),""))=(AU5))+2*((IFERROR(--MID(AM5,FIND("-",AM5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="AO5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AP5" s="11">
+      <c r="AP5" s="11" t="str">
         <f>IF(OR($C5="",AO5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO5,FIND("-",AO5)-1),"")=AU5,IFERROR(--MID(AO5,FIND("-",AO5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AO5,FIND("-",AO5)-1),""))-(IFERROR(--MID(AO5,FIND("-",AO5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AO5,FIND("-",AO5)-1),""))-(IFERROR(--MID(AO5,FIND("-",AO5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AO5,FIND("-",AO5)-1),""))=(AU5))+2*((IFERROR(--MID(AO5,FIND("-",AO5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="AQ5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AR5" s="11">
+      <c r="AR5" s="11" t="str">
         <f>IF(OR($C5="",AQ5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ5,FIND("-",AQ5)-1),"")=AU5,IFERROR(--MID(AQ5,FIND("-",AQ5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AQ5,FIND("-",AQ5)-1),""))-(IFERROR(--MID(AQ5,FIND("-",AQ5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AQ5,FIND("-",AQ5)-1),""))-(IFERROR(--MID(AQ5,FIND("-",AQ5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AQ5,FIND("-",AQ5)-1),""))=(AU5))+2*((IFERROR(--MID(AQ5,FIND("-",AQ5)+1,99),""))=(AV5))),""))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AS5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT5" s="11">
+      <c r="AT5" s="11" t="str">
         <f>IF(OR($C5="",AS5=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS5,FIND("-",AS5)-1),"")=AU5,IFERROR(--MID(AS5,FIND("-",AS5)+1,99),"")=AV5),10,5*(SIGN((IFERROR(--LEFT(AS5,FIND("-",AS5)-1),""))-(IFERROR(--MID(AS5,FIND("-",AS5)+1,99),"")))=SIGN((AU5)-(AV5)))+2*(((IFERROR(--LEFT(AS5,FIND("-",AS5)-1),""))-(IFERROR(--MID(AS5,FIND("-",AS5)+1,99),"")))=((AU5)-(AV5)))+2*((IFERROR(--LEFT(AS5,FIND("-",AS5)-1),""))=(AU5))+2*((IFERROR(--MID(AS5,FIND("-",AS5)+1,99),""))=(AV5))),""))</f>
-        <v>7</v>
-      </c>
-      <c r="AU5" s="11">
+        <v/>
+      </c>
+      <c r="AU5" s="11" t="str">
         <f>IF($C5="","",IFERROR(--LEFT($C5,FIND("-",$C5)-1),""))</f>
-        <v>2</v>
-      </c>
-      <c r="AV5" s="11">
+        <v/>
+      </c>
+      <c r="AV5" s="11" t="str">
         <f>IF($C5="","",IFERROR(--MID($C5,FIND("-",$C5)+1,99),""))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="6" spans="1:48" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -2287,7 +2285,7 @@
       <c r="AV6" s="12"/>
     </row>
     <row r="7" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="34"/>
@@ -2345,166 +2343,164 @@
       <c r="B8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="C8" s="10"/>
       <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="11" t="str">
         <f>IF(OR($C8="",E8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E8,FIND("-",E8)-1),"")=AU8,IFERROR(--MID(E8,FIND("-",E8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(E8,FIND("-",E8)-1),""))-(IFERROR(--MID(E8,FIND("-",E8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(E8,FIND("-",E8)-1),""))-(IFERROR(--MID(E8,FIND("-",E8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(E8,FIND("-",E8)-1),""))=(AU8))+2*((IFERROR(--MID(E8,FIND("-",E8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="11" t="str">
         <f>IF(OR($C8="",G8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G8,FIND("-",G8)-1),"")=AU8,IFERROR(--MID(G8,FIND("-",G8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(G8,FIND("-",G8)-1),""))-(IFERROR(--MID(G8,FIND("-",G8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(G8,FIND("-",G8)-1),""))-(IFERROR(--MID(G8,FIND("-",G8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(G8,FIND("-",G8)-1),""))=(AU8))+2*((IFERROR(--MID(G8,FIND("-",G8)+1,99),""))=(AV8))),""))</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="I8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="11" t="str">
         <f>IF(OR($C8="",I8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I8,FIND("-",I8)-1),"")=AU8,IFERROR(--MID(I8,FIND("-",I8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(I8,FIND("-",I8)-1),""))-(IFERROR(--MID(I8,FIND("-",I8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(I8,FIND("-",I8)-1),""))-(IFERROR(--MID(I8,FIND("-",I8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(I8,FIND("-",I8)-1),""))=(AU8))+2*((IFERROR(--MID(I8,FIND("-",I8)+1,99),""))=(AV8))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="K8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="11" t="str">
         <f>IF(OR($C8="",K8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K8,FIND("-",K8)-1),"")=AU8,IFERROR(--MID(K8,FIND("-",K8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(K8,FIND("-",K8)-1),""))-(IFERROR(--MID(K8,FIND("-",K8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(K8,FIND("-",K8)-1),""))-(IFERROR(--MID(K8,FIND("-",K8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(K8,FIND("-",K8)-1),""))=(AU8))+2*((IFERROR(--MID(K8,FIND("-",K8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="M8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="11" t="str">
         <f>IF(OR($C8="",M8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M8,FIND("-",M8)-1),"")=AU8,IFERROR(--MID(M8,FIND("-",M8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(M8,FIND("-",M8)-1),""))-(IFERROR(--MID(M8,FIND("-",M8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(M8,FIND("-",M8)-1),""))-(IFERROR(--MID(M8,FIND("-",M8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(M8,FIND("-",M8)-1),""))=(AU8))+2*((IFERROR(--MID(M8,FIND("-",M8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="11" t="str">
         <f>IF(OR($C8="",O8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O8,FIND("-",O8)-1),"")=AU8,IFERROR(--MID(O8,FIND("-",O8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(O8,FIND("-",O8)-1),""))-(IFERROR(--MID(O8,FIND("-",O8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(O8,FIND("-",O8)-1),""))-(IFERROR(--MID(O8,FIND("-",O8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(O8,FIND("-",O8)-1),""))=(AU8))+2*((IFERROR(--MID(O8,FIND("-",O8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="11" t="str">
         <f>IF(OR($C8="",Q8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q8,FIND("-",Q8)-1),"")=AU8,IFERROR(--MID(Q8,FIND("-",Q8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(Q8,FIND("-",Q8)-1),""))-(IFERROR(--MID(Q8,FIND("-",Q8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(Q8,FIND("-",Q8)-1),""))-(IFERROR(--MID(Q8,FIND("-",Q8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(Q8,FIND("-",Q8)-1),""))=(AU8))+2*((IFERROR(--MID(Q8,FIND("-",Q8)+1,99),""))=(AV8))),""))</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="S8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T8" s="11">
+      <c r="T8" s="11" t="str">
         <f>IF(OR($C8="",S8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S8,FIND("-",S8)-1),"")=AU8,IFERROR(--MID(S8,FIND("-",S8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(S8,FIND("-",S8)-1),""))-(IFERROR(--MID(S8,FIND("-",S8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(S8,FIND("-",S8)-1),""))-(IFERROR(--MID(S8,FIND("-",S8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(S8,FIND("-",S8)-1),""))=(AU8))+2*((IFERROR(--MID(S8,FIND("-",S8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V8" s="11">
+      <c r="V8" s="11" t="str">
         <f>IF(OR($C8="",U8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U8,FIND("-",U8)-1),"")=AU8,IFERROR(--MID(U8,FIND("-",U8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(U8,FIND("-",U8)-1),""))-(IFERROR(--MID(U8,FIND("-",U8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(U8,FIND("-",U8)-1),""))-(IFERROR(--MID(U8,FIND("-",U8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(U8,FIND("-",U8)-1),""))=(AU8))+2*((IFERROR(--MID(U8,FIND("-",U8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X8" s="11">
+      <c r="X8" s="11" t="str">
         <f>IF(OR($C8="",W8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W8,FIND("-",W8)-1),"")=AU8,IFERROR(--MID(W8,FIND("-",W8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(W8,FIND("-",W8)-1),""))-(IFERROR(--MID(W8,FIND("-",W8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(W8,FIND("-",W8)-1),""))-(IFERROR(--MID(W8,FIND("-",W8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(W8,FIND("-",W8)-1),""))=(AU8))+2*((IFERROR(--MID(W8,FIND("-",W8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z8" s="11">
+      <c r="Z8" s="11" t="str">
         <f>IF(OR($C8="",Y8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y8,FIND("-",Y8)-1),"")=AU8,IFERROR(--MID(Y8,FIND("-",Y8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(Y8,FIND("-",Y8)-1),""))-(IFERROR(--MID(Y8,FIND("-",Y8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(Y8,FIND("-",Y8)-1),""))-(IFERROR(--MID(Y8,FIND("-",Y8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(Y8,FIND("-",Y8)-1),""))=(AU8))+2*((IFERROR(--MID(Y8,FIND("-",Y8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AB8" s="11">
+      <c r="AB8" s="11" t="str">
         <f>IF(OR($C8="",AA8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA8,FIND("-",AA8)-1),"")=AU8,IFERROR(--MID(AA8,FIND("-",AA8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AA8,FIND("-",AA8)-1),""))-(IFERROR(--MID(AA8,FIND("-",AA8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AA8,FIND("-",AA8)-1),""))-(IFERROR(--MID(AA8,FIND("-",AA8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AA8,FIND("-",AA8)-1),""))=(AU8))+2*((IFERROR(--MID(AA8,FIND("-",AA8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AC8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AD8" s="11">
+      <c r="AD8" s="11" t="str">
         <f>IF(OR($C8="",AC8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC8,FIND("-",AC8)-1),"")=AU8,IFERROR(--MID(AC8,FIND("-",AC8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AC8,FIND("-",AC8)-1),""))-(IFERROR(--MID(AC8,FIND("-",AC8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AC8,FIND("-",AC8)-1),""))-(IFERROR(--MID(AC8,FIND("-",AC8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AC8,FIND("-",AC8)-1),""))=(AU8))+2*((IFERROR(--MID(AC8,FIND("-",AC8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AE8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AF8" s="11">
+      <c r="AF8" s="11" t="str">
         <f>IF(OR($C8="",AE8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE8,FIND("-",AE8)-1),"")=AU8,IFERROR(--MID(AE8,FIND("-",AE8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AE8,FIND("-",AE8)-1),""))-(IFERROR(--MID(AE8,FIND("-",AE8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AE8,FIND("-",AE8)-1),""))-(IFERROR(--MID(AE8,FIND("-",AE8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AE8,FIND("-",AE8)-1),""))=(AU8))+2*((IFERROR(--MID(AE8,FIND("-",AE8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AG8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AH8" s="11">
+      <c r="AH8" s="11" t="str">
         <f>IF(OR($C8="",AG8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG8,FIND("-",AG8)-1),"")=AU8,IFERROR(--MID(AG8,FIND("-",AG8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AG8,FIND("-",AG8)-1),""))-(IFERROR(--MID(AG8,FIND("-",AG8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AG8,FIND("-",AG8)-1),""))-(IFERROR(--MID(AG8,FIND("-",AG8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AG8,FIND("-",AG8)-1),""))=(AU8))+2*((IFERROR(--MID(AG8,FIND("-",AG8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AI8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AJ8" s="11">
+      <c r="AJ8" s="11" t="str">
         <f>IF(OR($C8="",AI8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI8,FIND("-",AI8)-1),"")=AU8,IFERROR(--MID(AI8,FIND("-",AI8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AI8,FIND("-",AI8)-1),""))-(IFERROR(--MID(AI8,FIND("-",AI8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AI8,FIND("-",AI8)-1),""))-(IFERROR(--MID(AI8,FIND("-",AI8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AI8,FIND("-",AI8)-1),""))=(AU8))+2*((IFERROR(--MID(AI8,FIND("-",AI8)+1,99),""))=(AV8))),""))</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="AK8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AL8" s="11">
+      <c r="AL8" s="11" t="str">
         <f>IF(OR($C8="",AK8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK8,FIND("-",AK8)-1),"")=AU8,IFERROR(--MID(AK8,FIND("-",AK8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AK8,FIND("-",AK8)-1),""))-(IFERROR(--MID(AK8,FIND("-",AK8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AK8,FIND("-",AK8)-1),""))-(IFERROR(--MID(AK8,FIND("-",AK8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AK8,FIND("-",AK8)-1),""))=(AU8))+2*((IFERROR(--MID(AK8,FIND("-",AK8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AM8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AN8" s="11">
+      <c r="AN8" s="11" t="str">
         <f>IF(OR($C8="",AM8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM8,FIND("-",AM8)-1),"")=AU8,IFERROR(--MID(AM8,FIND("-",AM8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AM8,FIND("-",AM8)-1),""))-(IFERROR(--MID(AM8,FIND("-",AM8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AM8,FIND("-",AM8)-1),""))-(IFERROR(--MID(AM8,FIND("-",AM8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AM8,FIND("-",AM8)-1),""))=(AU8))+2*((IFERROR(--MID(AM8,FIND("-",AM8)+1,99),""))=(AV8))),""))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="AO8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP8" s="11">
+      <c r="AP8" s="11" t="str">
         <f>IF(OR($C8="",AO8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO8,FIND("-",AO8)-1),"")=AU8,IFERROR(--MID(AO8,FIND("-",AO8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AO8,FIND("-",AO8)-1),""))-(IFERROR(--MID(AO8,FIND("-",AO8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AO8,FIND("-",AO8)-1),""))-(IFERROR(--MID(AO8,FIND("-",AO8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AO8,FIND("-",AO8)-1),""))=(AU8))+2*((IFERROR(--MID(AO8,FIND("-",AO8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AQ8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR8" s="11">
+      <c r="AR8" s="11" t="str">
         <f>IF(OR($C8="",AQ8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ8,FIND("-",AQ8)-1),"")=AU8,IFERROR(--MID(AQ8,FIND("-",AQ8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AQ8,FIND("-",AQ8)-1),""))-(IFERROR(--MID(AQ8,FIND("-",AQ8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AQ8,FIND("-",AQ8)-1),""))-(IFERROR(--MID(AQ8,FIND("-",AQ8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AQ8,FIND("-",AQ8)-1),""))=(AU8))+2*((IFERROR(--MID(AQ8,FIND("-",AQ8)+1,99),""))=(AV8))),""))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AS8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT8" s="11">
+      <c r="AT8" s="11" t="str">
         <f>IF(OR($C8="",AS8=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS8,FIND("-",AS8)-1),"")=AU8,IFERROR(--MID(AS8,FIND("-",AS8)+1,99),"")=AV8),10,5*(SIGN((IFERROR(--LEFT(AS8,FIND("-",AS8)-1),""))-(IFERROR(--MID(AS8,FIND("-",AS8)+1,99),"")))=SIGN((AU8)-(AV8)))+2*(((IFERROR(--LEFT(AS8,FIND("-",AS8)-1),""))-(IFERROR(--MID(AS8,FIND("-",AS8)+1,99),"")))=((AU8)-(AV8)))+2*((IFERROR(--LEFT(AS8,FIND("-",AS8)-1),""))=(AU8))+2*((IFERROR(--MID(AS8,FIND("-",AS8)+1,99),""))=(AV8))),""))</f>
-        <v>7</v>
-      </c>
-      <c r="AU8" s="11">
+        <v/>
+      </c>
+      <c r="AU8" s="11" t="str">
         <f>IF($C8="","",IFERROR(--LEFT($C8,FIND("-",$C8)-1),""))</f>
-        <v>2</v>
-      </c>
-      <c r="AV8" s="11">
+        <v/>
+      </c>
+      <c r="AV8" s="11" t="str">
         <f>IF($C8="","",IFERROR(--MID($C8,FIND("-",$C8)+1,99),""))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:48" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -2728,7 +2724,7 @@
       <c r="AV10" s="12"/>
     </row>
     <row r="11" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="34"/>
@@ -3167,7 +3163,7 @@
       <c r="AV14" s="12"/>
     </row>
     <row r="15" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
       <c r="B15" s="34"/>
@@ -4107,7 +4103,7 @@
       <c r="AV21" s="12"/>
     </row>
     <row r="22" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
       <c r="B22" s="34"/>
@@ -4880,7 +4876,7 @@
       <c r="AV27" s="12"/>
     </row>
     <row r="28" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
       <c r="B28" s="34"/>
@@ -5486,7 +5482,7 @@
       <c r="AV32" s="12"/>
     </row>
     <row r="33" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
       <c r="B33" s="34"/>
@@ -6426,7 +6422,7 @@
       <c r="AV39" s="12"/>
     </row>
     <row r="40" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="37" t="s">
+      <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
       <c r="B40" s="34"/>
@@ -7199,7 +7195,7 @@
       <c r="AV45" s="12"/>
     </row>
     <row r="46" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="37" t="s">
+      <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
       <c r="B46" s="34"/>
@@ -7805,7 +7801,7 @@
       <c r="AV50" s="12"/>
     </row>
     <row r="51" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="37" t="s">
+      <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
       <c r="B51" s="34"/>
@@ -8745,7 +8741,7 @@
       <c r="AV57" s="12"/>
     </row>
     <row r="58" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="37" t="s">
+      <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
       <c r="B58" s="34"/>
@@ -9518,7 +9514,7 @@
       <c r="AV63" s="12"/>
     </row>
     <row r="64" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="37" t="s">
+      <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
       <c r="B64" s="34"/>
@@ -10291,7 +10287,7 @@
       <c r="AV69" s="12"/>
     </row>
     <row r="70" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="37" t="s">
+      <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
       <c r="B70" s="34"/>
@@ -11064,7 +11060,7 @@
       <c r="AV75" s="12"/>
     </row>
     <row r="76" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="37" t="s">
+      <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
       <c r="B76" s="34"/>
@@ -11837,7 +11833,7 @@
       <c r="AV81" s="12"/>
     </row>
     <row r="82" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="37" t="s">
+      <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
       <c r="B82" s="34"/>
@@ -12944,7 +12940,7 @@
       <c r="AV89" s="12"/>
     </row>
     <row r="90" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="37" t="s">
+      <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
       <c r="B90" s="34"/>
@@ -14051,7 +14047,7 @@
       <c r="AV97" s="12"/>
     </row>
     <row r="98" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="37" t="s">
+      <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="34"/>
@@ -15158,7 +15154,7 @@
       <c r="AV105" s="12"/>
     </row>
     <row r="106" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="37" t="s">
+      <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
       <c r="B106" s="34"/>
@@ -15984,7 +15980,7 @@
       <c r="AV112" s="12"/>
     </row>
     <row r="113" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="33" t="s">
+      <c r="A113" s="42" t="s">
         <v>128</v>
       </c>
       <c r="B113" s="34"/>
@@ -16036,7 +16032,7 @@
       <c r="AV113" s="7"/>
     </row>
     <row r="114" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="37" t="s">
+      <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
       <c r="B114" s="34"/>
@@ -16266,7 +16262,7 @@
       <c r="AV116" s="12"/>
     </row>
     <row r="117" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="37" t="s">
+      <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
       <c r="B117" s="34"/>
@@ -16621,7 +16617,7 @@
       <c r="AV120" s="12"/>
     </row>
     <row r="121" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="37" t="s">
+      <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
       <c r="B121" s="34"/>
@@ -17101,7 +17097,7 @@
       <c r="AV125" s="12"/>
     </row>
     <row r="126" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="37" t="s">
+      <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
       <c r="B126" s="34"/>
@@ -17581,7 +17577,7 @@
       <c r="AV130" s="12"/>
     </row>
     <row r="131" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="37" t="s">
+      <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
       <c r="B131" s="34"/>
@@ -17936,7 +17932,7 @@
       <c r="AV134" s="12"/>
     </row>
     <row r="135" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="37" t="s">
+      <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
       <c r="B135" s="34"/>
@@ -18416,7 +18412,7 @@
       <c r="AV139" s="12"/>
     </row>
     <row r="140" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="37" t="s">
+      <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
       <c r="B140" s="34"/>
@@ -18824,7 +18820,7 @@
       <c r="AV144" s="12"/>
     </row>
     <row r="145" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="33" t="s">
+      <c r="A145" s="42" t="s">
         <v>167</v>
       </c>
       <c r="B145" s="34"/>
@@ -18876,7 +18872,7 @@
       <c r="AV145" s="7"/>
     </row>
     <row r="146" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="37" t="s">
+      <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
       <c r="B146" s="34"/>
@@ -19231,7 +19227,7 @@
       <c r="AV149" s="12"/>
     </row>
     <row r="150" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="37" t="s">
+      <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
       <c r="B150" s="34"/>
@@ -19461,7 +19457,7 @@
       <c r="AV152" s="12"/>
     </row>
     <row r="153" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="37" t="s">
+      <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
       <c r="B153" s="34"/>
@@ -19816,7 +19812,7 @@
       <c r="AV156" s="12"/>
     </row>
     <row r="157" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="37" t="s">
+      <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
       <c r="B157" s="34"/>
@@ -20349,7 +20345,7 @@
       <c r="AV162" s="12"/>
     </row>
     <row r="163" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="33" t="s">
+      <c r="A163" s="42" t="s">
         <v>187</v>
       </c>
       <c r="B163" s="34"/>
@@ -20401,7 +20397,7 @@
       <c r="AV163" s="7"/>
     </row>
     <row r="164" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="37" t="s">
+      <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
       <c r="B164" s="34"/>
@@ -20631,7 +20627,7 @@
       <c r="AV166" s="12"/>
     </row>
     <row r="167" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="37" t="s">
+      <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
       <c r="B167" s="34"/>
@@ -20861,7 +20857,7 @@
       <c r="AV169" s="12"/>
     </row>
     <row r="170" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="37" t="s">
+      <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
       <c r="B170" s="34"/>
@@ -21091,7 +21087,7 @@
       <c r="AV172" s="12"/>
     </row>
     <row r="173" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="37" t="s">
+      <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
       <c r="B173" s="34"/>
@@ -21374,7 +21370,7 @@
       <c r="AV176" s="12"/>
     </row>
     <row r="177" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="33" t="s">
+      <c r="A177" s="42" t="s">
         <v>200</v>
       </c>
       <c r="B177" s="34"/>
@@ -21426,7 +21422,7 @@
       <c r="AV177" s="7"/>
     </row>
     <row r="178" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="37" t="s">
+      <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
       <c r="B178" s="34"/>
@@ -21656,7 +21652,7 @@
       <c r="AV180" s="12"/>
     </row>
     <row r="181" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="37" t="s">
+      <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
       <c r="B181" s="34"/>
@@ -21939,7 +21935,7 @@
       <c r="AV184" s="12"/>
     </row>
     <row r="185" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="33" t="s">
+      <c r="A185" s="42" t="s">
         <v>207</v>
       </c>
       <c r="B185" s="34"/>
@@ -21991,7 +21987,7 @@
       <c r="AV185" s="7"/>
     </row>
     <row r="186" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="37" t="s">
+      <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
       <c r="B186" s="34"/>
@@ -22274,7 +22270,7 @@
       <c r="AV189" s="12"/>
     </row>
     <row r="190" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="33" t="s">
+      <c r="A190" s="42" t="s">
         <v>211</v>
       </c>
       <c r="B190" s="34"/>
@@ -22326,7 +22322,7 @@
       <c r="AV190" s="7"/>
     </row>
     <row r="191" spans="1:48" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="37" t="s">
+      <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
       <c r="B191" s="34"/>
@@ -22610,6 +22606,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="A185:AT185"/>
+    <mergeCell ref="A40:AT40"/>
+    <mergeCell ref="A82:AT82"/>
+    <mergeCell ref="A4:AT4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AT3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AT33"/>
+    <mergeCell ref="A15:AT15"/>
+    <mergeCell ref="A191:AT191"/>
+    <mergeCell ref="A145:AT145"/>
+    <mergeCell ref="A163:AT163"/>
+    <mergeCell ref="A173:AT173"/>
+    <mergeCell ref="A114:AT114"/>
+    <mergeCell ref="A186:AT186"/>
+    <mergeCell ref="A167:AT167"/>
+    <mergeCell ref="A157:AT157"/>
+    <mergeCell ref="A181:AT181"/>
+    <mergeCell ref="A126:AT126"/>
+    <mergeCell ref="A140:AT140"/>
+    <mergeCell ref="A131:AT131"/>
+    <mergeCell ref="A190:AT190"/>
+    <mergeCell ref="A170:AT170"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A22:AT22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A178:AT178"/>
+    <mergeCell ref="A70:AT70"/>
+    <mergeCell ref="A153:AT153"/>
+    <mergeCell ref="A177:AT177"/>
+    <mergeCell ref="A113:AT113"/>
+    <mergeCell ref="A117:AT117"/>
+    <mergeCell ref="A146:AT146"/>
+    <mergeCell ref="A76:AT76"/>
+    <mergeCell ref="A164:AT164"/>
+    <mergeCell ref="A106:AT106"/>
+    <mergeCell ref="A150:AT150"/>
+    <mergeCell ref="A90:AT90"/>
+    <mergeCell ref="A98:AT98"/>
+    <mergeCell ref="A121:AT121"/>
+    <mergeCell ref="A135:AT135"/>
     <mergeCell ref="A51:AT51"/>
     <mergeCell ref="A58:AT58"/>
     <mergeCell ref="A64:AT64"/>
@@ -22626,59 +22675,6 @@
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="A28:AT28"/>
-    <mergeCell ref="A178:AT178"/>
-    <mergeCell ref="A70:AT70"/>
-    <mergeCell ref="A153:AT153"/>
-    <mergeCell ref="A177:AT177"/>
-    <mergeCell ref="A113:AT113"/>
-    <mergeCell ref="A117:AT117"/>
-    <mergeCell ref="A146:AT146"/>
-    <mergeCell ref="A76:AT76"/>
-    <mergeCell ref="A164:AT164"/>
-    <mergeCell ref="A106:AT106"/>
-    <mergeCell ref="A150:AT150"/>
-    <mergeCell ref="A90:AT90"/>
-    <mergeCell ref="A98:AT98"/>
-    <mergeCell ref="A121:AT121"/>
-    <mergeCell ref="A135:AT135"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A22:AT22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A33:AT33"/>
-    <mergeCell ref="A15:AT15"/>
-    <mergeCell ref="A191:AT191"/>
-    <mergeCell ref="A145:AT145"/>
-    <mergeCell ref="A163:AT163"/>
-    <mergeCell ref="A173:AT173"/>
-    <mergeCell ref="A114:AT114"/>
-    <mergeCell ref="A186:AT186"/>
-    <mergeCell ref="A167:AT167"/>
-    <mergeCell ref="A157:AT157"/>
-    <mergeCell ref="A181:AT181"/>
-    <mergeCell ref="A126:AT126"/>
-    <mergeCell ref="A140:AT140"/>
-    <mergeCell ref="A131:AT131"/>
-    <mergeCell ref="A190:AT190"/>
-    <mergeCell ref="A170:AT170"/>
-    <mergeCell ref="A185:AT185"/>
-    <mergeCell ref="A40:AT40"/>
-    <mergeCell ref="A82:AT82"/>
-    <mergeCell ref="A4:AT4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AT3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25278,6 +25274,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -25289,16 +25295,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -25348,7 +25344,7 @@
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <f t="shared" ref="A3:A23" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
         <f>Wedstrijden_beheer!O1</f>
@@ -25356,7 +25352,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
@@ -25364,13 +25360,13 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" ref="E3:E23" si="1">C3+D3</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>Wedstrijden_beheer!AK1</f>
@@ -25378,7 +25374,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AK17</f>
@@ -25386,13 +25382,13 @@
       </c>
       <c r="E4" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="str">
         <f>Wedstrijden_beheer!U1</f>
@@ -25400,7 +25396,7 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!U17</f>
@@ -25408,13 +25404,13 @@
       </c>
       <c r="E5" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1" t="str">
         <f>Wedstrijden_beheer!W1</f>
@@ -25422,7 +25418,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!W17</f>
@@ -25430,13 +25426,13 @@
       </c>
       <c r="E6" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B7" s="1" t="str">
         <f>Wedstrijden_beheer!S1</f>
@@ -25444,7 +25440,7 @@
       </c>
       <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D7" s="11">
         <f>Bonus_beheer!S17</f>
@@ -25452,13 +25448,13 @@
       </c>
       <c r="E7" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B8" s="1" t="str">
         <f>Wedstrijden_beheer!AG1</f>
@@ -25466,7 +25462,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!AG17</f>
@@ -25474,7 +25470,7 @@
       </c>
       <c r="E8" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25488,7 +25484,7 @@
       </c>
       <c r="C9" s="11">
         <f>SUM(Wedstrijden_beheer!AT3:'Wedstrijden_beheer'!AT194)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D9" s="11">
         <f>Bonus_beheer!AS17</f>
@@ -25496,13 +25492,13 @@
       </c>
       <c r="E9" s="11">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>Wedstrijden_beheer!E1</f>
@@ -25510,7 +25506,7 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!E17</f>
@@ -25518,13 +25514,13 @@
       </c>
       <c r="E10" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>Wedstrijden_beheer!AO1</f>
@@ -25532,7 +25528,7 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -25540,13 +25536,13 @@
       </c>
       <c r="E11" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B12" s="1" t="str">
         <f>Wedstrijden_beheer!K1</f>
@@ -25554,7 +25550,7 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!K17</f>
@@ -25562,13 +25558,13 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B13" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -25576,7 +25572,7 @@
       </c>
       <c r="C13" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D13" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -25584,7 +25580,7 @@
       </c>
       <c r="E13" s="11">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25598,7 +25594,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -25606,7 +25602,7 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -25620,7 +25616,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!AT4:'Wedstrijden_beheer'!AT195)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!AS18</f>
@@ -25628,13 +25624,13 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B16" s="1" t="str">
         <f>Wedstrijden_beheer!Y1</f>
@@ -25642,7 +25638,7 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!Y17</f>
@@ -25650,13 +25646,13 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B17" s="1" t="str">
         <f>Wedstrijden_beheer!AA1</f>
@@ -25664,7 +25660,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -25672,13 +25668,13 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!M1</f>
@@ -25686,7 +25682,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!M17</f>
@@ -25694,13 +25690,13 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>Wedstrijden_beheer!AC1</f>
@@ -25708,7 +25704,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -25716,13 +25712,13 @@
       </c>
       <c r="E19" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B20" s="1" t="str">
         <f>Wedstrijden_beheer!AE1</f>
@@ -25730,7 +25726,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -25738,13 +25734,13 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!G1</f>
@@ -25752,7 +25748,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!G17</f>
@@ -25760,13 +25756,13 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
@@ -25774,7 +25770,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!I17</f>
@@ -25782,13 +25778,13 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -25796,7 +25792,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -25804,7 +25800,7 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -26165,26 +26161,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -26379,26 +26355,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26415,4 +26392,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1434" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7EC24BF-A8FE-451F-B9BE-37B7EF49DE13}"/>
+  <xr:revisionPtr revIDLastSave="1460" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{880F7591-F372-41C1-9772-55B8F2472964}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5400" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="329">
   <si>
     <t>Tijd</t>
   </si>
@@ -1333,37 +1333,37 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1673,160 +1673,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.5703125" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.5703125" customWidth="1"/>
-    <col min="19" max="19" width="12.5703125" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.5703125" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" customWidth="1"/>
-    <col min="23" max="23" width="12.5703125" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" customWidth="1"/>
-    <col min="25" max="25" width="12.5703125" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="27" width="12.5703125" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.5703125" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.5703125" customWidth="1"/>
-    <col min="31" max="31" width="12.5703125" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.5703125" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.5703125" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.5703125" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.5703125" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.5703125" customWidth="1"/>
-    <col min="41" max="41" width="15.5703125" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.5703125" customWidth="1"/>
-    <col min="43" max="43" width="15.5703125" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.5703125" customWidth="1"/>
-    <col min="45" max="45" width="15.7109375" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.5703125" customWidth="1"/>
-    <col min="47" max="47" width="15.5703125" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.54296875" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.54296875" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" customWidth="1"/>
+    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.54296875" customWidth="1"/>
+    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.54296875" customWidth="1"/>
+    <col min="21" max="21" width="12.54296875" customWidth="1"/>
+    <col min="22" max="22" width="8.54296875" customWidth="1"/>
+    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.54296875" customWidth="1"/>
+    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.54296875" customWidth="1"/>
+    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.54296875" customWidth="1"/>
+    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.54296875" customWidth="1"/>
+    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.54296875" customWidth="1"/>
+    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.54296875" customWidth="1"/>
+    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.54296875" customWidth="1"/>
+    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.54296875" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.54296875" customWidth="1"/>
+    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.54296875" customWidth="1"/>
+    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.54296875" customWidth="1"/>
+    <col min="45" max="45" width="15.7265625" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.54296875" customWidth="1"/>
+    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.54296875" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="33" t="s">
+      <c r="F1" s="36"/>
+      <c r="G1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="34"/>
+      <c r="I1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="33" t="s">
+      <c r="J1" s="34"/>
+      <c r="K1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="33" t="s">
+      <c r="L1" s="34"/>
+      <c r="M1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="33" t="s">
+      <c r="N1" s="34"/>
+      <c r="O1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="33" t="s">
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="36"/>
-      <c r="S1" s="33" t="s">
+      <c r="R1" s="34"/>
+      <c r="S1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="36"/>
-      <c r="U1" s="33" t="s">
+      <c r="T1" s="34"/>
+      <c r="U1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="36"/>
-      <c r="W1" s="33" t="s">
+      <c r="V1" s="34"/>
+      <c r="W1" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="33" t="s">
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="33" t="s">
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="33" t="s">
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="33" t="s">
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="33" t="s">
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="33" t="s">
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="33" t="s">
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="36"/>
-      <c r="AM1" s="33" t="s">
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="36"/>
-      <c r="AO1" s="33" t="s">
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="AP1" s="36"/>
-      <c r="AQ1" s="33" t="s">
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="AR1" s="36"/>
-      <c r="AS1" s="33" t="s">
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="34"/>
-      <c r="AU1" s="33" t="s">
+      <c r="AT1" s="36"/>
+      <c r="AU1" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="34"/>
+      <c r="AV1" s="36"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1834,11 +1834,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A2" s="45"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="44"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A2" s="43"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
       </c>
@@ -1978,62 +1978,62 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
-      <c r="AR3" s="41"/>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="41"/>
-      <c r="AU3" s="41"/>
-      <c r="AV3" s="42"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="44"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="44"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="44"/>
+      <c r="AE3" s="44"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="44"/>
+      <c r="AH3" s="44"/>
+      <c r="AI3" s="44"/>
+      <c r="AJ3" s="44"/>
+      <c r="AK3" s="44"/>
+      <c r="AL3" s="44"/>
+      <c r="AM3" s="44"/>
+      <c r="AN3" s="44"/>
+      <c r="AO3" s="44"/>
+      <c r="AP3" s="44"/>
+      <c r="AQ3" s="44"/>
+      <c r="AR3" s="44"/>
+      <c r="AS3" s="44"/>
+      <c r="AT3" s="44"/>
+      <c r="AU3" s="44"/>
+      <c r="AV3" s="45"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="38"/>
@@ -2082,11 +2082,11 @@
       <c r="AS4" s="38"/>
       <c r="AT4" s="38"/>
       <c r="AU4" s="39"/>
-      <c r="AV4" s="36"/>
+      <c r="AV4" s="34"/>
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2320,8 +2320,8 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="37" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="38"/>
@@ -2370,11 +2370,11 @@
       <c r="AS7" s="38"/>
       <c r="AT7" s="38"/>
       <c r="AU7" s="39"/>
-      <c r="AV7" s="36"/>
+      <c r="AV7" s="34"/>
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2782,8 +2782,8 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
+    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="37" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="38"/>
@@ -2832,11 +2832,11 @@
       <c r="AS11" s="38"/>
       <c r="AT11" s="38"/>
       <c r="AU11" s="39"/>
-      <c r="AV11" s="36"/>
+      <c r="AV11" s="34"/>
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3242,8 +3242,8 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="37" t="s">
         <v>58</v>
       </c>
       <c r="B15" s="38"/>
@@ -3292,11 +3292,11 @@
       <c r="AS15" s="38"/>
       <c r="AT15" s="38"/>
       <c r="AU15" s="39"/>
-      <c r="AV15" s="36"/>
+      <c r="AV15" s="34"/>
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4224,8 +4224,8 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="37" t="s">
         <v>75</v>
       </c>
       <c r="B22" s="38"/>
@@ -4274,11 +4274,11 @@
       <c r="AS22" s="38"/>
       <c r="AT22" s="38"/>
       <c r="AU22" s="39"/>
-      <c r="AV22" s="36"/>
+      <c r="AV22" s="34"/>
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5032,8 +5032,8 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
+    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="37" t="s">
         <v>84</v>
       </c>
       <c r="B28" s="38"/>
@@ -5082,11 +5082,11 @@
       <c r="AS28" s="38"/>
       <c r="AT28" s="38"/>
       <c r="AU28" s="39"/>
-      <c r="AV28" s="36"/>
+      <c r="AV28" s="34"/>
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5666,8 +5666,8 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="40" t="s">
+    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="37" t="s">
         <v>92</v>
       </c>
       <c r="B33" s="38"/>
@@ -5716,11 +5716,11 @@
       <c r="AS33" s="38"/>
       <c r="AT33" s="38"/>
       <c r="AU33" s="39"/>
-      <c r="AV33" s="36"/>
+      <c r="AV33" s="34"/>
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6648,8 +6648,8 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
+    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="37" t="s">
         <v>103</v>
       </c>
       <c r="B40" s="38"/>
@@ -6698,11 +6698,11 @@
       <c r="AS40" s="38"/>
       <c r="AT40" s="38"/>
       <c r="AU40" s="39"/>
-      <c r="AV40" s="36"/>
+      <c r="AV40" s="34"/>
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="18"/>
       <c r="C45" s="13"/>
@@ -7456,8 +7456,8 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="40" t="s">
+    <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="37" t="s">
         <v>110</v>
       </c>
       <c r="B46" s="38"/>
@@ -7506,11 +7506,11 @@
       <c r="AS46" s="38"/>
       <c r="AT46" s="38"/>
       <c r="AU46" s="39"/>
-      <c r="AV46" s="36"/>
+      <c r="AV46" s="34"/>
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
       <c r="B50" s="18"/>
       <c r="C50" s="13"/>
@@ -8090,8 +8090,8 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="40" t="s">
+    <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="37" t="s">
         <v>111</v>
       </c>
       <c r="B51" s="38"/>
@@ -8140,11 +8140,11 @@
       <c r="AS51" s="38"/>
       <c r="AT51" s="38"/>
       <c r="AU51" s="39"/>
-      <c r="AV51" s="36"/>
+      <c r="AV51" s="34"/>
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
       <c r="B57" s="18"/>
       <c r="C57" s="13"/>
@@ -9072,8 +9072,8 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="40" t="s">
+    <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="37" t="s">
         <v>114</v>
       </c>
       <c r="B58" s="38"/>
@@ -9122,11 +9122,11 @@
       <c r="AS58" s="38"/>
       <c r="AT58" s="38"/>
       <c r="AU58" s="39"/>
-      <c r="AV58" s="36"/>
+      <c r="AV58" s="34"/>
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="12"/>
       <c r="B63" s="18"/>
       <c r="C63" s="13"/>
@@ -9880,8 +9880,8 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="40" t="s">
+    <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="37" t="s">
         <v>116</v>
       </c>
       <c r="B64" s="38"/>
@@ -9930,11 +9930,11 @@
       <c r="AS64" s="38"/>
       <c r="AT64" s="38"/>
       <c r="AU64" s="39"/>
-      <c r="AV64" s="36"/>
+      <c r="AV64" s="34"/>
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10108,7 +10108,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10282,7 +10282,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
       <c r="B69" s="18"/>
       <c r="C69" s="13"/>
@@ -10688,8 +10688,8 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="40" t="s">
+    <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="37" t="s">
         <v>117</v>
       </c>
       <c r="B70" s="38"/>
@@ -10738,11 +10738,11 @@
       <c r="AS70" s="38"/>
       <c r="AT70" s="38"/>
       <c r="AU70" s="39"/>
-      <c r="AV70" s="36"/>
+      <c r="AV70" s="34"/>
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11090,7 +11090,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11264,7 +11264,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
       <c r="B75" s="18"/>
       <c r="C75" s="13"/>
@@ -11496,8 +11496,8 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="40" t="s">
+    <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="37" t="s">
         <v>118</v>
       </c>
       <c r="B76" s="38"/>
@@ -11546,11 +11546,11 @@
       <c r="AS76" s="38"/>
       <c r="AT76" s="38"/>
       <c r="AU76" s="39"/>
-      <c r="AV76" s="36"/>
+      <c r="AV76" s="34"/>
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12"/>
       <c r="B81" s="18"/>
       <c r="C81" s="13"/>
@@ -12304,8 +12304,8 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="40" t="s">
+    <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="37" t="s">
         <v>119</v>
       </c>
       <c r="B82" s="38"/>
@@ -12354,11 +12354,11 @@
       <c r="AS82" s="38"/>
       <c r="AT82" s="38"/>
       <c r="AU82" s="39"/>
-      <c r="AV82" s="36"/>
+      <c r="AV82" s="34"/>
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -12880,7 +12880,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13054,7 +13054,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13228,7 +13228,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12"/>
       <c r="B89" s="18"/>
       <c r="C89" s="13"/>
@@ -13460,8 +13460,8 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="40" t="s">
+    <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="37" t="s">
         <v>122</v>
       </c>
       <c r="B90" s="38"/>
@@ -13510,11 +13510,11 @@
       <c r="AS90" s="38"/>
       <c r="AT90" s="38"/>
       <c r="AU90" s="39"/>
-      <c r="AV90" s="36"/>
+      <c r="AV90" s="34"/>
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13862,7 +13862,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14210,7 +14210,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14384,7 +14384,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14558,7 +14558,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="12"/>
       <c r="B97" s="18"/>
       <c r="C97" s="13"/>
@@ -14616,8 +14616,8 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="40" t="s">
+    <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="37" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="38"/>
@@ -14666,11 +14666,11 @@
       <c r="AS98" s="38"/>
       <c r="AT98" s="38"/>
       <c r="AU98" s="39"/>
-      <c r="AV98" s="36"/>
+      <c r="AV98" s="34"/>
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15018,7 +15018,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15192,7 +15192,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15540,7 +15540,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15714,7 +15714,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="12"/>
       <c r="B105" s="18"/>
       <c r="C105" s="13"/>
@@ -15772,8 +15772,8 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="40" t="s">
+    <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="37" t="s">
         <v>126</v>
       </c>
       <c r="B106" s="38"/>
@@ -15822,11 +15822,11 @@
       <c r="AS106" s="38"/>
       <c r="AT106" s="38"/>
       <c r="AU106" s="39"/>
-      <c r="AV106" s="36"/>
+      <c r="AV106" s="34"/>
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16000,7 +16000,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16174,7 +16174,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16348,7 +16348,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16522,7 +16522,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="12"/>
       <c r="B111" s="18"/>
       <c r="C111" s="13"/>
@@ -16580,7 +16580,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="12"/>
       <c r="B112" s="18"/>
       <c r="C112" s="13"/>
@@ -16638,8 +16638,8 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="37" t="s">
+    <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="42" t="s">
         <v>128</v>
       </c>
       <c r="B113" s="38"/>
@@ -16688,12 +16688,12 @@
       <c r="AS113" s="38"/>
       <c r="AT113" s="38"/>
       <c r="AU113" s="39"/>
-      <c r="AV113" s="36"/>
+      <c r="AV113" s="34"/>
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="40" t="s">
+    <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="37" t="s">
         <v>126</v>
       </c>
       <c r="B114" s="38"/>
@@ -16742,11 +16742,11 @@
       <c r="AS114" s="38"/>
       <c r="AT114" s="38"/>
       <c r="AU114" s="39"/>
-      <c r="AV114" s="36"/>
+      <c r="AV114" s="34"/>
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -16876,7 +16876,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="12"/>
       <c r="B116" s="18"/>
       <c r="C116" s="13"/>
@@ -16934,8 +16934,8 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="40" t="s">
+    <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="37" t="s">
         <v>131</v>
       </c>
       <c r="B117" s="38"/>
@@ -16984,11 +16984,11 @@
       <c r="AS117" s="38"/>
       <c r="AT117" s="38"/>
       <c r="AU117" s="39"/>
-      <c r="AV117" s="36"/>
+      <c r="AV117" s="34"/>
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17118,7 +17118,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17248,7 +17248,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="12"/>
       <c r="B120" s="18"/>
       <c r="C120" s="13"/>
@@ -17306,8 +17306,8 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="40" t="s">
+    <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="37" t="s">
         <v>136</v>
       </c>
       <c r="B121" s="38"/>
@@ -17356,11 +17356,11 @@
       <c r="AS121" s="38"/>
       <c r="AT121" s="38"/>
       <c r="AU121" s="39"/>
-      <c r="AV121" s="36"/>
+      <c r="AV121" s="34"/>
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17490,7 +17490,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17620,7 +17620,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17750,7 +17750,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="12"/>
       <c r="B125" s="18"/>
       <c r="C125" s="13"/>
@@ -17808,8 +17808,8 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="40" t="s">
+    <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="37" t="s">
         <v>143</v>
       </c>
       <c r="B126" s="38"/>
@@ -17858,11 +17858,11 @@
       <c r="AS126" s="38"/>
       <c r="AT126" s="38"/>
       <c r="AU126" s="39"/>
-      <c r="AV126" s="36"/>
+      <c r="AV126" s="34"/>
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -17992,7 +17992,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18122,7 +18122,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18252,7 +18252,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="12"/>
       <c r="B130" s="18"/>
       <c r="C130" s="13"/>
@@ -18310,8 +18310,8 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="40" t="s">
+    <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="37" t="s">
         <v>150</v>
       </c>
       <c r="B131" s="38"/>
@@ -18360,11 +18360,11 @@
       <c r="AS131" s="38"/>
       <c r="AT131" s="38"/>
       <c r="AU131" s="39"/>
-      <c r="AV131" s="36"/>
+      <c r="AV131" s="34"/>
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18494,7 +18494,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18624,7 +18624,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="12"/>
       <c r="B134" s="18"/>
       <c r="C134" s="13"/>
@@ -18682,8 +18682,8 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="40" t="s">
+    <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="37" t="s">
         <v>155</v>
       </c>
       <c r="B135" s="38"/>
@@ -18732,11 +18732,11 @@
       <c r="AS135" s="38"/>
       <c r="AT135" s="38"/>
       <c r="AU135" s="39"/>
-      <c r="AV135" s="36"/>
+      <c r="AV135" s="34"/>
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -18866,7 +18866,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -18996,7 +18996,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19126,7 +19126,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="12"/>
       <c r="B139" s="18"/>
       <c r="C139" s="13"/>
@@ -19184,8 +19184,8 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="40" t="s">
+    <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="37" t="s">
         <v>162</v>
       </c>
       <c r="B140" s="38"/>
@@ -19234,11 +19234,11 @@
       <c r="AS140" s="38"/>
       <c r="AT140" s="38"/>
       <c r="AU140" s="39"/>
-      <c r="AV140" s="36"/>
+      <c r="AV140" s="34"/>
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19368,7 +19368,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19498,7 +19498,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="12"/>
       <c r="B143" s="18"/>
       <c r="C143" s="13"/>
@@ -19556,7 +19556,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="12"/>
       <c r="B144" s="18"/>
       <c r="C144" s="13"/>
@@ -19614,8 +19614,8 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="37" t="s">
+    <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="42" t="s">
         <v>167</v>
       </c>
       <c r="B145" s="38"/>
@@ -19664,12 +19664,12 @@
       <c r="AS145" s="38"/>
       <c r="AT145" s="38"/>
       <c r="AU145" s="39"/>
-      <c r="AV145" s="36"/>
+      <c r="AV145" s="34"/>
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="40" t="s">
+    <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="37" t="s">
         <v>162</v>
       </c>
       <c r="B146" s="38"/>
@@ -19718,11 +19718,11 @@
       <c r="AS146" s="38"/>
       <c r="AT146" s="38"/>
       <c r="AU146" s="39"/>
-      <c r="AV146" s="36"/>
+      <c r="AV146" s="34"/>
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19852,7 +19852,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -19982,7 +19982,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="12"/>
       <c r="B149" s="18"/>
       <c r="C149" s="13"/>
@@ -20040,8 +20040,8 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="40" t="s">
+    <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="37" t="s">
         <v>172</v>
       </c>
       <c r="B150" s="38"/>
@@ -20090,11 +20090,11 @@
       <c r="AS150" s="38"/>
       <c r="AT150" s="38"/>
       <c r="AU150" s="39"/>
-      <c r="AV150" s="36"/>
+      <c r="AV150" s="34"/>
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20224,7 +20224,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="12"/>
       <c r="B152" s="18"/>
       <c r="C152" s="13"/>
@@ -20282,8 +20282,8 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="40" t="s">
+    <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="37" t="s">
         <v>175</v>
       </c>
       <c r="B153" s="38"/>
@@ -20332,11 +20332,11 @@
       <c r="AS153" s="38"/>
       <c r="AT153" s="38"/>
       <c r="AU153" s="39"/>
-      <c r="AV153" s="36"/>
+      <c r="AV153" s="34"/>
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20466,7 +20466,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20596,7 +20596,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="12"/>
       <c r="B156" s="18"/>
       <c r="C156" s="13"/>
@@ -20654,8 +20654,8 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="40" t="s">
+    <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="37" t="s">
         <v>180</v>
       </c>
       <c r="B157" s="38"/>
@@ -20704,11 +20704,11 @@
       <c r="AS157" s="38"/>
       <c r="AT157" s="38"/>
       <c r="AU157" s="39"/>
-      <c r="AV157" s="36"/>
+      <c r="AV157" s="34"/>
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -20968,7 +20968,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21098,7 +21098,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="12"/>
       <c r="B161" s="18"/>
       <c r="C161" s="13"/>
@@ -21156,7 +21156,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="12"/>
       <c r="B162" s="18"/>
       <c r="C162" s="13"/>
@@ -21214,8 +21214,8 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="37" t="s">
+    <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="42" t="s">
         <v>187</v>
       </c>
       <c r="B163" s="38"/>
@@ -21264,12 +21264,12 @@
       <c r="AS163" s="38"/>
       <c r="AT163" s="38"/>
       <c r="AU163" s="39"/>
-      <c r="AV163" s="36"/>
+      <c r="AV163" s="34"/>
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="40" t="s">
+    <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="37" t="s">
         <v>188</v>
       </c>
       <c r="B164" s="38"/>
@@ -21318,11 +21318,11 @@
       <c r="AS164" s="38"/>
       <c r="AT164" s="38"/>
       <c r="AU164" s="39"/>
-      <c r="AV164" s="36"/>
+      <c r="AV164" s="34"/>
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21452,7 +21452,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="12"/>
       <c r="B166" s="18"/>
       <c r="C166" s="13"/>
@@ -21510,8 +21510,8 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="40" t="s">
+    <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="37" t="s">
         <v>191</v>
       </c>
       <c r="B167" s="38"/>
@@ -21560,11 +21560,11 @@
       <c r="AS167" s="38"/>
       <c r="AT167" s="38"/>
       <c r="AU167" s="39"/>
-      <c r="AV167" s="36"/>
+      <c r="AV167" s="34"/>
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21694,7 +21694,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="12"/>
       <c r="B169" s="18"/>
       <c r="C169" s="13"/>
@@ -21752,8 +21752,8 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="40" t="s">
+    <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="37" t="s">
         <v>194</v>
       </c>
       <c r="B170" s="38"/>
@@ -21802,11 +21802,11 @@
       <c r="AS170" s="38"/>
       <c r="AT170" s="38"/>
       <c r="AU170" s="39"/>
-      <c r="AV170" s="36"/>
+      <c r="AV170" s="34"/>
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="12"/>
       <c r="B172" s="18"/>
       <c r="C172" s="13"/>
@@ -21994,8 +21994,8 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="40" t="s">
+    <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="37" t="s">
         <v>197</v>
       </c>
       <c r="B173" s="38"/>
@@ -22044,11 +22044,11 @@
       <c r="AS173" s="38"/>
       <c r="AT173" s="38"/>
       <c r="AU173" s="39"/>
-      <c r="AV173" s="36"/>
+      <c r="AV173" s="34"/>
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22178,7 +22178,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="12"/>
       <c r="B175" s="18"/>
       <c r="C175" s="13"/>
@@ -22236,7 +22236,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="12"/>
       <c r="B176" s="18"/>
       <c r="C176" s="13"/>
@@ -22294,8 +22294,8 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="37" t="s">
+    <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="42" t="s">
         <v>200</v>
       </c>
       <c r="B177" s="38"/>
@@ -22344,12 +22344,12 @@
       <c r="AS177" s="38"/>
       <c r="AT177" s="38"/>
       <c r="AU177" s="39"/>
-      <c r="AV177" s="36"/>
+      <c r="AV177" s="34"/>
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="40" t="s">
+    <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="37" t="s">
         <v>201</v>
       </c>
       <c r="B178" s="38"/>
@@ -22398,11 +22398,11 @@
       <c r="AS178" s="38"/>
       <c r="AT178" s="38"/>
       <c r="AU178" s="39"/>
-      <c r="AV178" s="36"/>
+      <c r="AV178" s="34"/>
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22532,7 +22532,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="12"/>
       <c r="B180" s="18"/>
       <c r="C180" s="13"/>
@@ -22590,8 +22590,8 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="40" t="s">
+    <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="37" t="s">
         <v>204</v>
       </c>
       <c r="B181" s="38"/>
@@ -22640,11 +22640,11 @@
       <c r="AS181" s="38"/>
       <c r="AT181" s="38"/>
       <c r="AU181" s="39"/>
-      <c r="AV181" s="36"/>
+      <c r="AV181" s="34"/>
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22774,7 +22774,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="12"/>
       <c r="B183" s="18"/>
       <c r="C183" s="13"/>
@@ -22832,7 +22832,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="12"/>
       <c r="B184" s="18"/>
       <c r="C184" s="13"/>
@@ -22890,8 +22890,8 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="37" t="s">
+    <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="42" t="s">
         <v>207</v>
       </c>
       <c r="B185" s="38"/>
@@ -22940,12 +22940,12 @@
       <c r="AS185" s="38"/>
       <c r="AT185" s="38"/>
       <c r="AU185" s="39"/>
-      <c r="AV185" s="36"/>
+      <c r="AV185" s="34"/>
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="40" t="s">
+    <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="37" t="s">
         <v>208</v>
       </c>
       <c r="B186" s="38"/>
@@ -22994,11 +22994,11 @@
       <c r="AS186" s="38"/>
       <c r="AT186" s="38"/>
       <c r="AU186" s="39"/>
-      <c r="AV186" s="36"/>
+      <c r="AV186" s="34"/>
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23128,7 +23128,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="12"/>
       <c r="B188" s="18"/>
       <c r="C188" s="13"/>
@@ -23186,7 +23186,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="12"/>
       <c r="B189" s="18"/>
       <c r="C189" s="13"/>
@@ -23244,8 +23244,8 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="37" t="s">
+    <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="42" t="s">
         <v>211</v>
       </c>
       <c r="B190" s="38"/>
@@ -23294,12 +23294,12 @@
       <c r="AS190" s="38"/>
       <c r="AT190" s="38"/>
       <c r="AU190" s="39"/>
-      <c r="AV190" s="36"/>
+      <c r="AV190" s="34"/>
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="40" t="s">
+    <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="37" t="s">
         <v>212</v>
       </c>
       <c r="B191" s="38"/>
@@ -23348,11 +23348,11 @@
       <c r="AS191" s="38"/>
       <c r="AT191" s="38"/>
       <c r="AU191" s="39"/>
-      <c r="AV191" s="36"/>
+      <c r="AV191" s="34"/>
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23482,7 +23482,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="12"/>
       <c r="B193" s="18"/>
       <c r="C193" s="13"/>
@@ -23540,7 +23540,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="12"/>
       <c r="B194" s="18"/>
       <c r="C194" s="13"/>
@@ -23600,13 +23600,47 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A70:AV70"/>
     <mergeCell ref="A153:AV153"/>
@@ -23623,53 +23657,19 @@
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
     <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23679,171 +23679,171 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.28515625" customWidth="1"/>
+    <col min="2" max="2" width="75.26953125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="23" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="23" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" style="23" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" style="23" customWidth="1"/>
-    <col min="25" max="25" width="10.5703125" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.5703125" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="23" customWidth="1"/>
-    <col min="29" max="29" width="10.5703125" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="23" customWidth="1"/>
-    <col min="31" max="31" width="10.5703125" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="23" customWidth="1"/>
-    <col min="33" max="33" width="10.5703125" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="23" customWidth="1"/>
-    <col min="35" max="35" width="10.5703125" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="23" customWidth="1"/>
-    <col min="37" max="37" width="10.5703125" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="23" customWidth="1"/>
-    <col min="39" max="39" width="10.5703125" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="23" customWidth="1"/>
-    <col min="41" max="41" width="10.5703125" customWidth="1"/>
-    <col min="42" max="42" width="12.5703125" customWidth="1"/>
-    <col min="43" max="43" width="10.5703125" customWidth="1"/>
-    <col min="44" max="44" width="12.5703125" style="23" customWidth="1"/>
-    <col min="45" max="45" width="10.5703125" customWidth="1"/>
-    <col min="46" max="46" width="12.5703125" style="23" customWidth="1"/>
-    <col min="47" max="47" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" customWidth="1"/>
+    <col min="12" max="12" width="12.54296875" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" customWidth="1"/>
+    <col min="14" max="14" width="12.54296875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" customWidth="1"/>
+    <col min="16" max="16" width="12.54296875" style="23" customWidth="1"/>
+    <col min="17" max="17" width="10.54296875" customWidth="1"/>
+    <col min="18" max="18" width="12.54296875" style="23" customWidth="1"/>
+    <col min="19" max="19" width="10.54296875" customWidth="1"/>
+    <col min="20" max="20" width="12.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" style="23" customWidth="1"/>
+    <col min="23" max="23" width="10.54296875" customWidth="1"/>
+    <col min="24" max="24" width="12.54296875" style="23" customWidth="1"/>
+    <col min="25" max="25" width="10.54296875" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" style="23" customWidth="1"/>
+    <col min="27" max="27" width="10.54296875" customWidth="1"/>
+    <col min="28" max="28" width="12.54296875" style="23" customWidth="1"/>
+    <col min="29" max="29" width="10.54296875" customWidth="1"/>
+    <col min="30" max="30" width="12.54296875" style="23" customWidth="1"/>
+    <col min="31" max="31" width="10.54296875" customWidth="1"/>
+    <col min="32" max="32" width="12.54296875" style="23" customWidth="1"/>
+    <col min="33" max="33" width="10.54296875" customWidth="1"/>
+    <col min="34" max="34" width="12.54296875" style="23" customWidth="1"/>
+    <col min="35" max="35" width="10.54296875" customWidth="1"/>
+    <col min="36" max="36" width="12.54296875" style="23" customWidth="1"/>
+    <col min="37" max="37" width="10.54296875" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="23" customWidth="1"/>
+    <col min="39" max="39" width="10.54296875" customWidth="1"/>
+    <col min="40" max="40" width="12.54296875" style="23" customWidth="1"/>
+    <col min="41" max="41" width="10.54296875" customWidth="1"/>
+    <col min="42" max="42" width="12.54296875" customWidth="1"/>
+    <col min="43" max="43" width="10.54296875" customWidth="1"/>
+    <col min="44" max="44" width="12.54296875" style="23" customWidth="1"/>
+    <col min="45" max="45" width="10.54296875" customWidth="1"/>
+    <col min="46" max="46" width="12.54296875" style="23" customWidth="1"/>
+    <col min="47" max="47" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="35" t="str">
+      <c r="D1" s="33" t="str">
         <f>Wedstrijden_beheer!E1</f>
         <v>Roland</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="35" t="str">
+      <c r="E1" s="34"/>
+      <c r="F1" s="33" t="str">
         <f>Wedstrijden_beheer!G1</f>
         <v>Nikki</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="str">
+      <c r="G1" s="34"/>
+      <c r="H1" s="33" t="str">
         <f>Wedstrijden_beheer!I1</f>
         <v>Abdussamed</v>
       </c>
-      <c r="I1" s="36"/>
-      <c r="J1" s="35" t="str">
+      <c r="I1" s="34"/>
+      <c r="J1" s="33" t="str">
         <f>Wedstrijden_beheer!K1</f>
         <v>Karsten</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="35" t="str">
+      <c r="K1" s="34"/>
+      <c r="L1" s="33" t="str">
         <f>Wedstrijden_beheer!M1</f>
         <v>Bas</v>
       </c>
-      <c r="M1" s="36"/>
-      <c r="N1" s="35" t="str">
+      <c r="M1" s="34"/>
+      <c r="N1" s="33" t="str">
         <f>Wedstrijden_beheer!O1</f>
         <v>Maik</v>
       </c>
-      <c r="O1" s="36"/>
-      <c r="P1" s="35" t="str">
+      <c r="O1" s="34"/>
+      <c r="P1" s="33" t="str">
         <f>Wedstrijden_beheer!Q1</f>
         <v>Simone</v>
       </c>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="35" t="str">
+      <c r="Q1" s="34"/>
+      <c r="R1" s="33" t="str">
         <f>Wedstrijden_beheer!S1</f>
         <v>Marc</v>
       </c>
-      <c r="S1" s="36"/>
-      <c r="T1" s="35" t="str">
+      <c r="S1" s="34"/>
+      <c r="T1" s="33" t="str">
         <f>Wedstrijden_beheer!U1</f>
         <v>Tom</v>
       </c>
-      <c r="U1" s="36"/>
-      <c r="V1" s="35" t="str">
+      <c r="U1" s="34"/>
+      <c r="V1" s="33" t="str">
         <f>Wedstrijden_beheer!W1</f>
         <v>Jos</v>
       </c>
-      <c r="W1" s="36"/>
-      <c r="X1" s="35" t="str">
+      <c r="W1" s="34"/>
+      <c r="X1" s="33" t="str">
         <f>Wedstrijden_beheer!Y1</f>
         <v>Lesley</v>
       </c>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="35" t="str">
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="33" t="str">
         <f>Wedstrijden_beheer!AA1</f>
         <v>Ivo</v>
       </c>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="35" t="str">
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="33" t="str">
         <f>Wedstrijden_beheer!AC1</f>
         <v>Ron</v>
       </c>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="35" t="str">
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="33" t="str">
         <f>Wedstrijden_beheer!AE1</f>
         <v>Jeroen</v>
       </c>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="35" t="str">
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="33" t="str">
         <f>Wedstrijden_beheer!AG1</f>
         <v>Erwin</v>
       </c>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="35" t="str">
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="33" t="str">
         <f>Wedstrijden_beheer!AI1</f>
         <v>Tim</v>
       </c>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="35" t="s">
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="AK1" s="36"/>
-      <c r="AL1" s="35" t="s">
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="36"/>
-      <c r="AN1" s="35" t="str">
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="33" t="str">
         <f>Wedstrijden_beheer!AO1</f>
         <v>Patrick</v>
       </c>
-      <c r="AO1" s="36"/>
-      <c r="AP1" s="35" t="str">
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="33" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
         <v>Jeno</v>
       </c>
-      <c r="AQ1" s="36"/>
-      <c r="AR1" s="33" t="str">
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="35" t="str">
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="34"/>
-      <c r="AT1" s="33" t="str">
+      <c r="AS1" s="36"/>
+      <c r="AT1" s="35" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="34"/>
+      <c r="AU1" s="36"/>
     </row>
-    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
       <c r="B2" s="25" t="s">
         <v>215</v>
@@ -23984,7 +23984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24147,7 +24147,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24310,7 +24310,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24473,7 +24473,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24636,7 +24636,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24799,7 +24799,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -24962,7 +24962,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25125,7 +25125,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25288,7 +25288,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25451,7 +25451,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25516,7 +25516,7 @@
         <v/>
       </c>
       <c r="T12" s="10" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="U12" s="11" t="str">
         <f t="shared" si="8"/>
@@ -25614,7 +25614,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25777,7 +25777,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -25940,7 +25940,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26103,7 +26103,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26266,7 +26266,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26385,6 +26385,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26396,17 +26407,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26418,16 +26418,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
@@ -26436,7 +26436,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>285</v>
       </c>
@@ -26453,9 +26453,9 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
-        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
@@ -26471,13 +26471,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f>C3+D3</f>
+        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
-        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
@@ -26493,13 +26493,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f>C4+D4</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
-        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B5" s="1" t="str">
@@ -26515,13 +26515,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f>C5+D5</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
-        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B6" s="1" t="str">
@@ -26537,13 +26537,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6+D6</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
-        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
@@ -26559,13 +26559,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f>C7+D7</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
-        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B8" s="1" t="str">
@@ -26581,13 +26581,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f>C8+D8</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
-        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="1" t="str">
@@ -26603,13 +26603,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f>C9+D9</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
-        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B10" s="1" t="str">
@@ -26625,13 +26625,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f>C10+D10</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
-        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B11" s="1" t="str">
@@ -26647,13 +26647,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f>C11+D11</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
-        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B12" s="1" t="str">
@@ -26669,13 +26669,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f>C12+D12</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
-        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B13" s="1" t="str">
@@ -26691,13 +26691,13 @@
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f>C13+D13</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
-        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
@@ -26713,13 +26713,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f>C14+D14</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
-        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
@@ -26735,13 +26735,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f>C15+D15</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
-        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="1" t="str">
@@ -26757,13 +26757,13 @@
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f>C16+D16</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
-        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B17" s="1" t="str">
@@ -26779,13 +26779,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f>C17+D17</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
-        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B18" s="1" t="str">
@@ -26801,13 +26801,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f>C18+D18</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
-        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B19" s="1" t="str">
@@ -26823,13 +26823,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f>C19+D19</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
-        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
@@ -26845,13 +26845,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f>C20+D20</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
-        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B21" s="1" t="str">
@@ -26867,13 +26867,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f>C21+D21</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
-        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="1" t="str">
@@ -26889,13 +26889,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f>C22+D22</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
-        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
@@ -26911,13 +26911,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f>C23+D23</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="11">
-        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B24" s="1" t="str">
@@ -26933,7 +26933,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f>C24+D24</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -26950,20 +26950,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.7109375" hidden="1"/>
+    <col min="3" max="16384" width="8.7265625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -26971,7 +26971,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -26979,7 +26979,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -26987,7 +26987,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -26995,7 +26995,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27003,7 +27003,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27011,7 +27011,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27019,7 +27019,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27035,16 +27035,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="55.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="30.7265625" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.7109375" hidden="1"/>
+    <col min="45" max="16384" width="8.7265625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>306</v>
       </c>
@@ -27092,7 +27092,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27103,7 +27103,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27114,7 +27114,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27125,7 +27125,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27136,7 +27136,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27147,7 +27147,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27158,7 +27158,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27174,15 +27174,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="26" t="s">
         <v>319</v>
       </c>
@@ -27193,100 +27193,107 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>322</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>323</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>24</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -27295,26 +27302,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27509,32 +27496,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27551,4 +27533,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1460" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{880F7591-F372-41C1-9772-55B8F2472964}"/>
+  <xr:revisionPtr revIDLastSave="1472" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC804CD-FC7E-426E-981B-232080740777}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1031,6 +1031,9 @@
   </si>
   <si>
     <t>Penso</t>
+  </si>
+  <si>
+    <t>7-1</t>
   </si>
 </sst>
 </file>
@@ -1333,29 +1336,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1363,6 +1363,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1739,94 +1742,94 @@
       <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="35" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="36"/>
+      <c r="I1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="34"/>
-      <c r="K1" s="35" t="s">
+      <c r="J1" s="36"/>
+      <c r="K1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="34"/>
-      <c r="M1" s="35" t="s">
+      <c r="L1" s="36"/>
+      <c r="M1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="34"/>
-      <c r="O1" s="35" t="s">
+      <c r="N1" s="36"/>
+      <c r="O1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35" t="s">
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="34"/>
-      <c r="S1" s="35" t="s">
+      <c r="R1" s="36"/>
+      <c r="S1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="34"/>
-      <c r="U1" s="35" t="s">
+      <c r="T1" s="36"/>
+      <c r="U1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="34"/>
-      <c r="W1" s="35" t="s">
+      <c r="V1" s="36"/>
+      <c r="W1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35" t="s">
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="35" t="s">
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="34"/>
-      <c r="AC1" s="35" t="s">
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="35" t="s">
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="35" t="s">
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="AH1" s="34"/>
-      <c r="AI1" s="35" t="s">
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="AJ1" s="34"/>
-      <c r="AK1" s="35" t="s">
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="34"/>
-      <c r="AM1" s="35" t="s">
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="34"/>
-      <c r="AO1" s="35" t="s">
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="AP1" s="34"/>
-      <c r="AQ1" s="35" t="s">
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="AR1" s="34"/>
-      <c r="AS1" s="35" t="s">
+      <c r="AR1" s="36"/>
+      <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="36"/>
-      <c r="AU1" s="35" t="s">
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="36"/>
+      <c r="AV1" s="39"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1835,9 +1838,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="43"/>
+      <c r="A2" s="42"/>
       <c r="B2" s="41"/>
-      <c r="C2" s="43"/>
+      <c r="C2" s="42"/>
       <c r="D2" s="41"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1979,110 +1982,110 @@
       </c>
     </row>
     <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="44"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44"/>
-      <c r="AA3" s="44"/>
-      <c r="AB3" s="44"/>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="44"/>
-      <c r="AE3" s="44"/>
-      <c r="AF3" s="44"/>
-      <c r="AG3" s="44"/>
-      <c r="AH3" s="44"/>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="44"/>
-      <c r="AK3" s="44"/>
-      <c r="AL3" s="44"/>
-      <c r="AM3" s="44"/>
-      <c r="AN3" s="44"/>
-      <c r="AO3" s="44"/>
-      <c r="AP3" s="44"/>
-      <c r="AQ3" s="44"/>
-      <c r="AR3" s="44"/>
-      <c r="AS3" s="44"/>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="44"/>
-      <c r="AV3" s="45"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
     <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="39"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="39"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="39"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="39"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="39"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="39"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="39"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="39"/>
-      <c r="AV4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="34"/>
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="34"/>
+      <c r="AK4" s="35"/>
+      <c r="AL4" s="34"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="34"/>
+      <c r="AO4" s="35"/>
+      <c r="AP4" s="34"/>
+      <c r="AQ4" s="34"/>
+      <c r="AR4" s="34"/>
+      <c r="AS4" s="34"/>
+      <c r="AT4" s="34"/>
+      <c r="AU4" s="35"/>
+      <c r="AV4" s="36"/>
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
@@ -2321,56 +2324,56 @@
       <c r="AX6" s="12"/>
     </row>
     <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="39"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="39"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="39"/>
-      <c r="AD7" s="38"/>
-      <c r="AE7" s="39"/>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="39"/>
-      <c r="AJ7" s="38"/>
-      <c r="AK7" s="39"/>
-      <c r="AL7" s="38"/>
-      <c r="AM7" s="39"/>
-      <c r="AN7" s="38"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="38"/>
-      <c r="AQ7" s="38"/>
-      <c r="AR7" s="38"/>
-      <c r="AS7" s="38"/>
-      <c r="AT7" s="38"/>
-      <c r="AU7" s="39"/>
-      <c r="AV7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="34"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="34"/>
+      <c r="AC7" s="35"/>
+      <c r="AD7" s="34"/>
+      <c r="AE7" s="35"/>
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="35"/>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="35"/>
+      <c r="AJ7" s="34"/>
+      <c r="AK7" s="35"/>
+      <c r="AL7" s="34"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="34"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="34"/>
+      <c r="AQ7" s="34"/>
+      <c r="AR7" s="34"/>
+      <c r="AS7" s="34"/>
+      <c r="AT7" s="34"/>
+      <c r="AU7" s="35"/>
+      <c r="AV7" s="36"/>
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
@@ -2557,171 +2560,173 @@
       <c r="B9" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="11" t="str">
+      <c r="F9" s="11">
         <f>IF(OR($C9="",E9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E9,FIND("-",E9)-1),"")=AW9,IFERROR(--MID(E9,FIND("-",E9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(E9,FIND("-",E9)-1),""))-(IFERROR(--MID(E9,FIND("-",E9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(E9,FIND("-",E9)-1),""))-(IFERROR(--MID(E9,FIND("-",E9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(E9,FIND("-",E9)-1),""))=(AW9))+2*((IFERROR(--MID(E9,FIND("-",E9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="11" t="str">
+      <c r="H9" s="11">
         <f>IF(OR($C9="",G9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G9,FIND("-",G9)-1),"")=AW9,IFERROR(--MID(G9,FIND("-",G9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(G9,FIND("-",G9)-1),""))-(IFERROR(--MID(G9,FIND("-",G9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(G9,FIND("-",G9)-1),""))-(IFERROR(--MID(G9,FIND("-",G9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(G9,FIND("-",G9)-1),""))=(AW9))+2*((IFERROR(--MID(G9,FIND("-",G9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="11" t="str">
+      <c r="J9" s="11">
         <f>IF(OR($C9="",I9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I9,FIND("-",I9)-1),"")=AW9,IFERROR(--MID(I9,FIND("-",I9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(I9,FIND("-",I9)-1),""))-(IFERROR(--MID(I9,FIND("-",I9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(I9,FIND("-",I9)-1),""))-(IFERROR(--MID(I9,FIND("-",I9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(I9,FIND("-",I9)-1),""))=(AW9))+2*((IFERROR(--MID(I9,FIND("-",I9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="11" t="str">
+      <c r="L9" s="11">
         <f>IF(OR($C9="",K9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K9,FIND("-",K9)-1),"")=AW9,IFERROR(--MID(K9,FIND("-",K9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(K9,FIND("-",K9)-1),""))-(IFERROR(--MID(K9,FIND("-",K9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(K9,FIND("-",K9)-1),""))-(IFERROR(--MID(K9,FIND("-",K9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(K9,FIND("-",K9)-1),""))=(AW9))+2*((IFERROR(--MID(K9,FIND("-",K9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="11" t="str">
+      <c r="N9" s="11">
         <f>IF(OR($C9="",M9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M9,FIND("-",M9)-1),"")=AW9,IFERROR(--MID(M9,FIND("-",M9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(M9,FIND("-",M9)-1),""))-(IFERROR(--MID(M9,FIND("-",M9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(M9,FIND("-",M9)-1),""))-(IFERROR(--MID(M9,FIND("-",M9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(M9,FIND("-",M9)-1),""))=(AW9))+2*((IFERROR(--MID(M9,FIND("-",M9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P9" s="11" t="str">
+      <c r="P9" s="11">
         <f>IF(OR($C9="",O9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O9,FIND("-",O9)-1),"")=AW9,IFERROR(--MID(O9,FIND("-",O9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(O9,FIND("-",O9)-1),""))-(IFERROR(--MID(O9,FIND("-",O9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(O9,FIND("-",O9)-1),""))-(IFERROR(--MID(O9,FIND("-",O9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(O9,FIND("-",O9)-1),""))=(AW9))+2*((IFERROR(--MID(O9,FIND("-",O9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R9" s="11" t="str">
+      <c r="R9" s="11">
         <f>IF(OR($C9="",Q9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q9,FIND("-",Q9)-1),"")=AW9,IFERROR(--MID(Q9,FIND("-",Q9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(Q9,FIND("-",Q9)-1),""))-(IFERROR(--MID(Q9,FIND("-",Q9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(Q9,FIND("-",Q9)-1),""))-(IFERROR(--MID(Q9,FIND("-",Q9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(Q9,FIND("-",Q9)-1),""))=(AW9))+2*((IFERROR(--MID(Q9,FIND("-",Q9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="S9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T9" s="11" t="str">
+      <c r="T9" s="11">
         <f>IF(OR($C9="",S9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S9,FIND("-",S9)-1),"")=AW9,IFERROR(--MID(S9,FIND("-",S9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(S9,FIND("-",S9)-1),""))-(IFERROR(--MID(S9,FIND("-",S9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(S9,FIND("-",S9)-1),""))-(IFERROR(--MID(S9,FIND("-",S9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(S9,FIND("-",S9)-1),""))=(AW9))+2*((IFERROR(--MID(S9,FIND("-",S9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V9" s="11" t="str">
+      <c r="V9" s="11">
         <f>IF(OR($C9="",U9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U9,FIND("-",U9)-1),"")=AW9,IFERROR(--MID(U9,FIND("-",U9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(U9,FIND("-",U9)-1),""))-(IFERROR(--MID(U9,FIND("-",U9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(U9,FIND("-",U9)-1),""))-(IFERROR(--MID(U9,FIND("-",U9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(U9,FIND("-",U9)-1),""))=(AW9))+2*((IFERROR(--MID(U9,FIND("-",U9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X9" s="11" t="str">
+      <c r="X9" s="11">
         <f>IF(OR($C9="",W9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W9,FIND("-",W9)-1),"")=AW9,IFERROR(--MID(W9,FIND("-",W9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(W9,FIND("-",W9)-1),""))-(IFERROR(--MID(W9,FIND("-",W9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(W9,FIND("-",W9)-1),""))-(IFERROR(--MID(W9,FIND("-",W9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(W9,FIND("-",W9)-1),""))=(AW9))+2*((IFERROR(--MID(W9,FIND("-",W9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z9" s="11" t="str">
+      <c r="Z9" s="11">
         <f>IF(OR($C9="",Y9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y9,FIND("-",Y9)-1),"")=AW9,IFERROR(--MID(Y9,FIND("-",Y9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(Y9,FIND("-",Y9)-1),""))-(IFERROR(--MID(Y9,FIND("-",Y9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(Y9,FIND("-",Y9)-1),""))-(IFERROR(--MID(Y9,FIND("-",Y9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(Y9,FIND("-",Y9)-1),""))=(AW9))+2*((IFERROR(--MID(Y9,FIND("-",Y9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AB9" s="11" t="str">
+      <c r="AB9" s="11">
         <f>IF(OR($C9="",AA9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA9,FIND("-",AA9)-1),"")=AW9,IFERROR(--MID(AA9,FIND("-",AA9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AA9,FIND("-",AA9)-1),""))-(IFERROR(--MID(AA9,FIND("-",AA9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AA9,FIND("-",AA9)-1),""))-(IFERROR(--MID(AA9,FIND("-",AA9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AA9,FIND("-",AA9)-1),""))=(AW9))+2*((IFERROR(--MID(AA9,FIND("-",AA9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AD9" s="11" t="str">
+      <c r="AD9" s="11">
         <f>IF(OR($C9="",AC9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC9,FIND("-",AC9)-1),"")=AW9,IFERROR(--MID(AC9,FIND("-",AC9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AC9,FIND("-",AC9)-1),""))-(IFERROR(--MID(AC9,FIND("-",AC9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AC9,FIND("-",AC9)-1),""))-(IFERROR(--MID(AC9,FIND("-",AC9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AC9,FIND("-",AC9)-1),""))=(AW9))+2*((IFERROR(--MID(AC9,FIND("-",AC9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF9" s="11" t="str">
+      <c r="AF9" s="11">
         <f>IF(OR($C9="",AE9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE9,FIND("-",AE9)-1),"")=AW9,IFERROR(--MID(AE9,FIND("-",AE9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AE9,FIND("-",AE9)-1),""))-(IFERROR(--MID(AE9,FIND("-",AE9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AE9,FIND("-",AE9)-1),""))-(IFERROR(--MID(AE9,FIND("-",AE9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AE9,FIND("-",AE9)-1),""))=(AW9))+2*((IFERROR(--MID(AE9,FIND("-",AE9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH9" s="11" t="str">
+      <c r="AH9" s="11">
         <f>IF(OR($C9="",AG9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG9,FIND("-",AG9)-1),"")=AW9,IFERROR(--MID(AG9,FIND("-",AG9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AG9,FIND("-",AG9)-1),""))-(IFERROR(--MID(AG9,FIND("-",AG9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AG9,FIND("-",AG9)-1),""))-(IFERROR(--MID(AG9,FIND("-",AG9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AG9,FIND("-",AG9)-1),""))=(AW9))+2*((IFERROR(--MID(AG9,FIND("-",AG9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ9" s="11" t="str">
+      <c r="AJ9" s="11">
         <f>IF(OR($C9="",AI9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI9,FIND("-",AI9)-1),"")=AW9,IFERROR(--MID(AI9,FIND("-",AI9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AI9,FIND("-",AI9)-1),""))-(IFERROR(--MID(AI9,FIND("-",AI9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AI9,FIND("-",AI9)-1),""))-(IFERROR(--MID(AI9,FIND("-",AI9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AI9,FIND("-",AI9)-1),""))=(AW9))+2*((IFERROR(--MID(AI9,FIND("-",AI9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AL9" s="11" t="str">
+      <c r="AL9" s="11">
         <f>IF(OR($C9="",AK9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK9,FIND("-",AK9)-1),"")=AW9,IFERROR(--MID(AK9,FIND("-",AK9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AK9,FIND("-",AK9)-1),""))-(IFERROR(--MID(AK9,FIND("-",AK9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AK9,FIND("-",AK9)-1),""))-(IFERROR(--MID(AK9,FIND("-",AK9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AK9,FIND("-",AK9)-1),""))=(AW9))+2*((IFERROR(--MID(AK9,FIND("-",AK9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN9" s="11" t="str">
+      <c r="AN9" s="11">
         <f>IF(OR($C9="",AM9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM9,FIND("-",AM9)-1),"")=AW9,IFERROR(--MID(AM9,FIND("-",AM9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AM9,FIND("-",AM9)-1),""))-(IFERROR(--MID(AM9,FIND("-",AM9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AM9,FIND("-",AM9)-1),""))-(IFERROR(--MID(AM9,FIND("-",AM9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AM9,FIND("-",AM9)-1),""))=(AW9))+2*((IFERROR(--MID(AM9,FIND("-",AM9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP9" s="11" t="str">
+      <c r="AP9" s="11">
         <f>IF(OR($C9="",AO9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO9,FIND("-",AO9)-1),"")=AW9,IFERROR(--MID(AO9,FIND("-",AO9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AO9,FIND("-",AO9)-1),""))-(IFERROR(--MID(AO9,FIND("-",AO9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AO9,FIND("-",AO9)-1),""))-(IFERROR(--MID(AO9,FIND("-",AO9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AO9,FIND("-",AO9)-1),""))=(AW9))+2*((IFERROR(--MID(AO9,FIND("-",AO9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR9" s="11" t="str">
+      <c r="AR9" s="11">
         <f>IF(OR($C9="",AQ9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ9,FIND("-",AQ9)-1),"")=AW9,IFERROR(--MID(AQ9,FIND("-",AQ9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AQ9,FIND("-",AQ9)-1),""))-(IFERROR(--MID(AQ9,FIND("-",AQ9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AQ9,FIND("-",AQ9)-1),""))-(IFERROR(--MID(AQ9,FIND("-",AQ9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AQ9,FIND("-",AQ9)-1),""))=(AW9))+2*((IFERROR(--MID(AQ9,FIND("-",AQ9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AT9" s="11" t="str">
+      <c r="AT9" s="11">
         <f>IF(OR($C9="",AS9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS9,FIND("-",AS9)-1),"")=AW9,IFERROR(--MID(AS9,FIND("-",AS9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AS9,FIND("-",AS9)-1),""))-(IFERROR(--MID(AS9,FIND("-",AS9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AS9,FIND("-",AS9)-1),""))-(IFERROR(--MID(AS9,FIND("-",AS9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AS9,FIND("-",AS9)-1),""))=(AW9))+2*((IFERROR(--MID(AS9,FIND("-",AS9)+1,99),""))=(AX9))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV9" s="11" t="str">
+      <c r="AV9" s="11">
         <f>IF(OR($C9="",AU9=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU9,FIND("-",AU9)-1),"")=AW9,IFERROR(--MID(AU9,FIND("-",AU9)+1,99),"")=AX9),10,5*(SIGN((IFERROR(--LEFT(AU9,FIND("-",AU9)-1),""))-(IFERROR(--MID(AU9,FIND("-",AU9)+1,99),"")))=SIGN((AW9)-(AX9)))+2*(((IFERROR(--LEFT(AU9,FIND("-",AU9)-1),""))-(IFERROR(--MID(AU9,FIND("-",AU9)+1,99),"")))=((AW9)-(AX9)))+2*((IFERROR(--LEFT(AU9,FIND("-",AU9)-1),""))=(AW9))+2*((IFERROR(--MID(AU9,FIND("-",AU9)+1,99),""))=(AX9))),""))</f>
-        <v/>
-      </c>
-      <c r="AW9" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW9" s="11">
         <f>IF($C9="","",IFERROR(--LEFT($C9,FIND("-",$C9)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX9" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="11">
         <f>IF($C9="","",IFERROR(--MID($C9,FIND("-",$C9)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -2783,56 +2788,56 @@
       <c r="AX10" s="12"/>
     </row>
     <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="38"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="38"/>
-      <c r="AE11" s="39"/>
-      <c r="AF11" s="38"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="38"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="38"/>
-      <c r="AK11" s="39"/>
-      <c r="AL11" s="38"/>
-      <c r="AM11" s="39"/>
-      <c r="AN11" s="38"/>
-      <c r="AO11" s="39"/>
-      <c r="AP11" s="38"/>
-      <c r="AQ11" s="38"/>
-      <c r="AR11" s="38"/>
-      <c r="AS11" s="38"/>
-      <c r="AT11" s="38"/>
-      <c r="AU11" s="39"/>
-      <c r="AV11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="34"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="34"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="34"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="34"/>
+      <c r="AC11" s="35"/>
+      <c r="AD11" s="34"/>
+      <c r="AE11" s="35"/>
+      <c r="AF11" s="34"/>
+      <c r="AG11" s="35"/>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="35"/>
+      <c r="AJ11" s="34"/>
+      <c r="AK11" s="35"/>
+      <c r="AL11" s="34"/>
+      <c r="AM11" s="35"/>
+      <c r="AN11" s="34"/>
+      <c r="AO11" s="35"/>
+      <c r="AP11" s="34"/>
+      <c r="AQ11" s="34"/>
+      <c r="AR11" s="34"/>
+      <c r="AS11" s="34"/>
+      <c r="AT11" s="34"/>
+      <c r="AU11" s="35"/>
+      <c r="AV11" s="36"/>
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
@@ -2843,171 +2848,173 @@
       <c r="B12" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="D12" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="11" t="str">
+      <c r="F12" s="11">
         <f>IF(OR($C12="",E12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E12,FIND("-",E12)-1),"")=AW12,IFERROR(--MID(E12,FIND("-",E12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(E12,FIND("-",E12)-1),""))-(IFERROR(--MID(E12,FIND("-",E12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(E12,FIND("-",E12)-1),""))-(IFERROR(--MID(E12,FIND("-",E12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(E12,FIND("-",E12)-1),""))=(AW12))+2*((IFERROR(--MID(E12,FIND("-",E12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="11" t="str">
+      <c r="H12" s="11">
         <f>IF(OR($C12="",G12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G12,FIND("-",G12)-1),"")=AW12,IFERROR(--MID(G12,FIND("-",G12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(G12,FIND("-",G12)-1),""))-(IFERROR(--MID(G12,FIND("-",G12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(G12,FIND("-",G12)-1),""))-(IFERROR(--MID(G12,FIND("-",G12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(G12,FIND("-",G12)-1),""))=(AW12))+2*((IFERROR(--MID(G12,FIND("-",G12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="11" t="str">
+      <c r="J12" s="11">
         <f>IF(OR($C12="",I12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I12,FIND("-",I12)-1),"")=AW12,IFERROR(--MID(I12,FIND("-",I12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(I12,FIND("-",I12)-1),""))-(IFERROR(--MID(I12,FIND("-",I12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(I12,FIND("-",I12)-1),""))-(IFERROR(--MID(I12,FIND("-",I12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(I12,FIND("-",I12)-1),""))=(AW12))+2*((IFERROR(--MID(I12,FIND("-",I12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="11" t="str">
+      <c r="L12" s="11">
         <f>IF(OR($C12="",K12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K12,FIND("-",K12)-1),"")=AW12,IFERROR(--MID(K12,FIND("-",K12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(K12,FIND("-",K12)-1),""))-(IFERROR(--MID(K12,FIND("-",K12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(K12,FIND("-",K12)-1),""))-(IFERROR(--MID(K12,FIND("-",K12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(K12,FIND("-",K12)-1),""))=(AW12))+2*((IFERROR(--MID(K12,FIND("-",K12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="11" t="str">
+      <c r="N12" s="11">
         <f>IF(OR($C12="",M12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M12,FIND("-",M12)-1),"")=AW12,IFERROR(--MID(M12,FIND("-",M12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(M12,FIND("-",M12)-1),""))-(IFERROR(--MID(M12,FIND("-",M12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(M12,FIND("-",M12)-1),""))-(IFERROR(--MID(M12,FIND("-",M12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(M12,FIND("-",M12)-1),""))=(AW12))+2*((IFERROR(--MID(M12,FIND("-",M12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P12" s="11" t="str">
+      <c r="P12" s="11">
         <f>IF(OR($C12="",O12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O12,FIND("-",O12)-1),"")=AW12,IFERROR(--MID(O12,FIND("-",O12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(O12,FIND("-",O12)-1),""))-(IFERROR(--MID(O12,FIND("-",O12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(O12,FIND("-",O12)-1),""))-(IFERROR(--MID(O12,FIND("-",O12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(O12,FIND("-",O12)-1),""))=(AW12))+2*((IFERROR(--MID(O12,FIND("-",O12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="11" t="str">
+      <c r="R12" s="11">
         <f>IF(OR($C12="",Q12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q12,FIND("-",Q12)-1),"")=AW12,IFERROR(--MID(Q12,FIND("-",Q12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(Q12,FIND("-",Q12)-1),""))-(IFERROR(--MID(Q12,FIND("-",Q12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(Q12,FIND("-",Q12)-1),""))-(IFERROR(--MID(Q12,FIND("-",Q12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(Q12,FIND("-",Q12)-1),""))=(AW12))+2*((IFERROR(--MID(Q12,FIND("-",Q12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="T12" s="11" t="str">
+      <c r="T12" s="11">
         <f>IF(OR($C12="",S12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S12,FIND("-",S12)-1),"")=AW12,IFERROR(--MID(S12,FIND("-",S12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(S12,FIND("-",S12)-1),""))-(IFERROR(--MID(S12,FIND("-",S12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(S12,FIND("-",S12)-1),""))-(IFERROR(--MID(S12,FIND("-",S12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(S12,FIND("-",S12)-1),""))=(AW12))+2*((IFERROR(--MID(S12,FIND("-",S12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V12" s="11" t="str">
+      <c r="V12" s="11">
         <f>IF(OR($C12="",U12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U12,FIND("-",U12)-1),"")=AW12,IFERROR(--MID(U12,FIND("-",U12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(U12,FIND("-",U12)-1),""))-(IFERROR(--MID(U12,FIND("-",U12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(U12,FIND("-",U12)-1),""))-(IFERROR(--MID(U12,FIND("-",U12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(U12,FIND("-",U12)-1),""))=(AW12))+2*((IFERROR(--MID(U12,FIND("-",U12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X12" s="11" t="str">
+      <c r="X12" s="11">
         <f>IF(OR($C12="",W12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W12,FIND("-",W12)-1),"")=AW12,IFERROR(--MID(W12,FIND("-",W12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(W12,FIND("-",W12)-1),""))-(IFERROR(--MID(W12,FIND("-",W12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(W12,FIND("-",W12)-1),""))-(IFERROR(--MID(W12,FIND("-",W12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(W12,FIND("-",W12)-1),""))=(AW12))+2*((IFERROR(--MID(W12,FIND("-",W12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z12" s="11" t="str">
+      <c r="Z12" s="11">
         <f>IF(OR($C12="",Y12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y12,FIND("-",Y12)-1),"")=AW12,IFERROR(--MID(Y12,FIND("-",Y12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(Y12,FIND("-",Y12)-1),""))-(IFERROR(--MID(Y12,FIND("-",Y12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(Y12,FIND("-",Y12)-1),""))-(IFERROR(--MID(Y12,FIND("-",Y12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(Y12,FIND("-",Y12)-1),""))=(AW12))+2*((IFERROR(--MID(Y12,FIND("-",Y12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB12" s="11" t="str">
+      <c r="AB12" s="11">
         <f>IF(OR($C12="",AA12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA12,FIND("-",AA12)-1),"")=AW12,IFERROR(--MID(AA12,FIND("-",AA12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AA12,FIND("-",AA12)-1),""))-(IFERROR(--MID(AA12,FIND("-",AA12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AA12,FIND("-",AA12)-1),""))-(IFERROR(--MID(AA12,FIND("-",AA12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AA12,FIND("-",AA12)-1),""))=(AW12))+2*((IFERROR(--MID(AA12,FIND("-",AA12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AD12" s="11" t="str">
+      <c r="AD12" s="11">
         <f>IF(OR($C12="",AC12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC12,FIND("-",AC12)-1),"")=AW12,IFERROR(--MID(AC12,FIND("-",AC12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AC12,FIND("-",AC12)-1),""))-(IFERROR(--MID(AC12,FIND("-",AC12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AC12,FIND("-",AC12)-1),""))-(IFERROR(--MID(AC12,FIND("-",AC12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AC12,FIND("-",AC12)-1),""))=(AW12))+2*((IFERROR(--MID(AC12,FIND("-",AC12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF12" s="11" t="str">
+      <c r="AF12" s="11">
         <f>IF(OR($C12="",AE12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE12,FIND("-",AE12)-1),"")=AW12,IFERROR(--MID(AE12,FIND("-",AE12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AE12,FIND("-",AE12)-1),""))-(IFERROR(--MID(AE12,FIND("-",AE12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AE12,FIND("-",AE12)-1),""))-(IFERROR(--MID(AE12,FIND("-",AE12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AE12,FIND("-",AE12)-1),""))=(AW12))+2*((IFERROR(--MID(AE12,FIND("-",AE12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH12" s="11" t="str">
+      <c r="AH12" s="11">
         <f>IF(OR($C12="",AG12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG12,FIND("-",AG12)-1),"")=AW12,IFERROR(--MID(AG12,FIND("-",AG12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AG12,FIND("-",AG12)-1),""))-(IFERROR(--MID(AG12,FIND("-",AG12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AG12,FIND("-",AG12)-1),""))-(IFERROR(--MID(AG12,FIND("-",AG12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AG12,FIND("-",AG12)-1),""))=(AW12))+2*((IFERROR(--MID(AG12,FIND("-",AG12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ12" s="11" t="str">
+      <c r="AJ12" s="11">
         <f>IF(OR($C12="",AI12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI12,FIND("-",AI12)-1),"")=AW12,IFERROR(--MID(AI12,FIND("-",AI12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AI12,FIND("-",AI12)-1),""))-(IFERROR(--MID(AI12,FIND("-",AI12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AI12,FIND("-",AI12)-1),""))-(IFERROR(--MID(AI12,FIND("-",AI12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AI12,FIND("-",AI12)-1),""))=(AW12))+2*((IFERROR(--MID(AI12,FIND("-",AI12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL12" s="11" t="str">
+      <c r="AL12" s="11">
         <f>IF(OR($C12="",AK12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK12,FIND("-",AK12)-1),"")=AW12,IFERROR(--MID(AK12,FIND("-",AK12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AK12,FIND("-",AK12)-1),""))-(IFERROR(--MID(AK12,FIND("-",AK12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AK12,FIND("-",AK12)-1),""))-(IFERROR(--MID(AK12,FIND("-",AK12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AK12,FIND("-",AK12)-1),""))=(AW12))+2*((IFERROR(--MID(AK12,FIND("-",AK12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM12" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN12" s="11" t="str">
+      <c r="AN12" s="11">
         <f>IF(OR($C12="",AM12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM12,FIND("-",AM12)-1),"")=AW12,IFERROR(--MID(AM12,FIND("-",AM12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AM12,FIND("-",AM12)-1),""))-(IFERROR(--MID(AM12,FIND("-",AM12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AM12,FIND("-",AM12)-1),""))-(IFERROR(--MID(AM12,FIND("-",AM12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AM12,FIND("-",AM12)-1),""))=(AW12))+2*((IFERROR(--MID(AM12,FIND("-",AM12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AP12" s="11" t="str">
+      <c r="AP12" s="11">
         <f>IF(OR($C12="",AO12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO12,FIND("-",AO12)-1),"")=AW12,IFERROR(--MID(AO12,FIND("-",AO12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AO12,FIND("-",AO12)-1),""))-(IFERROR(--MID(AO12,FIND("-",AO12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AO12,FIND("-",AO12)-1),""))-(IFERROR(--MID(AO12,FIND("-",AO12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AO12,FIND("-",AO12)-1),""))=(AW12))+2*((IFERROR(--MID(AO12,FIND("-",AO12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AR12" s="11" t="str">
+      <c r="AR12" s="11">
         <f>IF(OR($C12="",AQ12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ12,FIND("-",AQ12)-1),"")=AW12,IFERROR(--MID(AQ12,FIND("-",AQ12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AQ12,FIND("-",AQ12)-1),""))-(IFERROR(--MID(AQ12,FIND("-",AQ12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AQ12,FIND("-",AQ12)-1),""))-(IFERROR(--MID(AQ12,FIND("-",AQ12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AQ12,FIND("-",AQ12)-1),""))=(AW12))+2*((IFERROR(--MID(AQ12,FIND("-",AQ12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AT12" s="11" t="str">
+      <c r="AT12" s="11">
         <f>IF(OR($C12="",AS12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS12,FIND("-",AS12)-1),"")=AW12,IFERROR(--MID(AS12,FIND("-",AS12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AS12,FIND("-",AS12)-1),""))-(IFERROR(--MID(AS12,FIND("-",AS12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AS12,FIND("-",AS12)-1),""))-(IFERROR(--MID(AS12,FIND("-",AS12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AS12,FIND("-",AS12)-1),""))=(AW12))+2*((IFERROR(--MID(AS12,FIND("-",AS12)+1,99),""))=(AX12))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU12" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AV12" s="11" t="str">
+      <c r="AV12" s="11">
         <f>IF(OR($C12="",AU12=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU12,FIND("-",AU12)-1),"")=AW12,IFERROR(--MID(AU12,FIND("-",AU12)+1,99),"")=AX12),10,5*(SIGN((IFERROR(--LEFT(AU12,FIND("-",AU12)-1),""))-(IFERROR(--MID(AU12,FIND("-",AU12)+1,99),"")))=SIGN((AW12)-(AX12)))+2*(((IFERROR(--LEFT(AU12,FIND("-",AU12)-1),""))-(IFERROR(--MID(AU12,FIND("-",AU12)+1,99),"")))=((AW12)-(AX12)))+2*((IFERROR(--LEFT(AU12,FIND("-",AU12)-1),""))=(AW12))+2*((IFERROR(--MID(AU12,FIND("-",AU12)+1,99),""))=(AX12))),""))</f>
-        <v/>
-      </c>
-      <c r="AW12" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="11">
         <f>IF($C12="","",IFERROR(--LEFT($C12,FIND("-",$C12)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX12" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX12" s="11">
         <f>IF($C12="","",IFERROR(--MID($C12,FIND("-",$C12)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3017,171 +3024,173 @@
       <c r="B13" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="11" t="str">
+      <c r="F13" s="11">
         <f>IF(OR($C13="",E13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E13,FIND("-",E13)-1),"")=AW13,IFERROR(--MID(E13,FIND("-",E13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(E13,FIND("-",E13)-1),""))-(IFERROR(--MID(E13,FIND("-",E13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(E13,FIND("-",E13)-1),""))-(IFERROR(--MID(E13,FIND("-",E13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(E13,FIND("-",E13)-1),""))=(AW13))+2*((IFERROR(--MID(E13,FIND("-",E13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="11" t="str">
+      <c r="H13" s="11">
         <f>IF(OR($C13="",G13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G13,FIND("-",G13)-1),"")=AW13,IFERROR(--MID(G13,FIND("-",G13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(G13,FIND("-",G13)-1),""))-(IFERROR(--MID(G13,FIND("-",G13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(G13,FIND("-",G13)-1),""))-(IFERROR(--MID(G13,FIND("-",G13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(G13,FIND("-",G13)-1),""))=(AW13))+2*((IFERROR(--MID(G13,FIND("-",G13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="11" t="str">
+      <c r="J13" s="11">
         <f>IF(OR($C13="",I13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I13,FIND("-",I13)-1),"")=AW13,IFERROR(--MID(I13,FIND("-",I13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(I13,FIND("-",I13)-1),""))-(IFERROR(--MID(I13,FIND("-",I13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(I13,FIND("-",I13)-1),""))-(IFERROR(--MID(I13,FIND("-",I13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(I13,FIND("-",I13)-1),""))=(AW13))+2*((IFERROR(--MID(I13,FIND("-",I13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="11" t="str">
+      <c r="L13" s="11">
         <f>IF(OR($C13="",K13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K13,FIND("-",K13)-1),"")=AW13,IFERROR(--MID(K13,FIND("-",K13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(K13,FIND("-",K13)-1),""))-(IFERROR(--MID(K13,FIND("-",K13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(K13,FIND("-",K13)-1),""))-(IFERROR(--MID(K13,FIND("-",K13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(K13,FIND("-",K13)-1),""))=(AW13))+2*((IFERROR(--MID(K13,FIND("-",K13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="N13" s="11" t="str">
+      <c r="N13" s="11">
         <f>IF(OR($C13="",M13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M13,FIND("-",M13)-1),"")=AW13,IFERROR(--MID(M13,FIND("-",M13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(M13,FIND("-",M13)-1),""))-(IFERROR(--MID(M13,FIND("-",M13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(M13,FIND("-",M13)-1),""))-(IFERROR(--MID(M13,FIND("-",M13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(M13,FIND("-",M13)-1),""))=(AW13))+2*((IFERROR(--MID(M13,FIND("-",M13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="P13" s="11" t="str">
+      <c r="P13" s="11">
         <f>IF(OR($C13="",O13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O13,FIND("-",O13)-1),"")=AW13,IFERROR(--MID(O13,FIND("-",O13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(O13,FIND("-",O13)-1),""))-(IFERROR(--MID(O13,FIND("-",O13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(O13,FIND("-",O13)-1),""))-(IFERROR(--MID(O13,FIND("-",O13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(O13,FIND("-",O13)-1),""))=(AW13))+2*((IFERROR(--MID(O13,FIND("-",O13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="R13" s="11" t="str">
+      <c r="R13" s="11">
         <f>IF(OR($C13="",Q13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q13,FIND("-",Q13)-1),"")=AW13,IFERROR(--MID(Q13,FIND("-",Q13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(Q13,FIND("-",Q13)-1),""))-(IFERROR(--MID(Q13,FIND("-",Q13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(Q13,FIND("-",Q13)-1),""))-(IFERROR(--MID(Q13,FIND("-",Q13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(Q13,FIND("-",Q13)-1),""))=(AW13))+2*((IFERROR(--MID(Q13,FIND("-",Q13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S13" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T13" s="11" t="str">
+      <c r="T13" s="11">
         <f>IF(OR($C13="",S13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S13,FIND("-",S13)-1),"")=AW13,IFERROR(--MID(S13,FIND("-",S13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(S13,FIND("-",S13)-1),""))-(IFERROR(--MID(S13,FIND("-",S13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(S13,FIND("-",S13)-1),""))-(IFERROR(--MID(S13,FIND("-",S13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(S13,FIND("-",S13)-1),""))=(AW13))+2*((IFERROR(--MID(S13,FIND("-",S13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V13" s="11" t="str">
+      <c r="V13" s="11">
         <f>IF(OR($C13="",U13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U13,FIND("-",U13)-1),"")=AW13,IFERROR(--MID(U13,FIND("-",U13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(U13,FIND("-",U13)-1),""))-(IFERROR(--MID(U13,FIND("-",U13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(U13,FIND("-",U13)-1),""))-(IFERROR(--MID(U13,FIND("-",U13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(U13,FIND("-",U13)-1),""))=(AW13))+2*((IFERROR(--MID(U13,FIND("-",U13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X13" s="11" t="str">
+      <c r="X13" s="11">
         <f>IF(OR($C13="",W13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W13,FIND("-",W13)-1),"")=AW13,IFERROR(--MID(W13,FIND("-",W13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(W13,FIND("-",W13)-1),""))-(IFERROR(--MID(W13,FIND("-",W13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(W13,FIND("-",W13)-1),""))-(IFERROR(--MID(W13,FIND("-",W13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(W13,FIND("-",W13)-1),""))=(AW13))+2*((IFERROR(--MID(W13,FIND("-",W13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z13" s="11" t="str">
+      <c r="Z13" s="11">
         <f>IF(OR($C13="",Y13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y13,FIND("-",Y13)-1),"")=AW13,IFERROR(--MID(Y13,FIND("-",Y13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(Y13,FIND("-",Y13)-1),""))-(IFERROR(--MID(Y13,FIND("-",Y13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(Y13,FIND("-",Y13)-1),""))-(IFERROR(--MID(Y13,FIND("-",Y13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(Y13,FIND("-",Y13)-1),""))=(AW13))+2*((IFERROR(--MID(Y13,FIND("-",Y13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB13" s="11" t="str">
+      <c r="AB13" s="11">
         <f>IF(OR($C13="",AA13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA13,FIND("-",AA13)-1),"")=AW13,IFERROR(--MID(AA13,FIND("-",AA13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AA13,FIND("-",AA13)-1),""))-(IFERROR(--MID(AA13,FIND("-",AA13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AA13,FIND("-",AA13)-1),""))-(IFERROR(--MID(AA13,FIND("-",AA13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AA13,FIND("-",AA13)-1),""))=(AW13))+2*((IFERROR(--MID(AA13,FIND("-",AA13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AD13" s="11" t="str">
+      <c r="AD13" s="11">
         <f>IF(OR($C13="",AC13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC13,FIND("-",AC13)-1),"")=AW13,IFERROR(--MID(AC13,FIND("-",AC13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AC13,FIND("-",AC13)-1),""))-(IFERROR(--MID(AC13,FIND("-",AC13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AC13,FIND("-",AC13)-1),""))-(IFERROR(--MID(AC13,FIND("-",AC13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AC13,FIND("-",AC13)-1),""))=(AW13))+2*((IFERROR(--MID(AC13,FIND("-",AC13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF13" s="11" t="str">
+      <c r="AF13" s="11">
         <f>IF(OR($C13="",AE13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE13,FIND("-",AE13)-1),"")=AW13,IFERROR(--MID(AE13,FIND("-",AE13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AE13,FIND("-",AE13)-1),""))-(IFERROR(--MID(AE13,FIND("-",AE13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AE13,FIND("-",AE13)-1),""))-(IFERROR(--MID(AE13,FIND("-",AE13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AE13,FIND("-",AE13)-1),""))=(AW13))+2*((IFERROR(--MID(AE13,FIND("-",AE13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH13" s="11" t="str">
+      <c r="AH13" s="11">
         <f>IF(OR($C13="",AG13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG13,FIND("-",AG13)-1),"")=AW13,IFERROR(--MID(AG13,FIND("-",AG13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AG13,FIND("-",AG13)-1),""))-(IFERROR(--MID(AG13,FIND("-",AG13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AG13,FIND("-",AG13)-1),""))-(IFERROR(--MID(AG13,FIND("-",AG13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AG13,FIND("-",AG13)-1),""))=(AW13))+2*((IFERROR(--MID(AG13,FIND("-",AG13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI13" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AJ13" s="11" t="str">
+      <c r="AJ13" s="11">
         <f>IF(OR($C13="",AI13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI13,FIND("-",AI13)-1),"")=AW13,IFERROR(--MID(AI13,FIND("-",AI13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AI13,FIND("-",AI13)-1),""))-(IFERROR(--MID(AI13,FIND("-",AI13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AI13,FIND("-",AI13)-1),""))-(IFERROR(--MID(AI13,FIND("-",AI13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AI13,FIND("-",AI13)-1),""))=(AW13))+2*((IFERROR(--MID(AI13,FIND("-",AI13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL13" s="11" t="str">
+      <c r="AL13" s="11">
         <f>IF(OR($C13="",AK13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK13,FIND("-",AK13)-1),"")=AW13,IFERROR(--MID(AK13,FIND("-",AK13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AK13,FIND("-",AK13)-1),""))-(IFERROR(--MID(AK13,FIND("-",AK13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AK13,FIND("-",AK13)-1),""))-(IFERROR(--MID(AK13,FIND("-",AK13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AK13,FIND("-",AK13)-1),""))=(AW13))+2*((IFERROR(--MID(AK13,FIND("-",AK13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN13" s="11" t="str">
+      <c r="AN13" s="11">
         <f>IF(OR($C13="",AM13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM13,FIND("-",AM13)-1),"")=AW13,IFERROR(--MID(AM13,FIND("-",AM13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AM13,FIND("-",AM13)-1),""))-(IFERROR(--MID(AM13,FIND("-",AM13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AM13,FIND("-",AM13)-1),""))-(IFERROR(--MID(AM13,FIND("-",AM13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AM13,FIND("-",AM13)-1),""))=(AW13))+2*((IFERROR(--MID(AM13,FIND("-",AM13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AP13" s="11" t="str">
+      <c r="AP13" s="11">
         <f>IF(OR($C13="",AO13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO13,FIND("-",AO13)-1),"")=AW13,IFERROR(--MID(AO13,FIND("-",AO13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AO13,FIND("-",AO13)-1),""))-(IFERROR(--MID(AO13,FIND("-",AO13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AO13,FIND("-",AO13)-1),""))-(IFERROR(--MID(AO13,FIND("-",AO13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AO13,FIND("-",AO13)-1),""))=(AW13))+2*((IFERROR(--MID(AO13,FIND("-",AO13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AR13" s="11" t="str">
+      <c r="AR13" s="11">
         <f>IF(OR($C13="",AQ13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ13,FIND("-",AQ13)-1),"")=AW13,IFERROR(--MID(AQ13,FIND("-",AQ13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AQ13,FIND("-",AQ13)-1),""))-(IFERROR(--MID(AQ13,FIND("-",AQ13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AQ13,FIND("-",AQ13)-1),""))-(IFERROR(--MID(AQ13,FIND("-",AQ13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AQ13,FIND("-",AQ13)-1),""))=(AW13))+2*((IFERROR(--MID(AQ13,FIND("-",AQ13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AT13" s="11" t="str">
+      <c r="AT13" s="11">
         <f>IF(OR($C13="",AS13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS13,FIND("-",AS13)-1),"")=AW13,IFERROR(--MID(AS13,FIND("-",AS13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AS13,FIND("-",AS13)-1),""))-(IFERROR(--MID(AS13,FIND("-",AS13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AS13,FIND("-",AS13)-1),""))-(IFERROR(--MID(AS13,FIND("-",AS13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AS13,FIND("-",AS13)-1),""))=(AW13))+2*((IFERROR(--MID(AS13,FIND("-",AS13)+1,99),""))=(AX13))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AV13" s="11" t="str">
+      <c r="AV13" s="11">
         <f>IF(OR($C13="",AU13=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU13,FIND("-",AU13)-1),"")=AW13,IFERROR(--MID(AU13,FIND("-",AU13)+1,99),"")=AX13),10,5*(SIGN((IFERROR(--LEFT(AU13,FIND("-",AU13)-1),""))-(IFERROR(--MID(AU13,FIND("-",AU13)+1,99),"")))=SIGN((AW13)-(AX13)))+2*(((IFERROR(--LEFT(AU13,FIND("-",AU13)-1),""))-(IFERROR(--MID(AU13,FIND("-",AU13)+1,99),"")))=((AW13)-(AX13)))+2*((IFERROR(--LEFT(AU13,FIND("-",AU13)-1),""))=(AW13))+2*((IFERROR(--MID(AU13,FIND("-",AU13)+1,99),""))=(AX13))),""))</f>
-        <v/>
-      </c>
-      <c r="AW13" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="11">
         <f>IF($C13="","",IFERROR(--LEFT($C13,FIND("-",$C13)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX13" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX13" s="11">
         <f>IF($C13="","",IFERROR(--MID($C13,FIND("-",$C13)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3243,56 +3252,56 @@
       <c r="AX14" s="12"/>
     </row>
     <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="39"/>
-      <c r="X15" s="38"/>
-      <c r="Y15" s="39"/>
-      <c r="Z15" s="38"/>
-      <c r="AA15" s="39"/>
-      <c r="AB15" s="38"/>
-      <c r="AC15" s="39"/>
-      <c r="AD15" s="38"/>
-      <c r="AE15" s="39"/>
-      <c r="AF15" s="38"/>
-      <c r="AG15" s="39"/>
-      <c r="AH15" s="38"/>
-      <c r="AI15" s="39"/>
-      <c r="AJ15" s="38"/>
-      <c r="AK15" s="39"/>
-      <c r="AL15" s="38"/>
-      <c r="AM15" s="39"/>
-      <c r="AN15" s="38"/>
-      <c r="AO15" s="39"/>
-      <c r="AP15" s="38"/>
-      <c r="AQ15" s="38"/>
-      <c r="AR15" s="38"/>
-      <c r="AS15" s="38"/>
-      <c r="AT15" s="38"/>
-      <c r="AU15" s="39"/>
-      <c r="AV15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="34"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="34"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="34"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="34"/>
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="34"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="34"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="34"/>
+      <c r="AI15" s="35"/>
+      <c r="AJ15" s="34"/>
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="34"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="34"/>
+      <c r="AO15" s="35"/>
+      <c r="AP15" s="34"/>
+      <c r="AQ15" s="34"/>
+      <c r="AR15" s="34"/>
+      <c r="AS15" s="34"/>
+      <c r="AT15" s="34"/>
+      <c r="AU15" s="35"/>
+      <c r="AV15" s="36"/>
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
@@ -3303,171 +3312,173 @@
       <c r="B16" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D16" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="11" t="str">
+      <c r="F16" s="11">
         <f>IF(OR($C16="",E16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E16,FIND("-",E16)-1),"")=AW16,IFERROR(--MID(E16,FIND("-",E16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(E16,FIND("-",E16)-1),""))-(IFERROR(--MID(E16,FIND("-",E16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(E16,FIND("-",E16)-1),""))-(IFERROR(--MID(E16,FIND("-",E16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(E16,FIND("-",E16)-1),""))=(AW16))+2*((IFERROR(--MID(E16,FIND("-",E16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="11" t="str">
+      <c r="H16" s="11">
         <f>IF(OR($C16="",G16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G16,FIND("-",G16)-1),"")=AW16,IFERROR(--MID(G16,FIND("-",G16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(G16,FIND("-",G16)-1),""))-(IFERROR(--MID(G16,FIND("-",G16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(G16,FIND("-",G16)-1),""))-(IFERROR(--MID(G16,FIND("-",G16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(G16,FIND("-",G16)-1),""))=(AW16))+2*((IFERROR(--MID(G16,FIND("-",G16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="11" t="str">
+      <c r="J16" s="11">
         <f>IF(OR($C16="",I16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I16,FIND("-",I16)-1),"")=AW16,IFERROR(--MID(I16,FIND("-",I16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(I16,FIND("-",I16)-1),""))-(IFERROR(--MID(I16,FIND("-",I16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(I16,FIND("-",I16)-1),""))-(IFERROR(--MID(I16,FIND("-",I16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(I16,FIND("-",I16)-1),""))=(AW16))+2*((IFERROR(--MID(I16,FIND("-",I16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K16" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="11" t="str">
+      <c r="L16" s="11">
         <f>IF(OR($C16="",K16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K16,FIND("-",K16)-1),"")=AW16,IFERROR(--MID(K16,FIND("-",K16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(K16,FIND("-",K16)-1),""))-(IFERROR(--MID(K16,FIND("-",K16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(K16,FIND("-",K16)-1),""))-(IFERROR(--MID(K16,FIND("-",K16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(K16,FIND("-",K16)-1),""))=(AW16))+2*((IFERROR(--MID(K16,FIND("-",K16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="N16" s="11" t="str">
+      <c r="N16" s="11">
         <f>IF(OR($C16="",M16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M16,FIND("-",M16)-1),"")=AW16,IFERROR(--MID(M16,FIND("-",M16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(M16,FIND("-",M16)-1),""))-(IFERROR(--MID(M16,FIND("-",M16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(M16,FIND("-",M16)-1),""))-(IFERROR(--MID(M16,FIND("-",M16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(M16,FIND("-",M16)-1),""))=(AW16))+2*((IFERROR(--MID(M16,FIND("-",M16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P16" s="11" t="str">
+      <c r="P16" s="11">
         <f>IF(OR($C16="",O16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O16,FIND("-",O16)-1),"")=AW16,IFERROR(--MID(O16,FIND("-",O16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(O16,FIND("-",O16)-1),""))-(IFERROR(--MID(O16,FIND("-",O16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(O16,FIND("-",O16)-1),""))-(IFERROR(--MID(O16,FIND("-",O16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(O16,FIND("-",O16)-1),""))=(AW16))+2*((IFERROR(--MID(O16,FIND("-",O16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q16" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="R16" s="11" t="str">
+      <c r="R16" s="11">
         <f>IF(OR($C16="",Q16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q16,FIND("-",Q16)-1),"")=AW16,IFERROR(--MID(Q16,FIND("-",Q16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(Q16,FIND("-",Q16)-1),""))-(IFERROR(--MID(Q16,FIND("-",Q16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(Q16,FIND("-",Q16)-1),""))-(IFERROR(--MID(Q16,FIND("-",Q16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(Q16,FIND("-",Q16)-1),""))=(AW16))+2*((IFERROR(--MID(Q16,FIND("-",Q16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S16" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T16" s="11" t="str">
+      <c r="T16" s="11">
         <f>IF(OR($C16="",S16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S16,FIND("-",S16)-1),"")=AW16,IFERROR(--MID(S16,FIND("-",S16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(S16,FIND("-",S16)-1),""))-(IFERROR(--MID(S16,FIND("-",S16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(S16,FIND("-",S16)-1),""))-(IFERROR(--MID(S16,FIND("-",S16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(S16,FIND("-",S16)-1),""))=(AW16))+2*((IFERROR(--MID(S16,FIND("-",S16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V16" s="11" t="str">
+      <c r="V16" s="11">
         <f>IF(OR($C16="",U16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U16,FIND("-",U16)-1),"")=AW16,IFERROR(--MID(U16,FIND("-",U16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(U16,FIND("-",U16)-1),""))-(IFERROR(--MID(U16,FIND("-",U16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(U16,FIND("-",U16)-1),""))-(IFERROR(--MID(U16,FIND("-",U16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(U16,FIND("-",U16)-1),""))=(AW16))+2*((IFERROR(--MID(U16,FIND("-",U16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X16" s="11" t="str">
+      <c r="X16" s="11">
         <f>IF(OR($C16="",W16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W16,FIND("-",W16)-1),"")=AW16,IFERROR(--MID(W16,FIND("-",W16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(W16,FIND("-",W16)-1),""))-(IFERROR(--MID(W16,FIND("-",W16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(W16,FIND("-",W16)-1),""))-(IFERROR(--MID(W16,FIND("-",W16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(W16,FIND("-",W16)-1),""))=(AW16))+2*((IFERROR(--MID(W16,FIND("-",W16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z16" s="11" t="str">
+      <c r="Z16" s="11">
         <f>IF(OR($C16="",Y16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y16,FIND("-",Y16)-1),"")=AW16,IFERROR(--MID(Y16,FIND("-",Y16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(Y16,FIND("-",Y16)-1),""))-(IFERROR(--MID(Y16,FIND("-",Y16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(Y16,FIND("-",Y16)-1),""))-(IFERROR(--MID(Y16,FIND("-",Y16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(Y16,FIND("-",Y16)-1),""))=(AW16))+2*((IFERROR(--MID(Y16,FIND("-",Y16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA16" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AB16" s="11" t="str">
+      <c r="AB16" s="11">
         <f>IF(OR($C16="",AA16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA16,FIND("-",AA16)-1),"")=AW16,IFERROR(--MID(AA16,FIND("-",AA16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AA16,FIND("-",AA16)-1),""))-(IFERROR(--MID(AA16,FIND("-",AA16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AA16,FIND("-",AA16)-1),""))-(IFERROR(--MID(AA16,FIND("-",AA16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AA16,FIND("-",AA16)-1),""))=(AW16))+2*((IFERROR(--MID(AA16,FIND("-",AA16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC16" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD16" s="11" t="str">
+      <c r="AD16" s="11">
         <f>IF(OR($C16="",AC16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC16,FIND("-",AC16)-1),"")=AW16,IFERROR(--MID(AC16,FIND("-",AC16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AC16,FIND("-",AC16)-1),""))-(IFERROR(--MID(AC16,FIND("-",AC16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AC16,FIND("-",AC16)-1),""))-(IFERROR(--MID(AC16,FIND("-",AC16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AC16,FIND("-",AC16)-1),""))=(AW16))+2*((IFERROR(--MID(AC16,FIND("-",AC16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE16" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AF16" s="11" t="str">
+      <c r="AF16" s="11">
         <f>IF(OR($C16="",AE16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE16,FIND("-",AE16)-1),"")=AW16,IFERROR(--MID(AE16,FIND("-",AE16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AE16,FIND("-",AE16)-1),""))-(IFERROR(--MID(AE16,FIND("-",AE16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AE16,FIND("-",AE16)-1),""))-(IFERROR(--MID(AE16,FIND("-",AE16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AE16,FIND("-",AE16)-1),""))=(AW16))+2*((IFERROR(--MID(AE16,FIND("-",AE16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH16" s="11" t="str">
+      <c r="AH16" s="11">
         <f>IF(OR($C16="",AG16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG16,FIND("-",AG16)-1),"")=AW16,IFERROR(--MID(AG16,FIND("-",AG16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AG16,FIND("-",AG16)-1),""))-(IFERROR(--MID(AG16,FIND("-",AG16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AG16,FIND("-",AG16)-1),""))-(IFERROR(--MID(AG16,FIND("-",AG16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AG16,FIND("-",AG16)-1),""))=(AW16))+2*((IFERROR(--MID(AG16,FIND("-",AG16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AJ16" s="11" t="str">
+      <c r="AJ16" s="11">
         <f>IF(OR($C16="",AI16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI16,FIND("-",AI16)-1),"")=AW16,IFERROR(--MID(AI16,FIND("-",AI16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AI16,FIND("-",AI16)-1),""))-(IFERROR(--MID(AI16,FIND("-",AI16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AI16,FIND("-",AI16)-1),""))-(IFERROR(--MID(AI16,FIND("-",AI16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AI16,FIND("-",AI16)-1),""))=(AW16))+2*((IFERROR(--MID(AI16,FIND("-",AI16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL16" s="11" t="str">
+      <c r="AL16" s="11">
         <f>IF(OR($C16="",AK16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK16,FIND("-",AK16)-1),"")=AW16,IFERROR(--MID(AK16,FIND("-",AK16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AK16,FIND("-",AK16)-1),""))-(IFERROR(--MID(AK16,FIND("-",AK16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AK16,FIND("-",AK16)-1),""))-(IFERROR(--MID(AK16,FIND("-",AK16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AK16,FIND("-",AK16)-1),""))=(AW16))+2*((IFERROR(--MID(AK16,FIND("-",AK16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN16" s="11" t="str">
+      <c r="AN16" s="11">
         <f>IF(OR($C16="",AM16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM16,FIND("-",AM16)-1),"")=AW16,IFERROR(--MID(AM16,FIND("-",AM16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AM16,FIND("-",AM16)-1),""))-(IFERROR(--MID(AM16,FIND("-",AM16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AM16,FIND("-",AM16)-1),""))-(IFERROR(--MID(AM16,FIND("-",AM16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AM16,FIND("-",AM16)-1),""))=(AW16))+2*((IFERROR(--MID(AM16,FIND("-",AM16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP16" s="11" t="str">
+      <c r="AP16" s="11">
         <f>IF(OR($C16="",AO16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO16,FIND("-",AO16)-1),"")=AW16,IFERROR(--MID(AO16,FIND("-",AO16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AO16,FIND("-",AO16)-1),""))-(IFERROR(--MID(AO16,FIND("-",AO16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AO16,FIND("-",AO16)-1),""))-(IFERROR(--MID(AO16,FIND("-",AO16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AO16,FIND("-",AO16)-1),""))=(AW16))+2*((IFERROR(--MID(AO16,FIND("-",AO16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR16" s="11" t="str">
+      <c r="AR16" s="11">
         <f t="shared" ref="AR16:AR21" si="0">IF(OR($C16="",AQ16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ16,FIND("-",AQ16)-1),"")=AW16,IFERROR(--MID(AQ16,FIND("-",AQ16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AQ16,FIND("-",AQ16)-1),""))-(IFERROR(--MID(AQ16,FIND("-",AQ16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AQ16,FIND("-",AQ16)-1),""))-(IFERROR(--MID(AQ16,FIND("-",AQ16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AQ16,FIND("-",AQ16)-1),""))=(AW16))+2*((IFERROR(--MID(AQ16,FIND("-",AQ16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AT16" s="11" t="str">
+      <c r="AT16" s="11">
         <f t="shared" ref="AT16:AT21" si="1">IF(OR($C16="",AS16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS16,FIND("-",AS16)-1),"")=AW16,IFERROR(--MID(AS16,FIND("-",AS16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AS16,FIND("-",AS16)-1),""))-(IFERROR(--MID(AS16,FIND("-",AS16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AS16,FIND("-",AS16)-1),""))-(IFERROR(--MID(AS16,FIND("-",AS16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AS16,FIND("-",AS16)-1),""))=(AW16))+2*((IFERROR(--MID(AS16,FIND("-",AS16)+1,99),""))=(AX16))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU16" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AV16" s="11" t="str">
+      <c r="AV16" s="11">
         <f>IF(OR($C16="",AU16=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU16,FIND("-",AU16)-1),"")=AW16,IFERROR(--MID(AU16,FIND("-",AU16)+1,99),"")=AX16),10,5*(SIGN((IFERROR(--LEFT(AU16,FIND("-",AU16)-1),""))-(IFERROR(--MID(AU16,FIND("-",AU16)+1,99),"")))=SIGN((AW16)-(AX16)))+2*(((IFERROR(--LEFT(AU16,FIND("-",AU16)-1),""))-(IFERROR(--MID(AU16,FIND("-",AU16)+1,99),"")))=((AW16)-(AX16)))+2*((IFERROR(--LEFT(AU16,FIND("-",AU16)-1),""))=(AW16))+2*((IFERROR(--MID(AU16,FIND("-",AU16)+1,99),""))=(AX16))),""))</f>
-        <v/>
-      </c>
-      <c r="AW16" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW16" s="11">
         <f>IF($C16="","",IFERROR(--LEFT($C16,FIND("-",$C16)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX16" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX16" s="11">
         <f>IF($C16="","",IFERROR(--MID($C16,FIND("-",$C16)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3477,171 +3488,173 @@
       <c r="B17" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D17" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="11" t="str">
+      <c r="F17" s="11">
         <f>IF(OR($C17="",E17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E17,FIND("-",E17)-1),"")=AW17,IFERROR(--MID(E17,FIND("-",E17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(E17,FIND("-",E17)-1),""))-(IFERROR(--MID(E17,FIND("-",E17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(E17,FIND("-",E17)-1),""))-(IFERROR(--MID(E17,FIND("-",E17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(E17,FIND("-",E17)-1),""))=(AW17))+2*((IFERROR(--MID(E17,FIND("-",E17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="11" t="str">
+      <c r="H17" s="11">
         <f>IF(OR($C17="",G17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G17,FIND("-",G17)-1),"")=AW17,IFERROR(--MID(G17,FIND("-",G17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(G17,FIND("-",G17)-1),""))-(IFERROR(--MID(G17,FIND("-",G17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(G17,FIND("-",G17)-1),""))-(IFERROR(--MID(G17,FIND("-",G17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(G17,FIND("-",G17)-1),""))=(AW17))+2*((IFERROR(--MID(G17,FIND("-",G17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="11" t="str">
+      <c r="J17" s="11">
         <f>IF(OR($C17="",I17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I17,FIND("-",I17)-1),"")=AW17,IFERROR(--MID(I17,FIND("-",I17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(I17,FIND("-",I17)-1),""))-(IFERROR(--MID(I17,FIND("-",I17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(I17,FIND("-",I17)-1),""))-(IFERROR(--MID(I17,FIND("-",I17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(I17,FIND("-",I17)-1),""))=(AW17))+2*((IFERROR(--MID(I17,FIND("-",I17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L17" s="11" t="str">
+      <c r="L17" s="11">
         <f>IF(OR($C17="",K17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K17,FIND("-",K17)-1),"")=AW17,IFERROR(--MID(K17,FIND("-",K17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(K17,FIND("-",K17)-1),""))-(IFERROR(--MID(K17,FIND("-",K17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(K17,FIND("-",K17)-1),""))-(IFERROR(--MID(K17,FIND("-",K17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(K17,FIND("-",K17)-1),""))=(AW17))+2*((IFERROR(--MID(K17,FIND("-",K17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="N17" s="11" t="str">
+      <c r="N17" s="11">
         <f>IF(OR($C17="",M17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M17,FIND("-",M17)-1),"")=AW17,IFERROR(--MID(M17,FIND("-",M17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(M17,FIND("-",M17)-1),""))-(IFERROR(--MID(M17,FIND("-",M17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(M17,FIND("-",M17)-1),""))-(IFERROR(--MID(M17,FIND("-",M17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(M17,FIND("-",M17)-1),""))=(AW17))+2*((IFERROR(--MID(M17,FIND("-",M17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="P17" s="11" t="str">
+      <c r="P17" s="11">
         <f>IF(OR($C17="",O17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O17,FIND("-",O17)-1),"")=AW17,IFERROR(--MID(O17,FIND("-",O17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(O17,FIND("-",O17)-1),""))-(IFERROR(--MID(O17,FIND("-",O17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(O17,FIND("-",O17)-1),""))-(IFERROR(--MID(O17,FIND("-",O17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(O17,FIND("-",O17)-1),""))=(AW17))+2*((IFERROR(--MID(O17,FIND("-",O17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="R17" s="11" t="str">
+      <c r="R17" s="11">
         <f>IF(OR($C17="",Q17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q17,FIND("-",Q17)-1),"")=AW17,IFERROR(--MID(Q17,FIND("-",Q17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(Q17,FIND("-",Q17)-1),""))-(IFERROR(--MID(Q17,FIND("-",Q17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(Q17,FIND("-",Q17)-1),""))-(IFERROR(--MID(Q17,FIND("-",Q17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(Q17,FIND("-",Q17)-1),""))=(AW17))+2*((IFERROR(--MID(Q17,FIND("-",Q17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T17" s="11" t="str">
+      <c r="T17" s="11">
         <f>IF(OR($C17="",S17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S17,FIND("-",S17)-1),"")=AW17,IFERROR(--MID(S17,FIND("-",S17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(S17,FIND("-",S17)-1),""))-(IFERROR(--MID(S17,FIND("-",S17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(S17,FIND("-",S17)-1),""))-(IFERROR(--MID(S17,FIND("-",S17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(S17,FIND("-",S17)-1),""))=(AW17))+2*((IFERROR(--MID(S17,FIND("-",S17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V17" s="11" t="str">
+      <c r="V17" s="11">
         <f>IF(OR($C17="",U17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U17,FIND("-",U17)-1),"")=AW17,IFERROR(--MID(U17,FIND("-",U17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(U17,FIND("-",U17)-1),""))-(IFERROR(--MID(U17,FIND("-",U17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(U17,FIND("-",U17)-1),""))-(IFERROR(--MID(U17,FIND("-",U17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(U17,FIND("-",U17)-1),""))=(AW17))+2*((IFERROR(--MID(U17,FIND("-",U17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X17" s="11" t="str">
+      <c r="X17" s="11">
         <f>IF(OR($C17="",W17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W17,FIND("-",W17)-1),"")=AW17,IFERROR(--MID(W17,FIND("-",W17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(W17,FIND("-",W17)-1),""))-(IFERROR(--MID(W17,FIND("-",W17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(W17,FIND("-",W17)-1),""))-(IFERROR(--MID(W17,FIND("-",W17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(W17,FIND("-",W17)-1),""))=(AW17))+2*((IFERROR(--MID(W17,FIND("-",W17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z17" s="11" t="str">
+      <c r="Z17" s="11">
         <f>IF(OR($C17="",Y17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y17,FIND("-",Y17)-1),"")=AW17,IFERROR(--MID(Y17,FIND("-",Y17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(Y17,FIND("-",Y17)-1),""))-(IFERROR(--MID(Y17,FIND("-",Y17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(Y17,FIND("-",Y17)-1),""))-(IFERROR(--MID(Y17,FIND("-",Y17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(Y17,FIND("-",Y17)-1),""))=(AW17))+2*((IFERROR(--MID(Y17,FIND("-",Y17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AB17" s="11" t="str">
+      <c r="AB17" s="11">
         <f>IF(OR($C17="",AA17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA17,FIND("-",AA17)-1),"")=AW17,IFERROR(--MID(AA17,FIND("-",AA17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AA17,FIND("-",AA17)-1),""))-(IFERROR(--MID(AA17,FIND("-",AA17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AA17,FIND("-",AA17)-1),""))-(IFERROR(--MID(AA17,FIND("-",AA17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AA17,FIND("-",AA17)-1),""))=(AW17))+2*((IFERROR(--MID(AA17,FIND("-",AA17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AD17" s="11" t="str">
+      <c r="AD17" s="11">
         <f>IF(OR($C17="",AC17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC17,FIND("-",AC17)-1),"")=AW17,IFERROR(--MID(AC17,FIND("-",AC17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AC17,FIND("-",AC17)-1),""))-(IFERROR(--MID(AC17,FIND("-",AC17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AC17,FIND("-",AC17)-1),""))-(IFERROR(--MID(AC17,FIND("-",AC17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AC17,FIND("-",AC17)-1),""))=(AW17))+2*((IFERROR(--MID(AC17,FIND("-",AC17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AF17" s="11" t="str">
+      <c r="AF17" s="11">
         <f>IF(OR($C17="",AE17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE17,FIND("-",AE17)-1),"")=AW17,IFERROR(--MID(AE17,FIND("-",AE17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AE17,FIND("-",AE17)-1),""))-(IFERROR(--MID(AE17,FIND("-",AE17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AE17,FIND("-",AE17)-1),""))-(IFERROR(--MID(AE17,FIND("-",AE17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AE17,FIND("-",AE17)-1),""))=(AW17))+2*((IFERROR(--MID(AE17,FIND("-",AE17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AH17" s="11" t="str">
+      <c r="AH17" s="11">
         <f>IF(OR($C17="",AG17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG17,FIND("-",AG17)-1),"")=AW17,IFERROR(--MID(AG17,FIND("-",AG17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AG17,FIND("-",AG17)-1),""))-(IFERROR(--MID(AG17,FIND("-",AG17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AG17,FIND("-",AG17)-1),""))-(IFERROR(--MID(AG17,FIND("-",AG17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AG17,FIND("-",AG17)-1),""))=(AW17))+2*((IFERROR(--MID(AG17,FIND("-",AG17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AJ17" s="11" t="str">
+      <c r="AJ17" s="11">
         <f>IF(OR($C17="",AI17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI17,FIND("-",AI17)-1),"")=AW17,IFERROR(--MID(AI17,FIND("-",AI17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AI17,FIND("-",AI17)-1),""))-(IFERROR(--MID(AI17,FIND("-",AI17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AI17,FIND("-",AI17)-1),""))-(IFERROR(--MID(AI17,FIND("-",AI17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AI17,FIND("-",AI17)-1),""))=(AW17))+2*((IFERROR(--MID(AI17,FIND("-",AI17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL17" s="11" t="str">
+      <c r="AL17" s="11">
         <f>IF(OR($C17="",AK17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK17,FIND("-",AK17)-1),"")=AW17,IFERROR(--MID(AK17,FIND("-",AK17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AK17,FIND("-",AK17)-1),""))-(IFERROR(--MID(AK17,FIND("-",AK17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AK17,FIND("-",AK17)-1),""))-(IFERROR(--MID(AK17,FIND("-",AK17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AK17,FIND("-",AK17)-1),""))=(AW17))+2*((IFERROR(--MID(AK17,FIND("-",AK17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN17" s="11" t="str">
+      <c r="AN17" s="11">
         <f>IF(OR($C17="",AM17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM17,FIND("-",AM17)-1),"")=AW17,IFERROR(--MID(AM17,FIND("-",AM17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AM17,FIND("-",AM17)-1),""))-(IFERROR(--MID(AM17,FIND("-",AM17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AM17,FIND("-",AM17)-1),""))-(IFERROR(--MID(AM17,FIND("-",AM17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AM17,FIND("-",AM17)-1),""))=(AW17))+2*((IFERROR(--MID(AM17,FIND("-",AM17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AP17" s="11" t="str">
+      <c r="AP17" s="11">
         <f>IF(OR($C17="",AO17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO17,FIND("-",AO17)-1),"")=AW17,IFERROR(--MID(AO17,FIND("-",AO17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AO17,FIND("-",AO17)-1),""))-(IFERROR(--MID(AO17,FIND("-",AO17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AO17,FIND("-",AO17)-1),""))-(IFERROR(--MID(AO17,FIND("-",AO17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AO17,FIND("-",AO17)-1),""))=(AW17))+2*((IFERROR(--MID(AO17,FIND("-",AO17)+1,99),""))=(AX17))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR17" s="11" t="str">
+      <c r="AR17" s="11">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AT17" s="11" t="str">
+      <c r="AT17" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV17" s="11" t="str">
+      <c r="AV17" s="11">
         <f>IF(OR($C17="",AU17=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU17,FIND("-",AU17)-1),"")=AW17,IFERROR(--MID(AU17,FIND("-",AU17)+1,99),"")=AX17),10,5*(SIGN((IFERROR(--LEFT(AU17,FIND("-",AU17)-1),""))-(IFERROR(--MID(AU17,FIND("-",AU17)+1,99),"")))=SIGN((AW17)-(AX17)))+2*(((IFERROR(--LEFT(AU17,FIND("-",AU17)-1),""))-(IFERROR(--MID(AU17,FIND("-",AU17)+1,99),"")))=((AW17)-(AX17)))+2*((IFERROR(--LEFT(AU17,FIND("-",AU17)-1),""))=(AW17))+2*((IFERROR(--MID(AU17,FIND("-",AU17)+1,99),""))=(AX17))),""))</f>
-        <v/>
-      </c>
-      <c r="AW17" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW17" s="11">
         <f>IF($C17="","",IFERROR(--LEFT($C17,FIND("-",$C17)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX17" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="11">
         <f>IF($C17="","",IFERROR(--MID($C17,FIND("-",$C17)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3651,171 +3664,173 @@
       <c r="B18" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="D18" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="11" t="str">
+      <c r="F18" s="11">
         <f>IF(OR($C18="",E18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E18,FIND("-",E18)-1),"")=AW18,IFERROR(--MID(E18,FIND("-",E18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(E18,FIND("-",E18)-1),""))-(IFERROR(--MID(E18,FIND("-",E18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(E18,FIND("-",E18)-1),""))-(IFERROR(--MID(E18,FIND("-",E18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(E18,FIND("-",E18)-1),""))=(AW18))+2*((IFERROR(--MID(E18,FIND("-",E18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="11" t="str">
+      <c r="H18" s="11">
         <f>IF(OR($C18="",G18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G18,FIND("-",G18)-1),"")=AW18,IFERROR(--MID(G18,FIND("-",G18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(G18,FIND("-",G18)-1),""))-(IFERROR(--MID(G18,FIND("-",G18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(G18,FIND("-",G18)-1),""))-(IFERROR(--MID(G18,FIND("-",G18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(G18,FIND("-",G18)-1),""))=(AW18))+2*((IFERROR(--MID(G18,FIND("-",G18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="11" t="str">
+      <c r="J18" s="11">
         <f>IF(OR($C18="",I18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I18,FIND("-",I18)-1),"")=AW18,IFERROR(--MID(I18,FIND("-",I18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(I18,FIND("-",I18)-1),""))-(IFERROR(--MID(I18,FIND("-",I18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(I18,FIND("-",I18)-1),""))-(IFERROR(--MID(I18,FIND("-",I18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(I18,FIND("-",I18)-1),""))=(AW18))+2*((IFERROR(--MID(I18,FIND("-",I18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L18" s="11" t="str">
+      <c r="L18" s="11">
         <f>IF(OR($C18="",K18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K18,FIND("-",K18)-1),"")=AW18,IFERROR(--MID(K18,FIND("-",K18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(K18,FIND("-",K18)-1),""))-(IFERROR(--MID(K18,FIND("-",K18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(K18,FIND("-",K18)-1),""))-(IFERROR(--MID(K18,FIND("-",K18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(K18,FIND("-",K18)-1),""))=(AW18))+2*((IFERROR(--MID(K18,FIND("-",K18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="N18" s="11" t="str">
+      <c r="N18" s="11">
         <f>IF(OR($C18="",M18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M18,FIND("-",M18)-1),"")=AW18,IFERROR(--MID(M18,FIND("-",M18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(M18,FIND("-",M18)-1),""))-(IFERROR(--MID(M18,FIND("-",M18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(M18,FIND("-",M18)-1),""))-(IFERROR(--MID(M18,FIND("-",M18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(M18,FIND("-",M18)-1),""))=(AW18))+2*((IFERROR(--MID(M18,FIND("-",M18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P18" s="11" t="str">
+      <c r="P18" s="11">
         <f>IF(OR($C18="",O18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O18,FIND("-",O18)-1),"")=AW18,IFERROR(--MID(O18,FIND("-",O18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(O18,FIND("-",O18)-1),""))-(IFERROR(--MID(O18,FIND("-",O18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(O18,FIND("-",O18)-1),""))-(IFERROR(--MID(O18,FIND("-",O18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(O18,FIND("-",O18)-1),""))=(AW18))+2*((IFERROR(--MID(O18,FIND("-",O18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q18" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="R18" s="11" t="str">
+      <c r="R18" s="11">
         <f>IF(OR($C18="",Q18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q18,FIND("-",Q18)-1),"")=AW18,IFERROR(--MID(Q18,FIND("-",Q18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(Q18,FIND("-",Q18)-1),""))-(IFERROR(--MID(Q18,FIND("-",Q18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(Q18,FIND("-",Q18)-1),""))-(IFERROR(--MID(Q18,FIND("-",Q18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(Q18,FIND("-",Q18)-1),""))=(AW18))+2*((IFERROR(--MID(Q18,FIND("-",Q18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T18" s="11" t="str">
+      <c r="T18" s="11">
         <f>IF(OR($C18="",S18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S18,FIND("-",S18)-1),"")=AW18,IFERROR(--MID(S18,FIND("-",S18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(S18,FIND("-",S18)-1),""))-(IFERROR(--MID(S18,FIND("-",S18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(S18,FIND("-",S18)-1),""))-(IFERROR(--MID(S18,FIND("-",S18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(S18,FIND("-",S18)-1),""))=(AW18))+2*((IFERROR(--MID(S18,FIND("-",S18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="V18" s="11" t="str">
+      <c r="V18" s="11">
         <f>IF(OR($C18="",U18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U18,FIND("-",U18)-1),"")=AW18,IFERROR(--MID(U18,FIND("-",U18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(U18,FIND("-",U18)-1),""))-(IFERROR(--MID(U18,FIND("-",U18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(U18,FIND("-",U18)-1),""))-(IFERROR(--MID(U18,FIND("-",U18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(U18,FIND("-",U18)-1),""))=(AW18))+2*((IFERROR(--MID(U18,FIND("-",U18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X18" s="11" t="str">
+      <c r="X18" s="11">
         <f>IF(OR($C18="",W18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W18,FIND("-",W18)-1),"")=AW18,IFERROR(--MID(W18,FIND("-",W18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(W18,FIND("-",W18)-1),""))-(IFERROR(--MID(W18,FIND("-",W18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(W18,FIND("-",W18)-1),""))-(IFERROR(--MID(W18,FIND("-",W18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(W18,FIND("-",W18)-1),""))=(AW18))+2*((IFERROR(--MID(W18,FIND("-",W18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y18" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z18" s="11" t="str">
+      <c r="Z18" s="11">
         <f>IF(OR($C18="",Y18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y18,FIND("-",Y18)-1),"")=AW18,IFERROR(--MID(Y18,FIND("-",Y18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(Y18,FIND("-",Y18)-1),""))-(IFERROR(--MID(Y18,FIND("-",Y18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(Y18,FIND("-",Y18)-1),""))-(IFERROR(--MID(Y18,FIND("-",Y18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(Y18,FIND("-",Y18)-1),""))=(AW18))+2*((IFERROR(--MID(Y18,FIND("-",Y18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA18" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AB18" s="11" t="str">
+      <c r="AB18" s="11">
         <f>IF(OR($C18="",AA18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA18,FIND("-",AA18)-1),"")=AW18,IFERROR(--MID(AA18,FIND("-",AA18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AA18,FIND("-",AA18)-1),""))-(IFERROR(--MID(AA18,FIND("-",AA18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AA18,FIND("-",AA18)-1),""))-(IFERROR(--MID(AA18,FIND("-",AA18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AA18,FIND("-",AA18)-1),""))=(AW18))+2*((IFERROR(--MID(AA18,FIND("-",AA18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AD18" s="11" t="str">
+      <c r="AD18" s="11">
         <f>IF(OR($C18="",AC18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC18,FIND("-",AC18)-1),"")=AW18,IFERROR(--MID(AC18,FIND("-",AC18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AC18,FIND("-",AC18)-1),""))-(IFERROR(--MID(AC18,FIND("-",AC18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AC18,FIND("-",AC18)-1),""))-(IFERROR(--MID(AC18,FIND("-",AC18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AC18,FIND("-",AC18)-1),""))=(AW18))+2*((IFERROR(--MID(AC18,FIND("-",AC18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF18" s="11" t="str">
+      <c r="AF18" s="11">
         <f>IF(OR($C18="",AE18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE18,FIND("-",AE18)-1),"")=AW18,IFERROR(--MID(AE18,FIND("-",AE18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AE18,FIND("-",AE18)-1),""))-(IFERROR(--MID(AE18,FIND("-",AE18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AE18,FIND("-",AE18)-1),""))-(IFERROR(--MID(AE18,FIND("-",AE18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AE18,FIND("-",AE18)-1),""))=(AW18))+2*((IFERROR(--MID(AE18,FIND("-",AE18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AH18" s="11" t="str">
+      <c r="AH18" s="11">
         <f>IF(OR($C18="",AG18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG18,FIND("-",AG18)-1),"")=AW18,IFERROR(--MID(AG18,FIND("-",AG18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AG18,FIND("-",AG18)-1),""))-(IFERROR(--MID(AG18,FIND("-",AG18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AG18,FIND("-",AG18)-1),""))-(IFERROR(--MID(AG18,FIND("-",AG18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AG18,FIND("-",AG18)-1),""))=(AW18))+2*((IFERROR(--MID(AG18,FIND("-",AG18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AJ18" s="11" t="str">
+      <c r="AJ18" s="11">
         <f>IF(OR($C18="",AI18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI18,FIND("-",AI18)-1),"")=AW18,IFERROR(--MID(AI18,FIND("-",AI18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AI18,FIND("-",AI18)-1),""))-(IFERROR(--MID(AI18,FIND("-",AI18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AI18,FIND("-",AI18)-1),""))-(IFERROR(--MID(AI18,FIND("-",AI18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AI18,FIND("-",AI18)-1),""))=(AW18))+2*((IFERROR(--MID(AI18,FIND("-",AI18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL18" s="11" t="str">
+      <c r="AL18" s="11">
         <f>IF(OR($C18="",AK18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK18,FIND("-",AK18)-1),"")=AW18,IFERROR(--MID(AK18,FIND("-",AK18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AK18,FIND("-",AK18)-1),""))-(IFERROR(--MID(AK18,FIND("-",AK18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AK18,FIND("-",AK18)-1),""))-(IFERROR(--MID(AK18,FIND("-",AK18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AK18,FIND("-",AK18)-1),""))=(AW18))+2*((IFERROR(--MID(AK18,FIND("-",AK18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN18" s="11" t="str">
+      <c r="AN18" s="11">
         <f>IF(OR($C18="",AM18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM18,FIND("-",AM18)-1),"")=AW18,IFERROR(--MID(AM18,FIND("-",AM18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AM18,FIND("-",AM18)-1),""))-(IFERROR(--MID(AM18,FIND("-",AM18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AM18,FIND("-",AM18)-1),""))-(IFERROR(--MID(AM18,FIND("-",AM18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AM18,FIND("-",AM18)-1),""))=(AW18))+2*((IFERROR(--MID(AM18,FIND("-",AM18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO18" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AP18" s="11" t="str">
+      <c r="AP18" s="11">
         <f>IF(OR($C18="",AO18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO18,FIND("-",AO18)-1),"")=AW18,IFERROR(--MID(AO18,FIND("-",AO18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AO18,FIND("-",AO18)-1),""))-(IFERROR(--MID(AO18,FIND("-",AO18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AO18,FIND("-",AO18)-1),""))-(IFERROR(--MID(AO18,FIND("-",AO18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AO18,FIND("-",AO18)-1),""))=(AW18))+2*((IFERROR(--MID(AO18,FIND("-",AO18)+1,99),""))=(AX18))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR18" s="11" t="str">
+      <c r="AR18" s="11">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS18" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AT18" s="11" t="str">
+      <c r="AT18" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU18" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AV18" s="11" t="str">
+      <c r="AV18" s="11">
         <f>IF(OR($C18="",AU18=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU18,FIND("-",AU18)-1),"")=AW18,IFERROR(--MID(AU18,FIND("-",AU18)+1,99),"")=AX18),10,5*(SIGN((IFERROR(--LEFT(AU18,FIND("-",AU18)-1),""))-(IFERROR(--MID(AU18,FIND("-",AU18)+1,99),"")))=SIGN((AW18)-(AX18)))+2*(((IFERROR(--LEFT(AU18,FIND("-",AU18)-1),""))-(IFERROR(--MID(AU18,FIND("-",AU18)+1,99),"")))=((AW18)-(AX18)))+2*((IFERROR(--LEFT(AU18,FIND("-",AU18)-1),""))=(AW18))+2*((IFERROR(--MID(AU18,FIND("-",AU18)+1,99),""))=(AX18))),""))</f>
-        <v/>
-      </c>
-      <c r="AW18" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="11">
         <f>IF($C18="","",IFERROR(--LEFT($C18,FIND("-",$C18)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX18" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX18" s="11">
         <f>IF($C18="","",IFERROR(--MID($C18,FIND("-",$C18)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3825,171 +3840,173 @@
       <c r="B19" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="10" t="s">
+        <v>329</v>
+      </c>
       <c r="D19" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="11" t="str">
+      <c r="F19" s="11">
         <f>IF(OR($C19="",E19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E19,FIND("-",E19)-1),"")=AW19,IFERROR(--MID(E19,FIND("-",E19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(E19,FIND("-",E19)-1),""))-(IFERROR(--MID(E19,FIND("-",E19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(E19,FIND("-",E19)-1),""))-(IFERROR(--MID(E19,FIND("-",E19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(E19,FIND("-",E19)-1),""))=(AW19))+2*((IFERROR(--MID(E19,FIND("-",E19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="11" t="str">
+      <c r="H19" s="11">
         <f>IF(OR($C19="",G19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G19,FIND("-",G19)-1),"")=AW19,IFERROR(--MID(G19,FIND("-",G19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(G19,FIND("-",G19)-1),""))-(IFERROR(--MID(G19,FIND("-",G19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(G19,FIND("-",G19)-1),""))-(IFERROR(--MID(G19,FIND("-",G19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(G19,FIND("-",G19)-1),""))=(AW19))+2*((IFERROR(--MID(G19,FIND("-",G19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J19" s="11" t="str">
+      <c r="J19" s="11">
         <f>IF(OR($C19="",I19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I19,FIND("-",I19)-1),"")=AW19,IFERROR(--MID(I19,FIND("-",I19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(I19,FIND("-",I19)-1),""))-(IFERROR(--MID(I19,FIND("-",I19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(I19,FIND("-",I19)-1),""))-(IFERROR(--MID(I19,FIND("-",I19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(I19,FIND("-",I19)-1),""))=(AW19))+2*((IFERROR(--MID(I19,FIND("-",I19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="L19" s="11" t="str">
+      <c r="L19" s="11">
         <f>IF(OR($C19="",K19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K19,FIND("-",K19)-1),"")=AW19,IFERROR(--MID(K19,FIND("-",K19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(K19,FIND("-",K19)-1),""))-(IFERROR(--MID(K19,FIND("-",K19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(K19,FIND("-",K19)-1),""))-(IFERROR(--MID(K19,FIND("-",K19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(K19,FIND("-",K19)-1),""))=(AW19))+2*((IFERROR(--MID(K19,FIND("-",K19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M19" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="N19" s="11" t="str">
+      <c r="N19" s="11">
         <f>IF(OR($C19="",M19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M19,FIND("-",M19)-1),"")=AW19,IFERROR(--MID(M19,FIND("-",M19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(M19,FIND("-",M19)-1),""))-(IFERROR(--MID(M19,FIND("-",M19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(M19,FIND("-",M19)-1),""))-(IFERROR(--MID(M19,FIND("-",M19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(M19,FIND("-",M19)-1),""))=(AW19))+2*((IFERROR(--MID(M19,FIND("-",M19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="P19" s="11" t="str">
+      <c r="P19" s="11">
         <f>IF(OR($C19="",O19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O19,FIND("-",O19)-1),"")=AW19,IFERROR(--MID(O19,FIND("-",O19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(O19,FIND("-",O19)-1),""))-(IFERROR(--MID(O19,FIND("-",O19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(O19,FIND("-",O19)-1),""))-(IFERROR(--MID(O19,FIND("-",O19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(O19,FIND("-",O19)-1),""))=(AW19))+2*((IFERROR(--MID(O19,FIND("-",O19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R19" s="11" t="str">
+      <c r="R19" s="11">
         <f>IF(OR($C19="",Q19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q19,FIND("-",Q19)-1),"")=AW19,IFERROR(--MID(Q19,FIND("-",Q19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(Q19,FIND("-",Q19)-1),""))-(IFERROR(--MID(Q19,FIND("-",Q19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(Q19,FIND("-",Q19)-1),""))-(IFERROR(--MID(Q19,FIND("-",Q19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(Q19,FIND("-",Q19)-1),""))=(AW19))+2*((IFERROR(--MID(Q19,FIND("-",Q19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T19" s="11" t="str">
+      <c r="T19" s="11">
         <f>IF(OR($C19="",S19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S19,FIND("-",S19)-1),"")=AW19,IFERROR(--MID(S19,FIND("-",S19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(S19,FIND("-",S19)-1),""))-(IFERROR(--MID(S19,FIND("-",S19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(S19,FIND("-",S19)-1),""))-(IFERROR(--MID(S19,FIND("-",S19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(S19,FIND("-",S19)-1),""))=(AW19))+2*((IFERROR(--MID(S19,FIND("-",S19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V19" s="11" t="str">
+      <c r="V19" s="11">
         <f>IF(OR($C19="",U19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U19,FIND("-",U19)-1),"")=AW19,IFERROR(--MID(U19,FIND("-",U19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(U19,FIND("-",U19)-1),""))-(IFERROR(--MID(U19,FIND("-",U19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(U19,FIND("-",U19)-1),""))-(IFERROR(--MID(U19,FIND("-",U19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(U19,FIND("-",U19)-1),""))=(AW19))+2*((IFERROR(--MID(U19,FIND("-",U19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="W19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="X19" s="11" t="str">
+      <c r="X19" s="11">
         <f>IF(OR($C19="",W19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W19,FIND("-",W19)-1),"")=AW19,IFERROR(--MID(W19,FIND("-",W19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(W19,FIND("-",W19)-1),""))-(IFERROR(--MID(W19,FIND("-",W19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(W19,FIND("-",W19)-1),""))-(IFERROR(--MID(W19,FIND("-",W19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(W19,FIND("-",W19)-1),""))=(AW19))+2*((IFERROR(--MID(W19,FIND("-",W19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y19" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z19" s="11" t="str">
+      <c r="Z19" s="11">
         <f>IF(OR($C19="",Y19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y19,FIND("-",Y19)-1),"")=AW19,IFERROR(--MID(Y19,FIND("-",Y19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(Y19,FIND("-",Y19)-1),""))-(IFERROR(--MID(Y19,FIND("-",Y19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(Y19,FIND("-",Y19)-1),""))-(IFERROR(--MID(Y19,FIND("-",Y19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(Y19,FIND("-",Y19)-1),""))=(AW19))+2*((IFERROR(--MID(Y19,FIND("-",Y19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AB19" s="11" t="str">
+      <c r="AB19" s="11">
         <f>IF(OR($C19="",AA19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA19,FIND("-",AA19)-1),"")=AW19,IFERROR(--MID(AA19,FIND("-",AA19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AA19,FIND("-",AA19)-1),""))-(IFERROR(--MID(AA19,FIND("-",AA19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AA19,FIND("-",AA19)-1),""))-(IFERROR(--MID(AA19,FIND("-",AA19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AA19,FIND("-",AA19)-1),""))=(AW19))+2*((IFERROR(--MID(AA19,FIND("-",AA19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD19" s="11" t="str">
+      <c r="AD19" s="11">
         <f>IF(OR($C19="",AC19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC19,FIND("-",AC19)-1),"")=AW19,IFERROR(--MID(AC19,FIND("-",AC19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AC19,FIND("-",AC19)-1),""))-(IFERROR(--MID(AC19,FIND("-",AC19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AC19,FIND("-",AC19)-1),""))-(IFERROR(--MID(AC19,FIND("-",AC19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AC19,FIND("-",AC19)-1),""))=(AW19))+2*((IFERROR(--MID(AC19,FIND("-",AC19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AF19" s="11" t="str">
+      <c r="AF19" s="11">
         <f>IF(OR($C19="",AE19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE19,FIND("-",AE19)-1),"")=AW19,IFERROR(--MID(AE19,FIND("-",AE19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AE19,FIND("-",AE19)-1),""))-(IFERROR(--MID(AE19,FIND("-",AE19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AE19,FIND("-",AE19)-1),""))-(IFERROR(--MID(AE19,FIND("-",AE19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AE19,FIND("-",AE19)-1),""))=(AW19))+2*((IFERROR(--MID(AE19,FIND("-",AE19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AG19" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH19" s="11" t="str">
+      <c r="AH19" s="11">
         <f>IF(OR($C19="",AG19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG19,FIND("-",AG19)-1),"")=AW19,IFERROR(--MID(AG19,FIND("-",AG19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AG19,FIND("-",AG19)-1),""))-(IFERROR(--MID(AG19,FIND("-",AG19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AG19,FIND("-",AG19)-1),""))-(IFERROR(--MID(AG19,FIND("-",AG19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AG19,FIND("-",AG19)-1),""))=(AW19))+2*((IFERROR(--MID(AG19,FIND("-",AG19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI19" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AJ19" s="11" t="str">
+      <c r="AJ19" s="11">
         <f>IF(OR($C19="",AI19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI19,FIND("-",AI19)-1),"")=AW19,IFERROR(--MID(AI19,FIND("-",AI19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AI19,FIND("-",AI19)-1),""))-(IFERROR(--MID(AI19,FIND("-",AI19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AI19,FIND("-",AI19)-1),""))-(IFERROR(--MID(AI19,FIND("-",AI19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AI19,FIND("-",AI19)-1),""))=(AW19))+2*((IFERROR(--MID(AI19,FIND("-",AI19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AL19" s="11" t="str">
+      <c r="AL19" s="11">
         <f>IF(OR($C19="",AK19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK19,FIND("-",AK19)-1),"")=AW19,IFERROR(--MID(AK19,FIND("-",AK19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AK19,FIND("-",AK19)-1),""))-(IFERROR(--MID(AK19,FIND("-",AK19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AK19,FIND("-",AK19)-1),""))-(IFERROR(--MID(AK19,FIND("-",AK19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AK19,FIND("-",AK19)-1),""))=(AW19))+2*((IFERROR(--MID(AK19,FIND("-",AK19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AN19" s="11" t="str">
+      <c r="AN19" s="11">
         <f>IF(OR($C19="",AM19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM19,FIND("-",AM19)-1),"")=AW19,IFERROR(--MID(AM19,FIND("-",AM19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AM19,FIND("-",AM19)-1),""))-(IFERROR(--MID(AM19,FIND("-",AM19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AM19,FIND("-",AM19)-1),""))-(IFERROR(--MID(AM19,FIND("-",AM19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AM19,FIND("-",AM19)-1),""))=(AW19))+2*((IFERROR(--MID(AM19,FIND("-",AM19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AP19" s="11" t="str">
+      <c r="AP19" s="11">
         <f>IF(OR($C19="",AO19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO19,FIND("-",AO19)-1),"")=AW19,IFERROR(--MID(AO19,FIND("-",AO19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AO19,FIND("-",AO19)-1),""))-(IFERROR(--MID(AO19,FIND("-",AO19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AO19,FIND("-",AO19)-1),""))-(IFERROR(--MID(AO19,FIND("-",AO19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AO19,FIND("-",AO19)-1),""))=(AW19))+2*((IFERROR(--MID(AO19,FIND("-",AO19)+1,99),""))=(AX19))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AR19" s="11" t="str">
+      <c r="AR19" s="11">
         <f t="shared" si="0"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AT19" s="11" t="str">
+      <c r="AT19" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU19" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AV19" s="11" t="str">
+      <c r="AV19" s="11">
         <f>IF(OR($C19="",AU19=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU19,FIND("-",AU19)-1),"")=AW19,IFERROR(--MID(AU19,FIND("-",AU19)+1,99),"")=AX19),10,5*(SIGN((IFERROR(--LEFT(AU19,FIND("-",AU19)-1),""))-(IFERROR(--MID(AU19,FIND("-",AU19)+1,99),"")))=SIGN((AW19)-(AX19)))+2*(((IFERROR(--LEFT(AU19,FIND("-",AU19)-1),""))-(IFERROR(--MID(AU19,FIND("-",AU19)+1,99),"")))=((AW19)-(AX19)))+2*((IFERROR(--LEFT(AU19,FIND("-",AU19)-1),""))=(AW19))+2*((IFERROR(--MID(AU19,FIND("-",AU19)+1,99),""))=(AX19))),""))</f>
-        <v/>
-      </c>
-      <c r="AW19" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW19" s="11">
         <f>IF($C19="","",IFERROR(--LEFT($C19,FIND("-",$C19)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX19" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AX19" s="11">
         <f>IF($C19="","",IFERROR(--MID($C19,FIND("-",$C19)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3999,171 +4016,173 @@
       <c r="B20" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="11" t="str">
+      <c r="F20" s="11">
         <f>IF(OR($C20="",E20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E20,FIND("-",E20)-1),"")=AW20,IFERROR(--MID(E20,FIND("-",E20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(E20,FIND("-",E20)-1),""))-(IFERROR(--MID(E20,FIND("-",E20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(E20,FIND("-",E20)-1),""))-(IFERROR(--MID(E20,FIND("-",E20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(E20,FIND("-",E20)-1),""))=(AW20))+2*((IFERROR(--MID(E20,FIND("-",E20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="11" t="str">
+      <c r="H20" s="11">
         <f>IF(OR($C20="",G20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G20,FIND("-",G20)-1),"")=AW20,IFERROR(--MID(G20,FIND("-",G20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(G20,FIND("-",G20)-1),""))-(IFERROR(--MID(G20,FIND("-",G20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(G20,FIND("-",G20)-1),""))-(IFERROR(--MID(G20,FIND("-",G20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(G20,FIND("-",G20)-1),""))=(AW20))+2*((IFERROR(--MID(G20,FIND("-",G20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="11" t="str">
+      <c r="J20" s="11">
         <f>IF(OR($C20="",I20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I20,FIND("-",I20)-1),"")=AW20,IFERROR(--MID(I20,FIND("-",I20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(I20,FIND("-",I20)-1),""))-(IFERROR(--MID(I20,FIND("-",I20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(I20,FIND("-",I20)-1),""))-(IFERROR(--MID(I20,FIND("-",I20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(I20,FIND("-",I20)-1),""))=(AW20))+2*((IFERROR(--MID(I20,FIND("-",I20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L20" s="11" t="str">
+      <c r="L20" s="11">
         <f>IF(OR($C20="",K20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K20,FIND("-",K20)-1),"")=AW20,IFERROR(--MID(K20,FIND("-",K20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(K20,FIND("-",K20)-1),""))-(IFERROR(--MID(K20,FIND("-",K20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(K20,FIND("-",K20)-1),""))-(IFERROR(--MID(K20,FIND("-",K20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(K20,FIND("-",K20)-1),""))=(AW20))+2*((IFERROR(--MID(K20,FIND("-",K20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M20" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="N20" s="11" t="str">
+      <c r="N20" s="11">
         <f>IF(OR($C20="",M20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M20,FIND("-",M20)-1),"")=AW20,IFERROR(--MID(M20,FIND("-",M20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(M20,FIND("-",M20)-1),""))-(IFERROR(--MID(M20,FIND("-",M20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(M20,FIND("-",M20)-1),""))-(IFERROR(--MID(M20,FIND("-",M20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(M20,FIND("-",M20)-1),""))=(AW20))+2*((IFERROR(--MID(M20,FIND("-",M20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P20" s="11" t="str">
+      <c r="P20" s="11">
         <f>IF(OR($C20="",O20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O20,FIND("-",O20)-1),"")=AW20,IFERROR(--MID(O20,FIND("-",O20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(O20,FIND("-",O20)-1),""))-(IFERROR(--MID(O20,FIND("-",O20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(O20,FIND("-",O20)-1),""))-(IFERROR(--MID(O20,FIND("-",O20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(O20,FIND("-",O20)-1),""))=(AW20))+2*((IFERROR(--MID(O20,FIND("-",O20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q20" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="R20" s="11" t="str">
+      <c r="R20" s="11">
         <f>IF(OR($C20="",Q20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q20,FIND("-",Q20)-1),"")=AW20,IFERROR(--MID(Q20,FIND("-",Q20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(Q20,FIND("-",Q20)-1),""))-(IFERROR(--MID(Q20,FIND("-",Q20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(Q20,FIND("-",Q20)-1),""))-(IFERROR(--MID(Q20,FIND("-",Q20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(Q20,FIND("-",Q20)-1),""))=(AW20))+2*((IFERROR(--MID(Q20,FIND("-",Q20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S20" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T20" s="11" t="str">
+      <c r="T20" s="11">
         <f>IF(OR($C20="",S20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S20,FIND("-",S20)-1),"")=AW20,IFERROR(--MID(S20,FIND("-",S20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(S20,FIND("-",S20)-1),""))-(IFERROR(--MID(S20,FIND("-",S20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(S20,FIND("-",S20)-1),""))-(IFERROR(--MID(S20,FIND("-",S20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(S20,FIND("-",S20)-1),""))=(AW20))+2*((IFERROR(--MID(S20,FIND("-",S20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V20" s="11" t="str">
+      <c r="V20" s="11">
         <f>IF(OR($C20="",U20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U20,FIND("-",U20)-1),"")=AW20,IFERROR(--MID(U20,FIND("-",U20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(U20,FIND("-",U20)-1),""))-(IFERROR(--MID(U20,FIND("-",U20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(U20,FIND("-",U20)-1),""))-(IFERROR(--MID(U20,FIND("-",U20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(U20,FIND("-",U20)-1),""))=(AW20))+2*((IFERROR(--MID(U20,FIND("-",U20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X20" s="11" t="str">
+      <c r="X20" s="11">
         <f>IF(OR($C20="",W20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W20,FIND("-",W20)-1),"")=AW20,IFERROR(--MID(W20,FIND("-",W20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(W20,FIND("-",W20)-1),""))-(IFERROR(--MID(W20,FIND("-",W20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(W20,FIND("-",W20)-1),""))-(IFERROR(--MID(W20,FIND("-",W20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(W20,FIND("-",W20)-1),""))=(AW20))+2*((IFERROR(--MID(W20,FIND("-",W20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z20" s="11" t="str">
+      <c r="Z20" s="11">
         <f>IF(OR($C20="",Y20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y20,FIND("-",Y20)-1),"")=AW20,IFERROR(--MID(Y20,FIND("-",Y20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(Y20,FIND("-",Y20)-1),""))-(IFERROR(--MID(Y20,FIND("-",Y20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(Y20,FIND("-",Y20)-1),""))-(IFERROR(--MID(Y20,FIND("-",Y20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(Y20,FIND("-",Y20)-1),""))=(AW20))+2*((IFERROR(--MID(Y20,FIND("-",Y20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA20" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AB20" s="11" t="str">
+      <c r="AB20" s="11">
         <f>IF(OR($C20="",AA20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA20,FIND("-",AA20)-1),"")=AW20,IFERROR(--MID(AA20,FIND("-",AA20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AA20,FIND("-",AA20)-1),""))-(IFERROR(--MID(AA20,FIND("-",AA20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AA20,FIND("-",AA20)-1),""))-(IFERROR(--MID(AA20,FIND("-",AA20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AA20,FIND("-",AA20)-1),""))=(AW20))+2*((IFERROR(--MID(AA20,FIND("-",AA20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC20" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AD20" s="11" t="str">
+      <c r="AD20" s="11">
         <f>IF(OR($C20="",AC20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC20,FIND("-",AC20)-1),"")=AW20,IFERROR(--MID(AC20,FIND("-",AC20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AC20,FIND("-",AC20)-1),""))-(IFERROR(--MID(AC20,FIND("-",AC20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AC20,FIND("-",AC20)-1),""))-(IFERROR(--MID(AC20,FIND("-",AC20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AC20,FIND("-",AC20)-1),""))=(AW20))+2*((IFERROR(--MID(AC20,FIND("-",AC20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF20" s="11" t="str">
+      <c r="AF20" s="11">
         <f>IF(OR($C20="",AE20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE20,FIND("-",AE20)-1),"")=AW20,IFERROR(--MID(AE20,FIND("-",AE20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AE20,FIND("-",AE20)-1),""))-(IFERROR(--MID(AE20,FIND("-",AE20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AE20,FIND("-",AE20)-1),""))-(IFERROR(--MID(AE20,FIND("-",AE20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AE20,FIND("-",AE20)-1),""))=(AW20))+2*((IFERROR(--MID(AE20,FIND("-",AE20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH20" s="11" t="str">
+      <c r="AH20" s="11">
         <f>IF(OR($C20="",AG20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG20,FIND("-",AG20)-1),"")=AW20,IFERROR(--MID(AG20,FIND("-",AG20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AG20,FIND("-",AG20)-1),""))-(IFERROR(--MID(AG20,FIND("-",AG20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AG20,FIND("-",AG20)-1),""))-(IFERROR(--MID(AG20,FIND("-",AG20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AG20,FIND("-",AG20)-1),""))=(AW20))+2*((IFERROR(--MID(AG20,FIND("-",AG20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI20" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ20" s="11" t="str">
+      <c r="AJ20" s="11">
         <f>IF(OR($C20="",AI20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI20,FIND("-",AI20)-1),"")=AW20,IFERROR(--MID(AI20,FIND("-",AI20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AI20,FIND("-",AI20)-1),""))-(IFERROR(--MID(AI20,FIND("-",AI20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AI20,FIND("-",AI20)-1),""))-(IFERROR(--MID(AI20,FIND("-",AI20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AI20,FIND("-",AI20)-1),""))=(AW20))+2*((IFERROR(--MID(AI20,FIND("-",AI20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL20" s="11" t="str">
+      <c r="AL20" s="11">
         <f>IF(OR($C20="",AK20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK20,FIND("-",AK20)-1),"")=AW20,IFERROR(--MID(AK20,FIND("-",AK20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AK20,FIND("-",AK20)-1),""))-(IFERROR(--MID(AK20,FIND("-",AK20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AK20,FIND("-",AK20)-1),""))-(IFERROR(--MID(AK20,FIND("-",AK20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AK20,FIND("-",AK20)-1),""))=(AW20))+2*((IFERROR(--MID(AK20,FIND("-",AK20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN20" s="11" t="str">
+      <c r="AN20" s="11">
         <f>IF(OR($C20="",AM20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM20,FIND("-",AM20)-1),"")=AW20,IFERROR(--MID(AM20,FIND("-",AM20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AM20,FIND("-",AM20)-1),""))-(IFERROR(--MID(AM20,FIND("-",AM20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AM20,FIND("-",AM20)-1),""))-(IFERROR(--MID(AM20,FIND("-",AM20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AM20,FIND("-",AM20)-1),""))=(AW20))+2*((IFERROR(--MID(AM20,FIND("-",AM20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP20" s="11" t="str">
+      <c r="AP20" s="11">
         <f>IF(OR($C20="",AO20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO20,FIND("-",AO20)-1),"")=AW20,IFERROR(--MID(AO20,FIND("-",AO20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AO20,FIND("-",AO20)-1),""))-(IFERROR(--MID(AO20,FIND("-",AO20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AO20,FIND("-",AO20)-1),""))-(IFERROR(--MID(AO20,FIND("-",AO20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AO20,FIND("-",AO20)-1),""))=(AW20))+2*((IFERROR(--MID(AO20,FIND("-",AO20)+1,99),""))=(AX20))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AR20" s="11" t="str">
+      <c r="AR20" s="11">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AT20" s="11" t="str">
+      <c r="AT20" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU20" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AV20" s="11" t="str">
+      <c r="AV20" s="11">
         <f>IF(OR($C20="",AU20=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU20,FIND("-",AU20)-1),"")=AW20,IFERROR(--MID(AU20,FIND("-",AU20)+1,99),"")=AX20),10,5*(SIGN((IFERROR(--LEFT(AU20,FIND("-",AU20)-1),""))-(IFERROR(--MID(AU20,FIND("-",AU20)+1,99),"")))=SIGN((AW20)-(AX20)))+2*(((IFERROR(--LEFT(AU20,FIND("-",AU20)-1),""))-(IFERROR(--MID(AU20,FIND("-",AU20)+1,99),"")))=((AW20)-(AX20)))+2*((IFERROR(--LEFT(AU20,FIND("-",AU20)-1),""))=(AW20))+2*((IFERROR(--MID(AU20,FIND("-",AU20)+1,99),""))=(AX20))),""))</f>
-        <v/>
-      </c>
-      <c r="AW20" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW20" s="11">
         <f>IF($C20="","",IFERROR(--LEFT($C20,FIND("-",$C20)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX20" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX20" s="11">
         <f>IF($C20="","",IFERROR(--MID($C20,FIND("-",$C20)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -4225,56 +4244,56 @@
       <c r="AX21" s="12"/>
     </row>
     <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="38"/>
-      <c r="S22" s="39"/>
-      <c r="T22" s="38"/>
-      <c r="U22" s="39"/>
-      <c r="V22" s="38"/>
-      <c r="W22" s="39"/>
-      <c r="X22" s="38"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="38"/>
-      <c r="AA22" s="39"/>
-      <c r="AB22" s="38"/>
-      <c r="AC22" s="39"/>
-      <c r="AD22" s="38"/>
-      <c r="AE22" s="39"/>
-      <c r="AF22" s="38"/>
-      <c r="AG22" s="39"/>
-      <c r="AH22" s="38"/>
-      <c r="AI22" s="39"/>
-      <c r="AJ22" s="38"/>
-      <c r="AK22" s="39"/>
-      <c r="AL22" s="38"/>
-      <c r="AM22" s="39"/>
-      <c r="AN22" s="38"/>
-      <c r="AO22" s="39"/>
-      <c r="AP22" s="38"/>
-      <c r="AQ22" s="38"/>
-      <c r="AR22" s="38"/>
-      <c r="AS22" s="38"/>
-      <c r="AT22" s="38"/>
-      <c r="AU22" s="39"/>
-      <c r="AV22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="34"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="35"/>
+      <c r="AD22" s="34"/>
+      <c r="AE22" s="35"/>
+      <c r="AF22" s="34"/>
+      <c r="AG22" s="35"/>
+      <c r="AH22" s="34"/>
+      <c r="AI22" s="35"/>
+      <c r="AJ22" s="34"/>
+      <c r="AK22" s="35"/>
+      <c r="AL22" s="34"/>
+      <c r="AM22" s="35"/>
+      <c r="AN22" s="34"/>
+      <c r="AO22" s="35"/>
+      <c r="AP22" s="34"/>
+      <c r="AQ22" s="34"/>
+      <c r="AR22" s="34"/>
+      <c r="AS22" s="34"/>
+      <c r="AT22" s="34"/>
+      <c r="AU22" s="35"/>
+      <c r="AV22" s="36"/>
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
@@ -4285,171 +4304,173 @@
       <c r="B23" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D23" s="1" t="s">
         <v>77</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="11" t="str">
+      <c r="F23" s="11">
         <f>IF(OR($C23="",E23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E23,FIND("-",E23)-1),"")=AW23,IFERROR(--MID(E23,FIND("-",E23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(E23,FIND("-",E23)-1),""))-(IFERROR(--MID(E23,FIND("-",E23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(E23,FIND("-",E23)-1),""))-(IFERROR(--MID(E23,FIND("-",E23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(E23,FIND("-",E23)-1),""))=(AW23))+2*((IFERROR(--MID(E23,FIND("-",E23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="11" t="str">
+      <c r="H23" s="11">
         <f>IF(OR($C23="",G23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G23,FIND("-",G23)-1),"")=AW23,IFERROR(--MID(G23,FIND("-",G23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(G23,FIND("-",G23)-1),""))-(IFERROR(--MID(G23,FIND("-",G23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(G23,FIND("-",G23)-1),""))-(IFERROR(--MID(G23,FIND("-",G23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(G23,FIND("-",G23)-1),""))=(AW23))+2*((IFERROR(--MID(G23,FIND("-",G23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="11" t="str">
+      <c r="J23" s="11">
         <f>IF(OR($C23="",I23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I23,FIND("-",I23)-1),"")=AW23,IFERROR(--MID(I23,FIND("-",I23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(I23,FIND("-",I23)-1),""))-(IFERROR(--MID(I23,FIND("-",I23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(I23,FIND("-",I23)-1),""))-(IFERROR(--MID(I23,FIND("-",I23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(I23,FIND("-",I23)-1),""))=(AW23))+2*((IFERROR(--MID(I23,FIND("-",I23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K23" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="11" t="str">
+      <c r="L23" s="11">
         <f>IF(OR($C23="",K23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K23,FIND("-",K23)-1),"")=AW23,IFERROR(--MID(K23,FIND("-",K23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(K23,FIND("-",K23)-1),""))-(IFERROR(--MID(K23,FIND("-",K23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(K23,FIND("-",K23)-1),""))-(IFERROR(--MID(K23,FIND("-",K23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(K23,FIND("-",K23)-1),""))=(AW23))+2*((IFERROR(--MID(K23,FIND("-",K23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="N23" s="11" t="str">
+      <c r="N23" s="11">
         <f>IF(OR($C23="",M23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M23,FIND("-",M23)-1),"")=AW23,IFERROR(--MID(M23,FIND("-",M23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(M23,FIND("-",M23)-1),""))-(IFERROR(--MID(M23,FIND("-",M23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(M23,FIND("-",M23)-1),""))-(IFERROR(--MID(M23,FIND("-",M23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(M23,FIND("-",M23)-1),""))=(AW23))+2*((IFERROR(--MID(M23,FIND("-",M23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P23" s="11" t="str">
+      <c r="P23" s="11">
         <f>IF(OR($C23="",O23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O23,FIND("-",O23)-1),"")=AW23,IFERROR(--MID(O23,FIND("-",O23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(O23,FIND("-",O23)-1),""))-(IFERROR(--MID(O23,FIND("-",O23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(O23,FIND("-",O23)-1),""))-(IFERROR(--MID(O23,FIND("-",O23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(O23,FIND("-",O23)-1),""))=(AW23))+2*((IFERROR(--MID(O23,FIND("-",O23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q23" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R23" s="11" t="str">
+      <c r="R23" s="11">
         <f>IF(OR($C23="",Q23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q23,FIND("-",Q23)-1),"")=AW23,IFERROR(--MID(Q23,FIND("-",Q23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(Q23,FIND("-",Q23)-1),""))-(IFERROR(--MID(Q23,FIND("-",Q23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(Q23,FIND("-",Q23)-1),""))-(IFERROR(--MID(Q23,FIND("-",Q23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(Q23,FIND("-",Q23)-1),""))=(AW23))+2*((IFERROR(--MID(Q23,FIND("-",Q23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S23" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T23" s="11" t="str">
+      <c r="T23" s="11">
         <f>IF(OR($C23="",S23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S23,FIND("-",S23)-1),"")=AW23,IFERROR(--MID(S23,FIND("-",S23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(S23,FIND("-",S23)-1),""))-(IFERROR(--MID(S23,FIND("-",S23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(S23,FIND("-",S23)-1),""))-(IFERROR(--MID(S23,FIND("-",S23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(S23,FIND("-",S23)-1),""))=(AW23))+2*((IFERROR(--MID(S23,FIND("-",S23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V23" s="11" t="str">
+      <c r="V23" s="11">
         <f>IF(OR($C23="",U23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U23,FIND("-",U23)-1),"")=AW23,IFERROR(--MID(U23,FIND("-",U23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(U23,FIND("-",U23)-1),""))-(IFERROR(--MID(U23,FIND("-",U23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(U23,FIND("-",U23)-1),""))-(IFERROR(--MID(U23,FIND("-",U23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(U23,FIND("-",U23)-1),""))=(AW23))+2*((IFERROR(--MID(U23,FIND("-",U23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X23" s="11" t="str">
+      <c r="X23" s="11">
         <f>IF(OR($C23="",W23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W23,FIND("-",W23)-1),"")=AW23,IFERROR(--MID(W23,FIND("-",W23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(W23,FIND("-",W23)-1),""))-(IFERROR(--MID(W23,FIND("-",W23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(W23,FIND("-",W23)-1),""))-(IFERROR(--MID(W23,FIND("-",W23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(W23,FIND("-",W23)-1),""))=(AW23))+2*((IFERROR(--MID(W23,FIND("-",W23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z23" s="11" t="str">
+      <c r="Z23" s="11">
         <f>IF(OR($C23="",Y23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y23,FIND("-",Y23)-1),"")=AW23,IFERROR(--MID(Y23,FIND("-",Y23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(Y23,FIND("-",Y23)-1),""))-(IFERROR(--MID(Y23,FIND("-",Y23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(Y23,FIND("-",Y23)-1),""))-(IFERROR(--MID(Y23,FIND("-",Y23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(Y23,FIND("-",Y23)-1),""))=(AW23))+2*((IFERROR(--MID(Y23,FIND("-",Y23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA23" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AB23" s="11" t="str">
+      <c r="AB23" s="11">
         <f>IF(OR($C23="",AA23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA23,FIND("-",AA23)-1),"")=AW23,IFERROR(--MID(AA23,FIND("-",AA23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AA23,FIND("-",AA23)-1),""))-(IFERROR(--MID(AA23,FIND("-",AA23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AA23,FIND("-",AA23)-1),""))-(IFERROR(--MID(AA23,FIND("-",AA23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AA23,FIND("-",AA23)-1),""))=(AW23))+2*((IFERROR(--MID(AA23,FIND("-",AA23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC23" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AD23" s="11" t="str">
+      <c r="AD23" s="11">
         <f>IF(OR($C23="",AC23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC23,FIND("-",AC23)-1),"")=AW23,IFERROR(--MID(AC23,FIND("-",AC23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AC23,FIND("-",AC23)-1),""))-(IFERROR(--MID(AC23,FIND("-",AC23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AC23,FIND("-",AC23)-1),""))-(IFERROR(--MID(AC23,FIND("-",AC23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AC23,FIND("-",AC23)-1),""))=(AW23))+2*((IFERROR(--MID(AC23,FIND("-",AC23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF23" s="11" t="str">
+      <c r="AF23" s="11">
         <f>IF(OR($C23="",AE23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE23,FIND("-",AE23)-1),"")=AW23,IFERROR(--MID(AE23,FIND("-",AE23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AE23,FIND("-",AE23)-1),""))-(IFERROR(--MID(AE23,FIND("-",AE23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AE23,FIND("-",AE23)-1),""))-(IFERROR(--MID(AE23,FIND("-",AE23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AE23,FIND("-",AE23)-1),""))=(AW23))+2*((IFERROR(--MID(AE23,FIND("-",AE23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG23" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AH23" s="11" t="str">
+      <c r="AH23" s="11">
         <f>IF(OR($C23="",AG23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG23,FIND("-",AG23)-1),"")=AW23,IFERROR(--MID(AG23,FIND("-",AG23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AG23,FIND("-",AG23)-1),""))-(IFERROR(--MID(AG23,FIND("-",AG23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AG23,FIND("-",AG23)-1),""))-(IFERROR(--MID(AG23,FIND("-",AG23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AG23,FIND("-",AG23)-1),""))=(AW23))+2*((IFERROR(--MID(AG23,FIND("-",AG23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI23" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AJ23" s="11" t="str">
+      <c r="AJ23" s="11">
         <f>IF(OR($C23="",AI23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI23,FIND("-",AI23)-1),"")=AW23,IFERROR(--MID(AI23,FIND("-",AI23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AI23,FIND("-",AI23)-1),""))-(IFERROR(--MID(AI23,FIND("-",AI23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AI23,FIND("-",AI23)-1),""))-(IFERROR(--MID(AI23,FIND("-",AI23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AI23,FIND("-",AI23)-1),""))=(AW23))+2*((IFERROR(--MID(AI23,FIND("-",AI23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AL23" s="11" t="str">
+      <c r="AL23" s="11">
         <f>IF(OR($C23="",AK23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK23,FIND("-",AK23)-1),"")=AW23,IFERROR(--MID(AK23,FIND("-",AK23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AK23,FIND("-",AK23)-1),""))-(IFERROR(--MID(AK23,FIND("-",AK23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AK23,FIND("-",AK23)-1),""))-(IFERROR(--MID(AK23,FIND("-",AK23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AK23,FIND("-",AK23)-1),""))=(AW23))+2*((IFERROR(--MID(AK23,FIND("-",AK23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM23" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AN23" s="11" t="str">
+      <c r="AN23" s="11">
         <f>IF(OR($C23="",AM23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM23,FIND("-",AM23)-1),"")=AW23,IFERROR(--MID(AM23,FIND("-",AM23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AM23,FIND("-",AM23)-1),""))-(IFERROR(--MID(AM23,FIND("-",AM23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AM23,FIND("-",AM23)-1),""))-(IFERROR(--MID(AM23,FIND("-",AM23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AM23,FIND("-",AM23)-1),""))=(AW23))+2*((IFERROR(--MID(AM23,FIND("-",AM23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP23" s="11" t="str">
+      <c r="AP23" s="11">
         <f>IF(OR($C23="",AO23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO23,FIND("-",AO23)-1),"")=AW23,IFERROR(--MID(AO23,FIND("-",AO23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AO23,FIND("-",AO23)-1),""))-(IFERROR(--MID(AO23,FIND("-",AO23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AO23,FIND("-",AO23)-1),""))-(IFERROR(--MID(AO23,FIND("-",AO23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AO23,FIND("-",AO23)-1),""))=(AW23))+2*((IFERROR(--MID(AO23,FIND("-",AO23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR23" s="11" t="str">
+      <c r="AR23" s="11">
         <f>IF(OR($C23="",AQ23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ23,FIND("-",AQ23)-1),"")=AW23,IFERROR(--MID(AQ23,FIND("-",AQ23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AQ23,FIND("-",AQ23)-1),""))-(IFERROR(--MID(AQ23,FIND("-",AQ23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AQ23,FIND("-",AQ23)-1),""))-(IFERROR(--MID(AQ23,FIND("-",AQ23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AQ23,FIND("-",AQ23)-1),""))=(AW23))+2*((IFERROR(--MID(AQ23,FIND("-",AQ23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT23" s="11" t="str">
+      <c r="AT23" s="11">
         <f>IF(OR($C23="",AS23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS23,FIND("-",AS23)-1),"")=AW23,IFERROR(--MID(AS23,FIND("-",AS23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AS23,FIND("-",AS23)-1),""))-(IFERROR(--MID(AS23,FIND("-",AS23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AS23,FIND("-",AS23)-1),""))-(IFERROR(--MID(AS23,FIND("-",AS23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AS23,FIND("-",AS23)-1),""))=(AW23))+2*((IFERROR(--MID(AS23,FIND("-",AS23)+1,99),""))=(AX23))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AV23" s="11" t="str">
+      <c r="AV23" s="11">
         <f>IF(OR($C23="",AU23=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU23,FIND("-",AU23)-1),"")=AW23,IFERROR(--MID(AU23,FIND("-",AU23)+1,99),"")=AX23),10,5*(SIGN((IFERROR(--LEFT(AU23,FIND("-",AU23)-1),""))-(IFERROR(--MID(AU23,FIND("-",AU23)+1,99),"")))=SIGN((AW23)-(AX23)))+2*(((IFERROR(--LEFT(AU23,FIND("-",AU23)-1),""))-(IFERROR(--MID(AU23,FIND("-",AU23)+1,99),"")))=((AW23)-(AX23)))+2*((IFERROR(--LEFT(AU23,FIND("-",AU23)-1),""))=(AW23))+2*((IFERROR(--MID(AU23,FIND("-",AU23)+1,99),""))=(AX23))),""))</f>
-        <v/>
-      </c>
-      <c r="AW23" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW23" s="11">
         <f>IF($C23="","",IFERROR(--LEFT($C23,FIND("-",$C23)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX23" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX23" s="11">
         <f>IF($C23="","",IFERROR(--MID($C23,FIND("-",$C23)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -4459,171 +4480,173 @@
       <c r="B24" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="10" t="s">
+        <v>113</v>
+      </c>
       <c r="D24" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="11" t="str">
+      <c r="F24" s="11">
         <f>IF(OR($C24="",E24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E24,FIND("-",E24)-1),"")=AW24,IFERROR(--MID(E24,FIND("-",E24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(E24,FIND("-",E24)-1),""))-(IFERROR(--MID(E24,FIND("-",E24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(E24,FIND("-",E24)-1),""))-(IFERROR(--MID(E24,FIND("-",E24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(E24,FIND("-",E24)-1),""))=(AW24))+2*((IFERROR(--MID(E24,FIND("-",E24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="11" t="str">
+      <c r="H24" s="11">
         <f>IF(OR($C24="",G24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G24,FIND("-",G24)-1),"")=AW24,IFERROR(--MID(G24,FIND("-",G24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(G24,FIND("-",G24)-1),""))-(IFERROR(--MID(G24,FIND("-",G24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(G24,FIND("-",G24)-1),""))-(IFERROR(--MID(G24,FIND("-",G24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(G24,FIND("-",G24)-1),""))=(AW24))+2*((IFERROR(--MID(G24,FIND("-",G24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J24" s="11" t="str">
+      <c r="J24" s="11">
         <f>IF(OR($C24="",I24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I24,FIND("-",I24)-1),"")=AW24,IFERROR(--MID(I24,FIND("-",I24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(I24,FIND("-",I24)-1),""))-(IFERROR(--MID(I24,FIND("-",I24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(I24,FIND("-",I24)-1),""))-(IFERROR(--MID(I24,FIND("-",I24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(I24,FIND("-",I24)-1),""))=(AW24))+2*((IFERROR(--MID(I24,FIND("-",I24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K24" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L24" s="11" t="str">
+      <c r="L24" s="11">
         <f>IF(OR($C24="",K24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K24,FIND("-",K24)-1),"")=AW24,IFERROR(--MID(K24,FIND("-",K24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(K24,FIND("-",K24)-1),""))-(IFERROR(--MID(K24,FIND("-",K24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(K24,FIND("-",K24)-1),""))-(IFERROR(--MID(K24,FIND("-",K24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(K24,FIND("-",K24)-1),""))=(AW24))+2*((IFERROR(--MID(K24,FIND("-",K24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N24" s="11" t="str">
+      <c r="N24" s="11">
         <f>IF(OR($C24="",M24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M24,FIND("-",M24)-1),"")=AW24,IFERROR(--MID(M24,FIND("-",M24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(M24,FIND("-",M24)-1),""))-(IFERROR(--MID(M24,FIND("-",M24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(M24,FIND("-",M24)-1),""))-(IFERROR(--MID(M24,FIND("-",M24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(M24,FIND("-",M24)-1),""))=(AW24))+2*((IFERROR(--MID(M24,FIND("-",M24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="P24" s="11" t="str">
+      <c r="P24" s="11">
         <f>IF(OR($C24="",O24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O24,FIND("-",O24)-1),"")=AW24,IFERROR(--MID(O24,FIND("-",O24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(O24,FIND("-",O24)-1),""))-(IFERROR(--MID(O24,FIND("-",O24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(O24,FIND("-",O24)-1),""))-(IFERROR(--MID(O24,FIND("-",O24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(O24,FIND("-",O24)-1),""))=(AW24))+2*((IFERROR(--MID(O24,FIND("-",O24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q24" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="R24" s="11" t="str">
+      <c r="R24" s="11">
         <f>IF(OR($C24="",Q24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q24,FIND("-",Q24)-1),"")=AW24,IFERROR(--MID(Q24,FIND("-",Q24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(Q24,FIND("-",Q24)-1),""))-(IFERROR(--MID(Q24,FIND("-",Q24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(Q24,FIND("-",Q24)-1),""))-(IFERROR(--MID(Q24,FIND("-",Q24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(Q24,FIND("-",Q24)-1),""))=(AW24))+2*((IFERROR(--MID(Q24,FIND("-",Q24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T24" s="11" t="str">
+      <c r="T24" s="11">
         <f>IF(OR($C24="",S24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S24,FIND("-",S24)-1),"")=AW24,IFERROR(--MID(S24,FIND("-",S24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(S24,FIND("-",S24)-1),""))-(IFERROR(--MID(S24,FIND("-",S24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(S24,FIND("-",S24)-1),""))-(IFERROR(--MID(S24,FIND("-",S24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(S24,FIND("-",S24)-1),""))=(AW24))+2*((IFERROR(--MID(S24,FIND("-",S24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V24" s="11" t="str">
+      <c r="V24" s="11">
         <f>IF(OR($C24="",U24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U24,FIND("-",U24)-1),"")=AW24,IFERROR(--MID(U24,FIND("-",U24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(U24,FIND("-",U24)-1),""))-(IFERROR(--MID(U24,FIND("-",U24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(U24,FIND("-",U24)-1),""))-(IFERROR(--MID(U24,FIND("-",U24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(U24,FIND("-",U24)-1),""))=(AW24))+2*((IFERROR(--MID(U24,FIND("-",U24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X24" s="11" t="str">
+      <c r="X24" s="11">
         <f>IF(OR($C24="",W24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W24,FIND("-",W24)-1),"")=AW24,IFERROR(--MID(W24,FIND("-",W24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(W24,FIND("-",W24)-1),""))-(IFERROR(--MID(W24,FIND("-",W24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(W24,FIND("-",W24)-1),""))-(IFERROR(--MID(W24,FIND("-",W24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(W24,FIND("-",W24)-1),""))=(AW24))+2*((IFERROR(--MID(W24,FIND("-",W24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="Z24" s="11" t="str">
+      <c r="Z24" s="11">
         <f>IF(OR($C24="",Y24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y24,FIND("-",Y24)-1),"")=AW24,IFERROR(--MID(Y24,FIND("-",Y24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(Y24,FIND("-",Y24)-1),""))-(IFERROR(--MID(Y24,FIND("-",Y24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(Y24,FIND("-",Y24)-1),""))-(IFERROR(--MID(Y24,FIND("-",Y24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(Y24,FIND("-",Y24)-1),""))=(AW24))+2*((IFERROR(--MID(Y24,FIND("-",Y24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AB24" s="11" t="str">
+      <c r="AB24" s="11">
         <f>IF(OR($C24="",AA24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA24,FIND("-",AA24)-1),"")=AW24,IFERROR(--MID(AA24,FIND("-",AA24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AA24,FIND("-",AA24)-1),""))-(IFERROR(--MID(AA24,FIND("-",AA24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AA24,FIND("-",AA24)-1),""))-(IFERROR(--MID(AA24,FIND("-",AA24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AA24,FIND("-",AA24)-1),""))=(AW24))+2*((IFERROR(--MID(AA24,FIND("-",AA24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD24" s="11" t="str">
+      <c r="AD24" s="11">
         <f>IF(OR($C24="",AC24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC24,FIND("-",AC24)-1),"")=AW24,IFERROR(--MID(AC24,FIND("-",AC24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AC24,FIND("-",AC24)-1),""))-(IFERROR(--MID(AC24,FIND("-",AC24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AC24,FIND("-",AC24)-1),""))-(IFERROR(--MID(AC24,FIND("-",AC24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AC24,FIND("-",AC24)-1),""))=(AW24))+2*((IFERROR(--MID(AC24,FIND("-",AC24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AF24" s="11" t="str">
+      <c r="AF24" s="11">
         <f>IF(OR($C24="",AE24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE24,FIND("-",AE24)-1),"")=AW24,IFERROR(--MID(AE24,FIND("-",AE24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AE24,FIND("-",AE24)-1),""))-(IFERROR(--MID(AE24,FIND("-",AE24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AE24,FIND("-",AE24)-1),""))-(IFERROR(--MID(AE24,FIND("-",AE24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AE24,FIND("-",AE24)-1),""))=(AW24))+2*((IFERROR(--MID(AE24,FIND("-",AE24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AG24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH24" s="11" t="str">
+      <c r="AH24" s="11">
         <f>IF(OR($C24="",AG24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG24,FIND("-",AG24)-1),"")=AW24,IFERROR(--MID(AG24,FIND("-",AG24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AG24,FIND("-",AG24)-1),""))-(IFERROR(--MID(AG24,FIND("-",AG24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AG24,FIND("-",AG24)-1),""))-(IFERROR(--MID(AG24,FIND("-",AG24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AG24,FIND("-",AG24)-1),""))=(AW24))+2*((IFERROR(--MID(AG24,FIND("-",AG24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ24" s="11" t="str">
+      <c r="AJ24" s="11">
         <f>IF(OR($C24="",AI24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI24,FIND("-",AI24)-1),"")=AW24,IFERROR(--MID(AI24,FIND("-",AI24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AI24,FIND("-",AI24)-1),""))-(IFERROR(--MID(AI24,FIND("-",AI24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AI24,FIND("-",AI24)-1),""))-(IFERROR(--MID(AI24,FIND("-",AI24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AI24,FIND("-",AI24)-1),""))=(AW24))+2*((IFERROR(--MID(AI24,FIND("-",AI24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL24" s="11" t="str">
+      <c r="AL24" s="11">
         <f>IF(OR($C24="",AK24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK24,FIND("-",AK24)-1),"")=AW24,IFERROR(--MID(AK24,FIND("-",AK24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AK24,FIND("-",AK24)-1),""))-(IFERROR(--MID(AK24,FIND("-",AK24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AK24,FIND("-",AK24)-1),""))-(IFERROR(--MID(AK24,FIND("-",AK24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AK24,FIND("-",AK24)-1),""))=(AW24))+2*((IFERROR(--MID(AK24,FIND("-",AK24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AN24" s="11" t="str">
+      <c r="AN24" s="11">
         <f>IF(OR($C24="",AM24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM24,FIND("-",AM24)-1),"")=AW24,IFERROR(--MID(AM24,FIND("-",AM24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AM24,FIND("-",AM24)-1),""))-(IFERROR(--MID(AM24,FIND("-",AM24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AM24,FIND("-",AM24)-1),""))-(IFERROR(--MID(AM24,FIND("-",AM24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AM24,FIND("-",AM24)-1),""))=(AW24))+2*((IFERROR(--MID(AM24,FIND("-",AM24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO24" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AP24" s="11" t="str">
+      <c r="AP24" s="11">
         <f>IF(OR($C24="",AO24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO24,FIND("-",AO24)-1),"")=AW24,IFERROR(--MID(AO24,FIND("-",AO24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AO24,FIND("-",AO24)-1),""))-(IFERROR(--MID(AO24,FIND("-",AO24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AO24,FIND("-",AO24)-1),""))-(IFERROR(--MID(AO24,FIND("-",AO24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AO24,FIND("-",AO24)-1),""))=(AW24))+2*((IFERROR(--MID(AO24,FIND("-",AO24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AR24" s="11" t="str">
+      <c r="AR24" s="11">
         <f>IF(OR($C24="",AQ24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ24,FIND("-",AQ24)-1),"")=AW24,IFERROR(--MID(AQ24,FIND("-",AQ24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AQ24,FIND("-",AQ24)-1),""))-(IFERROR(--MID(AQ24,FIND("-",AQ24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AQ24,FIND("-",AQ24)-1),""))-(IFERROR(--MID(AQ24,FIND("-",AQ24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AQ24,FIND("-",AQ24)-1),""))=(AW24))+2*((IFERROR(--MID(AQ24,FIND("-",AQ24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT24" s="11" t="str">
+      <c r="AT24" s="11">
         <f>IF(OR($C24="",AS24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS24,FIND("-",AS24)-1),"")=AW24,IFERROR(--MID(AS24,FIND("-",AS24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AS24,FIND("-",AS24)-1),""))-(IFERROR(--MID(AS24,FIND("-",AS24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AS24,FIND("-",AS24)-1),""))-(IFERROR(--MID(AS24,FIND("-",AS24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AS24,FIND("-",AS24)-1),""))=(AW24))+2*((IFERROR(--MID(AS24,FIND("-",AS24)+1,99),""))=(AX24))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU24" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AV24" s="11" t="str">
+      <c r="AV24" s="11">
         <f>IF(OR($C24="",AU24=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU24,FIND("-",AU24)-1),"")=AW24,IFERROR(--MID(AU24,FIND("-",AU24)+1,99),"")=AX24),10,5*(SIGN((IFERROR(--LEFT(AU24,FIND("-",AU24)-1),""))-(IFERROR(--MID(AU24,FIND("-",AU24)+1,99),"")))=SIGN((AW24)-(AX24)))+2*(((IFERROR(--LEFT(AU24,FIND("-",AU24)-1),""))-(IFERROR(--MID(AU24,FIND("-",AU24)+1,99),"")))=((AW24)-(AX24)))+2*((IFERROR(--LEFT(AU24,FIND("-",AU24)-1),""))=(AW24))+2*((IFERROR(--MID(AU24,FIND("-",AU24)+1,99),""))=(AX24))),""))</f>
-        <v/>
-      </c>
-      <c r="AW24" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW24" s="11">
         <f>IF($C24="","",IFERROR(--LEFT($C24,FIND("-",$C24)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX24" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AX24" s="11">
         <f>IF($C24="","",IFERROR(--MID($C24,FIND("-",$C24)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5033,56 +5056,56 @@
       <c r="AX27" s="12"/>
     </row>
     <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="38"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="39"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="39"/>
-      <c r="X28" s="38"/>
-      <c r="Y28" s="39"/>
-      <c r="Z28" s="38"/>
-      <c r="AA28" s="39"/>
-      <c r="AB28" s="38"/>
-      <c r="AC28" s="39"/>
-      <c r="AD28" s="38"/>
-      <c r="AE28" s="39"/>
-      <c r="AF28" s="38"/>
-      <c r="AG28" s="39"/>
-      <c r="AH28" s="38"/>
-      <c r="AI28" s="39"/>
-      <c r="AJ28" s="38"/>
-      <c r="AK28" s="39"/>
-      <c r="AL28" s="38"/>
-      <c r="AM28" s="39"/>
-      <c r="AN28" s="38"/>
-      <c r="AO28" s="39"/>
-      <c r="AP28" s="38"/>
-      <c r="AQ28" s="38"/>
-      <c r="AR28" s="38"/>
-      <c r="AS28" s="38"/>
-      <c r="AT28" s="38"/>
-      <c r="AU28" s="39"/>
-      <c r="AV28" s="34"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="34"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="34"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="34"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="34"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="34"/>
+      <c r="AE28" s="35"/>
+      <c r="AF28" s="34"/>
+      <c r="AG28" s="35"/>
+      <c r="AH28" s="34"/>
+      <c r="AI28" s="35"/>
+      <c r="AJ28" s="34"/>
+      <c r="AK28" s="35"/>
+      <c r="AL28" s="34"/>
+      <c r="AM28" s="35"/>
+      <c r="AN28" s="34"/>
+      <c r="AO28" s="35"/>
+      <c r="AP28" s="34"/>
+      <c r="AQ28" s="34"/>
+      <c r="AR28" s="34"/>
+      <c r="AS28" s="34"/>
+      <c r="AT28" s="34"/>
+      <c r="AU28" s="35"/>
+      <c r="AV28" s="36"/>
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
@@ -5667,56 +5690,56 @@
       <c r="AX32" s="12"/>
     </row>
     <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="38"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="38"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="39"/>
-      <c r="R33" s="38"/>
-      <c r="S33" s="39"/>
-      <c r="T33" s="38"/>
-      <c r="U33" s="39"/>
-      <c r="V33" s="38"/>
-      <c r="W33" s="39"/>
-      <c r="X33" s="38"/>
-      <c r="Y33" s="39"/>
-      <c r="Z33" s="38"/>
-      <c r="AA33" s="39"/>
-      <c r="AB33" s="38"/>
-      <c r="AC33" s="39"/>
-      <c r="AD33" s="38"/>
-      <c r="AE33" s="39"/>
-      <c r="AF33" s="38"/>
-      <c r="AG33" s="39"/>
-      <c r="AH33" s="38"/>
-      <c r="AI33" s="39"/>
-      <c r="AJ33" s="38"/>
-      <c r="AK33" s="39"/>
-      <c r="AL33" s="38"/>
-      <c r="AM33" s="39"/>
-      <c r="AN33" s="38"/>
-      <c r="AO33" s="39"/>
-      <c r="AP33" s="38"/>
-      <c r="AQ33" s="38"/>
-      <c r="AR33" s="38"/>
-      <c r="AS33" s="38"/>
-      <c r="AT33" s="38"/>
-      <c r="AU33" s="39"/>
-      <c r="AV33" s="34"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="34"/>
+      <c r="U33" s="35"/>
+      <c r="V33" s="34"/>
+      <c r="W33" s="35"/>
+      <c r="X33" s="34"/>
+      <c r="Y33" s="35"/>
+      <c r="Z33" s="34"/>
+      <c r="AA33" s="35"/>
+      <c r="AB33" s="34"/>
+      <c r="AC33" s="35"/>
+      <c r="AD33" s="34"/>
+      <c r="AE33" s="35"/>
+      <c r="AF33" s="34"/>
+      <c r="AG33" s="35"/>
+      <c r="AH33" s="34"/>
+      <c r="AI33" s="35"/>
+      <c r="AJ33" s="34"/>
+      <c r="AK33" s="35"/>
+      <c r="AL33" s="34"/>
+      <c r="AM33" s="35"/>
+      <c r="AN33" s="34"/>
+      <c r="AO33" s="35"/>
+      <c r="AP33" s="34"/>
+      <c r="AQ33" s="34"/>
+      <c r="AR33" s="34"/>
+      <c r="AS33" s="34"/>
+      <c r="AT33" s="34"/>
+      <c r="AU33" s="35"/>
+      <c r="AV33" s="36"/>
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
@@ -6649,56 +6672,56 @@
       <c r="AX39" s="12"/>
     </row>
     <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="37" t="s">
+      <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="38"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="38"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="38"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="38"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="38"/>
-      <c r="Q40" s="39"/>
-      <c r="R40" s="38"/>
-      <c r="S40" s="39"/>
-      <c r="T40" s="38"/>
-      <c r="U40" s="39"/>
-      <c r="V40" s="38"/>
-      <c r="W40" s="39"/>
-      <c r="X40" s="38"/>
-      <c r="Y40" s="39"/>
-      <c r="Z40" s="38"/>
-      <c r="AA40" s="39"/>
-      <c r="AB40" s="38"/>
-      <c r="AC40" s="39"/>
-      <c r="AD40" s="38"/>
-      <c r="AE40" s="39"/>
-      <c r="AF40" s="38"/>
-      <c r="AG40" s="39"/>
-      <c r="AH40" s="38"/>
-      <c r="AI40" s="39"/>
-      <c r="AJ40" s="38"/>
-      <c r="AK40" s="39"/>
-      <c r="AL40" s="38"/>
-      <c r="AM40" s="39"/>
-      <c r="AN40" s="38"/>
-      <c r="AO40" s="39"/>
-      <c r="AP40" s="38"/>
-      <c r="AQ40" s="38"/>
-      <c r="AR40" s="38"/>
-      <c r="AS40" s="38"/>
-      <c r="AT40" s="38"/>
-      <c r="AU40" s="39"/>
-      <c r="AV40" s="34"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="34"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="34"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="34"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="34"/>
+      <c r="S40" s="35"/>
+      <c r="T40" s="34"/>
+      <c r="U40" s="35"/>
+      <c r="V40" s="34"/>
+      <c r="W40" s="35"/>
+      <c r="X40" s="34"/>
+      <c r="Y40" s="35"/>
+      <c r="Z40" s="34"/>
+      <c r="AA40" s="35"/>
+      <c r="AB40" s="34"/>
+      <c r="AC40" s="35"/>
+      <c r="AD40" s="34"/>
+      <c r="AE40" s="35"/>
+      <c r="AF40" s="34"/>
+      <c r="AG40" s="35"/>
+      <c r="AH40" s="34"/>
+      <c r="AI40" s="35"/>
+      <c r="AJ40" s="34"/>
+      <c r="AK40" s="35"/>
+      <c r="AL40" s="34"/>
+      <c r="AM40" s="35"/>
+      <c r="AN40" s="34"/>
+      <c r="AO40" s="35"/>
+      <c r="AP40" s="34"/>
+      <c r="AQ40" s="34"/>
+      <c r="AR40" s="34"/>
+      <c r="AS40" s="34"/>
+      <c r="AT40" s="34"/>
+      <c r="AU40" s="35"/>
+      <c r="AV40" s="36"/>
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
@@ -7457,56 +7480,56 @@
       <c r="AX45" s="12"/>
     </row>
     <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="37" t="s">
+      <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="38"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="39"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="39"/>
-      <c r="L46" s="38"/>
-      <c r="M46" s="39"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="38"/>
-      <c r="Q46" s="39"/>
-      <c r="R46" s="38"/>
-      <c r="S46" s="39"/>
-      <c r="T46" s="38"/>
-      <c r="U46" s="39"/>
-      <c r="V46" s="38"/>
-      <c r="W46" s="39"/>
-      <c r="X46" s="38"/>
-      <c r="Y46" s="39"/>
-      <c r="Z46" s="38"/>
-      <c r="AA46" s="39"/>
-      <c r="AB46" s="38"/>
-      <c r="AC46" s="39"/>
-      <c r="AD46" s="38"/>
-      <c r="AE46" s="39"/>
-      <c r="AF46" s="38"/>
-      <c r="AG46" s="39"/>
-      <c r="AH46" s="38"/>
-      <c r="AI46" s="39"/>
-      <c r="AJ46" s="38"/>
-      <c r="AK46" s="39"/>
-      <c r="AL46" s="38"/>
-      <c r="AM46" s="39"/>
-      <c r="AN46" s="38"/>
-      <c r="AO46" s="39"/>
-      <c r="AP46" s="38"/>
-      <c r="AQ46" s="38"/>
-      <c r="AR46" s="38"/>
-      <c r="AS46" s="38"/>
-      <c r="AT46" s="38"/>
-      <c r="AU46" s="39"/>
-      <c r="AV46" s="34"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="34"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="34"/>
+      <c r="M46" s="35"/>
+      <c r="N46" s="34"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="34"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="34"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="34"/>
+      <c r="U46" s="35"/>
+      <c r="V46" s="34"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="34"/>
+      <c r="Y46" s="35"/>
+      <c r="Z46" s="34"/>
+      <c r="AA46" s="35"/>
+      <c r="AB46" s="34"/>
+      <c r="AC46" s="35"/>
+      <c r="AD46" s="34"/>
+      <c r="AE46" s="35"/>
+      <c r="AF46" s="34"/>
+      <c r="AG46" s="35"/>
+      <c r="AH46" s="34"/>
+      <c r="AI46" s="35"/>
+      <c r="AJ46" s="34"/>
+      <c r="AK46" s="35"/>
+      <c r="AL46" s="34"/>
+      <c r="AM46" s="35"/>
+      <c r="AN46" s="34"/>
+      <c r="AO46" s="35"/>
+      <c r="AP46" s="34"/>
+      <c r="AQ46" s="34"/>
+      <c r="AR46" s="34"/>
+      <c r="AS46" s="34"/>
+      <c r="AT46" s="34"/>
+      <c r="AU46" s="35"/>
+      <c r="AV46" s="36"/>
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
@@ -8091,56 +8114,56 @@
       <c r="AX50" s="12"/>
     </row>
     <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="37" t="s">
+      <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="38"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="38"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="38"/>
-      <c r="K51" s="39"/>
-      <c r="L51" s="38"/>
-      <c r="M51" s="39"/>
-      <c r="N51" s="38"/>
-      <c r="O51" s="39"/>
-      <c r="P51" s="38"/>
-      <c r="Q51" s="39"/>
-      <c r="R51" s="38"/>
-      <c r="S51" s="39"/>
-      <c r="T51" s="38"/>
-      <c r="U51" s="39"/>
-      <c r="V51" s="38"/>
-      <c r="W51" s="39"/>
-      <c r="X51" s="38"/>
-      <c r="Y51" s="39"/>
-      <c r="Z51" s="38"/>
-      <c r="AA51" s="39"/>
-      <c r="AB51" s="38"/>
-      <c r="AC51" s="39"/>
-      <c r="AD51" s="38"/>
-      <c r="AE51" s="39"/>
-      <c r="AF51" s="38"/>
-      <c r="AG51" s="39"/>
-      <c r="AH51" s="38"/>
-      <c r="AI51" s="39"/>
-      <c r="AJ51" s="38"/>
-      <c r="AK51" s="39"/>
-      <c r="AL51" s="38"/>
-      <c r="AM51" s="39"/>
-      <c r="AN51" s="38"/>
-      <c r="AO51" s="39"/>
-      <c r="AP51" s="38"/>
-      <c r="AQ51" s="38"/>
-      <c r="AR51" s="38"/>
-      <c r="AS51" s="38"/>
-      <c r="AT51" s="38"/>
-      <c r="AU51" s="39"/>
-      <c r="AV51" s="34"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="35"/>
+      <c r="N51" s="34"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="34"/>
+      <c r="Q51" s="35"/>
+      <c r="R51" s="34"/>
+      <c r="S51" s="35"/>
+      <c r="T51" s="34"/>
+      <c r="U51" s="35"/>
+      <c r="V51" s="34"/>
+      <c r="W51" s="35"/>
+      <c r="X51" s="34"/>
+      <c r="Y51" s="35"/>
+      <c r="Z51" s="34"/>
+      <c r="AA51" s="35"/>
+      <c r="AB51" s="34"/>
+      <c r="AC51" s="35"/>
+      <c r="AD51" s="34"/>
+      <c r="AE51" s="35"/>
+      <c r="AF51" s="34"/>
+      <c r="AG51" s="35"/>
+      <c r="AH51" s="34"/>
+      <c r="AI51" s="35"/>
+      <c r="AJ51" s="34"/>
+      <c r="AK51" s="35"/>
+      <c r="AL51" s="34"/>
+      <c r="AM51" s="35"/>
+      <c r="AN51" s="34"/>
+      <c r="AO51" s="35"/>
+      <c r="AP51" s="34"/>
+      <c r="AQ51" s="34"/>
+      <c r="AR51" s="34"/>
+      <c r="AS51" s="34"/>
+      <c r="AT51" s="34"/>
+      <c r="AU51" s="35"/>
+      <c r="AV51" s="36"/>
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
@@ -9073,56 +9096,56 @@
       <c r="AX57" s="12"/>
     </row>
     <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="37" t="s">
+      <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="38"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="39"/>
-      <c r="L58" s="38"/>
-      <c r="M58" s="39"/>
-      <c r="N58" s="38"/>
-      <c r="O58" s="39"/>
-      <c r="P58" s="38"/>
-      <c r="Q58" s="39"/>
-      <c r="R58" s="38"/>
-      <c r="S58" s="39"/>
-      <c r="T58" s="38"/>
-      <c r="U58" s="39"/>
-      <c r="V58" s="38"/>
-      <c r="W58" s="39"/>
-      <c r="X58" s="38"/>
-      <c r="Y58" s="39"/>
-      <c r="Z58" s="38"/>
-      <c r="AA58" s="39"/>
-      <c r="AB58" s="38"/>
-      <c r="AC58" s="39"/>
-      <c r="AD58" s="38"/>
-      <c r="AE58" s="39"/>
-      <c r="AF58" s="38"/>
-      <c r="AG58" s="39"/>
-      <c r="AH58" s="38"/>
-      <c r="AI58" s="39"/>
-      <c r="AJ58" s="38"/>
-      <c r="AK58" s="39"/>
-      <c r="AL58" s="38"/>
-      <c r="AM58" s="39"/>
-      <c r="AN58" s="38"/>
-      <c r="AO58" s="39"/>
-      <c r="AP58" s="38"/>
-      <c r="AQ58" s="38"/>
-      <c r="AR58" s="38"/>
-      <c r="AS58" s="38"/>
-      <c r="AT58" s="38"/>
-      <c r="AU58" s="39"/>
-      <c r="AV58" s="34"/>
+      <c r="B58" s="34"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="34"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="34"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="34"/>
+      <c r="M58" s="35"/>
+      <c r="N58" s="34"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="34"/>
+      <c r="Q58" s="35"/>
+      <c r="R58" s="34"/>
+      <c r="S58" s="35"/>
+      <c r="T58" s="34"/>
+      <c r="U58" s="35"/>
+      <c r="V58" s="34"/>
+      <c r="W58" s="35"/>
+      <c r="X58" s="34"/>
+      <c r="Y58" s="35"/>
+      <c r="Z58" s="34"/>
+      <c r="AA58" s="35"/>
+      <c r="AB58" s="34"/>
+      <c r="AC58" s="35"/>
+      <c r="AD58" s="34"/>
+      <c r="AE58" s="35"/>
+      <c r="AF58" s="34"/>
+      <c r="AG58" s="35"/>
+      <c r="AH58" s="34"/>
+      <c r="AI58" s="35"/>
+      <c r="AJ58" s="34"/>
+      <c r="AK58" s="35"/>
+      <c r="AL58" s="34"/>
+      <c r="AM58" s="35"/>
+      <c r="AN58" s="34"/>
+      <c r="AO58" s="35"/>
+      <c r="AP58" s="34"/>
+      <c r="AQ58" s="34"/>
+      <c r="AR58" s="34"/>
+      <c r="AS58" s="34"/>
+      <c r="AT58" s="34"/>
+      <c r="AU58" s="35"/>
+      <c r="AV58" s="36"/>
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
@@ -9881,56 +9904,56 @@
       <c r="AX63" s="12"/>
     </row>
     <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="37" t="s">
+      <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="39"/>
-      <c r="L64" s="38"/>
-      <c r="M64" s="39"/>
-      <c r="N64" s="38"/>
-      <c r="O64" s="39"/>
-      <c r="P64" s="38"/>
-      <c r="Q64" s="39"/>
-      <c r="R64" s="38"/>
-      <c r="S64" s="39"/>
-      <c r="T64" s="38"/>
-      <c r="U64" s="39"/>
-      <c r="V64" s="38"/>
-      <c r="W64" s="39"/>
-      <c r="X64" s="38"/>
-      <c r="Y64" s="39"/>
-      <c r="Z64" s="38"/>
-      <c r="AA64" s="39"/>
-      <c r="AB64" s="38"/>
-      <c r="AC64" s="39"/>
-      <c r="AD64" s="38"/>
-      <c r="AE64" s="39"/>
-      <c r="AF64" s="38"/>
-      <c r="AG64" s="39"/>
-      <c r="AH64" s="38"/>
-      <c r="AI64" s="39"/>
-      <c r="AJ64" s="38"/>
-      <c r="AK64" s="39"/>
-      <c r="AL64" s="38"/>
-      <c r="AM64" s="39"/>
-      <c r="AN64" s="38"/>
-      <c r="AO64" s="39"/>
-      <c r="AP64" s="38"/>
-      <c r="AQ64" s="38"/>
-      <c r="AR64" s="38"/>
-      <c r="AS64" s="38"/>
-      <c r="AT64" s="38"/>
-      <c r="AU64" s="39"/>
-      <c r="AV64" s="34"/>
+      <c r="B64" s="34"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="35"/>
+      <c r="J64" s="34"/>
+      <c r="K64" s="35"/>
+      <c r="L64" s="34"/>
+      <c r="M64" s="35"/>
+      <c r="N64" s="34"/>
+      <c r="O64" s="35"/>
+      <c r="P64" s="34"/>
+      <c r="Q64" s="35"/>
+      <c r="R64" s="34"/>
+      <c r="S64" s="35"/>
+      <c r="T64" s="34"/>
+      <c r="U64" s="35"/>
+      <c r="V64" s="34"/>
+      <c r="W64" s="35"/>
+      <c r="X64" s="34"/>
+      <c r="Y64" s="35"/>
+      <c r="Z64" s="34"/>
+      <c r="AA64" s="35"/>
+      <c r="AB64" s="34"/>
+      <c r="AC64" s="35"/>
+      <c r="AD64" s="34"/>
+      <c r="AE64" s="35"/>
+      <c r="AF64" s="34"/>
+      <c r="AG64" s="35"/>
+      <c r="AH64" s="34"/>
+      <c r="AI64" s="35"/>
+      <c r="AJ64" s="34"/>
+      <c r="AK64" s="35"/>
+      <c r="AL64" s="34"/>
+      <c r="AM64" s="35"/>
+      <c r="AN64" s="34"/>
+      <c r="AO64" s="35"/>
+      <c r="AP64" s="34"/>
+      <c r="AQ64" s="34"/>
+      <c r="AR64" s="34"/>
+      <c r="AS64" s="34"/>
+      <c r="AT64" s="34"/>
+      <c r="AU64" s="35"/>
+      <c r="AV64" s="36"/>
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
@@ -10689,56 +10712,56 @@
       <c r="AX69" s="12"/>
     </row>
     <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="37" t="s">
+      <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B70" s="38"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="38"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="38"/>
-      <c r="K70" s="39"/>
-      <c r="L70" s="38"/>
-      <c r="M70" s="39"/>
-      <c r="N70" s="38"/>
-      <c r="O70" s="39"/>
-      <c r="P70" s="38"/>
-      <c r="Q70" s="39"/>
-      <c r="R70" s="38"/>
-      <c r="S70" s="39"/>
-      <c r="T70" s="38"/>
-      <c r="U70" s="39"/>
-      <c r="V70" s="38"/>
-      <c r="W70" s="39"/>
-      <c r="X70" s="38"/>
-      <c r="Y70" s="39"/>
-      <c r="Z70" s="38"/>
-      <c r="AA70" s="39"/>
-      <c r="AB70" s="38"/>
-      <c r="AC70" s="39"/>
-      <c r="AD70" s="38"/>
-      <c r="AE70" s="39"/>
-      <c r="AF70" s="38"/>
-      <c r="AG70" s="39"/>
-      <c r="AH70" s="38"/>
-      <c r="AI70" s="39"/>
-      <c r="AJ70" s="38"/>
-      <c r="AK70" s="39"/>
-      <c r="AL70" s="38"/>
-      <c r="AM70" s="39"/>
-      <c r="AN70" s="38"/>
-      <c r="AO70" s="39"/>
-      <c r="AP70" s="38"/>
-      <c r="AQ70" s="38"/>
-      <c r="AR70" s="38"/>
-      <c r="AS70" s="38"/>
-      <c r="AT70" s="38"/>
-      <c r="AU70" s="39"/>
-      <c r="AV70" s="34"/>
+      <c r="B70" s="34"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="34"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="34"/>
+      <c r="I70" s="35"/>
+      <c r="J70" s="34"/>
+      <c r="K70" s="35"/>
+      <c r="L70" s="34"/>
+      <c r="M70" s="35"/>
+      <c r="N70" s="34"/>
+      <c r="O70" s="35"/>
+      <c r="P70" s="34"/>
+      <c r="Q70" s="35"/>
+      <c r="R70" s="34"/>
+      <c r="S70" s="35"/>
+      <c r="T70" s="34"/>
+      <c r="U70" s="35"/>
+      <c r="V70" s="34"/>
+      <c r="W70" s="35"/>
+      <c r="X70" s="34"/>
+      <c r="Y70" s="35"/>
+      <c r="Z70" s="34"/>
+      <c r="AA70" s="35"/>
+      <c r="AB70" s="34"/>
+      <c r="AC70" s="35"/>
+      <c r="AD70" s="34"/>
+      <c r="AE70" s="35"/>
+      <c r="AF70" s="34"/>
+      <c r="AG70" s="35"/>
+      <c r="AH70" s="34"/>
+      <c r="AI70" s="35"/>
+      <c r="AJ70" s="34"/>
+      <c r="AK70" s="35"/>
+      <c r="AL70" s="34"/>
+      <c r="AM70" s="35"/>
+      <c r="AN70" s="34"/>
+      <c r="AO70" s="35"/>
+      <c r="AP70" s="34"/>
+      <c r="AQ70" s="34"/>
+      <c r="AR70" s="34"/>
+      <c r="AS70" s="34"/>
+      <c r="AT70" s="34"/>
+      <c r="AU70" s="35"/>
+      <c r="AV70" s="36"/>
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
@@ -11497,56 +11520,56 @@
       <c r="AX75" s="12"/>
     </row>
     <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="37" t="s">
+      <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="38"/>
-      <c r="C76" s="39"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="39"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="39"/>
-      <c r="L76" s="38"/>
-      <c r="M76" s="39"/>
-      <c r="N76" s="38"/>
-      <c r="O76" s="39"/>
-      <c r="P76" s="38"/>
-      <c r="Q76" s="39"/>
-      <c r="R76" s="38"/>
-      <c r="S76" s="39"/>
-      <c r="T76" s="38"/>
-      <c r="U76" s="39"/>
-      <c r="V76" s="38"/>
-      <c r="W76" s="39"/>
-      <c r="X76" s="38"/>
-      <c r="Y76" s="39"/>
-      <c r="Z76" s="38"/>
-      <c r="AA76" s="39"/>
-      <c r="AB76" s="38"/>
-      <c r="AC76" s="39"/>
-      <c r="AD76" s="38"/>
-      <c r="AE76" s="39"/>
-      <c r="AF76" s="38"/>
-      <c r="AG76" s="39"/>
-      <c r="AH76" s="38"/>
-      <c r="AI76" s="39"/>
-      <c r="AJ76" s="38"/>
-      <c r="AK76" s="39"/>
-      <c r="AL76" s="38"/>
-      <c r="AM76" s="39"/>
-      <c r="AN76" s="38"/>
-      <c r="AO76" s="39"/>
-      <c r="AP76" s="38"/>
-      <c r="AQ76" s="38"/>
-      <c r="AR76" s="38"/>
-      <c r="AS76" s="38"/>
-      <c r="AT76" s="38"/>
-      <c r="AU76" s="39"/>
-      <c r="AV76" s="34"/>
+      <c r="B76" s="34"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="34"/>
+      <c r="E76" s="35"/>
+      <c r="F76" s="34"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="35"/>
+      <c r="J76" s="34"/>
+      <c r="K76" s="35"/>
+      <c r="L76" s="34"/>
+      <c r="M76" s="35"/>
+      <c r="N76" s="34"/>
+      <c r="O76" s="35"/>
+      <c r="P76" s="34"/>
+      <c r="Q76" s="35"/>
+      <c r="R76" s="34"/>
+      <c r="S76" s="35"/>
+      <c r="T76" s="34"/>
+      <c r="U76" s="35"/>
+      <c r="V76" s="34"/>
+      <c r="W76" s="35"/>
+      <c r="X76" s="34"/>
+      <c r="Y76" s="35"/>
+      <c r="Z76" s="34"/>
+      <c r="AA76" s="35"/>
+      <c r="AB76" s="34"/>
+      <c r="AC76" s="35"/>
+      <c r="AD76" s="34"/>
+      <c r="AE76" s="35"/>
+      <c r="AF76" s="34"/>
+      <c r="AG76" s="35"/>
+      <c r="AH76" s="34"/>
+      <c r="AI76" s="35"/>
+      <c r="AJ76" s="34"/>
+      <c r="AK76" s="35"/>
+      <c r="AL76" s="34"/>
+      <c r="AM76" s="35"/>
+      <c r="AN76" s="34"/>
+      <c r="AO76" s="35"/>
+      <c r="AP76" s="34"/>
+      <c r="AQ76" s="34"/>
+      <c r="AR76" s="34"/>
+      <c r="AS76" s="34"/>
+      <c r="AT76" s="34"/>
+      <c r="AU76" s="35"/>
+      <c r="AV76" s="36"/>
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
@@ -12305,56 +12328,56 @@
       <c r="AX81" s="12"/>
     </row>
     <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="37" t="s">
+      <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B82" s="38"/>
-      <c r="C82" s="39"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="39"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="39"/>
-      <c r="H82" s="38"/>
-      <c r="I82" s="39"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="39"/>
-      <c r="L82" s="38"/>
-      <c r="M82" s="39"/>
-      <c r="N82" s="38"/>
-      <c r="O82" s="39"/>
-      <c r="P82" s="38"/>
-      <c r="Q82" s="39"/>
-      <c r="R82" s="38"/>
-      <c r="S82" s="39"/>
-      <c r="T82" s="38"/>
-      <c r="U82" s="39"/>
-      <c r="V82" s="38"/>
-      <c r="W82" s="39"/>
-      <c r="X82" s="38"/>
-      <c r="Y82" s="39"/>
-      <c r="Z82" s="38"/>
-      <c r="AA82" s="39"/>
-      <c r="AB82" s="38"/>
-      <c r="AC82" s="39"/>
-      <c r="AD82" s="38"/>
-      <c r="AE82" s="39"/>
-      <c r="AF82" s="38"/>
-      <c r="AG82" s="39"/>
-      <c r="AH82" s="38"/>
-      <c r="AI82" s="39"/>
-      <c r="AJ82" s="38"/>
-      <c r="AK82" s="39"/>
-      <c r="AL82" s="38"/>
-      <c r="AM82" s="39"/>
-      <c r="AN82" s="38"/>
-      <c r="AO82" s="39"/>
-      <c r="AP82" s="38"/>
-      <c r="AQ82" s="38"/>
-      <c r="AR82" s="38"/>
-      <c r="AS82" s="38"/>
-      <c r="AT82" s="38"/>
-      <c r="AU82" s="39"/>
-      <c r="AV82" s="34"/>
+      <c r="B82" s="34"/>
+      <c r="C82" s="35"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="35"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="34"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="34"/>
+      <c r="K82" s="35"/>
+      <c r="L82" s="34"/>
+      <c r="M82" s="35"/>
+      <c r="N82" s="34"/>
+      <c r="O82" s="35"/>
+      <c r="P82" s="34"/>
+      <c r="Q82" s="35"/>
+      <c r="R82" s="34"/>
+      <c r="S82" s="35"/>
+      <c r="T82" s="34"/>
+      <c r="U82" s="35"/>
+      <c r="V82" s="34"/>
+      <c r="W82" s="35"/>
+      <c r="X82" s="34"/>
+      <c r="Y82" s="35"/>
+      <c r="Z82" s="34"/>
+      <c r="AA82" s="35"/>
+      <c r="AB82" s="34"/>
+      <c r="AC82" s="35"/>
+      <c r="AD82" s="34"/>
+      <c r="AE82" s="35"/>
+      <c r="AF82" s="34"/>
+      <c r="AG82" s="35"/>
+      <c r="AH82" s="34"/>
+      <c r="AI82" s="35"/>
+      <c r="AJ82" s="34"/>
+      <c r="AK82" s="35"/>
+      <c r="AL82" s="34"/>
+      <c r="AM82" s="35"/>
+      <c r="AN82" s="34"/>
+      <c r="AO82" s="35"/>
+      <c r="AP82" s="34"/>
+      <c r="AQ82" s="34"/>
+      <c r="AR82" s="34"/>
+      <c r="AS82" s="34"/>
+      <c r="AT82" s="34"/>
+      <c r="AU82" s="35"/>
+      <c r="AV82" s="36"/>
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
@@ -13461,56 +13484,56 @@
       <c r="AX89" s="12"/>
     </row>
     <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="37" t="s">
+      <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="38"/>
-      <c r="C90" s="39"/>
-      <c r="D90" s="38"/>
-      <c r="E90" s="39"/>
-      <c r="F90" s="38"/>
-      <c r="G90" s="39"/>
-      <c r="H90" s="38"/>
-      <c r="I90" s="39"/>
-      <c r="J90" s="38"/>
-      <c r="K90" s="39"/>
-      <c r="L90" s="38"/>
-      <c r="M90" s="39"/>
-      <c r="N90" s="38"/>
-      <c r="O90" s="39"/>
-      <c r="P90" s="38"/>
-      <c r="Q90" s="39"/>
-      <c r="R90" s="38"/>
-      <c r="S90" s="39"/>
-      <c r="T90" s="38"/>
-      <c r="U90" s="39"/>
-      <c r="V90" s="38"/>
-      <c r="W90" s="39"/>
-      <c r="X90" s="38"/>
-      <c r="Y90" s="39"/>
-      <c r="Z90" s="38"/>
-      <c r="AA90" s="39"/>
-      <c r="AB90" s="38"/>
-      <c r="AC90" s="39"/>
-      <c r="AD90" s="38"/>
-      <c r="AE90" s="39"/>
-      <c r="AF90" s="38"/>
-      <c r="AG90" s="39"/>
-      <c r="AH90" s="38"/>
-      <c r="AI90" s="39"/>
-      <c r="AJ90" s="38"/>
-      <c r="AK90" s="39"/>
-      <c r="AL90" s="38"/>
-      <c r="AM90" s="39"/>
-      <c r="AN90" s="38"/>
-      <c r="AO90" s="39"/>
-      <c r="AP90" s="38"/>
-      <c r="AQ90" s="38"/>
-      <c r="AR90" s="38"/>
-      <c r="AS90" s="38"/>
-      <c r="AT90" s="38"/>
-      <c r="AU90" s="39"/>
-      <c r="AV90" s="34"/>
+      <c r="B90" s="34"/>
+      <c r="C90" s="35"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="35"/>
+      <c r="F90" s="34"/>
+      <c r="G90" s="35"/>
+      <c r="H90" s="34"/>
+      <c r="I90" s="35"/>
+      <c r="J90" s="34"/>
+      <c r="K90" s="35"/>
+      <c r="L90" s="34"/>
+      <c r="M90" s="35"/>
+      <c r="N90" s="34"/>
+      <c r="O90" s="35"/>
+      <c r="P90" s="34"/>
+      <c r="Q90" s="35"/>
+      <c r="R90" s="34"/>
+      <c r="S90" s="35"/>
+      <c r="T90" s="34"/>
+      <c r="U90" s="35"/>
+      <c r="V90" s="34"/>
+      <c r="W90" s="35"/>
+      <c r="X90" s="34"/>
+      <c r="Y90" s="35"/>
+      <c r="Z90" s="34"/>
+      <c r="AA90" s="35"/>
+      <c r="AB90" s="34"/>
+      <c r="AC90" s="35"/>
+      <c r="AD90" s="34"/>
+      <c r="AE90" s="35"/>
+      <c r="AF90" s="34"/>
+      <c r="AG90" s="35"/>
+      <c r="AH90" s="34"/>
+      <c r="AI90" s="35"/>
+      <c r="AJ90" s="34"/>
+      <c r="AK90" s="35"/>
+      <c r="AL90" s="34"/>
+      <c r="AM90" s="35"/>
+      <c r="AN90" s="34"/>
+      <c r="AO90" s="35"/>
+      <c r="AP90" s="34"/>
+      <c r="AQ90" s="34"/>
+      <c r="AR90" s="34"/>
+      <c r="AS90" s="34"/>
+      <c r="AT90" s="34"/>
+      <c r="AU90" s="35"/>
+      <c r="AV90" s="36"/>
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
@@ -14617,56 +14640,56 @@
       <c r="AX97" s="12"/>
     </row>
     <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="37" t="s">
+      <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="B98" s="38"/>
-      <c r="C98" s="39"/>
-      <c r="D98" s="38"/>
-      <c r="E98" s="39"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="39"/>
-      <c r="H98" s="38"/>
-      <c r="I98" s="39"/>
-      <c r="J98" s="38"/>
-      <c r="K98" s="39"/>
-      <c r="L98" s="38"/>
-      <c r="M98" s="39"/>
-      <c r="N98" s="38"/>
-      <c r="O98" s="39"/>
-      <c r="P98" s="38"/>
-      <c r="Q98" s="39"/>
-      <c r="R98" s="38"/>
-      <c r="S98" s="39"/>
-      <c r="T98" s="38"/>
-      <c r="U98" s="39"/>
-      <c r="V98" s="38"/>
-      <c r="W98" s="39"/>
-      <c r="X98" s="38"/>
-      <c r="Y98" s="39"/>
-      <c r="Z98" s="38"/>
-      <c r="AA98" s="39"/>
-      <c r="AB98" s="38"/>
-      <c r="AC98" s="39"/>
-      <c r="AD98" s="38"/>
-      <c r="AE98" s="39"/>
-      <c r="AF98" s="38"/>
-      <c r="AG98" s="39"/>
-      <c r="AH98" s="38"/>
-      <c r="AI98" s="39"/>
-      <c r="AJ98" s="38"/>
-      <c r="AK98" s="39"/>
-      <c r="AL98" s="38"/>
-      <c r="AM98" s="39"/>
-      <c r="AN98" s="38"/>
-      <c r="AO98" s="39"/>
-      <c r="AP98" s="38"/>
-      <c r="AQ98" s="38"/>
-      <c r="AR98" s="38"/>
-      <c r="AS98" s="38"/>
-      <c r="AT98" s="38"/>
-      <c r="AU98" s="39"/>
-      <c r="AV98" s="34"/>
+      <c r="B98" s="34"/>
+      <c r="C98" s="35"/>
+      <c r="D98" s="34"/>
+      <c r="E98" s="35"/>
+      <c r="F98" s="34"/>
+      <c r="G98" s="35"/>
+      <c r="H98" s="34"/>
+      <c r="I98" s="35"/>
+      <c r="J98" s="34"/>
+      <c r="K98" s="35"/>
+      <c r="L98" s="34"/>
+      <c r="M98" s="35"/>
+      <c r="N98" s="34"/>
+      <c r="O98" s="35"/>
+      <c r="P98" s="34"/>
+      <c r="Q98" s="35"/>
+      <c r="R98" s="34"/>
+      <c r="S98" s="35"/>
+      <c r="T98" s="34"/>
+      <c r="U98" s="35"/>
+      <c r="V98" s="34"/>
+      <c r="W98" s="35"/>
+      <c r="X98" s="34"/>
+      <c r="Y98" s="35"/>
+      <c r="Z98" s="34"/>
+      <c r="AA98" s="35"/>
+      <c r="AB98" s="34"/>
+      <c r="AC98" s="35"/>
+      <c r="AD98" s="34"/>
+      <c r="AE98" s="35"/>
+      <c r="AF98" s="34"/>
+      <c r="AG98" s="35"/>
+      <c r="AH98" s="34"/>
+      <c r="AI98" s="35"/>
+      <c r="AJ98" s="34"/>
+      <c r="AK98" s="35"/>
+      <c r="AL98" s="34"/>
+      <c r="AM98" s="35"/>
+      <c r="AN98" s="34"/>
+      <c r="AO98" s="35"/>
+      <c r="AP98" s="34"/>
+      <c r="AQ98" s="34"/>
+      <c r="AR98" s="34"/>
+      <c r="AS98" s="34"/>
+      <c r="AT98" s="34"/>
+      <c r="AU98" s="35"/>
+      <c r="AV98" s="36"/>
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
@@ -15773,56 +15796,56 @@
       <c r="AX105" s="12"/>
     </row>
     <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="37" t="s">
+      <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="B106" s="38"/>
-      <c r="C106" s="39"/>
-      <c r="D106" s="38"/>
-      <c r="E106" s="39"/>
-      <c r="F106" s="38"/>
-      <c r="G106" s="39"/>
-      <c r="H106" s="38"/>
-      <c r="I106" s="39"/>
-      <c r="J106" s="38"/>
-      <c r="K106" s="39"/>
-      <c r="L106" s="38"/>
-      <c r="M106" s="39"/>
-      <c r="N106" s="38"/>
-      <c r="O106" s="39"/>
-      <c r="P106" s="38"/>
-      <c r="Q106" s="39"/>
-      <c r="R106" s="38"/>
-      <c r="S106" s="39"/>
-      <c r="T106" s="38"/>
-      <c r="U106" s="39"/>
-      <c r="V106" s="38"/>
-      <c r="W106" s="39"/>
-      <c r="X106" s="38"/>
-      <c r="Y106" s="39"/>
-      <c r="Z106" s="38"/>
-      <c r="AA106" s="39"/>
-      <c r="AB106" s="38"/>
-      <c r="AC106" s="39"/>
-      <c r="AD106" s="38"/>
-      <c r="AE106" s="39"/>
-      <c r="AF106" s="38"/>
-      <c r="AG106" s="39"/>
-      <c r="AH106" s="38"/>
-      <c r="AI106" s="39"/>
-      <c r="AJ106" s="38"/>
-      <c r="AK106" s="39"/>
-      <c r="AL106" s="38"/>
-      <c r="AM106" s="39"/>
-      <c r="AN106" s="38"/>
-      <c r="AO106" s="39"/>
-      <c r="AP106" s="38"/>
-      <c r="AQ106" s="38"/>
-      <c r="AR106" s="38"/>
-      <c r="AS106" s="38"/>
-      <c r="AT106" s="38"/>
-      <c r="AU106" s="39"/>
-      <c r="AV106" s="34"/>
+      <c r="B106" s="34"/>
+      <c r="C106" s="35"/>
+      <c r="D106" s="34"/>
+      <c r="E106" s="35"/>
+      <c r="F106" s="34"/>
+      <c r="G106" s="35"/>
+      <c r="H106" s="34"/>
+      <c r="I106" s="35"/>
+      <c r="J106" s="34"/>
+      <c r="K106" s="35"/>
+      <c r="L106" s="34"/>
+      <c r="M106" s="35"/>
+      <c r="N106" s="34"/>
+      <c r="O106" s="35"/>
+      <c r="P106" s="34"/>
+      <c r="Q106" s="35"/>
+      <c r="R106" s="34"/>
+      <c r="S106" s="35"/>
+      <c r="T106" s="34"/>
+      <c r="U106" s="35"/>
+      <c r="V106" s="34"/>
+      <c r="W106" s="35"/>
+      <c r="X106" s="34"/>
+      <c r="Y106" s="35"/>
+      <c r="Z106" s="34"/>
+      <c r="AA106" s="35"/>
+      <c r="AB106" s="34"/>
+      <c r="AC106" s="35"/>
+      <c r="AD106" s="34"/>
+      <c r="AE106" s="35"/>
+      <c r="AF106" s="34"/>
+      <c r="AG106" s="35"/>
+      <c r="AH106" s="34"/>
+      <c r="AI106" s="35"/>
+      <c r="AJ106" s="34"/>
+      <c r="AK106" s="35"/>
+      <c r="AL106" s="34"/>
+      <c r="AM106" s="35"/>
+      <c r="AN106" s="34"/>
+      <c r="AO106" s="35"/>
+      <c r="AP106" s="34"/>
+      <c r="AQ106" s="34"/>
+      <c r="AR106" s="34"/>
+      <c r="AS106" s="34"/>
+      <c r="AT106" s="34"/>
+      <c r="AU106" s="35"/>
+      <c r="AV106" s="36"/>
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
@@ -16639,110 +16662,110 @@
       <c r="AX112" s="12"/>
     </row>
     <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="42" t="s">
+      <c r="A113" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="38"/>
-      <c r="C113" s="39"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="39"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="39"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="39"/>
-      <c r="J113" s="38"/>
-      <c r="K113" s="39"/>
-      <c r="L113" s="38"/>
-      <c r="M113" s="39"/>
-      <c r="N113" s="38"/>
-      <c r="O113" s="39"/>
-      <c r="P113" s="38"/>
-      <c r="Q113" s="39"/>
-      <c r="R113" s="38"/>
-      <c r="S113" s="39"/>
-      <c r="T113" s="38"/>
-      <c r="U113" s="39"/>
-      <c r="V113" s="38"/>
-      <c r="W113" s="39"/>
-      <c r="X113" s="38"/>
-      <c r="Y113" s="39"/>
-      <c r="Z113" s="38"/>
-      <c r="AA113" s="39"/>
-      <c r="AB113" s="38"/>
-      <c r="AC113" s="39"/>
-      <c r="AD113" s="38"/>
-      <c r="AE113" s="39"/>
-      <c r="AF113" s="38"/>
-      <c r="AG113" s="39"/>
-      <c r="AH113" s="38"/>
-      <c r="AI113" s="39"/>
-      <c r="AJ113" s="38"/>
-      <c r="AK113" s="39"/>
-      <c r="AL113" s="38"/>
-      <c r="AM113" s="39"/>
-      <c r="AN113" s="38"/>
-      <c r="AO113" s="39"/>
-      <c r="AP113" s="38"/>
-      <c r="AQ113" s="38"/>
-      <c r="AR113" s="38"/>
-      <c r="AS113" s="38"/>
-      <c r="AT113" s="38"/>
-      <c r="AU113" s="39"/>
-      <c r="AV113" s="34"/>
+      <c r="B113" s="34"/>
+      <c r="C113" s="35"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="35"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="35"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="35"/>
+      <c r="J113" s="34"/>
+      <c r="K113" s="35"/>
+      <c r="L113" s="34"/>
+      <c r="M113" s="35"/>
+      <c r="N113" s="34"/>
+      <c r="O113" s="35"/>
+      <c r="P113" s="34"/>
+      <c r="Q113" s="35"/>
+      <c r="R113" s="34"/>
+      <c r="S113" s="35"/>
+      <c r="T113" s="34"/>
+      <c r="U113" s="35"/>
+      <c r="V113" s="34"/>
+      <c r="W113" s="35"/>
+      <c r="X113" s="34"/>
+      <c r="Y113" s="35"/>
+      <c r="Z113" s="34"/>
+      <c r="AA113" s="35"/>
+      <c r="AB113" s="34"/>
+      <c r="AC113" s="35"/>
+      <c r="AD113" s="34"/>
+      <c r="AE113" s="35"/>
+      <c r="AF113" s="34"/>
+      <c r="AG113" s="35"/>
+      <c r="AH113" s="34"/>
+      <c r="AI113" s="35"/>
+      <c r="AJ113" s="34"/>
+      <c r="AK113" s="35"/>
+      <c r="AL113" s="34"/>
+      <c r="AM113" s="35"/>
+      <c r="AN113" s="34"/>
+      <c r="AO113" s="35"/>
+      <c r="AP113" s="34"/>
+      <c r="AQ113" s="34"/>
+      <c r="AR113" s="34"/>
+      <c r="AS113" s="34"/>
+      <c r="AT113" s="34"/>
+      <c r="AU113" s="35"/>
+      <c r="AV113" s="36"/>
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
     <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="37" t="s">
+      <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="B114" s="38"/>
-      <c r="C114" s="39"/>
-      <c r="D114" s="38"/>
-      <c r="E114" s="39"/>
-      <c r="F114" s="38"/>
-      <c r="G114" s="39"/>
-      <c r="H114" s="38"/>
-      <c r="I114" s="39"/>
-      <c r="J114" s="38"/>
-      <c r="K114" s="39"/>
-      <c r="L114" s="38"/>
-      <c r="M114" s="39"/>
-      <c r="N114" s="38"/>
-      <c r="O114" s="39"/>
-      <c r="P114" s="38"/>
-      <c r="Q114" s="39"/>
-      <c r="R114" s="38"/>
-      <c r="S114" s="39"/>
-      <c r="T114" s="38"/>
-      <c r="U114" s="39"/>
-      <c r="V114" s="38"/>
-      <c r="W114" s="39"/>
-      <c r="X114" s="38"/>
-      <c r="Y114" s="39"/>
-      <c r="Z114" s="38"/>
-      <c r="AA114" s="39"/>
-      <c r="AB114" s="38"/>
-      <c r="AC114" s="39"/>
-      <c r="AD114" s="38"/>
-      <c r="AE114" s="39"/>
-      <c r="AF114" s="38"/>
-      <c r="AG114" s="39"/>
-      <c r="AH114" s="38"/>
-      <c r="AI114" s="39"/>
-      <c r="AJ114" s="38"/>
-      <c r="AK114" s="39"/>
-      <c r="AL114" s="38"/>
-      <c r="AM114" s="39"/>
-      <c r="AN114" s="38"/>
-      <c r="AO114" s="39"/>
-      <c r="AP114" s="38"/>
-      <c r="AQ114" s="38"/>
-      <c r="AR114" s="38"/>
-      <c r="AS114" s="38"/>
-      <c r="AT114" s="38"/>
-      <c r="AU114" s="39"/>
-      <c r="AV114" s="34"/>
+      <c r="B114" s="34"/>
+      <c r="C114" s="35"/>
+      <c r="D114" s="34"/>
+      <c r="E114" s="35"/>
+      <c r="F114" s="34"/>
+      <c r="G114" s="35"/>
+      <c r="H114" s="34"/>
+      <c r="I114" s="35"/>
+      <c r="J114" s="34"/>
+      <c r="K114" s="35"/>
+      <c r="L114" s="34"/>
+      <c r="M114" s="35"/>
+      <c r="N114" s="34"/>
+      <c r="O114" s="35"/>
+      <c r="P114" s="34"/>
+      <c r="Q114" s="35"/>
+      <c r="R114" s="34"/>
+      <c r="S114" s="35"/>
+      <c r="T114" s="34"/>
+      <c r="U114" s="35"/>
+      <c r="V114" s="34"/>
+      <c r="W114" s="35"/>
+      <c r="X114" s="34"/>
+      <c r="Y114" s="35"/>
+      <c r="Z114" s="34"/>
+      <c r="AA114" s="35"/>
+      <c r="AB114" s="34"/>
+      <c r="AC114" s="35"/>
+      <c r="AD114" s="34"/>
+      <c r="AE114" s="35"/>
+      <c r="AF114" s="34"/>
+      <c r="AG114" s="35"/>
+      <c r="AH114" s="34"/>
+      <c r="AI114" s="35"/>
+      <c r="AJ114" s="34"/>
+      <c r="AK114" s="35"/>
+      <c r="AL114" s="34"/>
+      <c r="AM114" s="35"/>
+      <c r="AN114" s="34"/>
+      <c r="AO114" s="35"/>
+      <c r="AP114" s="34"/>
+      <c r="AQ114" s="34"/>
+      <c r="AR114" s="34"/>
+      <c r="AS114" s="34"/>
+      <c r="AT114" s="34"/>
+      <c r="AU114" s="35"/>
+      <c r="AV114" s="36"/>
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
@@ -16935,56 +16958,56 @@
       <c r="AX116" s="12"/>
     </row>
     <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="37" t="s">
+      <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B117" s="38"/>
-      <c r="C117" s="39"/>
-      <c r="D117" s="38"/>
-      <c r="E117" s="39"/>
-      <c r="F117" s="38"/>
-      <c r="G117" s="39"/>
-      <c r="H117" s="38"/>
-      <c r="I117" s="39"/>
-      <c r="J117" s="38"/>
-      <c r="K117" s="39"/>
-      <c r="L117" s="38"/>
-      <c r="M117" s="39"/>
-      <c r="N117" s="38"/>
-      <c r="O117" s="39"/>
-      <c r="P117" s="38"/>
-      <c r="Q117" s="39"/>
-      <c r="R117" s="38"/>
-      <c r="S117" s="39"/>
-      <c r="T117" s="38"/>
-      <c r="U117" s="39"/>
-      <c r="V117" s="38"/>
-      <c r="W117" s="39"/>
-      <c r="X117" s="38"/>
-      <c r="Y117" s="39"/>
-      <c r="Z117" s="38"/>
-      <c r="AA117" s="39"/>
-      <c r="AB117" s="38"/>
-      <c r="AC117" s="39"/>
-      <c r="AD117" s="38"/>
-      <c r="AE117" s="39"/>
-      <c r="AF117" s="38"/>
-      <c r="AG117" s="39"/>
-      <c r="AH117" s="38"/>
-      <c r="AI117" s="39"/>
-      <c r="AJ117" s="38"/>
-      <c r="AK117" s="39"/>
-      <c r="AL117" s="38"/>
-      <c r="AM117" s="39"/>
-      <c r="AN117" s="38"/>
-      <c r="AO117" s="39"/>
-      <c r="AP117" s="38"/>
-      <c r="AQ117" s="38"/>
-      <c r="AR117" s="38"/>
-      <c r="AS117" s="38"/>
-      <c r="AT117" s="38"/>
-      <c r="AU117" s="39"/>
-      <c r="AV117" s="34"/>
+      <c r="B117" s="34"/>
+      <c r="C117" s="35"/>
+      <c r="D117" s="34"/>
+      <c r="E117" s="35"/>
+      <c r="F117" s="34"/>
+      <c r="G117" s="35"/>
+      <c r="H117" s="34"/>
+      <c r="I117" s="35"/>
+      <c r="J117" s="34"/>
+      <c r="K117" s="35"/>
+      <c r="L117" s="34"/>
+      <c r="M117" s="35"/>
+      <c r="N117" s="34"/>
+      <c r="O117" s="35"/>
+      <c r="P117" s="34"/>
+      <c r="Q117" s="35"/>
+      <c r="R117" s="34"/>
+      <c r="S117" s="35"/>
+      <c r="T117" s="34"/>
+      <c r="U117" s="35"/>
+      <c r="V117" s="34"/>
+      <c r="W117" s="35"/>
+      <c r="X117" s="34"/>
+      <c r="Y117" s="35"/>
+      <c r="Z117" s="34"/>
+      <c r="AA117" s="35"/>
+      <c r="AB117" s="34"/>
+      <c r="AC117" s="35"/>
+      <c r="AD117" s="34"/>
+      <c r="AE117" s="35"/>
+      <c r="AF117" s="34"/>
+      <c r="AG117" s="35"/>
+      <c r="AH117" s="34"/>
+      <c r="AI117" s="35"/>
+      <c r="AJ117" s="34"/>
+      <c r="AK117" s="35"/>
+      <c r="AL117" s="34"/>
+      <c r="AM117" s="35"/>
+      <c r="AN117" s="34"/>
+      <c r="AO117" s="35"/>
+      <c r="AP117" s="34"/>
+      <c r="AQ117" s="34"/>
+      <c r="AR117" s="34"/>
+      <c r="AS117" s="34"/>
+      <c r="AT117" s="34"/>
+      <c r="AU117" s="35"/>
+      <c r="AV117" s="36"/>
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
@@ -17307,56 +17330,56 @@
       <c r="AX120" s="12"/>
     </row>
     <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="37" t="s">
+      <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="B121" s="38"/>
-      <c r="C121" s="39"/>
-      <c r="D121" s="38"/>
-      <c r="E121" s="39"/>
-      <c r="F121" s="38"/>
-      <c r="G121" s="39"/>
-      <c r="H121" s="38"/>
-      <c r="I121" s="39"/>
-      <c r="J121" s="38"/>
-      <c r="K121" s="39"/>
-      <c r="L121" s="38"/>
-      <c r="M121" s="39"/>
-      <c r="N121" s="38"/>
-      <c r="O121" s="39"/>
-      <c r="P121" s="38"/>
-      <c r="Q121" s="39"/>
-      <c r="R121" s="38"/>
-      <c r="S121" s="39"/>
-      <c r="T121" s="38"/>
-      <c r="U121" s="39"/>
-      <c r="V121" s="38"/>
-      <c r="W121" s="39"/>
-      <c r="X121" s="38"/>
-      <c r="Y121" s="39"/>
-      <c r="Z121" s="38"/>
-      <c r="AA121" s="39"/>
-      <c r="AB121" s="38"/>
-      <c r="AC121" s="39"/>
-      <c r="AD121" s="38"/>
-      <c r="AE121" s="39"/>
-      <c r="AF121" s="38"/>
-      <c r="AG121" s="39"/>
-      <c r="AH121" s="38"/>
-      <c r="AI121" s="39"/>
-      <c r="AJ121" s="38"/>
-      <c r="AK121" s="39"/>
-      <c r="AL121" s="38"/>
-      <c r="AM121" s="39"/>
-      <c r="AN121" s="38"/>
-      <c r="AO121" s="39"/>
-      <c r="AP121" s="38"/>
-      <c r="AQ121" s="38"/>
-      <c r="AR121" s="38"/>
-      <c r="AS121" s="38"/>
-      <c r="AT121" s="38"/>
-      <c r="AU121" s="39"/>
-      <c r="AV121" s="34"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="35"/>
+      <c r="D121" s="34"/>
+      <c r="E121" s="35"/>
+      <c r="F121" s="34"/>
+      <c r="G121" s="35"/>
+      <c r="H121" s="34"/>
+      <c r="I121" s="35"/>
+      <c r="J121" s="34"/>
+      <c r="K121" s="35"/>
+      <c r="L121" s="34"/>
+      <c r="M121" s="35"/>
+      <c r="N121" s="34"/>
+      <c r="O121" s="35"/>
+      <c r="P121" s="34"/>
+      <c r="Q121" s="35"/>
+      <c r="R121" s="34"/>
+      <c r="S121" s="35"/>
+      <c r="T121" s="34"/>
+      <c r="U121" s="35"/>
+      <c r="V121" s="34"/>
+      <c r="W121" s="35"/>
+      <c r="X121" s="34"/>
+      <c r="Y121" s="35"/>
+      <c r="Z121" s="34"/>
+      <c r="AA121" s="35"/>
+      <c r="AB121" s="34"/>
+      <c r="AC121" s="35"/>
+      <c r="AD121" s="34"/>
+      <c r="AE121" s="35"/>
+      <c r="AF121" s="34"/>
+      <c r="AG121" s="35"/>
+      <c r="AH121" s="34"/>
+      <c r="AI121" s="35"/>
+      <c r="AJ121" s="34"/>
+      <c r="AK121" s="35"/>
+      <c r="AL121" s="34"/>
+      <c r="AM121" s="35"/>
+      <c r="AN121" s="34"/>
+      <c r="AO121" s="35"/>
+      <c r="AP121" s="34"/>
+      <c r="AQ121" s="34"/>
+      <c r="AR121" s="34"/>
+      <c r="AS121" s="34"/>
+      <c r="AT121" s="34"/>
+      <c r="AU121" s="35"/>
+      <c r="AV121" s="36"/>
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
@@ -17809,56 +17832,56 @@
       <c r="AX125" s="12"/>
     </row>
     <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="37" t="s">
+      <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="B126" s="38"/>
-      <c r="C126" s="39"/>
-      <c r="D126" s="38"/>
-      <c r="E126" s="39"/>
-      <c r="F126" s="38"/>
-      <c r="G126" s="39"/>
-      <c r="H126" s="38"/>
-      <c r="I126" s="39"/>
-      <c r="J126" s="38"/>
-      <c r="K126" s="39"/>
-      <c r="L126" s="38"/>
-      <c r="M126" s="39"/>
-      <c r="N126" s="38"/>
-      <c r="O126" s="39"/>
-      <c r="P126" s="38"/>
-      <c r="Q126" s="39"/>
-      <c r="R126" s="38"/>
-      <c r="S126" s="39"/>
-      <c r="T126" s="38"/>
-      <c r="U126" s="39"/>
-      <c r="V126" s="38"/>
-      <c r="W126" s="39"/>
-      <c r="X126" s="38"/>
-      <c r="Y126" s="39"/>
-      <c r="Z126" s="38"/>
-      <c r="AA126" s="39"/>
-      <c r="AB126" s="38"/>
-      <c r="AC126" s="39"/>
-      <c r="AD126" s="38"/>
-      <c r="AE126" s="39"/>
-      <c r="AF126" s="38"/>
-      <c r="AG126" s="39"/>
-      <c r="AH126" s="38"/>
-      <c r="AI126" s="39"/>
-      <c r="AJ126" s="38"/>
-      <c r="AK126" s="39"/>
-      <c r="AL126" s="38"/>
-      <c r="AM126" s="39"/>
-      <c r="AN126" s="38"/>
-      <c r="AO126" s="39"/>
-      <c r="AP126" s="38"/>
-      <c r="AQ126" s="38"/>
-      <c r="AR126" s="38"/>
-      <c r="AS126" s="38"/>
-      <c r="AT126" s="38"/>
-      <c r="AU126" s="39"/>
-      <c r="AV126" s="34"/>
+      <c r="B126" s="34"/>
+      <c r="C126" s="35"/>
+      <c r="D126" s="34"/>
+      <c r="E126" s="35"/>
+      <c r="F126" s="34"/>
+      <c r="G126" s="35"/>
+      <c r="H126" s="34"/>
+      <c r="I126" s="35"/>
+      <c r="J126" s="34"/>
+      <c r="K126" s="35"/>
+      <c r="L126" s="34"/>
+      <c r="M126" s="35"/>
+      <c r="N126" s="34"/>
+      <c r="O126" s="35"/>
+      <c r="P126" s="34"/>
+      <c r="Q126" s="35"/>
+      <c r="R126" s="34"/>
+      <c r="S126" s="35"/>
+      <c r="T126" s="34"/>
+      <c r="U126" s="35"/>
+      <c r="V126" s="34"/>
+      <c r="W126" s="35"/>
+      <c r="X126" s="34"/>
+      <c r="Y126" s="35"/>
+      <c r="Z126" s="34"/>
+      <c r="AA126" s="35"/>
+      <c r="AB126" s="34"/>
+      <c r="AC126" s="35"/>
+      <c r="AD126" s="34"/>
+      <c r="AE126" s="35"/>
+      <c r="AF126" s="34"/>
+      <c r="AG126" s="35"/>
+      <c r="AH126" s="34"/>
+      <c r="AI126" s="35"/>
+      <c r="AJ126" s="34"/>
+      <c r="AK126" s="35"/>
+      <c r="AL126" s="34"/>
+      <c r="AM126" s="35"/>
+      <c r="AN126" s="34"/>
+      <c r="AO126" s="35"/>
+      <c r="AP126" s="34"/>
+      <c r="AQ126" s="34"/>
+      <c r="AR126" s="34"/>
+      <c r="AS126" s="34"/>
+      <c r="AT126" s="34"/>
+      <c r="AU126" s="35"/>
+      <c r="AV126" s="36"/>
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
@@ -18311,56 +18334,56 @@
       <c r="AX130" s="12"/>
     </row>
     <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="37" t="s">
+      <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="B131" s="38"/>
-      <c r="C131" s="39"/>
-      <c r="D131" s="38"/>
-      <c r="E131" s="39"/>
-      <c r="F131" s="38"/>
-      <c r="G131" s="39"/>
-      <c r="H131" s="38"/>
-      <c r="I131" s="39"/>
-      <c r="J131" s="38"/>
-      <c r="K131" s="39"/>
-      <c r="L131" s="38"/>
-      <c r="M131" s="39"/>
-      <c r="N131" s="38"/>
-      <c r="O131" s="39"/>
-      <c r="P131" s="38"/>
-      <c r="Q131" s="39"/>
-      <c r="R131" s="38"/>
-      <c r="S131" s="39"/>
-      <c r="T131" s="38"/>
-      <c r="U131" s="39"/>
-      <c r="V131" s="38"/>
-      <c r="W131" s="39"/>
-      <c r="X131" s="38"/>
-      <c r="Y131" s="39"/>
-      <c r="Z131" s="38"/>
-      <c r="AA131" s="39"/>
-      <c r="AB131" s="38"/>
-      <c r="AC131" s="39"/>
-      <c r="AD131" s="38"/>
-      <c r="AE131" s="39"/>
-      <c r="AF131" s="38"/>
-      <c r="AG131" s="39"/>
-      <c r="AH131" s="38"/>
-      <c r="AI131" s="39"/>
-      <c r="AJ131" s="38"/>
-      <c r="AK131" s="39"/>
-      <c r="AL131" s="38"/>
-      <c r="AM131" s="39"/>
-      <c r="AN131" s="38"/>
-      <c r="AO131" s="39"/>
-      <c r="AP131" s="38"/>
-      <c r="AQ131" s="38"/>
-      <c r="AR131" s="38"/>
-      <c r="AS131" s="38"/>
-      <c r="AT131" s="38"/>
-      <c r="AU131" s="39"/>
-      <c r="AV131" s="34"/>
+      <c r="B131" s="34"/>
+      <c r="C131" s="35"/>
+      <c r="D131" s="34"/>
+      <c r="E131" s="35"/>
+      <c r="F131" s="34"/>
+      <c r="G131" s="35"/>
+      <c r="H131" s="34"/>
+      <c r="I131" s="35"/>
+      <c r="J131" s="34"/>
+      <c r="K131" s="35"/>
+      <c r="L131" s="34"/>
+      <c r="M131" s="35"/>
+      <c r="N131" s="34"/>
+      <c r="O131" s="35"/>
+      <c r="P131" s="34"/>
+      <c r="Q131" s="35"/>
+      <c r="R131" s="34"/>
+      <c r="S131" s="35"/>
+      <c r="T131" s="34"/>
+      <c r="U131" s="35"/>
+      <c r="V131" s="34"/>
+      <c r="W131" s="35"/>
+      <c r="X131" s="34"/>
+      <c r="Y131" s="35"/>
+      <c r="Z131" s="34"/>
+      <c r="AA131" s="35"/>
+      <c r="AB131" s="34"/>
+      <c r="AC131" s="35"/>
+      <c r="AD131" s="34"/>
+      <c r="AE131" s="35"/>
+      <c r="AF131" s="34"/>
+      <c r="AG131" s="35"/>
+      <c r="AH131" s="34"/>
+      <c r="AI131" s="35"/>
+      <c r="AJ131" s="34"/>
+      <c r="AK131" s="35"/>
+      <c r="AL131" s="34"/>
+      <c r="AM131" s="35"/>
+      <c r="AN131" s="34"/>
+      <c r="AO131" s="35"/>
+      <c r="AP131" s="34"/>
+      <c r="AQ131" s="34"/>
+      <c r="AR131" s="34"/>
+      <c r="AS131" s="34"/>
+      <c r="AT131" s="34"/>
+      <c r="AU131" s="35"/>
+      <c r="AV131" s="36"/>
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
@@ -18683,56 +18706,56 @@
       <c r="AX134" s="12"/>
     </row>
     <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="37" t="s">
+      <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="B135" s="38"/>
-      <c r="C135" s="39"/>
-      <c r="D135" s="38"/>
-      <c r="E135" s="39"/>
-      <c r="F135" s="38"/>
-      <c r="G135" s="39"/>
-      <c r="H135" s="38"/>
-      <c r="I135" s="39"/>
-      <c r="J135" s="38"/>
-      <c r="K135" s="39"/>
-      <c r="L135" s="38"/>
-      <c r="M135" s="39"/>
-      <c r="N135" s="38"/>
-      <c r="O135" s="39"/>
-      <c r="P135" s="38"/>
-      <c r="Q135" s="39"/>
-      <c r="R135" s="38"/>
-      <c r="S135" s="39"/>
-      <c r="T135" s="38"/>
-      <c r="U135" s="39"/>
-      <c r="V135" s="38"/>
-      <c r="W135" s="39"/>
-      <c r="X135" s="38"/>
-      <c r="Y135" s="39"/>
-      <c r="Z135" s="38"/>
-      <c r="AA135" s="39"/>
-      <c r="AB135" s="38"/>
-      <c r="AC135" s="39"/>
-      <c r="AD135" s="38"/>
-      <c r="AE135" s="39"/>
-      <c r="AF135" s="38"/>
-      <c r="AG135" s="39"/>
-      <c r="AH135" s="38"/>
-      <c r="AI135" s="39"/>
-      <c r="AJ135" s="38"/>
-      <c r="AK135" s="39"/>
-      <c r="AL135" s="38"/>
-      <c r="AM135" s="39"/>
-      <c r="AN135" s="38"/>
-      <c r="AO135" s="39"/>
-      <c r="AP135" s="38"/>
-      <c r="AQ135" s="38"/>
-      <c r="AR135" s="38"/>
-      <c r="AS135" s="38"/>
-      <c r="AT135" s="38"/>
-      <c r="AU135" s="39"/>
-      <c r="AV135" s="34"/>
+      <c r="B135" s="34"/>
+      <c r="C135" s="35"/>
+      <c r="D135" s="34"/>
+      <c r="E135" s="35"/>
+      <c r="F135" s="34"/>
+      <c r="G135" s="35"/>
+      <c r="H135" s="34"/>
+      <c r="I135" s="35"/>
+      <c r="J135" s="34"/>
+      <c r="K135" s="35"/>
+      <c r="L135" s="34"/>
+      <c r="M135" s="35"/>
+      <c r="N135" s="34"/>
+      <c r="O135" s="35"/>
+      <c r="P135" s="34"/>
+      <c r="Q135" s="35"/>
+      <c r="R135" s="34"/>
+      <c r="S135" s="35"/>
+      <c r="T135" s="34"/>
+      <c r="U135" s="35"/>
+      <c r="V135" s="34"/>
+      <c r="W135" s="35"/>
+      <c r="X135" s="34"/>
+      <c r="Y135" s="35"/>
+      <c r="Z135" s="34"/>
+      <c r="AA135" s="35"/>
+      <c r="AB135" s="34"/>
+      <c r="AC135" s="35"/>
+      <c r="AD135" s="34"/>
+      <c r="AE135" s="35"/>
+      <c r="AF135" s="34"/>
+      <c r="AG135" s="35"/>
+      <c r="AH135" s="34"/>
+      <c r="AI135" s="35"/>
+      <c r="AJ135" s="34"/>
+      <c r="AK135" s="35"/>
+      <c r="AL135" s="34"/>
+      <c r="AM135" s="35"/>
+      <c r="AN135" s="34"/>
+      <c r="AO135" s="35"/>
+      <c r="AP135" s="34"/>
+      <c r="AQ135" s="34"/>
+      <c r="AR135" s="34"/>
+      <c r="AS135" s="34"/>
+      <c r="AT135" s="34"/>
+      <c r="AU135" s="35"/>
+      <c r="AV135" s="36"/>
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
@@ -19185,56 +19208,56 @@
       <c r="AX139" s="12"/>
     </row>
     <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="37" t="s">
+      <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B140" s="38"/>
-      <c r="C140" s="39"/>
-      <c r="D140" s="38"/>
-      <c r="E140" s="39"/>
-      <c r="F140" s="38"/>
-      <c r="G140" s="39"/>
-      <c r="H140" s="38"/>
-      <c r="I140" s="39"/>
-      <c r="J140" s="38"/>
-      <c r="K140" s="39"/>
-      <c r="L140" s="38"/>
-      <c r="M140" s="39"/>
-      <c r="N140" s="38"/>
-      <c r="O140" s="39"/>
-      <c r="P140" s="38"/>
-      <c r="Q140" s="39"/>
-      <c r="R140" s="38"/>
-      <c r="S140" s="39"/>
-      <c r="T140" s="38"/>
-      <c r="U140" s="39"/>
-      <c r="V140" s="38"/>
-      <c r="W140" s="39"/>
-      <c r="X140" s="38"/>
-      <c r="Y140" s="39"/>
-      <c r="Z140" s="38"/>
-      <c r="AA140" s="39"/>
-      <c r="AB140" s="38"/>
-      <c r="AC140" s="39"/>
-      <c r="AD140" s="38"/>
-      <c r="AE140" s="39"/>
-      <c r="AF140" s="38"/>
-      <c r="AG140" s="39"/>
-      <c r="AH140" s="38"/>
-      <c r="AI140" s="39"/>
-      <c r="AJ140" s="38"/>
-      <c r="AK140" s="39"/>
-      <c r="AL140" s="38"/>
-      <c r="AM140" s="39"/>
-      <c r="AN140" s="38"/>
-      <c r="AO140" s="39"/>
-      <c r="AP140" s="38"/>
-      <c r="AQ140" s="38"/>
-      <c r="AR140" s="38"/>
-      <c r="AS140" s="38"/>
-      <c r="AT140" s="38"/>
-      <c r="AU140" s="39"/>
-      <c r="AV140" s="34"/>
+      <c r="B140" s="34"/>
+      <c r="C140" s="35"/>
+      <c r="D140" s="34"/>
+      <c r="E140" s="35"/>
+      <c r="F140" s="34"/>
+      <c r="G140" s="35"/>
+      <c r="H140" s="34"/>
+      <c r="I140" s="35"/>
+      <c r="J140" s="34"/>
+      <c r="K140" s="35"/>
+      <c r="L140" s="34"/>
+      <c r="M140" s="35"/>
+      <c r="N140" s="34"/>
+      <c r="O140" s="35"/>
+      <c r="P140" s="34"/>
+      <c r="Q140" s="35"/>
+      <c r="R140" s="34"/>
+      <c r="S140" s="35"/>
+      <c r="T140" s="34"/>
+      <c r="U140" s="35"/>
+      <c r="V140" s="34"/>
+      <c r="W140" s="35"/>
+      <c r="X140" s="34"/>
+      <c r="Y140" s="35"/>
+      <c r="Z140" s="34"/>
+      <c r="AA140" s="35"/>
+      <c r="AB140" s="34"/>
+      <c r="AC140" s="35"/>
+      <c r="AD140" s="34"/>
+      <c r="AE140" s="35"/>
+      <c r="AF140" s="34"/>
+      <c r="AG140" s="35"/>
+      <c r="AH140" s="34"/>
+      <c r="AI140" s="35"/>
+      <c r="AJ140" s="34"/>
+      <c r="AK140" s="35"/>
+      <c r="AL140" s="34"/>
+      <c r="AM140" s="35"/>
+      <c r="AN140" s="34"/>
+      <c r="AO140" s="35"/>
+      <c r="AP140" s="34"/>
+      <c r="AQ140" s="34"/>
+      <c r="AR140" s="34"/>
+      <c r="AS140" s="34"/>
+      <c r="AT140" s="34"/>
+      <c r="AU140" s="35"/>
+      <c r="AV140" s="36"/>
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
@@ -19615,110 +19638,110 @@
       <c r="AX144" s="12"/>
     </row>
     <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="42" t="s">
+      <c r="A145" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="B145" s="38"/>
-      <c r="C145" s="39"/>
-      <c r="D145" s="38"/>
-      <c r="E145" s="39"/>
-      <c r="F145" s="38"/>
-      <c r="G145" s="39"/>
-      <c r="H145" s="38"/>
-      <c r="I145" s="39"/>
-      <c r="J145" s="38"/>
-      <c r="K145" s="39"/>
-      <c r="L145" s="38"/>
-      <c r="M145" s="39"/>
-      <c r="N145" s="38"/>
-      <c r="O145" s="39"/>
-      <c r="P145" s="38"/>
-      <c r="Q145" s="39"/>
-      <c r="R145" s="38"/>
-      <c r="S145" s="39"/>
-      <c r="T145" s="38"/>
-      <c r="U145" s="39"/>
-      <c r="V145" s="38"/>
-      <c r="W145" s="39"/>
-      <c r="X145" s="38"/>
-      <c r="Y145" s="39"/>
-      <c r="Z145" s="38"/>
-      <c r="AA145" s="39"/>
-      <c r="AB145" s="38"/>
-      <c r="AC145" s="39"/>
-      <c r="AD145" s="38"/>
-      <c r="AE145" s="39"/>
-      <c r="AF145" s="38"/>
-      <c r="AG145" s="39"/>
-      <c r="AH145" s="38"/>
-      <c r="AI145" s="39"/>
-      <c r="AJ145" s="38"/>
-      <c r="AK145" s="39"/>
-      <c r="AL145" s="38"/>
-      <c r="AM145" s="39"/>
-      <c r="AN145" s="38"/>
-      <c r="AO145" s="39"/>
-      <c r="AP145" s="38"/>
-      <c r="AQ145" s="38"/>
-      <c r="AR145" s="38"/>
-      <c r="AS145" s="38"/>
-      <c r="AT145" s="38"/>
-      <c r="AU145" s="39"/>
-      <c r="AV145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="35"/>
+      <c r="D145" s="34"/>
+      <c r="E145" s="35"/>
+      <c r="F145" s="34"/>
+      <c r="G145" s="35"/>
+      <c r="H145" s="34"/>
+      <c r="I145" s="35"/>
+      <c r="J145" s="34"/>
+      <c r="K145" s="35"/>
+      <c r="L145" s="34"/>
+      <c r="M145" s="35"/>
+      <c r="N145" s="34"/>
+      <c r="O145" s="35"/>
+      <c r="P145" s="34"/>
+      <c r="Q145" s="35"/>
+      <c r="R145" s="34"/>
+      <c r="S145" s="35"/>
+      <c r="T145" s="34"/>
+      <c r="U145" s="35"/>
+      <c r="V145" s="34"/>
+      <c r="W145" s="35"/>
+      <c r="X145" s="34"/>
+      <c r="Y145" s="35"/>
+      <c r="Z145" s="34"/>
+      <c r="AA145" s="35"/>
+      <c r="AB145" s="34"/>
+      <c r="AC145" s="35"/>
+      <c r="AD145" s="34"/>
+      <c r="AE145" s="35"/>
+      <c r="AF145" s="34"/>
+      <c r="AG145" s="35"/>
+      <c r="AH145" s="34"/>
+      <c r="AI145" s="35"/>
+      <c r="AJ145" s="34"/>
+      <c r="AK145" s="35"/>
+      <c r="AL145" s="34"/>
+      <c r="AM145" s="35"/>
+      <c r="AN145" s="34"/>
+      <c r="AO145" s="35"/>
+      <c r="AP145" s="34"/>
+      <c r="AQ145" s="34"/>
+      <c r="AR145" s="34"/>
+      <c r="AS145" s="34"/>
+      <c r="AT145" s="34"/>
+      <c r="AU145" s="35"/>
+      <c r="AV145" s="36"/>
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
     <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="37" t="s">
+      <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B146" s="38"/>
-      <c r="C146" s="39"/>
-      <c r="D146" s="38"/>
-      <c r="E146" s="39"/>
-      <c r="F146" s="38"/>
-      <c r="G146" s="39"/>
-      <c r="H146" s="38"/>
-      <c r="I146" s="39"/>
-      <c r="J146" s="38"/>
-      <c r="K146" s="39"/>
-      <c r="L146" s="38"/>
-      <c r="M146" s="39"/>
-      <c r="N146" s="38"/>
-      <c r="O146" s="39"/>
-      <c r="P146" s="38"/>
-      <c r="Q146" s="39"/>
-      <c r="R146" s="38"/>
-      <c r="S146" s="39"/>
-      <c r="T146" s="38"/>
-      <c r="U146" s="39"/>
-      <c r="V146" s="38"/>
-      <c r="W146" s="39"/>
-      <c r="X146" s="38"/>
-      <c r="Y146" s="39"/>
-      <c r="Z146" s="38"/>
-      <c r="AA146" s="39"/>
-      <c r="AB146" s="38"/>
-      <c r="AC146" s="39"/>
-      <c r="AD146" s="38"/>
-      <c r="AE146" s="39"/>
-      <c r="AF146" s="38"/>
-      <c r="AG146" s="39"/>
-      <c r="AH146" s="38"/>
-      <c r="AI146" s="39"/>
-      <c r="AJ146" s="38"/>
-      <c r="AK146" s="39"/>
-      <c r="AL146" s="38"/>
-      <c r="AM146" s="39"/>
-      <c r="AN146" s="38"/>
-      <c r="AO146" s="39"/>
-      <c r="AP146" s="38"/>
-      <c r="AQ146" s="38"/>
-      <c r="AR146" s="38"/>
-      <c r="AS146" s="38"/>
-      <c r="AT146" s="38"/>
-      <c r="AU146" s="39"/>
-      <c r="AV146" s="34"/>
+      <c r="B146" s="34"/>
+      <c r="C146" s="35"/>
+      <c r="D146" s="34"/>
+      <c r="E146" s="35"/>
+      <c r="F146" s="34"/>
+      <c r="G146" s="35"/>
+      <c r="H146" s="34"/>
+      <c r="I146" s="35"/>
+      <c r="J146" s="34"/>
+      <c r="K146" s="35"/>
+      <c r="L146" s="34"/>
+      <c r="M146" s="35"/>
+      <c r="N146" s="34"/>
+      <c r="O146" s="35"/>
+      <c r="P146" s="34"/>
+      <c r="Q146" s="35"/>
+      <c r="R146" s="34"/>
+      <c r="S146" s="35"/>
+      <c r="T146" s="34"/>
+      <c r="U146" s="35"/>
+      <c r="V146" s="34"/>
+      <c r="W146" s="35"/>
+      <c r="X146" s="34"/>
+      <c r="Y146" s="35"/>
+      <c r="Z146" s="34"/>
+      <c r="AA146" s="35"/>
+      <c r="AB146" s="34"/>
+      <c r="AC146" s="35"/>
+      <c r="AD146" s="34"/>
+      <c r="AE146" s="35"/>
+      <c r="AF146" s="34"/>
+      <c r="AG146" s="35"/>
+      <c r="AH146" s="34"/>
+      <c r="AI146" s="35"/>
+      <c r="AJ146" s="34"/>
+      <c r="AK146" s="35"/>
+      <c r="AL146" s="34"/>
+      <c r="AM146" s="35"/>
+      <c r="AN146" s="34"/>
+      <c r="AO146" s="35"/>
+      <c r="AP146" s="34"/>
+      <c r="AQ146" s="34"/>
+      <c r="AR146" s="34"/>
+      <c r="AS146" s="34"/>
+      <c r="AT146" s="34"/>
+      <c r="AU146" s="35"/>
+      <c r="AV146" s="36"/>
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
@@ -20041,56 +20064,56 @@
       <c r="AX149" s="12"/>
     </row>
     <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="37" t="s">
+      <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="B150" s="38"/>
-      <c r="C150" s="39"/>
-      <c r="D150" s="38"/>
-      <c r="E150" s="39"/>
-      <c r="F150" s="38"/>
-      <c r="G150" s="39"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="39"/>
-      <c r="J150" s="38"/>
-      <c r="K150" s="39"/>
-      <c r="L150" s="38"/>
-      <c r="M150" s="39"/>
-      <c r="N150" s="38"/>
-      <c r="O150" s="39"/>
-      <c r="P150" s="38"/>
-      <c r="Q150" s="39"/>
-      <c r="R150" s="38"/>
-      <c r="S150" s="39"/>
-      <c r="T150" s="38"/>
-      <c r="U150" s="39"/>
-      <c r="V150" s="38"/>
-      <c r="W150" s="39"/>
-      <c r="X150" s="38"/>
-      <c r="Y150" s="39"/>
-      <c r="Z150" s="38"/>
-      <c r="AA150" s="39"/>
-      <c r="AB150" s="38"/>
-      <c r="AC150" s="39"/>
-      <c r="AD150" s="38"/>
-      <c r="AE150" s="39"/>
-      <c r="AF150" s="38"/>
-      <c r="AG150" s="39"/>
-      <c r="AH150" s="38"/>
-      <c r="AI150" s="39"/>
-      <c r="AJ150" s="38"/>
-      <c r="AK150" s="39"/>
-      <c r="AL150" s="38"/>
-      <c r="AM150" s="39"/>
-      <c r="AN150" s="38"/>
-      <c r="AO150" s="39"/>
-      <c r="AP150" s="38"/>
-      <c r="AQ150" s="38"/>
-      <c r="AR150" s="38"/>
-      <c r="AS150" s="38"/>
-      <c r="AT150" s="38"/>
-      <c r="AU150" s="39"/>
-      <c r="AV150" s="34"/>
+      <c r="B150" s="34"/>
+      <c r="C150" s="35"/>
+      <c r="D150" s="34"/>
+      <c r="E150" s="35"/>
+      <c r="F150" s="34"/>
+      <c r="G150" s="35"/>
+      <c r="H150" s="34"/>
+      <c r="I150" s="35"/>
+      <c r="J150" s="34"/>
+      <c r="K150" s="35"/>
+      <c r="L150" s="34"/>
+      <c r="M150" s="35"/>
+      <c r="N150" s="34"/>
+      <c r="O150" s="35"/>
+      <c r="P150" s="34"/>
+      <c r="Q150" s="35"/>
+      <c r="R150" s="34"/>
+      <c r="S150" s="35"/>
+      <c r="T150" s="34"/>
+      <c r="U150" s="35"/>
+      <c r="V150" s="34"/>
+      <c r="W150" s="35"/>
+      <c r="X150" s="34"/>
+      <c r="Y150" s="35"/>
+      <c r="Z150" s="34"/>
+      <c r="AA150" s="35"/>
+      <c r="AB150" s="34"/>
+      <c r="AC150" s="35"/>
+      <c r="AD150" s="34"/>
+      <c r="AE150" s="35"/>
+      <c r="AF150" s="34"/>
+      <c r="AG150" s="35"/>
+      <c r="AH150" s="34"/>
+      <c r="AI150" s="35"/>
+      <c r="AJ150" s="34"/>
+      <c r="AK150" s="35"/>
+      <c r="AL150" s="34"/>
+      <c r="AM150" s="35"/>
+      <c r="AN150" s="34"/>
+      <c r="AO150" s="35"/>
+      <c r="AP150" s="34"/>
+      <c r="AQ150" s="34"/>
+      <c r="AR150" s="34"/>
+      <c r="AS150" s="34"/>
+      <c r="AT150" s="34"/>
+      <c r="AU150" s="35"/>
+      <c r="AV150" s="36"/>
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
@@ -20283,56 +20306,56 @@
       <c r="AX152" s="12"/>
     </row>
     <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="37" t="s">
+      <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="B153" s="38"/>
-      <c r="C153" s="39"/>
-      <c r="D153" s="38"/>
-      <c r="E153" s="39"/>
-      <c r="F153" s="38"/>
-      <c r="G153" s="39"/>
-      <c r="H153" s="38"/>
-      <c r="I153" s="39"/>
-      <c r="J153" s="38"/>
-      <c r="K153" s="39"/>
-      <c r="L153" s="38"/>
-      <c r="M153" s="39"/>
-      <c r="N153" s="38"/>
-      <c r="O153" s="39"/>
-      <c r="P153" s="38"/>
-      <c r="Q153" s="39"/>
-      <c r="R153" s="38"/>
-      <c r="S153" s="39"/>
-      <c r="T153" s="38"/>
-      <c r="U153" s="39"/>
-      <c r="V153" s="38"/>
-      <c r="W153" s="39"/>
-      <c r="X153" s="38"/>
-      <c r="Y153" s="39"/>
-      <c r="Z153" s="38"/>
-      <c r="AA153" s="39"/>
-      <c r="AB153" s="38"/>
-      <c r="AC153" s="39"/>
-      <c r="AD153" s="38"/>
-      <c r="AE153" s="39"/>
-      <c r="AF153" s="38"/>
-      <c r="AG153" s="39"/>
-      <c r="AH153" s="38"/>
-      <c r="AI153" s="39"/>
-      <c r="AJ153" s="38"/>
-      <c r="AK153" s="39"/>
-      <c r="AL153" s="38"/>
-      <c r="AM153" s="39"/>
-      <c r="AN153" s="38"/>
-      <c r="AO153" s="39"/>
-      <c r="AP153" s="38"/>
-      <c r="AQ153" s="38"/>
-      <c r="AR153" s="38"/>
-      <c r="AS153" s="38"/>
-      <c r="AT153" s="38"/>
-      <c r="AU153" s="39"/>
-      <c r="AV153" s="34"/>
+      <c r="B153" s="34"/>
+      <c r="C153" s="35"/>
+      <c r="D153" s="34"/>
+      <c r="E153" s="35"/>
+      <c r="F153" s="34"/>
+      <c r="G153" s="35"/>
+      <c r="H153" s="34"/>
+      <c r="I153" s="35"/>
+      <c r="J153" s="34"/>
+      <c r="K153" s="35"/>
+      <c r="L153" s="34"/>
+      <c r="M153" s="35"/>
+      <c r="N153" s="34"/>
+      <c r="O153" s="35"/>
+      <c r="P153" s="34"/>
+      <c r="Q153" s="35"/>
+      <c r="R153" s="34"/>
+      <c r="S153" s="35"/>
+      <c r="T153" s="34"/>
+      <c r="U153" s="35"/>
+      <c r="V153" s="34"/>
+      <c r="W153" s="35"/>
+      <c r="X153" s="34"/>
+      <c r="Y153" s="35"/>
+      <c r="Z153" s="34"/>
+      <c r="AA153" s="35"/>
+      <c r="AB153" s="34"/>
+      <c r="AC153" s="35"/>
+      <c r="AD153" s="34"/>
+      <c r="AE153" s="35"/>
+      <c r="AF153" s="34"/>
+      <c r="AG153" s="35"/>
+      <c r="AH153" s="34"/>
+      <c r="AI153" s="35"/>
+      <c r="AJ153" s="34"/>
+      <c r="AK153" s="35"/>
+      <c r="AL153" s="34"/>
+      <c r="AM153" s="35"/>
+      <c r="AN153" s="34"/>
+      <c r="AO153" s="35"/>
+      <c r="AP153" s="34"/>
+      <c r="AQ153" s="34"/>
+      <c r="AR153" s="34"/>
+      <c r="AS153" s="34"/>
+      <c r="AT153" s="34"/>
+      <c r="AU153" s="35"/>
+      <c r="AV153" s="36"/>
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
@@ -20655,56 +20678,56 @@
       <c r="AX156" s="12"/>
     </row>
     <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="37" t="s">
+      <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="B157" s="38"/>
-      <c r="C157" s="39"/>
-      <c r="D157" s="38"/>
-      <c r="E157" s="39"/>
-      <c r="F157" s="38"/>
-      <c r="G157" s="39"/>
-      <c r="H157" s="38"/>
-      <c r="I157" s="39"/>
-      <c r="J157" s="38"/>
-      <c r="K157" s="39"/>
-      <c r="L157" s="38"/>
-      <c r="M157" s="39"/>
-      <c r="N157" s="38"/>
-      <c r="O157" s="39"/>
-      <c r="P157" s="38"/>
-      <c r="Q157" s="39"/>
-      <c r="R157" s="38"/>
-      <c r="S157" s="39"/>
-      <c r="T157" s="38"/>
-      <c r="U157" s="39"/>
-      <c r="V157" s="38"/>
-      <c r="W157" s="39"/>
-      <c r="X157" s="38"/>
-      <c r="Y157" s="39"/>
-      <c r="Z157" s="38"/>
-      <c r="AA157" s="39"/>
-      <c r="AB157" s="38"/>
-      <c r="AC157" s="39"/>
-      <c r="AD157" s="38"/>
-      <c r="AE157" s="39"/>
-      <c r="AF157" s="38"/>
-      <c r="AG157" s="39"/>
-      <c r="AH157" s="38"/>
-      <c r="AI157" s="39"/>
-      <c r="AJ157" s="38"/>
-      <c r="AK157" s="39"/>
-      <c r="AL157" s="38"/>
-      <c r="AM157" s="39"/>
-      <c r="AN157" s="38"/>
-      <c r="AO157" s="39"/>
-      <c r="AP157" s="38"/>
-      <c r="AQ157" s="38"/>
-      <c r="AR157" s="38"/>
-      <c r="AS157" s="38"/>
-      <c r="AT157" s="38"/>
-      <c r="AU157" s="39"/>
-      <c r="AV157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="35"/>
+      <c r="D157" s="34"/>
+      <c r="E157" s="35"/>
+      <c r="F157" s="34"/>
+      <c r="G157" s="35"/>
+      <c r="H157" s="34"/>
+      <c r="I157" s="35"/>
+      <c r="J157" s="34"/>
+      <c r="K157" s="35"/>
+      <c r="L157" s="34"/>
+      <c r="M157" s="35"/>
+      <c r="N157" s="34"/>
+      <c r="O157" s="35"/>
+      <c r="P157" s="34"/>
+      <c r="Q157" s="35"/>
+      <c r="R157" s="34"/>
+      <c r="S157" s="35"/>
+      <c r="T157" s="34"/>
+      <c r="U157" s="35"/>
+      <c r="V157" s="34"/>
+      <c r="W157" s="35"/>
+      <c r="X157" s="34"/>
+      <c r="Y157" s="35"/>
+      <c r="Z157" s="34"/>
+      <c r="AA157" s="35"/>
+      <c r="AB157" s="34"/>
+      <c r="AC157" s="35"/>
+      <c r="AD157" s="34"/>
+      <c r="AE157" s="35"/>
+      <c r="AF157" s="34"/>
+      <c r="AG157" s="35"/>
+      <c r="AH157" s="34"/>
+      <c r="AI157" s="35"/>
+      <c r="AJ157" s="34"/>
+      <c r="AK157" s="35"/>
+      <c r="AL157" s="34"/>
+      <c r="AM157" s="35"/>
+      <c r="AN157" s="34"/>
+      <c r="AO157" s="35"/>
+      <c r="AP157" s="34"/>
+      <c r="AQ157" s="34"/>
+      <c r="AR157" s="34"/>
+      <c r="AS157" s="34"/>
+      <c r="AT157" s="34"/>
+      <c r="AU157" s="35"/>
+      <c r="AV157" s="36"/>
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
@@ -21215,110 +21238,110 @@
       <c r="AX162" s="12"/>
     </row>
     <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="42" t="s">
+      <c r="A163" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="B163" s="38"/>
-      <c r="C163" s="39"/>
-      <c r="D163" s="38"/>
-      <c r="E163" s="39"/>
-      <c r="F163" s="38"/>
-      <c r="G163" s="39"/>
-      <c r="H163" s="38"/>
-      <c r="I163" s="39"/>
-      <c r="J163" s="38"/>
-      <c r="K163" s="39"/>
-      <c r="L163" s="38"/>
-      <c r="M163" s="39"/>
-      <c r="N163" s="38"/>
-      <c r="O163" s="39"/>
-      <c r="P163" s="38"/>
-      <c r="Q163" s="39"/>
-      <c r="R163" s="38"/>
-      <c r="S163" s="39"/>
-      <c r="T163" s="38"/>
-      <c r="U163" s="39"/>
-      <c r="V163" s="38"/>
-      <c r="W163" s="39"/>
-      <c r="X163" s="38"/>
-      <c r="Y163" s="39"/>
-      <c r="Z163" s="38"/>
-      <c r="AA163" s="39"/>
-      <c r="AB163" s="38"/>
-      <c r="AC163" s="39"/>
-      <c r="AD163" s="38"/>
-      <c r="AE163" s="39"/>
-      <c r="AF163" s="38"/>
-      <c r="AG163" s="39"/>
-      <c r="AH163" s="38"/>
-      <c r="AI163" s="39"/>
-      <c r="AJ163" s="38"/>
-      <c r="AK163" s="39"/>
-      <c r="AL163" s="38"/>
-      <c r="AM163" s="39"/>
-      <c r="AN163" s="38"/>
-      <c r="AO163" s="39"/>
-      <c r="AP163" s="38"/>
-      <c r="AQ163" s="38"/>
-      <c r="AR163" s="38"/>
-      <c r="AS163" s="38"/>
-      <c r="AT163" s="38"/>
-      <c r="AU163" s="39"/>
-      <c r="AV163" s="34"/>
+      <c r="B163" s="34"/>
+      <c r="C163" s="35"/>
+      <c r="D163" s="34"/>
+      <c r="E163" s="35"/>
+      <c r="F163" s="34"/>
+      <c r="G163" s="35"/>
+      <c r="H163" s="34"/>
+      <c r="I163" s="35"/>
+      <c r="J163" s="34"/>
+      <c r="K163" s="35"/>
+      <c r="L163" s="34"/>
+      <c r="M163" s="35"/>
+      <c r="N163" s="34"/>
+      <c r="O163" s="35"/>
+      <c r="P163" s="34"/>
+      <c r="Q163" s="35"/>
+      <c r="R163" s="34"/>
+      <c r="S163" s="35"/>
+      <c r="T163" s="34"/>
+      <c r="U163" s="35"/>
+      <c r="V163" s="34"/>
+      <c r="W163" s="35"/>
+      <c r="X163" s="34"/>
+      <c r="Y163" s="35"/>
+      <c r="Z163" s="34"/>
+      <c r="AA163" s="35"/>
+      <c r="AB163" s="34"/>
+      <c r="AC163" s="35"/>
+      <c r="AD163" s="34"/>
+      <c r="AE163" s="35"/>
+      <c r="AF163" s="34"/>
+      <c r="AG163" s="35"/>
+      <c r="AH163" s="34"/>
+      <c r="AI163" s="35"/>
+      <c r="AJ163" s="34"/>
+      <c r="AK163" s="35"/>
+      <c r="AL163" s="34"/>
+      <c r="AM163" s="35"/>
+      <c r="AN163" s="34"/>
+      <c r="AO163" s="35"/>
+      <c r="AP163" s="34"/>
+      <c r="AQ163" s="34"/>
+      <c r="AR163" s="34"/>
+      <c r="AS163" s="34"/>
+      <c r="AT163" s="34"/>
+      <c r="AU163" s="35"/>
+      <c r="AV163" s="36"/>
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
     <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="37" t="s">
+      <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="B164" s="38"/>
-      <c r="C164" s="39"/>
-      <c r="D164" s="38"/>
-      <c r="E164" s="39"/>
-      <c r="F164" s="38"/>
-      <c r="G164" s="39"/>
-      <c r="H164" s="38"/>
-      <c r="I164" s="39"/>
-      <c r="J164" s="38"/>
-      <c r="K164" s="39"/>
-      <c r="L164" s="38"/>
-      <c r="M164" s="39"/>
-      <c r="N164" s="38"/>
-      <c r="O164" s="39"/>
-      <c r="P164" s="38"/>
-      <c r="Q164" s="39"/>
-      <c r="R164" s="38"/>
-      <c r="S164" s="39"/>
-      <c r="T164" s="38"/>
-      <c r="U164" s="39"/>
-      <c r="V164" s="38"/>
-      <c r="W164" s="39"/>
-      <c r="X164" s="38"/>
-      <c r="Y164" s="39"/>
-      <c r="Z164" s="38"/>
-      <c r="AA164" s="39"/>
-      <c r="AB164" s="38"/>
-      <c r="AC164" s="39"/>
-      <c r="AD164" s="38"/>
-      <c r="AE164" s="39"/>
-      <c r="AF164" s="38"/>
-      <c r="AG164" s="39"/>
-      <c r="AH164" s="38"/>
-      <c r="AI164" s="39"/>
-      <c r="AJ164" s="38"/>
-      <c r="AK164" s="39"/>
-      <c r="AL164" s="38"/>
-      <c r="AM164" s="39"/>
-      <c r="AN164" s="38"/>
-      <c r="AO164" s="39"/>
-      <c r="AP164" s="38"/>
-      <c r="AQ164" s="38"/>
-      <c r="AR164" s="38"/>
-      <c r="AS164" s="38"/>
-      <c r="AT164" s="38"/>
-      <c r="AU164" s="39"/>
-      <c r="AV164" s="34"/>
+      <c r="B164" s="34"/>
+      <c r="C164" s="35"/>
+      <c r="D164" s="34"/>
+      <c r="E164" s="35"/>
+      <c r="F164" s="34"/>
+      <c r="G164" s="35"/>
+      <c r="H164" s="34"/>
+      <c r="I164" s="35"/>
+      <c r="J164" s="34"/>
+      <c r="K164" s="35"/>
+      <c r="L164" s="34"/>
+      <c r="M164" s="35"/>
+      <c r="N164" s="34"/>
+      <c r="O164" s="35"/>
+      <c r="P164" s="34"/>
+      <c r="Q164" s="35"/>
+      <c r="R164" s="34"/>
+      <c r="S164" s="35"/>
+      <c r="T164" s="34"/>
+      <c r="U164" s="35"/>
+      <c r="V164" s="34"/>
+      <c r="W164" s="35"/>
+      <c r="X164" s="34"/>
+      <c r="Y164" s="35"/>
+      <c r="Z164" s="34"/>
+      <c r="AA164" s="35"/>
+      <c r="AB164" s="34"/>
+      <c r="AC164" s="35"/>
+      <c r="AD164" s="34"/>
+      <c r="AE164" s="35"/>
+      <c r="AF164" s="34"/>
+      <c r="AG164" s="35"/>
+      <c r="AH164" s="34"/>
+      <c r="AI164" s="35"/>
+      <c r="AJ164" s="34"/>
+      <c r="AK164" s="35"/>
+      <c r="AL164" s="34"/>
+      <c r="AM164" s="35"/>
+      <c r="AN164" s="34"/>
+      <c r="AO164" s="35"/>
+      <c r="AP164" s="34"/>
+      <c r="AQ164" s="34"/>
+      <c r="AR164" s="34"/>
+      <c r="AS164" s="34"/>
+      <c r="AT164" s="34"/>
+      <c r="AU164" s="35"/>
+      <c r="AV164" s="36"/>
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
@@ -21511,56 +21534,56 @@
       <c r="AX166" s="12"/>
     </row>
     <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="37" t="s">
+      <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="B167" s="38"/>
-      <c r="C167" s="39"/>
-      <c r="D167" s="38"/>
-      <c r="E167" s="39"/>
-      <c r="F167" s="38"/>
-      <c r="G167" s="39"/>
-      <c r="H167" s="38"/>
-      <c r="I167" s="39"/>
-      <c r="J167" s="38"/>
-      <c r="K167" s="39"/>
-      <c r="L167" s="38"/>
-      <c r="M167" s="39"/>
-      <c r="N167" s="38"/>
-      <c r="O167" s="39"/>
-      <c r="P167" s="38"/>
-      <c r="Q167" s="39"/>
-      <c r="R167" s="38"/>
-      <c r="S167" s="39"/>
-      <c r="T167" s="38"/>
-      <c r="U167" s="39"/>
-      <c r="V167" s="38"/>
-      <c r="W167" s="39"/>
-      <c r="X167" s="38"/>
-      <c r="Y167" s="39"/>
-      <c r="Z167" s="38"/>
-      <c r="AA167" s="39"/>
-      <c r="AB167" s="38"/>
-      <c r="AC167" s="39"/>
-      <c r="AD167" s="38"/>
-      <c r="AE167" s="39"/>
-      <c r="AF167" s="38"/>
-      <c r="AG167" s="39"/>
-      <c r="AH167" s="38"/>
-      <c r="AI167" s="39"/>
-      <c r="AJ167" s="38"/>
-      <c r="AK167" s="39"/>
-      <c r="AL167" s="38"/>
-      <c r="AM167" s="39"/>
-      <c r="AN167" s="38"/>
-      <c r="AO167" s="39"/>
-      <c r="AP167" s="38"/>
-      <c r="AQ167" s="38"/>
-      <c r="AR167" s="38"/>
-      <c r="AS167" s="38"/>
-      <c r="AT167" s="38"/>
-      <c r="AU167" s="39"/>
-      <c r="AV167" s="34"/>
+      <c r="B167" s="34"/>
+      <c r="C167" s="35"/>
+      <c r="D167" s="34"/>
+      <c r="E167" s="35"/>
+      <c r="F167" s="34"/>
+      <c r="G167" s="35"/>
+      <c r="H167" s="34"/>
+      <c r="I167" s="35"/>
+      <c r="J167" s="34"/>
+      <c r="K167" s="35"/>
+      <c r="L167" s="34"/>
+      <c r="M167" s="35"/>
+      <c r="N167" s="34"/>
+      <c r="O167" s="35"/>
+      <c r="P167" s="34"/>
+      <c r="Q167" s="35"/>
+      <c r="R167" s="34"/>
+      <c r="S167" s="35"/>
+      <c r="T167" s="34"/>
+      <c r="U167" s="35"/>
+      <c r="V167" s="34"/>
+      <c r="W167" s="35"/>
+      <c r="X167" s="34"/>
+      <c r="Y167" s="35"/>
+      <c r="Z167" s="34"/>
+      <c r="AA167" s="35"/>
+      <c r="AB167" s="34"/>
+      <c r="AC167" s="35"/>
+      <c r="AD167" s="34"/>
+      <c r="AE167" s="35"/>
+      <c r="AF167" s="34"/>
+      <c r="AG167" s="35"/>
+      <c r="AH167" s="34"/>
+      <c r="AI167" s="35"/>
+      <c r="AJ167" s="34"/>
+      <c r="AK167" s="35"/>
+      <c r="AL167" s="34"/>
+      <c r="AM167" s="35"/>
+      <c r="AN167" s="34"/>
+      <c r="AO167" s="35"/>
+      <c r="AP167" s="34"/>
+      <c r="AQ167" s="34"/>
+      <c r="AR167" s="34"/>
+      <c r="AS167" s="34"/>
+      <c r="AT167" s="34"/>
+      <c r="AU167" s="35"/>
+      <c r="AV167" s="36"/>
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
@@ -21753,56 +21776,56 @@
       <c r="AX169" s="12"/>
     </row>
     <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="37" t="s">
+      <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="B170" s="38"/>
-      <c r="C170" s="39"/>
-      <c r="D170" s="38"/>
-      <c r="E170" s="39"/>
-      <c r="F170" s="38"/>
-      <c r="G170" s="39"/>
-      <c r="H170" s="38"/>
-      <c r="I170" s="39"/>
-      <c r="J170" s="38"/>
-      <c r="K170" s="39"/>
-      <c r="L170" s="38"/>
-      <c r="M170" s="39"/>
-      <c r="N170" s="38"/>
-      <c r="O170" s="39"/>
-      <c r="P170" s="38"/>
-      <c r="Q170" s="39"/>
-      <c r="R170" s="38"/>
-      <c r="S170" s="39"/>
-      <c r="T170" s="38"/>
-      <c r="U170" s="39"/>
-      <c r="V170" s="38"/>
-      <c r="W170" s="39"/>
-      <c r="X170" s="38"/>
-      <c r="Y170" s="39"/>
-      <c r="Z170" s="38"/>
-      <c r="AA170" s="39"/>
-      <c r="AB170" s="38"/>
-      <c r="AC170" s="39"/>
-      <c r="AD170" s="38"/>
-      <c r="AE170" s="39"/>
-      <c r="AF170" s="38"/>
-      <c r="AG170" s="39"/>
-      <c r="AH170" s="38"/>
-      <c r="AI170" s="39"/>
-      <c r="AJ170" s="38"/>
-      <c r="AK170" s="39"/>
-      <c r="AL170" s="38"/>
-      <c r="AM170" s="39"/>
-      <c r="AN170" s="38"/>
-      <c r="AO170" s="39"/>
-      <c r="AP170" s="38"/>
-      <c r="AQ170" s="38"/>
-      <c r="AR170" s="38"/>
-      <c r="AS170" s="38"/>
-      <c r="AT170" s="38"/>
-      <c r="AU170" s="39"/>
-      <c r="AV170" s="34"/>
+      <c r="B170" s="34"/>
+      <c r="C170" s="35"/>
+      <c r="D170" s="34"/>
+      <c r="E170" s="35"/>
+      <c r="F170" s="34"/>
+      <c r="G170" s="35"/>
+      <c r="H170" s="34"/>
+      <c r="I170" s="35"/>
+      <c r="J170" s="34"/>
+      <c r="K170" s="35"/>
+      <c r="L170" s="34"/>
+      <c r="M170" s="35"/>
+      <c r="N170" s="34"/>
+      <c r="O170" s="35"/>
+      <c r="P170" s="34"/>
+      <c r="Q170" s="35"/>
+      <c r="R170" s="34"/>
+      <c r="S170" s="35"/>
+      <c r="T170" s="34"/>
+      <c r="U170" s="35"/>
+      <c r="V170" s="34"/>
+      <c r="W170" s="35"/>
+      <c r="X170" s="34"/>
+      <c r="Y170" s="35"/>
+      <c r="Z170" s="34"/>
+      <c r="AA170" s="35"/>
+      <c r="AB170" s="34"/>
+      <c r="AC170" s="35"/>
+      <c r="AD170" s="34"/>
+      <c r="AE170" s="35"/>
+      <c r="AF170" s="34"/>
+      <c r="AG170" s="35"/>
+      <c r="AH170" s="34"/>
+      <c r="AI170" s="35"/>
+      <c r="AJ170" s="34"/>
+      <c r="AK170" s="35"/>
+      <c r="AL170" s="34"/>
+      <c r="AM170" s="35"/>
+      <c r="AN170" s="34"/>
+      <c r="AO170" s="35"/>
+      <c r="AP170" s="34"/>
+      <c r="AQ170" s="34"/>
+      <c r="AR170" s="34"/>
+      <c r="AS170" s="34"/>
+      <c r="AT170" s="34"/>
+      <c r="AU170" s="35"/>
+      <c r="AV170" s="36"/>
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
@@ -21995,56 +22018,56 @@
       <c r="AX172" s="12"/>
     </row>
     <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="37" t="s">
+      <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="B173" s="38"/>
-      <c r="C173" s="39"/>
-      <c r="D173" s="38"/>
-      <c r="E173" s="39"/>
-      <c r="F173" s="38"/>
-      <c r="G173" s="39"/>
-      <c r="H173" s="38"/>
-      <c r="I173" s="39"/>
-      <c r="J173" s="38"/>
-      <c r="K173" s="39"/>
-      <c r="L173" s="38"/>
-      <c r="M173" s="39"/>
-      <c r="N173" s="38"/>
-      <c r="O173" s="39"/>
-      <c r="P173" s="38"/>
-      <c r="Q173" s="39"/>
-      <c r="R173" s="38"/>
-      <c r="S173" s="39"/>
-      <c r="T173" s="38"/>
-      <c r="U173" s="39"/>
-      <c r="V173" s="38"/>
-      <c r="W173" s="39"/>
-      <c r="X173" s="38"/>
-      <c r="Y173" s="39"/>
-      <c r="Z173" s="38"/>
-      <c r="AA173" s="39"/>
-      <c r="AB173" s="38"/>
-      <c r="AC173" s="39"/>
-      <c r="AD173" s="38"/>
-      <c r="AE173" s="39"/>
-      <c r="AF173" s="38"/>
-      <c r="AG173" s="39"/>
-      <c r="AH173" s="38"/>
-      <c r="AI173" s="39"/>
-      <c r="AJ173" s="38"/>
-      <c r="AK173" s="39"/>
-      <c r="AL173" s="38"/>
-      <c r="AM173" s="39"/>
-      <c r="AN173" s="38"/>
-      <c r="AO173" s="39"/>
-      <c r="AP173" s="38"/>
-      <c r="AQ173" s="38"/>
-      <c r="AR173" s="38"/>
-      <c r="AS173" s="38"/>
-      <c r="AT173" s="38"/>
-      <c r="AU173" s="39"/>
-      <c r="AV173" s="34"/>
+      <c r="B173" s="34"/>
+      <c r="C173" s="35"/>
+      <c r="D173" s="34"/>
+      <c r="E173" s="35"/>
+      <c r="F173" s="34"/>
+      <c r="G173" s="35"/>
+      <c r="H173" s="34"/>
+      <c r="I173" s="35"/>
+      <c r="J173" s="34"/>
+      <c r="K173" s="35"/>
+      <c r="L173" s="34"/>
+      <c r="M173" s="35"/>
+      <c r="N173" s="34"/>
+      <c r="O173" s="35"/>
+      <c r="P173" s="34"/>
+      <c r="Q173" s="35"/>
+      <c r="R173" s="34"/>
+      <c r="S173" s="35"/>
+      <c r="T173" s="34"/>
+      <c r="U173" s="35"/>
+      <c r="V173" s="34"/>
+      <c r="W173" s="35"/>
+      <c r="X173" s="34"/>
+      <c r="Y173" s="35"/>
+      <c r="Z173" s="34"/>
+      <c r="AA173" s="35"/>
+      <c r="AB173" s="34"/>
+      <c r="AC173" s="35"/>
+      <c r="AD173" s="34"/>
+      <c r="AE173" s="35"/>
+      <c r="AF173" s="34"/>
+      <c r="AG173" s="35"/>
+      <c r="AH173" s="34"/>
+      <c r="AI173" s="35"/>
+      <c r="AJ173" s="34"/>
+      <c r="AK173" s="35"/>
+      <c r="AL173" s="34"/>
+      <c r="AM173" s="35"/>
+      <c r="AN173" s="34"/>
+      <c r="AO173" s="35"/>
+      <c r="AP173" s="34"/>
+      <c r="AQ173" s="34"/>
+      <c r="AR173" s="34"/>
+      <c r="AS173" s="34"/>
+      <c r="AT173" s="34"/>
+      <c r="AU173" s="35"/>
+      <c r="AV173" s="36"/>
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
@@ -22295,110 +22318,110 @@
       <c r="AX176" s="12"/>
     </row>
     <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="42" t="s">
+      <c r="A177" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="B177" s="38"/>
-      <c r="C177" s="39"/>
-      <c r="D177" s="38"/>
-      <c r="E177" s="39"/>
-      <c r="F177" s="38"/>
-      <c r="G177" s="39"/>
-      <c r="H177" s="38"/>
-      <c r="I177" s="39"/>
-      <c r="J177" s="38"/>
-      <c r="K177" s="39"/>
-      <c r="L177" s="38"/>
-      <c r="M177" s="39"/>
-      <c r="N177" s="38"/>
-      <c r="O177" s="39"/>
-      <c r="P177" s="38"/>
-      <c r="Q177" s="39"/>
-      <c r="R177" s="38"/>
-      <c r="S177" s="39"/>
-      <c r="T177" s="38"/>
-      <c r="U177" s="39"/>
-      <c r="V177" s="38"/>
-      <c r="W177" s="39"/>
-      <c r="X177" s="38"/>
-      <c r="Y177" s="39"/>
-      <c r="Z177" s="38"/>
-      <c r="AA177" s="39"/>
-      <c r="AB177" s="38"/>
-      <c r="AC177" s="39"/>
-      <c r="AD177" s="38"/>
-      <c r="AE177" s="39"/>
-      <c r="AF177" s="38"/>
-      <c r="AG177" s="39"/>
-      <c r="AH177" s="38"/>
-      <c r="AI177" s="39"/>
-      <c r="AJ177" s="38"/>
-      <c r="AK177" s="39"/>
-      <c r="AL177" s="38"/>
-      <c r="AM177" s="39"/>
-      <c r="AN177" s="38"/>
-      <c r="AO177" s="39"/>
-      <c r="AP177" s="38"/>
-      <c r="AQ177" s="38"/>
-      <c r="AR177" s="38"/>
-      <c r="AS177" s="38"/>
-      <c r="AT177" s="38"/>
-      <c r="AU177" s="39"/>
-      <c r="AV177" s="34"/>
+      <c r="B177" s="34"/>
+      <c r="C177" s="35"/>
+      <c r="D177" s="34"/>
+      <c r="E177" s="35"/>
+      <c r="F177" s="34"/>
+      <c r="G177" s="35"/>
+      <c r="H177" s="34"/>
+      <c r="I177" s="35"/>
+      <c r="J177" s="34"/>
+      <c r="K177" s="35"/>
+      <c r="L177" s="34"/>
+      <c r="M177" s="35"/>
+      <c r="N177" s="34"/>
+      <c r="O177" s="35"/>
+      <c r="P177" s="34"/>
+      <c r="Q177" s="35"/>
+      <c r="R177" s="34"/>
+      <c r="S177" s="35"/>
+      <c r="T177" s="34"/>
+      <c r="U177" s="35"/>
+      <c r="V177" s="34"/>
+      <c r="W177" s="35"/>
+      <c r="X177" s="34"/>
+      <c r="Y177" s="35"/>
+      <c r="Z177" s="34"/>
+      <c r="AA177" s="35"/>
+      <c r="AB177" s="34"/>
+      <c r="AC177" s="35"/>
+      <c r="AD177" s="34"/>
+      <c r="AE177" s="35"/>
+      <c r="AF177" s="34"/>
+      <c r="AG177" s="35"/>
+      <c r="AH177" s="34"/>
+      <c r="AI177" s="35"/>
+      <c r="AJ177" s="34"/>
+      <c r="AK177" s="35"/>
+      <c r="AL177" s="34"/>
+      <c r="AM177" s="35"/>
+      <c r="AN177" s="34"/>
+      <c r="AO177" s="35"/>
+      <c r="AP177" s="34"/>
+      <c r="AQ177" s="34"/>
+      <c r="AR177" s="34"/>
+      <c r="AS177" s="34"/>
+      <c r="AT177" s="34"/>
+      <c r="AU177" s="35"/>
+      <c r="AV177" s="36"/>
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
     <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="37" t="s">
+      <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="B178" s="38"/>
-      <c r="C178" s="39"/>
-      <c r="D178" s="38"/>
-      <c r="E178" s="39"/>
-      <c r="F178" s="38"/>
-      <c r="G178" s="39"/>
-      <c r="H178" s="38"/>
-      <c r="I178" s="39"/>
-      <c r="J178" s="38"/>
-      <c r="K178" s="39"/>
-      <c r="L178" s="38"/>
-      <c r="M178" s="39"/>
-      <c r="N178" s="38"/>
-      <c r="O178" s="39"/>
-      <c r="P178" s="38"/>
-      <c r="Q178" s="39"/>
-      <c r="R178" s="38"/>
-      <c r="S178" s="39"/>
-      <c r="T178" s="38"/>
-      <c r="U178" s="39"/>
-      <c r="V178" s="38"/>
-      <c r="W178" s="39"/>
-      <c r="X178" s="38"/>
-      <c r="Y178" s="39"/>
-      <c r="Z178" s="38"/>
-      <c r="AA178" s="39"/>
-      <c r="AB178" s="38"/>
-      <c r="AC178" s="39"/>
-      <c r="AD178" s="38"/>
-      <c r="AE178" s="39"/>
-      <c r="AF178" s="38"/>
-      <c r="AG178" s="39"/>
-      <c r="AH178" s="38"/>
-      <c r="AI178" s="39"/>
-      <c r="AJ178" s="38"/>
-      <c r="AK178" s="39"/>
-      <c r="AL178" s="38"/>
-      <c r="AM178" s="39"/>
-      <c r="AN178" s="38"/>
-      <c r="AO178" s="39"/>
-      <c r="AP178" s="38"/>
-      <c r="AQ178" s="38"/>
-      <c r="AR178" s="38"/>
-      <c r="AS178" s="38"/>
-      <c r="AT178" s="38"/>
-      <c r="AU178" s="39"/>
-      <c r="AV178" s="34"/>
+      <c r="B178" s="34"/>
+      <c r="C178" s="35"/>
+      <c r="D178" s="34"/>
+      <c r="E178" s="35"/>
+      <c r="F178" s="34"/>
+      <c r="G178" s="35"/>
+      <c r="H178" s="34"/>
+      <c r="I178" s="35"/>
+      <c r="J178" s="34"/>
+      <c r="K178" s="35"/>
+      <c r="L178" s="34"/>
+      <c r="M178" s="35"/>
+      <c r="N178" s="34"/>
+      <c r="O178" s="35"/>
+      <c r="P178" s="34"/>
+      <c r="Q178" s="35"/>
+      <c r="R178" s="34"/>
+      <c r="S178" s="35"/>
+      <c r="T178" s="34"/>
+      <c r="U178" s="35"/>
+      <c r="V178" s="34"/>
+      <c r="W178" s="35"/>
+      <c r="X178" s="34"/>
+      <c r="Y178" s="35"/>
+      <c r="Z178" s="34"/>
+      <c r="AA178" s="35"/>
+      <c r="AB178" s="34"/>
+      <c r="AC178" s="35"/>
+      <c r="AD178" s="34"/>
+      <c r="AE178" s="35"/>
+      <c r="AF178" s="34"/>
+      <c r="AG178" s="35"/>
+      <c r="AH178" s="34"/>
+      <c r="AI178" s="35"/>
+      <c r="AJ178" s="34"/>
+      <c r="AK178" s="35"/>
+      <c r="AL178" s="34"/>
+      <c r="AM178" s="35"/>
+      <c r="AN178" s="34"/>
+      <c r="AO178" s="35"/>
+      <c r="AP178" s="34"/>
+      <c r="AQ178" s="34"/>
+      <c r="AR178" s="34"/>
+      <c r="AS178" s="34"/>
+      <c r="AT178" s="34"/>
+      <c r="AU178" s="35"/>
+      <c r="AV178" s="36"/>
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
@@ -22591,56 +22614,56 @@
       <c r="AX180" s="12"/>
     </row>
     <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="37" t="s">
+      <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="B181" s="38"/>
-      <c r="C181" s="39"/>
-      <c r="D181" s="38"/>
-      <c r="E181" s="39"/>
-      <c r="F181" s="38"/>
-      <c r="G181" s="39"/>
-      <c r="H181" s="38"/>
-      <c r="I181" s="39"/>
-      <c r="J181" s="38"/>
-      <c r="K181" s="39"/>
-      <c r="L181" s="38"/>
-      <c r="M181" s="39"/>
-      <c r="N181" s="38"/>
-      <c r="O181" s="39"/>
-      <c r="P181" s="38"/>
-      <c r="Q181" s="39"/>
-      <c r="R181" s="38"/>
-      <c r="S181" s="39"/>
-      <c r="T181" s="38"/>
-      <c r="U181" s="39"/>
-      <c r="V181" s="38"/>
-      <c r="W181" s="39"/>
-      <c r="X181" s="38"/>
-      <c r="Y181" s="39"/>
-      <c r="Z181" s="38"/>
-      <c r="AA181" s="39"/>
-      <c r="AB181" s="38"/>
-      <c r="AC181" s="39"/>
-      <c r="AD181" s="38"/>
-      <c r="AE181" s="39"/>
-      <c r="AF181" s="38"/>
-      <c r="AG181" s="39"/>
-      <c r="AH181" s="38"/>
-      <c r="AI181" s="39"/>
-      <c r="AJ181" s="38"/>
-      <c r="AK181" s="39"/>
-      <c r="AL181" s="38"/>
-      <c r="AM181" s="39"/>
-      <c r="AN181" s="38"/>
-      <c r="AO181" s="39"/>
-      <c r="AP181" s="38"/>
-      <c r="AQ181" s="38"/>
-      <c r="AR181" s="38"/>
-      <c r="AS181" s="38"/>
-      <c r="AT181" s="38"/>
-      <c r="AU181" s="39"/>
-      <c r="AV181" s="34"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="35"/>
+      <c r="D181" s="34"/>
+      <c r="E181" s="35"/>
+      <c r="F181" s="34"/>
+      <c r="G181" s="35"/>
+      <c r="H181" s="34"/>
+      <c r="I181" s="35"/>
+      <c r="J181" s="34"/>
+      <c r="K181" s="35"/>
+      <c r="L181" s="34"/>
+      <c r="M181" s="35"/>
+      <c r="N181" s="34"/>
+      <c r="O181" s="35"/>
+      <c r="P181" s="34"/>
+      <c r="Q181" s="35"/>
+      <c r="R181" s="34"/>
+      <c r="S181" s="35"/>
+      <c r="T181" s="34"/>
+      <c r="U181" s="35"/>
+      <c r="V181" s="34"/>
+      <c r="W181" s="35"/>
+      <c r="X181" s="34"/>
+      <c r="Y181" s="35"/>
+      <c r="Z181" s="34"/>
+      <c r="AA181" s="35"/>
+      <c r="AB181" s="34"/>
+      <c r="AC181" s="35"/>
+      <c r="AD181" s="34"/>
+      <c r="AE181" s="35"/>
+      <c r="AF181" s="34"/>
+      <c r="AG181" s="35"/>
+      <c r="AH181" s="34"/>
+      <c r="AI181" s="35"/>
+      <c r="AJ181" s="34"/>
+      <c r="AK181" s="35"/>
+      <c r="AL181" s="34"/>
+      <c r="AM181" s="35"/>
+      <c r="AN181" s="34"/>
+      <c r="AO181" s="35"/>
+      <c r="AP181" s="34"/>
+      <c r="AQ181" s="34"/>
+      <c r="AR181" s="34"/>
+      <c r="AS181" s="34"/>
+      <c r="AT181" s="34"/>
+      <c r="AU181" s="35"/>
+      <c r="AV181" s="36"/>
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
@@ -22891,110 +22914,110 @@
       <c r="AX184" s="12"/>
     </row>
     <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="42" t="s">
+      <c r="A185" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B185" s="38"/>
-      <c r="C185" s="39"/>
-      <c r="D185" s="38"/>
-      <c r="E185" s="39"/>
-      <c r="F185" s="38"/>
-      <c r="G185" s="39"/>
-      <c r="H185" s="38"/>
-      <c r="I185" s="39"/>
-      <c r="J185" s="38"/>
-      <c r="K185" s="39"/>
-      <c r="L185" s="38"/>
-      <c r="M185" s="39"/>
-      <c r="N185" s="38"/>
-      <c r="O185" s="39"/>
-      <c r="P185" s="38"/>
-      <c r="Q185" s="39"/>
-      <c r="R185" s="38"/>
-      <c r="S185" s="39"/>
-      <c r="T185" s="38"/>
-      <c r="U185" s="39"/>
-      <c r="V185" s="38"/>
-      <c r="W185" s="39"/>
-      <c r="X185" s="38"/>
-      <c r="Y185" s="39"/>
-      <c r="Z185" s="38"/>
-      <c r="AA185" s="39"/>
-      <c r="AB185" s="38"/>
-      <c r="AC185" s="39"/>
-      <c r="AD185" s="38"/>
-      <c r="AE185" s="39"/>
-      <c r="AF185" s="38"/>
-      <c r="AG185" s="39"/>
-      <c r="AH185" s="38"/>
-      <c r="AI185" s="39"/>
-      <c r="AJ185" s="38"/>
-      <c r="AK185" s="39"/>
-      <c r="AL185" s="38"/>
-      <c r="AM185" s="39"/>
-      <c r="AN185" s="38"/>
-      <c r="AO185" s="39"/>
-      <c r="AP185" s="38"/>
-      <c r="AQ185" s="38"/>
-      <c r="AR185" s="38"/>
-      <c r="AS185" s="38"/>
-      <c r="AT185" s="38"/>
-      <c r="AU185" s="39"/>
-      <c r="AV185" s="34"/>
+      <c r="B185" s="34"/>
+      <c r="C185" s="35"/>
+      <c r="D185" s="34"/>
+      <c r="E185" s="35"/>
+      <c r="F185" s="34"/>
+      <c r="G185" s="35"/>
+      <c r="H185" s="34"/>
+      <c r="I185" s="35"/>
+      <c r="J185" s="34"/>
+      <c r="K185" s="35"/>
+      <c r="L185" s="34"/>
+      <c r="M185" s="35"/>
+      <c r="N185" s="34"/>
+      <c r="O185" s="35"/>
+      <c r="P185" s="34"/>
+      <c r="Q185" s="35"/>
+      <c r="R185" s="34"/>
+      <c r="S185" s="35"/>
+      <c r="T185" s="34"/>
+      <c r="U185" s="35"/>
+      <c r="V185" s="34"/>
+      <c r="W185" s="35"/>
+      <c r="X185" s="34"/>
+      <c r="Y185" s="35"/>
+      <c r="Z185" s="34"/>
+      <c r="AA185" s="35"/>
+      <c r="AB185" s="34"/>
+      <c r="AC185" s="35"/>
+      <c r="AD185" s="34"/>
+      <c r="AE185" s="35"/>
+      <c r="AF185" s="34"/>
+      <c r="AG185" s="35"/>
+      <c r="AH185" s="34"/>
+      <c r="AI185" s="35"/>
+      <c r="AJ185" s="34"/>
+      <c r="AK185" s="35"/>
+      <c r="AL185" s="34"/>
+      <c r="AM185" s="35"/>
+      <c r="AN185" s="34"/>
+      <c r="AO185" s="35"/>
+      <c r="AP185" s="34"/>
+      <c r="AQ185" s="34"/>
+      <c r="AR185" s="34"/>
+      <c r="AS185" s="34"/>
+      <c r="AT185" s="34"/>
+      <c r="AU185" s="35"/>
+      <c r="AV185" s="36"/>
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
     <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="37" t="s">
+      <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="B186" s="38"/>
-      <c r="C186" s="39"/>
-      <c r="D186" s="38"/>
-      <c r="E186" s="39"/>
-      <c r="F186" s="38"/>
-      <c r="G186" s="39"/>
-      <c r="H186" s="38"/>
-      <c r="I186" s="39"/>
-      <c r="J186" s="38"/>
-      <c r="K186" s="39"/>
-      <c r="L186" s="38"/>
-      <c r="M186" s="39"/>
-      <c r="N186" s="38"/>
-      <c r="O186" s="39"/>
-      <c r="P186" s="38"/>
-      <c r="Q186" s="39"/>
-      <c r="R186" s="38"/>
-      <c r="S186" s="39"/>
-      <c r="T186" s="38"/>
-      <c r="U186" s="39"/>
-      <c r="V186" s="38"/>
-      <c r="W186" s="39"/>
-      <c r="X186" s="38"/>
-      <c r="Y186" s="39"/>
-      <c r="Z186" s="38"/>
-      <c r="AA186" s="39"/>
-      <c r="AB186" s="38"/>
-      <c r="AC186" s="39"/>
-      <c r="AD186" s="38"/>
-      <c r="AE186" s="39"/>
-      <c r="AF186" s="38"/>
-      <c r="AG186" s="39"/>
-      <c r="AH186" s="38"/>
-      <c r="AI186" s="39"/>
-      <c r="AJ186" s="38"/>
-      <c r="AK186" s="39"/>
-      <c r="AL186" s="38"/>
-      <c r="AM186" s="39"/>
-      <c r="AN186" s="38"/>
-      <c r="AO186" s="39"/>
-      <c r="AP186" s="38"/>
-      <c r="AQ186" s="38"/>
-      <c r="AR186" s="38"/>
-      <c r="AS186" s="38"/>
-      <c r="AT186" s="38"/>
-      <c r="AU186" s="39"/>
-      <c r="AV186" s="34"/>
+      <c r="B186" s="34"/>
+      <c r="C186" s="35"/>
+      <c r="D186" s="34"/>
+      <c r="E186" s="35"/>
+      <c r="F186" s="34"/>
+      <c r="G186" s="35"/>
+      <c r="H186" s="34"/>
+      <c r="I186" s="35"/>
+      <c r="J186" s="34"/>
+      <c r="K186" s="35"/>
+      <c r="L186" s="34"/>
+      <c r="M186" s="35"/>
+      <c r="N186" s="34"/>
+      <c r="O186" s="35"/>
+      <c r="P186" s="34"/>
+      <c r="Q186" s="35"/>
+      <c r="R186" s="34"/>
+      <c r="S186" s="35"/>
+      <c r="T186" s="34"/>
+      <c r="U186" s="35"/>
+      <c r="V186" s="34"/>
+      <c r="W186" s="35"/>
+      <c r="X186" s="34"/>
+      <c r="Y186" s="35"/>
+      <c r="Z186" s="34"/>
+      <c r="AA186" s="35"/>
+      <c r="AB186" s="34"/>
+      <c r="AC186" s="35"/>
+      <c r="AD186" s="34"/>
+      <c r="AE186" s="35"/>
+      <c r="AF186" s="34"/>
+      <c r="AG186" s="35"/>
+      <c r="AH186" s="34"/>
+      <c r="AI186" s="35"/>
+      <c r="AJ186" s="34"/>
+      <c r="AK186" s="35"/>
+      <c r="AL186" s="34"/>
+      <c r="AM186" s="35"/>
+      <c r="AN186" s="34"/>
+      <c r="AO186" s="35"/>
+      <c r="AP186" s="34"/>
+      <c r="AQ186" s="34"/>
+      <c r="AR186" s="34"/>
+      <c r="AS186" s="34"/>
+      <c r="AT186" s="34"/>
+      <c r="AU186" s="35"/>
+      <c r="AV186" s="36"/>
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
@@ -23245,110 +23268,110 @@
       <c r="AX189" s="12"/>
     </row>
     <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="42" t="s">
+      <c r="A190" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="B190" s="38"/>
-      <c r="C190" s="39"/>
-      <c r="D190" s="38"/>
-      <c r="E190" s="39"/>
-      <c r="F190" s="38"/>
-      <c r="G190" s="39"/>
-      <c r="H190" s="38"/>
-      <c r="I190" s="39"/>
-      <c r="J190" s="38"/>
-      <c r="K190" s="39"/>
-      <c r="L190" s="38"/>
-      <c r="M190" s="39"/>
-      <c r="N190" s="38"/>
-      <c r="O190" s="39"/>
-      <c r="P190" s="38"/>
-      <c r="Q190" s="39"/>
-      <c r="R190" s="38"/>
-      <c r="S190" s="39"/>
-      <c r="T190" s="38"/>
-      <c r="U190" s="39"/>
-      <c r="V190" s="38"/>
-      <c r="W190" s="39"/>
-      <c r="X190" s="38"/>
-      <c r="Y190" s="39"/>
-      <c r="Z190" s="38"/>
-      <c r="AA190" s="39"/>
-      <c r="AB190" s="38"/>
-      <c r="AC190" s="39"/>
-      <c r="AD190" s="38"/>
-      <c r="AE190" s="39"/>
-      <c r="AF190" s="38"/>
-      <c r="AG190" s="39"/>
-      <c r="AH190" s="38"/>
-      <c r="AI190" s="39"/>
-      <c r="AJ190" s="38"/>
-      <c r="AK190" s="39"/>
-      <c r="AL190" s="38"/>
-      <c r="AM190" s="39"/>
-      <c r="AN190" s="38"/>
-      <c r="AO190" s="39"/>
-      <c r="AP190" s="38"/>
-      <c r="AQ190" s="38"/>
-      <c r="AR190" s="38"/>
-      <c r="AS190" s="38"/>
-      <c r="AT190" s="38"/>
-      <c r="AU190" s="39"/>
-      <c r="AV190" s="34"/>
+      <c r="B190" s="34"/>
+      <c r="C190" s="35"/>
+      <c r="D190" s="34"/>
+      <c r="E190" s="35"/>
+      <c r="F190" s="34"/>
+      <c r="G190" s="35"/>
+      <c r="H190" s="34"/>
+      <c r="I190" s="35"/>
+      <c r="J190" s="34"/>
+      <c r="K190" s="35"/>
+      <c r="L190" s="34"/>
+      <c r="M190" s="35"/>
+      <c r="N190" s="34"/>
+      <c r="O190" s="35"/>
+      <c r="P190" s="34"/>
+      <c r="Q190" s="35"/>
+      <c r="R190" s="34"/>
+      <c r="S190" s="35"/>
+      <c r="T190" s="34"/>
+      <c r="U190" s="35"/>
+      <c r="V190" s="34"/>
+      <c r="W190" s="35"/>
+      <c r="X190" s="34"/>
+      <c r="Y190" s="35"/>
+      <c r="Z190" s="34"/>
+      <c r="AA190" s="35"/>
+      <c r="AB190" s="34"/>
+      <c r="AC190" s="35"/>
+      <c r="AD190" s="34"/>
+      <c r="AE190" s="35"/>
+      <c r="AF190" s="34"/>
+      <c r="AG190" s="35"/>
+      <c r="AH190" s="34"/>
+      <c r="AI190" s="35"/>
+      <c r="AJ190" s="34"/>
+      <c r="AK190" s="35"/>
+      <c r="AL190" s="34"/>
+      <c r="AM190" s="35"/>
+      <c r="AN190" s="34"/>
+      <c r="AO190" s="35"/>
+      <c r="AP190" s="34"/>
+      <c r="AQ190" s="34"/>
+      <c r="AR190" s="34"/>
+      <c r="AS190" s="34"/>
+      <c r="AT190" s="34"/>
+      <c r="AU190" s="35"/>
+      <c r="AV190" s="36"/>
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
     <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="37" t="s">
+      <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="B191" s="38"/>
-      <c r="C191" s="39"/>
-      <c r="D191" s="38"/>
-      <c r="E191" s="39"/>
-      <c r="F191" s="38"/>
-      <c r="G191" s="39"/>
-      <c r="H191" s="38"/>
-      <c r="I191" s="39"/>
-      <c r="J191" s="38"/>
-      <c r="K191" s="39"/>
-      <c r="L191" s="38"/>
-      <c r="M191" s="39"/>
-      <c r="N191" s="38"/>
-      <c r="O191" s="39"/>
-      <c r="P191" s="38"/>
-      <c r="Q191" s="39"/>
-      <c r="R191" s="38"/>
-      <c r="S191" s="39"/>
-      <c r="T191" s="38"/>
-      <c r="U191" s="39"/>
-      <c r="V191" s="38"/>
-      <c r="W191" s="39"/>
-      <c r="X191" s="38"/>
-      <c r="Y191" s="39"/>
-      <c r="Z191" s="38"/>
-      <c r="AA191" s="39"/>
-      <c r="AB191" s="38"/>
-      <c r="AC191" s="39"/>
-      <c r="AD191" s="38"/>
-      <c r="AE191" s="39"/>
-      <c r="AF191" s="38"/>
-      <c r="AG191" s="39"/>
-      <c r="AH191" s="38"/>
-      <c r="AI191" s="39"/>
-      <c r="AJ191" s="38"/>
-      <c r="AK191" s="39"/>
-      <c r="AL191" s="38"/>
-      <c r="AM191" s="39"/>
-      <c r="AN191" s="38"/>
-      <c r="AO191" s="39"/>
-      <c r="AP191" s="38"/>
-      <c r="AQ191" s="38"/>
-      <c r="AR191" s="38"/>
-      <c r="AS191" s="38"/>
-      <c r="AT191" s="38"/>
-      <c r="AU191" s="39"/>
-      <c r="AV191" s="34"/>
+      <c r="B191" s="34"/>
+      <c r="C191" s="35"/>
+      <c r="D191" s="34"/>
+      <c r="E191" s="35"/>
+      <c r="F191" s="34"/>
+      <c r="G191" s="35"/>
+      <c r="H191" s="34"/>
+      <c r="I191" s="35"/>
+      <c r="J191" s="34"/>
+      <c r="K191" s="35"/>
+      <c r="L191" s="34"/>
+      <c r="M191" s="35"/>
+      <c r="N191" s="34"/>
+      <c r="O191" s="35"/>
+      <c r="P191" s="34"/>
+      <c r="Q191" s="35"/>
+      <c r="R191" s="34"/>
+      <c r="S191" s="35"/>
+      <c r="T191" s="34"/>
+      <c r="U191" s="35"/>
+      <c r="V191" s="34"/>
+      <c r="W191" s="35"/>
+      <c r="X191" s="34"/>
+      <c r="Y191" s="35"/>
+      <c r="Z191" s="34"/>
+      <c r="AA191" s="35"/>
+      <c r="AB191" s="34"/>
+      <c r="AC191" s="35"/>
+      <c r="AD191" s="34"/>
+      <c r="AE191" s="35"/>
+      <c r="AF191" s="34"/>
+      <c r="AG191" s="35"/>
+      <c r="AH191" s="34"/>
+      <c r="AI191" s="35"/>
+      <c r="AJ191" s="34"/>
+      <c r="AK191" s="35"/>
+      <c r="AL191" s="34"/>
+      <c r="AM191" s="35"/>
+      <c r="AN191" s="34"/>
+      <c r="AO191" s="35"/>
+      <c r="AP191" s="34"/>
+      <c r="AQ191" s="34"/>
+      <c r="AR191" s="34"/>
+      <c r="AS191" s="34"/>
+      <c r="AT191" s="34"/>
+      <c r="AU191" s="35"/>
+      <c r="AV191" s="36"/>
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
@@ -23600,6 +23623,8 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
     <mergeCell ref="A4:AV4"/>
     <mergeCell ref="AE1:AF1"/>
@@ -23613,6 +23638,10 @@
     <mergeCell ref="A3:AV3"/>
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="A191:AV191"/>
     <mergeCell ref="A145:AV145"/>
     <mergeCell ref="A163:AV163"/>
@@ -23627,21 +23656,29 @@
     <mergeCell ref="A131:AV131"/>
     <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="S1:T1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="A170:AV170"/>
     <mergeCell ref="A46:AV46"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="A33:AV33"/>
     <mergeCell ref="A15:AV15"/>
     <mergeCell ref="AS1:AT1"/>
     <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
     <mergeCell ref="A153:AV153"/>
     <mergeCell ref="A177:AV177"/>
@@ -23656,20 +23693,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23734,114 +23757,114 @@
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="33" t="str">
+      <c r="D1" s="45" t="str">
         <f>Wedstrijden_beheer!E1</f>
         <v>Roland</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="33" t="str">
+      <c r="E1" s="36"/>
+      <c r="F1" s="45" t="str">
         <f>Wedstrijden_beheer!G1</f>
         <v>Nikki</v>
       </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="33" t="str">
+      <c r="G1" s="36"/>
+      <c r="H1" s="45" t="str">
         <f>Wedstrijden_beheer!I1</f>
         <v>Abdussamed</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="33" t="str">
+      <c r="I1" s="36"/>
+      <c r="J1" s="45" t="str">
         <f>Wedstrijden_beheer!K1</f>
         <v>Karsten</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="33" t="str">
+      <c r="K1" s="36"/>
+      <c r="L1" s="45" t="str">
         <f>Wedstrijden_beheer!M1</f>
         <v>Bas</v>
       </c>
-      <c r="M1" s="34"/>
-      <c r="N1" s="33" t="str">
+      <c r="M1" s="36"/>
+      <c r="N1" s="45" t="str">
         <f>Wedstrijden_beheer!O1</f>
         <v>Maik</v>
       </c>
-      <c r="O1" s="34"/>
-      <c r="P1" s="33" t="str">
+      <c r="O1" s="36"/>
+      <c r="P1" s="45" t="str">
         <f>Wedstrijden_beheer!Q1</f>
         <v>Simone</v>
       </c>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="33" t="str">
+      <c r="Q1" s="36"/>
+      <c r="R1" s="45" t="str">
         <f>Wedstrijden_beheer!S1</f>
         <v>Marc</v>
       </c>
-      <c r="S1" s="34"/>
-      <c r="T1" s="33" t="str">
+      <c r="S1" s="36"/>
+      <c r="T1" s="45" t="str">
         <f>Wedstrijden_beheer!U1</f>
         <v>Tom</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="33" t="str">
+      <c r="U1" s="36"/>
+      <c r="V1" s="45" t="str">
         <f>Wedstrijden_beheer!W1</f>
         <v>Jos</v>
       </c>
-      <c r="W1" s="34"/>
-      <c r="X1" s="33" t="str">
+      <c r="W1" s="36"/>
+      <c r="X1" s="45" t="str">
         <f>Wedstrijden_beheer!Y1</f>
         <v>Lesley</v>
       </c>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="33" t="str">
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="45" t="str">
         <f>Wedstrijden_beheer!AA1</f>
         <v>Ivo</v>
       </c>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="33" t="str">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="45" t="str">
         <f>Wedstrijden_beheer!AC1</f>
         <v>Ron</v>
       </c>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="33" t="str">
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="45" t="str">
         <f>Wedstrijden_beheer!AE1</f>
         <v>Jeroen</v>
       </c>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="33" t="str">
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="45" t="str">
         <f>Wedstrijden_beheer!AG1</f>
         <v>Erwin</v>
       </c>
-      <c r="AG1" s="34"/>
-      <c r="AH1" s="33" t="str">
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="45" t="str">
         <f>Wedstrijden_beheer!AI1</f>
         <v>Tim</v>
       </c>
-      <c r="AI1" s="34"/>
-      <c r="AJ1" s="33" t="s">
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="AK1" s="34"/>
-      <c r="AL1" s="33" t="s">
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="34"/>
-      <c r="AN1" s="33" t="str">
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="45" t="str">
         <f>Wedstrijden_beheer!AO1</f>
         <v>Patrick</v>
       </c>
-      <c r="AO1" s="34"/>
-      <c r="AP1" s="33" t="str">
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="45" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
         <v>Jeno</v>
       </c>
-      <c r="AQ1" s="34"/>
-      <c r="AR1" s="35" t="str">
+      <c r="AQ1" s="36"/>
+      <c r="AR1" s="37" t="str">
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="36"/>
-      <c r="AT1" s="35" t="str">
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="36"/>
+      <c r="AU1" s="39"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
@@ -26455,294 +26478,294 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
-        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C3" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>17</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>62</v>
       </c>
       <c r="D3" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
-        <v>17</v>
+        <f>C3+D3</f>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>14</v>
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>52</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f>C4+D4</f>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>14</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>51</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f>C5+D5</f>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>14</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>51</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f>C6+D6</f>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>12</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>50</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>C7+D7</f>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>12</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>49</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>C8+D8</f>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>12</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>47</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>C9+D9</f>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>12</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>47</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>C10+D10</f>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>12</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>46</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>C11+D11</f>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>12</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>46</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!K17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>C12+D12</f>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>12</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>44</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>C13+D13</f>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>9</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>44</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>C14+D14</f>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>9</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>43</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>C15+D15</f>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="str">
         <f>Wedstrijden_beheer!AO1</f>
@@ -26750,86 +26773,86 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>C16+D16</f>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>9</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>41</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>C17+D17</f>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>9</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>40</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>C18+D18</f>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>9</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>40</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>C19+D19</f>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
@@ -26838,103 +26861,103 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f>C20+D20</f>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>7</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>38</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f>C21+D21</f>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>7</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>38</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f>C22+D22</f>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
         <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>2</v>
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
+        <v>36</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>C23+D23</f>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="11">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C24" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>2</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>35</v>
       </c>
       <c r="D24" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>C24+D24</f>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -27546,16 +27569,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1472" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC804CD-FC7E-426E-981B-232080740777}"/>
+  <xr:revisionPtr revIDLastSave="1479" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583AFAB7-813D-4950-8B47-7D6B82AD6A49}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-4428" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1354,10 +1354,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1676,60 +1676,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" customWidth="1"/>
-    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.54296875" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.54296875" customWidth="1"/>
-    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.54296875" customWidth="1"/>
-    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.54296875" customWidth="1"/>
-    <col min="21" max="21" width="12.54296875" customWidth="1"/>
-    <col min="22" max="22" width="8.54296875" customWidth="1"/>
-    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.54296875" customWidth="1"/>
-    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.54296875" customWidth="1"/>
-    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.54296875" customWidth="1"/>
-    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.54296875" customWidth="1"/>
-    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.54296875" customWidth="1"/>
-    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.54296875" customWidth="1"/>
-    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.54296875" customWidth="1"/>
-    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.54296875" customWidth="1"/>
-    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.54296875" customWidth="1"/>
-    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.54296875" customWidth="1"/>
-    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.54296875" customWidth="1"/>
-    <col min="45" max="45" width="15.7265625" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.54296875" customWidth="1"/>
-    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.5703125" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.5703125" customWidth="1"/>
+    <col min="25" max="25" width="12.5703125" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.5703125" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.5703125" customWidth="1"/>
+    <col min="29" max="29" width="12.5703125" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.5703125" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.5703125" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.5703125" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.5703125" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.5703125" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.5703125" customWidth="1"/>
+    <col min="41" max="41" width="15.5703125" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.5703125" customWidth="1"/>
+    <col min="43" max="43" width="15.5703125" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.5703125" customWidth="1"/>
+    <col min="45" max="45" width="15.7109375" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.5703125" customWidth="1"/>
+    <col min="47" max="47" width="15.5703125" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.5703125" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -1837,11 +1837,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="42"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="41"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2323,7 +2323,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2787,7 +2787,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3251,7 +3251,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4243,7 +4243,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
@@ -4297,7 +4297,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4649,355 +4649,359 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D25" s="1" t="s">
         <v>81</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="11" t="str">
+      <c r="F25" s="11">
         <f>IF(OR($C25="",E25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E25,FIND("-",E25)-1),"")=AW25,IFERROR(--MID(E25,FIND("-",E25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(E25,FIND("-",E25)-1),""))-(IFERROR(--MID(E25,FIND("-",E25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(E25,FIND("-",E25)-1),""))-(IFERROR(--MID(E25,FIND("-",E25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(E25,FIND("-",E25)-1),""))=(AW25))+2*((IFERROR(--MID(E25,FIND("-",E25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H25" s="11" t="str">
+      <c r="H25" s="11">
         <f>IF(OR($C25="",G25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G25,FIND("-",G25)-1),"")=AW25,IFERROR(--MID(G25,FIND("-",G25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(G25,FIND("-",G25)-1),""))-(IFERROR(--MID(G25,FIND("-",G25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(G25,FIND("-",G25)-1),""))-(IFERROR(--MID(G25,FIND("-",G25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(G25,FIND("-",G25)-1),""))=(AW25))+2*((IFERROR(--MID(G25,FIND("-",G25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="11" t="str">
+      <c r="J25" s="11">
         <f>IF(OR($C25="",I25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I25,FIND("-",I25)-1),"")=AW25,IFERROR(--MID(I25,FIND("-",I25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(I25,FIND("-",I25)-1),""))-(IFERROR(--MID(I25,FIND("-",I25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(I25,FIND("-",I25)-1),""))-(IFERROR(--MID(I25,FIND("-",I25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(I25,FIND("-",I25)-1),""))=(AW25))+2*((IFERROR(--MID(I25,FIND("-",I25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L25" s="11" t="str">
+      <c r="L25" s="11">
         <f>IF(OR($C25="",K25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K25,FIND("-",K25)-1),"")=AW25,IFERROR(--MID(K25,FIND("-",K25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(K25,FIND("-",K25)-1),""))-(IFERROR(--MID(K25,FIND("-",K25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(K25,FIND("-",K25)-1),""))-(IFERROR(--MID(K25,FIND("-",K25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(K25,FIND("-",K25)-1),""))=(AW25))+2*((IFERROR(--MID(K25,FIND("-",K25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="N25" s="11" t="str">
+      <c r="N25" s="11">
         <f>IF(OR($C25="",M25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M25,FIND("-",M25)-1),"")=AW25,IFERROR(--MID(M25,FIND("-",M25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(M25,FIND("-",M25)-1),""))-(IFERROR(--MID(M25,FIND("-",M25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(M25,FIND("-",M25)-1),""))-(IFERROR(--MID(M25,FIND("-",M25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(M25,FIND("-",M25)-1),""))=(AW25))+2*((IFERROR(--MID(M25,FIND("-",M25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="P25" s="11" t="str">
+      <c r="P25" s="11">
         <f>IF(OR($C25="",O25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O25,FIND("-",O25)-1),"")=AW25,IFERROR(--MID(O25,FIND("-",O25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(O25,FIND("-",O25)-1),""))-(IFERROR(--MID(O25,FIND("-",O25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(O25,FIND("-",O25)-1),""))-(IFERROR(--MID(O25,FIND("-",O25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(O25,FIND("-",O25)-1),""))=(AW25))+2*((IFERROR(--MID(O25,FIND("-",O25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R25" s="11" t="str">
+      <c r="R25" s="11">
         <f>IF(OR($C25="",Q25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q25,FIND("-",Q25)-1),"")=AW25,IFERROR(--MID(Q25,FIND("-",Q25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(Q25,FIND("-",Q25)-1),""))-(IFERROR(--MID(Q25,FIND("-",Q25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(Q25,FIND("-",Q25)-1),""))-(IFERROR(--MID(Q25,FIND("-",Q25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(Q25,FIND("-",Q25)-1),""))=(AW25))+2*((IFERROR(--MID(Q25,FIND("-",Q25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T25" s="11" t="str">
+      <c r="T25" s="11">
         <f>IF(OR($C25="",S25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S25,FIND("-",S25)-1),"")=AW25,IFERROR(--MID(S25,FIND("-",S25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(S25,FIND("-",S25)-1),""))-(IFERROR(--MID(S25,FIND("-",S25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(S25,FIND("-",S25)-1),""))-(IFERROR(--MID(S25,FIND("-",S25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(S25,FIND("-",S25)-1),""))=(AW25))+2*((IFERROR(--MID(S25,FIND("-",S25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V25" s="11" t="str">
+      <c r="V25" s="11">
         <f>IF(OR($C25="",U25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U25,FIND("-",U25)-1),"")=AW25,IFERROR(--MID(U25,FIND("-",U25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(U25,FIND("-",U25)-1),""))-(IFERROR(--MID(U25,FIND("-",U25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(U25,FIND("-",U25)-1),""))-(IFERROR(--MID(U25,FIND("-",U25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(U25,FIND("-",U25)-1),""))=(AW25))+2*((IFERROR(--MID(U25,FIND("-",U25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="X25" s="11" t="str">
+      <c r="X25" s="11">
         <f>IF(OR($C25="",W25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W25,FIND("-",W25)-1),"")=AW25,IFERROR(--MID(W25,FIND("-",W25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(W25,FIND("-",W25)-1),""))-(IFERROR(--MID(W25,FIND("-",W25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(W25,FIND("-",W25)-1),""))-(IFERROR(--MID(W25,FIND("-",W25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(W25,FIND("-",W25)-1),""))=(AW25))+2*((IFERROR(--MID(W25,FIND("-",W25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="Z25" s="11" t="str">
+      <c r="Z25" s="11">
         <f>IF(OR($C25="",Y25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y25,FIND("-",Y25)-1),"")=AW25,IFERROR(--MID(Y25,FIND("-",Y25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(Y25,FIND("-",Y25)-1),""))-(IFERROR(--MID(Y25,FIND("-",Y25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(Y25,FIND("-",Y25)-1),""))-(IFERROR(--MID(Y25,FIND("-",Y25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(Y25,FIND("-",Y25)-1),""))=(AW25))+2*((IFERROR(--MID(Y25,FIND("-",Y25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AB25" s="11" t="str">
+      <c r="AB25" s="11">
         <f>IF(OR($C25="",AA25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA25,FIND("-",AA25)-1),"")=AW25,IFERROR(--MID(AA25,FIND("-",AA25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AA25,FIND("-",AA25)-1),""))-(IFERROR(--MID(AA25,FIND("-",AA25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AA25,FIND("-",AA25)-1),""))-(IFERROR(--MID(AA25,FIND("-",AA25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AA25,FIND("-",AA25)-1),""))=(AW25))+2*((IFERROR(--MID(AA25,FIND("-",AA25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AD25" s="11" t="str">
+      <c r="AD25" s="11">
         <f>IF(OR($C25="",AC25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC25,FIND("-",AC25)-1),"")=AW25,IFERROR(--MID(AC25,FIND("-",AC25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AC25,FIND("-",AC25)-1),""))-(IFERROR(--MID(AC25,FIND("-",AC25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AC25,FIND("-",AC25)-1),""))-(IFERROR(--MID(AC25,FIND("-",AC25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AC25,FIND("-",AC25)-1),""))=(AW25))+2*((IFERROR(--MID(AC25,FIND("-",AC25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF25" s="11" t="str">
+      <c r="AF25" s="11">
         <f>IF(OR($C25="",AE25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE25,FIND("-",AE25)-1),"")=AW25,IFERROR(--MID(AE25,FIND("-",AE25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AE25,FIND("-",AE25)-1),""))-(IFERROR(--MID(AE25,FIND("-",AE25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AE25,FIND("-",AE25)-1),""))-(IFERROR(--MID(AE25,FIND("-",AE25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AE25,FIND("-",AE25)-1),""))=(AW25))+2*((IFERROR(--MID(AE25,FIND("-",AE25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH25" s="11" t="str">
+      <c r="AH25" s="11">
         <f>IF(OR($C25="",AG25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG25,FIND("-",AG25)-1),"")=AW25,IFERROR(--MID(AG25,FIND("-",AG25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AG25,FIND("-",AG25)-1),""))-(IFERROR(--MID(AG25,FIND("-",AG25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AG25,FIND("-",AG25)-1),""))-(IFERROR(--MID(AG25,FIND("-",AG25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AG25,FIND("-",AG25)-1),""))=(AW25))+2*((IFERROR(--MID(AG25,FIND("-",AG25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AJ25" s="11" t="str">
+      <c r="AJ25" s="11">
         <f>IF(OR($C25="",AI25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI25,FIND("-",AI25)-1),"")=AW25,IFERROR(--MID(AI25,FIND("-",AI25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AI25,FIND("-",AI25)-1),""))-(IFERROR(--MID(AI25,FIND("-",AI25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AI25,FIND("-",AI25)-1),""))-(IFERROR(--MID(AI25,FIND("-",AI25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AI25,FIND("-",AI25)-1),""))=(AW25))+2*((IFERROR(--MID(AI25,FIND("-",AI25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AL25" s="11" t="str">
+      <c r="AL25" s="11">
         <f>IF(OR($C25="",AK25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK25,FIND("-",AK25)-1),"")=AW25,IFERROR(--MID(AK25,FIND("-",AK25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AK25,FIND("-",AK25)-1),""))-(IFERROR(--MID(AK25,FIND("-",AK25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AK25,FIND("-",AK25)-1),""))-(IFERROR(--MID(AK25,FIND("-",AK25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AK25,FIND("-",AK25)-1),""))=(AW25))+2*((IFERROR(--MID(AK25,FIND("-",AK25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AN25" s="11" t="str">
+      <c r="AN25" s="11">
         <f>IF(OR($C25="",AM25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM25,FIND("-",AM25)-1),"")=AW25,IFERROR(--MID(AM25,FIND("-",AM25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AM25,FIND("-",AM25)-1),""))-(IFERROR(--MID(AM25,FIND("-",AM25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AM25,FIND("-",AM25)-1),""))-(IFERROR(--MID(AM25,FIND("-",AM25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AM25,FIND("-",AM25)-1),""))=(AW25))+2*((IFERROR(--MID(AM25,FIND("-",AM25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AP25" s="11" t="str">
+      <c r="AP25" s="11">
         <f>IF(OR($C25="",AO25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO25,FIND("-",AO25)-1),"")=AW25,IFERROR(--MID(AO25,FIND("-",AO25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AO25,FIND("-",AO25)-1),""))-(IFERROR(--MID(AO25,FIND("-",AO25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AO25,FIND("-",AO25)-1),""))-(IFERROR(--MID(AO25,FIND("-",AO25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AO25,FIND("-",AO25)-1),""))=(AW25))+2*((IFERROR(--MID(AO25,FIND("-",AO25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AR25" s="11" t="str">
+      <c r="AR25" s="11">
         <f>IF(OR($C25="",AQ25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ25,FIND("-",AQ25)-1),"")=AW25,IFERROR(--MID(AQ25,FIND("-",AQ25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AQ25,FIND("-",AQ25)-1),""))-(IFERROR(--MID(AQ25,FIND("-",AQ25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AQ25,FIND("-",AQ25)-1),""))-(IFERROR(--MID(AQ25,FIND("-",AQ25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AQ25,FIND("-",AQ25)-1),""))=(AW25))+2*((IFERROR(--MID(AQ25,FIND("-",AQ25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AT25" s="11" t="str">
+      <c r="AT25" s="11">
         <f>IF(OR($C25="",AS25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS25,FIND("-",AS25)-1),"")=AW25,IFERROR(--MID(AS25,FIND("-",AS25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AS25,FIND("-",AS25)-1),""))-(IFERROR(--MID(AS25,FIND("-",AS25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AS25,FIND("-",AS25)-1),""))-(IFERROR(--MID(AS25,FIND("-",AS25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AS25,FIND("-",AS25)-1),""))=(AW25))+2*((IFERROR(--MID(AS25,FIND("-",AS25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU25" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV25" s="11" t="str">
+      <c r="AV25" s="11">
         <f>IF(OR($C25="",AU25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU25,FIND("-",AU25)-1),"")=AW25,IFERROR(--MID(AU25,FIND("-",AU25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AU25,FIND("-",AU25)-1),""))-(IFERROR(--MID(AU25,FIND("-",AU25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AU25,FIND("-",AU25)-1),""))-(IFERROR(--MID(AU25,FIND("-",AU25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AU25,FIND("-",AU25)-1),""))=(AW25))+2*((IFERROR(--MID(AU25,FIND("-",AU25)+1,99),""))=(AX25))),""))</f>
-        <v/>
-      </c>
-      <c r="AW25" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW25" s="11">
         <f>IF($C25="","",IFERROR(--LEFT($C25,FIND("-",$C25)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX25" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX25" s="11">
         <f>IF($C25="","",IFERROR(--MID($C25,FIND("-",$C25)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D26" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="11" t="str">
+      <c r="F26" s="11">
         <f>IF(OR($C26="",E26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E26,FIND("-",E26)-1),"")=AW26,IFERROR(--MID(E26,FIND("-",E26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(E26,FIND("-",E26)-1),""))-(IFERROR(--MID(E26,FIND("-",E26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(E26,FIND("-",E26)-1),""))-(IFERROR(--MID(E26,FIND("-",E26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(E26,FIND("-",E26)-1),""))=(AW26))+2*((IFERROR(--MID(E26,FIND("-",E26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="11" t="str">
+      <c r="H26" s="11">
         <f>IF(OR($C26="",G26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G26,FIND("-",G26)-1),"")=AW26,IFERROR(--MID(G26,FIND("-",G26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(G26,FIND("-",G26)-1),""))-(IFERROR(--MID(G26,FIND("-",G26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(G26,FIND("-",G26)-1),""))-(IFERROR(--MID(G26,FIND("-",G26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(G26,FIND("-",G26)-1),""))=(AW26))+2*((IFERROR(--MID(G26,FIND("-",G26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="11" t="str">
+      <c r="J26" s="11">
         <f>IF(OR($C26="",I26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I26,FIND("-",I26)-1),"")=AW26,IFERROR(--MID(I26,FIND("-",I26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(I26,FIND("-",I26)-1),""))-(IFERROR(--MID(I26,FIND("-",I26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(I26,FIND("-",I26)-1),""))-(IFERROR(--MID(I26,FIND("-",I26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(I26,FIND("-",I26)-1),""))=(AW26))+2*((IFERROR(--MID(I26,FIND("-",I26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K26" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L26" s="11" t="str">
+      <c r="L26" s="11">
         <f>IF(OR($C26="",K26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K26,FIND("-",K26)-1),"")=AW26,IFERROR(--MID(K26,FIND("-",K26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(K26,FIND("-",K26)-1),""))-(IFERROR(--MID(K26,FIND("-",K26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(K26,FIND("-",K26)-1),""))-(IFERROR(--MID(K26,FIND("-",K26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(K26,FIND("-",K26)-1),""))=(AW26))+2*((IFERROR(--MID(K26,FIND("-",K26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M26" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N26" s="11" t="str">
+      <c r="N26" s="11">
         <f>IF(OR($C26="",M26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M26,FIND("-",M26)-1),"")=AW26,IFERROR(--MID(M26,FIND("-",M26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(M26,FIND("-",M26)-1),""))-(IFERROR(--MID(M26,FIND("-",M26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(M26,FIND("-",M26)-1),""))-(IFERROR(--MID(M26,FIND("-",M26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(M26,FIND("-",M26)-1),""))=(AW26))+2*((IFERROR(--MID(M26,FIND("-",M26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P26" s="11" t="str">
+      <c r="P26" s="11">
         <f>IF(OR($C26="",O26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O26,FIND("-",O26)-1),"")=AW26,IFERROR(--MID(O26,FIND("-",O26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(O26,FIND("-",O26)-1),""))-(IFERROR(--MID(O26,FIND("-",O26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(O26,FIND("-",O26)-1),""))-(IFERROR(--MID(O26,FIND("-",O26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(O26,FIND("-",O26)-1),""))=(AW26))+2*((IFERROR(--MID(O26,FIND("-",O26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R26" s="11" t="str">
+      <c r="R26" s="11">
         <f>IF(OR($C26="",Q26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q26,FIND("-",Q26)-1),"")=AW26,IFERROR(--MID(Q26,FIND("-",Q26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(Q26,FIND("-",Q26)-1),""))-(IFERROR(--MID(Q26,FIND("-",Q26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(Q26,FIND("-",Q26)-1),""))-(IFERROR(--MID(Q26,FIND("-",Q26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(Q26,FIND("-",Q26)-1),""))=(AW26))+2*((IFERROR(--MID(Q26,FIND("-",Q26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T26" s="11" t="str">
+      <c r="T26" s="11">
         <f>IF(OR($C26="",S26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S26,FIND("-",S26)-1),"")=AW26,IFERROR(--MID(S26,FIND("-",S26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(S26,FIND("-",S26)-1),""))-(IFERROR(--MID(S26,FIND("-",S26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(S26,FIND("-",S26)-1),""))-(IFERROR(--MID(S26,FIND("-",S26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(S26,FIND("-",S26)-1),""))=(AW26))+2*((IFERROR(--MID(S26,FIND("-",S26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V26" s="11" t="str">
+      <c r="V26" s="11">
         <f>IF(OR($C26="",U26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U26,FIND("-",U26)-1),"")=AW26,IFERROR(--MID(U26,FIND("-",U26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(U26,FIND("-",U26)-1),""))-(IFERROR(--MID(U26,FIND("-",U26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(U26,FIND("-",U26)-1),""))-(IFERROR(--MID(U26,FIND("-",U26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(U26,FIND("-",U26)-1),""))=(AW26))+2*((IFERROR(--MID(U26,FIND("-",U26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X26" s="11" t="str">
+      <c r="X26" s="11">
         <f>IF(OR($C26="",W26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W26,FIND("-",W26)-1),"")=AW26,IFERROR(--MID(W26,FIND("-",W26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(W26,FIND("-",W26)-1),""))-(IFERROR(--MID(W26,FIND("-",W26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(W26,FIND("-",W26)-1),""))-(IFERROR(--MID(W26,FIND("-",W26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(W26,FIND("-",W26)-1),""))=(AW26))+2*((IFERROR(--MID(W26,FIND("-",W26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z26" s="11" t="str">
+      <c r="Z26" s="11">
         <f>IF(OR($C26="",Y26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y26,FIND("-",Y26)-1),"")=AW26,IFERROR(--MID(Y26,FIND("-",Y26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(Y26,FIND("-",Y26)-1),""))-(IFERROR(--MID(Y26,FIND("-",Y26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(Y26,FIND("-",Y26)-1),""))-(IFERROR(--MID(Y26,FIND("-",Y26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(Y26,FIND("-",Y26)-1),""))=(AW26))+2*((IFERROR(--MID(Y26,FIND("-",Y26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA26" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB26" s="11" t="str">
+      <c r="AB26" s="11">
         <f>IF(OR($C26="",AA26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA26,FIND("-",AA26)-1),"")=AW26,IFERROR(--MID(AA26,FIND("-",AA26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AA26,FIND("-",AA26)-1),""))-(IFERROR(--MID(AA26,FIND("-",AA26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AA26,FIND("-",AA26)-1),""))-(IFERROR(--MID(AA26,FIND("-",AA26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AA26,FIND("-",AA26)-1),""))=(AW26))+2*((IFERROR(--MID(AA26,FIND("-",AA26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD26" s="11" t="str">
+      <c r="AD26" s="11">
         <f>IF(OR($C26="",AC26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC26,FIND("-",AC26)-1),"")=AW26,IFERROR(--MID(AC26,FIND("-",AC26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AC26,FIND("-",AC26)-1),""))-(IFERROR(--MID(AC26,FIND("-",AC26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AC26,FIND("-",AC26)-1),""))-(IFERROR(--MID(AC26,FIND("-",AC26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AC26,FIND("-",AC26)-1),""))=(AW26))+2*((IFERROR(--MID(AC26,FIND("-",AC26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF26" s="11" t="str">
+      <c r="AF26" s="11">
         <f>IF(OR($C26="",AE26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE26,FIND("-",AE26)-1),"")=AW26,IFERROR(--MID(AE26,FIND("-",AE26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AE26,FIND("-",AE26)-1),""))-(IFERROR(--MID(AE26,FIND("-",AE26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AE26,FIND("-",AE26)-1),""))-(IFERROR(--MID(AE26,FIND("-",AE26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AE26,FIND("-",AE26)-1),""))=(AW26))+2*((IFERROR(--MID(AE26,FIND("-",AE26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH26" s="11" t="str">
+      <c r="AH26" s="11">
         <f>IF(OR($C26="",AG26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG26,FIND("-",AG26)-1),"")=AW26,IFERROR(--MID(AG26,FIND("-",AG26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AG26,FIND("-",AG26)-1),""))-(IFERROR(--MID(AG26,FIND("-",AG26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AG26,FIND("-",AG26)-1),""))-(IFERROR(--MID(AG26,FIND("-",AG26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AG26,FIND("-",AG26)-1),""))=(AW26))+2*((IFERROR(--MID(AG26,FIND("-",AG26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI26" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ26" s="11" t="str">
+      <c r="AJ26" s="11">
         <f>IF(OR($C26="",AI26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI26,FIND("-",AI26)-1),"")=AW26,IFERROR(--MID(AI26,FIND("-",AI26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AI26,FIND("-",AI26)-1),""))-(IFERROR(--MID(AI26,FIND("-",AI26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AI26,FIND("-",AI26)-1),""))-(IFERROR(--MID(AI26,FIND("-",AI26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AI26,FIND("-",AI26)-1),""))=(AW26))+2*((IFERROR(--MID(AI26,FIND("-",AI26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL26" s="11" t="str">
+      <c r="AL26" s="11">
         <f>IF(OR($C26="",AK26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK26,FIND("-",AK26)-1),"")=AW26,IFERROR(--MID(AK26,FIND("-",AK26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AK26,FIND("-",AK26)-1),""))-(IFERROR(--MID(AK26,FIND("-",AK26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AK26,FIND("-",AK26)-1),""))-(IFERROR(--MID(AK26,FIND("-",AK26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AK26,FIND("-",AK26)-1),""))=(AW26))+2*((IFERROR(--MID(AK26,FIND("-",AK26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN26" s="11" t="str">
+      <c r="AN26" s="11">
         <f>IF(OR($C26="",AM26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM26,FIND("-",AM26)-1),"")=AW26,IFERROR(--MID(AM26,FIND("-",AM26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AM26,FIND("-",AM26)-1),""))-(IFERROR(--MID(AM26,FIND("-",AM26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AM26,FIND("-",AM26)-1),""))-(IFERROR(--MID(AM26,FIND("-",AM26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AM26,FIND("-",AM26)-1),""))=(AW26))+2*((IFERROR(--MID(AM26,FIND("-",AM26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO26" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP26" s="11" t="str">
+      <c r="AP26" s="11">
         <f>IF(OR($C26="",AO26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO26,FIND("-",AO26)-1),"")=AW26,IFERROR(--MID(AO26,FIND("-",AO26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AO26,FIND("-",AO26)-1),""))-(IFERROR(--MID(AO26,FIND("-",AO26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AO26,FIND("-",AO26)-1),""))-(IFERROR(--MID(AO26,FIND("-",AO26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AO26,FIND("-",AO26)-1),""))=(AW26))+2*((IFERROR(--MID(AO26,FIND("-",AO26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ26" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AR26" s="11" t="str">
+      <c r="AR26" s="11">
         <f>IF(OR($C26="",AQ26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ26,FIND("-",AQ26)-1),"")=AW26,IFERROR(--MID(AQ26,FIND("-",AQ26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AQ26,FIND("-",AQ26)-1),""))-(IFERROR(--MID(AQ26,FIND("-",AQ26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AQ26,FIND("-",AQ26)-1),""))-(IFERROR(--MID(AQ26,FIND("-",AQ26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AQ26,FIND("-",AQ26)-1),""))=(AW26))+2*((IFERROR(--MID(AQ26,FIND("-",AQ26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT26" s="11" t="str">
+      <c r="AT26" s="11">
         <f>IF(OR($C26="",AS26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS26,FIND("-",AS26)-1),"")=AW26,IFERROR(--MID(AS26,FIND("-",AS26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AS26,FIND("-",AS26)-1),""))-(IFERROR(--MID(AS26,FIND("-",AS26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AS26,FIND("-",AS26)-1),""))-(IFERROR(--MID(AS26,FIND("-",AS26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AS26,FIND("-",AS26)-1),""))=(AW26))+2*((IFERROR(--MID(AS26,FIND("-",AS26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AU26" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AV26" s="11" t="str">
+      <c r="AV26" s="11">
         <f>IF(OR($C26="",AU26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU26,FIND("-",AU26)-1),"")=AW26,IFERROR(--MID(AU26,FIND("-",AU26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AU26,FIND("-",AU26)-1),""))-(IFERROR(--MID(AU26,FIND("-",AU26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AU26,FIND("-",AU26)-1),""))-(IFERROR(--MID(AU26,FIND("-",AU26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AU26,FIND("-",AU26)-1),""))=(AW26))+2*((IFERROR(--MID(AU26,FIND("-",AU26)+1,99),""))=(AX26))),""))</f>
-        <v/>
-      </c>
-      <c r="AW26" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW26" s="11">
         <f>IF($C26="","",IFERROR(--LEFT($C26,FIND("-",$C26)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX26" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX26" s="11">
         <f>IF($C26="","",IFERROR(--MID($C26,FIND("-",$C26)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5055,7 +5059,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
@@ -5109,355 +5113,359 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>1</v>
       </c>
       <c r="B29" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D29" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="11" t="str">
+      <c r="F29" s="11">
         <f>IF(OR($C29="",E29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E29,FIND("-",E29)-1),"")=AW29,IFERROR(--MID(E29,FIND("-",E29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(E29,FIND("-",E29)-1),""))-(IFERROR(--MID(E29,FIND("-",E29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(E29,FIND("-",E29)-1),""))-(IFERROR(--MID(E29,FIND("-",E29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(E29,FIND("-",E29)-1),""))=(AW29))+2*((IFERROR(--MID(E29,FIND("-",E29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H29" s="11" t="str">
+      <c r="H29" s="11">
         <f>IF(OR($C29="",G29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G29,FIND("-",G29)-1),"")=AW29,IFERROR(--MID(G29,FIND("-",G29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(G29,FIND("-",G29)-1),""))-(IFERROR(--MID(G29,FIND("-",G29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(G29,FIND("-",G29)-1),""))-(IFERROR(--MID(G29,FIND("-",G29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(G29,FIND("-",G29)-1),""))=(AW29))+2*((IFERROR(--MID(G29,FIND("-",G29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J29" s="11" t="str">
+      <c r="J29" s="11">
         <f>IF(OR($C29="",I29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I29,FIND("-",I29)-1),"")=AW29,IFERROR(--MID(I29,FIND("-",I29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(I29,FIND("-",I29)-1),""))-(IFERROR(--MID(I29,FIND("-",I29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(I29,FIND("-",I29)-1),""))-(IFERROR(--MID(I29,FIND("-",I29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(I29,FIND("-",I29)-1),""))=(AW29))+2*((IFERROR(--MID(I29,FIND("-",I29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L29" s="11" t="str">
+      <c r="L29" s="11">
         <f>IF(OR($C29="",K29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K29,FIND("-",K29)-1),"")=AW29,IFERROR(--MID(K29,FIND("-",K29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(K29,FIND("-",K29)-1),""))-(IFERROR(--MID(K29,FIND("-",K29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(K29,FIND("-",K29)-1),""))-(IFERROR(--MID(K29,FIND("-",K29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(K29,FIND("-",K29)-1),""))=(AW29))+2*((IFERROR(--MID(K29,FIND("-",K29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="N29" s="11" t="str">
+      <c r="N29" s="11">
         <f>IF(OR($C29="",M29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M29,FIND("-",M29)-1),"")=AW29,IFERROR(--MID(M29,FIND("-",M29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(M29,FIND("-",M29)-1),""))-(IFERROR(--MID(M29,FIND("-",M29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(M29,FIND("-",M29)-1),""))-(IFERROR(--MID(M29,FIND("-",M29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(M29,FIND("-",M29)-1),""))=(AW29))+2*((IFERROR(--MID(M29,FIND("-",M29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="P29" s="11" t="str">
+      <c r="P29" s="11">
         <f>IF(OR($C29="",O29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O29,FIND("-",O29)-1),"")=AW29,IFERROR(--MID(O29,FIND("-",O29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(O29,FIND("-",O29)-1),""))-(IFERROR(--MID(O29,FIND("-",O29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(O29,FIND("-",O29)-1),""))-(IFERROR(--MID(O29,FIND("-",O29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(O29,FIND("-",O29)-1),""))=(AW29))+2*((IFERROR(--MID(O29,FIND("-",O29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q29" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="R29" s="11" t="str">
+      <c r="R29" s="11">
         <f>IF(OR($C29="",Q29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q29,FIND("-",Q29)-1),"")=AW29,IFERROR(--MID(Q29,FIND("-",Q29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(Q29,FIND("-",Q29)-1),""))-(IFERROR(--MID(Q29,FIND("-",Q29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(Q29,FIND("-",Q29)-1),""))-(IFERROR(--MID(Q29,FIND("-",Q29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(Q29,FIND("-",Q29)-1),""))=(AW29))+2*((IFERROR(--MID(Q29,FIND("-",Q29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S29" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T29" s="11" t="str">
+      <c r="T29" s="11">
         <f>IF(OR($C29="",S29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S29,FIND("-",S29)-1),"")=AW29,IFERROR(--MID(S29,FIND("-",S29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(S29,FIND("-",S29)-1),""))-(IFERROR(--MID(S29,FIND("-",S29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(S29,FIND("-",S29)-1),""))-(IFERROR(--MID(S29,FIND("-",S29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(S29,FIND("-",S29)-1),""))=(AW29))+2*((IFERROR(--MID(S29,FIND("-",S29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V29" s="11" t="str">
+      <c r="V29" s="11">
         <f>IF(OR($C29="",U29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U29,FIND("-",U29)-1),"")=AW29,IFERROR(--MID(U29,FIND("-",U29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(U29,FIND("-",U29)-1),""))-(IFERROR(--MID(U29,FIND("-",U29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(U29,FIND("-",U29)-1),""))-(IFERROR(--MID(U29,FIND("-",U29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(U29,FIND("-",U29)-1),""))=(AW29))+2*((IFERROR(--MID(U29,FIND("-",U29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X29" s="11" t="str">
+      <c r="X29" s="11">
         <f>IF(OR($C29="",W29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W29,FIND("-",W29)-1),"")=AW29,IFERROR(--MID(W29,FIND("-",W29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(W29,FIND("-",W29)-1),""))-(IFERROR(--MID(W29,FIND("-",W29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(W29,FIND("-",W29)-1),""))-(IFERROR(--MID(W29,FIND("-",W29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(W29,FIND("-",W29)-1),""))=(AW29))+2*((IFERROR(--MID(W29,FIND("-",W29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z29" s="11" t="str">
+      <c r="Z29" s="11">
         <f>IF(OR($C29="",Y29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y29,FIND("-",Y29)-1),"")=AW29,IFERROR(--MID(Y29,FIND("-",Y29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(Y29,FIND("-",Y29)-1),""))-(IFERROR(--MID(Y29,FIND("-",Y29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(Y29,FIND("-",Y29)-1),""))-(IFERROR(--MID(Y29,FIND("-",Y29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(Y29,FIND("-",Y29)-1),""))=(AW29))+2*((IFERROR(--MID(Y29,FIND("-",Y29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB29" s="11" t="str">
+      <c r="AB29" s="11">
         <f>IF(OR($C29="",AA29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA29,FIND("-",AA29)-1),"")=AW29,IFERROR(--MID(AA29,FIND("-",AA29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AA29,FIND("-",AA29)-1),""))-(IFERROR(--MID(AA29,FIND("-",AA29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AA29,FIND("-",AA29)-1),""))-(IFERROR(--MID(AA29,FIND("-",AA29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AA29,FIND("-",AA29)-1),""))=(AW29))+2*((IFERROR(--MID(AA29,FIND("-",AA29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC29" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AD29" s="11" t="str">
+      <c r="AD29" s="11">
         <f>IF(OR($C29="",AC29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC29,FIND("-",AC29)-1),"")=AW29,IFERROR(--MID(AC29,FIND("-",AC29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AC29,FIND("-",AC29)-1),""))-(IFERROR(--MID(AC29,FIND("-",AC29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AC29,FIND("-",AC29)-1),""))-(IFERROR(--MID(AC29,FIND("-",AC29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AC29,FIND("-",AC29)-1),""))=(AW29))+2*((IFERROR(--MID(AC29,FIND("-",AC29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF29" s="11" t="str">
+      <c r="AF29" s="11">
         <f>IF(OR($C29="",AE29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE29,FIND("-",AE29)-1),"")=AW29,IFERROR(--MID(AE29,FIND("-",AE29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AE29,FIND("-",AE29)-1),""))-(IFERROR(--MID(AE29,FIND("-",AE29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AE29,FIND("-",AE29)-1),""))-(IFERROR(--MID(AE29,FIND("-",AE29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AE29,FIND("-",AE29)-1),""))=(AW29))+2*((IFERROR(--MID(AE29,FIND("-",AE29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH29" s="11" t="str">
+      <c r="AH29" s="11">
         <f>IF(OR($C29="",AG29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG29,FIND("-",AG29)-1),"")=AW29,IFERROR(--MID(AG29,FIND("-",AG29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AG29,FIND("-",AG29)-1),""))-(IFERROR(--MID(AG29,FIND("-",AG29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AG29,FIND("-",AG29)-1),""))-(IFERROR(--MID(AG29,FIND("-",AG29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AG29,FIND("-",AG29)-1),""))=(AW29))+2*((IFERROR(--MID(AG29,FIND("-",AG29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AJ29" s="11" t="str">
+      <c r="AJ29" s="11">
         <f>IF(OR($C29="",AI29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI29,FIND("-",AI29)-1),"")=AW29,IFERROR(--MID(AI29,FIND("-",AI29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AI29,FIND("-",AI29)-1),""))-(IFERROR(--MID(AI29,FIND("-",AI29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AI29,FIND("-",AI29)-1),""))-(IFERROR(--MID(AI29,FIND("-",AI29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AI29,FIND("-",AI29)-1),""))=(AW29))+2*((IFERROR(--MID(AI29,FIND("-",AI29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL29" s="11" t="str">
+      <c r="AL29" s="11">
         <f>IF(OR($C29="",AK29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK29,FIND("-",AK29)-1),"")=AW29,IFERROR(--MID(AK29,FIND("-",AK29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AK29,FIND("-",AK29)-1),""))-(IFERROR(--MID(AK29,FIND("-",AK29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AK29,FIND("-",AK29)-1),""))-(IFERROR(--MID(AK29,FIND("-",AK29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AK29,FIND("-",AK29)-1),""))=(AW29))+2*((IFERROR(--MID(AK29,FIND("-",AK29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM29" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN29" s="11" t="str">
+      <c r="AN29" s="11">
         <f>IF(OR($C29="",AM29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM29,FIND("-",AM29)-1),"")=AW29,IFERROR(--MID(AM29,FIND("-",AM29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AM29,FIND("-",AM29)-1),""))-(IFERROR(--MID(AM29,FIND("-",AM29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AM29,FIND("-",AM29)-1),""))-(IFERROR(--MID(AM29,FIND("-",AM29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AM29,FIND("-",AM29)-1),""))=(AW29))+2*((IFERROR(--MID(AM29,FIND("-",AM29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO29" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AP29" s="11" t="str">
+      <c r="AP29" s="11">
         <f>IF(OR($C29="",AO29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO29,FIND("-",AO29)-1),"")=AW29,IFERROR(--MID(AO29,FIND("-",AO29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AO29,FIND("-",AO29)-1),""))-(IFERROR(--MID(AO29,FIND("-",AO29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AO29,FIND("-",AO29)-1),""))-(IFERROR(--MID(AO29,FIND("-",AO29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AO29,FIND("-",AO29)-1),""))=(AW29))+2*((IFERROR(--MID(AO29,FIND("-",AO29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR29" s="11" t="str">
+      <c r="AR29" s="11">
         <f>IF(OR($C29="",AQ29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ29,FIND("-",AQ29)-1),"")=AW29,IFERROR(--MID(AQ29,FIND("-",AQ29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AQ29,FIND("-",AQ29)-1),""))-(IFERROR(--MID(AQ29,FIND("-",AQ29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AQ29,FIND("-",AQ29)-1),""))-(IFERROR(--MID(AQ29,FIND("-",AQ29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AQ29,FIND("-",AQ29)-1),""))=(AW29))+2*((IFERROR(--MID(AQ29,FIND("-",AQ29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS29" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AT29" s="11" t="str">
+      <c r="AT29" s="11">
         <f>IF(OR($C29="",AS29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS29,FIND("-",AS29)-1),"")=AW29,IFERROR(--MID(AS29,FIND("-",AS29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AS29,FIND("-",AS29)-1),""))-(IFERROR(--MID(AS29,FIND("-",AS29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AS29,FIND("-",AS29)-1),""))-(IFERROR(--MID(AS29,FIND("-",AS29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AS29,FIND("-",AS29)-1),""))=(AW29))+2*((IFERROR(--MID(AS29,FIND("-",AS29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU29" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AV29" s="11" t="str">
+      <c r="AV29" s="11">
         <f>IF(OR($C29="",AU29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU29,FIND("-",AU29)-1),"")=AW29,IFERROR(--MID(AU29,FIND("-",AU29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AU29,FIND("-",AU29)-1),""))-(IFERROR(--MID(AU29,FIND("-",AU29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AU29,FIND("-",AU29)-1),""))-(IFERROR(--MID(AU29,FIND("-",AU29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AU29,FIND("-",AU29)-1),""))=(AW29))+2*((IFERROR(--MID(AU29,FIND("-",AU29)+1,99),""))=(AX29))),""))</f>
-        <v/>
-      </c>
-      <c r="AW29" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW29" s="11">
         <f>IF($C29="","",IFERROR(--LEFT($C29,FIND("-",$C29)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX29" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX29" s="11">
         <f>IF($C29="","",IFERROR(--MID($C29,FIND("-",$C29)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="D30" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="11" t="str">
+      <c r="F30" s="11">
         <f>IF(OR($C30="",E30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E30,FIND("-",E30)-1),"")=AW30,IFERROR(--MID(E30,FIND("-",E30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(E30,FIND("-",E30)-1),""))-(IFERROR(--MID(E30,FIND("-",E30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(E30,FIND("-",E30)-1),""))-(IFERROR(--MID(E30,FIND("-",E30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(E30,FIND("-",E30)-1),""))=(AW30))+2*((IFERROR(--MID(E30,FIND("-",E30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H30" s="11" t="str">
+      <c r="H30" s="11">
         <f>IF(OR($C30="",G30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G30,FIND("-",G30)-1),"")=AW30,IFERROR(--MID(G30,FIND("-",G30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(G30,FIND("-",G30)-1),""))-(IFERROR(--MID(G30,FIND("-",G30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(G30,FIND("-",G30)-1),""))-(IFERROR(--MID(G30,FIND("-",G30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(G30,FIND("-",G30)-1),""))=(AW30))+2*((IFERROR(--MID(G30,FIND("-",G30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="11" t="str">
+      <c r="J30" s="11">
         <f>IF(OR($C30="",I30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I30,FIND("-",I30)-1),"")=AW30,IFERROR(--MID(I30,FIND("-",I30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(I30,FIND("-",I30)-1),""))-(IFERROR(--MID(I30,FIND("-",I30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(I30,FIND("-",I30)-1),""))-(IFERROR(--MID(I30,FIND("-",I30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(I30,FIND("-",I30)-1),""))=(AW30))+2*((IFERROR(--MID(I30,FIND("-",I30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K30" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L30" s="11" t="str">
+      <c r="L30" s="11">
         <f>IF(OR($C30="",K30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K30,FIND("-",K30)-1),"")=AW30,IFERROR(--MID(K30,FIND("-",K30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(K30,FIND("-",K30)-1),""))-(IFERROR(--MID(K30,FIND("-",K30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(K30,FIND("-",K30)-1),""))-(IFERROR(--MID(K30,FIND("-",K30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(K30,FIND("-",K30)-1),""))=(AW30))+2*((IFERROR(--MID(K30,FIND("-",K30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N30" s="11" t="str">
+      <c r="N30" s="11">
         <f>IF(OR($C30="",M30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M30,FIND("-",M30)-1),"")=AW30,IFERROR(--MID(M30,FIND("-",M30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(M30,FIND("-",M30)-1),""))-(IFERROR(--MID(M30,FIND("-",M30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(M30,FIND("-",M30)-1),""))-(IFERROR(--MID(M30,FIND("-",M30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(M30,FIND("-",M30)-1),""))=(AW30))+2*((IFERROR(--MID(M30,FIND("-",M30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O30" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="P30" s="11" t="str">
+      <c r="P30" s="11">
         <f>IF(OR($C30="",O30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O30,FIND("-",O30)-1),"")=AW30,IFERROR(--MID(O30,FIND("-",O30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(O30,FIND("-",O30)-1),""))-(IFERROR(--MID(O30,FIND("-",O30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(O30,FIND("-",O30)-1),""))-(IFERROR(--MID(O30,FIND("-",O30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(O30,FIND("-",O30)-1),""))=(AW30))+2*((IFERROR(--MID(O30,FIND("-",O30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q30" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="R30" s="11" t="str">
+      <c r="R30" s="11">
         <f>IF(OR($C30="",Q30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q30,FIND("-",Q30)-1),"")=AW30,IFERROR(--MID(Q30,FIND("-",Q30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(Q30,FIND("-",Q30)-1),""))-(IFERROR(--MID(Q30,FIND("-",Q30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(Q30,FIND("-",Q30)-1),""))-(IFERROR(--MID(Q30,FIND("-",Q30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(Q30,FIND("-",Q30)-1),""))=(AW30))+2*((IFERROR(--MID(Q30,FIND("-",Q30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T30" s="11" t="str">
+      <c r="T30" s="11">
         <f>IF(OR($C30="",S30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S30,FIND("-",S30)-1),"")=AW30,IFERROR(--MID(S30,FIND("-",S30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(S30,FIND("-",S30)-1),""))-(IFERROR(--MID(S30,FIND("-",S30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(S30,FIND("-",S30)-1),""))-(IFERROR(--MID(S30,FIND("-",S30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(S30,FIND("-",S30)-1),""))=(AW30))+2*((IFERROR(--MID(S30,FIND("-",S30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="V30" s="11" t="str">
+      <c r="V30" s="11">
         <f>IF(OR($C30="",U30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U30,FIND("-",U30)-1),"")=AW30,IFERROR(--MID(U30,FIND("-",U30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(U30,FIND("-",U30)-1),""))-(IFERROR(--MID(U30,FIND("-",U30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(U30,FIND("-",U30)-1),""))-(IFERROR(--MID(U30,FIND("-",U30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(U30,FIND("-",U30)-1),""))=(AW30))+2*((IFERROR(--MID(U30,FIND("-",U30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X30" s="11" t="str">
+      <c r="X30" s="11">
         <f>IF(OR($C30="",W30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W30,FIND("-",W30)-1),"")=AW30,IFERROR(--MID(W30,FIND("-",W30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(W30,FIND("-",W30)-1),""))-(IFERROR(--MID(W30,FIND("-",W30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(W30,FIND("-",W30)-1),""))-(IFERROR(--MID(W30,FIND("-",W30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(W30,FIND("-",W30)-1),""))=(AW30))+2*((IFERROR(--MID(W30,FIND("-",W30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z30" s="11" t="str">
+      <c r="Z30" s="11">
         <f>IF(OR($C30="",Y30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y30,FIND("-",Y30)-1),"")=AW30,IFERROR(--MID(Y30,FIND("-",Y30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(Y30,FIND("-",Y30)-1),""))-(IFERROR(--MID(Y30,FIND("-",Y30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(Y30,FIND("-",Y30)-1),""))-(IFERROR(--MID(Y30,FIND("-",Y30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(Y30,FIND("-",Y30)-1),""))=(AW30))+2*((IFERROR(--MID(Y30,FIND("-",Y30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AB30" s="11" t="str">
+      <c r="AB30" s="11">
         <f>IF(OR($C30="",AA30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA30,FIND("-",AA30)-1),"")=AW30,IFERROR(--MID(AA30,FIND("-",AA30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AA30,FIND("-",AA30)-1),""))-(IFERROR(--MID(AA30,FIND("-",AA30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AA30,FIND("-",AA30)-1),""))-(IFERROR(--MID(AA30,FIND("-",AA30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AA30,FIND("-",AA30)-1),""))=(AW30))+2*((IFERROR(--MID(AA30,FIND("-",AA30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC30" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD30" s="11" t="str">
+      <c r="AD30" s="11">
         <f>IF(OR($C30="",AC30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC30,FIND("-",AC30)-1),"")=AW30,IFERROR(--MID(AC30,FIND("-",AC30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AC30,FIND("-",AC30)-1),""))-(IFERROR(--MID(AC30,FIND("-",AC30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AC30,FIND("-",AC30)-1),""))-(IFERROR(--MID(AC30,FIND("-",AC30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AC30,FIND("-",AC30)-1),""))=(AW30))+2*((IFERROR(--MID(AC30,FIND("-",AC30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF30" s="11" t="str">
+      <c r="AF30" s="11">
         <f>IF(OR($C30="",AE30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE30,FIND("-",AE30)-1),"")=AW30,IFERROR(--MID(AE30,FIND("-",AE30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AE30,FIND("-",AE30)-1),""))-(IFERROR(--MID(AE30,FIND("-",AE30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AE30,FIND("-",AE30)-1),""))-(IFERROR(--MID(AE30,FIND("-",AE30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AE30,FIND("-",AE30)-1),""))=(AW30))+2*((IFERROR(--MID(AE30,FIND("-",AE30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH30" s="11" t="str">
+      <c r="AH30" s="11">
         <f>IF(OR($C30="",AG30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG30,FIND("-",AG30)-1),"")=AW30,IFERROR(--MID(AG30,FIND("-",AG30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AG30,FIND("-",AG30)-1),""))-(IFERROR(--MID(AG30,FIND("-",AG30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AG30,FIND("-",AG30)-1),""))-(IFERROR(--MID(AG30,FIND("-",AG30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AG30,FIND("-",AG30)-1),""))=(AW30))+2*((IFERROR(--MID(AG30,FIND("-",AG30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ30" s="11" t="str">
+      <c r="AJ30" s="11">
         <f>IF(OR($C30="",AI30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI30,FIND("-",AI30)-1),"")=AW30,IFERROR(--MID(AI30,FIND("-",AI30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AI30,FIND("-",AI30)-1),""))-(IFERROR(--MID(AI30,FIND("-",AI30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AI30,FIND("-",AI30)-1),""))-(IFERROR(--MID(AI30,FIND("-",AI30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AI30,FIND("-",AI30)-1),""))=(AW30))+2*((IFERROR(--MID(AI30,FIND("-",AI30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL30" s="11" t="str">
+      <c r="AL30" s="11">
         <f>IF(OR($C30="",AK30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK30,FIND("-",AK30)-1),"")=AW30,IFERROR(--MID(AK30,FIND("-",AK30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AK30,FIND("-",AK30)-1),""))-(IFERROR(--MID(AK30,FIND("-",AK30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AK30,FIND("-",AK30)-1),""))-(IFERROR(--MID(AK30,FIND("-",AK30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AK30,FIND("-",AK30)-1),""))=(AW30))+2*((IFERROR(--MID(AK30,FIND("-",AK30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AN30" s="11" t="str">
+      <c r="AN30" s="11">
         <f>IF(OR($C30="",AM30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM30,FIND("-",AM30)-1),"")=AW30,IFERROR(--MID(AM30,FIND("-",AM30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AM30,FIND("-",AM30)-1),""))-(IFERROR(--MID(AM30,FIND("-",AM30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AM30,FIND("-",AM30)-1),""))-(IFERROR(--MID(AM30,FIND("-",AM30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AM30,FIND("-",AM30)-1),""))=(AW30))+2*((IFERROR(--MID(AM30,FIND("-",AM30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP30" s="11" t="str">
+      <c r="AP30" s="11">
         <f>IF(OR($C30="",AO30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO30,FIND("-",AO30)-1),"")=AW30,IFERROR(--MID(AO30,FIND("-",AO30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AO30,FIND("-",AO30)-1),""))-(IFERROR(--MID(AO30,FIND("-",AO30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AO30,FIND("-",AO30)-1),""))-(IFERROR(--MID(AO30,FIND("-",AO30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AO30,FIND("-",AO30)-1),""))=(AW30))+2*((IFERROR(--MID(AO30,FIND("-",AO30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ30" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AR30" s="11" t="str">
+      <c r="AR30" s="11">
         <f>IF(OR($C30="",AQ30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ30,FIND("-",AQ30)-1),"")=AW30,IFERROR(--MID(AQ30,FIND("-",AQ30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AQ30,FIND("-",AQ30)-1),""))-(IFERROR(--MID(AQ30,FIND("-",AQ30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AQ30,FIND("-",AQ30)-1),""))-(IFERROR(--MID(AQ30,FIND("-",AQ30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AQ30,FIND("-",AQ30)-1),""))=(AW30))+2*((IFERROR(--MID(AQ30,FIND("-",AQ30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT30" s="11" t="str">
+      <c r="AT30" s="11">
         <f>IF(OR($C30="",AS30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS30,FIND("-",AS30)-1),"")=AW30,IFERROR(--MID(AS30,FIND("-",AS30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AS30,FIND("-",AS30)-1),""))-(IFERROR(--MID(AS30,FIND("-",AS30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AS30,FIND("-",AS30)-1),""))-(IFERROR(--MID(AS30,FIND("-",AS30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AS30,FIND("-",AS30)-1),""))=(AW30))+2*((IFERROR(--MID(AS30,FIND("-",AS30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AV30" s="11" t="str">
+      <c r="AV30" s="11">
         <f>IF(OR($C30="",AU30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU30,FIND("-",AU30)-1),"")=AW30,IFERROR(--MID(AU30,FIND("-",AU30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AU30,FIND("-",AU30)-1),""))-(IFERROR(--MID(AU30,FIND("-",AU30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AU30,FIND("-",AU30)-1),""))-(IFERROR(--MID(AU30,FIND("-",AU30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AU30,FIND("-",AU30)-1),""))=(AW30))+2*((IFERROR(--MID(AU30,FIND("-",AU30)+1,99),""))=(AX30))),""))</f>
-        <v/>
-      </c>
-      <c r="AW30" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW30" s="11">
         <f>IF($C30="","",IFERROR(--LEFT($C30,FIND("-",$C30)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX30" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX30" s="11">
         <f>IF($C30="","",IFERROR(--MID($C30,FIND("-",$C30)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5631,7 +5639,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5689,7 +5697,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
@@ -5743,7 +5751,7 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5917,7 +5925,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6091,7 +6099,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6265,7 +6273,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6439,7 +6447,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6613,7 +6621,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6671,7 +6679,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
@@ -6725,7 +6733,7 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6899,7 +6907,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7073,7 +7081,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7247,7 +7255,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7421,7 +7429,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="18"/>
       <c r="C45" s="13"/>
@@ -7479,7 +7487,7 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
@@ -7533,7 +7541,7 @@
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7707,7 +7715,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7881,7 +7889,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8055,7 +8063,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="18"/>
       <c r="C50" s="13"/>
@@ -8113,7 +8121,7 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
@@ -8167,7 +8175,7 @@
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8341,7 +8349,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8515,7 +8523,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8689,7 +8697,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8863,7 +8871,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9037,7 +9045,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="18"/>
       <c r="C57" s="13"/>
@@ -9095,7 +9103,7 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
@@ -9149,7 +9157,7 @@
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9323,7 +9331,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9497,7 +9505,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9671,7 +9679,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9845,7 +9853,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12"/>
       <c r="B63" s="18"/>
       <c r="C63" s="13"/>
@@ -9903,7 +9911,7 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
@@ -9957,7 +9965,7 @@
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10131,7 +10139,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10305,7 +10313,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10479,7 +10487,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10653,7 +10661,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="18"/>
       <c r="C69" s="13"/>
@@ -10711,7 +10719,7 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
@@ -10765,7 +10773,7 @@
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -10939,7 +10947,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11113,7 +11121,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11287,7 +11295,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11461,7 +11469,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="18"/>
       <c r="C75" s="13"/>
@@ -11519,7 +11527,7 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
@@ -11573,7 +11581,7 @@
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11747,7 +11755,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -11921,7 +11929,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12095,7 +12103,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12269,7 +12277,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="18"/>
       <c r="C81" s="13"/>
@@ -12327,7 +12335,7 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
@@ -12381,7 +12389,7 @@
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12555,7 +12563,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12729,7 +12737,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -12903,7 +12911,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13077,7 +13085,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13251,7 +13259,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13425,7 +13433,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="18"/>
       <c r="C89" s="13"/>
@@ -13483,7 +13491,7 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
@@ -13537,7 +13545,7 @@
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13711,7 +13719,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13885,7 +13893,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14059,7 +14067,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14233,7 +14241,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14407,7 +14415,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14581,7 +14589,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="18"/>
       <c r="C97" s="13"/>
@@ -14639,7 +14647,7 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
@@ -14693,7 +14701,7 @@
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14867,7 +14875,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15041,7 +15049,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15215,7 +15223,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15389,7 +15397,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15563,7 +15571,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15737,7 +15745,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="12"/>
       <c r="B105" s="18"/>
       <c r="C105" s="13"/>
@@ -15795,7 +15803,7 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
@@ -15849,7 +15857,7 @@
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16023,7 +16031,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16197,7 +16205,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16371,7 +16379,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16545,7 +16553,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12"/>
       <c r="B111" s="18"/>
       <c r="C111" s="13"/>
@@ -16603,7 +16611,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12"/>
       <c r="B112" s="18"/>
       <c r="C112" s="13"/>
@@ -16661,7 +16669,7 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="38" t="s">
         <v>128</v>
       </c>
@@ -16715,7 +16723,7 @@
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
@@ -16769,7 +16777,7 @@
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -16899,7 +16907,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12"/>
       <c r="B116" s="18"/>
       <c r="C116" s="13"/>
@@ -16957,7 +16965,7 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
@@ -17011,7 +17019,7 @@
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17141,7 +17149,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17271,7 +17279,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12"/>
       <c r="B120" s="18"/>
       <c r="C120" s="13"/>
@@ -17329,7 +17337,7 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
@@ -17383,7 +17391,7 @@
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17513,7 +17521,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17643,7 +17651,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17773,7 +17781,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12"/>
       <c r="B125" s="18"/>
       <c r="C125" s="13"/>
@@ -17831,7 +17839,7 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
@@ -17885,7 +17893,7 @@
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18015,7 +18023,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18145,7 +18153,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18275,7 +18283,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="18"/>
       <c r="C130" s="13"/>
@@ -18333,7 +18341,7 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
@@ -18387,7 +18395,7 @@
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18517,7 +18525,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18647,7 +18655,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="18"/>
       <c r="C134" s="13"/>
@@ -18705,7 +18713,7 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
@@ -18759,7 +18767,7 @@
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -18889,7 +18897,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19019,7 +19027,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19149,7 +19157,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12"/>
       <c r="B139" s="18"/>
       <c r="C139" s="13"/>
@@ -19207,7 +19215,7 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
@@ -19261,7 +19269,7 @@
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19391,7 +19399,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19521,7 +19529,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12"/>
       <c r="B143" s="18"/>
       <c r="C143" s="13"/>
@@ -19579,7 +19587,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12"/>
       <c r="B144" s="18"/>
       <c r="C144" s="13"/>
@@ -19637,7 +19645,7 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="38" t="s">
         <v>167</v>
       </c>
@@ -19691,7 +19699,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
@@ -19745,7 +19753,7 @@
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19875,7 +19883,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20005,7 +20013,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12"/>
       <c r="B149" s="18"/>
       <c r="C149" s="13"/>
@@ -20063,7 +20071,7 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
@@ -20117,7 +20125,7 @@
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20247,7 +20255,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12"/>
       <c r="B152" s="18"/>
       <c r="C152" s="13"/>
@@ -20305,7 +20313,7 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
@@ -20359,7 +20367,7 @@
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20489,7 +20497,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20619,7 +20627,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12"/>
       <c r="B156" s="18"/>
       <c r="C156" s="13"/>
@@ -20677,7 +20685,7 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
@@ -20731,7 +20739,7 @@
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20861,7 +20869,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -20991,7 +20999,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21121,7 +21129,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12"/>
       <c r="B161" s="18"/>
       <c r="C161" s="13"/>
@@ -21179,7 +21187,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12"/>
       <c r="B162" s="18"/>
       <c r="C162" s="13"/>
@@ -21237,7 +21245,7 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="38" t="s">
         <v>187</v>
       </c>
@@ -21291,7 +21299,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
@@ -21345,7 +21353,7 @@
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21475,7 +21483,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12"/>
       <c r="B166" s="18"/>
       <c r="C166" s="13"/>
@@ -21533,7 +21541,7 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
@@ -21587,7 +21595,7 @@
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21717,7 +21725,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
       <c r="B169" s="18"/>
       <c r="C169" s="13"/>
@@ -21775,7 +21783,7 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
@@ -21829,7 +21837,7 @@
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -21959,7 +21967,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="18"/>
       <c r="C172" s="13"/>
@@ -22017,7 +22025,7 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
@@ -22071,7 +22079,7 @@
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22201,7 +22209,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12"/>
       <c r="B175" s="18"/>
       <c r="C175" s="13"/>
@@ -22259,7 +22267,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12"/>
       <c r="B176" s="18"/>
       <c r="C176" s="13"/>
@@ -22317,7 +22325,7 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="38" t="s">
         <v>200</v>
       </c>
@@ -22371,7 +22379,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
@@ -22425,7 +22433,7 @@
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22555,7 +22563,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12"/>
       <c r="B180" s="18"/>
       <c r="C180" s="13"/>
@@ -22613,7 +22621,7 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
@@ -22667,7 +22675,7 @@
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22797,7 +22805,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12"/>
       <c r="B183" s="18"/>
       <c r="C183" s="13"/>
@@ -22855,7 +22863,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12"/>
       <c r="B184" s="18"/>
       <c r="C184" s="13"/>
@@ -22913,7 +22921,7 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="38" t="s">
         <v>207</v>
       </c>
@@ -22967,7 +22975,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
@@ -23021,7 +23029,7 @@
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23151,7 +23159,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12"/>
       <c r="B188" s="18"/>
       <c r="C188" s="13"/>
@@ -23209,7 +23217,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12"/>
       <c r="B189" s="18"/>
       <c r="C189" s="13"/>
@@ -23267,7 +23275,7 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="38" t="s">
         <v>211</v>
       </c>
@@ -23321,7 +23329,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
@@ -23375,7 +23383,7 @@
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23505,7 +23513,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12"/>
       <c r="B193" s="18"/>
       <c r="C193" s="13"/>
@@ -23563,7 +23571,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12"/>
       <c r="B194" s="18"/>
       <c r="C194" s="13"/>
@@ -23702,58 +23710,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.26953125" customWidth="1"/>
+    <col min="2" max="2" width="75.28515625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" customWidth="1"/>
-    <col min="12" max="12" width="12.54296875" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" customWidth="1"/>
-    <col min="14" max="14" width="12.54296875" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.54296875" customWidth="1"/>
-    <col min="16" max="16" width="12.54296875" style="23" customWidth="1"/>
-    <col min="17" max="17" width="10.54296875" customWidth="1"/>
-    <col min="18" max="18" width="12.54296875" style="23" customWidth="1"/>
-    <col min="19" max="19" width="10.54296875" customWidth="1"/>
-    <col min="20" max="20" width="12.54296875" customWidth="1"/>
-    <col min="21" max="21" width="10.54296875" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" style="23" customWidth="1"/>
-    <col min="23" max="23" width="10.54296875" customWidth="1"/>
-    <col min="24" max="24" width="12.54296875" style="23" customWidth="1"/>
-    <col min="25" max="25" width="10.54296875" customWidth="1"/>
-    <col min="26" max="26" width="12.54296875" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.54296875" customWidth="1"/>
-    <col min="28" max="28" width="12.54296875" style="23" customWidth="1"/>
-    <col min="29" max="29" width="10.54296875" customWidth="1"/>
-    <col min="30" max="30" width="12.54296875" style="23" customWidth="1"/>
-    <col min="31" max="31" width="10.54296875" customWidth="1"/>
-    <col min="32" max="32" width="12.54296875" style="23" customWidth="1"/>
-    <col min="33" max="33" width="10.54296875" customWidth="1"/>
-    <col min="34" max="34" width="12.54296875" style="23" customWidth="1"/>
-    <col min="35" max="35" width="10.54296875" customWidth="1"/>
-    <col min="36" max="36" width="12.54296875" style="23" customWidth="1"/>
-    <col min="37" max="37" width="10.54296875" customWidth="1"/>
-    <col min="38" max="38" width="12.54296875" style="23" customWidth="1"/>
-    <col min="39" max="39" width="10.54296875" customWidth="1"/>
-    <col min="40" max="40" width="12.54296875" style="23" customWidth="1"/>
-    <col min="41" max="41" width="10.54296875" customWidth="1"/>
-    <col min="42" max="42" width="12.54296875" customWidth="1"/>
-    <col min="43" max="43" width="10.54296875" customWidth="1"/>
-    <col min="44" max="44" width="12.54296875" style="23" customWidth="1"/>
-    <col min="45" max="45" width="10.54296875" customWidth="1"/>
-    <col min="46" max="46" width="12.54296875" style="23" customWidth="1"/>
-    <col min="47" max="47" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="23" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="23" customWidth="1"/>
+    <col min="19" max="19" width="10.5703125" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="23" customWidth="1"/>
+    <col min="23" max="23" width="10.5703125" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" style="23" customWidth="1"/>
+    <col min="25" max="25" width="10.5703125" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" style="23" customWidth="1"/>
+    <col min="27" max="27" width="10.5703125" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" style="23" customWidth="1"/>
+    <col min="29" max="29" width="10.5703125" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" style="23" customWidth="1"/>
+    <col min="31" max="31" width="10.5703125" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" style="23" customWidth="1"/>
+    <col min="33" max="33" width="10.5703125" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="23" customWidth="1"/>
+    <col min="35" max="35" width="10.5703125" customWidth="1"/>
+    <col min="36" max="36" width="12.5703125" style="23" customWidth="1"/>
+    <col min="37" max="37" width="10.5703125" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="23" customWidth="1"/>
+    <col min="39" max="39" width="10.5703125" customWidth="1"/>
+    <col min="40" max="40" width="12.5703125" style="23" customWidth="1"/>
+    <col min="41" max="41" width="10.5703125" customWidth="1"/>
+    <col min="42" max="42" width="12.5703125" customWidth="1"/>
+    <col min="43" max="43" width="10.5703125" customWidth="1"/>
+    <col min="44" max="44" width="12.5703125" style="23" customWidth="1"/>
+    <col min="45" max="45" width="10.5703125" customWidth="1"/>
+    <col min="46" max="46" width="12.5703125" style="23" customWidth="1"/>
+    <col min="47" max="47" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23866,7 +23874,7 @@
       </c>
       <c r="AU1" s="39"/>
     </row>
-    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21"/>
       <c r="B2" s="25" t="s">
         <v>215</v>
@@ -24007,7 +24015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24170,7 +24178,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24333,7 +24341,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24496,7 +24504,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24659,7 +24667,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24822,7 +24830,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -24985,7 +24993,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25148,7 +25156,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25311,7 +25319,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25474,7 +25482,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25637,7 +25645,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25800,7 +25808,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -25963,7 +25971,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26126,7 +26134,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26289,7 +26297,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26441,16 +26449,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.7265625" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
@@ -26459,7 +26467,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>285</v>
       </c>
@@ -26476,7 +26484,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
@@ -26487,7 +26495,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26495,10 +26503,10 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
         <v>2</v>
@@ -26509,7 +26517,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26517,35 +26525,35 @@
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>51</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>58</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
@@ -26553,7 +26561,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!I17</f>
@@ -26561,211 +26569,211 @@
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>50</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>57</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>49</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>56</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>47</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>55</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
         <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>47</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>55</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
         <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
+      </c>
+      <c r="C11" s="11">
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>53</v>
+      </c>
+      <c r="D11" s="11">
+        <f>Bonus_beheer!Y17</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <f>C11+D11</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="str">
         <f>Wedstrijden_beheer!AK1</f>
         <v>Kim</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>46</v>
-      </c>
-      <c r="D11" s="11">
+        <v>52</v>
+      </c>
+      <c r="D12" s="11">
         <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
-      <c r="E11" s="11">
-        <f>C11+D11</f>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11">
-        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
-      </c>
-      <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>46</v>
-      </c>
-      <c r="D12" s="11">
-        <f>Bonus_beheer!G17</f>
-        <v>0</v>
-      </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>44</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>51</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
         <v>11</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>44</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>51</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
         <v>13</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>43</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>50</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
         <f>Wedstrijden_beheer!AO1</f>
@@ -26773,7 +26781,7 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -26781,183 +26789,183 @@
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
+      </c>
+      <c r="C17" s="11">
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>49</v>
+      </c>
+      <c r="D17" s="11">
+        <f>Bonus_beheer!Q17</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="11">
+        <f>C17+D17</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
+      </c>
+      <c r="C18" s="11">
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>49</v>
+      </c>
+      <c r="D18" s="11">
+        <f>Bonus_beheer!Q18</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="11">
+        <f>C18+D18</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="str">
         <f>Wedstrijden_beheer!AG1</f>
         <v>Erwin</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>41</v>
-      </c>
-      <c r="D17" s="11">
+        <v>47</v>
+      </c>
+      <c r="D19" s="11">
         <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
-      <c r="E17" s="11">
-        <f>C17+D17</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11">
-        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
-      </c>
-      <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>40</v>
-      </c>
-      <c r="D18" s="11">
-        <f>Bonus_beheer!Q17</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="11">
-        <f>C18+D18</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11">
-        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
-        <v>16</v>
-      </c>
-      <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
-      </c>
-      <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>40</v>
-      </c>
-      <c r="D19" s="11">
-        <f>Bonus_beheer!Q18</f>
-        <v>0</v>
-      </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C20" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>39</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>46</v>
       </c>
       <c r="D20" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="str">
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
+      </c>
+      <c r="C21" s="11">
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>46</v>
+      </c>
+      <c r="D21" s="11">
+        <f>Bonus_beheer!AI17</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="11">
+        <f>C21+D21</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
+        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
         <v>Kristel</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>38</v>
-      </c>
-      <c r="D21" s="11">
+        <v>42</v>
+      </c>
+      <c r="D22" s="11">
         <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
-      <c r="E21" s="11">
-        <f>C21+D21</f>
-        <v>38</v>
+      <c r="E22" s="11">
+        <f>C22+D22</f>
+        <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11">
-        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
-        <v>19</v>
-      </c>
-      <c r="B22" s="1" t="str">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!AC1</f>
         <v>Ron</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>38</v>
-      </c>
-      <c r="D22" s="11">
+        <v>42</v>
+      </c>
+      <c r="D23" s="11">
         <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
-      <c r="E22" s="11">
-        <f>C22+D22</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="11">
-        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
-      </c>
-      <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>36</v>
-      </c>
-      <c r="D23" s="11">
-        <f>Bonus_beheer!K17</f>
-        <v>0</v>
-      </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
       </c>
       <c r="C24" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>35</v>
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
+        <v>40</v>
       </c>
       <c r="D24" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -26973,20 +26981,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" hidden="1"/>
+    <col min="3" max="16384" width="8.7109375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -26994,7 +27002,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27002,7 +27010,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27010,7 +27018,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27018,7 +27026,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27026,7 +27034,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27034,7 +27042,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27042,7 +27050,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27058,16 +27066,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" customWidth="1"/>
-    <col min="3" max="3" width="30.7265625" customWidth="1"/>
+    <col min="1" max="1" width="55.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.7265625" hidden="1"/>
+    <col min="45" max="16384" width="8.7109375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>306</v>
       </c>
@@ -27115,7 +27123,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27126,7 +27134,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27137,7 +27145,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27148,7 +27156,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27159,7 +27167,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27170,7 +27178,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27181,7 +27189,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27198,14 +27206,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>319</v>
       </c>
@@ -27216,7 +27224,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27227,7 +27235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>23</v>
       </c>
@@ -27235,7 +27243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -27243,7 +27251,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>323</v>
       </c>
@@ -27251,7 +27259,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -27259,62 +27267,62 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>4</v>
       </c>

--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1479" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583AFAB7-813D-4950-8B47-7D6B82AD6A49}"/>
+  <xr:revisionPtr revIDLastSave="1483" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF77DD2-2785-4E36-BB7D-8E34393317E0}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-4428" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -5472,171 +5472,173 @@
       <c r="B31" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="D31" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="11" t="str">
+      <c r="F31" s="11">
         <f>IF(OR($C31="",E31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E31,FIND("-",E31)-1),"")=AW31,IFERROR(--MID(E31,FIND("-",E31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(E31,FIND("-",E31)-1),""))-(IFERROR(--MID(E31,FIND("-",E31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(E31,FIND("-",E31)-1),""))-(IFERROR(--MID(E31,FIND("-",E31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(E31,FIND("-",E31)-1),""))=(AW31))+2*((IFERROR(--MID(E31,FIND("-",E31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H31" s="11" t="str">
+      <c r="H31" s="11">
         <f>IF(OR($C31="",G31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G31,FIND("-",G31)-1),"")=AW31,IFERROR(--MID(G31,FIND("-",G31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(G31,FIND("-",G31)-1),""))-(IFERROR(--MID(G31,FIND("-",G31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(G31,FIND("-",G31)-1),""))-(IFERROR(--MID(G31,FIND("-",G31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(G31,FIND("-",G31)-1),""))=(AW31))+2*((IFERROR(--MID(G31,FIND("-",G31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J31" s="11" t="str">
+      <c r="J31" s="11">
         <f>IF(OR($C31="",I31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I31,FIND("-",I31)-1),"")=AW31,IFERROR(--MID(I31,FIND("-",I31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(I31,FIND("-",I31)-1),""))-(IFERROR(--MID(I31,FIND("-",I31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(I31,FIND("-",I31)-1),""))-(IFERROR(--MID(I31,FIND("-",I31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(I31,FIND("-",I31)-1),""))=(AW31))+2*((IFERROR(--MID(I31,FIND("-",I31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L31" s="11" t="str">
+      <c r="L31" s="11">
         <f>IF(OR($C31="",K31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K31,FIND("-",K31)-1),"")=AW31,IFERROR(--MID(K31,FIND("-",K31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(K31,FIND("-",K31)-1),""))-(IFERROR(--MID(K31,FIND("-",K31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(K31,FIND("-",K31)-1),""))-(IFERROR(--MID(K31,FIND("-",K31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(K31,FIND("-",K31)-1),""))=(AW31))+2*((IFERROR(--MID(K31,FIND("-",K31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N31" s="11" t="str">
+      <c r="N31" s="11">
         <f>IF(OR($C31="",M31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M31,FIND("-",M31)-1),"")=AW31,IFERROR(--MID(M31,FIND("-",M31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(M31,FIND("-",M31)-1),""))-(IFERROR(--MID(M31,FIND("-",M31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(M31,FIND("-",M31)-1),""))-(IFERROR(--MID(M31,FIND("-",M31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(M31,FIND("-",M31)-1),""))=(AW31))+2*((IFERROR(--MID(M31,FIND("-",M31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P31" s="11" t="str">
+      <c r="P31" s="11">
         <f>IF(OR($C31="",O31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O31,FIND("-",O31)-1),"")=AW31,IFERROR(--MID(O31,FIND("-",O31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(O31,FIND("-",O31)-1),""))-(IFERROR(--MID(O31,FIND("-",O31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(O31,FIND("-",O31)-1),""))-(IFERROR(--MID(O31,FIND("-",O31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(O31,FIND("-",O31)-1),""))=(AW31))+2*((IFERROR(--MID(O31,FIND("-",O31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q31" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R31" s="11" t="str">
+      <c r="R31" s="11">
         <f>IF(OR($C31="",Q31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q31,FIND("-",Q31)-1),"")=AW31,IFERROR(--MID(Q31,FIND("-",Q31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(Q31,FIND("-",Q31)-1),""))-(IFERROR(--MID(Q31,FIND("-",Q31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(Q31,FIND("-",Q31)-1),""))-(IFERROR(--MID(Q31,FIND("-",Q31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(Q31,FIND("-",Q31)-1),""))=(AW31))+2*((IFERROR(--MID(Q31,FIND("-",Q31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T31" s="11" t="str">
+      <c r="T31" s="11">
         <f>IF(OR($C31="",S31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S31,FIND("-",S31)-1),"")=AW31,IFERROR(--MID(S31,FIND("-",S31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(S31,FIND("-",S31)-1),""))-(IFERROR(--MID(S31,FIND("-",S31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(S31,FIND("-",S31)-1),""))-(IFERROR(--MID(S31,FIND("-",S31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(S31,FIND("-",S31)-1),""))=(AW31))+2*((IFERROR(--MID(S31,FIND("-",S31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="U31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V31" s="11" t="str">
+      <c r="V31" s="11">
         <f>IF(OR($C31="",U31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U31,FIND("-",U31)-1),"")=AW31,IFERROR(--MID(U31,FIND("-",U31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(U31,FIND("-",U31)-1),""))-(IFERROR(--MID(U31,FIND("-",U31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(U31,FIND("-",U31)-1),""))-(IFERROR(--MID(U31,FIND("-",U31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(U31,FIND("-",U31)-1),""))=(AW31))+2*((IFERROR(--MID(U31,FIND("-",U31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X31" s="11" t="str">
+      <c r="X31" s="11">
         <f>IF(OR($C31="",W31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W31,FIND("-",W31)-1),"")=AW31,IFERROR(--MID(W31,FIND("-",W31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(W31,FIND("-",W31)-1),""))-(IFERROR(--MID(W31,FIND("-",W31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(W31,FIND("-",W31)-1),""))-(IFERROR(--MID(W31,FIND("-",W31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(W31,FIND("-",W31)-1),""))=(AW31))+2*((IFERROR(--MID(W31,FIND("-",W31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z31" s="11" t="str">
+      <c r="Z31" s="11">
         <f>IF(OR($C31="",Y31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y31,FIND("-",Y31)-1),"")=AW31,IFERROR(--MID(Y31,FIND("-",Y31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(Y31,FIND("-",Y31)-1),""))-(IFERROR(--MID(Y31,FIND("-",Y31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(Y31,FIND("-",Y31)-1),""))-(IFERROR(--MID(Y31,FIND("-",Y31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(Y31,FIND("-",Y31)-1),""))=(AW31))+2*((IFERROR(--MID(Y31,FIND("-",Y31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AB31" s="11" t="str">
+      <c r="AB31" s="11">
         <f>IF(OR($C31="",AA31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA31,FIND("-",AA31)-1),"")=AW31,IFERROR(--MID(AA31,FIND("-",AA31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AA31,FIND("-",AA31)-1),""))-(IFERROR(--MID(AA31,FIND("-",AA31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AA31,FIND("-",AA31)-1),""))-(IFERROR(--MID(AA31,FIND("-",AA31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AA31,FIND("-",AA31)-1),""))=(AW31))+2*((IFERROR(--MID(AA31,FIND("-",AA31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC31" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="AD31" s="11" t="str">
+      <c r="AD31" s="11">
         <f>IF(OR($C31="",AC31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC31,FIND("-",AC31)-1),"")=AW31,IFERROR(--MID(AC31,FIND("-",AC31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AC31,FIND("-",AC31)-1),""))-(IFERROR(--MID(AC31,FIND("-",AC31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AC31,FIND("-",AC31)-1),""))-(IFERROR(--MID(AC31,FIND("-",AC31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AC31,FIND("-",AC31)-1),""))=(AW31))+2*((IFERROR(--MID(AC31,FIND("-",AC31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AF31" s="11" t="str">
+      <c r="AF31" s="11">
         <f>IF(OR($C31="",AE31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE31,FIND("-",AE31)-1),"")=AW31,IFERROR(--MID(AE31,FIND("-",AE31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AE31,FIND("-",AE31)-1),""))-(IFERROR(--MID(AE31,FIND("-",AE31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AE31,FIND("-",AE31)-1),""))-(IFERROR(--MID(AE31,FIND("-",AE31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AE31,FIND("-",AE31)-1),""))=(AW31))+2*((IFERROR(--MID(AE31,FIND("-",AE31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AH31" s="11" t="str">
+      <c r="AH31" s="11">
         <f>IF(OR($C31="",AG31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG31,FIND("-",AG31)-1),"")=AW31,IFERROR(--MID(AG31,FIND("-",AG31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AG31,FIND("-",AG31)-1),""))-(IFERROR(--MID(AG31,FIND("-",AG31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AG31,FIND("-",AG31)-1),""))-(IFERROR(--MID(AG31,FIND("-",AG31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AG31,FIND("-",AG31)-1),""))=(AW31))+2*((IFERROR(--MID(AG31,FIND("-",AG31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI31" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ31" s="11" t="str">
+      <c r="AJ31" s="11">
         <f>IF(OR($C31="",AI31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI31,FIND("-",AI31)-1),"")=AW31,IFERROR(--MID(AI31,FIND("-",AI31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AI31,FIND("-",AI31)-1),""))-(IFERROR(--MID(AI31,FIND("-",AI31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AI31,FIND("-",AI31)-1),""))-(IFERROR(--MID(AI31,FIND("-",AI31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AI31,FIND("-",AI31)-1),""))=(AW31))+2*((IFERROR(--MID(AI31,FIND("-",AI31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AL31" s="11" t="str">
+      <c r="AL31" s="11">
         <f>IF(OR($C31="",AK31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK31,FIND("-",AK31)-1),"")=AW31,IFERROR(--MID(AK31,FIND("-",AK31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AK31,FIND("-",AK31)-1),""))-(IFERROR(--MID(AK31,FIND("-",AK31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AK31,FIND("-",AK31)-1),""))-(IFERROR(--MID(AK31,FIND("-",AK31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AK31,FIND("-",AK31)-1),""))=(AW31))+2*((IFERROR(--MID(AK31,FIND("-",AK31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AN31" s="11" t="str">
+      <c r="AN31" s="11">
         <f>IF(OR($C31="",AM31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM31,FIND("-",AM31)-1),"")=AW31,IFERROR(--MID(AM31,FIND("-",AM31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AM31,FIND("-",AM31)-1),""))-(IFERROR(--MID(AM31,FIND("-",AM31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AM31,FIND("-",AM31)-1),""))-(IFERROR(--MID(AM31,FIND("-",AM31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AM31,FIND("-",AM31)-1),""))=(AW31))+2*((IFERROR(--MID(AM31,FIND("-",AM31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AP31" s="11" t="str">
+      <c r="AP31" s="11">
         <f>IF(OR($C31="",AO31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO31,FIND("-",AO31)-1),"")=AW31,IFERROR(--MID(AO31,FIND("-",AO31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AO31,FIND("-",AO31)-1),""))-(IFERROR(--MID(AO31,FIND("-",AO31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AO31,FIND("-",AO31)-1),""))-(IFERROR(--MID(AO31,FIND("-",AO31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AO31,FIND("-",AO31)-1),""))=(AW31))+2*((IFERROR(--MID(AO31,FIND("-",AO31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ31" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AR31" s="11" t="str">
+      <c r="AR31" s="11">
         <f>IF(OR($C31="",AQ31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ31,FIND("-",AQ31)-1),"")=AW31,IFERROR(--MID(AQ31,FIND("-",AQ31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AQ31,FIND("-",AQ31)-1),""))-(IFERROR(--MID(AQ31,FIND("-",AQ31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AQ31,FIND("-",AQ31)-1),""))-(IFERROR(--MID(AQ31,FIND("-",AQ31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AQ31,FIND("-",AQ31)-1),""))=(AW31))+2*((IFERROR(--MID(AQ31,FIND("-",AQ31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT31" s="11" t="str">
+      <c r="AT31" s="11">
         <f>IF(OR($C31="",AS31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS31,FIND("-",AS31)-1),"")=AW31,IFERROR(--MID(AS31,FIND("-",AS31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AS31,FIND("-",AS31)-1),""))-(IFERROR(--MID(AS31,FIND("-",AS31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AS31,FIND("-",AS31)-1),""))-(IFERROR(--MID(AS31,FIND("-",AS31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AS31,FIND("-",AS31)-1),""))=(AW31))+2*((IFERROR(--MID(AS31,FIND("-",AS31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV31" s="11" t="str">
+      <c r="AV31" s="11">
         <f>IF(OR($C31="",AU31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU31,FIND("-",AU31)-1),"")=AW31,IFERROR(--MID(AU31,FIND("-",AU31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AU31,FIND("-",AU31)-1),""))-(IFERROR(--MID(AU31,FIND("-",AU31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AU31,FIND("-",AU31)-1),""))-(IFERROR(--MID(AU31,FIND("-",AU31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AU31,FIND("-",AU31)-1),""))=(AW31))+2*((IFERROR(--MID(AU31,FIND("-",AU31)+1,99),""))=(AX31))),""))</f>
-        <v/>
-      </c>
-      <c r="AW31" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW31" s="11">
         <f>IF($C31="","",IFERROR(--LEFT($C31,FIND("-",$C31)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX31" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX31" s="11">
         <f>IF($C31="","",IFERROR(--MID($C31,FIND("-",$C31)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5758,171 +5760,173 @@
       <c r="B34" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="10"/>
+      <c r="C34" s="10" t="s">
+        <v>115</v>
+      </c>
       <c r="D34" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="11" t="str">
+      <c r="F34" s="11">
         <f>IF(OR($C34="",E34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E34,FIND("-",E34)-1),"")=AW34,IFERROR(--MID(E34,FIND("-",E34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(E34,FIND("-",E34)-1),""))-(IFERROR(--MID(E34,FIND("-",E34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(E34,FIND("-",E34)-1),""))-(IFERROR(--MID(E34,FIND("-",E34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(E34,FIND("-",E34)-1),""))=(AW34))+2*((IFERROR(--MID(E34,FIND("-",E34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="11" t="str">
+      <c r="H34" s="11">
         <f>IF(OR($C34="",G34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G34,FIND("-",G34)-1),"")=AW34,IFERROR(--MID(G34,FIND("-",G34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(G34,FIND("-",G34)-1),""))-(IFERROR(--MID(G34,FIND("-",G34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(G34,FIND("-",G34)-1),""))-(IFERROR(--MID(G34,FIND("-",G34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(G34,FIND("-",G34)-1),""))=(AW34))+2*((IFERROR(--MID(G34,FIND("-",G34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J34" s="11" t="str">
+      <c r="J34" s="11">
         <f>IF(OR($C34="",I34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I34,FIND("-",I34)-1),"")=AW34,IFERROR(--MID(I34,FIND("-",I34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(I34,FIND("-",I34)-1),""))-(IFERROR(--MID(I34,FIND("-",I34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(I34,FIND("-",I34)-1),""))-(IFERROR(--MID(I34,FIND("-",I34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(I34,FIND("-",I34)-1),""))=(AW34))+2*((IFERROR(--MID(I34,FIND("-",I34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="L34" s="11" t="str">
+      <c r="L34" s="11">
         <f>IF(OR($C34="",K34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K34,FIND("-",K34)-1),"")=AW34,IFERROR(--MID(K34,FIND("-",K34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(K34,FIND("-",K34)-1),""))-(IFERROR(--MID(K34,FIND("-",K34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(K34,FIND("-",K34)-1),""))-(IFERROR(--MID(K34,FIND("-",K34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(K34,FIND("-",K34)-1),""))=(AW34))+2*((IFERROR(--MID(K34,FIND("-",K34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="N34" s="11" t="str">
+      <c r="N34" s="11">
         <f>IF(OR($C34="",M34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M34,FIND("-",M34)-1),"")=AW34,IFERROR(--MID(M34,FIND("-",M34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(M34,FIND("-",M34)-1),""))-(IFERROR(--MID(M34,FIND("-",M34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(M34,FIND("-",M34)-1),""))-(IFERROR(--MID(M34,FIND("-",M34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(M34,FIND("-",M34)-1),""))=(AW34))+2*((IFERROR(--MID(M34,FIND("-",M34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O34" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="P34" s="11" t="str">
+      <c r="P34" s="11">
         <f>IF(OR($C34="",O34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O34,FIND("-",O34)-1),"")=AW34,IFERROR(--MID(O34,FIND("-",O34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(O34,FIND("-",O34)-1),""))-(IFERROR(--MID(O34,FIND("-",O34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(O34,FIND("-",O34)-1),""))-(IFERROR(--MID(O34,FIND("-",O34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(O34,FIND("-",O34)-1),""))=(AW34))+2*((IFERROR(--MID(O34,FIND("-",O34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="R34" s="11" t="str">
+      <c r="R34" s="11">
         <f>IF(OR($C34="",Q34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q34,FIND("-",Q34)-1),"")=AW34,IFERROR(--MID(Q34,FIND("-",Q34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(Q34,FIND("-",Q34)-1),""))-(IFERROR(--MID(Q34,FIND("-",Q34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(Q34,FIND("-",Q34)-1),""))-(IFERROR(--MID(Q34,FIND("-",Q34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(Q34,FIND("-",Q34)-1),""))=(AW34))+2*((IFERROR(--MID(Q34,FIND("-",Q34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S34" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T34" s="11" t="str">
+      <c r="T34" s="11">
         <f>IF(OR($C34="",S34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S34,FIND("-",S34)-1),"")=AW34,IFERROR(--MID(S34,FIND("-",S34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(S34,FIND("-",S34)-1),""))-(IFERROR(--MID(S34,FIND("-",S34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(S34,FIND("-",S34)-1),""))-(IFERROR(--MID(S34,FIND("-",S34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(S34,FIND("-",S34)-1),""))=(AW34))+2*((IFERROR(--MID(S34,FIND("-",S34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V34" s="11" t="str">
+      <c r="V34" s="11">
         <f>IF(OR($C34="",U34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U34,FIND("-",U34)-1),"")=AW34,IFERROR(--MID(U34,FIND("-",U34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(U34,FIND("-",U34)-1),""))-(IFERROR(--MID(U34,FIND("-",U34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(U34,FIND("-",U34)-1),""))-(IFERROR(--MID(U34,FIND("-",U34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(U34,FIND("-",U34)-1),""))=(AW34))+2*((IFERROR(--MID(U34,FIND("-",U34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="W34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X34" s="11" t="str">
+      <c r="X34" s="11">
         <f>IF(OR($C34="",W34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W34,FIND("-",W34)-1),"")=AW34,IFERROR(--MID(W34,FIND("-",W34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(W34,FIND("-",W34)-1),""))-(IFERROR(--MID(W34,FIND("-",W34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(W34,FIND("-",W34)-1),""))-(IFERROR(--MID(W34,FIND("-",W34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(W34,FIND("-",W34)-1),""))=(AW34))+2*((IFERROR(--MID(W34,FIND("-",W34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z34" s="11" t="str">
+      <c r="Z34" s="11">
         <f>IF(OR($C34="",Y34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y34,FIND("-",Y34)-1),"")=AW34,IFERROR(--MID(Y34,FIND("-",Y34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(Y34,FIND("-",Y34)-1),""))-(IFERROR(--MID(Y34,FIND("-",Y34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(Y34,FIND("-",Y34)-1),""))-(IFERROR(--MID(Y34,FIND("-",Y34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(Y34,FIND("-",Y34)-1),""))=(AW34))+2*((IFERROR(--MID(Y34,FIND("-",Y34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AB34" s="11" t="str">
+      <c r="AB34" s="11">
         <f>IF(OR($C34="",AA34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA34,FIND("-",AA34)-1),"")=AW34,IFERROR(--MID(AA34,FIND("-",AA34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AA34,FIND("-",AA34)-1),""))-(IFERROR(--MID(AA34,FIND("-",AA34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AA34,FIND("-",AA34)-1),""))-(IFERROR(--MID(AA34,FIND("-",AA34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AA34,FIND("-",AA34)-1),""))=(AW34))+2*((IFERROR(--MID(AA34,FIND("-",AA34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC34" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AD34" s="11" t="str">
+      <c r="AD34" s="11">
         <f>IF(OR($C34="",AC34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC34,FIND("-",AC34)-1),"")=AW34,IFERROR(--MID(AC34,FIND("-",AC34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AC34,FIND("-",AC34)-1),""))-(IFERROR(--MID(AC34,FIND("-",AC34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AC34,FIND("-",AC34)-1),""))-(IFERROR(--MID(AC34,FIND("-",AC34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AC34,FIND("-",AC34)-1),""))=(AW34))+2*((IFERROR(--MID(AC34,FIND("-",AC34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE34" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AF34" s="11" t="str">
+      <c r="AF34" s="11">
         <f>IF(OR($C34="",AE34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE34,FIND("-",AE34)-1),"")=AW34,IFERROR(--MID(AE34,FIND("-",AE34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AE34,FIND("-",AE34)-1),""))-(IFERROR(--MID(AE34,FIND("-",AE34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AE34,FIND("-",AE34)-1),""))-(IFERROR(--MID(AE34,FIND("-",AE34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AE34,FIND("-",AE34)-1),""))=(AW34))+2*((IFERROR(--MID(AE34,FIND("-",AE34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AG34" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH34" s="11" t="str">
+      <c r="AH34" s="11">
         <f>IF(OR($C34="",AG34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG34,FIND("-",AG34)-1),"")=AW34,IFERROR(--MID(AG34,FIND("-",AG34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AG34,FIND("-",AG34)-1),""))-(IFERROR(--MID(AG34,FIND("-",AG34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AG34,FIND("-",AG34)-1),""))-(IFERROR(--MID(AG34,FIND("-",AG34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AG34,FIND("-",AG34)-1),""))=(AW34))+2*((IFERROR(--MID(AG34,FIND("-",AG34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AJ34" s="11" t="str">
+      <c r="AJ34" s="11">
         <f>IF(OR($C34="",AI34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI34,FIND("-",AI34)-1),"")=AW34,IFERROR(--MID(AI34,FIND("-",AI34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AI34,FIND("-",AI34)-1),""))-(IFERROR(--MID(AI34,FIND("-",AI34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AI34,FIND("-",AI34)-1),""))-(IFERROR(--MID(AI34,FIND("-",AI34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AI34,FIND("-",AI34)-1),""))=(AW34))+2*((IFERROR(--MID(AI34,FIND("-",AI34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AL34" s="11" t="str">
+      <c r="AL34" s="11">
         <f>IF(OR($C34="",AK34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK34,FIND("-",AK34)-1),"")=AW34,IFERROR(--MID(AK34,FIND("-",AK34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AK34,FIND("-",AK34)-1),""))-(IFERROR(--MID(AK34,FIND("-",AK34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AK34,FIND("-",AK34)-1),""))-(IFERROR(--MID(AK34,FIND("-",AK34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AK34,FIND("-",AK34)-1),""))=(AW34))+2*((IFERROR(--MID(AK34,FIND("-",AK34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN34" s="11" t="str">
+      <c r="AN34" s="11">
         <f>IF(OR($C34="",AM34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM34,FIND("-",AM34)-1),"")=AW34,IFERROR(--MID(AM34,FIND("-",AM34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AM34,FIND("-",AM34)-1),""))-(IFERROR(--MID(AM34,FIND("-",AM34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AM34,FIND("-",AM34)-1),""))-(IFERROR(--MID(AM34,FIND("-",AM34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AM34,FIND("-",AM34)-1),""))=(AW34))+2*((IFERROR(--MID(AM34,FIND("-",AM34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO34" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP34" s="11" t="str">
+      <c r="AP34" s="11">
         <f>IF(OR($C34="",AO34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO34,FIND("-",AO34)-1),"")=AW34,IFERROR(--MID(AO34,FIND("-",AO34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AO34,FIND("-",AO34)-1),""))-(IFERROR(--MID(AO34,FIND("-",AO34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AO34,FIND("-",AO34)-1),""))-(IFERROR(--MID(AO34,FIND("-",AO34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AO34,FIND("-",AO34)-1),""))=(AW34))+2*((IFERROR(--MID(AO34,FIND("-",AO34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ34" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR34" s="11" t="str">
+      <c r="AR34" s="11">
         <f t="shared" ref="AR34:AR39" si="2">IF(OR($C34="",AQ34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ34,FIND("-",AQ34)-1),"")=AW34,IFERROR(--MID(AQ34,FIND("-",AQ34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AQ34,FIND("-",AQ34)-1),""))-(IFERROR(--MID(AQ34,FIND("-",AQ34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AQ34,FIND("-",AQ34)-1),""))-(IFERROR(--MID(AQ34,FIND("-",AQ34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AQ34,FIND("-",AQ34)-1),""))=(AW34))+2*((IFERROR(--MID(AQ34,FIND("-",AQ34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AT34" s="11" t="str">
+      <c r="AT34" s="11">
         <f t="shared" ref="AT34:AT39" si="3">IF(OR($C34="",AS34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS34,FIND("-",AS34)-1),"")=AW34,IFERROR(--MID(AS34,FIND("-",AS34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AS34,FIND("-",AS34)-1),""))-(IFERROR(--MID(AS34,FIND("-",AS34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AS34,FIND("-",AS34)-1),""))-(IFERROR(--MID(AS34,FIND("-",AS34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AS34,FIND("-",AS34)-1),""))=(AW34))+2*((IFERROR(--MID(AS34,FIND("-",AS34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU34" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV34" s="11" t="str">
+      <c r="AV34" s="11">
         <f>IF(OR($C34="",AU34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU34,FIND("-",AU34)-1),"")=AW34,IFERROR(--MID(AU34,FIND("-",AU34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AU34,FIND("-",AU34)-1),""))-(IFERROR(--MID(AU34,FIND("-",AU34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AU34,FIND("-",AU34)-1),""))-(IFERROR(--MID(AU34,FIND("-",AU34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AU34,FIND("-",AU34)-1),""))=(AW34))+2*((IFERROR(--MID(AU34,FIND("-",AU34)+1,99),""))=(AX34))),""))</f>
-        <v/>
-      </c>
-      <c r="AW34" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW34" s="11">
         <f>IF($C34="","",IFERROR(--LEFT($C34,FIND("-",$C34)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX34" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX34" s="11">
         <f>IF($C34="","",IFERROR(--MID($C34,FIND("-",$C34)+1,99),""))</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5932,171 +5936,173 @@
       <c r="B35" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="D35" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F35" s="11" t="str">
+      <c r="F35" s="11">
         <f>IF(OR($C35="",E35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E35,FIND("-",E35)-1),"")=AW35,IFERROR(--MID(E35,FIND("-",E35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(E35,FIND("-",E35)-1),""))-(IFERROR(--MID(E35,FIND("-",E35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(E35,FIND("-",E35)-1),""))-(IFERROR(--MID(E35,FIND("-",E35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(E35,FIND("-",E35)-1),""))=(AW35))+2*((IFERROR(--MID(E35,FIND("-",E35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H35" s="11" t="str">
+      <c r="H35" s="11">
         <f>IF(OR($C35="",G35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G35,FIND("-",G35)-1),"")=AW35,IFERROR(--MID(G35,FIND("-",G35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(G35,FIND("-",G35)-1),""))-(IFERROR(--MID(G35,FIND("-",G35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(G35,FIND("-",G35)-1),""))-(IFERROR(--MID(G35,FIND("-",G35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(G35,FIND("-",G35)-1),""))=(AW35))+2*((IFERROR(--MID(G35,FIND("-",G35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J35" s="11" t="str">
+      <c r="J35" s="11">
         <f>IF(OR($C35="",I35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I35,FIND("-",I35)-1),"")=AW35,IFERROR(--MID(I35,FIND("-",I35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(I35,FIND("-",I35)-1),""))-(IFERROR(--MID(I35,FIND("-",I35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(I35,FIND("-",I35)-1),""))-(IFERROR(--MID(I35,FIND("-",I35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(I35,FIND("-",I35)-1),""))=(AW35))+2*((IFERROR(--MID(I35,FIND("-",I35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L35" s="11" t="str">
+      <c r="L35" s="11">
         <f>IF(OR($C35="",K35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K35,FIND("-",K35)-1),"")=AW35,IFERROR(--MID(K35,FIND("-",K35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(K35,FIND("-",K35)-1),""))-(IFERROR(--MID(K35,FIND("-",K35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(K35,FIND("-",K35)-1),""))-(IFERROR(--MID(K35,FIND("-",K35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(K35,FIND("-",K35)-1),""))=(AW35))+2*((IFERROR(--MID(K35,FIND("-",K35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="N35" s="11" t="str">
+      <c r="N35" s="11">
         <f>IF(OR($C35="",M35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M35,FIND("-",M35)-1),"")=AW35,IFERROR(--MID(M35,FIND("-",M35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(M35,FIND("-",M35)-1),""))-(IFERROR(--MID(M35,FIND("-",M35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(M35,FIND("-",M35)-1),""))-(IFERROR(--MID(M35,FIND("-",M35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(M35,FIND("-",M35)-1),""))=(AW35))+2*((IFERROR(--MID(M35,FIND("-",M35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P35" s="11" t="str">
+      <c r="P35" s="11">
         <f>IF(OR($C35="",O35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O35,FIND("-",O35)-1),"")=AW35,IFERROR(--MID(O35,FIND("-",O35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(O35,FIND("-",O35)-1),""))-(IFERROR(--MID(O35,FIND("-",O35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(O35,FIND("-",O35)-1),""))-(IFERROR(--MID(O35,FIND("-",O35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(O35,FIND("-",O35)-1),""))=(AW35))+2*((IFERROR(--MID(O35,FIND("-",O35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="R35" s="11" t="str">
+      <c r="R35" s="11">
         <f>IF(OR($C35="",Q35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q35,FIND("-",Q35)-1),"")=AW35,IFERROR(--MID(Q35,FIND("-",Q35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(Q35,FIND("-",Q35)-1),""))-(IFERROR(--MID(Q35,FIND("-",Q35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(Q35,FIND("-",Q35)-1),""))-(IFERROR(--MID(Q35,FIND("-",Q35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(Q35,FIND("-",Q35)-1),""))=(AW35))+2*((IFERROR(--MID(Q35,FIND("-",Q35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S35" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T35" s="11" t="str">
+      <c r="T35" s="11">
         <f>IF(OR($C35="",S35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S35,FIND("-",S35)-1),"")=AW35,IFERROR(--MID(S35,FIND("-",S35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(S35,FIND("-",S35)-1),""))-(IFERROR(--MID(S35,FIND("-",S35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(S35,FIND("-",S35)-1),""))-(IFERROR(--MID(S35,FIND("-",S35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(S35,FIND("-",S35)-1),""))=(AW35))+2*((IFERROR(--MID(S35,FIND("-",S35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V35" s="11" t="str">
+      <c r="V35" s="11">
         <f>IF(OR($C35="",U35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U35,FIND("-",U35)-1),"")=AW35,IFERROR(--MID(U35,FIND("-",U35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(U35,FIND("-",U35)-1),""))-(IFERROR(--MID(U35,FIND("-",U35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(U35,FIND("-",U35)-1),""))-(IFERROR(--MID(U35,FIND("-",U35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(U35,FIND("-",U35)-1),""))=(AW35))+2*((IFERROR(--MID(U35,FIND("-",U35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X35" s="11" t="str">
+      <c r="X35" s="11">
         <f>IF(OR($C35="",W35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W35,FIND("-",W35)-1),"")=AW35,IFERROR(--MID(W35,FIND("-",W35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(W35,FIND("-",W35)-1),""))-(IFERROR(--MID(W35,FIND("-",W35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(W35,FIND("-",W35)-1),""))-(IFERROR(--MID(W35,FIND("-",W35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(W35,FIND("-",W35)-1),""))=(AW35))+2*((IFERROR(--MID(W35,FIND("-",W35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z35" s="11" t="str">
+      <c r="Z35" s="11">
         <f>IF(OR($C35="",Y35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y35,FIND("-",Y35)-1),"")=AW35,IFERROR(--MID(Y35,FIND("-",Y35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(Y35,FIND("-",Y35)-1),""))-(IFERROR(--MID(Y35,FIND("-",Y35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(Y35,FIND("-",Y35)-1),""))-(IFERROR(--MID(Y35,FIND("-",Y35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(Y35,FIND("-",Y35)-1),""))=(AW35))+2*((IFERROR(--MID(Y35,FIND("-",Y35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB35" s="11" t="str">
+      <c r="AB35" s="11">
         <f>IF(OR($C35="",AA35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA35,FIND("-",AA35)-1),"")=AW35,IFERROR(--MID(AA35,FIND("-",AA35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AA35,FIND("-",AA35)-1),""))-(IFERROR(--MID(AA35,FIND("-",AA35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AA35,FIND("-",AA35)-1),""))-(IFERROR(--MID(AA35,FIND("-",AA35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AA35,FIND("-",AA35)-1),""))=(AW35))+2*((IFERROR(--MID(AA35,FIND("-",AA35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD35" s="11" t="str">
+      <c r="AD35" s="11">
         <f>IF(OR($C35="",AC35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC35,FIND("-",AC35)-1),"")=AW35,IFERROR(--MID(AC35,FIND("-",AC35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AC35,FIND("-",AC35)-1),""))-(IFERROR(--MID(AC35,FIND("-",AC35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AC35,FIND("-",AC35)-1),""))-(IFERROR(--MID(AC35,FIND("-",AC35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AC35,FIND("-",AC35)-1),""))=(AW35))+2*((IFERROR(--MID(AC35,FIND("-",AC35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF35" s="11" t="str">
+      <c r="AF35" s="11">
         <f>IF(OR($C35="",AE35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE35,FIND("-",AE35)-1),"")=AW35,IFERROR(--MID(AE35,FIND("-",AE35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AE35,FIND("-",AE35)-1),""))-(IFERROR(--MID(AE35,FIND("-",AE35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AE35,FIND("-",AE35)-1),""))-(IFERROR(--MID(AE35,FIND("-",AE35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AE35,FIND("-",AE35)-1),""))=(AW35))+2*((IFERROR(--MID(AE35,FIND("-",AE35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AH35" s="11" t="str">
+      <c r="AH35" s="11">
         <f>IF(OR($C35="",AG35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG35,FIND("-",AG35)-1),"")=AW35,IFERROR(--MID(AG35,FIND("-",AG35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AG35,FIND("-",AG35)-1),""))-(IFERROR(--MID(AG35,FIND("-",AG35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AG35,FIND("-",AG35)-1),""))-(IFERROR(--MID(AG35,FIND("-",AG35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AG35,FIND("-",AG35)-1),""))=(AW35))+2*((IFERROR(--MID(AG35,FIND("-",AG35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AJ35" s="11" t="str">
+      <c r="AJ35" s="11">
         <f>IF(OR($C35="",AI35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI35,FIND("-",AI35)-1),"")=AW35,IFERROR(--MID(AI35,FIND("-",AI35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AI35,FIND("-",AI35)-1),""))-(IFERROR(--MID(AI35,FIND("-",AI35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AI35,FIND("-",AI35)-1),""))-(IFERROR(--MID(AI35,FIND("-",AI35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AI35,FIND("-",AI35)-1),""))=(AW35))+2*((IFERROR(--MID(AI35,FIND("-",AI35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL35" s="11" t="str">
+      <c r="AL35" s="11">
         <f>IF(OR($C35="",AK35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK35,FIND("-",AK35)-1),"")=AW35,IFERROR(--MID(AK35,FIND("-",AK35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AK35,FIND("-",AK35)-1),""))-(IFERROR(--MID(AK35,FIND("-",AK35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AK35,FIND("-",AK35)-1),""))-(IFERROR(--MID(AK35,FIND("-",AK35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AK35,FIND("-",AK35)-1),""))=(AW35))+2*((IFERROR(--MID(AK35,FIND("-",AK35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM35" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN35" s="11" t="str">
+      <c r="AN35" s="11">
         <f>IF(OR($C35="",AM35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM35,FIND("-",AM35)-1),"")=AW35,IFERROR(--MID(AM35,FIND("-",AM35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AM35,FIND("-",AM35)-1),""))-(IFERROR(--MID(AM35,FIND("-",AM35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AM35,FIND("-",AM35)-1),""))-(IFERROR(--MID(AM35,FIND("-",AM35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AM35,FIND("-",AM35)-1),""))=(AW35))+2*((IFERROR(--MID(AM35,FIND("-",AM35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AP35" s="11" t="str">
+      <c r="AP35" s="11">
         <f>IF(OR($C35="",AO35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO35,FIND("-",AO35)-1),"")=AW35,IFERROR(--MID(AO35,FIND("-",AO35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AO35,FIND("-",AO35)-1),""))-(IFERROR(--MID(AO35,FIND("-",AO35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AO35,FIND("-",AO35)-1),""))-(IFERROR(--MID(AO35,FIND("-",AO35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AO35,FIND("-",AO35)-1),""))=(AW35))+2*((IFERROR(--MID(AO35,FIND("-",AO35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR35" s="11" t="str">
+      <c r="AR35" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS35" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT35" s="11" t="str">
+      <c r="AT35" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV35" s="11" t="str">
+      <c r="AV35" s="11">
         <f>IF(OR($C35="",AU35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU35,FIND("-",AU35)-1),"")=AW35,IFERROR(--MID(AU35,FIND("-",AU35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AU35,FIND("-",AU35)-1),""))-(IFERROR(--MID(AU35,FIND("-",AU35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AU35,FIND("-",AU35)-1),""))-(IFERROR(--MID(AU35,FIND("-",AU35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AU35,FIND("-",AU35)-1),""))=(AW35))+2*((IFERROR(--MID(AU35,FIND("-",AU35)+1,99),""))=(AX35))),""))</f>
-        <v/>
-      </c>
-      <c r="AW35" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW35" s="11">
         <f>IF($C35="","",IFERROR(--LEFT($C35,FIND("-",$C35)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX35" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX35" s="11">
         <f>IF($C35="","",IFERROR(--MID($C35,FIND("-",$C35)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26490,20 +26496,20 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
       </c>
       <c r="C3" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>66</v>
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>89</v>
       </c>
       <c r="D3" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26512,20 +26518,20 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>65</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>85</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26534,20 +26540,20 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>58</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>81</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26561,7 +26567,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!I17</f>
@@ -26569,29 +26575,29 @@
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>57</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>77</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26600,86 +26606,86 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>56</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>76</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>55</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>76</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>55</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>55</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>74</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>53</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>74</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26688,20 +26694,20 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>52</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>72</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26710,64 +26716,64 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>51</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>71</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>51</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>70</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>50</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>70</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26776,26 +26782,26 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>49</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>69</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -26803,7 +26809,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -26811,13 +26817,13 @@
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -26825,7 +26831,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -26833,7 +26839,7 @@
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26842,20 +26848,20 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>47</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>66</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26869,7 +26875,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26877,13 +26883,13 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -26891,7 +26897,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26899,7 +26905,7 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26913,7 +26919,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -26921,7 +26927,7 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -26935,7 +26941,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26943,7 +26949,7 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -26957,7 +26963,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26965,7 +26971,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -27577,16 +27583,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
     <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1483" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF77DD2-2785-4E36-BB7D-8E34393317E0}"/>
+  <xr:revisionPtr revIDLastSave="1496" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A299896-DD91-4E2C-944A-706BE07FE8AB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -6112,171 +6112,173 @@
       <c r="B36" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="D36" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F36" s="11" t="str">
+      <c r="F36" s="11">
         <f>IF(OR($C36="",E36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E36,FIND("-",E36)-1),"")=AW36,IFERROR(--MID(E36,FIND("-",E36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(E36,FIND("-",E36)-1),""))-(IFERROR(--MID(E36,FIND("-",E36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(E36,FIND("-",E36)-1),""))-(IFERROR(--MID(E36,FIND("-",E36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(E36,FIND("-",E36)-1),""))=(AW36))+2*((IFERROR(--MID(E36,FIND("-",E36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H36" s="11" t="str">
+      <c r="H36" s="11">
         <f>IF(OR($C36="",G36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G36,FIND("-",G36)-1),"")=AW36,IFERROR(--MID(G36,FIND("-",G36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(G36,FIND("-",G36)-1),""))-(IFERROR(--MID(G36,FIND("-",G36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(G36,FIND("-",G36)-1),""))-(IFERROR(--MID(G36,FIND("-",G36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(G36,FIND("-",G36)-1),""))=(AW36))+2*((IFERROR(--MID(G36,FIND("-",G36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J36" s="11" t="str">
+      <c r="J36" s="11">
         <f>IF(OR($C36="",I36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I36,FIND("-",I36)-1),"")=AW36,IFERROR(--MID(I36,FIND("-",I36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(I36,FIND("-",I36)-1),""))-(IFERROR(--MID(I36,FIND("-",I36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(I36,FIND("-",I36)-1),""))-(IFERROR(--MID(I36,FIND("-",I36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(I36,FIND("-",I36)-1),""))=(AW36))+2*((IFERROR(--MID(I36,FIND("-",I36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L36" s="11" t="str">
+      <c r="L36" s="11">
         <f>IF(OR($C36="",K36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K36,FIND("-",K36)-1),"")=AW36,IFERROR(--MID(K36,FIND("-",K36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(K36,FIND("-",K36)-1),""))-(IFERROR(--MID(K36,FIND("-",K36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(K36,FIND("-",K36)-1),""))-(IFERROR(--MID(K36,FIND("-",K36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(K36,FIND("-",K36)-1),""))=(AW36))+2*((IFERROR(--MID(K36,FIND("-",K36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="N36" s="11" t="str">
+      <c r="N36" s="11">
         <f>IF(OR($C36="",M36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M36,FIND("-",M36)-1),"")=AW36,IFERROR(--MID(M36,FIND("-",M36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(M36,FIND("-",M36)-1),""))-(IFERROR(--MID(M36,FIND("-",M36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(M36,FIND("-",M36)-1),""))-(IFERROR(--MID(M36,FIND("-",M36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(M36,FIND("-",M36)-1),""))=(AW36))+2*((IFERROR(--MID(M36,FIND("-",M36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P36" s="11" t="str">
+      <c r="P36" s="11">
         <f>IF(OR($C36="",O36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O36,FIND("-",O36)-1),"")=AW36,IFERROR(--MID(O36,FIND("-",O36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(O36,FIND("-",O36)-1),""))-(IFERROR(--MID(O36,FIND("-",O36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(O36,FIND("-",O36)-1),""))-(IFERROR(--MID(O36,FIND("-",O36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(O36,FIND("-",O36)-1),""))=(AW36))+2*((IFERROR(--MID(O36,FIND("-",O36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R36" s="11" t="str">
+      <c r="R36" s="11">
         <f>IF(OR($C36="",Q36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q36,FIND("-",Q36)-1),"")=AW36,IFERROR(--MID(Q36,FIND("-",Q36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(Q36,FIND("-",Q36)-1),""))-(IFERROR(--MID(Q36,FIND("-",Q36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(Q36,FIND("-",Q36)-1),""))-(IFERROR(--MID(Q36,FIND("-",Q36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(Q36,FIND("-",Q36)-1),""))=(AW36))+2*((IFERROR(--MID(Q36,FIND("-",Q36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S36" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T36" s="11" t="str">
+      <c r="T36" s="11">
         <f>IF(OR($C36="",S36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S36,FIND("-",S36)-1),"")=AW36,IFERROR(--MID(S36,FIND("-",S36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(S36,FIND("-",S36)-1),""))-(IFERROR(--MID(S36,FIND("-",S36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(S36,FIND("-",S36)-1),""))-(IFERROR(--MID(S36,FIND("-",S36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(S36,FIND("-",S36)-1),""))=(AW36))+2*((IFERROR(--MID(S36,FIND("-",S36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V36" s="11" t="str">
+      <c r="V36" s="11">
         <f>IF(OR($C36="",U36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U36,FIND("-",U36)-1),"")=AW36,IFERROR(--MID(U36,FIND("-",U36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(U36,FIND("-",U36)-1),""))-(IFERROR(--MID(U36,FIND("-",U36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(U36,FIND("-",U36)-1),""))-(IFERROR(--MID(U36,FIND("-",U36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(U36,FIND("-",U36)-1),""))=(AW36))+2*((IFERROR(--MID(U36,FIND("-",U36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X36" s="11" t="str">
+      <c r="X36" s="11">
         <f>IF(OR($C36="",W36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W36,FIND("-",W36)-1),"")=AW36,IFERROR(--MID(W36,FIND("-",W36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(W36,FIND("-",W36)-1),""))-(IFERROR(--MID(W36,FIND("-",W36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(W36,FIND("-",W36)-1),""))-(IFERROR(--MID(W36,FIND("-",W36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(W36,FIND("-",W36)-1),""))=(AW36))+2*((IFERROR(--MID(W36,FIND("-",W36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z36" s="11" t="str">
+      <c r="Z36" s="11">
         <f>IF(OR($C36="",Y36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y36,FIND("-",Y36)-1),"")=AW36,IFERROR(--MID(Y36,FIND("-",Y36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(Y36,FIND("-",Y36)-1),""))-(IFERROR(--MID(Y36,FIND("-",Y36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(Y36,FIND("-",Y36)-1),""))-(IFERROR(--MID(Y36,FIND("-",Y36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(Y36,FIND("-",Y36)-1),""))=(AW36))+2*((IFERROR(--MID(Y36,FIND("-",Y36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AB36" s="11" t="str">
+      <c r="AB36" s="11">
         <f>IF(OR($C36="",AA36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA36,FIND("-",AA36)-1),"")=AW36,IFERROR(--MID(AA36,FIND("-",AA36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AA36,FIND("-",AA36)-1),""))-(IFERROR(--MID(AA36,FIND("-",AA36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AA36,FIND("-",AA36)-1),""))-(IFERROR(--MID(AA36,FIND("-",AA36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AA36,FIND("-",AA36)-1),""))=(AW36))+2*((IFERROR(--MID(AA36,FIND("-",AA36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC36" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AD36" s="11" t="str">
+      <c r="AD36" s="11">
         <f>IF(OR($C36="",AC36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC36,FIND("-",AC36)-1),"")=AW36,IFERROR(--MID(AC36,FIND("-",AC36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AC36,FIND("-",AC36)-1),""))-(IFERROR(--MID(AC36,FIND("-",AC36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AC36,FIND("-",AC36)-1),""))-(IFERROR(--MID(AC36,FIND("-",AC36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AC36,FIND("-",AC36)-1),""))=(AW36))+2*((IFERROR(--MID(AC36,FIND("-",AC36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF36" s="11" t="str">
+      <c r="AF36" s="11">
         <f>IF(OR($C36="",AE36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE36,FIND("-",AE36)-1),"")=AW36,IFERROR(--MID(AE36,FIND("-",AE36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AE36,FIND("-",AE36)-1),""))-(IFERROR(--MID(AE36,FIND("-",AE36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AE36,FIND("-",AE36)-1),""))-(IFERROR(--MID(AE36,FIND("-",AE36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AE36,FIND("-",AE36)-1),""))=(AW36))+2*((IFERROR(--MID(AE36,FIND("-",AE36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG36" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH36" s="11" t="str">
+      <c r="AH36" s="11">
         <f>IF(OR($C36="",AG36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG36,FIND("-",AG36)-1),"")=AW36,IFERROR(--MID(AG36,FIND("-",AG36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AG36,FIND("-",AG36)-1),""))-(IFERROR(--MID(AG36,FIND("-",AG36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AG36,FIND("-",AG36)-1),""))-(IFERROR(--MID(AG36,FIND("-",AG36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AG36,FIND("-",AG36)-1),""))=(AW36))+2*((IFERROR(--MID(AG36,FIND("-",AG36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ36" s="11" t="str">
+      <c r="AJ36" s="11">
         <f>IF(OR($C36="",AI36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI36,FIND("-",AI36)-1),"")=AW36,IFERROR(--MID(AI36,FIND("-",AI36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AI36,FIND("-",AI36)-1),""))-(IFERROR(--MID(AI36,FIND("-",AI36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AI36,FIND("-",AI36)-1),""))-(IFERROR(--MID(AI36,FIND("-",AI36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AI36,FIND("-",AI36)-1),""))=(AW36))+2*((IFERROR(--MID(AI36,FIND("-",AI36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL36" s="11" t="str">
+      <c r="AL36" s="11">
         <f>IF(OR($C36="",AK36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK36,FIND("-",AK36)-1),"")=AW36,IFERROR(--MID(AK36,FIND("-",AK36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AK36,FIND("-",AK36)-1),""))-(IFERROR(--MID(AK36,FIND("-",AK36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AK36,FIND("-",AK36)-1),""))-(IFERROR(--MID(AK36,FIND("-",AK36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AK36,FIND("-",AK36)-1),""))=(AW36))+2*((IFERROR(--MID(AK36,FIND("-",AK36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN36" s="11" t="str">
+      <c r="AN36" s="11">
         <f>IF(OR($C36="",AM36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM36,FIND("-",AM36)-1),"")=AW36,IFERROR(--MID(AM36,FIND("-",AM36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AM36,FIND("-",AM36)-1),""))-(IFERROR(--MID(AM36,FIND("-",AM36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AM36,FIND("-",AM36)-1),""))-(IFERROR(--MID(AM36,FIND("-",AM36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AM36,FIND("-",AM36)-1),""))=(AW36))+2*((IFERROR(--MID(AM36,FIND("-",AM36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP36" s="11" t="str">
+      <c r="AP36" s="11">
         <f>IF(OR($C36="",AO36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO36,FIND("-",AO36)-1),"")=AW36,IFERROR(--MID(AO36,FIND("-",AO36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AO36,FIND("-",AO36)-1),""))-(IFERROR(--MID(AO36,FIND("-",AO36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AO36,FIND("-",AO36)-1),""))-(IFERROR(--MID(AO36,FIND("-",AO36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AO36,FIND("-",AO36)-1),""))=(AW36))+2*((IFERROR(--MID(AO36,FIND("-",AO36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ36" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR36" s="11" t="str">
+      <c r="AR36" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS36" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT36" s="11" t="str">
+      <c r="AT36" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AV36" s="11" t="str">
+      <c r="AV36" s="11">
         <f>IF(OR($C36="",AU36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU36,FIND("-",AU36)-1),"")=AW36,IFERROR(--MID(AU36,FIND("-",AU36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AU36,FIND("-",AU36)-1),""))-(IFERROR(--MID(AU36,FIND("-",AU36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AU36,FIND("-",AU36)-1),""))-(IFERROR(--MID(AU36,FIND("-",AU36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AU36,FIND("-",AU36)-1),""))=(AW36))+2*((IFERROR(--MID(AU36,FIND("-",AU36)+1,99),""))=(AX36))),""))</f>
-        <v/>
-      </c>
-      <c r="AW36" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW36" s="11">
         <f>IF($C36="","",IFERROR(--LEFT($C36,FIND("-",$C36)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX36" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX36" s="11">
         <f>IF($C36="","",IFERROR(--MID($C36,FIND("-",$C36)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26501,7 +26503,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26509,7 +26511,7 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26523,7 +26525,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26531,7 +26533,7 @@
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26545,7 +26547,7 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -26553,7 +26555,7 @@
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26562,42 +26564,42 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>79</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>83</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>77</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>83</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26606,86 +26608,86 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>76</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>81</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>76</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>79</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>74</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>79</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>74</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>79</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26694,42 +26696,42 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>72</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>77</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>71</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>77</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26738,20 +26740,20 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>70</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>76</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26760,20 +26762,20 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>70</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>76</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26782,64 +26784,64 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>69</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>75</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>68</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>75</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>68</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>74</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26853,7 +26855,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -26861,7 +26863,7 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26875,7 +26877,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26883,7 +26885,7 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26897,7 +26899,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26905,7 +26907,7 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26914,42 +26916,42 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>61</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>68</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>61</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>63</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -26963,7 +26965,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26971,7 +26973,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -27211,7 +27213,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -27237,41 +27239,26 @@
       <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>323</v>
       </c>
-      <c r="C5" t="s">
-        <v>324</v>
-      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -27323,14 +27310,39 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>

--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1496" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A299896-DD91-4E2C-944A-706BE07FE8AB}"/>
+  <xr:revisionPtr revIDLastSave="1500" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E84F76D5-954D-4A4C-BC71-B735888FE712}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-50" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,21 +1348,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1676,76 +1676,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.5703125" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.5703125" customWidth="1"/>
-    <col min="19" max="19" width="12.5703125" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.5703125" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" customWidth="1"/>
-    <col min="23" max="23" width="12.5703125" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" customWidth="1"/>
-    <col min="25" max="25" width="12.5703125" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="27" width="12.5703125" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.5703125" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.5703125" customWidth="1"/>
-    <col min="31" max="31" width="12.5703125" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.5703125" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.5703125" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.5703125" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.5703125" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.5703125" customWidth="1"/>
-    <col min="41" max="41" width="15.5703125" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.5703125" customWidth="1"/>
-    <col min="43" max="43" width="15.5703125" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.5703125" customWidth="1"/>
-    <col min="45" max="45" width="15.7109375" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.5703125" customWidth="1"/>
-    <col min="47" max="47" width="15.5703125" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.54296875" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.54296875" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" customWidth="1"/>
+    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.54296875" customWidth="1"/>
+    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.54296875" customWidth="1"/>
+    <col min="21" max="21" width="12.54296875" customWidth="1"/>
+    <col min="22" max="22" width="8.54296875" customWidth="1"/>
+    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.54296875" customWidth="1"/>
+    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.54296875" customWidth="1"/>
+    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.54296875" customWidth="1"/>
+    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.54296875" customWidth="1"/>
+    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.54296875" customWidth="1"/>
+    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.54296875" customWidth="1"/>
+    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.54296875" customWidth="1"/>
+    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.54296875" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.54296875" customWidth="1"/>
+    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.54296875" customWidth="1"/>
+    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.54296875" customWidth="1"/>
+    <col min="45" max="45" width="15.7265625" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.54296875" customWidth="1"/>
+    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.54296875" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="44"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="39"/>
+      <c r="AT1" s="44"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="39"/>
+      <c r="AV1" s="44"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1837,10 +1837,10 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A2" s="43"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1981,61 +1981,61 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="40"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2323,7 +2323,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2787,7 +2787,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3251,7 +3251,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4243,7 +4243,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
@@ -4297,7 +4297,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5059,7 +5059,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
@@ -5113,7 +5113,7 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5699,7 +5699,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6281,355 +6281,359 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
       <c r="B37" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D37" s="1" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="11" t="str">
+      <c r="F37" s="11">
         <f>IF(OR($C37="",E37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E37,FIND("-",E37)-1),"")=AW37,IFERROR(--MID(E37,FIND("-",E37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(E37,FIND("-",E37)-1),""))-(IFERROR(--MID(E37,FIND("-",E37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(E37,FIND("-",E37)-1),""))-(IFERROR(--MID(E37,FIND("-",E37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(E37,FIND("-",E37)-1),""))=(AW37))+2*((IFERROR(--MID(E37,FIND("-",E37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H37" s="11" t="str">
+      <c r="H37" s="11">
         <f>IF(OR($C37="",G37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G37,FIND("-",G37)-1),"")=AW37,IFERROR(--MID(G37,FIND("-",G37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(G37,FIND("-",G37)-1),""))-(IFERROR(--MID(G37,FIND("-",G37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(G37,FIND("-",G37)-1),""))-(IFERROR(--MID(G37,FIND("-",G37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(G37,FIND("-",G37)-1),""))=(AW37))+2*((IFERROR(--MID(G37,FIND("-",G37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J37" s="11" t="str">
+      <c r="J37" s="11">
         <f>IF(OR($C37="",I37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I37,FIND("-",I37)-1),"")=AW37,IFERROR(--MID(I37,FIND("-",I37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(I37,FIND("-",I37)-1),""))-(IFERROR(--MID(I37,FIND("-",I37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(I37,FIND("-",I37)-1),""))-(IFERROR(--MID(I37,FIND("-",I37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(I37,FIND("-",I37)-1),""))=(AW37))+2*((IFERROR(--MID(I37,FIND("-",I37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="11" t="str">
+      <c r="L37" s="11">
         <f>IF(OR($C37="",K37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K37,FIND("-",K37)-1),"")=AW37,IFERROR(--MID(K37,FIND("-",K37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(K37,FIND("-",K37)-1),""))-(IFERROR(--MID(K37,FIND("-",K37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(K37,FIND("-",K37)-1),""))-(IFERROR(--MID(K37,FIND("-",K37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(K37,FIND("-",K37)-1),""))=(AW37))+2*((IFERROR(--MID(K37,FIND("-",K37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N37" s="11" t="str">
+      <c r="N37" s="11">
         <f>IF(OR($C37="",M37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M37,FIND("-",M37)-1),"")=AW37,IFERROR(--MID(M37,FIND("-",M37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(M37,FIND("-",M37)-1),""))-(IFERROR(--MID(M37,FIND("-",M37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(M37,FIND("-",M37)-1),""))-(IFERROR(--MID(M37,FIND("-",M37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(M37,FIND("-",M37)-1),""))=(AW37))+2*((IFERROR(--MID(M37,FIND("-",M37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="P37" s="11" t="str">
+      <c r="P37" s="11">
         <f>IF(OR($C37="",O37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O37,FIND("-",O37)-1),"")=AW37,IFERROR(--MID(O37,FIND("-",O37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(O37,FIND("-",O37)-1),""))-(IFERROR(--MID(O37,FIND("-",O37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(O37,FIND("-",O37)-1),""))-(IFERROR(--MID(O37,FIND("-",O37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(O37,FIND("-",O37)-1),""))=(AW37))+2*((IFERROR(--MID(O37,FIND("-",O37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R37" s="11" t="str">
+      <c r="R37" s="11">
         <f>IF(OR($C37="",Q37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q37,FIND("-",Q37)-1),"")=AW37,IFERROR(--MID(Q37,FIND("-",Q37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(Q37,FIND("-",Q37)-1),""))-(IFERROR(--MID(Q37,FIND("-",Q37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(Q37,FIND("-",Q37)-1),""))-(IFERROR(--MID(Q37,FIND("-",Q37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(Q37,FIND("-",Q37)-1),""))=(AW37))+2*((IFERROR(--MID(Q37,FIND("-",Q37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T37" s="11" t="str">
+      <c r="T37" s="11">
         <f>IF(OR($C37="",S37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S37,FIND("-",S37)-1),"")=AW37,IFERROR(--MID(S37,FIND("-",S37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(S37,FIND("-",S37)-1),""))-(IFERROR(--MID(S37,FIND("-",S37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(S37,FIND("-",S37)-1),""))-(IFERROR(--MID(S37,FIND("-",S37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(S37,FIND("-",S37)-1),""))=(AW37))+2*((IFERROR(--MID(S37,FIND("-",S37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V37" s="11" t="str">
+      <c r="V37" s="11">
         <f>IF(OR($C37="",U37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U37,FIND("-",U37)-1),"")=AW37,IFERROR(--MID(U37,FIND("-",U37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(U37,FIND("-",U37)-1),""))-(IFERROR(--MID(U37,FIND("-",U37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(U37,FIND("-",U37)-1),""))-(IFERROR(--MID(U37,FIND("-",U37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(U37,FIND("-",U37)-1),""))=(AW37))+2*((IFERROR(--MID(U37,FIND("-",U37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X37" s="11" t="str">
+      <c r="X37" s="11">
         <f>IF(OR($C37="",W37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W37,FIND("-",W37)-1),"")=AW37,IFERROR(--MID(W37,FIND("-",W37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(W37,FIND("-",W37)-1),""))-(IFERROR(--MID(W37,FIND("-",W37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(W37,FIND("-",W37)-1),""))-(IFERROR(--MID(W37,FIND("-",W37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(W37,FIND("-",W37)-1),""))=(AW37))+2*((IFERROR(--MID(W37,FIND("-",W37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z37" s="11" t="str">
+      <c r="Z37" s="11">
         <f>IF(OR($C37="",Y37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y37,FIND("-",Y37)-1),"")=AW37,IFERROR(--MID(Y37,FIND("-",Y37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(Y37,FIND("-",Y37)-1),""))-(IFERROR(--MID(Y37,FIND("-",Y37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(Y37,FIND("-",Y37)-1),""))-(IFERROR(--MID(Y37,FIND("-",Y37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(Y37,FIND("-",Y37)-1),""))=(AW37))+2*((IFERROR(--MID(Y37,FIND("-",Y37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AB37" s="11" t="str">
+      <c r="AB37" s="11">
         <f>IF(OR($C37="",AA37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA37,FIND("-",AA37)-1),"")=AW37,IFERROR(--MID(AA37,FIND("-",AA37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AA37,FIND("-",AA37)-1),""))-(IFERROR(--MID(AA37,FIND("-",AA37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AA37,FIND("-",AA37)-1),""))-(IFERROR(--MID(AA37,FIND("-",AA37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AA37,FIND("-",AA37)-1),""))=(AW37))+2*((IFERROR(--MID(AA37,FIND("-",AA37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD37" s="11" t="str">
+      <c r="AD37" s="11">
         <f>IF(OR($C37="",AC37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC37,FIND("-",AC37)-1),"")=AW37,IFERROR(--MID(AC37,FIND("-",AC37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AC37,FIND("-",AC37)-1),""))-(IFERROR(--MID(AC37,FIND("-",AC37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AC37,FIND("-",AC37)-1),""))-(IFERROR(--MID(AC37,FIND("-",AC37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AC37,FIND("-",AC37)-1),""))=(AW37))+2*((IFERROR(--MID(AC37,FIND("-",AC37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AF37" s="11" t="str">
+      <c r="AF37" s="11">
         <f>IF(OR($C37="",AE37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE37,FIND("-",AE37)-1),"")=AW37,IFERROR(--MID(AE37,FIND("-",AE37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AE37,FIND("-",AE37)-1),""))-(IFERROR(--MID(AE37,FIND("-",AE37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AE37,FIND("-",AE37)-1),""))-(IFERROR(--MID(AE37,FIND("-",AE37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AE37,FIND("-",AE37)-1),""))=(AW37))+2*((IFERROR(--MID(AE37,FIND("-",AE37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AH37" s="11" t="str">
+      <c r="AH37" s="11">
         <f>IF(OR($C37="",AG37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG37,FIND("-",AG37)-1),"")=AW37,IFERROR(--MID(AG37,FIND("-",AG37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AG37,FIND("-",AG37)-1),""))-(IFERROR(--MID(AG37,FIND("-",AG37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AG37,FIND("-",AG37)-1),""))-(IFERROR(--MID(AG37,FIND("-",AG37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AG37,FIND("-",AG37)-1),""))=(AW37))+2*((IFERROR(--MID(AG37,FIND("-",AG37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ37" s="11" t="str">
+      <c r="AJ37" s="11">
         <f>IF(OR($C37="",AI37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI37,FIND("-",AI37)-1),"")=AW37,IFERROR(--MID(AI37,FIND("-",AI37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AI37,FIND("-",AI37)-1),""))-(IFERROR(--MID(AI37,FIND("-",AI37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AI37,FIND("-",AI37)-1),""))-(IFERROR(--MID(AI37,FIND("-",AI37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AI37,FIND("-",AI37)-1),""))=(AW37))+2*((IFERROR(--MID(AI37,FIND("-",AI37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AL37" s="11" t="str">
+      <c r="AL37" s="11">
         <f>IF(OR($C37="",AK37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK37,FIND("-",AK37)-1),"")=AW37,IFERROR(--MID(AK37,FIND("-",AK37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AK37,FIND("-",AK37)-1),""))-(IFERROR(--MID(AK37,FIND("-",AK37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AK37,FIND("-",AK37)-1),""))-(IFERROR(--MID(AK37,FIND("-",AK37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AK37,FIND("-",AK37)-1),""))=(AW37))+2*((IFERROR(--MID(AK37,FIND("-",AK37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN37" s="11" t="str">
+      <c r="AN37" s="11">
         <f>IF(OR($C37="",AM37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM37,FIND("-",AM37)-1),"")=AW37,IFERROR(--MID(AM37,FIND("-",AM37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AM37,FIND("-",AM37)-1),""))-(IFERROR(--MID(AM37,FIND("-",AM37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AM37,FIND("-",AM37)-1),""))-(IFERROR(--MID(AM37,FIND("-",AM37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AM37,FIND("-",AM37)-1),""))=(AW37))+2*((IFERROR(--MID(AM37,FIND("-",AM37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AP37" s="11" t="str">
+      <c r="AP37" s="11">
         <f>IF(OR($C37="",AO37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO37,FIND("-",AO37)-1),"")=AW37,IFERROR(--MID(AO37,FIND("-",AO37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AO37,FIND("-",AO37)-1),""))-(IFERROR(--MID(AO37,FIND("-",AO37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AO37,FIND("-",AO37)-1),""))-(IFERROR(--MID(AO37,FIND("-",AO37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AO37,FIND("-",AO37)-1),""))=(AW37))+2*((IFERROR(--MID(AO37,FIND("-",AO37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ37" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AR37" s="11" t="str">
+      <c r="AR37" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS37" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT37" s="11" t="str">
+      <c r="AT37" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU37" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AV37" s="11" t="str">
+      <c r="AV37" s="11">
         <f>IF(OR($C37="",AU37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU37,FIND("-",AU37)-1),"")=AW37,IFERROR(--MID(AU37,FIND("-",AU37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AU37,FIND("-",AU37)-1),""))-(IFERROR(--MID(AU37,FIND("-",AU37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AU37,FIND("-",AU37)-1),""))-(IFERROR(--MID(AU37,FIND("-",AU37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AU37,FIND("-",AU37)-1),""))=(AW37))+2*((IFERROR(--MID(AU37,FIND("-",AU37)+1,99),""))=(AX37))),""))</f>
-        <v/>
-      </c>
-      <c r="AW37" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW37" s="11">
         <f>IF($C37="","",IFERROR(--LEFT($C37,FIND("-",$C37)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX37" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX37" s="11">
         <f>IF($C37="","",IFERROR(--MID($C37,FIND("-",$C37)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C38" s="10"/>
+      <c r="C38" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="D38" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F38" s="11" t="str">
+      <c r="F38" s="11">
         <f>IF(OR($C38="",E38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E38,FIND("-",E38)-1),"")=AW38,IFERROR(--MID(E38,FIND("-",E38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(E38,FIND("-",E38)-1),""))-(IFERROR(--MID(E38,FIND("-",E38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(E38,FIND("-",E38)-1),""))-(IFERROR(--MID(E38,FIND("-",E38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(E38,FIND("-",E38)-1),""))=(AW38))+2*((IFERROR(--MID(E38,FIND("-",E38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H38" s="11" t="str">
+      <c r="H38" s="11">
         <f>IF(OR($C38="",G38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G38,FIND("-",G38)-1),"")=AW38,IFERROR(--MID(G38,FIND("-",G38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(G38,FIND("-",G38)-1),""))-(IFERROR(--MID(G38,FIND("-",G38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(G38,FIND("-",G38)-1),""))-(IFERROR(--MID(G38,FIND("-",G38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(G38,FIND("-",G38)-1),""))=(AW38))+2*((IFERROR(--MID(G38,FIND("-",G38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="11" t="str">
+      <c r="J38" s="11">
         <f>IF(OR($C38="",I38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I38,FIND("-",I38)-1),"")=AW38,IFERROR(--MID(I38,FIND("-",I38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(I38,FIND("-",I38)-1),""))-(IFERROR(--MID(I38,FIND("-",I38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(I38,FIND("-",I38)-1),""))-(IFERROR(--MID(I38,FIND("-",I38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(I38,FIND("-",I38)-1),""))=(AW38))+2*((IFERROR(--MID(I38,FIND("-",I38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K38" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="L38" s="11" t="str">
+      <c r="L38" s="11">
         <f>IF(OR($C38="",K38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K38,FIND("-",K38)-1),"")=AW38,IFERROR(--MID(K38,FIND("-",K38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(K38,FIND("-",K38)-1),""))-(IFERROR(--MID(K38,FIND("-",K38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(K38,FIND("-",K38)-1),""))-(IFERROR(--MID(K38,FIND("-",K38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(K38,FIND("-",K38)-1),""))=(AW38))+2*((IFERROR(--MID(K38,FIND("-",K38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N38" s="11" t="str">
+      <c r="N38" s="11">
         <f>IF(OR($C38="",M38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M38,FIND("-",M38)-1),"")=AW38,IFERROR(--MID(M38,FIND("-",M38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(M38,FIND("-",M38)-1),""))-(IFERROR(--MID(M38,FIND("-",M38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(M38,FIND("-",M38)-1),""))-(IFERROR(--MID(M38,FIND("-",M38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(M38,FIND("-",M38)-1),""))=(AW38))+2*((IFERROR(--MID(M38,FIND("-",M38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P38" s="11" t="str">
+      <c r="P38" s="11">
         <f>IF(OR($C38="",O38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O38,FIND("-",O38)-1),"")=AW38,IFERROR(--MID(O38,FIND("-",O38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(O38,FIND("-",O38)-1),""))-(IFERROR(--MID(O38,FIND("-",O38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(O38,FIND("-",O38)-1),""))-(IFERROR(--MID(O38,FIND("-",O38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(O38,FIND("-",O38)-1),""))=(AW38))+2*((IFERROR(--MID(O38,FIND("-",O38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R38" s="11" t="str">
+      <c r="R38" s="11">
         <f>IF(OR($C38="",Q38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q38,FIND("-",Q38)-1),"")=AW38,IFERROR(--MID(Q38,FIND("-",Q38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(Q38,FIND("-",Q38)-1),""))-(IFERROR(--MID(Q38,FIND("-",Q38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(Q38,FIND("-",Q38)-1),""))-(IFERROR(--MID(Q38,FIND("-",Q38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(Q38,FIND("-",Q38)-1),""))=(AW38))+2*((IFERROR(--MID(Q38,FIND("-",Q38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S38" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T38" s="11" t="str">
+      <c r="T38" s="11">
         <f>IF(OR($C38="",S38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S38,FIND("-",S38)-1),"")=AW38,IFERROR(--MID(S38,FIND("-",S38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(S38,FIND("-",S38)-1),""))-(IFERROR(--MID(S38,FIND("-",S38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(S38,FIND("-",S38)-1),""))-(IFERROR(--MID(S38,FIND("-",S38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(S38,FIND("-",S38)-1),""))=(AW38))+2*((IFERROR(--MID(S38,FIND("-",S38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V38" s="11" t="str">
+      <c r="V38" s="11">
         <f>IF(OR($C38="",U38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U38,FIND("-",U38)-1),"")=AW38,IFERROR(--MID(U38,FIND("-",U38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(U38,FIND("-",U38)-1),""))-(IFERROR(--MID(U38,FIND("-",U38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(U38,FIND("-",U38)-1),""))-(IFERROR(--MID(U38,FIND("-",U38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(U38,FIND("-",U38)-1),""))=(AW38))+2*((IFERROR(--MID(U38,FIND("-",U38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X38" s="11" t="str">
+      <c r="X38" s="11">
         <f>IF(OR($C38="",W38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W38,FIND("-",W38)-1),"")=AW38,IFERROR(--MID(W38,FIND("-",W38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(W38,FIND("-",W38)-1),""))-(IFERROR(--MID(W38,FIND("-",W38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(W38,FIND("-",W38)-1),""))-(IFERROR(--MID(W38,FIND("-",W38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(W38,FIND("-",W38)-1),""))=(AW38))+2*((IFERROR(--MID(W38,FIND("-",W38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z38" s="11" t="str">
+      <c r="Z38" s="11">
         <f>IF(OR($C38="",Y38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y38,FIND("-",Y38)-1),"")=AW38,IFERROR(--MID(Y38,FIND("-",Y38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(Y38,FIND("-",Y38)-1),""))-(IFERROR(--MID(Y38,FIND("-",Y38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(Y38,FIND("-",Y38)-1),""))-(IFERROR(--MID(Y38,FIND("-",Y38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(Y38,FIND("-",Y38)-1),""))=(AW38))+2*((IFERROR(--MID(Y38,FIND("-",Y38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB38" s="11" t="str">
+      <c r="AB38" s="11">
         <f>IF(OR($C38="",AA38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA38,FIND("-",AA38)-1),"")=AW38,IFERROR(--MID(AA38,FIND("-",AA38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AA38,FIND("-",AA38)-1),""))-(IFERROR(--MID(AA38,FIND("-",AA38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AA38,FIND("-",AA38)-1),""))-(IFERROR(--MID(AA38,FIND("-",AA38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AA38,FIND("-",AA38)-1),""))=(AW38))+2*((IFERROR(--MID(AA38,FIND("-",AA38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC38" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD38" s="11" t="str">
+      <c r="AD38" s="11">
         <f>IF(OR($C38="",AC38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC38,FIND("-",AC38)-1),"")=AW38,IFERROR(--MID(AC38,FIND("-",AC38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AC38,FIND("-",AC38)-1),""))-(IFERROR(--MID(AC38,FIND("-",AC38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AC38,FIND("-",AC38)-1),""))-(IFERROR(--MID(AC38,FIND("-",AC38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AC38,FIND("-",AC38)-1),""))=(AW38))+2*((IFERROR(--MID(AC38,FIND("-",AC38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF38" s="11" t="str">
+      <c r="AF38" s="11">
         <f>IF(OR($C38="",AE38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE38,FIND("-",AE38)-1),"")=AW38,IFERROR(--MID(AE38,FIND("-",AE38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AE38,FIND("-",AE38)-1),""))-(IFERROR(--MID(AE38,FIND("-",AE38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AE38,FIND("-",AE38)-1),""))-(IFERROR(--MID(AE38,FIND("-",AE38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AE38,FIND("-",AE38)-1),""))=(AW38))+2*((IFERROR(--MID(AE38,FIND("-",AE38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AG38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH38" s="11" t="str">
+      <c r="AH38" s="11">
         <f>IF(OR($C38="",AG38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG38,FIND("-",AG38)-1),"")=AW38,IFERROR(--MID(AG38,FIND("-",AG38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AG38,FIND("-",AG38)-1),""))-(IFERROR(--MID(AG38,FIND("-",AG38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AG38,FIND("-",AG38)-1),""))-(IFERROR(--MID(AG38,FIND("-",AG38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AG38,FIND("-",AG38)-1),""))=(AW38))+2*((IFERROR(--MID(AG38,FIND("-",AG38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AJ38" s="11" t="str">
+      <c r="AJ38" s="11">
         <f>IF(OR($C38="",AI38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI38,FIND("-",AI38)-1),"")=AW38,IFERROR(--MID(AI38,FIND("-",AI38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AI38,FIND("-",AI38)-1),""))-(IFERROR(--MID(AI38,FIND("-",AI38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AI38,FIND("-",AI38)-1),""))-(IFERROR(--MID(AI38,FIND("-",AI38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AI38,FIND("-",AI38)-1),""))=(AW38))+2*((IFERROR(--MID(AI38,FIND("-",AI38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL38" s="11" t="str">
+      <c r="AL38" s="11">
         <f>IF(OR($C38="",AK38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK38,FIND("-",AK38)-1),"")=AW38,IFERROR(--MID(AK38,FIND("-",AK38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AK38,FIND("-",AK38)-1),""))-(IFERROR(--MID(AK38,FIND("-",AK38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AK38,FIND("-",AK38)-1),""))-(IFERROR(--MID(AK38,FIND("-",AK38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AK38,FIND("-",AK38)-1),""))=(AW38))+2*((IFERROR(--MID(AK38,FIND("-",AK38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AN38" s="11" t="str">
+      <c r="AN38" s="11">
         <f>IF(OR($C38="",AM38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM38,FIND("-",AM38)-1),"")=AW38,IFERROR(--MID(AM38,FIND("-",AM38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AM38,FIND("-",AM38)-1),""))-(IFERROR(--MID(AM38,FIND("-",AM38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AM38,FIND("-",AM38)-1),""))-(IFERROR(--MID(AM38,FIND("-",AM38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AM38,FIND("-",AM38)-1),""))=(AW38))+2*((IFERROR(--MID(AM38,FIND("-",AM38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AP38" s="11" t="str">
+      <c r="AP38" s="11">
         <f>IF(OR($C38="",AO38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO38,FIND("-",AO38)-1),"")=AW38,IFERROR(--MID(AO38,FIND("-",AO38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AO38,FIND("-",AO38)-1),""))-(IFERROR(--MID(AO38,FIND("-",AO38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AO38,FIND("-",AO38)-1),""))-(IFERROR(--MID(AO38,FIND("-",AO38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AO38,FIND("-",AO38)-1),""))=(AW38))+2*((IFERROR(--MID(AO38,FIND("-",AO38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ38" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AR38" s="11" t="str">
+      <c r="AR38" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS38" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT38" s="11" t="str">
+      <c r="AT38" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AV38" s="11" t="str">
+      <c r="AV38" s="11">
         <f>IF(OR($C38="",AU38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU38,FIND("-",AU38)-1),"")=AW38,IFERROR(--MID(AU38,FIND("-",AU38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AU38,FIND("-",AU38)-1),""))-(IFERROR(--MID(AU38,FIND("-",AU38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AU38,FIND("-",AU38)-1),""))-(IFERROR(--MID(AU38,FIND("-",AU38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AU38,FIND("-",AU38)-1),""))=(AW38))+2*((IFERROR(--MID(AU38,FIND("-",AU38)+1,99),""))=(AX38))),""))</f>
-        <v/>
-      </c>
-      <c r="AW38" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW38" s="11">
         <f>IF($C38="","",IFERROR(--LEFT($C38,FIND("-",$C38)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX38" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX38" s="11">
         <f>IF($C38="","",IFERROR(--MID($C38,FIND("-",$C38)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6687,7 +6691,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
@@ -6741,355 +6745,359 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
       <c r="B41" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D41" s="1" t="s">
         <v>105</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F41" s="11" t="str">
+      <c r="F41" s="11">
         <f>IF(OR($C41="",E41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E41,FIND("-",E41)-1),"")=AW41,IFERROR(--MID(E41,FIND("-",E41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(E41,FIND("-",E41)-1),""))-(IFERROR(--MID(E41,FIND("-",E41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(E41,FIND("-",E41)-1),""))-(IFERROR(--MID(E41,FIND("-",E41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(E41,FIND("-",E41)-1),""))=(AW41))+2*((IFERROR(--MID(E41,FIND("-",E41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H41" s="11" t="str">
+      <c r="H41" s="11">
         <f>IF(OR($C41="",G41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G41,FIND("-",G41)-1),"")=AW41,IFERROR(--MID(G41,FIND("-",G41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(G41,FIND("-",G41)-1),""))-(IFERROR(--MID(G41,FIND("-",G41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(G41,FIND("-",G41)-1),""))-(IFERROR(--MID(G41,FIND("-",G41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(G41,FIND("-",G41)-1),""))=(AW41))+2*((IFERROR(--MID(G41,FIND("-",G41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="11" t="str">
+      <c r="J41" s="11">
         <f>IF(OR($C41="",I41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I41,FIND("-",I41)-1),"")=AW41,IFERROR(--MID(I41,FIND("-",I41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(I41,FIND("-",I41)-1),""))-(IFERROR(--MID(I41,FIND("-",I41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(I41,FIND("-",I41)-1),""))-(IFERROR(--MID(I41,FIND("-",I41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(I41,FIND("-",I41)-1),""))=(AW41))+2*((IFERROR(--MID(I41,FIND("-",I41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="11" t="str">
+      <c r="L41" s="11">
         <f>IF(OR($C41="",K41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K41,FIND("-",K41)-1),"")=AW41,IFERROR(--MID(K41,FIND("-",K41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(K41,FIND("-",K41)-1),""))-(IFERROR(--MID(K41,FIND("-",K41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(K41,FIND("-",K41)-1),""))-(IFERROR(--MID(K41,FIND("-",K41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(K41,FIND("-",K41)-1),""))=(AW41))+2*((IFERROR(--MID(K41,FIND("-",K41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N41" s="11" t="str">
+      <c r="N41" s="11">
         <f>IF(OR($C41="",M41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M41,FIND("-",M41)-1),"")=AW41,IFERROR(--MID(M41,FIND("-",M41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(M41,FIND("-",M41)-1),""))-(IFERROR(--MID(M41,FIND("-",M41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(M41,FIND("-",M41)-1),""))-(IFERROR(--MID(M41,FIND("-",M41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(M41,FIND("-",M41)-1),""))=(AW41))+2*((IFERROR(--MID(M41,FIND("-",M41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P41" s="11" t="str">
+      <c r="P41" s="11">
         <f>IF(OR($C41="",O41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O41,FIND("-",O41)-1),"")=AW41,IFERROR(--MID(O41,FIND("-",O41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(O41,FIND("-",O41)-1),""))-(IFERROR(--MID(O41,FIND("-",O41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(O41,FIND("-",O41)-1),""))-(IFERROR(--MID(O41,FIND("-",O41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(O41,FIND("-",O41)-1),""))=(AW41))+2*((IFERROR(--MID(O41,FIND("-",O41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q41" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R41" s="11" t="str">
+      <c r="R41" s="11">
         <f>IF(OR($C41="",Q41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q41,FIND("-",Q41)-1),"")=AW41,IFERROR(--MID(Q41,FIND("-",Q41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(Q41,FIND("-",Q41)-1),""))-(IFERROR(--MID(Q41,FIND("-",Q41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(Q41,FIND("-",Q41)-1),""))-(IFERROR(--MID(Q41,FIND("-",Q41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(Q41,FIND("-",Q41)-1),""))=(AW41))+2*((IFERROR(--MID(Q41,FIND("-",Q41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T41" s="11" t="str">
+      <c r="T41" s="11">
         <f>IF(OR($C41="",S41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S41,FIND("-",S41)-1),"")=AW41,IFERROR(--MID(S41,FIND("-",S41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(S41,FIND("-",S41)-1),""))-(IFERROR(--MID(S41,FIND("-",S41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(S41,FIND("-",S41)-1),""))-(IFERROR(--MID(S41,FIND("-",S41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(S41,FIND("-",S41)-1),""))=(AW41))+2*((IFERROR(--MID(S41,FIND("-",S41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V41" s="11" t="str">
+      <c r="V41" s="11">
         <f>IF(OR($C41="",U41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U41,FIND("-",U41)-1),"")=AW41,IFERROR(--MID(U41,FIND("-",U41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(U41,FIND("-",U41)-1),""))-(IFERROR(--MID(U41,FIND("-",U41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(U41,FIND("-",U41)-1),""))-(IFERROR(--MID(U41,FIND("-",U41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(U41,FIND("-",U41)-1),""))=(AW41))+2*((IFERROR(--MID(U41,FIND("-",U41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X41" s="11" t="str">
+      <c r="X41" s="11">
         <f>IF(OR($C41="",W41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W41,FIND("-",W41)-1),"")=AW41,IFERROR(--MID(W41,FIND("-",W41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(W41,FIND("-",W41)-1),""))-(IFERROR(--MID(W41,FIND("-",W41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(W41,FIND("-",W41)-1),""))-(IFERROR(--MID(W41,FIND("-",W41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(W41,FIND("-",W41)-1),""))=(AW41))+2*((IFERROR(--MID(W41,FIND("-",W41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z41" s="11" t="str">
+      <c r="Z41" s="11">
         <f>IF(OR($C41="",Y41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y41,FIND("-",Y41)-1),"")=AW41,IFERROR(--MID(Y41,FIND("-",Y41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(Y41,FIND("-",Y41)-1),""))-(IFERROR(--MID(Y41,FIND("-",Y41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(Y41,FIND("-",Y41)-1),""))-(IFERROR(--MID(Y41,FIND("-",Y41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(Y41,FIND("-",Y41)-1),""))=(AW41))+2*((IFERROR(--MID(Y41,FIND("-",Y41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AB41" s="11" t="str">
+      <c r="AB41" s="11">
         <f>IF(OR($C41="",AA41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA41,FIND("-",AA41)-1),"")=AW41,IFERROR(--MID(AA41,FIND("-",AA41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AA41,FIND("-",AA41)-1),""))-(IFERROR(--MID(AA41,FIND("-",AA41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AA41,FIND("-",AA41)-1),""))-(IFERROR(--MID(AA41,FIND("-",AA41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AA41,FIND("-",AA41)-1),""))=(AW41))+2*((IFERROR(--MID(AA41,FIND("-",AA41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AD41" s="11" t="str">
+      <c r="AD41" s="11">
         <f>IF(OR($C41="",AC41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC41,FIND("-",AC41)-1),"")=AW41,IFERROR(--MID(AC41,FIND("-",AC41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AC41,FIND("-",AC41)-1),""))-(IFERROR(--MID(AC41,FIND("-",AC41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AC41,FIND("-",AC41)-1),""))-(IFERROR(--MID(AC41,FIND("-",AC41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AC41,FIND("-",AC41)-1),""))=(AW41))+2*((IFERROR(--MID(AC41,FIND("-",AC41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE41" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF41" s="11" t="str">
+      <c r="AF41" s="11">
         <f>IF(OR($C41="",AE41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE41,FIND("-",AE41)-1),"")=AW41,IFERROR(--MID(AE41,FIND("-",AE41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AE41,FIND("-",AE41)-1),""))-(IFERROR(--MID(AE41,FIND("-",AE41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AE41,FIND("-",AE41)-1),""))-(IFERROR(--MID(AE41,FIND("-",AE41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AE41,FIND("-",AE41)-1),""))=(AW41))+2*((IFERROR(--MID(AE41,FIND("-",AE41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG41" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AH41" s="11" t="str">
+      <c r="AH41" s="11">
         <f>IF(OR($C41="",AG41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG41,FIND("-",AG41)-1),"")=AW41,IFERROR(--MID(AG41,FIND("-",AG41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AG41,FIND("-",AG41)-1),""))-(IFERROR(--MID(AG41,FIND("-",AG41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AG41,FIND("-",AG41)-1),""))-(IFERROR(--MID(AG41,FIND("-",AG41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AG41,FIND("-",AG41)-1),""))=(AW41))+2*((IFERROR(--MID(AG41,FIND("-",AG41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ41" s="11" t="str">
+      <c r="AJ41" s="11">
         <f>IF(OR($C41="",AI41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI41,FIND("-",AI41)-1),"")=AW41,IFERROR(--MID(AI41,FIND("-",AI41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AI41,FIND("-",AI41)-1),""))-(IFERROR(--MID(AI41,FIND("-",AI41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AI41,FIND("-",AI41)-1),""))-(IFERROR(--MID(AI41,FIND("-",AI41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AI41,FIND("-",AI41)-1),""))=(AW41))+2*((IFERROR(--MID(AI41,FIND("-",AI41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL41" s="11" t="str">
+      <c r="AL41" s="11">
         <f>IF(OR($C41="",AK41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK41,FIND("-",AK41)-1),"")=AW41,IFERROR(--MID(AK41,FIND("-",AK41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AK41,FIND("-",AK41)-1),""))-(IFERROR(--MID(AK41,FIND("-",AK41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AK41,FIND("-",AK41)-1),""))-(IFERROR(--MID(AK41,FIND("-",AK41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AK41,FIND("-",AK41)-1),""))=(AW41))+2*((IFERROR(--MID(AK41,FIND("-",AK41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN41" s="11" t="str">
+      <c r="AN41" s="11">
         <f>IF(OR($C41="",AM41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM41,FIND("-",AM41)-1),"")=AW41,IFERROR(--MID(AM41,FIND("-",AM41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AM41,FIND("-",AM41)-1),""))-(IFERROR(--MID(AM41,FIND("-",AM41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AM41,FIND("-",AM41)-1),""))-(IFERROR(--MID(AM41,FIND("-",AM41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AM41,FIND("-",AM41)-1),""))=(AW41))+2*((IFERROR(--MID(AM41,FIND("-",AM41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP41" s="11" t="str">
+      <c r="AP41" s="11">
         <f>IF(OR($C41="",AO41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO41,FIND("-",AO41)-1),"")=AW41,IFERROR(--MID(AO41,FIND("-",AO41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AO41,FIND("-",AO41)-1),""))-(IFERROR(--MID(AO41,FIND("-",AO41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AO41,FIND("-",AO41)-1),""))-(IFERROR(--MID(AO41,FIND("-",AO41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AO41,FIND("-",AO41)-1),""))=(AW41))+2*((IFERROR(--MID(AO41,FIND("-",AO41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ41" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR41" s="11" t="str">
+      <c r="AR41" s="11">
         <f>IF(OR($C41="",AQ41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ41,FIND("-",AQ41)-1),"")=AW41,IFERROR(--MID(AQ41,FIND("-",AQ41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AQ41,FIND("-",AQ41)-1),""))-(IFERROR(--MID(AQ41,FIND("-",AQ41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AQ41,FIND("-",AQ41)-1),""))-(IFERROR(--MID(AQ41,FIND("-",AQ41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AQ41,FIND("-",AQ41)-1),""))=(AW41))+2*((IFERROR(--MID(AQ41,FIND("-",AQ41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AT41" s="11" t="str">
+      <c r="AT41" s="11">
         <f>IF(OR($C41="",AS41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS41,FIND("-",AS41)-1),"")=AW41,IFERROR(--MID(AS41,FIND("-",AS41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AS41,FIND("-",AS41)-1),""))-(IFERROR(--MID(AS41,FIND("-",AS41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AS41,FIND("-",AS41)-1),""))-(IFERROR(--MID(AS41,FIND("-",AS41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AS41,FIND("-",AS41)-1),""))=(AW41))+2*((IFERROR(--MID(AS41,FIND("-",AS41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AV41" s="11" t="str">
+      <c r="AV41" s="11">
         <f>IF(OR($C41="",AU41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU41,FIND("-",AU41)-1),"")=AW41,IFERROR(--MID(AU41,FIND("-",AU41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AU41,FIND("-",AU41)-1),""))-(IFERROR(--MID(AU41,FIND("-",AU41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AU41,FIND("-",AU41)-1),""))-(IFERROR(--MID(AU41,FIND("-",AU41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AU41,FIND("-",AU41)-1),""))=(AW41))+2*((IFERROR(--MID(AU41,FIND("-",AU41)+1,99),""))=(AX41))),""))</f>
-        <v/>
-      </c>
-      <c r="AW41" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW41" s="11">
         <f>IF($C41="","",IFERROR(--LEFT($C41,FIND("-",$C41)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX41" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX41" s="11">
         <f>IF($C41="","",IFERROR(--MID($C41,FIND("-",$C41)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
       <c r="B42" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C42" s="10"/>
+      <c r="C42" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="D42" s="1" t="s">
         <v>108</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="11" t="str">
+      <c r="F42" s="11">
         <f>IF(OR($C42="",E42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E42,FIND("-",E42)-1),"")=AW42,IFERROR(--MID(E42,FIND("-",E42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(E42,FIND("-",E42)-1),""))-(IFERROR(--MID(E42,FIND("-",E42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(E42,FIND("-",E42)-1),""))-(IFERROR(--MID(E42,FIND("-",E42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(E42,FIND("-",E42)-1),""))=(AW42))+2*((IFERROR(--MID(E42,FIND("-",E42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H42" s="11" t="str">
+      <c r="H42" s="11">
         <f>IF(OR($C42="",G42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G42,FIND("-",G42)-1),"")=AW42,IFERROR(--MID(G42,FIND("-",G42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(G42,FIND("-",G42)-1),""))-(IFERROR(--MID(G42,FIND("-",G42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(G42,FIND("-",G42)-1),""))-(IFERROR(--MID(G42,FIND("-",G42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(G42,FIND("-",G42)-1),""))=(AW42))+2*((IFERROR(--MID(G42,FIND("-",G42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J42" s="11" t="str">
+      <c r="J42" s="11">
         <f>IF(OR($C42="",I42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I42,FIND("-",I42)-1),"")=AW42,IFERROR(--MID(I42,FIND("-",I42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(I42,FIND("-",I42)-1),""))-(IFERROR(--MID(I42,FIND("-",I42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(I42,FIND("-",I42)-1),""))-(IFERROR(--MID(I42,FIND("-",I42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(I42,FIND("-",I42)-1),""))=(AW42))+2*((IFERROR(--MID(I42,FIND("-",I42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K42" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L42" s="11" t="str">
+      <c r="L42" s="11">
         <f>IF(OR($C42="",K42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K42,FIND("-",K42)-1),"")=AW42,IFERROR(--MID(K42,FIND("-",K42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(K42,FIND("-",K42)-1),""))-(IFERROR(--MID(K42,FIND("-",K42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(K42,FIND("-",K42)-1),""))-(IFERROR(--MID(K42,FIND("-",K42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(K42,FIND("-",K42)-1),""))=(AW42))+2*((IFERROR(--MID(K42,FIND("-",K42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M42" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N42" s="11" t="str">
+      <c r="N42" s="11">
         <f>IF(OR($C42="",M42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M42,FIND("-",M42)-1),"")=AW42,IFERROR(--MID(M42,FIND("-",M42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(M42,FIND("-",M42)-1),""))-(IFERROR(--MID(M42,FIND("-",M42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(M42,FIND("-",M42)-1),""))-(IFERROR(--MID(M42,FIND("-",M42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(M42,FIND("-",M42)-1),""))=(AW42))+2*((IFERROR(--MID(M42,FIND("-",M42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O42" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="P42" s="11" t="str">
+      <c r="P42" s="11">
         <f>IF(OR($C42="",O42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O42,FIND("-",O42)-1),"")=AW42,IFERROR(--MID(O42,FIND("-",O42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(O42,FIND("-",O42)-1),""))-(IFERROR(--MID(O42,FIND("-",O42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(O42,FIND("-",O42)-1),""))-(IFERROR(--MID(O42,FIND("-",O42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(O42,FIND("-",O42)-1),""))=(AW42))+2*((IFERROR(--MID(O42,FIND("-",O42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q42" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="R42" s="11" t="str">
+      <c r="R42" s="11">
         <f>IF(OR($C42="",Q42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q42,FIND("-",Q42)-1),"")=AW42,IFERROR(--MID(Q42,FIND("-",Q42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(Q42,FIND("-",Q42)-1),""))-(IFERROR(--MID(Q42,FIND("-",Q42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(Q42,FIND("-",Q42)-1),""))-(IFERROR(--MID(Q42,FIND("-",Q42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(Q42,FIND("-",Q42)-1),""))=(AW42))+2*((IFERROR(--MID(Q42,FIND("-",Q42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T42" s="11" t="str">
+      <c r="T42" s="11">
         <f>IF(OR($C42="",S42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S42,FIND("-",S42)-1),"")=AW42,IFERROR(--MID(S42,FIND("-",S42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(S42,FIND("-",S42)-1),""))-(IFERROR(--MID(S42,FIND("-",S42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(S42,FIND("-",S42)-1),""))-(IFERROR(--MID(S42,FIND("-",S42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(S42,FIND("-",S42)-1),""))=(AW42))+2*((IFERROR(--MID(S42,FIND("-",S42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="V42" s="11" t="str">
+      <c r="V42" s="11">
         <f>IF(OR($C42="",U42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U42,FIND("-",U42)-1),"")=AW42,IFERROR(--MID(U42,FIND("-",U42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(U42,FIND("-",U42)-1),""))-(IFERROR(--MID(U42,FIND("-",U42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(U42,FIND("-",U42)-1),""))-(IFERROR(--MID(U42,FIND("-",U42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(U42,FIND("-",U42)-1),""))=(AW42))+2*((IFERROR(--MID(U42,FIND("-",U42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="W42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X42" s="11" t="str">
+      <c r="X42" s="11">
         <f>IF(OR($C42="",W42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W42,FIND("-",W42)-1),"")=AW42,IFERROR(--MID(W42,FIND("-",W42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(W42,FIND("-",W42)-1),""))-(IFERROR(--MID(W42,FIND("-",W42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(W42,FIND("-",W42)-1),""))-(IFERROR(--MID(W42,FIND("-",W42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(W42,FIND("-",W42)-1),""))=(AW42))+2*((IFERROR(--MID(W42,FIND("-",W42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="Z42" s="11" t="str">
+      <c r="Z42" s="11">
         <f>IF(OR($C42="",Y42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y42,FIND("-",Y42)-1),"")=AW42,IFERROR(--MID(Y42,FIND("-",Y42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(Y42,FIND("-",Y42)-1),""))-(IFERROR(--MID(Y42,FIND("-",Y42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(Y42,FIND("-",Y42)-1),""))-(IFERROR(--MID(Y42,FIND("-",Y42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(Y42,FIND("-",Y42)-1),""))=(AW42))+2*((IFERROR(--MID(Y42,FIND("-",Y42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AB42" s="11" t="str">
+      <c r="AB42" s="11">
         <f>IF(OR($C42="",AA42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA42,FIND("-",AA42)-1),"")=AW42,IFERROR(--MID(AA42,FIND("-",AA42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AA42,FIND("-",AA42)-1),""))-(IFERROR(--MID(AA42,FIND("-",AA42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AA42,FIND("-",AA42)-1),""))-(IFERROR(--MID(AA42,FIND("-",AA42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AA42,FIND("-",AA42)-1),""))=(AW42))+2*((IFERROR(--MID(AA42,FIND("-",AA42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC42" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD42" s="11" t="str">
+      <c r="AD42" s="11">
         <f>IF(OR($C42="",AC42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC42,FIND("-",AC42)-1),"")=AW42,IFERROR(--MID(AC42,FIND("-",AC42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AC42,FIND("-",AC42)-1),""))-(IFERROR(--MID(AC42,FIND("-",AC42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AC42,FIND("-",AC42)-1),""))-(IFERROR(--MID(AC42,FIND("-",AC42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AC42,FIND("-",AC42)-1),""))=(AW42))+2*((IFERROR(--MID(AC42,FIND("-",AC42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF42" s="11" t="str">
+      <c r="AF42" s="11">
         <f>IF(OR($C42="",AE42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE42,FIND("-",AE42)-1),"")=AW42,IFERROR(--MID(AE42,FIND("-",AE42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AE42,FIND("-",AE42)-1),""))-(IFERROR(--MID(AE42,FIND("-",AE42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AE42,FIND("-",AE42)-1),""))-(IFERROR(--MID(AE42,FIND("-",AE42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AE42,FIND("-",AE42)-1),""))=(AW42))+2*((IFERROR(--MID(AE42,FIND("-",AE42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH42" s="11" t="str">
+      <c r="AH42" s="11">
         <f>IF(OR($C42="",AG42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG42,FIND("-",AG42)-1),"")=AW42,IFERROR(--MID(AG42,FIND("-",AG42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AG42,FIND("-",AG42)-1),""))-(IFERROR(--MID(AG42,FIND("-",AG42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AG42,FIND("-",AG42)-1),""))-(IFERROR(--MID(AG42,FIND("-",AG42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AG42,FIND("-",AG42)-1),""))=(AW42))+2*((IFERROR(--MID(AG42,FIND("-",AG42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AJ42" s="11" t="str">
+      <c r="AJ42" s="11">
         <f>IF(OR($C42="",AI42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI42,FIND("-",AI42)-1),"")=AW42,IFERROR(--MID(AI42,FIND("-",AI42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AI42,FIND("-",AI42)-1),""))-(IFERROR(--MID(AI42,FIND("-",AI42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AI42,FIND("-",AI42)-1),""))-(IFERROR(--MID(AI42,FIND("-",AI42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AI42,FIND("-",AI42)-1),""))=(AW42))+2*((IFERROR(--MID(AI42,FIND("-",AI42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL42" s="11" t="str">
+      <c r="AL42" s="11">
         <f>IF(OR($C42="",AK42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK42,FIND("-",AK42)-1),"")=AW42,IFERROR(--MID(AK42,FIND("-",AK42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AK42,FIND("-",AK42)-1),""))-(IFERROR(--MID(AK42,FIND("-",AK42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AK42,FIND("-",AK42)-1),""))-(IFERROR(--MID(AK42,FIND("-",AK42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AK42,FIND("-",AK42)-1),""))=(AW42))+2*((IFERROR(--MID(AK42,FIND("-",AK42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN42" s="11" t="str">
+      <c r="AN42" s="11">
         <f>IF(OR($C42="",AM42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM42,FIND("-",AM42)-1),"")=AW42,IFERROR(--MID(AM42,FIND("-",AM42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AM42,FIND("-",AM42)-1),""))-(IFERROR(--MID(AM42,FIND("-",AM42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AM42,FIND("-",AM42)-1),""))-(IFERROR(--MID(AM42,FIND("-",AM42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AM42,FIND("-",AM42)-1),""))=(AW42))+2*((IFERROR(--MID(AM42,FIND("-",AM42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AP42" s="11" t="str">
+      <c r="AP42" s="11">
         <f>IF(OR($C42="",AO42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO42,FIND("-",AO42)-1),"")=AW42,IFERROR(--MID(AO42,FIND("-",AO42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AO42,FIND("-",AO42)-1),""))-(IFERROR(--MID(AO42,FIND("-",AO42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AO42,FIND("-",AO42)-1),""))-(IFERROR(--MID(AO42,FIND("-",AO42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AO42,FIND("-",AO42)-1),""))=(AW42))+2*((IFERROR(--MID(AO42,FIND("-",AO42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR42" s="11" t="str">
+      <c r="AR42" s="11">
         <f>IF(OR($C42="",AQ42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ42,FIND("-",AQ42)-1),"")=AW42,IFERROR(--MID(AQ42,FIND("-",AQ42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AQ42,FIND("-",AQ42)-1),""))-(IFERROR(--MID(AQ42,FIND("-",AQ42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AQ42,FIND("-",AQ42)-1),""))-(IFERROR(--MID(AQ42,FIND("-",AQ42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AQ42,FIND("-",AQ42)-1),""))=(AW42))+2*((IFERROR(--MID(AQ42,FIND("-",AQ42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS42" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT42" s="11" t="str">
+      <c r="AT42" s="11">
         <f>IF(OR($C42="",AS42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS42,FIND("-",AS42)-1),"")=AW42,IFERROR(--MID(AS42,FIND("-",AS42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AS42,FIND("-",AS42)-1),""))-(IFERROR(--MID(AS42,FIND("-",AS42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AS42,FIND("-",AS42)-1),""))-(IFERROR(--MID(AS42,FIND("-",AS42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AS42,FIND("-",AS42)-1),""))=(AW42))+2*((IFERROR(--MID(AS42,FIND("-",AS42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AV42" s="11" t="str">
+      <c r="AV42" s="11">
         <f>IF(OR($C42="",AU42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU42,FIND("-",AU42)-1),"")=AW42,IFERROR(--MID(AU42,FIND("-",AU42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AU42,FIND("-",AU42)-1),""))-(IFERROR(--MID(AU42,FIND("-",AU42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AU42,FIND("-",AU42)-1),""))-(IFERROR(--MID(AU42,FIND("-",AU42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AU42,FIND("-",AU42)-1),""))=(AW42))+2*((IFERROR(--MID(AU42,FIND("-",AU42)+1,99),""))=(AX42))),""))</f>
-        <v/>
-      </c>
-      <c r="AW42" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW42" s="11">
         <f>IF($C42="","",IFERROR(--LEFT($C42,FIND("-",$C42)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX42" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX42" s="11">
         <f>IF($C42="","",IFERROR(--MID($C42,FIND("-",$C42)+1,99),""))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7263,7 +7271,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7437,7 +7445,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="18"/>
       <c r="C45" s="13"/>
@@ -7495,7 +7503,7 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
@@ -7549,7 +7557,7 @@
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7723,7 +7731,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7897,7 +7905,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8071,7 +8079,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
       <c r="B50" s="18"/>
       <c r="C50" s="13"/>
@@ -8129,7 +8137,7 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
@@ -8183,7 +8191,7 @@
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8357,7 +8365,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8531,7 +8539,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8705,7 +8713,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8879,7 +8887,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9053,7 +9061,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
       <c r="B57" s="18"/>
       <c r="C57" s="13"/>
@@ -9111,7 +9119,7 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
@@ -9165,7 +9173,7 @@
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9339,7 +9347,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9513,7 +9521,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9687,7 +9695,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9861,7 +9869,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="12"/>
       <c r="B63" s="18"/>
       <c r="C63" s="13"/>
@@ -9919,7 +9927,7 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
@@ -9973,7 +9981,7 @@
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10147,7 +10155,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10321,7 +10329,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10495,7 +10503,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10669,7 +10677,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
       <c r="B69" s="18"/>
       <c r="C69" s="13"/>
@@ -10727,7 +10735,7 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
@@ -10781,7 +10789,7 @@
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -10955,7 +10963,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11129,7 +11137,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11303,7 +11311,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11477,7 +11485,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
       <c r="B75" s="18"/>
       <c r="C75" s="13"/>
@@ -11535,7 +11543,7 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
@@ -11589,7 +11597,7 @@
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11763,7 +11771,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -11937,7 +11945,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12111,7 +12119,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12285,7 +12293,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12"/>
       <c r="B81" s="18"/>
       <c r="C81" s="13"/>
@@ -12343,7 +12351,7 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
@@ -12397,7 +12405,7 @@
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12571,7 +12579,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12745,7 +12753,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -12919,7 +12927,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13093,7 +13101,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13267,7 +13275,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13441,7 +13449,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12"/>
       <c r="B89" s="18"/>
       <c r="C89" s="13"/>
@@ -13499,7 +13507,7 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
@@ -13553,7 +13561,7 @@
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13727,7 +13735,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13901,7 +13909,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14075,7 +14083,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14249,7 +14257,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14423,7 +14431,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14597,7 +14605,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="12"/>
       <c r="B97" s="18"/>
       <c r="C97" s="13"/>
@@ -14655,7 +14663,7 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
@@ -14709,7 +14717,7 @@
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14883,7 +14891,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15057,7 +15065,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15231,7 +15239,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15405,7 +15413,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15579,7 +15587,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15753,7 +15761,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="12"/>
       <c r="B105" s="18"/>
       <c r="C105" s="13"/>
@@ -15811,7 +15819,7 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
@@ -15865,7 +15873,7 @@
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16039,7 +16047,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16213,7 +16221,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16387,7 +16395,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16561,7 +16569,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="12"/>
       <c r="B111" s="18"/>
       <c r="C111" s="13"/>
@@ -16619,7 +16627,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="12"/>
       <c r="B112" s="18"/>
       <c r="C112" s="13"/>
@@ -16677,7 +16685,7 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="38" t="s">
         <v>128</v>
       </c>
@@ -16731,7 +16739,7 @@
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
@@ -16785,7 +16793,7 @@
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -16915,7 +16923,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="12"/>
       <c r="B116" s="18"/>
       <c r="C116" s="13"/>
@@ -16973,7 +16981,7 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
@@ -17027,7 +17035,7 @@
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17157,7 +17165,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17287,7 +17295,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="12"/>
       <c r="B120" s="18"/>
       <c r="C120" s="13"/>
@@ -17345,7 +17353,7 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
@@ -17399,7 +17407,7 @@
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17529,7 +17537,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17659,7 +17667,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17789,7 +17797,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="12"/>
       <c r="B125" s="18"/>
       <c r="C125" s="13"/>
@@ -17847,7 +17855,7 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
@@ -17901,7 +17909,7 @@
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18031,7 +18039,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18161,7 +18169,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18291,7 +18299,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="12"/>
       <c r="B130" s="18"/>
       <c r="C130" s="13"/>
@@ -18349,7 +18357,7 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
@@ -18403,7 +18411,7 @@
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18533,7 +18541,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18663,7 +18671,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="12"/>
       <c r="B134" s="18"/>
       <c r="C134" s="13"/>
@@ -18721,7 +18729,7 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
@@ -18775,7 +18783,7 @@
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -18905,7 +18913,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19035,7 +19043,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19165,7 +19173,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="12"/>
       <c r="B139" s="18"/>
       <c r="C139" s="13"/>
@@ -19223,7 +19231,7 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
@@ -19277,7 +19285,7 @@
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19407,7 +19415,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19537,7 +19545,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="12"/>
       <c r="B143" s="18"/>
       <c r="C143" s="13"/>
@@ -19595,7 +19603,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="12"/>
       <c r="B144" s="18"/>
       <c r="C144" s="13"/>
@@ -19653,7 +19661,7 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="38" t="s">
         <v>167</v>
       </c>
@@ -19707,7 +19715,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
@@ -19761,7 +19769,7 @@
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19891,7 +19899,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20021,7 +20029,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="12"/>
       <c r="B149" s="18"/>
       <c r="C149" s="13"/>
@@ -20079,7 +20087,7 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
@@ -20133,7 +20141,7 @@
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20263,7 +20271,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="12"/>
       <c r="B152" s="18"/>
       <c r="C152" s="13"/>
@@ -20321,7 +20329,7 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
@@ -20375,7 +20383,7 @@
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20505,7 +20513,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20635,7 +20643,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="12"/>
       <c r="B156" s="18"/>
       <c r="C156" s="13"/>
@@ -20693,7 +20701,7 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
@@ -20747,7 +20755,7 @@
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20877,7 +20885,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -21007,7 +21015,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21137,7 +21145,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="12"/>
       <c r="B161" s="18"/>
       <c r="C161" s="13"/>
@@ -21195,7 +21203,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="12"/>
       <c r="B162" s="18"/>
       <c r="C162" s="13"/>
@@ -21253,7 +21261,7 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="38" t="s">
         <v>187</v>
       </c>
@@ -21307,7 +21315,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
@@ -21361,7 +21369,7 @@
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21491,7 +21499,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="12"/>
       <c r="B166" s="18"/>
       <c r="C166" s="13"/>
@@ -21549,7 +21557,7 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
@@ -21603,7 +21611,7 @@
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21733,7 +21741,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="12"/>
       <c r="B169" s="18"/>
       <c r="C169" s="13"/>
@@ -21791,7 +21799,7 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
@@ -21845,7 +21853,7 @@
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -21975,7 +21983,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="12"/>
       <c r="B172" s="18"/>
       <c r="C172" s="13"/>
@@ -22033,7 +22041,7 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
@@ -22087,7 +22095,7 @@
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22217,7 +22225,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="12"/>
       <c r="B175" s="18"/>
       <c r="C175" s="13"/>
@@ -22275,7 +22283,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="12"/>
       <c r="B176" s="18"/>
       <c r="C176" s="13"/>
@@ -22333,7 +22341,7 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="38" t="s">
         <v>200</v>
       </c>
@@ -22387,7 +22395,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
@@ -22441,7 +22449,7 @@
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22571,7 +22579,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="12"/>
       <c r="B180" s="18"/>
       <c r="C180" s="13"/>
@@ -22629,7 +22637,7 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
@@ -22683,7 +22691,7 @@
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22813,7 +22821,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="12"/>
       <c r="B183" s="18"/>
       <c r="C183" s="13"/>
@@ -22871,7 +22879,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="12"/>
       <c r="B184" s="18"/>
       <c r="C184" s="13"/>
@@ -22929,7 +22937,7 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="38" t="s">
         <v>207</v>
       </c>
@@ -22983,7 +22991,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
@@ -23037,7 +23045,7 @@
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23167,7 +23175,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="12"/>
       <c r="B188" s="18"/>
       <c r="C188" s="13"/>
@@ -23225,7 +23233,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="12"/>
       <c r="B189" s="18"/>
       <c r="C189" s="13"/>
@@ -23283,7 +23291,7 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="38" t="s">
         <v>211</v>
       </c>
@@ -23337,7 +23345,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
@@ -23391,7 +23399,7 @@
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23521,7 +23529,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="12"/>
       <c r="B193" s="18"/>
       <c r="C193" s="13"/>
@@ -23579,7 +23587,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="12"/>
       <c r="B194" s="18"/>
       <c r="C194" s="13"/>
@@ -23639,6 +23647,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23655,60 +23717,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23718,58 +23726,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.28515625" customWidth="1"/>
+    <col min="2" max="2" width="75.26953125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="23" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="23" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" style="23" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" style="23" customWidth="1"/>
-    <col min="25" max="25" width="10.5703125" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.5703125" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="23" customWidth="1"/>
-    <col min="29" max="29" width="10.5703125" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="23" customWidth="1"/>
-    <col min="31" max="31" width="10.5703125" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="23" customWidth="1"/>
-    <col min="33" max="33" width="10.5703125" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="23" customWidth="1"/>
-    <col min="35" max="35" width="10.5703125" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="23" customWidth="1"/>
-    <col min="37" max="37" width="10.5703125" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="23" customWidth="1"/>
-    <col min="39" max="39" width="10.5703125" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="23" customWidth="1"/>
-    <col min="41" max="41" width="10.5703125" customWidth="1"/>
-    <col min="42" max="42" width="12.5703125" customWidth="1"/>
-    <col min="43" max="43" width="10.5703125" customWidth="1"/>
-    <col min="44" max="44" width="12.5703125" style="23" customWidth="1"/>
-    <col min="45" max="45" width="10.5703125" customWidth="1"/>
-    <col min="46" max="46" width="12.5703125" style="23" customWidth="1"/>
-    <col min="47" max="47" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" customWidth="1"/>
+    <col min="12" max="12" width="12.54296875" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" customWidth="1"/>
+    <col min="14" max="14" width="12.54296875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" customWidth="1"/>
+    <col min="16" max="16" width="12.54296875" style="23" customWidth="1"/>
+    <col min="17" max="17" width="10.54296875" customWidth="1"/>
+    <col min="18" max="18" width="12.54296875" style="23" customWidth="1"/>
+    <col min="19" max="19" width="10.54296875" customWidth="1"/>
+    <col min="20" max="20" width="12.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" style="23" customWidth="1"/>
+    <col min="23" max="23" width="10.54296875" customWidth="1"/>
+    <col min="24" max="24" width="12.54296875" style="23" customWidth="1"/>
+    <col min="25" max="25" width="10.54296875" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" style="23" customWidth="1"/>
+    <col min="27" max="27" width="10.54296875" customWidth="1"/>
+    <col min="28" max="28" width="12.54296875" style="23" customWidth="1"/>
+    <col min="29" max="29" width="10.54296875" customWidth="1"/>
+    <col min="30" max="30" width="12.54296875" style="23" customWidth="1"/>
+    <col min="31" max="31" width="10.54296875" customWidth="1"/>
+    <col min="32" max="32" width="12.54296875" style="23" customWidth="1"/>
+    <col min="33" max="33" width="10.54296875" customWidth="1"/>
+    <col min="34" max="34" width="12.54296875" style="23" customWidth="1"/>
+    <col min="35" max="35" width="10.54296875" customWidth="1"/>
+    <col min="36" max="36" width="12.54296875" style="23" customWidth="1"/>
+    <col min="37" max="37" width="10.54296875" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="23" customWidth="1"/>
+    <col min="39" max="39" width="10.54296875" customWidth="1"/>
+    <col min="40" max="40" width="12.54296875" style="23" customWidth="1"/>
+    <col min="41" max="41" width="10.54296875" customWidth="1"/>
+    <col min="42" max="42" width="12.54296875" customWidth="1"/>
+    <col min="43" max="43" width="10.54296875" customWidth="1"/>
+    <col min="44" max="44" width="12.54296875" style="23" customWidth="1"/>
+    <col min="45" max="45" width="10.54296875" customWidth="1"/>
+    <col min="46" max="46" width="12.54296875" style="23" customWidth="1"/>
+    <col min="47" max="47" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23875,14 +23883,14 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="39"/>
+      <c r="AS1" s="44"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="39"/>
+      <c r="AU1" s="44"/>
     </row>
-    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
       <c r="B2" s="25" t="s">
         <v>215</v>
@@ -24023,7 +24031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24186,7 +24194,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24349,7 +24357,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24512,7 +24520,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24675,7 +24683,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24838,7 +24846,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -25001,7 +25009,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25164,7 +25172,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25327,7 +25335,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25490,7 +25498,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25653,7 +25661,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25816,7 +25824,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -25979,7 +25987,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26142,7 +26150,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26305,7 +26313,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26424,6 +26432,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26435,17 +26454,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26457,16 +26465,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
@@ -26475,7 +26483,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>285</v>
       </c>
@@ -26492,9 +26500,9 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
-        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
@@ -26503,20 +26511,20 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f>C3+D3</f>
-        <v>96</v>
+        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
+        <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
-        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
@@ -26525,20 +26533,20 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f>C4+D4</f>
-        <v>92</v>
+        <f t="shared" si="1"/>
+        <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
-        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
@@ -26547,21 +26555,21 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f>C5+D5</f>
-        <v>88</v>
+        <f t="shared" si="1"/>
+        <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
-        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="str">
         <f>Wedstrijden_beheer!G1</f>
@@ -26569,20 +26577,20 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6+D6</f>
-        <v>83</v>
+        <f t="shared" si="1"/>
+        <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
-        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B7" s="1" t="str">
@@ -26591,21 +26599,21 @@
       </c>
       <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D7" s="11">
         <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f>C7+D7</f>
-        <v>83</v>
+        <f t="shared" si="1"/>
+        <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
-        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="str">
         <f>Wedstrijden_beheer!U1</f>
@@ -26613,21 +26621,21 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f>C8+D8</f>
-        <v>81</v>
+        <f t="shared" si="1"/>
+        <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
-        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
@@ -26635,21 +26643,21 @@
       </c>
       <c r="C9" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D9" s="11">
         <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f>C9+D9</f>
-        <v>79</v>
+        <f t="shared" si="1"/>
+        <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
-        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>Wedstrijden_beheer!M1</f>
@@ -26657,21 +26665,21 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f>C10+D10</f>
-        <v>79</v>
+        <f t="shared" si="1"/>
+        <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
-        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>Wedstrijden_beheer!Y1</f>
@@ -26679,21 +26687,21 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f>C11+D11</f>
-        <v>79</v>
+        <f t="shared" si="1"/>
+        <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
-        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="B12" s="1" t="str">
         <f>Wedstrijden_beheer!AU1</f>
@@ -26701,21 +26709,21 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f>C12+D12</f>
-        <v>77</v>
+        <f t="shared" si="1"/>
+        <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
-        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="B13" s="1" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
@@ -26723,21 +26731,21 @@
       </c>
       <c r="C13" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D13" s="11">
         <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f>C13+D13</f>
-        <v>77</v>
+        <f t="shared" si="1"/>
+        <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
-        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="B14" s="1" t="str">
         <f>Wedstrijden_beheer!AG1</f>
@@ -26745,21 +26753,21 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f>C14+D14</f>
-        <v>76</v>
+        <f t="shared" si="1"/>
+        <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
-        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>Wedstrijden_beheer!E1</f>
@@ -26767,21 +26775,21 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f>C15+D15</f>
-        <v>76</v>
+        <f t="shared" si="1"/>
+        <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
-        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -26789,21 +26797,21 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f>C16+D16</f>
-        <v>75</v>
+        <f t="shared" si="1"/>
+        <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
-        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -26811,21 +26819,21 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f>C17+D17</f>
-        <v>75</v>
+        <f t="shared" si="1"/>
+        <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
-        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!S1</f>
@@ -26833,21 +26841,21 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f>C18+D18</f>
-        <v>74</v>
+        <f t="shared" si="1"/>
+        <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
-        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>Wedstrijden_beheer!AO1</f>
@@ -26855,21 +26863,21 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f>C19+D19</f>
-        <v>73</v>
+        <f t="shared" si="1"/>
+        <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
-        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="str">
         <f>Wedstrijden_beheer!W1</f>
@@ -26877,21 +26885,21 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f>C20+D20</f>
-        <v>72</v>
+        <f t="shared" si="1"/>
+        <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
-        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -26899,21 +26907,21 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f>C21+D21</f>
-        <v>70</v>
+        <f t="shared" si="1"/>
+        <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
-        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!AC1</f>
@@ -26921,21 +26929,21 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f>C22+D22</f>
-        <v>68</v>
+        <f t="shared" si="1"/>
+        <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
-        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -26943,20 +26951,20 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f>C23+D23</f>
-        <v>63</v>
+        <f t="shared" si="1"/>
+        <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="11">
-        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
@@ -26965,15 +26973,15 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f>C24+D24</f>
-        <v>57</v>
+        <f t="shared" si="1"/>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -26989,20 +26997,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.7109375" hidden="1"/>
+    <col min="3" max="16384" width="8.7265625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27010,7 +27018,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27018,7 +27026,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27026,7 +27034,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27034,7 +27042,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27042,7 +27050,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27050,7 +27058,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27058,7 +27066,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27074,16 +27082,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="55.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="30.7265625" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.7109375" hidden="1"/>
+    <col min="45" max="16384" width="8.7265625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>306</v>
       </c>
@@ -27131,7 +27139,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27142,7 +27150,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27153,7 +27161,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27164,7 +27172,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27175,7 +27183,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27186,7 +27194,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27197,7 +27205,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27214,14 +27222,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="26" t="s">
         <v>319</v>
       </c>
@@ -27232,7 +27240,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27240,107 +27248,107 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
         <v>324</v>
       </c>
@@ -27351,6 +27359,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27545,27 +27573,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27582,29 +27615,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1500" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E84F76D5-954D-4A4C-BC71-B735888FE712}"/>
+  <xr:revisionPtr revIDLastSave="1504" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85EAEB5-B1BB-4644-AB6A-3227D00E60B4}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-50" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,21 +1348,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1676,76 +1676,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" customWidth="1"/>
-    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.54296875" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.54296875" customWidth="1"/>
-    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.54296875" customWidth="1"/>
-    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.54296875" customWidth="1"/>
-    <col min="21" max="21" width="12.54296875" customWidth="1"/>
-    <col min="22" max="22" width="8.54296875" customWidth="1"/>
-    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.54296875" customWidth="1"/>
-    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.54296875" customWidth="1"/>
-    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.54296875" customWidth="1"/>
-    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.54296875" customWidth="1"/>
-    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.54296875" customWidth="1"/>
-    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.54296875" customWidth="1"/>
-    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.54296875" customWidth="1"/>
-    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.54296875" customWidth="1"/>
-    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.54296875" customWidth="1"/>
-    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.54296875" customWidth="1"/>
-    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.54296875" customWidth="1"/>
-    <col min="45" max="45" width="15.7265625" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.54296875" customWidth="1"/>
-    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.5703125" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.5703125" customWidth="1"/>
+    <col min="25" max="25" width="12.5703125" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.5703125" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.5703125" customWidth="1"/>
+    <col min="29" max="29" width="12.5703125" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.5703125" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.5703125" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.5703125" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.5703125" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.5703125" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.5703125" customWidth="1"/>
+    <col min="41" max="41" width="15.5703125" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.5703125" customWidth="1"/>
+    <col min="43" max="43" width="15.5703125" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.5703125" customWidth="1"/>
+    <col min="45" max="45" width="15.7109375" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.5703125" customWidth="1"/>
+    <col min="47" max="47" width="15.5703125" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.5703125" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="44"/>
+      <c r="AT1" s="39"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="44"/>
+      <c r="AV1" s="39"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1837,10 +1837,10 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="43"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A2" s="41"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1981,61 +1981,61 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2323,7 +2323,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2787,7 +2787,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3251,7 +3251,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4243,7 +4243,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
@@ -4297,7 +4297,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5059,7 +5059,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
@@ -5113,7 +5113,7 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5699,7 +5699,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6691,7 +6691,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
@@ -6745,7 +6745,7 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7097,355 +7097,359 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
       <c r="B43" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="10"/>
+      <c r="C43" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D43" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="11" t="str">
+      <c r="F43" s="11">
         <f>IF(OR($C43="",E43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E43,FIND("-",E43)-1),"")=AW43,IFERROR(--MID(E43,FIND("-",E43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(E43,FIND("-",E43)-1),""))-(IFERROR(--MID(E43,FIND("-",E43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(E43,FIND("-",E43)-1),""))-(IFERROR(--MID(E43,FIND("-",E43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(E43,FIND("-",E43)-1),""))=(AW43))+2*((IFERROR(--MID(E43,FIND("-",E43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="11" t="str">
+      <c r="H43" s="11">
         <f>IF(OR($C43="",G43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G43,FIND("-",G43)-1),"")=AW43,IFERROR(--MID(G43,FIND("-",G43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(G43,FIND("-",G43)-1),""))-(IFERROR(--MID(G43,FIND("-",G43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(G43,FIND("-",G43)-1),""))-(IFERROR(--MID(G43,FIND("-",G43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(G43,FIND("-",G43)-1),""))=(AW43))+2*((IFERROR(--MID(G43,FIND("-",G43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="11" t="str">
+      <c r="J43" s="11">
         <f>IF(OR($C43="",I43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I43,FIND("-",I43)-1),"")=AW43,IFERROR(--MID(I43,FIND("-",I43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(I43,FIND("-",I43)-1),""))-(IFERROR(--MID(I43,FIND("-",I43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(I43,FIND("-",I43)-1),""))-(IFERROR(--MID(I43,FIND("-",I43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(I43,FIND("-",I43)-1),""))=(AW43))+2*((IFERROR(--MID(I43,FIND("-",I43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K43" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L43" s="11" t="str">
+      <c r="L43" s="11">
         <f>IF(OR($C43="",K43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K43,FIND("-",K43)-1),"")=AW43,IFERROR(--MID(K43,FIND("-",K43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(K43,FIND("-",K43)-1),""))-(IFERROR(--MID(K43,FIND("-",K43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(K43,FIND("-",K43)-1),""))-(IFERROR(--MID(K43,FIND("-",K43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(K43,FIND("-",K43)-1),""))=(AW43))+2*((IFERROR(--MID(K43,FIND("-",K43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N43" s="11" t="str">
+      <c r="N43" s="11">
         <f>IF(OR($C43="",M43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M43,FIND("-",M43)-1),"")=AW43,IFERROR(--MID(M43,FIND("-",M43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(M43,FIND("-",M43)-1),""))-(IFERROR(--MID(M43,FIND("-",M43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(M43,FIND("-",M43)-1),""))-(IFERROR(--MID(M43,FIND("-",M43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(M43,FIND("-",M43)-1),""))=(AW43))+2*((IFERROR(--MID(M43,FIND("-",M43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P43" s="11" t="str">
+      <c r="P43" s="11">
         <f>IF(OR($C43="",O43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O43,FIND("-",O43)-1),"")=AW43,IFERROR(--MID(O43,FIND("-",O43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(O43,FIND("-",O43)-1),""))-(IFERROR(--MID(O43,FIND("-",O43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(O43,FIND("-",O43)-1),""))-(IFERROR(--MID(O43,FIND("-",O43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(O43,FIND("-",O43)-1),""))=(AW43))+2*((IFERROR(--MID(O43,FIND("-",O43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="R43" s="11" t="str">
+      <c r="R43" s="11">
         <f>IF(OR($C43="",Q43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q43,FIND("-",Q43)-1),"")=AW43,IFERROR(--MID(Q43,FIND("-",Q43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(Q43,FIND("-",Q43)-1),""))-(IFERROR(--MID(Q43,FIND("-",Q43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(Q43,FIND("-",Q43)-1),""))-(IFERROR(--MID(Q43,FIND("-",Q43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(Q43,FIND("-",Q43)-1),""))=(AW43))+2*((IFERROR(--MID(Q43,FIND("-",Q43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S43" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T43" s="11" t="str">
+      <c r="T43" s="11">
         <f>IF(OR($C43="",S43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S43,FIND("-",S43)-1),"")=AW43,IFERROR(--MID(S43,FIND("-",S43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(S43,FIND("-",S43)-1),""))-(IFERROR(--MID(S43,FIND("-",S43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(S43,FIND("-",S43)-1),""))-(IFERROR(--MID(S43,FIND("-",S43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(S43,FIND("-",S43)-1),""))=(AW43))+2*((IFERROR(--MID(S43,FIND("-",S43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V43" s="11" t="str">
+      <c r="V43" s="11">
         <f>IF(OR($C43="",U43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U43,FIND("-",U43)-1),"")=AW43,IFERROR(--MID(U43,FIND("-",U43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(U43,FIND("-",U43)-1),""))-(IFERROR(--MID(U43,FIND("-",U43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(U43,FIND("-",U43)-1),""))-(IFERROR(--MID(U43,FIND("-",U43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(U43,FIND("-",U43)-1),""))=(AW43))+2*((IFERROR(--MID(U43,FIND("-",U43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X43" s="11" t="str">
+      <c r="X43" s="11">
         <f>IF(OR($C43="",W43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W43,FIND("-",W43)-1),"")=AW43,IFERROR(--MID(W43,FIND("-",W43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(W43,FIND("-",W43)-1),""))-(IFERROR(--MID(W43,FIND("-",W43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(W43,FIND("-",W43)-1),""))-(IFERROR(--MID(W43,FIND("-",W43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(W43,FIND("-",W43)-1),""))=(AW43))+2*((IFERROR(--MID(W43,FIND("-",W43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z43" s="11" t="str">
+      <c r="Z43" s="11">
         <f>IF(OR($C43="",Y43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y43,FIND("-",Y43)-1),"")=AW43,IFERROR(--MID(Y43,FIND("-",Y43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(Y43,FIND("-",Y43)-1),""))-(IFERROR(--MID(Y43,FIND("-",Y43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(Y43,FIND("-",Y43)-1),""))-(IFERROR(--MID(Y43,FIND("-",Y43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(Y43,FIND("-",Y43)-1),""))=(AW43))+2*((IFERROR(--MID(Y43,FIND("-",Y43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA43" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AB43" s="11" t="str">
+      <c r="AB43" s="11">
         <f>IF(OR($C43="",AA43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA43,FIND("-",AA43)-1),"")=AW43,IFERROR(--MID(AA43,FIND("-",AA43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AA43,FIND("-",AA43)-1),""))-(IFERROR(--MID(AA43,FIND("-",AA43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AA43,FIND("-",AA43)-1),""))-(IFERROR(--MID(AA43,FIND("-",AA43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AA43,FIND("-",AA43)-1),""))=(AW43))+2*((IFERROR(--MID(AA43,FIND("-",AA43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC43" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AD43" s="11" t="str">
+      <c r="AD43" s="11">
         <f>IF(OR($C43="",AC43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC43,FIND("-",AC43)-1),"")=AW43,IFERROR(--MID(AC43,FIND("-",AC43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AC43,FIND("-",AC43)-1),""))-(IFERROR(--MID(AC43,FIND("-",AC43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AC43,FIND("-",AC43)-1),""))-(IFERROR(--MID(AC43,FIND("-",AC43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AC43,FIND("-",AC43)-1),""))=(AW43))+2*((IFERROR(--MID(AC43,FIND("-",AC43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF43" s="11" t="str">
+      <c r="AF43" s="11">
         <f>IF(OR($C43="",AE43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE43,FIND("-",AE43)-1),"")=AW43,IFERROR(--MID(AE43,FIND("-",AE43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AE43,FIND("-",AE43)-1),""))-(IFERROR(--MID(AE43,FIND("-",AE43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AE43,FIND("-",AE43)-1),""))-(IFERROR(--MID(AE43,FIND("-",AE43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AE43,FIND("-",AE43)-1),""))=(AW43))+2*((IFERROR(--MID(AE43,FIND("-",AE43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH43" s="11" t="str">
+      <c r="AH43" s="11">
         <f>IF(OR($C43="",AG43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG43,FIND("-",AG43)-1),"")=AW43,IFERROR(--MID(AG43,FIND("-",AG43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AG43,FIND("-",AG43)-1),""))-(IFERROR(--MID(AG43,FIND("-",AG43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AG43,FIND("-",AG43)-1),""))-(IFERROR(--MID(AG43,FIND("-",AG43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AG43,FIND("-",AG43)-1),""))=(AW43))+2*((IFERROR(--MID(AG43,FIND("-",AG43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ43" s="11" t="str">
+      <c r="AJ43" s="11">
         <f>IF(OR($C43="",AI43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI43,FIND("-",AI43)-1),"")=AW43,IFERROR(--MID(AI43,FIND("-",AI43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AI43,FIND("-",AI43)-1),""))-(IFERROR(--MID(AI43,FIND("-",AI43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AI43,FIND("-",AI43)-1),""))-(IFERROR(--MID(AI43,FIND("-",AI43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AI43,FIND("-",AI43)-1),""))=(AW43))+2*((IFERROR(--MID(AI43,FIND("-",AI43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AL43" s="11" t="str">
+      <c r="AL43" s="11">
         <f>IF(OR($C43="",AK43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK43,FIND("-",AK43)-1),"")=AW43,IFERROR(--MID(AK43,FIND("-",AK43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AK43,FIND("-",AK43)-1),""))-(IFERROR(--MID(AK43,FIND("-",AK43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AK43,FIND("-",AK43)-1),""))-(IFERROR(--MID(AK43,FIND("-",AK43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AK43,FIND("-",AK43)-1),""))=(AW43))+2*((IFERROR(--MID(AK43,FIND("-",AK43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN43" s="11" t="str">
+      <c r="AN43" s="11">
         <f>IF(OR($C43="",AM43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM43,FIND("-",AM43)-1),"")=AW43,IFERROR(--MID(AM43,FIND("-",AM43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AM43,FIND("-",AM43)-1),""))-(IFERROR(--MID(AM43,FIND("-",AM43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AM43,FIND("-",AM43)-1),""))-(IFERROR(--MID(AM43,FIND("-",AM43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AM43,FIND("-",AM43)-1),""))=(AW43))+2*((IFERROR(--MID(AM43,FIND("-",AM43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO43" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AP43" s="11" t="str">
+      <c r="AP43" s="11">
         <f>IF(OR($C43="",AO43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO43,FIND("-",AO43)-1),"")=AW43,IFERROR(--MID(AO43,FIND("-",AO43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AO43,FIND("-",AO43)-1),""))-(IFERROR(--MID(AO43,FIND("-",AO43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AO43,FIND("-",AO43)-1),""))-(IFERROR(--MID(AO43,FIND("-",AO43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AO43,FIND("-",AO43)-1),""))=(AW43))+2*((IFERROR(--MID(AO43,FIND("-",AO43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ43" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR43" s="11" t="str">
+      <c r="AR43" s="11">
         <f>IF(OR($C43="",AQ43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ43,FIND("-",AQ43)-1),"")=AW43,IFERROR(--MID(AQ43,FIND("-",AQ43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AQ43,FIND("-",AQ43)-1),""))-(IFERROR(--MID(AQ43,FIND("-",AQ43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AQ43,FIND("-",AQ43)-1),""))-(IFERROR(--MID(AQ43,FIND("-",AQ43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AQ43,FIND("-",AQ43)-1),""))=(AW43))+2*((IFERROR(--MID(AQ43,FIND("-",AQ43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT43" s="11" t="str">
+      <c r="AT43" s="11">
         <f>IF(OR($C43="",AS43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS43,FIND("-",AS43)-1),"")=AW43,IFERROR(--MID(AS43,FIND("-",AS43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AS43,FIND("-",AS43)-1),""))-(IFERROR(--MID(AS43,FIND("-",AS43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AS43,FIND("-",AS43)-1),""))-(IFERROR(--MID(AS43,FIND("-",AS43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AS43,FIND("-",AS43)-1),""))=(AW43))+2*((IFERROR(--MID(AS43,FIND("-",AS43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV43" s="11" t="str">
+      <c r="AV43" s="11">
         <f>IF(OR($C43="",AU43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU43,FIND("-",AU43)-1),"")=AW43,IFERROR(--MID(AU43,FIND("-",AU43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AU43,FIND("-",AU43)-1),""))-(IFERROR(--MID(AU43,FIND("-",AU43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AU43,FIND("-",AU43)-1),""))-(IFERROR(--MID(AU43,FIND("-",AU43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AU43,FIND("-",AU43)-1),""))=(AW43))+2*((IFERROR(--MID(AU43,FIND("-",AU43)+1,99),""))=(AX43))),""))</f>
-        <v/>
-      </c>
-      <c r="AW43" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW43" s="11">
         <f>IF($C43="","",IFERROR(--LEFT($C43,FIND("-",$C43)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX43" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX43" s="11">
         <f>IF($C43="","",IFERROR(--MID($C43,FIND("-",$C43)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F44" s="11" t="str">
+      <c r="F44" s="11">
         <f>IF(OR($C44="",E44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E44,FIND("-",E44)-1),"")=AW44,IFERROR(--MID(E44,FIND("-",E44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(E44,FIND("-",E44)-1),""))-(IFERROR(--MID(E44,FIND("-",E44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(E44,FIND("-",E44)-1),""))-(IFERROR(--MID(E44,FIND("-",E44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(E44,FIND("-",E44)-1),""))=(AW44))+2*((IFERROR(--MID(E44,FIND("-",E44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H44" s="11" t="str">
+      <c r="H44" s="11">
         <f>IF(OR($C44="",G44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G44,FIND("-",G44)-1),"")=AW44,IFERROR(--MID(G44,FIND("-",G44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(G44,FIND("-",G44)-1),""))-(IFERROR(--MID(G44,FIND("-",G44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(G44,FIND("-",G44)-1),""))-(IFERROR(--MID(G44,FIND("-",G44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(G44,FIND("-",G44)-1),""))=(AW44))+2*((IFERROR(--MID(G44,FIND("-",G44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J44" s="11" t="str">
+      <c r="J44" s="11">
         <f>IF(OR($C44="",I44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I44,FIND("-",I44)-1),"")=AW44,IFERROR(--MID(I44,FIND("-",I44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(I44,FIND("-",I44)-1),""))-(IFERROR(--MID(I44,FIND("-",I44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(I44,FIND("-",I44)-1),""))-(IFERROR(--MID(I44,FIND("-",I44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(I44,FIND("-",I44)-1),""))=(AW44))+2*((IFERROR(--MID(I44,FIND("-",I44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L44" s="11" t="str">
+      <c r="L44" s="11">
         <f>IF(OR($C44="",K44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K44,FIND("-",K44)-1),"")=AW44,IFERROR(--MID(K44,FIND("-",K44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(K44,FIND("-",K44)-1),""))-(IFERROR(--MID(K44,FIND("-",K44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(K44,FIND("-",K44)-1),""))-(IFERROR(--MID(K44,FIND("-",K44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(K44,FIND("-",K44)-1),""))=(AW44))+2*((IFERROR(--MID(K44,FIND("-",K44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M44" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N44" s="11" t="str">
+      <c r="N44" s="11">
         <f>IF(OR($C44="",M44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M44,FIND("-",M44)-1),"")=AW44,IFERROR(--MID(M44,FIND("-",M44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(M44,FIND("-",M44)-1),""))-(IFERROR(--MID(M44,FIND("-",M44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(M44,FIND("-",M44)-1),""))-(IFERROR(--MID(M44,FIND("-",M44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(M44,FIND("-",M44)-1),""))=(AW44))+2*((IFERROR(--MID(M44,FIND("-",M44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O44" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P44" s="11" t="str">
+      <c r="P44" s="11">
         <f>IF(OR($C44="",O44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O44,FIND("-",O44)-1),"")=AW44,IFERROR(--MID(O44,FIND("-",O44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(O44,FIND("-",O44)-1),""))-(IFERROR(--MID(O44,FIND("-",O44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(O44,FIND("-",O44)-1),""))-(IFERROR(--MID(O44,FIND("-",O44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(O44,FIND("-",O44)-1),""))=(AW44))+2*((IFERROR(--MID(O44,FIND("-",O44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q44" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R44" s="11" t="str">
+      <c r="R44" s="11">
         <f>IF(OR($C44="",Q44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q44,FIND("-",Q44)-1),"")=AW44,IFERROR(--MID(Q44,FIND("-",Q44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(Q44,FIND("-",Q44)-1),""))-(IFERROR(--MID(Q44,FIND("-",Q44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(Q44,FIND("-",Q44)-1),""))-(IFERROR(--MID(Q44,FIND("-",Q44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(Q44,FIND("-",Q44)-1),""))=(AW44))+2*((IFERROR(--MID(Q44,FIND("-",Q44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T44" s="11" t="str">
+      <c r="T44" s="11">
         <f>IF(OR($C44="",S44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S44,FIND("-",S44)-1),"")=AW44,IFERROR(--MID(S44,FIND("-",S44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(S44,FIND("-",S44)-1),""))-(IFERROR(--MID(S44,FIND("-",S44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(S44,FIND("-",S44)-1),""))-(IFERROR(--MID(S44,FIND("-",S44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(S44,FIND("-",S44)-1),""))=(AW44))+2*((IFERROR(--MID(S44,FIND("-",S44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V44" s="11" t="str">
+      <c r="V44" s="11">
         <f>IF(OR($C44="",U44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U44,FIND("-",U44)-1),"")=AW44,IFERROR(--MID(U44,FIND("-",U44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(U44,FIND("-",U44)-1),""))-(IFERROR(--MID(U44,FIND("-",U44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(U44,FIND("-",U44)-1),""))-(IFERROR(--MID(U44,FIND("-",U44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(U44,FIND("-",U44)-1),""))=(AW44))+2*((IFERROR(--MID(U44,FIND("-",U44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W44" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X44" s="11" t="str">
+      <c r="X44" s="11">
         <f>IF(OR($C44="",W44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W44,FIND("-",W44)-1),"")=AW44,IFERROR(--MID(W44,FIND("-",W44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(W44,FIND("-",W44)-1),""))-(IFERROR(--MID(W44,FIND("-",W44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(W44,FIND("-",W44)-1),""))-(IFERROR(--MID(W44,FIND("-",W44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(W44,FIND("-",W44)-1),""))=(AW44))+2*((IFERROR(--MID(W44,FIND("-",W44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z44" s="11" t="str">
+      <c r="Z44" s="11">
         <f>IF(OR($C44="",Y44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y44,FIND("-",Y44)-1),"")=AW44,IFERROR(--MID(Y44,FIND("-",Y44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(Y44,FIND("-",Y44)-1),""))-(IFERROR(--MID(Y44,FIND("-",Y44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(Y44,FIND("-",Y44)-1),""))-(IFERROR(--MID(Y44,FIND("-",Y44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(Y44,FIND("-",Y44)-1),""))=(AW44))+2*((IFERROR(--MID(Y44,FIND("-",Y44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA44" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB44" s="11" t="str">
+      <c r="AB44" s="11">
         <f>IF(OR($C44="",AA44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA44,FIND("-",AA44)-1),"")=AW44,IFERROR(--MID(AA44,FIND("-",AA44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AA44,FIND("-",AA44)-1),""))-(IFERROR(--MID(AA44,FIND("-",AA44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AA44,FIND("-",AA44)-1),""))-(IFERROR(--MID(AA44,FIND("-",AA44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AA44,FIND("-",AA44)-1),""))=(AW44))+2*((IFERROR(--MID(AA44,FIND("-",AA44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD44" s="11" t="str">
+      <c r="AD44" s="11">
         <f>IF(OR($C44="",AC44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC44,FIND("-",AC44)-1),"")=AW44,IFERROR(--MID(AC44,FIND("-",AC44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AC44,FIND("-",AC44)-1),""))-(IFERROR(--MID(AC44,FIND("-",AC44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AC44,FIND("-",AC44)-1),""))-(IFERROR(--MID(AC44,FIND("-",AC44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AC44,FIND("-",AC44)-1),""))=(AW44))+2*((IFERROR(--MID(AC44,FIND("-",AC44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF44" s="11" t="str">
+      <c r="AF44" s="11">
         <f>IF(OR($C44="",AE44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE44,FIND("-",AE44)-1),"")=AW44,IFERROR(--MID(AE44,FIND("-",AE44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AE44,FIND("-",AE44)-1),""))-(IFERROR(--MID(AE44,FIND("-",AE44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AE44,FIND("-",AE44)-1),""))-(IFERROR(--MID(AE44,FIND("-",AE44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AE44,FIND("-",AE44)-1),""))=(AW44))+2*((IFERROR(--MID(AE44,FIND("-",AE44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH44" s="11" t="str">
+      <c r="AH44" s="11">
         <f>IF(OR($C44="",AG44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG44,FIND("-",AG44)-1),"")=AW44,IFERROR(--MID(AG44,FIND("-",AG44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AG44,FIND("-",AG44)-1),""))-(IFERROR(--MID(AG44,FIND("-",AG44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AG44,FIND("-",AG44)-1),""))-(IFERROR(--MID(AG44,FIND("-",AG44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AG44,FIND("-",AG44)-1),""))=(AW44))+2*((IFERROR(--MID(AG44,FIND("-",AG44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ44" s="11" t="str">
+      <c r="AJ44" s="11">
         <f>IF(OR($C44="",AI44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI44,FIND("-",AI44)-1),"")=AW44,IFERROR(--MID(AI44,FIND("-",AI44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AI44,FIND("-",AI44)-1),""))-(IFERROR(--MID(AI44,FIND("-",AI44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AI44,FIND("-",AI44)-1),""))-(IFERROR(--MID(AI44,FIND("-",AI44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AI44,FIND("-",AI44)-1),""))=(AW44))+2*((IFERROR(--MID(AI44,FIND("-",AI44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AL44" s="11" t="str">
+      <c r="AL44" s="11">
         <f>IF(OR($C44="",AK44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK44,FIND("-",AK44)-1),"")=AW44,IFERROR(--MID(AK44,FIND("-",AK44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AK44,FIND("-",AK44)-1),""))-(IFERROR(--MID(AK44,FIND("-",AK44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AK44,FIND("-",AK44)-1),""))-(IFERROR(--MID(AK44,FIND("-",AK44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AK44,FIND("-",AK44)-1),""))=(AW44))+2*((IFERROR(--MID(AK44,FIND("-",AK44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN44" s="11" t="str">
+      <c r="AN44" s="11">
         <f>IF(OR($C44="",AM44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM44,FIND("-",AM44)-1),"")=AW44,IFERROR(--MID(AM44,FIND("-",AM44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AM44,FIND("-",AM44)-1),""))-(IFERROR(--MID(AM44,FIND("-",AM44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AM44,FIND("-",AM44)-1),""))-(IFERROR(--MID(AM44,FIND("-",AM44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AM44,FIND("-",AM44)-1),""))=(AW44))+2*((IFERROR(--MID(AM44,FIND("-",AM44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP44" s="11" t="str">
+      <c r="AP44" s="11">
         <f>IF(OR($C44="",AO44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO44,FIND("-",AO44)-1),"")=AW44,IFERROR(--MID(AO44,FIND("-",AO44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AO44,FIND("-",AO44)-1),""))-(IFERROR(--MID(AO44,FIND("-",AO44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AO44,FIND("-",AO44)-1),""))-(IFERROR(--MID(AO44,FIND("-",AO44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AO44,FIND("-",AO44)-1),""))=(AW44))+2*((IFERROR(--MID(AO44,FIND("-",AO44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR44" s="11" t="str">
+      <c r="AR44" s="11">
         <f>IF(OR($C44="",AQ44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ44,FIND("-",AQ44)-1),"")=AW44,IFERROR(--MID(AQ44,FIND("-",AQ44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AQ44,FIND("-",AQ44)-1),""))-(IFERROR(--MID(AQ44,FIND("-",AQ44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AQ44,FIND("-",AQ44)-1),""))-(IFERROR(--MID(AQ44,FIND("-",AQ44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AQ44,FIND("-",AQ44)-1),""))=(AW44))+2*((IFERROR(--MID(AQ44,FIND("-",AQ44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS44" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT44" s="11" t="str">
+      <c r="AT44" s="11">
         <f>IF(OR($C44="",AS44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS44,FIND("-",AS44)-1),"")=AW44,IFERROR(--MID(AS44,FIND("-",AS44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AS44,FIND("-",AS44)-1),""))-(IFERROR(--MID(AS44,FIND("-",AS44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AS44,FIND("-",AS44)-1),""))-(IFERROR(--MID(AS44,FIND("-",AS44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AS44,FIND("-",AS44)-1),""))=(AW44))+2*((IFERROR(--MID(AS44,FIND("-",AS44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AV44" s="11" t="str">
+      <c r="AV44" s="11">
         <f>IF(OR($C44="",AU44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU44,FIND("-",AU44)-1),"")=AW44,IFERROR(--MID(AU44,FIND("-",AU44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AU44,FIND("-",AU44)-1),""))-(IFERROR(--MID(AU44,FIND("-",AU44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AU44,FIND("-",AU44)-1),""))-(IFERROR(--MID(AU44,FIND("-",AU44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AU44,FIND("-",AU44)-1),""))=(AW44))+2*((IFERROR(--MID(AU44,FIND("-",AU44)+1,99),""))=(AX44))),""))</f>
-        <v/>
-      </c>
-      <c r="AW44" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW44" s="11">
         <f>IF($C44="","",IFERROR(--LEFT($C44,FIND("-",$C44)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX44" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX44" s="11">
         <f>IF($C44="","",IFERROR(--MID($C44,FIND("-",$C44)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="18"/>
       <c r="C45" s="13"/>
@@ -7503,7 +7507,7 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
@@ -7557,355 +7561,359 @@
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>1</v>
       </c>
       <c r="B47" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="D47" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F47" s="11" t="str">
+      <c r="F47" s="11">
         <f>IF(OR($C47="",E47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E47,FIND("-",E47)-1),"")=AW47,IFERROR(--MID(E47,FIND("-",E47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(E47,FIND("-",E47)-1),""))-(IFERROR(--MID(E47,FIND("-",E47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(E47,FIND("-",E47)-1),""))-(IFERROR(--MID(E47,FIND("-",E47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(E47,FIND("-",E47)-1),""))=(AW47))+2*((IFERROR(--MID(E47,FIND("-",E47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H47" s="11" t="str">
+      <c r="H47" s="11">
         <f>IF(OR($C47="",G47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G47,FIND("-",G47)-1),"")=AW47,IFERROR(--MID(G47,FIND("-",G47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(G47,FIND("-",G47)-1),""))-(IFERROR(--MID(G47,FIND("-",G47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(G47,FIND("-",G47)-1),""))-(IFERROR(--MID(G47,FIND("-",G47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(G47,FIND("-",G47)-1),""))=(AW47))+2*((IFERROR(--MID(G47,FIND("-",G47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J47" s="11" t="str">
+      <c r="J47" s="11">
         <f>IF(OR($C47="",I47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I47,FIND("-",I47)-1),"")=AW47,IFERROR(--MID(I47,FIND("-",I47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(I47,FIND("-",I47)-1),""))-(IFERROR(--MID(I47,FIND("-",I47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(I47,FIND("-",I47)-1),""))-(IFERROR(--MID(I47,FIND("-",I47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(I47,FIND("-",I47)-1),""))=(AW47))+2*((IFERROR(--MID(I47,FIND("-",I47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L47" s="11" t="str">
+      <c r="L47" s="11">
         <f>IF(OR($C47="",K47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K47,FIND("-",K47)-1),"")=AW47,IFERROR(--MID(K47,FIND("-",K47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(K47,FIND("-",K47)-1),""))-(IFERROR(--MID(K47,FIND("-",K47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(K47,FIND("-",K47)-1),""))-(IFERROR(--MID(K47,FIND("-",K47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(K47,FIND("-",K47)-1),""))=(AW47))+2*((IFERROR(--MID(K47,FIND("-",K47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N47" s="11" t="str">
+      <c r="N47" s="11">
         <f>IF(OR($C47="",M47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M47,FIND("-",M47)-1),"")=AW47,IFERROR(--MID(M47,FIND("-",M47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(M47,FIND("-",M47)-1),""))-(IFERROR(--MID(M47,FIND("-",M47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(M47,FIND("-",M47)-1),""))-(IFERROR(--MID(M47,FIND("-",M47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(M47,FIND("-",M47)-1),""))=(AW47))+2*((IFERROR(--MID(M47,FIND("-",M47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P47" s="11" t="str">
+      <c r="P47" s="11">
         <f>IF(OR($C47="",O47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O47,FIND("-",O47)-1),"")=AW47,IFERROR(--MID(O47,FIND("-",O47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(O47,FIND("-",O47)-1),""))-(IFERROR(--MID(O47,FIND("-",O47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(O47,FIND("-",O47)-1),""))-(IFERROR(--MID(O47,FIND("-",O47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(O47,FIND("-",O47)-1),""))=(AW47))+2*((IFERROR(--MID(O47,FIND("-",O47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R47" s="11" t="str">
+      <c r="R47" s="11">
         <f>IF(OR($C47="",Q47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q47,FIND("-",Q47)-1),"")=AW47,IFERROR(--MID(Q47,FIND("-",Q47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(Q47,FIND("-",Q47)-1),""))-(IFERROR(--MID(Q47,FIND("-",Q47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(Q47,FIND("-",Q47)-1),""))-(IFERROR(--MID(Q47,FIND("-",Q47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(Q47,FIND("-",Q47)-1),""))=(AW47))+2*((IFERROR(--MID(Q47,FIND("-",Q47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S47" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T47" s="11" t="str">
+      <c r="T47" s="11">
         <f>IF(OR($C47="",S47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S47,FIND("-",S47)-1),"")=AW47,IFERROR(--MID(S47,FIND("-",S47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(S47,FIND("-",S47)-1),""))-(IFERROR(--MID(S47,FIND("-",S47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(S47,FIND("-",S47)-1),""))-(IFERROR(--MID(S47,FIND("-",S47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(S47,FIND("-",S47)-1),""))=(AW47))+2*((IFERROR(--MID(S47,FIND("-",S47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V47" s="11" t="str">
+      <c r="V47" s="11">
         <f>IF(OR($C47="",U47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U47,FIND("-",U47)-1),"")=AW47,IFERROR(--MID(U47,FIND("-",U47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(U47,FIND("-",U47)-1),""))-(IFERROR(--MID(U47,FIND("-",U47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(U47,FIND("-",U47)-1),""))-(IFERROR(--MID(U47,FIND("-",U47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(U47,FIND("-",U47)-1),""))=(AW47))+2*((IFERROR(--MID(U47,FIND("-",U47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W47" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X47" s="11" t="str">
+      <c r="X47" s="11">
         <f>IF(OR($C47="",W47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W47,FIND("-",W47)-1),"")=AW47,IFERROR(--MID(W47,FIND("-",W47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(W47,FIND("-",W47)-1),""))-(IFERROR(--MID(W47,FIND("-",W47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(W47,FIND("-",W47)-1),""))-(IFERROR(--MID(W47,FIND("-",W47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(W47,FIND("-",W47)-1),""))=(AW47))+2*((IFERROR(--MID(W47,FIND("-",W47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y47" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="Z47" s="11" t="str">
+      <c r="Z47" s="11">
         <f>IF(OR($C47="",Y47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y47,FIND("-",Y47)-1),"")=AW47,IFERROR(--MID(Y47,FIND("-",Y47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(Y47,FIND("-",Y47)-1),""))-(IFERROR(--MID(Y47,FIND("-",Y47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(Y47,FIND("-",Y47)-1),""))-(IFERROR(--MID(Y47,FIND("-",Y47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(Y47,FIND("-",Y47)-1),""))=(AW47))+2*((IFERROR(--MID(Y47,FIND("-",Y47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AB47" s="11" t="str">
+      <c r="AB47" s="11">
         <f>IF(OR($C47="",AA47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA47,FIND("-",AA47)-1),"")=AW47,IFERROR(--MID(AA47,FIND("-",AA47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AA47,FIND("-",AA47)-1),""))-(IFERROR(--MID(AA47,FIND("-",AA47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AA47,FIND("-",AA47)-1),""))-(IFERROR(--MID(AA47,FIND("-",AA47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AA47,FIND("-",AA47)-1),""))=(AW47))+2*((IFERROR(--MID(AA47,FIND("-",AA47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC47" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD47" s="11" t="str">
+      <c r="AD47" s="11">
         <f>IF(OR($C47="",AC47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC47,FIND("-",AC47)-1),"")=AW47,IFERROR(--MID(AC47,FIND("-",AC47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AC47,FIND("-",AC47)-1),""))-(IFERROR(--MID(AC47,FIND("-",AC47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AC47,FIND("-",AC47)-1),""))-(IFERROR(--MID(AC47,FIND("-",AC47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AC47,FIND("-",AC47)-1),""))=(AW47))+2*((IFERROR(--MID(AC47,FIND("-",AC47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF47" s="11" t="str">
+      <c r="AF47" s="11">
         <f>IF(OR($C47="",AE47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE47,FIND("-",AE47)-1),"")=AW47,IFERROR(--MID(AE47,FIND("-",AE47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AE47,FIND("-",AE47)-1),""))-(IFERROR(--MID(AE47,FIND("-",AE47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AE47,FIND("-",AE47)-1),""))-(IFERROR(--MID(AE47,FIND("-",AE47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AE47,FIND("-",AE47)-1),""))=(AW47))+2*((IFERROR(--MID(AE47,FIND("-",AE47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG47" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AH47" s="11" t="str">
+      <c r="AH47" s="11">
         <f>IF(OR($C47="",AG47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG47,FIND("-",AG47)-1),"")=AW47,IFERROR(--MID(AG47,FIND("-",AG47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AG47,FIND("-",AG47)-1),""))-(IFERROR(--MID(AG47,FIND("-",AG47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AG47,FIND("-",AG47)-1),""))-(IFERROR(--MID(AG47,FIND("-",AG47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AG47,FIND("-",AG47)-1),""))=(AW47))+2*((IFERROR(--MID(AG47,FIND("-",AG47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ47" s="11" t="str">
+      <c r="AJ47" s="11">
         <f>IF(OR($C47="",AI47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI47,FIND("-",AI47)-1),"")=AW47,IFERROR(--MID(AI47,FIND("-",AI47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AI47,FIND("-",AI47)-1),""))-(IFERROR(--MID(AI47,FIND("-",AI47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AI47,FIND("-",AI47)-1),""))-(IFERROR(--MID(AI47,FIND("-",AI47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AI47,FIND("-",AI47)-1),""))=(AW47))+2*((IFERROR(--MID(AI47,FIND("-",AI47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AL47" s="11" t="str">
+      <c r="AL47" s="11">
         <f>IF(OR($C47="",AK47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK47,FIND("-",AK47)-1),"")=AW47,IFERROR(--MID(AK47,FIND("-",AK47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AK47,FIND("-",AK47)-1),""))-(IFERROR(--MID(AK47,FIND("-",AK47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AK47,FIND("-",AK47)-1),""))-(IFERROR(--MID(AK47,FIND("-",AK47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AK47,FIND("-",AK47)-1),""))=(AW47))+2*((IFERROR(--MID(AK47,FIND("-",AK47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM47" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AN47" s="11" t="str">
+      <c r="AN47" s="11">
         <f>IF(OR($C47="",AM47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM47,FIND("-",AM47)-1),"")=AW47,IFERROR(--MID(AM47,FIND("-",AM47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AM47,FIND("-",AM47)-1),""))-(IFERROR(--MID(AM47,FIND("-",AM47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AM47,FIND("-",AM47)-1),""))-(IFERROR(--MID(AM47,FIND("-",AM47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AM47,FIND("-",AM47)-1),""))=(AW47))+2*((IFERROR(--MID(AM47,FIND("-",AM47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP47" s="11" t="str">
+      <c r="AP47" s="11">
         <f>IF(OR($C47="",AO47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO47,FIND("-",AO47)-1),"")=AW47,IFERROR(--MID(AO47,FIND("-",AO47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AO47,FIND("-",AO47)-1),""))-(IFERROR(--MID(AO47,FIND("-",AO47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AO47,FIND("-",AO47)-1),""))-(IFERROR(--MID(AO47,FIND("-",AO47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AO47,FIND("-",AO47)-1),""))=(AW47))+2*((IFERROR(--MID(AO47,FIND("-",AO47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ47" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR47" s="11" t="str">
+      <c r="AR47" s="11">
         <f>IF(OR($C47="",AQ47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ47,FIND("-",AQ47)-1),"")=AW47,IFERROR(--MID(AQ47,FIND("-",AQ47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AQ47,FIND("-",AQ47)-1),""))-(IFERROR(--MID(AQ47,FIND("-",AQ47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AQ47,FIND("-",AQ47)-1),""))-(IFERROR(--MID(AQ47,FIND("-",AQ47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AQ47,FIND("-",AQ47)-1),""))=(AW47))+2*((IFERROR(--MID(AQ47,FIND("-",AQ47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AT47" s="11" t="str">
+      <c r="AT47" s="11">
         <f>IF(OR($C47="",AS47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS47,FIND("-",AS47)-1),"")=AW47,IFERROR(--MID(AS47,FIND("-",AS47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AS47,FIND("-",AS47)-1),""))-(IFERROR(--MID(AS47,FIND("-",AS47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AS47,FIND("-",AS47)-1),""))-(IFERROR(--MID(AS47,FIND("-",AS47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AS47,FIND("-",AS47)-1),""))=(AW47))+2*((IFERROR(--MID(AS47,FIND("-",AS47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU47" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV47" s="11" t="str">
+      <c r="AV47" s="11">
         <f>IF(OR($C47="",AU47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU47,FIND("-",AU47)-1),"")=AW47,IFERROR(--MID(AU47,FIND("-",AU47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AU47,FIND("-",AU47)-1),""))-(IFERROR(--MID(AU47,FIND("-",AU47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AU47,FIND("-",AU47)-1),""))-(IFERROR(--MID(AU47,FIND("-",AU47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AU47,FIND("-",AU47)-1),""))=(AW47))+2*((IFERROR(--MID(AU47,FIND("-",AU47)+1,99),""))=(AX47))),""))</f>
-        <v/>
-      </c>
-      <c r="AW47" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW47" s="11">
         <f>IF($C47="","",IFERROR(--LEFT($C47,FIND("-",$C47)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX47" s="11" t="str">
+        <v>6</v>
+      </c>
+      <c r="AX47" s="11">
         <f>IF($C47="","",IFERROR(--MID($C47,FIND("-",$C47)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
       <c r="B48" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F48" s="11" t="str">
+      <c r="F48" s="11">
         <f>IF(OR($C48="",E48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E48,FIND("-",E48)-1),"")=AW48,IFERROR(--MID(E48,FIND("-",E48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(E48,FIND("-",E48)-1),""))-(IFERROR(--MID(E48,FIND("-",E48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(E48,FIND("-",E48)-1),""))-(IFERROR(--MID(E48,FIND("-",E48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(E48,FIND("-",E48)-1),""))=(AW48))+2*((IFERROR(--MID(E48,FIND("-",E48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H48" s="11" t="str">
+      <c r="H48" s="11">
         <f>IF(OR($C48="",G48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G48,FIND("-",G48)-1),"")=AW48,IFERROR(--MID(G48,FIND("-",G48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(G48,FIND("-",G48)-1),""))-(IFERROR(--MID(G48,FIND("-",G48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(G48,FIND("-",G48)-1),""))-(IFERROR(--MID(G48,FIND("-",G48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(G48,FIND("-",G48)-1),""))=(AW48))+2*((IFERROR(--MID(G48,FIND("-",G48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J48" s="11" t="str">
+      <c r="J48" s="11">
         <f>IF(OR($C48="",I48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I48,FIND("-",I48)-1),"")=AW48,IFERROR(--MID(I48,FIND("-",I48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(I48,FIND("-",I48)-1),""))-(IFERROR(--MID(I48,FIND("-",I48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(I48,FIND("-",I48)-1),""))-(IFERROR(--MID(I48,FIND("-",I48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(I48,FIND("-",I48)-1),""))=(AW48))+2*((IFERROR(--MID(I48,FIND("-",I48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K48" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L48" s="11" t="str">
+      <c r="L48" s="11">
         <f>IF(OR($C48="",K48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K48,FIND("-",K48)-1),"")=AW48,IFERROR(--MID(K48,FIND("-",K48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(K48,FIND("-",K48)-1),""))-(IFERROR(--MID(K48,FIND("-",K48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(K48,FIND("-",K48)-1),""))-(IFERROR(--MID(K48,FIND("-",K48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(K48,FIND("-",K48)-1),""))=(AW48))+2*((IFERROR(--MID(K48,FIND("-",K48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N48" s="11" t="str">
+      <c r="N48" s="11">
         <f>IF(OR($C48="",M48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M48,FIND("-",M48)-1),"")=AW48,IFERROR(--MID(M48,FIND("-",M48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(M48,FIND("-",M48)-1),""))-(IFERROR(--MID(M48,FIND("-",M48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(M48,FIND("-",M48)-1),""))-(IFERROR(--MID(M48,FIND("-",M48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(M48,FIND("-",M48)-1),""))=(AW48))+2*((IFERROR(--MID(M48,FIND("-",M48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P48" s="11" t="str">
+      <c r="P48" s="11">
         <f>IF(OR($C48="",O48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O48,FIND("-",O48)-1),"")=AW48,IFERROR(--MID(O48,FIND("-",O48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(O48,FIND("-",O48)-1),""))-(IFERROR(--MID(O48,FIND("-",O48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(O48,FIND("-",O48)-1),""))-(IFERROR(--MID(O48,FIND("-",O48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(O48,FIND("-",O48)-1),""))=(AW48))+2*((IFERROR(--MID(O48,FIND("-",O48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="R48" s="11" t="str">
+      <c r="R48" s="11">
         <f>IF(OR($C48="",Q48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q48,FIND("-",Q48)-1),"")=AW48,IFERROR(--MID(Q48,FIND("-",Q48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(Q48,FIND("-",Q48)-1),""))-(IFERROR(--MID(Q48,FIND("-",Q48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(Q48,FIND("-",Q48)-1),""))-(IFERROR(--MID(Q48,FIND("-",Q48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(Q48,FIND("-",Q48)-1),""))=(AW48))+2*((IFERROR(--MID(Q48,FIND("-",Q48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S48" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="T48" s="11" t="str">
+      <c r="T48" s="11">
         <f>IF(OR($C48="",S48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S48,FIND("-",S48)-1),"")=AW48,IFERROR(--MID(S48,FIND("-",S48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(S48,FIND("-",S48)-1),""))-(IFERROR(--MID(S48,FIND("-",S48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(S48,FIND("-",S48)-1),""))-(IFERROR(--MID(S48,FIND("-",S48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(S48,FIND("-",S48)-1),""))=(AW48))+2*((IFERROR(--MID(S48,FIND("-",S48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V48" s="11" t="str">
+      <c r="V48" s="11">
         <f>IF(OR($C48="",U48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U48,FIND("-",U48)-1),"")=AW48,IFERROR(--MID(U48,FIND("-",U48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(U48,FIND("-",U48)-1),""))-(IFERROR(--MID(U48,FIND("-",U48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(U48,FIND("-",U48)-1),""))-(IFERROR(--MID(U48,FIND("-",U48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(U48,FIND("-",U48)-1),""))=(AW48))+2*((IFERROR(--MID(U48,FIND("-",U48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W48" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X48" s="11" t="str">
+      <c r="X48" s="11">
         <f>IF(OR($C48="",W48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W48,FIND("-",W48)-1),"")=AW48,IFERROR(--MID(W48,FIND("-",W48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(W48,FIND("-",W48)-1),""))-(IFERROR(--MID(W48,FIND("-",W48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(W48,FIND("-",W48)-1),""))-(IFERROR(--MID(W48,FIND("-",W48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(W48,FIND("-",W48)-1),""))=(AW48))+2*((IFERROR(--MID(W48,FIND("-",W48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z48" s="11" t="str">
+      <c r="Z48" s="11">
         <f>IF(OR($C48="",Y48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y48,FIND("-",Y48)-1),"")=AW48,IFERROR(--MID(Y48,FIND("-",Y48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(Y48,FIND("-",Y48)-1),""))-(IFERROR(--MID(Y48,FIND("-",Y48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(Y48,FIND("-",Y48)-1),""))-(IFERROR(--MID(Y48,FIND("-",Y48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(Y48,FIND("-",Y48)-1),""))=(AW48))+2*((IFERROR(--MID(Y48,FIND("-",Y48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AB48" s="11" t="str">
+      <c r="AB48" s="11">
         <f>IF(OR($C48="",AA48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA48,FIND("-",AA48)-1),"")=AW48,IFERROR(--MID(AA48,FIND("-",AA48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AA48,FIND("-",AA48)-1),""))-(IFERROR(--MID(AA48,FIND("-",AA48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AA48,FIND("-",AA48)-1),""))-(IFERROR(--MID(AA48,FIND("-",AA48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AA48,FIND("-",AA48)-1),""))=(AW48))+2*((IFERROR(--MID(AA48,FIND("-",AA48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD48" s="11" t="str">
+      <c r="AD48" s="11">
         <f>IF(OR($C48="",AC48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC48,FIND("-",AC48)-1),"")=AW48,IFERROR(--MID(AC48,FIND("-",AC48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AC48,FIND("-",AC48)-1),""))-(IFERROR(--MID(AC48,FIND("-",AC48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AC48,FIND("-",AC48)-1),""))-(IFERROR(--MID(AC48,FIND("-",AC48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AC48,FIND("-",AC48)-1),""))=(AW48))+2*((IFERROR(--MID(AC48,FIND("-",AC48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF48" s="11" t="str">
+      <c r="AF48" s="11">
         <f>IF(OR($C48="",AE48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE48,FIND("-",AE48)-1),"")=AW48,IFERROR(--MID(AE48,FIND("-",AE48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AE48,FIND("-",AE48)-1),""))-(IFERROR(--MID(AE48,FIND("-",AE48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AE48,FIND("-",AE48)-1),""))-(IFERROR(--MID(AE48,FIND("-",AE48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AE48,FIND("-",AE48)-1),""))=(AW48))+2*((IFERROR(--MID(AE48,FIND("-",AE48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG48" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH48" s="11" t="str">
+      <c r="AH48" s="11">
         <f>IF(OR($C48="",AG48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG48,FIND("-",AG48)-1),"")=AW48,IFERROR(--MID(AG48,FIND("-",AG48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AG48,FIND("-",AG48)-1),""))-(IFERROR(--MID(AG48,FIND("-",AG48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AG48,FIND("-",AG48)-1),""))-(IFERROR(--MID(AG48,FIND("-",AG48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AG48,FIND("-",AG48)-1),""))=(AW48))+2*((IFERROR(--MID(AG48,FIND("-",AG48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AJ48" s="11" t="str">
+      <c r="AJ48" s="11">
         <f>IF(OR($C48="",AI48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI48,FIND("-",AI48)-1),"")=AW48,IFERROR(--MID(AI48,FIND("-",AI48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AI48,FIND("-",AI48)-1),""))-(IFERROR(--MID(AI48,FIND("-",AI48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AI48,FIND("-",AI48)-1),""))-(IFERROR(--MID(AI48,FIND("-",AI48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AI48,FIND("-",AI48)-1),""))=(AW48))+2*((IFERROR(--MID(AI48,FIND("-",AI48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL48" s="11" t="str">
+      <c r="AL48" s="11">
         <f>IF(OR($C48="",AK48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK48,FIND("-",AK48)-1),"")=AW48,IFERROR(--MID(AK48,FIND("-",AK48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AK48,FIND("-",AK48)-1),""))-(IFERROR(--MID(AK48,FIND("-",AK48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AK48,FIND("-",AK48)-1),""))-(IFERROR(--MID(AK48,FIND("-",AK48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AK48,FIND("-",AK48)-1),""))=(AW48))+2*((IFERROR(--MID(AK48,FIND("-",AK48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM48" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AN48" s="11" t="str">
+      <c r="AN48" s="11">
         <f>IF(OR($C48="",AM48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM48,FIND("-",AM48)-1),"")=AW48,IFERROR(--MID(AM48,FIND("-",AM48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AM48,FIND("-",AM48)-1),""))-(IFERROR(--MID(AM48,FIND("-",AM48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AM48,FIND("-",AM48)-1),""))-(IFERROR(--MID(AM48,FIND("-",AM48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AM48,FIND("-",AM48)-1),""))=(AW48))+2*((IFERROR(--MID(AM48,FIND("-",AM48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO48" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP48" s="11" t="str">
+      <c r="AP48" s="11">
         <f>IF(OR($C48="",AO48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO48,FIND("-",AO48)-1),"")=AW48,IFERROR(--MID(AO48,FIND("-",AO48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AO48,FIND("-",AO48)-1),""))-(IFERROR(--MID(AO48,FIND("-",AO48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AO48,FIND("-",AO48)-1),""))-(IFERROR(--MID(AO48,FIND("-",AO48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AO48,FIND("-",AO48)-1),""))=(AW48))+2*((IFERROR(--MID(AO48,FIND("-",AO48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR48" s="11" t="str">
+      <c r="AR48" s="11">
         <f>IF(OR($C48="",AQ48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ48,FIND("-",AQ48)-1),"")=AW48,IFERROR(--MID(AQ48,FIND("-",AQ48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AQ48,FIND("-",AQ48)-1),""))-(IFERROR(--MID(AQ48,FIND("-",AQ48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AQ48,FIND("-",AQ48)-1),""))-(IFERROR(--MID(AQ48,FIND("-",AQ48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AQ48,FIND("-",AQ48)-1),""))=(AW48))+2*((IFERROR(--MID(AQ48,FIND("-",AQ48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AT48" s="11" t="str">
+      <c r="AT48" s="11">
         <f>IF(OR($C48="",AS48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS48,FIND("-",AS48)-1),"")=AW48,IFERROR(--MID(AS48,FIND("-",AS48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AS48,FIND("-",AS48)-1),""))-(IFERROR(--MID(AS48,FIND("-",AS48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AS48,FIND("-",AS48)-1),""))-(IFERROR(--MID(AS48,FIND("-",AS48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AS48,FIND("-",AS48)-1),""))=(AW48))+2*((IFERROR(--MID(AS48,FIND("-",AS48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU48" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AV48" s="11" t="str">
+      <c r="AV48" s="11">
         <f>IF(OR($C48="",AU48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU48,FIND("-",AU48)-1),"")=AW48,IFERROR(--MID(AU48,FIND("-",AU48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AU48,FIND("-",AU48)-1),""))-(IFERROR(--MID(AU48,FIND("-",AU48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AU48,FIND("-",AU48)-1),""))-(IFERROR(--MID(AU48,FIND("-",AU48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AU48,FIND("-",AU48)-1),""))=(AW48))+2*((IFERROR(--MID(AU48,FIND("-",AU48)+1,99),""))=(AX48))),""))</f>
-        <v/>
-      </c>
-      <c r="AW48" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW48" s="11">
         <f>IF($C48="","",IFERROR(--LEFT($C48,FIND("-",$C48)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX48" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX48" s="11">
         <f>IF($C48="","",IFERROR(--MID($C48,FIND("-",$C48)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8079,7 +8087,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="18"/>
       <c r="C50" s="13"/>
@@ -8137,7 +8145,7 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
@@ -8191,7 +8199,7 @@
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8365,7 +8373,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8539,7 +8547,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8713,7 +8721,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8887,7 +8895,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9061,7 +9069,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="18"/>
       <c r="C57" s="13"/>
@@ -9119,7 +9127,7 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
@@ -9173,7 +9181,7 @@
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9347,7 +9355,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9521,7 +9529,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9695,7 +9703,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9869,7 +9877,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12"/>
       <c r="B63" s="18"/>
       <c r="C63" s="13"/>
@@ -9927,7 +9935,7 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
@@ -9981,7 +9989,7 @@
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10155,7 +10163,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10329,7 +10337,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10503,7 +10511,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10677,7 +10685,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="18"/>
       <c r="C69" s="13"/>
@@ -10735,7 +10743,7 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
@@ -10789,7 +10797,7 @@
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -10963,7 +10971,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11137,7 +11145,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11311,7 +11319,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11485,7 +11493,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="18"/>
       <c r="C75" s="13"/>
@@ -11543,7 +11551,7 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
@@ -11597,7 +11605,7 @@
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11771,7 +11779,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -11945,7 +11953,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12119,7 +12127,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12293,7 +12301,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="18"/>
       <c r="C81" s="13"/>
@@ -12351,7 +12359,7 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
@@ -12405,7 +12413,7 @@
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12579,7 +12587,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12753,7 +12761,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -12927,7 +12935,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13101,7 +13109,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13275,7 +13283,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13449,7 +13457,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="18"/>
       <c r="C89" s="13"/>
@@ -13507,7 +13515,7 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
@@ -13561,7 +13569,7 @@
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13735,7 +13743,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13909,7 +13917,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14083,7 +14091,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14257,7 +14265,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14431,7 +14439,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14605,7 +14613,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="18"/>
       <c r="C97" s="13"/>
@@ -14663,7 +14671,7 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
@@ -14717,7 +14725,7 @@
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14891,7 +14899,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15065,7 +15073,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15239,7 +15247,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15413,7 +15421,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15587,7 +15595,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15761,7 +15769,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="12"/>
       <c r="B105" s="18"/>
       <c r="C105" s="13"/>
@@ -15819,7 +15827,7 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
@@ -15873,7 +15881,7 @@
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16047,7 +16055,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16221,7 +16229,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16395,7 +16403,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16569,7 +16577,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12"/>
       <c r="B111" s="18"/>
       <c r="C111" s="13"/>
@@ -16627,7 +16635,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12"/>
       <c r="B112" s="18"/>
       <c r="C112" s="13"/>
@@ -16685,7 +16693,7 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="38" t="s">
         <v>128</v>
       </c>
@@ -16739,7 +16747,7 @@
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
@@ -16793,7 +16801,7 @@
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -16923,7 +16931,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12"/>
       <c r="B116" s="18"/>
       <c r="C116" s="13"/>
@@ -16981,7 +16989,7 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
@@ -17035,7 +17043,7 @@
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17165,7 +17173,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17295,7 +17303,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12"/>
       <c r="B120" s="18"/>
       <c r="C120" s="13"/>
@@ -17353,7 +17361,7 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
@@ -17407,7 +17415,7 @@
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17537,7 +17545,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17667,7 +17675,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17797,7 +17805,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12"/>
       <c r="B125" s="18"/>
       <c r="C125" s="13"/>
@@ -17855,7 +17863,7 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
@@ -17909,7 +17917,7 @@
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18039,7 +18047,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18169,7 +18177,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18299,7 +18307,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="18"/>
       <c r="C130" s="13"/>
@@ -18357,7 +18365,7 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
@@ -18411,7 +18419,7 @@
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18541,7 +18549,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18671,7 +18679,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="18"/>
       <c r="C134" s="13"/>
@@ -18729,7 +18737,7 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
@@ -18783,7 +18791,7 @@
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -18913,7 +18921,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19043,7 +19051,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19173,7 +19181,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12"/>
       <c r="B139" s="18"/>
       <c r="C139" s="13"/>
@@ -19231,7 +19239,7 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
@@ -19285,7 +19293,7 @@
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19415,7 +19423,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19545,7 +19553,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12"/>
       <c r="B143" s="18"/>
       <c r="C143" s="13"/>
@@ -19603,7 +19611,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12"/>
       <c r="B144" s="18"/>
       <c r="C144" s="13"/>
@@ -19661,7 +19669,7 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="38" t="s">
         <v>167</v>
       </c>
@@ -19715,7 +19723,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
@@ -19769,7 +19777,7 @@
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19899,7 +19907,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20029,7 +20037,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12"/>
       <c r="B149" s="18"/>
       <c r="C149" s="13"/>
@@ -20087,7 +20095,7 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
@@ -20141,7 +20149,7 @@
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20271,7 +20279,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12"/>
       <c r="B152" s="18"/>
       <c r="C152" s="13"/>
@@ -20329,7 +20337,7 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
@@ -20383,7 +20391,7 @@
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20513,7 +20521,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20643,7 +20651,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12"/>
       <c r="B156" s="18"/>
       <c r="C156" s="13"/>
@@ -20701,7 +20709,7 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
@@ -20755,7 +20763,7 @@
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20885,7 +20893,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -21015,7 +21023,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21145,7 +21153,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12"/>
       <c r="B161" s="18"/>
       <c r="C161" s="13"/>
@@ -21203,7 +21211,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12"/>
       <c r="B162" s="18"/>
       <c r="C162" s="13"/>
@@ -21261,7 +21269,7 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="38" t="s">
         <v>187</v>
       </c>
@@ -21315,7 +21323,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
@@ -21369,7 +21377,7 @@
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21499,7 +21507,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12"/>
       <c r="B166" s="18"/>
       <c r="C166" s="13"/>
@@ -21557,7 +21565,7 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
@@ -21611,7 +21619,7 @@
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21741,7 +21749,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
       <c r="B169" s="18"/>
       <c r="C169" s="13"/>
@@ -21799,7 +21807,7 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
@@ -21853,7 +21861,7 @@
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -21983,7 +21991,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="18"/>
       <c r="C172" s="13"/>
@@ -22041,7 +22049,7 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
@@ -22095,7 +22103,7 @@
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22225,7 +22233,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12"/>
       <c r="B175" s="18"/>
       <c r="C175" s="13"/>
@@ -22283,7 +22291,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12"/>
       <c r="B176" s="18"/>
       <c r="C176" s="13"/>
@@ -22341,7 +22349,7 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="38" t="s">
         <v>200</v>
       </c>
@@ -22395,7 +22403,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
@@ -22449,7 +22457,7 @@
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22579,7 +22587,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12"/>
       <c r="B180" s="18"/>
       <c r="C180" s="13"/>
@@ -22637,7 +22645,7 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
@@ -22691,7 +22699,7 @@
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22821,7 +22829,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12"/>
       <c r="B183" s="18"/>
       <c r="C183" s="13"/>
@@ -22879,7 +22887,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12"/>
       <c r="B184" s="18"/>
       <c r="C184" s="13"/>
@@ -22937,7 +22945,7 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="38" t="s">
         <v>207</v>
       </c>
@@ -22991,7 +22999,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
@@ -23045,7 +23053,7 @@
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23175,7 +23183,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12"/>
       <c r="B188" s="18"/>
       <c r="C188" s="13"/>
@@ -23233,7 +23241,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12"/>
       <c r="B189" s="18"/>
       <c r="C189" s="13"/>
@@ -23291,7 +23299,7 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="38" t="s">
         <v>211</v>
       </c>
@@ -23345,7 +23353,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
@@ -23399,7 +23407,7 @@
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23529,7 +23537,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12"/>
       <c r="B193" s="18"/>
       <c r="C193" s="13"/>
@@ -23587,7 +23595,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12"/>
       <c r="B194" s="18"/>
       <c r="C194" s="13"/>
@@ -23647,6 +23655,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23663,60 +23725,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23726,58 +23734,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.26953125" customWidth="1"/>
+    <col min="2" max="2" width="75.28515625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" customWidth="1"/>
-    <col min="12" max="12" width="12.54296875" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" customWidth="1"/>
-    <col min="14" max="14" width="12.54296875" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.54296875" customWidth="1"/>
-    <col min="16" max="16" width="12.54296875" style="23" customWidth="1"/>
-    <col min="17" max="17" width="10.54296875" customWidth="1"/>
-    <col min="18" max="18" width="12.54296875" style="23" customWidth="1"/>
-    <col min="19" max="19" width="10.54296875" customWidth="1"/>
-    <col min="20" max="20" width="12.54296875" customWidth="1"/>
-    <col min="21" max="21" width="10.54296875" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" style="23" customWidth="1"/>
-    <col min="23" max="23" width="10.54296875" customWidth="1"/>
-    <col min="24" max="24" width="12.54296875" style="23" customWidth="1"/>
-    <col min="25" max="25" width="10.54296875" customWidth="1"/>
-    <col min="26" max="26" width="12.54296875" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.54296875" customWidth="1"/>
-    <col min="28" max="28" width="12.54296875" style="23" customWidth="1"/>
-    <col min="29" max="29" width="10.54296875" customWidth="1"/>
-    <col min="30" max="30" width="12.54296875" style="23" customWidth="1"/>
-    <col min="31" max="31" width="10.54296875" customWidth="1"/>
-    <col min="32" max="32" width="12.54296875" style="23" customWidth="1"/>
-    <col min="33" max="33" width="10.54296875" customWidth="1"/>
-    <col min="34" max="34" width="12.54296875" style="23" customWidth="1"/>
-    <col min="35" max="35" width="10.54296875" customWidth="1"/>
-    <col min="36" max="36" width="12.54296875" style="23" customWidth="1"/>
-    <col min="37" max="37" width="10.54296875" customWidth="1"/>
-    <col min="38" max="38" width="12.54296875" style="23" customWidth="1"/>
-    <col min="39" max="39" width="10.54296875" customWidth="1"/>
-    <col min="40" max="40" width="12.54296875" style="23" customWidth="1"/>
-    <col min="41" max="41" width="10.54296875" customWidth="1"/>
-    <col min="42" max="42" width="12.54296875" customWidth="1"/>
-    <col min="43" max="43" width="10.54296875" customWidth="1"/>
-    <col min="44" max="44" width="12.54296875" style="23" customWidth="1"/>
-    <col min="45" max="45" width="10.54296875" customWidth="1"/>
-    <col min="46" max="46" width="12.54296875" style="23" customWidth="1"/>
-    <col min="47" max="47" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="23" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="23" customWidth="1"/>
+    <col min="19" max="19" width="10.5703125" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="23" customWidth="1"/>
+    <col min="23" max="23" width="10.5703125" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" style="23" customWidth="1"/>
+    <col min="25" max="25" width="10.5703125" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" style="23" customWidth="1"/>
+    <col min="27" max="27" width="10.5703125" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" style="23" customWidth="1"/>
+    <col min="29" max="29" width="10.5703125" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" style="23" customWidth="1"/>
+    <col min="31" max="31" width="10.5703125" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" style="23" customWidth="1"/>
+    <col min="33" max="33" width="10.5703125" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="23" customWidth="1"/>
+    <col min="35" max="35" width="10.5703125" customWidth="1"/>
+    <col min="36" max="36" width="12.5703125" style="23" customWidth="1"/>
+    <col min="37" max="37" width="10.5703125" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="23" customWidth="1"/>
+    <col min="39" max="39" width="10.5703125" customWidth="1"/>
+    <col min="40" max="40" width="12.5703125" style="23" customWidth="1"/>
+    <col min="41" max="41" width="10.5703125" customWidth="1"/>
+    <col min="42" max="42" width="12.5703125" customWidth="1"/>
+    <col min="43" max="43" width="10.5703125" customWidth="1"/>
+    <col min="44" max="44" width="12.5703125" style="23" customWidth="1"/>
+    <col min="45" max="45" width="10.5703125" customWidth="1"/>
+    <col min="46" max="46" width="12.5703125" style="23" customWidth="1"/>
+    <col min="47" max="47" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23883,14 +23891,14 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="44"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="44"/>
+      <c r="AU1" s="39"/>
     </row>
-    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21"/>
       <c r="B2" s="25" t="s">
         <v>215</v>
@@ -24031,7 +24039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24194,7 +24202,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24357,7 +24365,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24520,7 +24528,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24683,7 +24691,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24846,7 +24854,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -25009,7 +25017,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25172,7 +25180,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25335,7 +25343,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25498,7 +25506,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25661,7 +25669,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25824,7 +25832,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -25987,7 +25995,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26150,7 +26158,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26313,7 +26321,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26432,6 +26440,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26443,17 +26462,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26465,16 +26473,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.7265625" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
@@ -26483,7 +26491,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>285</v>
       </c>
@@ -26500,7 +26508,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
@@ -26511,7 +26519,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26519,13 +26527,13 @@
       </c>
       <c r="E3" s="11">
         <f t="shared" ref="E3:E24" si="1">C3+D3</f>
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>Wedstrijden_beheer!AA1</f>
@@ -26533,7 +26541,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26541,13 +26549,13 @@
       </c>
       <c r="E4" s="11">
         <f t="shared" si="1"/>
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="str">
         <f>Wedstrijden_beheer!AE1</f>
@@ -26555,7 +26563,7 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -26563,10 +26571,10 @@
       </c>
       <c r="E5" s="11">
         <f t="shared" si="1"/>
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -26577,7 +26585,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!G17</f>
@@ -26585,13 +26593,13 @@
       </c>
       <c r="E6" s="11">
         <f t="shared" si="1"/>
-        <v>99</v>
+        <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
         <f>Wedstrijden_beheer!AK1</f>
@@ -26599,7 +26607,7 @@
       </c>
       <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D7" s="11">
         <f>Bonus_beheer!AK17</f>
@@ -26607,13 +26615,13 @@
       </c>
       <c r="E7" s="11">
         <f t="shared" si="1"/>
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="str">
         <f>Wedstrijden_beheer!U1</f>
@@ -26621,7 +26629,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!U17</f>
@@ -26629,13 +26637,13 @@
       </c>
       <c r="E8" s="11">
         <f t="shared" si="1"/>
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
@@ -26643,7 +26651,7 @@
       </c>
       <c r="C9" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D9" s="11">
         <f>Bonus_beheer!I17</f>
@@ -26651,13 +26659,13 @@
       </c>
       <c r="E9" s="11">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>Wedstrijden_beheer!M1</f>
@@ -26665,7 +26673,7 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!M17</f>
@@ -26673,13 +26681,13 @@
       </c>
       <c r="E10" s="11">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>Wedstrijden_beheer!Y1</f>
@@ -26687,7 +26695,7 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!Y17</f>
@@ -26695,13 +26703,13 @@
       </c>
       <c r="E11" s="11">
         <f t="shared" si="1"/>
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="str">
         <f>Wedstrijden_beheer!AU1</f>
@@ -26709,7 +26717,7 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!AU17</f>
@@ -26717,13 +26725,13 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
@@ -26731,7 +26739,7 @@
       </c>
       <c r="C13" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D13" s="11">
         <f>Bonus_beheer!AU18</f>
@@ -26739,13 +26747,13 @@
       </c>
       <c r="E13" s="11">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1" t="str">
         <f>Wedstrijden_beheer!AG1</f>
@@ -26753,7 +26761,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!AG17</f>
@@ -26761,13 +26769,13 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>Wedstrijden_beheer!E1</f>
@@ -26775,7 +26783,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!E17</f>
@@ -26783,13 +26791,13 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -26797,7 +26805,7 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -26805,13 +26813,13 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" si="1"/>
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -26819,7 +26827,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -26827,13 +26835,13 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" si="1"/>
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!S1</f>
@@ -26841,7 +26849,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!S17</f>
@@ -26849,13 +26857,13 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>Wedstrijden_beheer!AO1</f>
@@ -26863,7 +26871,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -26871,13 +26879,13 @@
       </c>
       <c r="E19" s="11">
         <f t="shared" si="1"/>
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="str">
         <f>Wedstrijden_beheer!W1</f>
@@ -26885,7 +26893,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26893,13 +26901,13 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" si="1"/>
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -26907,7 +26915,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26915,13 +26923,13 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" si="1"/>
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!AC1</f>
@@ -26929,7 +26937,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26937,13 +26945,13 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" si="1"/>
-        <v>73</v>
+        <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -26951,7 +26959,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -26959,10 +26967,10 @@
       </c>
       <c r="E23" s="11">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -26973,7 +26981,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26981,7 +26989,7 @@
       </c>
       <c r="E24" s="11">
         <f t="shared" si="1"/>
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -26997,20 +27005,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" hidden="1"/>
+    <col min="3" max="16384" width="8.7109375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27018,7 +27026,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27026,7 +27034,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27034,7 +27042,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27042,7 +27050,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27050,7 +27058,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27058,7 +27066,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27066,7 +27074,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27082,16 +27090,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" customWidth="1"/>
-    <col min="3" max="3" width="30.7265625" customWidth="1"/>
+    <col min="1" max="1" width="55.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.7265625" hidden="1"/>
+    <col min="45" max="16384" width="8.7109375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>306</v>
       </c>
@@ -27139,7 +27147,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27150,7 +27158,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27161,7 +27169,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27172,7 +27180,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27183,7 +27191,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27194,7 +27202,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27205,7 +27213,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27222,14 +27230,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>319</v>
       </c>
@@ -27240,7 +27248,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27248,107 +27256,107 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>324</v>
       </c>
@@ -27359,26 +27367,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27573,32 +27561,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27615,4 +27598,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1504" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85EAEB5-B1BB-4644-AB6A-3227D00E60B4}"/>
+  <xr:revisionPtr revIDLastSave="1519" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1DC7F51-233E-4AB8-A0B0-E61B70A7C02D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Stand!$E$2:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Wedstrijden_beheer!$A$1:$AX$194</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,21 +1349,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1388,6 +1389,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1676,76 +1681,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.5703125" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.5703125" customWidth="1"/>
-    <col min="19" max="19" width="12.5703125" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.5703125" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" customWidth="1"/>
-    <col min="23" max="23" width="12.5703125" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" customWidth="1"/>
-    <col min="25" max="25" width="12.5703125" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="27" width="12.5703125" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.5703125" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.5703125" customWidth="1"/>
-    <col min="31" max="31" width="12.5703125" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.5703125" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.5703125" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.5703125" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.5703125" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.5703125" customWidth="1"/>
-    <col min="41" max="41" width="15.5703125" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.5703125" customWidth="1"/>
-    <col min="43" max="43" width="15.5703125" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.5703125" customWidth="1"/>
-    <col min="45" max="45" width="15.7109375" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.5703125" customWidth="1"/>
-    <col min="47" max="47" width="15.5703125" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.54296875" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.54296875" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" customWidth="1"/>
+    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.54296875" customWidth="1"/>
+    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.54296875" customWidth="1"/>
+    <col min="21" max="21" width="12.54296875" customWidth="1"/>
+    <col min="22" max="22" width="8.54296875" customWidth="1"/>
+    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.54296875" customWidth="1"/>
+    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.54296875" customWidth="1"/>
+    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.54296875" customWidth="1"/>
+    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.54296875" customWidth="1"/>
+    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.54296875" customWidth="1"/>
+    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.54296875" customWidth="1"/>
+    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.54296875" customWidth="1"/>
+    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.54296875" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.54296875" customWidth="1"/>
+    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.54296875" customWidth="1"/>
+    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.54296875" customWidth="1"/>
+    <col min="45" max="45" width="15.7265625" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.54296875" customWidth="1"/>
+    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.54296875" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="44"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1830,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="39"/>
+      <c r="AT1" s="44"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="39"/>
+      <c r="AV1" s="44"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1837,10 +1842,10 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A2" s="43"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1981,61 +1986,61 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="40"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
@@ -2089,7 +2094,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2265,7 +2270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2323,7 +2328,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -2377,7 +2382,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2553,7 +2558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2729,7 +2734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2787,7 +2792,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
@@ -2841,7 +2846,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3017,7 +3022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3193,7 +3198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3251,7 +3256,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
@@ -3305,7 +3310,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3481,7 +3486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3657,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3833,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4009,7 +4014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4185,7 +4190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4243,7 +4248,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
@@ -4297,7 +4302,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4473,7 +4478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4649,7 +4654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4825,7 +4830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -5001,7 +5006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5059,7 +5064,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
@@ -5113,7 +5118,7 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5289,7 +5294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5465,7 +5470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5641,7 +5646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5699,7 +5704,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
@@ -5753,7 +5758,7 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5929,7 +5934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6105,7 +6110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6281,7 +6286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6457,7 +6462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6633,7 +6638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6691,7 +6696,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
@@ -6745,7 +6750,7 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6921,7 +6926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7097,7 +7102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7273,7 +7278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7449,7 +7454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="18"/>
       <c r="C45" s="13"/>
@@ -7507,7 +7512,7 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
@@ -7561,7 +7566,7 @@
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7737,7 +7742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7913,181 +7918,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
       <c r="B49" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="D49" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F49" s="11" t="str">
+      <c r="F49" s="11">
         <f>IF(OR($C49="",E49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E49,FIND("-",E49)-1),"")=AW49,IFERROR(--MID(E49,FIND("-",E49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(E49,FIND("-",E49)-1),""))-(IFERROR(--MID(E49,FIND("-",E49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(E49,FIND("-",E49)-1),""))-(IFERROR(--MID(E49,FIND("-",E49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(E49,FIND("-",E49)-1),""))=(AW49))+2*((IFERROR(--MID(E49,FIND("-",E49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H49" s="11" t="str">
+      <c r="H49" s="11">
         <f>IF(OR($C49="",G49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G49,FIND("-",G49)-1),"")=AW49,IFERROR(--MID(G49,FIND("-",G49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(G49,FIND("-",G49)-1),""))-(IFERROR(--MID(G49,FIND("-",G49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(G49,FIND("-",G49)-1),""))-(IFERROR(--MID(G49,FIND("-",G49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(G49,FIND("-",G49)-1),""))=(AW49))+2*((IFERROR(--MID(G49,FIND("-",G49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J49" s="11" t="str">
+      <c r="J49" s="11">
         <f>IF(OR($C49="",I49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I49,FIND("-",I49)-1),"")=AW49,IFERROR(--MID(I49,FIND("-",I49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(I49,FIND("-",I49)-1),""))-(IFERROR(--MID(I49,FIND("-",I49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(I49,FIND("-",I49)-1),""))-(IFERROR(--MID(I49,FIND("-",I49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(I49,FIND("-",I49)-1),""))=(AW49))+2*((IFERROR(--MID(I49,FIND("-",I49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L49" s="11" t="str">
+      <c r="L49" s="11">
         <f>IF(OR($C49="",K49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K49,FIND("-",K49)-1),"")=AW49,IFERROR(--MID(K49,FIND("-",K49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(K49,FIND("-",K49)-1),""))-(IFERROR(--MID(K49,FIND("-",K49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(K49,FIND("-",K49)-1),""))-(IFERROR(--MID(K49,FIND("-",K49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(K49,FIND("-",K49)-1),""))=(AW49))+2*((IFERROR(--MID(K49,FIND("-",K49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M49" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N49" s="11" t="str">
+      <c r="N49" s="11">
         <f>IF(OR($C49="",M49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M49,FIND("-",M49)-1),"")=AW49,IFERROR(--MID(M49,FIND("-",M49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(M49,FIND("-",M49)-1),""))-(IFERROR(--MID(M49,FIND("-",M49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(M49,FIND("-",M49)-1),""))-(IFERROR(--MID(M49,FIND("-",M49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(M49,FIND("-",M49)-1),""))=(AW49))+2*((IFERROR(--MID(M49,FIND("-",M49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P49" s="11" t="str">
+      <c r="P49" s="11">
         <f>IF(OR($C49="",O49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O49,FIND("-",O49)-1),"")=AW49,IFERROR(--MID(O49,FIND("-",O49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(O49,FIND("-",O49)-1),""))-(IFERROR(--MID(O49,FIND("-",O49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(O49,FIND("-",O49)-1),""))-(IFERROR(--MID(O49,FIND("-",O49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(O49,FIND("-",O49)-1),""))=(AW49))+2*((IFERROR(--MID(O49,FIND("-",O49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q49" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R49" s="11" t="str">
+      <c r="R49" s="11">
         <f>IF(OR($C49="",Q49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q49,FIND("-",Q49)-1),"")=AW49,IFERROR(--MID(Q49,FIND("-",Q49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(Q49,FIND("-",Q49)-1),""))-(IFERROR(--MID(Q49,FIND("-",Q49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(Q49,FIND("-",Q49)-1),""))-(IFERROR(--MID(Q49,FIND("-",Q49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(Q49,FIND("-",Q49)-1),""))=(AW49))+2*((IFERROR(--MID(Q49,FIND("-",Q49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S49" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="T49" s="11" t="str">
+      <c r="T49" s="11">
         <f>IF(OR($C49="",S49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S49,FIND("-",S49)-1),"")=AW49,IFERROR(--MID(S49,FIND("-",S49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(S49,FIND("-",S49)-1),""))-(IFERROR(--MID(S49,FIND("-",S49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(S49,FIND("-",S49)-1),""))-(IFERROR(--MID(S49,FIND("-",S49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(S49,FIND("-",S49)-1),""))=(AW49))+2*((IFERROR(--MID(S49,FIND("-",S49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U49" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V49" s="11" t="str">
+      <c r="V49" s="11">
         <f>IF(OR($C49="",U49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U49,FIND("-",U49)-1),"")=AW49,IFERROR(--MID(U49,FIND("-",U49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(U49,FIND("-",U49)-1),""))-(IFERROR(--MID(U49,FIND("-",U49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(U49,FIND("-",U49)-1),""))-(IFERROR(--MID(U49,FIND("-",U49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(U49,FIND("-",U49)-1),""))=(AW49))+2*((IFERROR(--MID(U49,FIND("-",U49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X49" s="11" t="str">
+      <c r="X49" s="11">
         <f>IF(OR($C49="",W49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W49,FIND("-",W49)-1),"")=AW49,IFERROR(--MID(W49,FIND("-",W49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(W49,FIND("-",W49)-1),""))-(IFERROR(--MID(W49,FIND("-",W49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(W49,FIND("-",W49)-1),""))-(IFERROR(--MID(W49,FIND("-",W49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(W49,FIND("-",W49)-1),""))=(AW49))+2*((IFERROR(--MID(W49,FIND("-",W49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y49" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z49" s="11" t="str">
+      <c r="Z49" s="11">
         <f>IF(OR($C49="",Y49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y49,FIND("-",Y49)-1),"")=AW49,IFERROR(--MID(Y49,FIND("-",Y49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(Y49,FIND("-",Y49)-1),""))-(IFERROR(--MID(Y49,FIND("-",Y49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(Y49,FIND("-",Y49)-1),""))-(IFERROR(--MID(Y49,FIND("-",Y49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(Y49,FIND("-",Y49)-1),""))=(AW49))+2*((IFERROR(--MID(Y49,FIND("-",Y49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA49" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB49" s="11" t="str">
+      <c r="AB49" s="11">
         <f>IF(OR($C49="",AA49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA49,FIND("-",AA49)-1),"")=AW49,IFERROR(--MID(AA49,FIND("-",AA49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AA49,FIND("-",AA49)-1),""))-(IFERROR(--MID(AA49,FIND("-",AA49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AA49,FIND("-",AA49)-1),""))-(IFERROR(--MID(AA49,FIND("-",AA49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AA49,FIND("-",AA49)-1),""))=(AW49))+2*((IFERROR(--MID(AA49,FIND("-",AA49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC49" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AD49" s="11" t="str">
+      <c r="AD49" s="11">
         <f>IF(OR($C49="",AC49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC49,FIND("-",AC49)-1),"")=AW49,IFERROR(--MID(AC49,FIND("-",AC49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AC49,FIND("-",AC49)-1),""))-(IFERROR(--MID(AC49,FIND("-",AC49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AC49,FIND("-",AC49)-1),""))-(IFERROR(--MID(AC49,FIND("-",AC49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AC49,FIND("-",AC49)-1),""))=(AW49))+2*((IFERROR(--MID(AC49,FIND("-",AC49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF49" s="11" t="str">
+      <c r="AF49" s="11">
         <f>IF(OR($C49="",AE49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE49,FIND("-",AE49)-1),"")=AW49,IFERROR(--MID(AE49,FIND("-",AE49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AE49,FIND("-",AE49)-1),""))-(IFERROR(--MID(AE49,FIND("-",AE49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AE49,FIND("-",AE49)-1),""))-(IFERROR(--MID(AE49,FIND("-",AE49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AE49,FIND("-",AE49)-1),""))=(AW49))+2*((IFERROR(--MID(AE49,FIND("-",AE49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH49" s="11" t="str">
+      <c r="AH49" s="11">
         <f>IF(OR($C49="",AG49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG49,FIND("-",AG49)-1),"")=AW49,IFERROR(--MID(AG49,FIND("-",AG49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AG49,FIND("-",AG49)-1),""))-(IFERROR(--MID(AG49,FIND("-",AG49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AG49,FIND("-",AG49)-1),""))-(IFERROR(--MID(AG49,FIND("-",AG49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AG49,FIND("-",AG49)-1),""))=(AW49))+2*((IFERROR(--MID(AG49,FIND("-",AG49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI49" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ49" s="11" t="str">
+      <c r="AJ49" s="11">
         <f>IF(OR($C49="",AI49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI49,FIND("-",AI49)-1),"")=AW49,IFERROR(--MID(AI49,FIND("-",AI49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AI49,FIND("-",AI49)-1),""))-(IFERROR(--MID(AI49,FIND("-",AI49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AI49,FIND("-",AI49)-1),""))-(IFERROR(--MID(AI49,FIND("-",AI49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AI49,FIND("-",AI49)-1),""))=(AW49))+2*((IFERROR(--MID(AI49,FIND("-",AI49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AL49" s="11" t="str">
+      <c r="AL49" s="11">
         <f>IF(OR($C49="",AK49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK49,FIND("-",AK49)-1),"")=AW49,IFERROR(--MID(AK49,FIND("-",AK49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AK49,FIND("-",AK49)-1),""))-(IFERROR(--MID(AK49,FIND("-",AK49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AK49,FIND("-",AK49)-1),""))-(IFERROR(--MID(AK49,FIND("-",AK49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AK49,FIND("-",AK49)-1),""))=(AW49))+2*((IFERROR(--MID(AK49,FIND("-",AK49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN49" s="11" t="str">
+      <c r="AN49" s="11">
         <f>IF(OR($C49="",AM49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM49,FIND("-",AM49)-1),"")=AW49,IFERROR(--MID(AM49,FIND("-",AM49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AM49,FIND("-",AM49)-1),""))-(IFERROR(--MID(AM49,FIND("-",AM49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AM49,FIND("-",AM49)-1),""))-(IFERROR(--MID(AM49,FIND("-",AM49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AM49,FIND("-",AM49)-1),""))=(AW49))+2*((IFERROR(--MID(AM49,FIND("-",AM49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP49" s="11" t="str">
+      <c r="AP49" s="11">
         <f>IF(OR($C49="",AO49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO49,FIND("-",AO49)-1),"")=AW49,IFERROR(--MID(AO49,FIND("-",AO49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AO49,FIND("-",AO49)-1),""))-(IFERROR(--MID(AO49,FIND("-",AO49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AO49,FIND("-",AO49)-1),""))-(IFERROR(--MID(AO49,FIND("-",AO49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AO49,FIND("-",AO49)-1),""))=(AW49))+2*((IFERROR(--MID(AO49,FIND("-",AO49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ49" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR49" s="11" t="str">
+      <c r="AR49" s="11">
         <f>IF(OR($C49="",AQ49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ49,FIND("-",AQ49)-1),"")=AW49,IFERROR(--MID(AQ49,FIND("-",AQ49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AQ49,FIND("-",AQ49)-1),""))-(IFERROR(--MID(AQ49,FIND("-",AQ49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AQ49,FIND("-",AQ49)-1),""))-(IFERROR(--MID(AQ49,FIND("-",AQ49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AQ49,FIND("-",AQ49)-1),""))=(AW49))+2*((IFERROR(--MID(AQ49,FIND("-",AQ49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS49" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT49" s="11" t="str">
+      <c r="AT49" s="11">
         <f>IF(OR($C49="",AS49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS49,FIND("-",AS49)-1),"")=AW49,IFERROR(--MID(AS49,FIND("-",AS49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AS49,FIND("-",AS49)-1),""))-(IFERROR(--MID(AS49,FIND("-",AS49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AS49,FIND("-",AS49)-1),""))-(IFERROR(--MID(AS49,FIND("-",AS49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AS49,FIND("-",AS49)-1),""))=(AW49))+2*((IFERROR(--MID(AS49,FIND("-",AS49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU49" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV49" s="11" t="str">
+      <c r="AV49" s="11">
         <f>IF(OR($C49="",AU49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU49,FIND("-",AU49)-1),"")=AW49,IFERROR(--MID(AU49,FIND("-",AU49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AU49,FIND("-",AU49)-1),""))-(IFERROR(--MID(AU49,FIND("-",AU49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AU49,FIND("-",AU49)-1),""))-(IFERROR(--MID(AU49,FIND("-",AU49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AU49,FIND("-",AU49)-1),""))=(AW49))+2*((IFERROR(--MID(AU49,FIND("-",AU49)+1,99),""))=(AX49))),""))</f>
-        <v/>
-      </c>
-      <c r="AW49" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW49" s="11">
         <f>IF($C49="","",IFERROR(--LEFT($C49,FIND("-",$C49)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX49" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX49" s="11">
         <f>IF($C49="","",IFERROR(--MID($C49,FIND("-",$C49)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
       <c r="B50" s="18"/>
       <c r="C50" s="13"/>
@@ -8145,7 +8152,7 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
@@ -8199,877 +8206,887 @@
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9">
         <v>1</v>
       </c>
       <c r="B52" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
+      <c r="C52" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D52" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F52" s="11" t="str">
+      <c r="F52" s="11">
         <f>IF(OR($C52="",E52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E52,FIND("-",E52)-1),"")=AW52,IFERROR(--MID(E52,FIND("-",E52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(E52,FIND("-",E52)-1),""))-(IFERROR(--MID(E52,FIND("-",E52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(E52,FIND("-",E52)-1),""))-(IFERROR(--MID(E52,FIND("-",E52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(E52,FIND("-",E52)-1),""))=(AW52))+2*((IFERROR(--MID(E52,FIND("-",E52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H52" s="11" t="str">
+      <c r="H52" s="11">
         <f>IF(OR($C52="",G52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G52,FIND("-",G52)-1),"")=AW52,IFERROR(--MID(G52,FIND("-",G52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(G52,FIND("-",G52)-1),""))-(IFERROR(--MID(G52,FIND("-",G52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(G52,FIND("-",G52)-1),""))-(IFERROR(--MID(G52,FIND("-",G52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(G52,FIND("-",G52)-1),""))=(AW52))+2*((IFERROR(--MID(G52,FIND("-",G52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I52" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J52" s="11" t="str">
+      <c r="J52" s="11">
         <f>IF(OR($C52="",I52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I52,FIND("-",I52)-1),"")=AW52,IFERROR(--MID(I52,FIND("-",I52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(I52,FIND("-",I52)-1),""))-(IFERROR(--MID(I52,FIND("-",I52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(I52,FIND("-",I52)-1),""))-(IFERROR(--MID(I52,FIND("-",I52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(I52,FIND("-",I52)-1),""))=(AW52))+2*((IFERROR(--MID(I52,FIND("-",I52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K52" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L52" s="11" t="str">
+      <c r="L52" s="11">
         <f>IF(OR($C52="",K52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K52,FIND("-",K52)-1),"")=AW52,IFERROR(--MID(K52,FIND("-",K52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(K52,FIND("-",K52)-1),""))-(IFERROR(--MID(K52,FIND("-",K52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(K52,FIND("-",K52)-1),""))-(IFERROR(--MID(K52,FIND("-",K52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(K52,FIND("-",K52)-1),""))=(AW52))+2*((IFERROR(--MID(K52,FIND("-",K52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N52" s="11" t="str">
+      <c r="N52" s="11">
         <f>IF(OR($C52="",M52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M52,FIND("-",M52)-1),"")=AW52,IFERROR(--MID(M52,FIND("-",M52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(M52,FIND("-",M52)-1),""))-(IFERROR(--MID(M52,FIND("-",M52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(M52,FIND("-",M52)-1),""))-(IFERROR(--MID(M52,FIND("-",M52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(M52,FIND("-",M52)-1),""))=(AW52))+2*((IFERROR(--MID(M52,FIND("-",M52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O52" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="P52" s="11" t="str">
+      <c r="P52" s="11">
         <f>IF(OR($C52="",O52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O52,FIND("-",O52)-1),"")=AW52,IFERROR(--MID(O52,FIND("-",O52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(O52,FIND("-",O52)-1),""))-(IFERROR(--MID(O52,FIND("-",O52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(O52,FIND("-",O52)-1),""))-(IFERROR(--MID(O52,FIND("-",O52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(O52,FIND("-",O52)-1),""))=(AW52))+2*((IFERROR(--MID(O52,FIND("-",O52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R52" s="11" t="str">
+      <c r="R52" s="11">
         <f>IF(OR($C52="",Q52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q52,FIND("-",Q52)-1),"")=AW52,IFERROR(--MID(Q52,FIND("-",Q52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(Q52,FIND("-",Q52)-1),""))-(IFERROR(--MID(Q52,FIND("-",Q52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(Q52,FIND("-",Q52)-1),""))-(IFERROR(--MID(Q52,FIND("-",Q52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(Q52,FIND("-",Q52)-1),""))=(AW52))+2*((IFERROR(--MID(Q52,FIND("-",Q52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S52" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T52" s="11" t="str">
+      <c r="T52" s="11">
         <f>IF(OR($C52="",S52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S52,FIND("-",S52)-1),"")=AW52,IFERROR(--MID(S52,FIND("-",S52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(S52,FIND("-",S52)-1),""))-(IFERROR(--MID(S52,FIND("-",S52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(S52,FIND("-",S52)-1),""))-(IFERROR(--MID(S52,FIND("-",S52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(S52,FIND("-",S52)-1),""))=(AW52))+2*((IFERROR(--MID(S52,FIND("-",S52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V52" s="11" t="str">
+      <c r="V52" s="11">
         <f>IF(OR($C52="",U52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U52,FIND("-",U52)-1),"")=AW52,IFERROR(--MID(U52,FIND("-",U52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(U52,FIND("-",U52)-1),""))-(IFERROR(--MID(U52,FIND("-",U52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(U52,FIND("-",U52)-1),""))-(IFERROR(--MID(U52,FIND("-",U52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(U52,FIND("-",U52)-1),""))=(AW52))+2*((IFERROR(--MID(U52,FIND("-",U52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W52" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="X52" s="11" t="str">
+      <c r="X52" s="11">
         <f>IF(OR($C52="",W52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W52,FIND("-",W52)-1),"")=AW52,IFERROR(--MID(W52,FIND("-",W52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(W52,FIND("-",W52)-1),""))-(IFERROR(--MID(W52,FIND("-",W52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(W52,FIND("-",W52)-1),""))-(IFERROR(--MID(W52,FIND("-",W52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(W52,FIND("-",W52)-1),""))=(AW52))+2*((IFERROR(--MID(W52,FIND("-",W52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Y52" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="Z52" s="11" t="str">
+      <c r="Z52" s="11">
         <f>IF(OR($C52="",Y52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y52,FIND("-",Y52)-1),"")=AW52,IFERROR(--MID(Y52,FIND("-",Y52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(Y52,FIND("-",Y52)-1),""))-(IFERROR(--MID(Y52,FIND("-",Y52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(Y52,FIND("-",Y52)-1),""))-(IFERROR(--MID(Y52,FIND("-",Y52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(Y52,FIND("-",Y52)-1),""))=(AW52))+2*((IFERROR(--MID(Y52,FIND("-",Y52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA52" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AB52" s="11" t="str">
+      <c r="AB52" s="11">
         <f>IF(OR($C52="",AA52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA52,FIND("-",AA52)-1),"")=AW52,IFERROR(--MID(AA52,FIND("-",AA52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AA52,FIND("-",AA52)-1),""))-(IFERROR(--MID(AA52,FIND("-",AA52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AA52,FIND("-",AA52)-1),""))-(IFERROR(--MID(AA52,FIND("-",AA52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AA52,FIND("-",AA52)-1),""))=(AW52))+2*((IFERROR(--MID(AA52,FIND("-",AA52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AD52" s="11" t="str">
+      <c r="AD52" s="11">
         <f>IF(OR($C52="",AC52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC52,FIND("-",AC52)-1),"")=AW52,IFERROR(--MID(AC52,FIND("-",AC52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AC52,FIND("-",AC52)-1),""))-(IFERROR(--MID(AC52,FIND("-",AC52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AC52,FIND("-",AC52)-1),""))-(IFERROR(--MID(AC52,FIND("-",AC52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AC52,FIND("-",AC52)-1),""))=(AW52))+2*((IFERROR(--MID(AC52,FIND("-",AC52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF52" s="11" t="str">
+      <c r="AF52" s="11">
         <f>IF(OR($C52="",AE52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE52,FIND("-",AE52)-1),"")=AW52,IFERROR(--MID(AE52,FIND("-",AE52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AE52,FIND("-",AE52)-1),""))-(IFERROR(--MID(AE52,FIND("-",AE52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AE52,FIND("-",AE52)-1),""))-(IFERROR(--MID(AE52,FIND("-",AE52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AE52,FIND("-",AE52)-1),""))=(AW52))+2*((IFERROR(--MID(AE52,FIND("-",AE52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG52" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH52" s="11" t="str">
+      <c r="AH52" s="11">
         <f>IF(OR($C52="",AG52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG52,FIND("-",AG52)-1),"")=AW52,IFERROR(--MID(AG52,FIND("-",AG52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AG52,FIND("-",AG52)-1),""))-(IFERROR(--MID(AG52,FIND("-",AG52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AG52,FIND("-",AG52)-1),""))-(IFERROR(--MID(AG52,FIND("-",AG52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AG52,FIND("-",AG52)-1),""))=(AW52))+2*((IFERROR(--MID(AG52,FIND("-",AG52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI52" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ52" s="11" t="str">
+      <c r="AJ52" s="11">
         <f>IF(OR($C52="",AI52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI52,FIND("-",AI52)-1),"")=AW52,IFERROR(--MID(AI52,FIND("-",AI52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AI52,FIND("-",AI52)-1),""))-(IFERROR(--MID(AI52,FIND("-",AI52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AI52,FIND("-",AI52)-1),""))-(IFERROR(--MID(AI52,FIND("-",AI52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AI52,FIND("-",AI52)-1),""))=(AW52))+2*((IFERROR(--MID(AI52,FIND("-",AI52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK52" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AL52" s="11" t="str">
+      <c r="AL52" s="11">
         <f>IF(OR($C52="",AK52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK52,FIND("-",AK52)-1),"")=AW52,IFERROR(--MID(AK52,FIND("-",AK52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AK52,FIND("-",AK52)-1),""))-(IFERROR(--MID(AK52,FIND("-",AK52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AK52,FIND("-",AK52)-1),""))-(IFERROR(--MID(AK52,FIND("-",AK52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AK52,FIND("-",AK52)-1),""))=(AW52))+2*((IFERROR(--MID(AK52,FIND("-",AK52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AN52" s="11" t="str">
+      <c r="AN52" s="11">
         <f>IF(OR($C52="",AM52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM52,FIND("-",AM52)-1),"")=AW52,IFERROR(--MID(AM52,FIND("-",AM52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AM52,FIND("-",AM52)-1),""))-(IFERROR(--MID(AM52,FIND("-",AM52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AM52,FIND("-",AM52)-1),""))-(IFERROR(--MID(AM52,FIND("-",AM52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AM52,FIND("-",AM52)-1),""))=(AW52))+2*((IFERROR(--MID(AM52,FIND("-",AM52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AP52" s="11" t="str">
+      <c r="AP52" s="11">
         <f>IF(OR($C52="",AO52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO52,FIND("-",AO52)-1),"")=AW52,IFERROR(--MID(AO52,FIND("-",AO52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AO52,FIND("-",AO52)-1),""))-(IFERROR(--MID(AO52,FIND("-",AO52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AO52,FIND("-",AO52)-1),""))-(IFERROR(--MID(AO52,FIND("-",AO52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AO52,FIND("-",AO52)-1),""))=(AW52))+2*((IFERROR(--MID(AO52,FIND("-",AO52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AR52" s="11" t="str">
+      <c r="AR52" s="11">
         <f t="shared" ref="AR52:AR57" si="4">IF(OR($C52="",AQ52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ52,FIND("-",AQ52)-1),"")=AW52,IFERROR(--MID(AQ52,FIND("-",AQ52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AQ52,FIND("-",AQ52)-1),""))-(IFERROR(--MID(AQ52,FIND("-",AQ52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AQ52,FIND("-",AQ52)-1),""))-(IFERROR(--MID(AQ52,FIND("-",AQ52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AQ52,FIND("-",AQ52)-1),""))=(AW52))+2*((IFERROR(--MID(AQ52,FIND("-",AQ52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT52" s="11" t="str">
+      <c r="AT52" s="11">
         <f t="shared" ref="AT52:AT57" si="5">IF(OR($C52="",AS52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS52,FIND("-",AS52)-1),"")=AW52,IFERROR(--MID(AS52,FIND("-",AS52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AS52,FIND("-",AS52)-1),""))-(IFERROR(--MID(AS52,FIND("-",AS52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AS52,FIND("-",AS52)-1),""))-(IFERROR(--MID(AS52,FIND("-",AS52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AS52,FIND("-",AS52)-1),""))=(AW52))+2*((IFERROR(--MID(AS52,FIND("-",AS52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AV52" s="11" t="str">
+      <c r="AV52" s="11">
         <f>IF(OR($C52="",AU52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU52,FIND("-",AU52)-1),"")=AW52,IFERROR(--MID(AU52,FIND("-",AU52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AU52,FIND("-",AU52)-1),""))-(IFERROR(--MID(AU52,FIND("-",AU52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AU52,FIND("-",AU52)-1),""))-(IFERROR(--MID(AU52,FIND("-",AU52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AU52,FIND("-",AU52)-1),""))=(AW52))+2*((IFERROR(--MID(AU52,FIND("-",AU52)+1,99),""))=(AX52))),""))</f>
-        <v/>
-      </c>
-      <c r="AW52" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW52" s="11">
         <f>IF($C52="","",IFERROR(--LEFT($C52,FIND("-",$C52)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX52" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX52" s="11">
         <f>IF($C52="","",IFERROR(--MID($C52,FIND("-",$C52)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
       <c r="B53" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="D53" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="11" t="str">
+      <c r="F53" s="11">
         <f>IF(OR($C53="",E53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E53,FIND("-",E53)-1),"")=AW53,IFERROR(--MID(E53,FIND("-",E53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(E53,FIND("-",E53)-1),""))-(IFERROR(--MID(E53,FIND("-",E53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(E53,FIND("-",E53)-1),""))-(IFERROR(--MID(E53,FIND("-",E53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(E53,FIND("-",E53)-1),""))=(AW53))+2*((IFERROR(--MID(E53,FIND("-",E53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H53" s="11" t="str">
+      <c r="H53" s="11">
         <f>IF(OR($C53="",G53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G53,FIND("-",G53)-1),"")=AW53,IFERROR(--MID(G53,FIND("-",G53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(G53,FIND("-",G53)-1),""))-(IFERROR(--MID(G53,FIND("-",G53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(G53,FIND("-",G53)-1),""))-(IFERROR(--MID(G53,FIND("-",G53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(G53,FIND("-",G53)-1),""))=(AW53))+2*((IFERROR(--MID(G53,FIND("-",G53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I53" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J53" s="11" t="str">
+      <c r="J53" s="11">
         <f>IF(OR($C53="",I53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I53,FIND("-",I53)-1),"")=AW53,IFERROR(--MID(I53,FIND("-",I53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(I53,FIND("-",I53)-1),""))-(IFERROR(--MID(I53,FIND("-",I53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(I53,FIND("-",I53)-1),""))-(IFERROR(--MID(I53,FIND("-",I53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(I53,FIND("-",I53)-1),""))=(AW53))+2*((IFERROR(--MID(I53,FIND("-",I53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K53" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="L53" s="11" t="str">
+      <c r="L53" s="11">
         <f>IF(OR($C53="",K53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K53,FIND("-",K53)-1),"")=AW53,IFERROR(--MID(K53,FIND("-",K53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(K53,FIND("-",K53)-1),""))-(IFERROR(--MID(K53,FIND("-",K53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(K53,FIND("-",K53)-1),""))-(IFERROR(--MID(K53,FIND("-",K53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(K53,FIND("-",K53)-1),""))=(AW53))+2*((IFERROR(--MID(K53,FIND("-",K53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N53" s="11" t="str">
+      <c r="N53" s="11">
         <f>IF(OR($C53="",M53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M53,FIND("-",M53)-1),"")=AW53,IFERROR(--MID(M53,FIND("-",M53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(M53,FIND("-",M53)-1),""))-(IFERROR(--MID(M53,FIND("-",M53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(M53,FIND("-",M53)-1),""))-(IFERROR(--MID(M53,FIND("-",M53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(M53,FIND("-",M53)-1),""))=(AW53))+2*((IFERROR(--MID(M53,FIND("-",M53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P53" s="11" t="str">
+      <c r="P53" s="11">
         <f>IF(OR($C53="",O53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O53,FIND("-",O53)-1),"")=AW53,IFERROR(--MID(O53,FIND("-",O53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(O53,FIND("-",O53)-1),""))-(IFERROR(--MID(O53,FIND("-",O53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(O53,FIND("-",O53)-1),""))-(IFERROR(--MID(O53,FIND("-",O53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(O53,FIND("-",O53)-1),""))=(AW53))+2*((IFERROR(--MID(O53,FIND("-",O53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="R53" s="11" t="str">
+      <c r="R53" s="11">
         <f>IF(OR($C53="",Q53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q53,FIND("-",Q53)-1),"")=AW53,IFERROR(--MID(Q53,FIND("-",Q53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(Q53,FIND("-",Q53)-1),""))-(IFERROR(--MID(Q53,FIND("-",Q53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(Q53,FIND("-",Q53)-1),""))-(IFERROR(--MID(Q53,FIND("-",Q53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(Q53,FIND("-",Q53)-1),""))=(AW53))+2*((IFERROR(--MID(Q53,FIND("-",Q53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T53" s="11" t="str">
+      <c r="T53" s="11">
         <f>IF(OR($C53="",S53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S53,FIND("-",S53)-1),"")=AW53,IFERROR(--MID(S53,FIND("-",S53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(S53,FIND("-",S53)-1),""))-(IFERROR(--MID(S53,FIND("-",S53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(S53,FIND("-",S53)-1),""))-(IFERROR(--MID(S53,FIND("-",S53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(S53,FIND("-",S53)-1),""))=(AW53))+2*((IFERROR(--MID(S53,FIND("-",S53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V53" s="11" t="str">
+      <c r="V53" s="11">
         <f>IF(OR($C53="",U53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U53,FIND("-",U53)-1),"")=AW53,IFERROR(--MID(U53,FIND("-",U53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(U53,FIND("-",U53)-1),""))-(IFERROR(--MID(U53,FIND("-",U53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(U53,FIND("-",U53)-1),""))-(IFERROR(--MID(U53,FIND("-",U53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(U53,FIND("-",U53)-1),""))=(AW53))+2*((IFERROR(--MID(U53,FIND("-",U53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="X53" s="11" t="str">
+      <c r="X53" s="11">
         <f>IF(OR($C53="",W53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W53,FIND("-",W53)-1),"")=AW53,IFERROR(--MID(W53,FIND("-",W53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(W53,FIND("-",W53)-1),""))-(IFERROR(--MID(W53,FIND("-",W53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(W53,FIND("-",W53)-1),""))-(IFERROR(--MID(W53,FIND("-",W53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(W53,FIND("-",W53)-1),""))=(AW53))+2*((IFERROR(--MID(W53,FIND("-",W53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Y53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="Z53" s="11" t="str">
+      <c r="Z53" s="11">
         <f>IF(OR($C53="",Y53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y53,FIND("-",Y53)-1),"")=AW53,IFERROR(--MID(Y53,FIND("-",Y53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(Y53,FIND("-",Y53)-1),""))-(IFERROR(--MID(Y53,FIND("-",Y53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(Y53,FIND("-",Y53)-1),""))-(IFERROR(--MID(Y53,FIND("-",Y53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(Y53,FIND("-",Y53)-1),""))=(AW53))+2*((IFERROR(--MID(Y53,FIND("-",Y53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AB53" s="11" t="str">
+      <c r="AB53" s="11">
         <f>IF(OR($C53="",AA53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA53,FIND("-",AA53)-1),"")=AW53,IFERROR(--MID(AA53,FIND("-",AA53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AA53,FIND("-",AA53)-1),""))-(IFERROR(--MID(AA53,FIND("-",AA53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AA53,FIND("-",AA53)-1),""))-(IFERROR(--MID(AA53,FIND("-",AA53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AA53,FIND("-",AA53)-1),""))=(AW53))+2*((IFERROR(--MID(AA53,FIND("-",AA53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD53" s="11" t="str">
+      <c r="AD53" s="11">
         <f>IF(OR($C53="",AC53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC53,FIND("-",AC53)-1),"")=AW53,IFERROR(--MID(AC53,FIND("-",AC53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AC53,FIND("-",AC53)-1),""))-(IFERROR(--MID(AC53,FIND("-",AC53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AC53,FIND("-",AC53)-1),""))-(IFERROR(--MID(AC53,FIND("-",AC53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AC53,FIND("-",AC53)-1),""))=(AW53))+2*((IFERROR(--MID(AC53,FIND("-",AC53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AE53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AF53" s="11" t="str">
+      <c r="AF53" s="11">
         <f>IF(OR($C53="",AE53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE53,FIND("-",AE53)-1),"")=AW53,IFERROR(--MID(AE53,FIND("-",AE53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AE53,FIND("-",AE53)-1),""))-(IFERROR(--MID(AE53,FIND("-",AE53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AE53,FIND("-",AE53)-1),""))-(IFERROR(--MID(AE53,FIND("-",AE53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AE53,FIND("-",AE53)-1),""))=(AW53))+2*((IFERROR(--MID(AE53,FIND("-",AE53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH53" s="11" t="str">
+      <c r="AH53" s="11">
         <f>IF(OR($C53="",AG53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG53,FIND("-",AG53)-1),"")=AW53,IFERROR(--MID(AG53,FIND("-",AG53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AG53,FIND("-",AG53)-1),""))-(IFERROR(--MID(AG53,FIND("-",AG53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AG53,FIND("-",AG53)-1),""))-(IFERROR(--MID(AG53,FIND("-",AG53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AG53,FIND("-",AG53)-1),""))=(AW53))+2*((IFERROR(--MID(AG53,FIND("-",AG53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AJ53" s="11" t="str">
+      <c r="AJ53" s="11">
         <f>IF(OR($C53="",AI53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI53,FIND("-",AI53)-1),"")=AW53,IFERROR(--MID(AI53,FIND("-",AI53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AI53,FIND("-",AI53)-1),""))-(IFERROR(--MID(AI53,FIND("-",AI53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AI53,FIND("-",AI53)-1),""))-(IFERROR(--MID(AI53,FIND("-",AI53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AI53,FIND("-",AI53)-1),""))=(AW53))+2*((IFERROR(--MID(AI53,FIND("-",AI53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK53" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AL53" s="11" t="str">
+      <c r="AL53" s="11">
         <f>IF(OR($C53="",AK53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK53,FIND("-",AK53)-1),"")=AW53,IFERROR(--MID(AK53,FIND("-",AK53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AK53,FIND("-",AK53)-1),""))-(IFERROR(--MID(AK53,FIND("-",AK53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AK53,FIND("-",AK53)-1),""))-(IFERROR(--MID(AK53,FIND("-",AK53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AK53,FIND("-",AK53)-1),""))=(AW53))+2*((IFERROR(--MID(AK53,FIND("-",AK53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AN53" s="11" t="str">
+      <c r="AN53" s="11">
         <f>IF(OR($C53="",AM53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM53,FIND("-",AM53)-1),"")=AW53,IFERROR(--MID(AM53,FIND("-",AM53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AM53,FIND("-",AM53)-1),""))-(IFERROR(--MID(AM53,FIND("-",AM53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AM53,FIND("-",AM53)-1),""))-(IFERROR(--MID(AM53,FIND("-",AM53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AM53,FIND("-",AM53)-1),""))=(AW53))+2*((IFERROR(--MID(AM53,FIND("-",AM53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AP53" s="11" t="str">
+      <c r="AP53" s="11">
         <f>IF(OR($C53="",AO53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO53,FIND("-",AO53)-1),"")=AW53,IFERROR(--MID(AO53,FIND("-",AO53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AO53,FIND("-",AO53)-1),""))-(IFERROR(--MID(AO53,FIND("-",AO53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AO53,FIND("-",AO53)-1),""))-(IFERROR(--MID(AO53,FIND("-",AO53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AO53,FIND("-",AO53)-1),""))=(AW53))+2*((IFERROR(--MID(AO53,FIND("-",AO53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ53" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AR53" s="11" t="str">
+      <c r="AR53" s="11">
         <f t="shared" si="4"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS53" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AT53" s="11" t="str">
+      <c r="AT53" s="11">
         <f t="shared" si="5"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU53" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AV53" s="11" t="str">
+      <c r="AV53" s="11">
         <f>IF(OR($C53="",AU53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU53,FIND("-",AU53)-1),"")=AW53,IFERROR(--MID(AU53,FIND("-",AU53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AU53,FIND("-",AU53)-1),""))-(IFERROR(--MID(AU53,FIND("-",AU53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AU53,FIND("-",AU53)-1),""))-(IFERROR(--MID(AU53,FIND("-",AU53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AU53,FIND("-",AU53)-1),""))=(AW53))+2*((IFERROR(--MID(AU53,FIND("-",AU53)+1,99),""))=(AX53))),""))</f>
-        <v/>
-      </c>
-      <c r="AW53" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW53" s="11">
         <f>IF($C53="","",IFERROR(--LEFT($C53,FIND("-",$C53)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX53" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX53" s="11">
         <f>IF($C53="","",IFERROR(--MID($C53,FIND("-",$C53)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
       <c r="B54" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="10"/>
+      <c r="C54" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D54" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F54" s="11" t="str">
+      <c r="F54" s="11">
         <f>IF(OR($C54="",E54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E54,FIND("-",E54)-1),"")=AW54,IFERROR(--MID(E54,FIND("-",E54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(E54,FIND("-",E54)-1),""))-(IFERROR(--MID(E54,FIND("-",E54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(E54,FIND("-",E54)-1),""))-(IFERROR(--MID(E54,FIND("-",E54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(E54,FIND("-",E54)-1),""))=(AW54))+2*((IFERROR(--MID(E54,FIND("-",E54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H54" s="11" t="str">
+      <c r="H54" s="11">
         <f>IF(OR($C54="",G54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G54,FIND("-",G54)-1),"")=AW54,IFERROR(--MID(G54,FIND("-",G54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(G54,FIND("-",G54)-1),""))-(IFERROR(--MID(G54,FIND("-",G54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(G54,FIND("-",G54)-1),""))-(IFERROR(--MID(G54,FIND("-",G54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(G54,FIND("-",G54)-1),""))=(AW54))+2*((IFERROR(--MID(G54,FIND("-",G54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J54" s="11" t="str">
+      <c r="J54" s="11">
         <f>IF(OR($C54="",I54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I54,FIND("-",I54)-1),"")=AW54,IFERROR(--MID(I54,FIND("-",I54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(I54,FIND("-",I54)-1),""))-(IFERROR(--MID(I54,FIND("-",I54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(I54,FIND("-",I54)-1),""))-(IFERROR(--MID(I54,FIND("-",I54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(I54,FIND("-",I54)-1),""))=(AW54))+2*((IFERROR(--MID(I54,FIND("-",I54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K54" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L54" s="11" t="str">
+      <c r="L54" s="11">
         <f>IF(OR($C54="",K54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K54,FIND("-",K54)-1),"")=AW54,IFERROR(--MID(K54,FIND("-",K54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(K54,FIND("-",K54)-1),""))-(IFERROR(--MID(K54,FIND("-",K54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(K54,FIND("-",K54)-1),""))-(IFERROR(--MID(K54,FIND("-",K54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(K54,FIND("-",K54)-1),""))=(AW54))+2*((IFERROR(--MID(K54,FIND("-",K54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M54" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N54" s="11" t="str">
+      <c r="N54" s="11">
         <f>IF(OR($C54="",M54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M54,FIND("-",M54)-1),"")=AW54,IFERROR(--MID(M54,FIND("-",M54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(M54,FIND("-",M54)-1),""))-(IFERROR(--MID(M54,FIND("-",M54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(M54,FIND("-",M54)-1),""))-(IFERROR(--MID(M54,FIND("-",M54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(M54,FIND("-",M54)-1),""))=(AW54))+2*((IFERROR(--MID(M54,FIND("-",M54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P54" s="11" t="str">
+      <c r="P54" s="11">
         <f>IF(OR($C54="",O54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O54,FIND("-",O54)-1),"")=AW54,IFERROR(--MID(O54,FIND("-",O54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(O54,FIND("-",O54)-1),""))-(IFERROR(--MID(O54,FIND("-",O54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(O54,FIND("-",O54)-1),""))-(IFERROR(--MID(O54,FIND("-",O54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(O54,FIND("-",O54)-1),""))=(AW54))+2*((IFERROR(--MID(O54,FIND("-",O54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="R54" s="11" t="str">
+      <c r="R54" s="11">
         <f>IF(OR($C54="",Q54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q54,FIND("-",Q54)-1),"")=AW54,IFERROR(--MID(Q54,FIND("-",Q54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(Q54,FIND("-",Q54)-1),""))-(IFERROR(--MID(Q54,FIND("-",Q54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(Q54,FIND("-",Q54)-1),""))-(IFERROR(--MID(Q54,FIND("-",Q54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(Q54,FIND("-",Q54)-1),""))=(AW54))+2*((IFERROR(--MID(Q54,FIND("-",Q54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S54" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T54" s="11" t="str">
+      <c r="T54" s="11">
         <f>IF(OR($C54="",S54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S54,FIND("-",S54)-1),"")=AW54,IFERROR(--MID(S54,FIND("-",S54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(S54,FIND("-",S54)-1),""))-(IFERROR(--MID(S54,FIND("-",S54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(S54,FIND("-",S54)-1),""))-(IFERROR(--MID(S54,FIND("-",S54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(S54,FIND("-",S54)-1),""))=(AW54))+2*((IFERROR(--MID(S54,FIND("-",S54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V54" s="11" t="str">
+      <c r="V54" s="11">
         <f>IF(OR($C54="",U54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U54,FIND("-",U54)-1),"")=AW54,IFERROR(--MID(U54,FIND("-",U54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(U54,FIND("-",U54)-1),""))-(IFERROR(--MID(U54,FIND("-",U54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(U54,FIND("-",U54)-1),""))-(IFERROR(--MID(U54,FIND("-",U54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(U54,FIND("-",U54)-1),""))=(AW54))+2*((IFERROR(--MID(U54,FIND("-",U54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X54" s="11" t="str">
+      <c r="X54" s="11">
         <f>IF(OR($C54="",W54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W54,FIND("-",W54)-1),"")=AW54,IFERROR(--MID(W54,FIND("-",W54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(W54,FIND("-",W54)-1),""))-(IFERROR(--MID(W54,FIND("-",W54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(W54,FIND("-",W54)-1),""))-(IFERROR(--MID(W54,FIND("-",W54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(W54,FIND("-",W54)-1),""))=(AW54))+2*((IFERROR(--MID(W54,FIND("-",W54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z54" s="11" t="str">
+      <c r="Z54" s="11">
         <f>IF(OR($C54="",Y54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y54,FIND("-",Y54)-1),"")=AW54,IFERROR(--MID(Y54,FIND("-",Y54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(Y54,FIND("-",Y54)-1),""))-(IFERROR(--MID(Y54,FIND("-",Y54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(Y54,FIND("-",Y54)-1),""))-(IFERROR(--MID(Y54,FIND("-",Y54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(Y54,FIND("-",Y54)-1),""))=(AW54))+2*((IFERROR(--MID(Y54,FIND("-",Y54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AB54" s="11" t="str">
+      <c r="AB54" s="11">
         <f>IF(OR($C54="",AA54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA54,FIND("-",AA54)-1),"")=AW54,IFERROR(--MID(AA54,FIND("-",AA54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AA54,FIND("-",AA54)-1),""))-(IFERROR(--MID(AA54,FIND("-",AA54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AA54,FIND("-",AA54)-1),""))-(IFERROR(--MID(AA54,FIND("-",AA54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AA54,FIND("-",AA54)-1),""))=(AW54))+2*((IFERROR(--MID(AA54,FIND("-",AA54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC54" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD54" s="11" t="str">
+      <c r="AD54" s="11">
         <f>IF(OR($C54="",AC54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC54,FIND("-",AC54)-1),"")=AW54,IFERROR(--MID(AC54,FIND("-",AC54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AC54,FIND("-",AC54)-1),""))-(IFERROR(--MID(AC54,FIND("-",AC54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AC54,FIND("-",AC54)-1),""))-(IFERROR(--MID(AC54,FIND("-",AC54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AC54,FIND("-",AC54)-1),""))=(AW54))+2*((IFERROR(--MID(AC54,FIND("-",AC54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF54" s="11" t="str">
+      <c r="AF54" s="11">
         <f>IF(OR($C54="",AE54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE54,FIND("-",AE54)-1),"")=AW54,IFERROR(--MID(AE54,FIND("-",AE54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AE54,FIND("-",AE54)-1),""))-(IFERROR(--MID(AE54,FIND("-",AE54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AE54,FIND("-",AE54)-1),""))-(IFERROR(--MID(AE54,FIND("-",AE54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AE54,FIND("-",AE54)-1),""))=(AW54))+2*((IFERROR(--MID(AE54,FIND("-",AE54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG54" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH54" s="11" t="str">
+      <c r="AH54" s="11">
         <f>IF(OR($C54="",AG54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG54,FIND("-",AG54)-1),"")=AW54,IFERROR(--MID(AG54,FIND("-",AG54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AG54,FIND("-",AG54)-1),""))-(IFERROR(--MID(AG54,FIND("-",AG54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AG54,FIND("-",AG54)-1),""))-(IFERROR(--MID(AG54,FIND("-",AG54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AG54,FIND("-",AG54)-1),""))=(AW54))+2*((IFERROR(--MID(AG54,FIND("-",AG54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI54" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ54" s="11" t="str">
+      <c r="AJ54" s="11">
         <f>IF(OR($C54="",AI54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI54,FIND("-",AI54)-1),"")=AW54,IFERROR(--MID(AI54,FIND("-",AI54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AI54,FIND("-",AI54)-1),""))-(IFERROR(--MID(AI54,FIND("-",AI54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AI54,FIND("-",AI54)-1),""))-(IFERROR(--MID(AI54,FIND("-",AI54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AI54,FIND("-",AI54)-1),""))=(AW54))+2*((IFERROR(--MID(AI54,FIND("-",AI54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL54" s="11" t="str">
+      <c r="AL54" s="11">
         <f>IF(OR($C54="",AK54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK54,FIND("-",AK54)-1),"")=AW54,IFERROR(--MID(AK54,FIND("-",AK54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AK54,FIND("-",AK54)-1),""))-(IFERROR(--MID(AK54,FIND("-",AK54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AK54,FIND("-",AK54)-1),""))-(IFERROR(--MID(AK54,FIND("-",AK54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AK54,FIND("-",AK54)-1),""))=(AW54))+2*((IFERROR(--MID(AK54,FIND("-",AK54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM54" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN54" s="11" t="str">
+      <c r="AN54" s="11">
         <f>IF(OR($C54="",AM54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM54,FIND("-",AM54)-1),"")=AW54,IFERROR(--MID(AM54,FIND("-",AM54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AM54,FIND("-",AM54)-1),""))-(IFERROR(--MID(AM54,FIND("-",AM54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AM54,FIND("-",AM54)-1),""))-(IFERROR(--MID(AM54,FIND("-",AM54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AM54,FIND("-",AM54)-1),""))=(AW54))+2*((IFERROR(--MID(AM54,FIND("-",AM54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP54" s="11" t="str">
+      <c r="AP54" s="11">
         <f>IF(OR($C54="",AO54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO54,FIND("-",AO54)-1),"")=AW54,IFERROR(--MID(AO54,FIND("-",AO54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AO54,FIND("-",AO54)-1),""))-(IFERROR(--MID(AO54,FIND("-",AO54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AO54,FIND("-",AO54)-1),""))-(IFERROR(--MID(AO54,FIND("-",AO54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AO54,FIND("-",AO54)-1),""))=(AW54))+2*((IFERROR(--MID(AO54,FIND("-",AO54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR54" s="11" t="str">
+      <c r="AR54" s="11">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS54" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT54" s="11" t="str">
+      <c r="AT54" s="11">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU54" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV54" s="11" t="str">
+      <c r="AV54" s="11">
         <f>IF(OR($C54="",AU54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU54,FIND("-",AU54)-1),"")=AW54,IFERROR(--MID(AU54,FIND("-",AU54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AU54,FIND("-",AU54)-1),""))-(IFERROR(--MID(AU54,FIND("-",AU54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AU54,FIND("-",AU54)-1),""))-(IFERROR(--MID(AU54,FIND("-",AU54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AU54,FIND("-",AU54)-1),""))=(AW54))+2*((IFERROR(--MID(AU54,FIND("-",AU54)+1,99),""))=(AX54))),""))</f>
-        <v/>
-      </c>
-      <c r="AW54" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW54" s="11">
         <f>IF($C54="","",IFERROR(--LEFT($C54,FIND("-",$C54)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX54" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX54" s="11">
         <f>IF($C54="","",IFERROR(--MID($C54,FIND("-",$C54)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
       <c r="B55" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="10" t="s">
+        <v>113</v>
+      </c>
       <c r="D55" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F55" s="11" t="str">
+      <c r="F55" s="11">
         <f>IF(OR($C55="",E55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E55,FIND("-",E55)-1),"")=AW55,IFERROR(--MID(E55,FIND("-",E55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(E55,FIND("-",E55)-1),""))-(IFERROR(--MID(E55,FIND("-",E55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(E55,FIND("-",E55)-1),""))-(IFERROR(--MID(E55,FIND("-",E55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(E55,FIND("-",E55)-1),""))=(AW55))+2*((IFERROR(--MID(E55,FIND("-",E55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H55" s="11" t="str">
+      <c r="H55" s="11">
         <f>IF(OR($C55="",G55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G55,FIND("-",G55)-1),"")=AW55,IFERROR(--MID(G55,FIND("-",G55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(G55,FIND("-",G55)-1),""))-(IFERROR(--MID(G55,FIND("-",G55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(G55,FIND("-",G55)-1),""))-(IFERROR(--MID(G55,FIND("-",G55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(G55,FIND("-",G55)-1),""))=(AW55))+2*((IFERROR(--MID(G55,FIND("-",G55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J55" s="11" t="str">
+      <c r="J55" s="11">
         <f>IF(OR($C55="",I55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I55,FIND("-",I55)-1),"")=AW55,IFERROR(--MID(I55,FIND("-",I55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(I55,FIND("-",I55)-1),""))-(IFERROR(--MID(I55,FIND("-",I55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(I55,FIND("-",I55)-1),""))-(IFERROR(--MID(I55,FIND("-",I55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(I55,FIND("-",I55)-1),""))=(AW55))+2*((IFERROR(--MID(I55,FIND("-",I55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K55" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L55" s="11" t="str">
+      <c r="L55" s="11">
         <f>IF(OR($C55="",K55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K55,FIND("-",K55)-1),"")=AW55,IFERROR(--MID(K55,FIND("-",K55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(K55,FIND("-",K55)-1),""))-(IFERROR(--MID(K55,FIND("-",K55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(K55,FIND("-",K55)-1),""))-(IFERROR(--MID(K55,FIND("-",K55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(K55,FIND("-",K55)-1),""))=(AW55))+2*((IFERROR(--MID(K55,FIND("-",K55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N55" s="11" t="str">
+      <c r="N55" s="11">
         <f>IF(OR($C55="",M55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M55,FIND("-",M55)-1),"")=AW55,IFERROR(--MID(M55,FIND("-",M55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(M55,FIND("-",M55)-1),""))-(IFERROR(--MID(M55,FIND("-",M55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(M55,FIND("-",M55)-1),""))-(IFERROR(--MID(M55,FIND("-",M55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(M55,FIND("-",M55)-1),""))=(AW55))+2*((IFERROR(--MID(M55,FIND("-",M55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P55" s="11" t="str">
+      <c r="P55" s="11">
         <f>IF(OR($C55="",O55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O55,FIND("-",O55)-1),"")=AW55,IFERROR(--MID(O55,FIND("-",O55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(O55,FIND("-",O55)-1),""))-(IFERROR(--MID(O55,FIND("-",O55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(O55,FIND("-",O55)-1),""))-(IFERROR(--MID(O55,FIND("-",O55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(O55,FIND("-",O55)-1),""))=(AW55))+2*((IFERROR(--MID(O55,FIND("-",O55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q55" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R55" s="11" t="str">
+      <c r="R55" s="11">
         <f>IF(OR($C55="",Q55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q55,FIND("-",Q55)-1),"")=AW55,IFERROR(--MID(Q55,FIND("-",Q55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(Q55,FIND("-",Q55)-1),""))-(IFERROR(--MID(Q55,FIND("-",Q55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(Q55,FIND("-",Q55)-1),""))-(IFERROR(--MID(Q55,FIND("-",Q55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(Q55,FIND("-",Q55)-1),""))=(AW55))+2*((IFERROR(--MID(Q55,FIND("-",Q55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S55" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T55" s="11" t="str">
+      <c r="T55" s="11">
         <f>IF(OR($C55="",S55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S55,FIND("-",S55)-1),"")=AW55,IFERROR(--MID(S55,FIND("-",S55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(S55,FIND("-",S55)-1),""))-(IFERROR(--MID(S55,FIND("-",S55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(S55,FIND("-",S55)-1),""))-(IFERROR(--MID(S55,FIND("-",S55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(S55,FIND("-",S55)-1),""))=(AW55))+2*((IFERROR(--MID(S55,FIND("-",S55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V55" s="11" t="str">
+      <c r="V55" s="11">
         <f>IF(OR($C55="",U55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U55,FIND("-",U55)-1),"")=AW55,IFERROR(--MID(U55,FIND("-",U55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(U55,FIND("-",U55)-1),""))-(IFERROR(--MID(U55,FIND("-",U55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(U55,FIND("-",U55)-1),""))-(IFERROR(--MID(U55,FIND("-",U55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(U55,FIND("-",U55)-1),""))=(AW55))+2*((IFERROR(--MID(U55,FIND("-",U55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W55" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X55" s="11" t="str">
+      <c r="X55" s="11">
         <f>IF(OR($C55="",W55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W55,FIND("-",W55)-1),"")=AW55,IFERROR(--MID(W55,FIND("-",W55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(W55,FIND("-",W55)-1),""))-(IFERROR(--MID(W55,FIND("-",W55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(W55,FIND("-",W55)-1),""))-(IFERROR(--MID(W55,FIND("-",W55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(W55,FIND("-",W55)-1),""))=(AW55))+2*((IFERROR(--MID(W55,FIND("-",W55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z55" s="11" t="str">
+      <c r="Z55" s="11">
         <f>IF(OR($C55="",Y55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y55,FIND("-",Y55)-1),"")=AW55,IFERROR(--MID(Y55,FIND("-",Y55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(Y55,FIND("-",Y55)-1),""))-(IFERROR(--MID(Y55,FIND("-",Y55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(Y55,FIND("-",Y55)-1),""))-(IFERROR(--MID(Y55,FIND("-",Y55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(Y55,FIND("-",Y55)-1),""))=(AW55))+2*((IFERROR(--MID(Y55,FIND("-",Y55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA55" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB55" s="11" t="str">
+      <c r="AB55" s="11">
         <f>IF(OR($C55="",AA55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA55,FIND("-",AA55)-1),"")=AW55,IFERROR(--MID(AA55,FIND("-",AA55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AA55,FIND("-",AA55)-1),""))-(IFERROR(--MID(AA55,FIND("-",AA55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AA55,FIND("-",AA55)-1),""))-(IFERROR(--MID(AA55,FIND("-",AA55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AA55,FIND("-",AA55)-1),""))=(AW55))+2*((IFERROR(--MID(AA55,FIND("-",AA55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD55" s="11" t="str">
+      <c r="AD55" s="11">
         <f>IF(OR($C55="",AC55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC55,FIND("-",AC55)-1),"")=AW55,IFERROR(--MID(AC55,FIND("-",AC55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AC55,FIND("-",AC55)-1),""))-(IFERROR(--MID(AC55,FIND("-",AC55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AC55,FIND("-",AC55)-1),""))-(IFERROR(--MID(AC55,FIND("-",AC55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AC55,FIND("-",AC55)-1),""))=(AW55))+2*((IFERROR(--MID(AC55,FIND("-",AC55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE55" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF55" s="11" t="str">
+      <c r="AF55" s="11">
         <f>IF(OR($C55="",AE55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE55,FIND("-",AE55)-1),"")=AW55,IFERROR(--MID(AE55,FIND("-",AE55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AE55,FIND("-",AE55)-1),""))-(IFERROR(--MID(AE55,FIND("-",AE55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AE55,FIND("-",AE55)-1),""))-(IFERROR(--MID(AE55,FIND("-",AE55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AE55,FIND("-",AE55)-1),""))=(AW55))+2*((IFERROR(--MID(AE55,FIND("-",AE55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH55" s="11" t="str">
+      <c r="AH55" s="11">
         <f>IF(OR($C55="",AG55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG55,FIND("-",AG55)-1),"")=AW55,IFERROR(--MID(AG55,FIND("-",AG55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AG55,FIND("-",AG55)-1),""))-(IFERROR(--MID(AG55,FIND("-",AG55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AG55,FIND("-",AG55)-1),""))-(IFERROR(--MID(AG55,FIND("-",AG55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AG55,FIND("-",AG55)-1),""))=(AW55))+2*((IFERROR(--MID(AG55,FIND("-",AG55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI55" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ55" s="11" t="str">
+      <c r="AJ55" s="11">
         <f>IF(OR($C55="",AI55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI55,FIND("-",AI55)-1),"")=AW55,IFERROR(--MID(AI55,FIND("-",AI55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AI55,FIND("-",AI55)-1),""))-(IFERROR(--MID(AI55,FIND("-",AI55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AI55,FIND("-",AI55)-1),""))-(IFERROR(--MID(AI55,FIND("-",AI55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AI55,FIND("-",AI55)-1),""))=(AW55))+2*((IFERROR(--MID(AI55,FIND("-",AI55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK55" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL55" s="11" t="str">
+      <c r="AL55" s="11">
         <f>IF(OR($C55="",AK55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK55,FIND("-",AK55)-1),"")=AW55,IFERROR(--MID(AK55,FIND("-",AK55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AK55,FIND("-",AK55)-1),""))-(IFERROR(--MID(AK55,FIND("-",AK55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AK55,FIND("-",AK55)-1),""))-(IFERROR(--MID(AK55,FIND("-",AK55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AK55,FIND("-",AK55)-1),""))=(AW55))+2*((IFERROR(--MID(AK55,FIND("-",AK55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM55" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN55" s="11" t="str">
+      <c r="AN55" s="11">
         <f>IF(OR($C55="",AM55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM55,FIND("-",AM55)-1),"")=AW55,IFERROR(--MID(AM55,FIND("-",AM55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AM55,FIND("-",AM55)-1),""))-(IFERROR(--MID(AM55,FIND("-",AM55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AM55,FIND("-",AM55)-1),""))-(IFERROR(--MID(AM55,FIND("-",AM55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AM55,FIND("-",AM55)-1),""))=(AW55))+2*((IFERROR(--MID(AM55,FIND("-",AM55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO55" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP55" s="11" t="str">
+      <c r="AP55" s="11">
         <f>IF(OR($C55="",AO55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO55,FIND("-",AO55)-1),"")=AW55,IFERROR(--MID(AO55,FIND("-",AO55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AO55,FIND("-",AO55)-1),""))-(IFERROR(--MID(AO55,FIND("-",AO55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AO55,FIND("-",AO55)-1),""))-(IFERROR(--MID(AO55,FIND("-",AO55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AO55,FIND("-",AO55)-1),""))=(AW55))+2*((IFERROR(--MID(AO55,FIND("-",AO55)+1,99),""))=(AX55))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ55" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR55" s="11" t="str">
+      <c r="AR55" s="11">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS55" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT55" s="11" t="str">
+      <c r="AT55" s="11">
         <f t="shared" si="5"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU55" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV55" s="11" t="str">
+      <c r="AV55" s="11">
         <f>IF(OR($C55="",AU55=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU55,FIND("-",AU55)-1),"")=AW55,IFERROR(--MID(AU55,FIND("-",AU55)+1,99),"")=AX55),10,5*(SIGN((IFERROR(--LEFT(AU55,FIND("-",AU55)-1),""))-(IFERROR(--MID(AU55,FIND("-",AU55)+1,99),"")))=SIGN((AW55)-(AX55)))+2*(((IFERROR(--LEFT(AU55,FIND("-",AU55)-1),""))-(IFERROR(--MID(AU55,FIND("-",AU55)+1,99),"")))=((AW55)-(AX55)))+2*((IFERROR(--LEFT(AU55,FIND("-",AU55)-1),""))=(AW55))+2*((IFERROR(--MID(AU55,FIND("-",AU55)+1,99),""))=(AX55))),""))</f>
-        <v/>
-      </c>
-      <c r="AW55" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW55" s="11">
         <f>IF($C55="","",IFERROR(--LEFT($C55,FIND("-",$C55)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX55" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AX55" s="11">
         <f>IF($C55="","",IFERROR(--MID($C55,FIND("-",$C55)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
       <c r="B56" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="10"/>
+      <c r="C56" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="D56" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F56" s="11" t="str">
+      <c r="F56" s="11">
         <f>IF(OR($C56="",E56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E56,FIND("-",E56)-1),"")=AW56,IFERROR(--MID(E56,FIND("-",E56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(E56,FIND("-",E56)-1),""))-(IFERROR(--MID(E56,FIND("-",E56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(E56,FIND("-",E56)-1),""))-(IFERROR(--MID(E56,FIND("-",E56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(E56,FIND("-",E56)-1),""))=(AW56))+2*((IFERROR(--MID(E56,FIND("-",E56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H56" s="11" t="str">
+      <c r="H56" s="11">
         <f>IF(OR($C56="",G56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G56,FIND("-",G56)-1),"")=AW56,IFERROR(--MID(G56,FIND("-",G56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(G56,FIND("-",G56)-1),""))-(IFERROR(--MID(G56,FIND("-",G56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(G56,FIND("-",G56)-1),""))-(IFERROR(--MID(G56,FIND("-",G56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(G56,FIND("-",G56)-1),""))=(AW56))+2*((IFERROR(--MID(G56,FIND("-",G56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I56" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J56" s="11" t="str">
+      <c r="J56" s="11">
         <f>IF(OR($C56="",I56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I56,FIND("-",I56)-1),"")=AW56,IFERROR(--MID(I56,FIND("-",I56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(I56,FIND("-",I56)-1),""))-(IFERROR(--MID(I56,FIND("-",I56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(I56,FIND("-",I56)-1),""))-(IFERROR(--MID(I56,FIND("-",I56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(I56,FIND("-",I56)-1),""))=(AW56))+2*((IFERROR(--MID(I56,FIND("-",I56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K56" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L56" s="11" t="str">
+      <c r="L56" s="11">
         <f>IF(OR($C56="",K56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K56,FIND("-",K56)-1),"")=AW56,IFERROR(--MID(K56,FIND("-",K56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(K56,FIND("-",K56)-1),""))-(IFERROR(--MID(K56,FIND("-",K56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(K56,FIND("-",K56)-1),""))-(IFERROR(--MID(K56,FIND("-",K56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(K56,FIND("-",K56)-1),""))=(AW56))+2*((IFERROR(--MID(K56,FIND("-",K56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M56" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="N56" s="11" t="str">
+      <c r="N56" s="11">
         <f>IF(OR($C56="",M56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M56,FIND("-",M56)-1),"")=AW56,IFERROR(--MID(M56,FIND("-",M56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(M56,FIND("-",M56)-1),""))-(IFERROR(--MID(M56,FIND("-",M56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(M56,FIND("-",M56)-1),""))-(IFERROR(--MID(M56,FIND("-",M56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(M56,FIND("-",M56)-1),""))=(AW56))+2*((IFERROR(--MID(M56,FIND("-",M56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O56" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="P56" s="11" t="str">
+      <c r="P56" s="11">
         <f>IF(OR($C56="",O56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O56,FIND("-",O56)-1),"")=AW56,IFERROR(--MID(O56,FIND("-",O56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(O56,FIND("-",O56)-1),""))-(IFERROR(--MID(O56,FIND("-",O56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(O56,FIND("-",O56)-1),""))-(IFERROR(--MID(O56,FIND("-",O56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(O56,FIND("-",O56)-1),""))=(AW56))+2*((IFERROR(--MID(O56,FIND("-",O56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q56" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="R56" s="11" t="str">
+      <c r="R56" s="11">
         <f>IF(OR($C56="",Q56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q56,FIND("-",Q56)-1),"")=AW56,IFERROR(--MID(Q56,FIND("-",Q56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(Q56,FIND("-",Q56)-1),""))-(IFERROR(--MID(Q56,FIND("-",Q56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(Q56,FIND("-",Q56)-1),""))-(IFERROR(--MID(Q56,FIND("-",Q56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(Q56,FIND("-",Q56)-1),""))=(AW56))+2*((IFERROR(--MID(Q56,FIND("-",Q56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S56" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T56" s="11" t="str">
+      <c r="T56" s="11">
         <f>IF(OR($C56="",S56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S56,FIND("-",S56)-1),"")=AW56,IFERROR(--MID(S56,FIND("-",S56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(S56,FIND("-",S56)-1),""))-(IFERROR(--MID(S56,FIND("-",S56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(S56,FIND("-",S56)-1),""))-(IFERROR(--MID(S56,FIND("-",S56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(S56,FIND("-",S56)-1),""))=(AW56))+2*((IFERROR(--MID(S56,FIND("-",S56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="U56" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V56" s="11" t="str">
+      <c r="V56" s="11">
         <f>IF(OR($C56="",U56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U56,FIND("-",U56)-1),"")=AW56,IFERROR(--MID(U56,FIND("-",U56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(U56,FIND("-",U56)-1),""))-(IFERROR(--MID(U56,FIND("-",U56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(U56,FIND("-",U56)-1),""))-(IFERROR(--MID(U56,FIND("-",U56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(U56,FIND("-",U56)-1),""))=(AW56))+2*((IFERROR(--MID(U56,FIND("-",U56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W56" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X56" s="11" t="str">
+      <c r="X56" s="11">
         <f>IF(OR($C56="",W56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W56,FIND("-",W56)-1),"")=AW56,IFERROR(--MID(W56,FIND("-",W56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(W56,FIND("-",W56)-1),""))-(IFERROR(--MID(W56,FIND("-",W56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(W56,FIND("-",W56)-1),""))-(IFERROR(--MID(W56,FIND("-",W56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(W56,FIND("-",W56)-1),""))=(AW56))+2*((IFERROR(--MID(W56,FIND("-",W56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Y56" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z56" s="11" t="str">
+      <c r="Z56" s="11">
         <f>IF(OR($C56="",Y56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y56,FIND("-",Y56)-1),"")=AW56,IFERROR(--MID(Y56,FIND("-",Y56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(Y56,FIND("-",Y56)-1),""))-(IFERROR(--MID(Y56,FIND("-",Y56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(Y56,FIND("-",Y56)-1),""))-(IFERROR(--MID(Y56,FIND("-",Y56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(Y56,FIND("-",Y56)-1),""))=(AW56))+2*((IFERROR(--MID(Y56,FIND("-",Y56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA56" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB56" s="11" t="str">
+      <c r="AB56" s="11">
         <f>IF(OR($C56="",AA56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA56,FIND("-",AA56)-1),"")=AW56,IFERROR(--MID(AA56,FIND("-",AA56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AA56,FIND("-",AA56)-1),""))-(IFERROR(--MID(AA56,FIND("-",AA56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AA56,FIND("-",AA56)-1),""))-(IFERROR(--MID(AA56,FIND("-",AA56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AA56,FIND("-",AA56)-1),""))=(AW56))+2*((IFERROR(--MID(AA56,FIND("-",AA56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC56" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AD56" s="11" t="str">
+      <c r="AD56" s="11">
         <f>IF(OR($C56="",AC56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC56,FIND("-",AC56)-1),"")=AW56,IFERROR(--MID(AC56,FIND("-",AC56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AC56,FIND("-",AC56)-1),""))-(IFERROR(--MID(AC56,FIND("-",AC56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AC56,FIND("-",AC56)-1),""))-(IFERROR(--MID(AC56,FIND("-",AC56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AC56,FIND("-",AC56)-1),""))=(AW56))+2*((IFERROR(--MID(AC56,FIND("-",AC56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE56" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF56" s="11" t="str">
+      <c r="AF56" s="11">
         <f>IF(OR($C56="",AE56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE56,FIND("-",AE56)-1),"")=AW56,IFERROR(--MID(AE56,FIND("-",AE56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AE56,FIND("-",AE56)-1),""))-(IFERROR(--MID(AE56,FIND("-",AE56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AE56,FIND("-",AE56)-1),""))-(IFERROR(--MID(AE56,FIND("-",AE56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AE56,FIND("-",AE56)-1),""))=(AW56))+2*((IFERROR(--MID(AE56,FIND("-",AE56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG56" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH56" s="11" t="str">
+      <c r="AH56" s="11">
         <f>IF(OR($C56="",AG56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG56,FIND("-",AG56)-1),"")=AW56,IFERROR(--MID(AG56,FIND("-",AG56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AG56,FIND("-",AG56)-1),""))-(IFERROR(--MID(AG56,FIND("-",AG56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AG56,FIND("-",AG56)-1),""))-(IFERROR(--MID(AG56,FIND("-",AG56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AG56,FIND("-",AG56)-1),""))=(AW56))+2*((IFERROR(--MID(AG56,FIND("-",AG56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI56" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ56" s="11" t="str">
+      <c r="AJ56" s="11">
         <f>IF(OR($C56="",AI56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI56,FIND("-",AI56)-1),"")=AW56,IFERROR(--MID(AI56,FIND("-",AI56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AI56,FIND("-",AI56)-1),""))-(IFERROR(--MID(AI56,FIND("-",AI56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AI56,FIND("-",AI56)-1),""))-(IFERROR(--MID(AI56,FIND("-",AI56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AI56,FIND("-",AI56)-1),""))=(AW56))+2*((IFERROR(--MID(AI56,FIND("-",AI56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK56" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL56" s="11" t="str">
+      <c r="AL56" s="11">
         <f>IF(OR($C56="",AK56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK56,FIND("-",AK56)-1),"")=AW56,IFERROR(--MID(AK56,FIND("-",AK56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AK56,FIND("-",AK56)-1),""))-(IFERROR(--MID(AK56,FIND("-",AK56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AK56,FIND("-",AK56)-1),""))-(IFERROR(--MID(AK56,FIND("-",AK56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AK56,FIND("-",AK56)-1),""))=(AW56))+2*((IFERROR(--MID(AK56,FIND("-",AK56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM56" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AN56" s="11" t="str">
+      <c r="AN56" s="11">
         <f>IF(OR($C56="",AM56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM56,FIND("-",AM56)-1),"")=AW56,IFERROR(--MID(AM56,FIND("-",AM56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AM56,FIND("-",AM56)-1),""))-(IFERROR(--MID(AM56,FIND("-",AM56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AM56,FIND("-",AM56)-1),""))-(IFERROR(--MID(AM56,FIND("-",AM56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AM56,FIND("-",AM56)-1),""))=(AW56))+2*((IFERROR(--MID(AM56,FIND("-",AM56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO56" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP56" s="11" t="str">
+      <c r="AP56" s="11">
         <f>IF(OR($C56="",AO56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO56,FIND("-",AO56)-1),"")=AW56,IFERROR(--MID(AO56,FIND("-",AO56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AO56,FIND("-",AO56)-1),""))-(IFERROR(--MID(AO56,FIND("-",AO56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AO56,FIND("-",AO56)-1),""))-(IFERROR(--MID(AO56,FIND("-",AO56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AO56,FIND("-",AO56)-1),""))=(AW56))+2*((IFERROR(--MID(AO56,FIND("-",AO56)+1,99),""))=(AX56))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ56" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AR56" s="11" t="str">
+      <c r="AR56" s="11">
         <f t="shared" si="4"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS56" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AT56" s="11" t="str">
+      <c r="AT56" s="11">
         <f t="shared" si="5"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU56" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AV56" s="11" t="str">
+      <c r="AV56" s="11">
         <f>IF(OR($C56="",AU56=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU56,FIND("-",AU56)-1),"")=AW56,IFERROR(--MID(AU56,FIND("-",AU56)+1,99),"")=AX56),10,5*(SIGN((IFERROR(--LEFT(AU56,FIND("-",AU56)-1),""))-(IFERROR(--MID(AU56,FIND("-",AU56)+1,99),"")))=SIGN((AW56)-(AX56)))+2*(((IFERROR(--LEFT(AU56,FIND("-",AU56)-1),""))-(IFERROR(--MID(AU56,FIND("-",AU56)+1,99),"")))=((AW56)-(AX56)))+2*((IFERROR(--LEFT(AU56,FIND("-",AU56)-1),""))=(AW56))+2*((IFERROR(--MID(AU56,FIND("-",AU56)+1,99),""))=(AX56))),""))</f>
-        <v/>
-      </c>
-      <c r="AW56" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW56" s="11">
         <f>IF($C56="","",IFERROR(--LEFT($C56,FIND("-",$C56)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX56" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX56" s="11">
         <f>IF($C56="","",IFERROR(--MID($C56,FIND("-",$C56)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
       <c r="B57" s="18"/>
       <c r="C57" s="13"/>
@@ -9127,7 +9144,7 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
@@ -9181,703 +9198,711 @@
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D59" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F59" s="11" t="str">
+      <c r="F59" s="11">
         <f>IF(OR($C59="",E59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E59,FIND("-",E59)-1),"")=AW59,IFERROR(--MID(E59,FIND("-",E59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(E59,FIND("-",E59)-1),""))-(IFERROR(--MID(E59,FIND("-",E59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(E59,FIND("-",E59)-1),""))-(IFERROR(--MID(E59,FIND("-",E59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(E59,FIND("-",E59)-1),""))=(AW59))+2*((IFERROR(--MID(E59,FIND("-",E59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H59" s="11" t="str">
+      <c r="H59" s="11">
         <f>IF(OR($C59="",G59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G59,FIND("-",G59)-1),"")=AW59,IFERROR(--MID(G59,FIND("-",G59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(G59,FIND("-",G59)-1),""))-(IFERROR(--MID(G59,FIND("-",G59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(G59,FIND("-",G59)-1),""))-(IFERROR(--MID(G59,FIND("-",G59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(G59,FIND("-",G59)-1),""))=(AW59))+2*((IFERROR(--MID(G59,FIND("-",G59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I59" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J59" s="11" t="str">
+      <c r="J59" s="11">
         <f>IF(OR($C59="",I59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I59,FIND("-",I59)-1),"")=AW59,IFERROR(--MID(I59,FIND("-",I59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(I59,FIND("-",I59)-1),""))-(IFERROR(--MID(I59,FIND("-",I59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(I59,FIND("-",I59)-1),""))-(IFERROR(--MID(I59,FIND("-",I59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(I59,FIND("-",I59)-1),""))=(AW59))+2*((IFERROR(--MID(I59,FIND("-",I59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L59" s="11" t="str">
+      <c r="L59" s="11">
         <f>IF(OR($C59="",K59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K59,FIND("-",K59)-1),"")=AW59,IFERROR(--MID(K59,FIND("-",K59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(K59,FIND("-",K59)-1),""))-(IFERROR(--MID(K59,FIND("-",K59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(K59,FIND("-",K59)-1),""))-(IFERROR(--MID(K59,FIND("-",K59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(K59,FIND("-",K59)-1),""))=(AW59))+2*((IFERROR(--MID(K59,FIND("-",K59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M59" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N59" s="11" t="str">
+      <c r="N59" s="11">
         <f>IF(OR($C59="",M59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M59,FIND("-",M59)-1),"")=AW59,IFERROR(--MID(M59,FIND("-",M59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(M59,FIND("-",M59)-1),""))-(IFERROR(--MID(M59,FIND("-",M59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(M59,FIND("-",M59)-1),""))-(IFERROR(--MID(M59,FIND("-",M59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(M59,FIND("-",M59)-1),""))=(AW59))+2*((IFERROR(--MID(M59,FIND("-",M59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P59" s="11" t="str">
+      <c r="P59" s="11">
         <f>IF(OR($C59="",O59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O59,FIND("-",O59)-1),"")=AW59,IFERROR(--MID(O59,FIND("-",O59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(O59,FIND("-",O59)-1),""))-(IFERROR(--MID(O59,FIND("-",O59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(O59,FIND("-",O59)-1),""))-(IFERROR(--MID(O59,FIND("-",O59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(O59,FIND("-",O59)-1),""))=(AW59))+2*((IFERROR(--MID(O59,FIND("-",O59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q59" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="R59" s="11" t="str">
+      <c r="R59" s="11">
         <f>IF(OR($C59="",Q59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q59,FIND("-",Q59)-1),"")=AW59,IFERROR(--MID(Q59,FIND("-",Q59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(Q59,FIND("-",Q59)-1),""))-(IFERROR(--MID(Q59,FIND("-",Q59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(Q59,FIND("-",Q59)-1),""))-(IFERROR(--MID(Q59,FIND("-",Q59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(Q59,FIND("-",Q59)-1),""))=(AW59))+2*((IFERROR(--MID(Q59,FIND("-",Q59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S59" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T59" s="11" t="str">
+      <c r="T59" s="11">
         <f>IF(OR($C59="",S59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S59,FIND("-",S59)-1),"")=AW59,IFERROR(--MID(S59,FIND("-",S59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(S59,FIND("-",S59)-1),""))-(IFERROR(--MID(S59,FIND("-",S59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(S59,FIND("-",S59)-1),""))-(IFERROR(--MID(S59,FIND("-",S59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(S59,FIND("-",S59)-1),""))=(AW59))+2*((IFERROR(--MID(S59,FIND("-",S59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U59" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V59" s="11" t="str">
+      <c r="V59" s="11">
         <f>IF(OR($C59="",U59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U59,FIND("-",U59)-1),"")=AW59,IFERROR(--MID(U59,FIND("-",U59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(U59,FIND("-",U59)-1),""))-(IFERROR(--MID(U59,FIND("-",U59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(U59,FIND("-",U59)-1),""))-(IFERROR(--MID(U59,FIND("-",U59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(U59,FIND("-",U59)-1),""))=(AW59))+2*((IFERROR(--MID(U59,FIND("-",U59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W59" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X59" s="11" t="str">
+      <c r="X59" s="11">
         <f>IF(OR($C59="",W59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W59,FIND("-",W59)-1),"")=AW59,IFERROR(--MID(W59,FIND("-",W59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(W59,FIND("-",W59)-1),""))-(IFERROR(--MID(W59,FIND("-",W59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(W59,FIND("-",W59)-1),""))-(IFERROR(--MID(W59,FIND("-",W59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(W59,FIND("-",W59)-1),""))=(AW59))+2*((IFERROR(--MID(W59,FIND("-",W59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y59" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z59" s="11" t="str">
+      <c r="Z59" s="11">
         <f>IF(OR($C59="",Y59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y59,FIND("-",Y59)-1),"")=AW59,IFERROR(--MID(Y59,FIND("-",Y59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(Y59,FIND("-",Y59)-1),""))-(IFERROR(--MID(Y59,FIND("-",Y59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(Y59,FIND("-",Y59)-1),""))-(IFERROR(--MID(Y59,FIND("-",Y59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(Y59,FIND("-",Y59)-1),""))=(AW59))+2*((IFERROR(--MID(Y59,FIND("-",Y59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA59" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB59" s="11" t="str">
+      <c r="AB59" s="11">
         <f>IF(OR($C59="",AA59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA59,FIND("-",AA59)-1),"")=AW59,IFERROR(--MID(AA59,FIND("-",AA59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AA59,FIND("-",AA59)-1),""))-(IFERROR(--MID(AA59,FIND("-",AA59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AA59,FIND("-",AA59)-1),""))-(IFERROR(--MID(AA59,FIND("-",AA59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AA59,FIND("-",AA59)-1),""))=(AW59))+2*((IFERROR(--MID(AA59,FIND("-",AA59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC59" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD59" s="11" t="str">
+      <c r="AD59" s="11">
         <f>IF(OR($C59="",AC59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC59,FIND("-",AC59)-1),"")=AW59,IFERROR(--MID(AC59,FIND("-",AC59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AC59,FIND("-",AC59)-1),""))-(IFERROR(--MID(AC59,FIND("-",AC59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AC59,FIND("-",AC59)-1),""))-(IFERROR(--MID(AC59,FIND("-",AC59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AC59,FIND("-",AC59)-1),""))=(AW59))+2*((IFERROR(--MID(AC59,FIND("-",AC59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE59" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF59" s="11" t="str">
+      <c r="AF59" s="11">
         <f>IF(OR($C59="",AE59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE59,FIND("-",AE59)-1),"")=AW59,IFERROR(--MID(AE59,FIND("-",AE59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AE59,FIND("-",AE59)-1),""))-(IFERROR(--MID(AE59,FIND("-",AE59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AE59,FIND("-",AE59)-1),""))-(IFERROR(--MID(AE59,FIND("-",AE59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AE59,FIND("-",AE59)-1),""))=(AW59))+2*((IFERROR(--MID(AE59,FIND("-",AE59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG59" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH59" s="11" t="str">
+      <c r="AH59" s="11">
         <f>IF(OR($C59="",AG59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG59,FIND("-",AG59)-1),"")=AW59,IFERROR(--MID(AG59,FIND("-",AG59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AG59,FIND("-",AG59)-1),""))-(IFERROR(--MID(AG59,FIND("-",AG59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AG59,FIND("-",AG59)-1),""))-(IFERROR(--MID(AG59,FIND("-",AG59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AG59,FIND("-",AG59)-1),""))=(AW59))+2*((IFERROR(--MID(AG59,FIND("-",AG59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI59" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ59" s="11" t="str">
+      <c r="AJ59" s="11">
         <f>IF(OR($C59="",AI59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI59,FIND("-",AI59)-1),"")=AW59,IFERROR(--MID(AI59,FIND("-",AI59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AI59,FIND("-",AI59)-1),""))-(IFERROR(--MID(AI59,FIND("-",AI59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AI59,FIND("-",AI59)-1),""))-(IFERROR(--MID(AI59,FIND("-",AI59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AI59,FIND("-",AI59)-1),""))=(AW59))+2*((IFERROR(--MID(AI59,FIND("-",AI59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK59" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL59" s="11" t="str">
+      <c r="AL59" s="11">
         <f>IF(OR($C59="",AK59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK59,FIND("-",AK59)-1),"")=AW59,IFERROR(--MID(AK59,FIND("-",AK59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AK59,FIND("-",AK59)-1),""))-(IFERROR(--MID(AK59,FIND("-",AK59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AK59,FIND("-",AK59)-1),""))-(IFERROR(--MID(AK59,FIND("-",AK59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AK59,FIND("-",AK59)-1),""))=(AW59))+2*((IFERROR(--MID(AK59,FIND("-",AK59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM59" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN59" s="11" t="str">
+      <c r="AN59" s="11">
         <f>IF(OR($C59="",AM59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM59,FIND("-",AM59)-1),"")=AW59,IFERROR(--MID(AM59,FIND("-",AM59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AM59,FIND("-",AM59)-1),""))-(IFERROR(--MID(AM59,FIND("-",AM59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AM59,FIND("-",AM59)-1),""))-(IFERROR(--MID(AM59,FIND("-",AM59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AM59,FIND("-",AM59)-1),""))=(AW59))+2*((IFERROR(--MID(AM59,FIND("-",AM59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO59" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP59" s="11" t="str">
+      <c r="AP59" s="11">
         <f>IF(OR($C59="",AO59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO59,FIND("-",AO59)-1),"")=AW59,IFERROR(--MID(AO59,FIND("-",AO59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AO59,FIND("-",AO59)-1),""))-(IFERROR(--MID(AO59,FIND("-",AO59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AO59,FIND("-",AO59)-1),""))-(IFERROR(--MID(AO59,FIND("-",AO59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AO59,FIND("-",AO59)-1),""))=(AW59))+2*((IFERROR(--MID(AO59,FIND("-",AO59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ59" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR59" s="11" t="str">
+      <c r="AR59" s="11">
         <f>IF(OR($C59="",AQ59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ59,FIND("-",AQ59)-1),"")=AW59,IFERROR(--MID(AQ59,FIND("-",AQ59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AQ59,FIND("-",AQ59)-1),""))-(IFERROR(--MID(AQ59,FIND("-",AQ59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AQ59,FIND("-",AQ59)-1),""))-(IFERROR(--MID(AQ59,FIND("-",AQ59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AQ59,FIND("-",AQ59)-1),""))=(AW59))+2*((IFERROR(--MID(AQ59,FIND("-",AQ59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS59" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AT59" s="11" t="str">
+      <c r="AT59" s="11">
         <f>IF(OR($C59="",AS59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS59,FIND("-",AS59)-1),"")=AW59,IFERROR(--MID(AS59,FIND("-",AS59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AS59,FIND("-",AS59)-1),""))-(IFERROR(--MID(AS59,FIND("-",AS59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AS59,FIND("-",AS59)-1),""))-(IFERROR(--MID(AS59,FIND("-",AS59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AS59,FIND("-",AS59)-1),""))=(AW59))+2*((IFERROR(--MID(AS59,FIND("-",AS59)+1,99),""))=(AX59))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU59" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV59" s="11" t="str">
+      <c r="AV59" s="11">
         <f>IF(OR($C59="",AU59=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU59,FIND("-",AU59)-1),"")=AW59,IFERROR(--MID(AU59,FIND("-",AU59)+1,99),"")=AX59),10,5*(SIGN((IFERROR(--LEFT(AU59,FIND("-",AU59)-1),""))-(IFERROR(--MID(AU59,FIND("-",AU59)+1,99),"")))=SIGN((AW59)-(AX59)))+2*(((IFERROR(--LEFT(AU59,FIND("-",AU59)-1),""))-(IFERROR(--MID(AU59,FIND("-",AU59)+1,99),"")))=((AW59)-(AX59)))+2*((IFERROR(--LEFT(AU59,FIND("-",AU59)-1),""))=(AW59))+2*((IFERROR(--MID(AU59,FIND("-",AU59)+1,99),""))=(AX59))),""))</f>
-        <v/>
-      </c>
-      <c r="AW59" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW59" s="11">
         <f>IF($C59="","",IFERROR(--LEFT($C59,FIND("-",$C59)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX59" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX59" s="11">
         <f>IF($C59="","",IFERROR(--MID($C59,FIND("-",$C59)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
       <c r="B60" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="10"/>
+      <c r="C60" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="D60" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F60" s="11" t="str">
+      <c r="F60" s="11">
         <f>IF(OR($C60="",E60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E60,FIND("-",E60)-1),"")=AW60,IFERROR(--MID(E60,FIND("-",E60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(E60,FIND("-",E60)-1),""))-(IFERROR(--MID(E60,FIND("-",E60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(E60,FIND("-",E60)-1),""))-(IFERROR(--MID(E60,FIND("-",E60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(E60,FIND("-",E60)-1),""))=(AW60))+2*((IFERROR(--MID(E60,FIND("-",E60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H60" s="11" t="str">
+      <c r="H60" s="11">
         <f>IF(OR($C60="",G60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G60,FIND("-",G60)-1),"")=AW60,IFERROR(--MID(G60,FIND("-",G60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(G60,FIND("-",G60)-1),""))-(IFERROR(--MID(G60,FIND("-",G60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(G60,FIND("-",G60)-1),""))-(IFERROR(--MID(G60,FIND("-",G60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(G60,FIND("-",G60)-1),""))=(AW60))+2*((IFERROR(--MID(G60,FIND("-",G60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I60" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J60" s="11" t="str">
+      <c r="J60" s="11">
         <f>IF(OR($C60="",I60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I60,FIND("-",I60)-1),"")=AW60,IFERROR(--MID(I60,FIND("-",I60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(I60,FIND("-",I60)-1),""))-(IFERROR(--MID(I60,FIND("-",I60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(I60,FIND("-",I60)-1),""))-(IFERROR(--MID(I60,FIND("-",I60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(I60,FIND("-",I60)-1),""))=(AW60))+2*((IFERROR(--MID(I60,FIND("-",I60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K60" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L60" s="11" t="str">
+      <c r="L60" s="11">
         <f>IF(OR($C60="",K60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K60,FIND("-",K60)-1),"")=AW60,IFERROR(--MID(K60,FIND("-",K60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(K60,FIND("-",K60)-1),""))-(IFERROR(--MID(K60,FIND("-",K60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(K60,FIND("-",K60)-1),""))-(IFERROR(--MID(K60,FIND("-",K60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(K60,FIND("-",K60)-1),""))=(AW60))+2*((IFERROR(--MID(K60,FIND("-",K60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M60" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="N60" s="11" t="str">
+      <c r="N60" s="11">
         <f>IF(OR($C60="",M60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M60,FIND("-",M60)-1),"")=AW60,IFERROR(--MID(M60,FIND("-",M60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(M60,FIND("-",M60)-1),""))-(IFERROR(--MID(M60,FIND("-",M60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(M60,FIND("-",M60)-1),""))-(IFERROR(--MID(M60,FIND("-",M60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(M60,FIND("-",M60)-1),""))=(AW60))+2*((IFERROR(--MID(M60,FIND("-",M60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O60" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P60" s="11" t="str">
+      <c r="P60" s="11">
         <f>IF(OR($C60="",O60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O60,FIND("-",O60)-1),"")=AW60,IFERROR(--MID(O60,FIND("-",O60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(O60,FIND("-",O60)-1),""))-(IFERROR(--MID(O60,FIND("-",O60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(O60,FIND("-",O60)-1),""))-(IFERROR(--MID(O60,FIND("-",O60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(O60,FIND("-",O60)-1),""))=(AW60))+2*((IFERROR(--MID(O60,FIND("-",O60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q60" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="R60" s="11" t="str">
+      <c r="R60" s="11">
         <f>IF(OR($C60="",Q60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q60,FIND("-",Q60)-1),"")=AW60,IFERROR(--MID(Q60,FIND("-",Q60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(Q60,FIND("-",Q60)-1),""))-(IFERROR(--MID(Q60,FIND("-",Q60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(Q60,FIND("-",Q60)-1),""))-(IFERROR(--MID(Q60,FIND("-",Q60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(Q60,FIND("-",Q60)-1),""))=(AW60))+2*((IFERROR(--MID(Q60,FIND("-",Q60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S60" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T60" s="11" t="str">
+      <c r="T60" s="11">
         <f>IF(OR($C60="",S60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S60,FIND("-",S60)-1),"")=AW60,IFERROR(--MID(S60,FIND("-",S60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(S60,FIND("-",S60)-1),""))-(IFERROR(--MID(S60,FIND("-",S60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(S60,FIND("-",S60)-1),""))-(IFERROR(--MID(S60,FIND("-",S60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(S60,FIND("-",S60)-1),""))=(AW60))+2*((IFERROR(--MID(S60,FIND("-",S60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U60" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V60" s="11" t="str">
+      <c r="V60" s="11">
         <f>IF(OR($C60="",U60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U60,FIND("-",U60)-1),"")=AW60,IFERROR(--MID(U60,FIND("-",U60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(U60,FIND("-",U60)-1),""))-(IFERROR(--MID(U60,FIND("-",U60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(U60,FIND("-",U60)-1),""))-(IFERROR(--MID(U60,FIND("-",U60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(U60,FIND("-",U60)-1),""))=(AW60))+2*((IFERROR(--MID(U60,FIND("-",U60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W60" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="X60" s="11" t="str">
+      <c r="X60" s="11">
         <f>IF(OR($C60="",W60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W60,FIND("-",W60)-1),"")=AW60,IFERROR(--MID(W60,FIND("-",W60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(W60,FIND("-",W60)-1),""))-(IFERROR(--MID(W60,FIND("-",W60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(W60,FIND("-",W60)-1),""))-(IFERROR(--MID(W60,FIND("-",W60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(W60,FIND("-",W60)-1),""))=(AW60))+2*((IFERROR(--MID(W60,FIND("-",W60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y60" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z60" s="11" t="str">
+      <c r="Z60" s="11">
         <f>IF(OR($C60="",Y60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y60,FIND("-",Y60)-1),"")=AW60,IFERROR(--MID(Y60,FIND("-",Y60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(Y60,FIND("-",Y60)-1),""))-(IFERROR(--MID(Y60,FIND("-",Y60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(Y60,FIND("-",Y60)-1),""))-(IFERROR(--MID(Y60,FIND("-",Y60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(Y60,FIND("-",Y60)-1),""))=(AW60))+2*((IFERROR(--MID(Y60,FIND("-",Y60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA60" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="AB60" s="11" t="str">
+      <c r="AB60" s="11">
         <f>IF(OR($C60="",AA60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA60,FIND("-",AA60)-1),"")=AW60,IFERROR(--MID(AA60,FIND("-",AA60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AA60,FIND("-",AA60)-1),""))-(IFERROR(--MID(AA60,FIND("-",AA60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AA60,FIND("-",AA60)-1),""))-(IFERROR(--MID(AA60,FIND("-",AA60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AA60,FIND("-",AA60)-1),""))=(AW60))+2*((IFERROR(--MID(AA60,FIND("-",AA60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC60" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AD60" s="11" t="str">
+      <c r="AD60" s="11">
         <f>IF(OR($C60="",AC60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC60,FIND("-",AC60)-1),"")=AW60,IFERROR(--MID(AC60,FIND("-",AC60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AC60,FIND("-",AC60)-1),""))-(IFERROR(--MID(AC60,FIND("-",AC60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AC60,FIND("-",AC60)-1),""))-(IFERROR(--MID(AC60,FIND("-",AC60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AC60,FIND("-",AC60)-1),""))=(AW60))+2*((IFERROR(--MID(AC60,FIND("-",AC60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE60" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AF60" s="11" t="str">
+      <c r="AF60" s="11">
         <f>IF(OR($C60="",AE60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE60,FIND("-",AE60)-1),"")=AW60,IFERROR(--MID(AE60,FIND("-",AE60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AE60,FIND("-",AE60)-1),""))-(IFERROR(--MID(AE60,FIND("-",AE60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AE60,FIND("-",AE60)-1),""))-(IFERROR(--MID(AE60,FIND("-",AE60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AE60,FIND("-",AE60)-1),""))=(AW60))+2*((IFERROR(--MID(AE60,FIND("-",AE60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG60" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH60" s="11" t="str">
+      <c r="AH60" s="11">
         <f>IF(OR($C60="",AG60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG60,FIND("-",AG60)-1),"")=AW60,IFERROR(--MID(AG60,FIND("-",AG60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AG60,FIND("-",AG60)-1),""))-(IFERROR(--MID(AG60,FIND("-",AG60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AG60,FIND("-",AG60)-1),""))-(IFERROR(--MID(AG60,FIND("-",AG60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AG60,FIND("-",AG60)-1),""))=(AW60))+2*((IFERROR(--MID(AG60,FIND("-",AG60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI60" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AJ60" s="11" t="str">
+      <c r="AJ60" s="11">
         <f>IF(OR($C60="",AI60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI60,FIND("-",AI60)-1),"")=AW60,IFERROR(--MID(AI60,FIND("-",AI60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AI60,FIND("-",AI60)-1),""))-(IFERROR(--MID(AI60,FIND("-",AI60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AI60,FIND("-",AI60)-1),""))-(IFERROR(--MID(AI60,FIND("-",AI60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AI60,FIND("-",AI60)-1),""))=(AW60))+2*((IFERROR(--MID(AI60,FIND("-",AI60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK60" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL60" s="11" t="str">
+      <c r="AL60" s="11">
         <f>IF(OR($C60="",AK60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK60,FIND("-",AK60)-1),"")=AW60,IFERROR(--MID(AK60,FIND("-",AK60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AK60,FIND("-",AK60)-1),""))-(IFERROR(--MID(AK60,FIND("-",AK60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AK60,FIND("-",AK60)-1),""))-(IFERROR(--MID(AK60,FIND("-",AK60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AK60,FIND("-",AK60)-1),""))=(AW60))+2*((IFERROR(--MID(AK60,FIND("-",AK60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM60" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN60" s="11" t="str">
+      <c r="AN60" s="11">
         <f>IF(OR($C60="",AM60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM60,FIND("-",AM60)-1),"")=AW60,IFERROR(--MID(AM60,FIND("-",AM60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AM60,FIND("-",AM60)-1),""))-(IFERROR(--MID(AM60,FIND("-",AM60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AM60,FIND("-",AM60)-1),""))-(IFERROR(--MID(AM60,FIND("-",AM60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AM60,FIND("-",AM60)-1),""))=(AW60))+2*((IFERROR(--MID(AM60,FIND("-",AM60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO60" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AP60" s="11" t="str">
+      <c r="AP60" s="11">
         <f>IF(OR($C60="",AO60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO60,FIND("-",AO60)-1),"")=AW60,IFERROR(--MID(AO60,FIND("-",AO60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AO60,FIND("-",AO60)-1),""))-(IFERROR(--MID(AO60,FIND("-",AO60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AO60,FIND("-",AO60)-1),""))-(IFERROR(--MID(AO60,FIND("-",AO60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AO60,FIND("-",AO60)-1),""))=(AW60))+2*((IFERROR(--MID(AO60,FIND("-",AO60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ60" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR60" s="11" t="str">
+      <c r="AR60" s="11">
         <f>IF(OR($C60="",AQ60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ60,FIND("-",AQ60)-1),"")=AW60,IFERROR(--MID(AQ60,FIND("-",AQ60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AQ60,FIND("-",AQ60)-1),""))-(IFERROR(--MID(AQ60,FIND("-",AQ60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AQ60,FIND("-",AQ60)-1),""))-(IFERROR(--MID(AQ60,FIND("-",AQ60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AQ60,FIND("-",AQ60)-1),""))=(AW60))+2*((IFERROR(--MID(AQ60,FIND("-",AQ60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS60" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT60" s="11" t="str">
+      <c r="AT60" s="11">
         <f>IF(OR($C60="",AS60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS60,FIND("-",AS60)-1),"")=AW60,IFERROR(--MID(AS60,FIND("-",AS60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AS60,FIND("-",AS60)-1),""))-(IFERROR(--MID(AS60,FIND("-",AS60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AS60,FIND("-",AS60)-1),""))-(IFERROR(--MID(AS60,FIND("-",AS60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AS60,FIND("-",AS60)-1),""))=(AW60))+2*((IFERROR(--MID(AS60,FIND("-",AS60)+1,99),""))=(AX60))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU60" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV60" s="11" t="str">
+      <c r="AV60" s="11">
         <f>IF(OR($C60="",AU60=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU60,FIND("-",AU60)-1),"")=AW60,IFERROR(--MID(AU60,FIND("-",AU60)+1,99),"")=AX60),10,5*(SIGN((IFERROR(--LEFT(AU60,FIND("-",AU60)-1),""))-(IFERROR(--MID(AU60,FIND("-",AU60)+1,99),"")))=SIGN((AW60)-(AX60)))+2*(((IFERROR(--LEFT(AU60,FIND("-",AU60)-1),""))-(IFERROR(--MID(AU60,FIND("-",AU60)+1,99),"")))=((AW60)-(AX60)))+2*((IFERROR(--LEFT(AU60,FIND("-",AU60)-1),""))=(AW60))+2*((IFERROR(--MID(AU60,FIND("-",AU60)+1,99),""))=(AX60))),""))</f>
-        <v/>
-      </c>
-      <c r="AW60" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW60" s="11">
         <f>IF($C60="","",IFERROR(--LEFT($C60,FIND("-",$C60)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX60" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX60" s="11">
         <f>IF($C60="","",IFERROR(--MID($C60,FIND("-",$C60)+1,99),""))</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="D61" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F61" s="11" t="str">
+      <c r="F61" s="11">
         <f>IF(OR($C61="",E61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E61,FIND("-",E61)-1),"")=AW61,IFERROR(--MID(E61,FIND("-",E61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(E61,FIND("-",E61)-1),""))-(IFERROR(--MID(E61,FIND("-",E61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(E61,FIND("-",E61)-1),""))-(IFERROR(--MID(E61,FIND("-",E61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(E61,FIND("-",E61)-1),""))=(AW61))+2*((IFERROR(--MID(E61,FIND("-",E61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H61" s="11" t="str">
+      <c r="H61" s="11">
         <f>IF(OR($C61="",G61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G61,FIND("-",G61)-1),"")=AW61,IFERROR(--MID(G61,FIND("-",G61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(G61,FIND("-",G61)-1),""))-(IFERROR(--MID(G61,FIND("-",G61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(G61,FIND("-",G61)-1),""))-(IFERROR(--MID(G61,FIND("-",G61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(G61,FIND("-",G61)-1),""))=(AW61))+2*((IFERROR(--MID(G61,FIND("-",G61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J61" s="11" t="str">
+      <c r="J61" s="11">
         <f>IF(OR($C61="",I61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I61,FIND("-",I61)-1),"")=AW61,IFERROR(--MID(I61,FIND("-",I61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(I61,FIND("-",I61)-1),""))-(IFERROR(--MID(I61,FIND("-",I61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(I61,FIND("-",I61)-1),""))-(IFERROR(--MID(I61,FIND("-",I61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(I61,FIND("-",I61)-1),""))=(AW61))+2*((IFERROR(--MID(I61,FIND("-",I61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K61" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L61" s="11" t="str">
+      <c r="L61" s="11">
         <f>IF(OR($C61="",K61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K61,FIND("-",K61)-1),"")=AW61,IFERROR(--MID(K61,FIND("-",K61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(K61,FIND("-",K61)-1),""))-(IFERROR(--MID(K61,FIND("-",K61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(K61,FIND("-",K61)-1),""))-(IFERROR(--MID(K61,FIND("-",K61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(K61,FIND("-",K61)-1),""))=(AW61))+2*((IFERROR(--MID(K61,FIND("-",K61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M61" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="N61" s="11" t="str">
+      <c r="N61" s="11">
         <f>IF(OR($C61="",M61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M61,FIND("-",M61)-1),"")=AW61,IFERROR(--MID(M61,FIND("-",M61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(M61,FIND("-",M61)-1),""))-(IFERROR(--MID(M61,FIND("-",M61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(M61,FIND("-",M61)-1),""))-(IFERROR(--MID(M61,FIND("-",M61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(M61,FIND("-",M61)-1),""))=(AW61))+2*((IFERROR(--MID(M61,FIND("-",M61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P61" s="11" t="str">
+      <c r="P61" s="11">
         <f>IF(OR($C61="",O61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O61,FIND("-",O61)-1),"")=AW61,IFERROR(--MID(O61,FIND("-",O61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(O61,FIND("-",O61)-1),""))-(IFERROR(--MID(O61,FIND("-",O61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(O61,FIND("-",O61)-1),""))-(IFERROR(--MID(O61,FIND("-",O61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(O61,FIND("-",O61)-1),""))=(AW61))+2*((IFERROR(--MID(O61,FIND("-",O61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="R61" s="11" t="str">
+      <c r="R61" s="11">
         <f>IF(OR($C61="",Q61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q61,FIND("-",Q61)-1),"")=AW61,IFERROR(--MID(Q61,FIND("-",Q61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(Q61,FIND("-",Q61)-1),""))-(IFERROR(--MID(Q61,FIND("-",Q61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(Q61,FIND("-",Q61)-1),""))-(IFERROR(--MID(Q61,FIND("-",Q61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(Q61,FIND("-",Q61)-1),""))=(AW61))+2*((IFERROR(--MID(Q61,FIND("-",Q61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="S61" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T61" s="11" t="str">
+      <c r="T61" s="11">
         <f>IF(OR($C61="",S61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S61,FIND("-",S61)-1),"")=AW61,IFERROR(--MID(S61,FIND("-",S61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(S61,FIND("-",S61)-1),""))-(IFERROR(--MID(S61,FIND("-",S61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(S61,FIND("-",S61)-1),""))-(IFERROR(--MID(S61,FIND("-",S61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(S61,FIND("-",S61)-1),""))=(AW61))+2*((IFERROR(--MID(S61,FIND("-",S61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U61" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V61" s="11" t="str">
+      <c r="V61" s="11">
         <f>IF(OR($C61="",U61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U61,FIND("-",U61)-1),"")=AW61,IFERROR(--MID(U61,FIND("-",U61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(U61,FIND("-",U61)-1),""))-(IFERROR(--MID(U61,FIND("-",U61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(U61,FIND("-",U61)-1),""))-(IFERROR(--MID(U61,FIND("-",U61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(U61,FIND("-",U61)-1),""))=(AW61))+2*((IFERROR(--MID(U61,FIND("-",U61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X61" s="11" t="str">
+      <c r="X61" s="11">
         <f>IF(OR($C61="",W61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W61,FIND("-",W61)-1),"")=AW61,IFERROR(--MID(W61,FIND("-",W61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(W61,FIND("-",W61)-1),""))-(IFERROR(--MID(W61,FIND("-",W61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(W61,FIND("-",W61)-1),""))-(IFERROR(--MID(W61,FIND("-",W61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(W61,FIND("-",W61)-1),""))=(AW61))+2*((IFERROR(--MID(W61,FIND("-",W61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z61" s="11" t="str">
+      <c r="Z61" s="11">
         <f>IF(OR($C61="",Y61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y61,FIND("-",Y61)-1),"")=AW61,IFERROR(--MID(Y61,FIND("-",Y61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(Y61,FIND("-",Y61)-1),""))-(IFERROR(--MID(Y61,FIND("-",Y61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(Y61,FIND("-",Y61)-1),""))-(IFERROR(--MID(Y61,FIND("-",Y61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(Y61,FIND("-",Y61)-1),""))=(AW61))+2*((IFERROR(--MID(Y61,FIND("-",Y61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA61" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AB61" s="11" t="str">
+      <c r="AB61" s="11">
         <f>IF(OR($C61="",AA61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA61,FIND("-",AA61)-1),"")=AW61,IFERROR(--MID(AA61,FIND("-",AA61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AA61,FIND("-",AA61)-1),""))-(IFERROR(--MID(AA61,FIND("-",AA61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AA61,FIND("-",AA61)-1),""))-(IFERROR(--MID(AA61,FIND("-",AA61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AA61,FIND("-",AA61)-1),""))=(AW61))+2*((IFERROR(--MID(AA61,FIND("-",AA61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC61" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD61" s="11" t="str">
+      <c r="AD61" s="11">
         <f>IF(OR($C61="",AC61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC61,FIND("-",AC61)-1),"")=AW61,IFERROR(--MID(AC61,FIND("-",AC61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AC61,FIND("-",AC61)-1),""))-(IFERROR(--MID(AC61,FIND("-",AC61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AC61,FIND("-",AC61)-1),""))-(IFERROR(--MID(AC61,FIND("-",AC61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AC61,FIND("-",AC61)-1),""))=(AW61))+2*((IFERROR(--MID(AC61,FIND("-",AC61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE61" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF61" s="11" t="str">
+      <c r="AF61" s="11">
         <f>IF(OR($C61="",AE61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE61,FIND("-",AE61)-1),"")=AW61,IFERROR(--MID(AE61,FIND("-",AE61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AE61,FIND("-",AE61)-1),""))-(IFERROR(--MID(AE61,FIND("-",AE61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AE61,FIND("-",AE61)-1),""))-(IFERROR(--MID(AE61,FIND("-",AE61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AE61,FIND("-",AE61)-1),""))=(AW61))+2*((IFERROR(--MID(AE61,FIND("-",AE61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG61" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH61" s="11" t="str">
+      <c r="AH61" s="11">
         <f>IF(OR($C61="",AG61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG61,FIND("-",AG61)-1),"")=AW61,IFERROR(--MID(AG61,FIND("-",AG61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AG61,FIND("-",AG61)-1),""))-(IFERROR(--MID(AG61,FIND("-",AG61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AG61,FIND("-",AG61)-1),""))-(IFERROR(--MID(AG61,FIND("-",AG61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AG61,FIND("-",AG61)-1),""))=(AW61))+2*((IFERROR(--MID(AG61,FIND("-",AG61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ61" s="11" t="str">
+      <c r="AJ61" s="11">
         <f>IF(OR($C61="",AI61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI61,FIND("-",AI61)-1),"")=AW61,IFERROR(--MID(AI61,FIND("-",AI61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AI61,FIND("-",AI61)-1),""))-(IFERROR(--MID(AI61,FIND("-",AI61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AI61,FIND("-",AI61)-1),""))-(IFERROR(--MID(AI61,FIND("-",AI61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AI61,FIND("-",AI61)-1),""))=(AW61))+2*((IFERROR(--MID(AI61,FIND("-",AI61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL61" s="11" t="str">
+      <c r="AL61" s="11">
         <f>IF(OR($C61="",AK61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK61,FIND("-",AK61)-1),"")=AW61,IFERROR(--MID(AK61,FIND("-",AK61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AK61,FIND("-",AK61)-1),""))-(IFERROR(--MID(AK61,FIND("-",AK61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AK61,FIND("-",AK61)-1),""))-(IFERROR(--MID(AK61,FIND("-",AK61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AK61,FIND("-",AK61)-1),""))=(AW61))+2*((IFERROR(--MID(AK61,FIND("-",AK61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AN61" s="11" t="str">
+      <c r="AN61" s="11">
         <f>IF(OR($C61="",AM61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM61,FIND("-",AM61)-1),"")=AW61,IFERROR(--MID(AM61,FIND("-",AM61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AM61,FIND("-",AM61)-1),""))-(IFERROR(--MID(AM61,FIND("-",AM61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AM61,FIND("-",AM61)-1),""))-(IFERROR(--MID(AM61,FIND("-",AM61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AM61,FIND("-",AM61)-1),""))=(AW61))+2*((IFERROR(--MID(AM61,FIND("-",AM61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AP61" s="11" t="str">
+      <c r="AP61" s="11">
         <f>IF(OR($C61="",AO61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO61,FIND("-",AO61)-1),"")=AW61,IFERROR(--MID(AO61,FIND("-",AO61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AO61,FIND("-",AO61)-1),""))-(IFERROR(--MID(AO61,FIND("-",AO61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AO61,FIND("-",AO61)-1),""))-(IFERROR(--MID(AO61,FIND("-",AO61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AO61,FIND("-",AO61)-1),""))=(AW61))+2*((IFERROR(--MID(AO61,FIND("-",AO61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ61" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AR61" s="11" t="str">
+      <c r="AR61" s="11">
         <f>IF(OR($C61="",AQ61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ61,FIND("-",AQ61)-1),"")=AW61,IFERROR(--MID(AQ61,FIND("-",AQ61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AQ61,FIND("-",AQ61)-1),""))-(IFERROR(--MID(AQ61,FIND("-",AQ61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AQ61,FIND("-",AQ61)-1),""))-(IFERROR(--MID(AQ61,FIND("-",AQ61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AQ61,FIND("-",AQ61)-1),""))=(AW61))+2*((IFERROR(--MID(AQ61,FIND("-",AQ61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AT61" s="11" t="str">
+      <c r="AT61" s="11">
         <f>IF(OR($C61="",AS61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS61,FIND("-",AS61)-1),"")=AW61,IFERROR(--MID(AS61,FIND("-",AS61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AS61,FIND("-",AS61)-1),""))-(IFERROR(--MID(AS61,FIND("-",AS61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AS61,FIND("-",AS61)-1),""))-(IFERROR(--MID(AS61,FIND("-",AS61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AS61,FIND("-",AS61)-1),""))=(AW61))+2*((IFERROR(--MID(AS61,FIND("-",AS61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AU61" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV61" s="11" t="str">
+      <c r="AV61" s="11">
         <f>IF(OR($C61="",AU61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU61,FIND("-",AU61)-1),"")=AW61,IFERROR(--MID(AU61,FIND("-",AU61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AU61,FIND("-",AU61)-1),""))-(IFERROR(--MID(AU61,FIND("-",AU61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AU61,FIND("-",AU61)-1),""))-(IFERROR(--MID(AU61,FIND("-",AU61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AU61,FIND("-",AU61)-1),""))=(AW61))+2*((IFERROR(--MID(AU61,FIND("-",AU61)+1,99),""))=(AX61))),""))</f>
-        <v/>
-      </c>
-      <c r="AW61" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW61" s="11">
         <f>IF($C61="","",IFERROR(--LEFT($C61,FIND("-",$C61)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX61" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX61" s="11">
         <f>IF($C61="","",IFERROR(--MID($C61,FIND("-",$C61)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="10"/>
+      <c r="C62" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D62" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F62" s="11" t="str">
+      <c r="F62" s="11">
         <f>IF(OR($C62="",E62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E62,FIND("-",E62)-1),"")=AW62,IFERROR(--MID(E62,FIND("-",E62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(E62,FIND("-",E62)-1),""))-(IFERROR(--MID(E62,FIND("-",E62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(E62,FIND("-",E62)-1),""))-(IFERROR(--MID(E62,FIND("-",E62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(E62,FIND("-",E62)-1),""))=(AW62))+2*((IFERROR(--MID(E62,FIND("-",E62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H62" s="11" t="str">
+      <c r="H62" s="11">
         <f>IF(OR($C62="",G62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G62,FIND("-",G62)-1),"")=AW62,IFERROR(--MID(G62,FIND("-",G62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(G62,FIND("-",G62)-1),""))-(IFERROR(--MID(G62,FIND("-",G62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(G62,FIND("-",G62)-1),""))-(IFERROR(--MID(G62,FIND("-",G62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(G62,FIND("-",G62)-1),""))=(AW62))+2*((IFERROR(--MID(G62,FIND("-",G62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I62" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J62" s="11" t="str">
+      <c r="J62" s="11">
         <f>IF(OR($C62="",I62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I62,FIND("-",I62)-1),"")=AW62,IFERROR(--MID(I62,FIND("-",I62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(I62,FIND("-",I62)-1),""))-(IFERROR(--MID(I62,FIND("-",I62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(I62,FIND("-",I62)-1),""))-(IFERROR(--MID(I62,FIND("-",I62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(I62,FIND("-",I62)-1),""))=(AW62))+2*((IFERROR(--MID(I62,FIND("-",I62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K62" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="L62" s="11" t="str">
+      <c r="L62" s="11">
         <f>IF(OR($C62="",K62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K62,FIND("-",K62)-1),"")=AW62,IFERROR(--MID(K62,FIND("-",K62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(K62,FIND("-",K62)-1),""))-(IFERROR(--MID(K62,FIND("-",K62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(K62,FIND("-",K62)-1),""))-(IFERROR(--MID(K62,FIND("-",K62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(K62,FIND("-",K62)-1),""))=(AW62))+2*((IFERROR(--MID(K62,FIND("-",K62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N62" s="11" t="str">
+      <c r="N62" s="11">
         <f>IF(OR($C62="",M62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M62,FIND("-",M62)-1),"")=AW62,IFERROR(--MID(M62,FIND("-",M62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(M62,FIND("-",M62)-1),""))-(IFERROR(--MID(M62,FIND("-",M62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(M62,FIND("-",M62)-1),""))-(IFERROR(--MID(M62,FIND("-",M62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(M62,FIND("-",M62)-1),""))=(AW62))+2*((IFERROR(--MID(M62,FIND("-",M62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O62" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="P62" s="11" t="str">
+      <c r="P62" s="11">
         <f>IF(OR($C62="",O62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O62,FIND("-",O62)-1),"")=AW62,IFERROR(--MID(O62,FIND("-",O62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(O62,FIND("-",O62)-1),""))-(IFERROR(--MID(O62,FIND("-",O62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(O62,FIND("-",O62)-1),""))-(IFERROR(--MID(O62,FIND("-",O62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(O62,FIND("-",O62)-1),""))=(AW62))+2*((IFERROR(--MID(O62,FIND("-",O62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q62" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R62" s="11" t="str">
+      <c r="R62" s="11">
         <f>IF(OR($C62="",Q62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q62,FIND("-",Q62)-1),"")=AW62,IFERROR(--MID(Q62,FIND("-",Q62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(Q62,FIND("-",Q62)-1),""))-(IFERROR(--MID(Q62,FIND("-",Q62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(Q62,FIND("-",Q62)-1),""))-(IFERROR(--MID(Q62,FIND("-",Q62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(Q62,FIND("-",Q62)-1),""))=(AW62))+2*((IFERROR(--MID(Q62,FIND("-",Q62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S62" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T62" s="11" t="str">
+      <c r="T62" s="11">
         <f>IF(OR($C62="",S62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S62,FIND("-",S62)-1),"")=AW62,IFERROR(--MID(S62,FIND("-",S62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(S62,FIND("-",S62)-1),""))-(IFERROR(--MID(S62,FIND("-",S62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(S62,FIND("-",S62)-1),""))-(IFERROR(--MID(S62,FIND("-",S62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(S62,FIND("-",S62)-1),""))=(AW62))+2*((IFERROR(--MID(S62,FIND("-",S62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V62" s="11" t="str">
+      <c r="V62" s="11">
         <f>IF(OR($C62="",U62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U62,FIND("-",U62)-1),"")=AW62,IFERROR(--MID(U62,FIND("-",U62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(U62,FIND("-",U62)-1),""))-(IFERROR(--MID(U62,FIND("-",U62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(U62,FIND("-",U62)-1),""))-(IFERROR(--MID(U62,FIND("-",U62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(U62,FIND("-",U62)-1),""))=(AW62))+2*((IFERROR(--MID(U62,FIND("-",U62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X62" s="11" t="str">
+      <c r="X62" s="11">
         <f>IF(OR($C62="",W62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W62,FIND("-",W62)-1),"")=AW62,IFERROR(--MID(W62,FIND("-",W62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(W62,FIND("-",W62)-1),""))-(IFERROR(--MID(W62,FIND("-",W62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(W62,FIND("-",W62)-1),""))-(IFERROR(--MID(W62,FIND("-",W62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(W62,FIND("-",W62)-1),""))=(AW62))+2*((IFERROR(--MID(W62,FIND("-",W62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y62" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z62" s="11" t="str">
+      <c r="Z62" s="11">
         <f>IF(OR($C62="",Y62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y62,FIND("-",Y62)-1),"")=AW62,IFERROR(--MID(Y62,FIND("-",Y62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(Y62,FIND("-",Y62)-1),""))-(IFERROR(--MID(Y62,FIND("-",Y62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(Y62,FIND("-",Y62)-1),""))-(IFERROR(--MID(Y62,FIND("-",Y62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(Y62,FIND("-",Y62)-1),""))=(AW62))+2*((IFERROR(--MID(Y62,FIND("-",Y62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AB62" s="11" t="str">
+      <c r="AB62" s="11">
         <f>IF(OR($C62="",AA62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA62,FIND("-",AA62)-1),"")=AW62,IFERROR(--MID(AA62,FIND("-",AA62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AA62,FIND("-",AA62)-1),""))-(IFERROR(--MID(AA62,FIND("-",AA62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AA62,FIND("-",AA62)-1),""))-(IFERROR(--MID(AA62,FIND("-",AA62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AA62,FIND("-",AA62)-1),""))=(AW62))+2*((IFERROR(--MID(AA62,FIND("-",AA62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD62" s="11" t="str">
+      <c r="AD62" s="11">
         <f>IF(OR($C62="",AC62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC62,FIND("-",AC62)-1),"")=AW62,IFERROR(--MID(AC62,FIND("-",AC62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AC62,FIND("-",AC62)-1),""))-(IFERROR(--MID(AC62,FIND("-",AC62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AC62,FIND("-",AC62)-1),""))-(IFERROR(--MID(AC62,FIND("-",AC62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AC62,FIND("-",AC62)-1),""))=(AW62))+2*((IFERROR(--MID(AC62,FIND("-",AC62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF62" s="11" t="str">
+      <c r="AF62" s="11">
         <f>IF(OR($C62="",AE62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE62,FIND("-",AE62)-1),"")=AW62,IFERROR(--MID(AE62,FIND("-",AE62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AE62,FIND("-",AE62)-1),""))-(IFERROR(--MID(AE62,FIND("-",AE62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AE62,FIND("-",AE62)-1),""))-(IFERROR(--MID(AE62,FIND("-",AE62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AE62,FIND("-",AE62)-1),""))=(AW62))+2*((IFERROR(--MID(AE62,FIND("-",AE62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH62" s="11" t="str">
+      <c r="AH62" s="11">
         <f>IF(OR($C62="",AG62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG62,FIND("-",AG62)-1),"")=AW62,IFERROR(--MID(AG62,FIND("-",AG62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AG62,FIND("-",AG62)-1),""))-(IFERROR(--MID(AG62,FIND("-",AG62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AG62,FIND("-",AG62)-1),""))-(IFERROR(--MID(AG62,FIND("-",AG62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AG62,FIND("-",AG62)-1),""))=(AW62))+2*((IFERROR(--MID(AG62,FIND("-",AG62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI62" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ62" s="11" t="str">
+      <c r="AJ62" s="11">
         <f>IF(OR($C62="",AI62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI62,FIND("-",AI62)-1),"")=AW62,IFERROR(--MID(AI62,FIND("-",AI62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AI62,FIND("-",AI62)-1),""))-(IFERROR(--MID(AI62,FIND("-",AI62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AI62,FIND("-",AI62)-1),""))-(IFERROR(--MID(AI62,FIND("-",AI62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AI62,FIND("-",AI62)-1),""))=(AW62))+2*((IFERROR(--MID(AI62,FIND("-",AI62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL62" s="11" t="str">
+      <c r="AL62" s="11">
         <f>IF(OR($C62="",AK62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK62,FIND("-",AK62)-1),"")=AW62,IFERROR(--MID(AK62,FIND("-",AK62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AK62,FIND("-",AK62)-1),""))-(IFERROR(--MID(AK62,FIND("-",AK62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AK62,FIND("-",AK62)-1),""))-(IFERROR(--MID(AK62,FIND("-",AK62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AK62,FIND("-",AK62)-1),""))=(AW62))+2*((IFERROR(--MID(AK62,FIND("-",AK62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM62" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN62" s="11" t="str">
+      <c r="AN62" s="11">
         <f>IF(OR($C62="",AM62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM62,FIND("-",AM62)-1),"")=AW62,IFERROR(--MID(AM62,FIND("-",AM62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AM62,FIND("-",AM62)-1),""))-(IFERROR(--MID(AM62,FIND("-",AM62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AM62,FIND("-",AM62)-1),""))-(IFERROR(--MID(AM62,FIND("-",AM62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AM62,FIND("-",AM62)-1),""))=(AW62))+2*((IFERROR(--MID(AM62,FIND("-",AM62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO62" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP62" s="11" t="str">
+      <c r="AP62" s="11">
         <f>IF(OR($C62="",AO62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO62,FIND("-",AO62)-1),"")=AW62,IFERROR(--MID(AO62,FIND("-",AO62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AO62,FIND("-",AO62)-1),""))-(IFERROR(--MID(AO62,FIND("-",AO62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AO62,FIND("-",AO62)-1),""))-(IFERROR(--MID(AO62,FIND("-",AO62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AO62,FIND("-",AO62)-1),""))=(AW62))+2*((IFERROR(--MID(AO62,FIND("-",AO62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ62" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR62" s="11" t="str">
+      <c r="AR62" s="11">
         <f>IF(OR($C62="",AQ62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ62,FIND("-",AQ62)-1),"")=AW62,IFERROR(--MID(AQ62,FIND("-",AQ62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AQ62,FIND("-",AQ62)-1),""))-(IFERROR(--MID(AQ62,FIND("-",AQ62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AQ62,FIND("-",AQ62)-1),""))-(IFERROR(--MID(AQ62,FIND("-",AQ62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AQ62,FIND("-",AQ62)-1),""))=(AW62))+2*((IFERROR(--MID(AQ62,FIND("-",AQ62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS62" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AT62" s="11" t="str">
+      <c r="AT62" s="11">
         <f>IF(OR($C62="",AS62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS62,FIND("-",AS62)-1),"")=AW62,IFERROR(--MID(AS62,FIND("-",AS62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AS62,FIND("-",AS62)-1),""))-(IFERROR(--MID(AS62,FIND("-",AS62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AS62,FIND("-",AS62)-1),""))-(IFERROR(--MID(AS62,FIND("-",AS62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AS62,FIND("-",AS62)-1),""))=(AW62))+2*((IFERROR(--MID(AS62,FIND("-",AS62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV62" s="11" t="str">
+      <c r="AV62" s="11">
         <f>IF(OR($C62="",AU62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU62,FIND("-",AU62)-1),"")=AW62,IFERROR(--MID(AU62,FIND("-",AU62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AU62,FIND("-",AU62)-1),""))-(IFERROR(--MID(AU62,FIND("-",AU62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AU62,FIND("-",AU62)-1),""))-(IFERROR(--MID(AU62,FIND("-",AU62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AU62,FIND("-",AU62)-1),""))=(AW62))+2*((IFERROR(--MID(AU62,FIND("-",AU62)+1,99),""))=(AX62))),""))</f>
-        <v/>
-      </c>
-      <c r="AW62" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW62" s="11">
         <f>IF($C62="","",IFERROR(--LEFT($C62,FIND("-",$C62)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX62" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX62" s="11">
         <f>IF($C62="","",IFERROR(--MID($C62,FIND("-",$C62)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="12"/>
       <c r="B63" s="18"/>
       <c r="C63" s="13"/>
@@ -9935,7 +9960,7 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
@@ -9989,355 +10014,359 @@
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>1</v>
       </c>
       <c r="B65" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="D65" s="1" t="s">
         <v>81</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F65" s="11" t="str">
+      <c r="F65" s="11">
         <f>IF(OR($C65="",E65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E65,FIND("-",E65)-1),"")=AW65,IFERROR(--MID(E65,FIND("-",E65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(E65,FIND("-",E65)-1),""))-(IFERROR(--MID(E65,FIND("-",E65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(E65,FIND("-",E65)-1),""))-(IFERROR(--MID(E65,FIND("-",E65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(E65,FIND("-",E65)-1),""))=(AW65))+2*((IFERROR(--MID(E65,FIND("-",E65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H65" s="11" t="str">
+      <c r="H65" s="11">
         <f>IF(OR($C65="",G65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G65,FIND("-",G65)-1),"")=AW65,IFERROR(--MID(G65,FIND("-",G65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(G65,FIND("-",G65)-1),""))-(IFERROR(--MID(G65,FIND("-",G65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(G65,FIND("-",G65)-1),""))-(IFERROR(--MID(G65,FIND("-",G65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(G65,FIND("-",G65)-1),""))=(AW65))+2*((IFERROR(--MID(G65,FIND("-",G65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J65" s="11" t="str">
+      <c r="J65" s="11">
         <f>IF(OR($C65="",I65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I65,FIND("-",I65)-1),"")=AW65,IFERROR(--MID(I65,FIND("-",I65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(I65,FIND("-",I65)-1),""))-(IFERROR(--MID(I65,FIND("-",I65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(I65,FIND("-",I65)-1),""))-(IFERROR(--MID(I65,FIND("-",I65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(I65,FIND("-",I65)-1),""))=(AW65))+2*((IFERROR(--MID(I65,FIND("-",I65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K65" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L65" s="11" t="str">
+      <c r="L65" s="11">
         <f>IF(OR($C65="",K65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K65,FIND("-",K65)-1),"")=AW65,IFERROR(--MID(K65,FIND("-",K65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(K65,FIND("-",K65)-1),""))-(IFERROR(--MID(K65,FIND("-",K65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(K65,FIND("-",K65)-1),""))-(IFERROR(--MID(K65,FIND("-",K65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(K65,FIND("-",K65)-1),""))=(AW65))+2*((IFERROR(--MID(K65,FIND("-",K65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M65" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N65" s="11" t="str">
+      <c r="N65" s="11">
         <f>IF(OR($C65="",M65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M65,FIND("-",M65)-1),"")=AW65,IFERROR(--MID(M65,FIND("-",M65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(M65,FIND("-",M65)-1),""))-(IFERROR(--MID(M65,FIND("-",M65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(M65,FIND("-",M65)-1),""))-(IFERROR(--MID(M65,FIND("-",M65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(M65,FIND("-",M65)-1),""))=(AW65))+2*((IFERROR(--MID(M65,FIND("-",M65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P65" s="11" t="str">
+      <c r="P65" s="11">
         <f>IF(OR($C65="",O65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O65,FIND("-",O65)-1),"")=AW65,IFERROR(--MID(O65,FIND("-",O65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(O65,FIND("-",O65)-1),""))-(IFERROR(--MID(O65,FIND("-",O65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(O65,FIND("-",O65)-1),""))-(IFERROR(--MID(O65,FIND("-",O65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(O65,FIND("-",O65)-1),""))=(AW65))+2*((IFERROR(--MID(O65,FIND("-",O65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q65" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="R65" s="11" t="str">
+      <c r="R65" s="11">
         <f>IF(OR($C65="",Q65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q65,FIND("-",Q65)-1),"")=AW65,IFERROR(--MID(Q65,FIND("-",Q65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(Q65,FIND("-",Q65)-1),""))-(IFERROR(--MID(Q65,FIND("-",Q65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(Q65,FIND("-",Q65)-1),""))-(IFERROR(--MID(Q65,FIND("-",Q65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(Q65,FIND("-",Q65)-1),""))=(AW65))+2*((IFERROR(--MID(Q65,FIND("-",Q65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S65" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T65" s="11" t="str">
+      <c r="T65" s="11">
         <f>IF(OR($C65="",S65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S65,FIND("-",S65)-1),"")=AW65,IFERROR(--MID(S65,FIND("-",S65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(S65,FIND("-",S65)-1),""))-(IFERROR(--MID(S65,FIND("-",S65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(S65,FIND("-",S65)-1),""))-(IFERROR(--MID(S65,FIND("-",S65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(S65,FIND("-",S65)-1),""))=(AW65))+2*((IFERROR(--MID(S65,FIND("-",S65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U65" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="V65" s="11" t="str">
+      <c r="V65" s="11">
         <f>IF(OR($C65="",U65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U65,FIND("-",U65)-1),"")=AW65,IFERROR(--MID(U65,FIND("-",U65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(U65,FIND("-",U65)-1),""))-(IFERROR(--MID(U65,FIND("-",U65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(U65,FIND("-",U65)-1),""))-(IFERROR(--MID(U65,FIND("-",U65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(U65,FIND("-",U65)-1),""))=(AW65))+2*((IFERROR(--MID(U65,FIND("-",U65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X65" s="11" t="str">
+      <c r="X65" s="11">
         <f>IF(OR($C65="",W65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W65,FIND("-",W65)-1),"")=AW65,IFERROR(--MID(W65,FIND("-",W65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(W65,FIND("-",W65)-1),""))-(IFERROR(--MID(W65,FIND("-",W65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(W65,FIND("-",W65)-1),""))-(IFERROR(--MID(W65,FIND("-",W65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(W65,FIND("-",W65)-1),""))=(AW65))+2*((IFERROR(--MID(W65,FIND("-",W65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z65" s="11" t="str">
+      <c r="Z65" s="11">
         <f>IF(OR($C65="",Y65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y65,FIND("-",Y65)-1),"")=AW65,IFERROR(--MID(Y65,FIND("-",Y65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(Y65,FIND("-",Y65)-1),""))-(IFERROR(--MID(Y65,FIND("-",Y65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(Y65,FIND("-",Y65)-1),""))-(IFERROR(--MID(Y65,FIND("-",Y65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(Y65,FIND("-",Y65)-1),""))=(AW65))+2*((IFERROR(--MID(Y65,FIND("-",Y65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA65" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AB65" s="11" t="str">
+      <c r="AB65" s="11">
         <f>IF(OR($C65="",AA65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA65,FIND("-",AA65)-1),"")=AW65,IFERROR(--MID(AA65,FIND("-",AA65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AA65,FIND("-",AA65)-1),""))-(IFERROR(--MID(AA65,FIND("-",AA65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AA65,FIND("-",AA65)-1),""))-(IFERROR(--MID(AA65,FIND("-",AA65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AA65,FIND("-",AA65)-1),""))=(AW65))+2*((IFERROR(--MID(AA65,FIND("-",AA65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD65" s="11" t="str">
+      <c r="AD65" s="11">
         <f>IF(OR($C65="",AC65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC65,FIND("-",AC65)-1),"")=AW65,IFERROR(--MID(AC65,FIND("-",AC65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AC65,FIND("-",AC65)-1),""))-(IFERROR(--MID(AC65,FIND("-",AC65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AC65,FIND("-",AC65)-1),""))-(IFERROR(--MID(AC65,FIND("-",AC65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AC65,FIND("-",AC65)-1),""))=(AW65))+2*((IFERROR(--MID(AC65,FIND("-",AC65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF65" s="11" t="str">
+      <c r="AF65" s="11">
         <f>IF(OR($C65="",AE65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE65,FIND("-",AE65)-1),"")=AW65,IFERROR(--MID(AE65,FIND("-",AE65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AE65,FIND("-",AE65)-1),""))-(IFERROR(--MID(AE65,FIND("-",AE65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AE65,FIND("-",AE65)-1),""))-(IFERROR(--MID(AE65,FIND("-",AE65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AE65,FIND("-",AE65)-1),""))=(AW65))+2*((IFERROR(--MID(AE65,FIND("-",AE65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH65" s="11" t="str">
+      <c r="AH65" s="11">
         <f>IF(OR($C65="",AG65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG65,FIND("-",AG65)-1),"")=AW65,IFERROR(--MID(AG65,FIND("-",AG65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AG65,FIND("-",AG65)-1),""))-(IFERROR(--MID(AG65,FIND("-",AG65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AG65,FIND("-",AG65)-1),""))-(IFERROR(--MID(AG65,FIND("-",AG65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AG65,FIND("-",AG65)-1),""))=(AW65))+2*((IFERROR(--MID(AG65,FIND("-",AG65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI65" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ65" s="11" t="str">
+      <c r="AJ65" s="11">
         <f>IF(OR($C65="",AI65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI65,FIND("-",AI65)-1),"")=AW65,IFERROR(--MID(AI65,FIND("-",AI65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AI65,FIND("-",AI65)-1),""))-(IFERROR(--MID(AI65,FIND("-",AI65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AI65,FIND("-",AI65)-1),""))-(IFERROR(--MID(AI65,FIND("-",AI65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AI65,FIND("-",AI65)-1),""))=(AW65))+2*((IFERROR(--MID(AI65,FIND("-",AI65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK65" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AL65" s="11" t="str">
+      <c r="AL65" s="11">
         <f>IF(OR($C65="",AK65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK65,FIND("-",AK65)-1),"")=AW65,IFERROR(--MID(AK65,FIND("-",AK65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AK65,FIND("-",AK65)-1),""))-(IFERROR(--MID(AK65,FIND("-",AK65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AK65,FIND("-",AK65)-1),""))-(IFERROR(--MID(AK65,FIND("-",AK65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AK65,FIND("-",AK65)-1),""))=(AW65))+2*((IFERROR(--MID(AK65,FIND("-",AK65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM65" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN65" s="11" t="str">
+      <c r="AN65" s="11">
         <f>IF(OR($C65="",AM65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM65,FIND("-",AM65)-1),"")=AW65,IFERROR(--MID(AM65,FIND("-",AM65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AM65,FIND("-",AM65)-1),""))-(IFERROR(--MID(AM65,FIND("-",AM65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AM65,FIND("-",AM65)-1),""))-(IFERROR(--MID(AM65,FIND("-",AM65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AM65,FIND("-",AM65)-1),""))=(AW65))+2*((IFERROR(--MID(AM65,FIND("-",AM65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP65" s="11" t="str">
+      <c r="AP65" s="11">
         <f>IF(OR($C65="",AO65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO65,FIND("-",AO65)-1),"")=AW65,IFERROR(--MID(AO65,FIND("-",AO65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AO65,FIND("-",AO65)-1),""))-(IFERROR(--MID(AO65,FIND("-",AO65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AO65,FIND("-",AO65)-1),""))-(IFERROR(--MID(AO65,FIND("-",AO65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AO65,FIND("-",AO65)-1),""))=(AW65))+2*((IFERROR(--MID(AO65,FIND("-",AO65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ65" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR65" s="11" t="str">
+      <c r="AR65" s="11">
         <f>IF(OR($C65="",AQ65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ65,FIND("-",AQ65)-1),"")=AW65,IFERROR(--MID(AQ65,FIND("-",AQ65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AQ65,FIND("-",AQ65)-1),""))-(IFERROR(--MID(AQ65,FIND("-",AQ65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AQ65,FIND("-",AQ65)-1),""))-(IFERROR(--MID(AQ65,FIND("-",AQ65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AQ65,FIND("-",AQ65)-1),""))=(AW65))+2*((IFERROR(--MID(AQ65,FIND("-",AQ65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS65" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AT65" s="11" t="str">
+      <c r="AT65" s="11">
         <f>IF(OR($C65="",AS65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS65,FIND("-",AS65)-1),"")=AW65,IFERROR(--MID(AS65,FIND("-",AS65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AS65,FIND("-",AS65)-1),""))-(IFERROR(--MID(AS65,FIND("-",AS65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AS65,FIND("-",AS65)-1),""))-(IFERROR(--MID(AS65,FIND("-",AS65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AS65,FIND("-",AS65)-1),""))=(AW65))+2*((IFERROR(--MID(AS65,FIND("-",AS65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV65" s="11" t="str">
+      <c r="AV65" s="11">
         <f>IF(OR($C65="",AU65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU65,FIND("-",AU65)-1),"")=AW65,IFERROR(--MID(AU65,FIND("-",AU65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AU65,FIND("-",AU65)-1),""))-(IFERROR(--MID(AU65,FIND("-",AU65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AU65,FIND("-",AU65)-1),""))-(IFERROR(--MID(AU65,FIND("-",AU65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AU65,FIND("-",AU65)-1),""))=(AW65))+2*((IFERROR(--MID(AU65,FIND("-",AU65)+1,99),""))=(AX65))),""))</f>
-        <v/>
-      </c>
-      <c r="AW65" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW65" s="11">
         <f>IF($C65="","",IFERROR(--LEFT($C65,FIND("-",$C65)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX65" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX65" s="11">
         <f>IF($C65="","",IFERROR(--MID($C65,FIND("-",$C65)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
       <c r="B66" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="10"/>
+      <c r="C66" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="D66" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F66" s="11" t="str">
+      <c r="F66" s="11">
         <f>IF(OR($C66="",E66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E66,FIND("-",E66)-1),"")=AW66,IFERROR(--MID(E66,FIND("-",E66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(E66,FIND("-",E66)-1),""))-(IFERROR(--MID(E66,FIND("-",E66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(E66,FIND("-",E66)-1),""))-(IFERROR(--MID(E66,FIND("-",E66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(E66,FIND("-",E66)-1),""))=(AW66))+2*((IFERROR(--MID(E66,FIND("-",E66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H66" s="11" t="str">
+      <c r="H66" s="11">
         <f>IF(OR($C66="",G66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G66,FIND("-",G66)-1),"")=AW66,IFERROR(--MID(G66,FIND("-",G66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(G66,FIND("-",G66)-1),""))-(IFERROR(--MID(G66,FIND("-",G66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(G66,FIND("-",G66)-1),""))-(IFERROR(--MID(G66,FIND("-",G66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(G66,FIND("-",G66)-1),""))=(AW66))+2*((IFERROR(--MID(G66,FIND("-",G66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I66" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J66" s="11" t="str">
+      <c r="J66" s="11">
         <f>IF(OR($C66="",I66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I66,FIND("-",I66)-1),"")=AW66,IFERROR(--MID(I66,FIND("-",I66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(I66,FIND("-",I66)-1),""))-(IFERROR(--MID(I66,FIND("-",I66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(I66,FIND("-",I66)-1),""))-(IFERROR(--MID(I66,FIND("-",I66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(I66,FIND("-",I66)-1),""))=(AW66))+2*((IFERROR(--MID(I66,FIND("-",I66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L66" s="11" t="str">
+      <c r="L66" s="11">
         <f>IF(OR($C66="",K66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K66,FIND("-",K66)-1),"")=AW66,IFERROR(--MID(K66,FIND("-",K66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(K66,FIND("-",K66)-1),""))-(IFERROR(--MID(K66,FIND("-",K66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(K66,FIND("-",K66)-1),""))-(IFERROR(--MID(K66,FIND("-",K66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(K66,FIND("-",K66)-1),""))=(AW66))+2*((IFERROR(--MID(K66,FIND("-",K66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N66" s="11" t="str">
+      <c r="N66" s="11">
         <f>IF(OR($C66="",M66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M66,FIND("-",M66)-1),"")=AW66,IFERROR(--MID(M66,FIND("-",M66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(M66,FIND("-",M66)-1),""))-(IFERROR(--MID(M66,FIND("-",M66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(M66,FIND("-",M66)-1),""))-(IFERROR(--MID(M66,FIND("-",M66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(M66,FIND("-",M66)-1),""))=(AW66))+2*((IFERROR(--MID(M66,FIND("-",M66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="P66" s="11" t="str">
+      <c r="P66" s="11">
         <f>IF(OR($C66="",O66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O66,FIND("-",O66)-1),"")=AW66,IFERROR(--MID(O66,FIND("-",O66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(O66,FIND("-",O66)-1),""))-(IFERROR(--MID(O66,FIND("-",O66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(O66,FIND("-",O66)-1),""))-(IFERROR(--MID(O66,FIND("-",O66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(O66,FIND("-",O66)-1),""))=(AW66))+2*((IFERROR(--MID(O66,FIND("-",O66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q66" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="R66" s="11" t="str">
+      <c r="R66" s="11">
         <f>IF(OR($C66="",Q66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q66,FIND("-",Q66)-1),"")=AW66,IFERROR(--MID(Q66,FIND("-",Q66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(Q66,FIND("-",Q66)-1),""))-(IFERROR(--MID(Q66,FIND("-",Q66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(Q66,FIND("-",Q66)-1),""))-(IFERROR(--MID(Q66,FIND("-",Q66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(Q66,FIND("-",Q66)-1),""))=(AW66))+2*((IFERROR(--MID(Q66,FIND("-",Q66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S66" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T66" s="11" t="str">
+      <c r="T66" s="11">
         <f>IF(OR($C66="",S66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S66,FIND("-",S66)-1),"")=AW66,IFERROR(--MID(S66,FIND("-",S66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(S66,FIND("-",S66)-1),""))-(IFERROR(--MID(S66,FIND("-",S66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(S66,FIND("-",S66)-1),""))-(IFERROR(--MID(S66,FIND("-",S66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(S66,FIND("-",S66)-1),""))=(AW66))+2*((IFERROR(--MID(S66,FIND("-",S66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V66" s="11" t="str">
+      <c r="V66" s="11">
         <f>IF(OR($C66="",U66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U66,FIND("-",U66)-1),"")=AW66,IFERROR(--MID(U66,FIND("-",U66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(U66,FIND("-",U66)-1),""))-(IFERROR(--MID(U66,FIND("-",U66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(U66,FIND("-",U66)-1),""))-(IFERROR(--MID(U66,FIND("-",U66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(U66,FIND("-",U66)-1),""))=(AW66))+2*((IFERROR(--MID(U66,FIND("-",U66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X66" s="11" t="str">
+      <c r="X66" s="11">
         <f>IF(OR($C66="",W66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W66,FIND("-",W66)-1),"")=AW66,IFERROR(--MID(W66,FIND("-",W66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(W66,FIND("-",W66)-1),""))-(IFERROR(--MID(W66,FIND("-",W66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(W66,FIND("-",W66)-1),""))-(IFERROR(--MID(W66,FIND("-",W66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(W66,FIND("-",W66)-1),""))=(AW66))+2*((IFERROR(--MID(W66,FIND("-",W66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y66" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="Z66" s="11" t="str">
+      <c r="Z66" s="11">
         <f>IF(OR($C66="",Y66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y66,FIND("-",Y66)-1),"")=AW66,IFERROR(--MID(Y66,FIND("-",Y66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(Y66,FIND("-",Y66)-1),""))-(IFERROR(--MID(Y66,FIND("-",Y66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(Y66,FIND("-",Y66)-1),""))-(IFERROR(--MID(Y66,FIND("-",Y66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(Y66,FIND("-",Y66)-1),""))=(AW66))+2*((IFERROR(--MID(Y66,FIND("-",Y66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB66" s="11" t="str">
+      <c r="AB66" s="11">
         <f>IF(OR($C66="",AA66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA66,FIND("-",AA66)-1),"")=AW66,IFERROR(--MID(AA66,FIND("-",AA66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AA66,FIND("-",AA66)-1),""))-(IFERROR(--MID(AA66,FIND("-",AA66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AA66,FIND("-",AA66)-1),""))-(IFERROR(--MID(AA66,FIND("-",AA66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AA66,FIND("-",AA66)-1),""))=(AW66))+2*((IFERROR(--MID(AA66,FIND("-",AA66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AD66" s="11" t="str">
+      <c r="AD66" s="11">
         <f>IF(OR($C66="",AC66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC66,FIND("-",AC66)-1),"")=AW66,IFERROR(--MID(AC66,FIND("-",AC66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AC66,FIND("-",AC66)-1),""))-(IFERROR(--MID(AC66,FIND("-",AC66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AC66,FIND("-",AC66)-1),""))-(IFERROR(--MID(AC66,FIND("-",AC66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AC66,FIND("-",AC66)-1),""))=(AW66))+2*((IFERROR(--MID(AC66,FIND("-",AC66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE66" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF66" s="11" t="str">
+      <c r="AF66" s="11">
         <f>IF(OR($C66="",AE66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE66,FIND("-",AE66)-1),"")=AW66,IFERROR(--MID(AE66,FIND("-",AE66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AE66,FIND("-",AE66)-1),""))-(IFERROR(--MID(AE66,FIND("-",AE66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AE66,FIND("-",AE66)-1),""))-(IFERROR(--MID(AE66,FIND("-",AE66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AE66,FIND("-",AE66)-1),""))=(AW66))+2*((IFERROR(--MID(AE66,FIND("-",AE66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH66" s="11" t="str">
+      <c r="AH66" s="11">
         <f>IF(OR($C66="",AG66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG66,FIND("-",AG66)-1),"")=AW66,IFERROR(--MID(AG66,FIND("-",AG66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AG66,FIND("-",AG66)-1),""))-(IFERROR(--MID(AG66,FIND("-",AG66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AG66,FIND("-",AG66)-1),""))-(IFERROR(--MID(AG66,FIND("-",AG66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AG66,FIND("-",AG66)-1),""))=(AW66))+2*((IFERROR(--MID(AG66,FIND("-",AG66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AJ66" s="11" t="str">
+      <c r="AJ66" s="11">
         <f>IF(OR($C66="",AI66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI66,FIND("-",AI66)-1),"")=AW66,IFERROR(--MID(AI66,FIND("-",AI66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AI66,FIND("-",AI66)-1),""))-(IFERROR(--MID(AI66,FIND("-",AI66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AI66,FIND("-",AI66)-1),""))-(IFERROR(--MID(AI66,FIND("-",AI66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AI66,FIND("-",AI66)-1),""))=(AW66))+2*((IFERROR(--MID(AI66,FIND("-",AI66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK66" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AL66" s="11" t="str">
+      <c r="AL66" s="11">
         <f>IF(OR($C66="",AK66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK66,FIND("-",AK66)-1),"")=AW66,IFERROR(--MID(AK66,FIND("-",AK66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AK66,FIND("-",AK66)-1),""))-(IFERROR(--MID(AK66,FIND("-",AK66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AK66,FIND("-",AK66)-1),""))-(IFERROR(--MID(AK66,FIND("-",AK66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AK66,FIND("-",AK66)-1),""))=(AW66))+2*((IFERROR(--MID(AK66,FIND("-",AK66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN66" s="11" t="str">
+      <c r="AN66" s="11">
         <f>IF(OR($C66="",AM66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM66,FIND("-",AM66)-1),"")=AW66,IFERROR(--MID(AM66,FIND("-",AM66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AM66,FIND("-",AM66)-1),""))-(IFERROR(--MID(AM66,FIND("-",AM66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AM66,FIND("-",AM66)-1),""))-(IFERROR(--MID(AM66,FIND("-",AM66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AM66,FIND("-",AM66)-1),""))=(AW66))+2*((IFERROR(--MID(AM66,FIND("-",AM66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO66" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AP66" s="11" t="str">
+      <c r="AP66" s="11">
         <f>IF(OR($C66="",AO66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO66,FIND("-",AO66)-1),"")=AW66,IFERROR(--MID(AO66,FIND("-",AO66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AO66,FIND("-",AO66)-1),""))-(IFERROR(--MID(AO66,FIND("-",AO66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AO66,FIND("-",AO66)-1),""))-(IFERROR(--MID(AO66,FIND("-",AO66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AO66,FIND("-",AO66)-1),""))=(AW66))+2*((IFERROR(--MID(AO66,FIND("-",AO66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR66" s="11" t="str">
+      <c r="AR66" s="11">
         <f>IF(OR($C66="",AQ66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ66,FIND("-",AQ66)-1),"")=AW66,IFERROR(--MID(AQ66,FIND("-",AQ66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AQ66,FIND("-",AQ66)-1),""))-(IFERROR(--MID(AQ66,FIND("-",AQ66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AQ66,FIND("-",AQ66)-1),""))-(IFERROR(--MID(AQ66,FIND("-",AQ66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AQ66,FIND("-",AQ66)-1),""))=(AW66))+2*((IFERROR(--MID(AQ66,FIND("-",AQ66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS66" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT66" s="11" t="str">
+      <c r="AT66" s="11">
         <f>IF(OR($C66="",AS66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS66,FIND("-",AS66)-1),"")=AW66,IFERROR(--MID(AS66,FIND("-",AS66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AS66,FIND("-",AS66)-1),""))-(IFERROR(--MID(AS66,FIND("-",AS66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AS66,FIND("-",AS66)-1),""))-(IFERROR(--MID(AS66,FIND("-",AS66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AS66,FIND("-",AS66)-1),""))=(AW66))+2*((IFERROR(--MID(AS66,FIND("-",AS66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU66" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV66" s="11" t="str">
+      <c r="AV66" s="11">
         <f>IF(OR($C66="",AU66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU66,FIND("-",AU66)-1),"")=AW66,IFERROR(--MID(AU66,FIND("-",AU66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AU66,FIND("-",AU66)-1),""))-(IFERROR(--MID(AU66,FIND("-",AU66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AU66,FIND("-",AU66)-1),""))-(IFERROR(--MID(AU66,FIND("-",AU66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AU66,FIND("-",AU66)-1),""))=(AW66))+2*((IFERROR(--MID(AU66,FIND("-",AU66)+1,99),""))=(AX66))),""))</f>
-        <v/>
-      </c>
-      <c r="AW66" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW66" s="11">
         <f>IF($C66="","",IFERROR(--LEFT($C66,FIND("-",$C66)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX66" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX66" s="11">
         <f>IF($C66="","",IFERROR(--MID($C66,FIND("-",$C66)+1,99),""))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10511,7 +10540,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10685,7 +10714,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
       <c r="B69" s="18"/>
       <c r="C69" s="13"/>
@@ -10743,7 +10772,7 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
@@ -10797,7 +10826,7 @@
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -10971,7 +11000,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11145,7 +11174,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11319,7 +11348,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11493,7 +11522,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
       <c r="B75" s="18"/>
       <c r="C75" s="13"/>
@@ -11551,7 +11580,7 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
@@ -11605,7 +11634,7 @@
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11779,7 +11808,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -11953,7 +11982,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12127,7 +12156,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12301,7 +12330,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12"/>
       <c r="B81" s="18"/>
       <c r="C81" s="13"/>
@@ -12359,7 +12388,7 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
@@ -12413,7 +12442,7 @@
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12587,7 +12616,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12761,7 +12790,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -12935,7 +12964,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13109,7 +13138,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13283,7 +13312,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13457,7 +13486,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12"/>
       <c r="B89" s="18"/>
       <c r="C89" s="13"/>
@@ -13515,7 +13544,7 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
@@ -13569,7 +13598,7 @@
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13743,7 +13772,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13917,7 +13946,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14091,7 +14120,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14265,7 +14294,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14439,7 +14468,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14613,7 +14642,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="12"/>
       <c r="B97" s="18"/>
       <c r="C97" s="13"/>
@@ -14671,7 +14700,7 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
@@ -14725,7 +14754,7 @@
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14899,7 +14928,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15073,7 +15102,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15247,7 +15276,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15421,7 +15450,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15595,7 +15624,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15769,7 +15798,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="12"/>
       <c r="B105" s="18"/>
       <c r="C105" s="13"/>
@@ -15827,7 +15856,7 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
@@ -15881,7 +15910,7 @@
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16055,7 +16084,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16229,7 +16258,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16403,7 +16432,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16577,7 +16606,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="12"/>
       <c r="B111" s="18"/>
       <c r="C111" s="13"/>
@@ -16635,7 +16664,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="12"/>
       <c r="B112" s="18"/>
       <c r="C112" s="13"/>
@@ -16693,7 +16722,7 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="38" t="s">
         <v>128</v>
       </c>
@@ -16747,7 +16776,7 @@
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
@@ -16801,7 +16830,7 @@
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -16931,7 +16960,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="12"/>
       <c r="B116" s="18"/>
       <c r="C116" s="13"/>
@@ -16989,7 +17018,7 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
@@ -17043,7 +17072,7 @@
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17173,7 +17202,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17303,7 +17332,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="12"/>
       <c r="B120" s="18"/>
       <c r="C120" s="13"/>
@@ -17361,7 +17390,7 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
@@ -17415,7 +17444,7 @@
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17545,7 +17574,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17675,7 +17704,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17805,7 +17834,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="12"/>
       <c r="B125" s="18"/>
       <c r="C125" s="13"/>
@@ -17863,7 +17892,7 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
@@ -17917,7 +17946,7 @@
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18047,7 +18076,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18177,7 +18206,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18307,7 +18336,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="12"/>
       <c r="B130" s="18"/>
       <c r="C130" s="13"/>
@@ -18365,7 +18394,7 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
@@ -18419,7 +18448,7 @@
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18549,7 +18578,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18679,7 +18708,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="12"/>
       <c r="B134" s="18"/>
       <c r="C134" s="13"/>
@@ -18737,7 +18766,7 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
@@ -18791,7 +18820,7 @@
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -18921,7 +18950,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19051,7 +19080,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19181,7 +19210,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="12"/>
       <c r="B139" s="18"/>
       <c r="C139" s="13"/>
@@ -19239,7 +19268,7 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
@@ -19293,7 +19322,7 @@
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19423,7 +19452,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19553,7 +19582,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="12"/>
       <c r="B143" s="18"/>
       <c r="C143" s="13"/>
@@ -19611,7 +19640,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="12"/>
       <c r="B144" s="18"/>
       <c r="C144" s="13"/>
@@ -19669,7 +19698,7 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="38" t="s">
         <v>167</v>
       </c>
@@ -19723,7 +19752,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
@@ -19777,7 +19806,7 @@
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19907,7 +19936,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20037,7 +20066,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="12"/>
       <c r="B149" s="18"/>
       <c r="C149" s="13"/>
@@ -20095,7 +20124,7 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
@@ -20149,7 +20178,7 @@
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20279,7 +20308,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="12"/>
       <c r="B152" s="18"/>
       <c r="C152" s="13"/>
@@ -20337,7 +20366,7 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
@@ -20391,7 +20420,7 @@
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20521,7 +20550,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20651,7 +20680,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="12"/>
       <c r="B156" s="18"/>
       <c r="C156" s="13"/>
@@ -20709,7 +20738,7 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
@@ -20763,7 +20792,7 @@
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20893,7 +20922,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -21023,7 +21052,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21153,7 +21182,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="12"/>
       <c r="B161" s="18"/>
       <c r="C161" s="13"/>
@@ -21211,7 +21240,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="12"/>
       <c r="B162" s="18"/>
       <c r="C162" s="13"/>
@@ -21269,7 +21298,7 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="38" t="s">
         <v>187</v>
       </c>
@@ -21323,7 +21352,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
@@ -21377,7 +21406,7 @@
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21507,7 +21536,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="12"/>
       <c r="B166" s="18"/>
       <c r="C166" s="13"/>
@@ -21565,7 +21594,7 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
@@ -21619,7 +21648,7 @@
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21749,7 +21778,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="12"/>
       <c r="B169" s="18"/>
       <c r="C169" s="13"/>
@@ -21807,7 +21836,7 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
@@ -21861,7 +21890,7 @@
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -21991,7 +22020,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="12"/>
       <c r="B172" s="18"/>
       <c r="C172" s="13"/>
@@ -22049,7 +22078,7 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
@@ -22103,7 +22132,7 @@
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22233,7 +22262,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="12"/>
       <c r="B175" s="18"/>
       <c r="C175" s="13"/>
@@ -22291,7 +22320,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="12"/>
       <c r="B176" s="18"/>
       <c r="C176" s="13"/>
@@ -22349,7 +22378,7 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="38" t="s">
         <v>200</v>
       </c>
@@ -22403,7 +22432,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
@@ -22457,7 +22486,7 @@
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22587,7 +22616,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="12"/>
       <c r="B180" s="18"/>
       <c r="C180" s="13"/>
@@ -22645,7 +22674,7 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
@@ -22699,7 +22728,7 @@
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22829,7 +22858,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="12"/>
       <c r="B183" s="18"/>
       <c r="C183" s="13"/>
@@ -22887,7 +22916,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="12"/>
       <c r="B184" s="18"/>
       <c r="C184" s="13"/>
@@ -22945,7 +22974,7 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="38" t="s">
         <v>207</v>
       </c>
@@ -22999,7 +23028,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
@@ -23053,7 +23082,7 @@
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23183,7 +23212,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="12"/>
       <c r="B188" s="18"/>
       <c r="C188" s="13"/>
@@ -23241,7 +23270,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="12"/>
       <c r="B189" s="18"/>
       <c r="C189" s="13"/>
@@ -23299,7 +23328,7 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="38" t="s">
         <v>211</v>
       </c>
@@ -23353,7 +23382,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
@@ -23407,7 +23436,7 @@
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23537,7 +23566,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="12"/>
       <c r="B193" s="18"/>
       <c r="C193" s="13"/>
@@ -23595,7 +23624,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="12"/>
       <c r="B194" s="18"/>
       <c r="C194" s="13"/>
@@ -23654,7 +23683,85 @@
       <c r="AX194" s="12"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AX194" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4" showButton="0"/>
+    <filterColumn colId="6" showButton="0"/>
+    <filterColumn colId="8" showButton="0"/>
+    <filterColumn colId="10" showButton="0"/>
+    <filterColumn colId="12" showButton="0"/>
+    <filterColumn colId="14" showButton="0"/>
+    <filterColumn colId="16" showButton="0"/>
+    <filterColumn colId="18" showButton="0"/>
+    <filterColumn colId="20" showButton="0"/>
+    <filterColumn colId="22" showButton="0"/>
+    <filterColumn colId="24" showButton="0"/>
+    <filterColumn colId="26" showButton="0"/>
+    <filterColumn colId="28" showButton="0"/>
+    <filterColumn colId="30" showButton="0"/>
+    <filterColumn colId="32" showButton="0"/>
+    <filterColumn colId="34" showButton="0"/>
+    <filterColumn colId="36" showButton="0"/>
+    <filterColumn colId="38" showButton="0"/>
+    <filterColumn colId="40" showButton="0"/>
+    <filterColumn colId="42" showButton="0"/>
+    <filterColumn colId="44" showButton="0"/>
+    <filterColumn colId="46" showButton="0"/>
+  </autoFilter>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23671,60 +23778,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23734,58 +23787,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.28515625" customWidth="1"/>
+    <col min="2" max="2" width="75.26953125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="23" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="23" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" style="23" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" style="23" customWidth="1"/>
-    <col min="25" max="25" width="10.5703125" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.5703125" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="23" customWidth="1"/>
-    <col min="29" max="29" width="10.5703125" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="23" customWidth="1"/>
-    <col min="31" max="31" width="10.5703125" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="23" customWidth="1"/>
-    <col min="33" max="33" width="10.5703125" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="23" customWidth="1"/>
-    <col min="35" max="35" width="10.5703125" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="23" customWidth="1"/>
-    <col min="37" max="37" width="10.5703125" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="23" customWidth="1"/>
-    <col min="39" max="39" width="10.5703125" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="23" customWidth="1"/>
-    <col min="41" max="41" width="10.5703125" customWidth="1"/>
-    <col min="42" max="42" width="12.5703125" customWidth="1"/>
-    <col min="43" max="43" width="10.5703125" customWidth="1"/>
-    <col min="44" max="44" width="12.5703125" style="23" customWidth="1"/>
-    <col min="45" max="45" width="10.5703125" customWidth="1"/>
-    <col min="46" max="46" width="12.5703125" style="23" customWidth="1"/>
-    <col min="47" max="47" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" customWidth="1"/>
+    <col min="12" max="12" width="12.54296875" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" customWidth="1"/>
+    <col min="14" max="14" width="12.54296875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" customWidth="1"/>
+    <col min="16" max="16" width="12.54296875" style="23" customWidth="1"/>
+    <col min="17" max="17" width="10.54296875" customWidth="1"/>
+    <col min="18" max="18" width="12.54296875" style="23" customWidth="1"/>
+    <col min="19" max="19" width="10.54296875" customWidth="1"/>
+    <col min="20" max="20" width="12.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" style="23" customWidth="1"/>
+    <col min="23" max="23" width="10.54296875" customWidth="1"/>
+    <col min="24" max="24" width="12.54296875" style="23" customWidth="1"/>
+    <col min="25" max="25" width="10.54296875" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" style="23" customWidth="1"/>
+    <col min="27" max="27" width="10.54296875" customWidth="1"/>
+    <col min="28" max="28" width="12.54296875" style="23" customWidth="1"/>
+    <col min="29" max="29" width="10.54296875" customWidth="1"/>
+    <col min="30" max="30" width="12.54296875" style="23" customWidth="1"/>
+    <col min="31" max="31" width="10.54296875" customWidth="1"/>
+    <col min="32" max="32" width="12.54296875" style="23" customWidth="1"/>
+    <col min="33" max="33" width="10.54296875" customWidth="1"/>
+    <col min="34" max="34" width="12.54296875" style="23" customWidth="1"/>
+    <col min="35" max="35" width="10.54296875" customWidth="1"/>
+    <col min="36" max="36" width="12.54296875" style="23" customWidth="1"/>
+    <col min="37" max="37" width="10.54296875" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="23" customWidth="1"/>
+    <col min="39" max="39" width="10.54296875" customWidth="1"/>
+    <col min="40" max="40" width="12.54296875" style="23" customWidth="1"/>
+    <col min="41" max="41" width="10.54296875" customWidth="1"/>
+    <col min="42" max="42" width="12.54296875" customWidth="1"/>
+    <col min="43" max="43" width="10.54296875" customWidth="1"/>
+    <col min="44" max="44" width="12.54296875" style="23" customWidth="1"/>
+    <col min="45" max="45" width="10.54296875" customWidth="1"/>
+    <col min="46" max="46" width="12.54296875" style="23" customWidth="1"/>
+    <col min="47" max="47" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23891,14 +23944,14 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="39"/>
+      <c r="AS1" s="44"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="39"/>
+      <c r="AU1" s="44"/>
     </row>
-    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
       <c r="B2" s="25" t="s">
         <v>215</v>
@@ -24039,7 +24092,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24202,7 +24255,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24365,7 +24418,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24528,7 +24581,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24691,7 +24744,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24854,7 +24907,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -25017,7 +25070,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25180,7 +25233,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25343,7 +25396,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25506,7 +25559,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25669,7 +25722,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25832,7 +25885,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -25995,7 +26048,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26158,7 +26211,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26321,7 +26374,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26440,6 +26493,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26451,17 +26515,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26473,16 +26526,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
@@ -26491,7 +26544,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>285</v>
       </c>
@@ -26508,9 +26561,9 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
-        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
@@ -26519,21 +26572,21 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
-        <v>136</v>
+        <f>C3+D3</f>
+        <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>Wedstrijden_beheer!AA1</f>
@@ -26541,87 +26594,87 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f t="shared" si="1"/>
-        <v>120</v>
+        <f>C4+D4</f>
+        <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>123</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>185</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f t="shared" si="1"/>
-        <v>123</v>
+        <f>C5+D5</f>
+        <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
+      </c>
+      <c r="C6" s="11">
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>184</v>
+      </c>
+      <c r="D6" s="11">
+        <f>Bonus_beheer!I17</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <f>C6+D6</f>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11">
+        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
-      </c>
-      <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>118</v>
-      </c>
-      <c r="D6" s="11">
-        <f>Bonus_beheer!G17</f>
+      <c r="B7" s="1" t="str">
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
+      </c>
+      <c r="C7" s="11">
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>183</v>
+      </c>
+      <c r="D7" s="11">
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
-      <c r="E6" s="11">
-        <f t="shared" si="1"/>
-        <v>118</v>
+      <c r="E7" s="11">
+        <f>C7+D7</f>
+        <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
-      </c>
-      <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>118</v>
-      </c>
-      <c r="D7" s="11">
-        <f>Bonus_beheer!AK17</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="11">
-        <f t="shared" si="1"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
         <f>Wedstrijden_beheer!U1</f>
@@ -26629,367 +26682,367 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f t="shared" si="1"/>
-        <v>114</v>
+        <f>C8+D8</f>
+        <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>119</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>177</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f t="shared" si="1"/>
-        <v>119</v>
+        <f>C9+D9</f>
+        <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
+      </c>
+      <c r="C10" s="11">
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>175</v>
+      </c>
+      <c r="D10" s="11">
+        <f>Bonus_beheer!AE17</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <f>C10+D10</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
+        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
+      </c>
+      <c r="C11" s="11">
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>175</v>
+      </c>
+      <c r="D11" s="11">
+        <f>Bonus_beheer!E17</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <f>C11+D11</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11">
+        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
+      </c>
+      <c r="C12" s="11">
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>174</v>
+      </c>
+      <c r="D12" s="11">
+        <f>Bonus_beheer!G17</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
+        <f>C12+D12</f>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
+        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="str">
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
+      </c>
+      <c r="C13" s="11">
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>168</v>
+      </c>
+      <c r="D13" s="11">
+        <f>Bonus_beheer!W17</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="11">
+        <f>C13+D13</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
+        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
+      </c>
+      <c r="C14" s="11">
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>167</v>
+      </c>
+      <c r="D14" s="11">
+        <f>Bonus_beheer!AK17</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="11">
+        <f>C14+D14</f>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
+        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="str">
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
+      </c>
+      <c r="C15" s="11">
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>165</v>
+      </c>
+      <c r="D15" s="11">
+        <f>Bonus_beheer!AM17</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="11">
+        <f>C15+D15</f>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
+        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="str">
+      <c r="B16" s="1" t="str">
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
+      </c>
+      <c r="C16" s="11">
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>161</v>
+      </c>
+      <c r="D16" s="11">
+        <f>Bonus_beheer!AU17</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="11">
+        <f>C16+D16</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
+        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
+      </c>
+      <c r="C17" s="11">
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>161</v>
+      </c>
+      <c r="D17" s="11">
+        <f>Bonus_beheer!AU18</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="11">
+        <f>C17+D17</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11">
+        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!M1</f>
         <v>Bas</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>107</v>
-      </c>
-      <c r="D10" s="11">
+        <v>159</v>
+      </c>
+      <c r="D18" s="11">
         <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
-      <c r="E10" s="11">
-        <f t="shared" si="1"/>
-        <v>107</v>
+      <c r="E18" s="11">
+        <f>C18+D18</f>
+        <v>159</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
-      </c>
-      <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>114</v>
-      </c>
-      <c r="D11" s="11">
-        <f>Bonus_beheer!Y17</f>
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11">
+        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
+      </c>
+      <c r="C19" s="11">
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>153</v>
+      </c>
+      <c r="D19" s="11">
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
-      <c r="E11" s="11">
-        <f t="shared" si="1"/>
-        <v>114</v>
+      <c r="E19" s="11">
+        <f>C19+D19</f>
+        <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
-      </c>
-      <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>110</v>
-      </c>
-      <c r="D12" s="11">
-        <f>Bonus_beheer!AU17</f>
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11">
+        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
+      </c>
+      <c r="C20" s="11">
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
+        <v>142</v>
+      </c>
+      <c r="D20" s="11">
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
-      <c r="E12" s="11">
-        <f t="shared" si="1"/>
-        <v>110</v>
+      <c r="E20" s="11">
+        <f>C20+D20</f>
+        <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
-      </c>
-      <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>110</v>
-      </c>
-      <c r="D13" s="11">
-        <f>Bonus_beheer!AU18</f>
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="11">
+        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
+      </c>
+      <c r="C21" s="11">
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>137</v>
+      </c>
+      <c r="D21" s="11">
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
-      <c r="E13" s="11">
-        <f t="shared" si="1"/>
-        <v>110</v>
+      <c r="E21" s="11">
+        <f>C21+D21</f>
+        <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
-      </c>
-      <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>114</v>
-      </c>
-      <c r="D14" s="11">
-        <f>Bonus_beheer!AG17</f>
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11">
+        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="str">
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
+      </c>
+      <c r="C22" s="11">
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>136</v>
+      </c>
+      <c r="D22" s="11">
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
-      <c r="E14" s="11">
-        <f t="shared" si="1"/>
-        <v>114</v>
+      <c r="E22" s="11">
+        <f>C22+D22</f>
+        <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
-      </c>
-      <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>110</v>
-      </c>
-      <c r="D15" s="11">
-        <f>Bonus_beheer!E17</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="11">
-        <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B16" s="1" t="str">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="11">
+        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
         <v>Simone</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>93</v>
-      </c>
-      <c r="D16" s="11">
+        <v>128</v>
+      </c>
+      <c r="D23" s="11">
         <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
-      <c r="E16" s="11">
-        <f t="shared" si="1"/>
-        <v>93</v>
+      <c r="E23" s="11">
+        <f>C23+D23</f>
+        <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="str">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="11">
+        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>93</v>
-      </c>
-      <c r="D17" s="11">
+        <v>128</v>
+      </c>
+      <c r="D24" s="11">
         <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
-      <c r="E17" s="11">
-        <f t="shared" si="1"/>
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
-      </c>
-      <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>102</v>
-      </c>
-      <c r="D18" s="11">
-        <f>Bonus_beheer!S17</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="11">
-        <f t="shared" si="1"/>
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
-      </c>
-      <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>111</v>
-      </c>
-      <c r="D19" s="11">
-        <f>Bonus_beheer!AO17</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="11">
-        <f t="shared" si="1"/>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B20" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
-      </c>
-      <c r="C20" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>97</v>
-      </c>
-      <c r="D20" s="11">
-        <f>Bonus_beheer!W17</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="11">
-        <f t="shared" si="1"/>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
-      </c>
-      <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>97</v>
-      </c>
-      <c r="D21" s="11">
-        <f>Bonus_beheer!AI17</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="11">
-        <f t="shared" si="1"/>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
-      </c>
-      <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>99</v>
-      </c>
-      <c r="D22" s="11">
-        <f>Bonus_beheer!AC17</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="11">
-        <f t="shared" si="1"/>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
-      </c>
-      <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>91</v>
-      </c>
-      <c r="D23" s="11">
-        <f>Bonus_beheer!AM17</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="11">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
-      </c>
-      <c r="C24" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>89</v>
-      </c>
-      <c r="D24" s="11">
-        <f>Bonus_beheer!K17</f>
-        <v>0</v>
-      </c>
       <c r="E24" s="11">
-        <f t="shared" si="1"/>
-        <v>89</v>
+        <f>C24+D24</f>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -27005,20 +27058,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.7109375" hidden="1"/>
+    <col min="3" max="16384" width="8.7265625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27026,7 +27079,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27034,7 +27087,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27042,7 +27095,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27050,7 +27103,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27058,7 +27111,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27066,7 +27119,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27074,7 +27127,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27090,16 +27143,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="55.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="30.7265625" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.7109375" hidden="1"/>
+    <col min="45" max="16384" width="8.7265625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>306</v>
       </c>
@@ -27147,7 +27200,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27158,7 +27211,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27169,7 +27222,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27180,7 +27233,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27191,7 +27244,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27202,7 +27255,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27213,7 +27266,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27230,14 +27283,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="26" t="s">
         <v>319</v>
       </c>
@@ -27248,7 +27301,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27256,107 +27309,107 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
         <v>324</v>
       </c>
@@ -27367,6 +27420,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27561,27 +27634,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27598,29 +27676,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1519" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1DC7F51-233E-4AB8-A0B0-E61B70A7C02D}"/>
+  <xr:revisionPtr revIDLastSave="1525" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3EBA5CC-668D-49F9-89ED-3789A591FD9F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1391,10 +1391,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -10373,171 +10369,173 @@
       <c r="B67" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="D67" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F67" s="11" t="str">
+      <c r="F67" s="11">
         <f>IF(OR($C67="",E67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E67,FIND("-",E67)-1),"")=AW67,IFERROR(--MID(E67,FIND("-",E67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(E67,FIND("-",E67)-1),""))-(IFERROR(--MID(E67,FIND("-",E67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(E67,FIND("-",E67)-1),""))-(IFERROR(--MID(E67,FIND("-",E67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(E67,FIND("-",E67)-1),""))=(AW67))+2*((IFERROR(--MID(E67,FIND("-",E67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H67" s="11" t="str">
+      <c r="H67" s="11">
         <f>IF(OR($C67="",G67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G67,FIND("-",G67)-1),"")=AW67,IFERROR(--MID(G67,FIND("-",G67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(G67,FIND("-",G67)-1),""))-(IFERROR(--MID(G67,FIND("-",G67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(G67,FIND("-",G67)-1),""))-(IFERROR(--MID(G67,FIND("-",G67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(G67,FIND("-",G67)-1),""))=(AW67))+2*((IFERROR(--MID(G67,FIND("-",G67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J67" s="11" t="str">
+      <c r="J67" s="11">
         <f>IF(OR($C67="",I67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I67,FIND("-",I67)-1),"")=AW67,IFERROR(--MID(I67,FIND("-",I67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(I67,FIND("-",I67)-1),""))-(IFERROR(--MID(I67,FIND("-",I67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(I67,FIND("-",I67)-1),""))-(IFERROR(--MID(I67,FIND("-",I67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(I67,FIND("-",I67)-1),""))=(AW67))+2*((IFERROR(--MID(I67,FIND("-",I67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K67" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L67" s="11" t="str">
+      <c r="L67" s="11">
         <f>IF(OR($C67="",K67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K67,FIND("-",K67)-1),"")=AW67,IFERROR(--MID(K67,FIND("-",K67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(K67,FIND("-",K67)-1),""))-(IFERROR(--MID(K67,FIND("-",K67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(K67,FIND("-",K67)-1),""))-(IFERROR(--MID(K67,FIND("-",K67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(K67,FIND("-",K67)-1),""))=(AW67))+2*((IFERROR(--MID(K67,FIND("-",K67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M67" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N67" s="11" t="str">
+      <c r="N67" s="11">
         <f>IF(OR($C67="",M67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M67,FIND("-",M67)-1),"")=AW67,IFERROR(--MID(M67,FIND("-",M67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(M67,FIND("-",M67)-1),""))-(IFERROR(--MID(M67,FIND("-",M67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(M67,FIND("-",M67)-1),""))-(IFERROR(--MID(M67,FIND("-",M67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(M67,FIND("-",M67)-1),""))=(AW67))+2*((IFERROR(--MID(M67,FIND("-",M67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P67" s="11" t="str">
+      <c r="P67" s="11">
         <f>IF(OR($C67="",O67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O67,FIND("-",O67)-1),"")=AW67,IFERROR(--MID(O67,FIND("-",O67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(O67,FIND("-",O67)-1),""))-(IFERROR(--MID(O67,FIND("-",O67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(O67,FIND("-",O67)-1),""))-(IFERROR(--MID(O67,FIND("-",O67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(O67,FIND("-",O67)-1),""))=(AW67))+2*((IFERROR(--MID(O67,FIND("-",O67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q67" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="R67" s="11" t="str">
+      <c r="R67" s="11">
         <f>IF(OR($C67="",Q67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q67,FIND("-",Q67)-1),"")=AW67,IFERROR(--MID(Q67,FIND("-",Q67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(Q67,FIND("-",Q67)-1),""))-(IFERROR(--MID(Q67,FIND("-",Q67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(Q67,FIND("-",Q67)-1),""))-(IFERROR(--MID(Q67,FIND("-",Q67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(Q67,FIND("-",Q67)-1),""))=(AW67))+2*((IFERROR(--MID(Q67,FIND("-",Q67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S67" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T67" s="11" t="str">
+      <c r="T67" s="11">
         <f>IF(OR($C67="",S67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S67,FIND("-",S67)-1),"")=AW67,IFERROR(--MID(S67,FIND("-",S67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(S67,FIND("-",S67)-1),""))-(IFERROR(--MID(S67,FIND("-",S67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(S67,FIND("-",S67)-1),""))-(IFERROR(--MID(S67,FIND("-",S67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(S67,FIND("-",S67)-1),""))=(AW67))+2*((IFERROR(--MID(S67,FIND("-",S67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U67" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="V67" s="11" t="str">
+      <c r="V67" s="11">
         <f>IF(OR($C67="",U67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U67,FIND("-",U67)-1),"")=AW67,IFERROR(--MID(U67,FIND("-",U67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(U67,FIND("-",U67)-1),""))-(IFERROR(--MID(U67,FIND("-",U67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(U67,FIND("-",U67)-1),""))-(IFERROR(--MID(U67,FIND("-",U67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(U67,FIND("-",U67)-1),""))=(AW67))+2*((IFERROR(--MID(U67,FIND("-",U67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W67" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X67" s="11" t="str">
+      <c r="X67" s="11">
         <f>IF(OR($C67="",W67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W67,FIND("-",W67)-1),"")=AW67,IFERROR(--MID(W67,FIND("-",W67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(W67,FIND("-",W67)-1),""))-(IFERROR(--MID(W67,FIND("-",W67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(W67,FIND("-",W67)-1),""))-(IFERROR(--MID(W67,FIND("-",W67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(W67,FIND("-",W67)-1),""))=(AW67))+2*((IFERROR(--MID(W67,FIND("-",W67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y67" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z67" s="11" t="str">
+      <c r="Z67" s="11">
         <f>IF(OR($C67="",Y67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y67,FIND("-",Y67)-1),"")=AW67,IFERROR(--MID(Y67,FIND("-",Y67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(Y67,FIND("-",Y67)-1),""))-(IFERROR(--MID(Y67,FIND("-",Y67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(Y67,FIND("-",Y67)-1),""))-(IFERROR(--MID(Y67,FIND("-",Y67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(Y67,FIND("-",Y67)-1),""))=(AW67))+2*((IFERROR(--MID(Y67,FIND("-",Y67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AB67" s="11" t="str">
+      <c r="AB67" s="11">
         <f>IF(OR($C67="",AA67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA67,FIND("-",AA67)-1),"")=AW67,IFERROR(--MID(AA67,FIND("-",AA67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AA67,FIND("-",AA67)-1),""))-(IFERROR(--MID(AA67,FIND("-",AA67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AA67,FIND("-",AA67)-1),""))-(IFERROR(--MID(AA67,FIND("-",AA67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AA67,FIND("-",AA67)-1),""))=(AW67))+2*((IFERROR(--MID(AA67,FIND("-",AA67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC67" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD67" s="11" t="str">
+      <c r="AD67" s="11">
         <f>IF(OR($C67="",AC67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC67,FIND("-",AC67)-1),"")=AW67,IFERROR(--MID(AC67,FIND("-",AC67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AC67,FIND("-",AC67)-1),""))-(IFERROR(--MID(AC67,FIND("-",AC67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AC67,FIND("-",AC67)-1),""))-(IFERROR(--MID(AC67,FIND("-",AC67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AC67,FIND("-",AC67)-1),""))=(AW67))+2*((IFERROR(--MID(AC67,FIND("-",AC67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF67" s="11" t="str">
+      <c r="AF67" s="11">
         <f>IF(OR($C67="",AE67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE67,FIND("-",AE67)-1),"")=AW67,IFERROR(--MID(AE67,FIND("-",AE67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AE67,FIND("-",AE67)-1),""))-(IFERROR(--MID(AE67,FIND("-",AE67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AE67,FIND("-",AE67)-1),""))-(IFERROR(--MID(AE67,FIND("-",AE67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AE67,FIND("-",AE67)-1),""))=(AW67))+2*((IFERROR(--MID(AE67,FIND("-",AE67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG67" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH67" s="11" t="str">
+      <c r="AH67" s="11">
         <f>IF(OR($C67="",AG67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG67,FIND("-",AG67)-1),"")=AW67,IFERROR(--MID(AG67,FIND("-",AG67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AG67,FIND("-",AG67)-1),""))-(IFERROR(--MID(AG67,FIND("-",AG67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AG67,FIND("-",AG67)-1),""))-(IFERROR(--MID(AG67,FIND("-",AG67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AG67,FIND("-",AG67)-1),""))=(AW67))+2*((IFERROR(--MID(AG67,FIND("-",AG67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI67" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ67" s="11" t="str">
+      <c r="AJ67" s="11">
         <f>IF(OR($C67="",AI67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI67,FIND("-",AI67)-1),"")=AW67,IFERROR(--MID(AI67,FIND("-",AI67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AI67,FIND("-",AI67)-1),""))-(IFERROR(--MID(AI67,FIND("-",AI67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AI67,FIND("-",AI67)-1),""))-(IFERROR(--MID(AI67,FIND("-",AI67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AI67,FIND("-",AI67)-1),""))=(AW67))+2*((IFERROR(--MID(AI67,FIND("-",AI67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL67" s="11" t="str">
+      <c r="AL67" s="11">
         <f>IF(OR($C67="",AK67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK67,FIND("-",AK67)-1),"")=AW67,IFERROR(--MID(AK67,FIND("-",AK67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AK67,FIND("-",AK67)-1),""))-(IFERROR(--MID(AK67,FIND("-",AK67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AK67,FIND("-",AK67)-1),""))-(IFERROR(--MID(AK67,FIND("-",AK67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AK67,FIND("-",AK67)-1),""))=(AW67))+2*((IFERROR(--MID(AK67,FIND("-",AK67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN67" s="11" t="str">
+      <c r="AN67" s="11">
         <f>IF(OR($C67="",AM67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM67,FIND("-",AM67)-1),"")=AW67,IFERROR(--MID(AM67,FIND("-",AM67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AM67,FIND("-",AM67)-1),""))-(IFERROR(--MID(AM67,FIND("-",AM67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AM67,FIND("-",AM67)-1),""))-(IFERROR(--MID(AM67,FIND("-",AM67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AM67,FIND("-",AM67)-1),""))=(AW67))+2*((IFERROR(--MID(AM67,FIND("-",AM67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO67" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AP67" s="11" t="str">
+      <c r="AP67" s="11">
         <f>IF(OR($C67="",AO67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO67,FIND("-",AO67)-1),"")=AW67,IFERROR(--MID(AO67,FIND("-",AO67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AO67,FIND("-",AO67)-1),""))-(IFERROR(--MID(AO67,FIND("-",AO67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AO67,FIND("-",AO67)-1),""))-(IFERROR(--MID(AO67,FIND("-",AO67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AO67,FIND("-",AO67)-1),""))=(AW67))+2*((IFERROR(--MID(AO67,FIND("-",AO67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ67" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR67" s="11" t="str">
+      <c r="AR67" s="11">
         <f>IF(OR($C67="",AQ67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ67,FIND("-",AQ67)-1),"")=AW67,IFERROR(--MID(AQ67,FIND("-",AQ67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AQ67,FIND("-",AQ67)-1),""))-(IFERROR(--MID(AQ67,FIND("-",AQ67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AQ67,FIND("-",AQ67)-1),""))-(IFERROR(--MID(AQ67,FIND("-",AQ67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AQ67,FIND("-",AQ67)-1),""))=(AW67))+2*((IFERROR(--MID(AQ67,FIND("-",AQ67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS67" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT67" s="11" t="str">
+      <c r="AT67" s="11">
         <f>IF(OR($C67="",AS67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS67,FIND("-",AS67)-1),"")=AW67,IFERROR(--MID(AS67,FIND("-",AS67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AS67,FIND("-",AS67)-1),""))-(IFERROR(--MID(AS67,FIND("-",AS67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AS67,FIND("-",AS67)-1),""))-(IFERROR(--MID(AS67,FIND("-",AS67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AS67,FIND("-",AS67)-1),""))=(AW67))+2*((IFERROR(--MID(AS67,FIND("-",AS67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU67" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AV67" s="11" t="str">
+      <c r="AV67" s="11">
         <f>IF(OR($C67="",AU67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU67,FIND("-",AU67)-1),"")=AW67,IFERROR(--MID(AU67,FIND("-",AU67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AU67,FIND("-",AU67)-1),""))-(IFERROR(--MID(AU67,FIND("-",AU67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AU67,FIND("-",AU67)-1),""))-(IFERROR(--MID(AU67,FIND("-",AU67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AU67,FIND("-",AU67)-1),""))=(AW67))+2*((IFERROR(--MID(AU67,FIND("-",AU67)+1,99),""))=(AX67))),""))</f>
-        <v/>
-      </c>
-      <c r="AW67" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW67" s="11">
         <f>IF($C67="","",IFERROR(--LEFT($C67,FIND("-",$C67)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX67" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX67" s="11">
         <f>IF($C67="","",IFERROR(--MID($C67,FIND("-",$C67)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -10547,171 +10545,173 @@
       <c r="B68" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C68" s="10"/>
+      <c r="C68" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="D68" s="1" t="s">
         <v>93</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F68" s="11" t="str">
+      <c r="F68" s="11">
         <f>IF(OR($C68="",E68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E68,FIND("-",E68)-1),"")=AW68,IFERROR(--MID(E68,FIND("-",E68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(E68,FIND("-",E68)-1),""))-(IFERROR(--MID(E68,FIND("-",E68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(E68,FIND("-",E68)-1),""))-(IFERROR(--MID(E68,FIND("-",E68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(E68,FIND("-",E68)-1),""))=(AW68))+2*((IFERROR(--MID(E68,FIND("-",E68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H68" s="11" t="str">
+      <c r="H68" s="11">
         <f>IF(OR($C68="",G68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G68,FIND("-",G68)-1),"")=AW68,IFERROR(--MID(G68,FIND("-",G68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(G68,FIND("-",G68)-1),""))-(IFERROR(--MID(G68,FIND("-",G68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(G68,FIND("-",G68)-1),""))-(IFERROR(--MID(G68,FIND("-",G68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(G68,FIND("-",G68)-1),""))=(AW68))+2*((IFERROR(--MID(G68,FIND("-",G68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J68" s="11" t="str">
+      <c r="J68" s="11">
         <f>IF(OR($C68="",I68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I68,FIND("-",I68)-1),"")=AW68,IFERROR(--MID(I68,FIND("-",I68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(I68,FIND("-",I68)-1),""))-(IFERROR(--MID(I68,FIND("-",I68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(I68,FIND("-",I68)-1),""))-(IFERROR(--MID(I68,FIND("-",I68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(I68,FIND("-",I68)-1),""))=(AW68))+2*((IFERROR(--MID(I68,FIND("-",I68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K68" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="L68" s="11" t="str">
+      <c r="L68" s="11">
         <f>IF(OR($C68="",K68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K68,FIND("-",K68)-1),"")=AW68,IFERROR(--MID(K68,FIND("-",K68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(K68,FIND("-",K68)-1),""))-(IFERROR(--MID(K68,FIND("-",K68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(K68,FIND("-",K68)-1),""))-(IFERROR(--MID(K68,FIND("-",K68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(K68,FIND("-",K68)-1),""))=(AW68))+2*((IFERROR(--MID(K68,FIND("-",K68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N68" s="11" t="str">
+      <c r="N68" s="11">
         <f>IF(OR($C68="",M68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M68,FIND("-",M68)-1),"")=AW68,IFERROR(--MID(M68,FIND("-",M68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(M68,FIND("-",M68)-1),""))-(IFERROR(--MID(M68,FIND("-",M68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(M68,FIND("-",M68)-1),""))-(IFERROR(--MID(M68,FIND("-",M68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(M68,FIND("-",M68)-1),""))=(AW68))+2*((IFERROR(--MID(M68,FIND("-",M68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="P68" s="11" t="str">
+      <c r="P68" s="11">
         <f>IF(OR($C68="",O68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O68,FIND("-",O68)-1),"")=AW68,IFERROR(--MID(O68,FIND("-",O68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(O68,FIND("-",O68)-1),""))-(IFERROR(--MID(O68,FIND("-",O68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(O68,FIND("-",O68)-1),""))-(IFERROR(--MID(O68,FIND("-",O68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(O68,FIND("-",O68)-1),""))=(AW68))+2*((IFERROR(--MID(O68,FIND("-",O68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q68" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="R68" s="11" t="str">
+      <c r="R68" s="11">
         <f>IF(OR($C68="",Q68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q68,FIND("-",Q68)-1),"")=AW68,IFERROR(--MID(Q68,FIND("-",Q68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(Q68,FIND("-",Q68)-1),""))-(IFERROR(--MID(Q68,FIND("-",Q68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(Q68,FIND("-",Q68)-1),""))-(IFERROR(--MID(Q68,FIND("-",Q68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(Q68,FIND("-",Q68)-1),""))=(AW68))+2*((IFERROR(--MID(Q68,FIND("-",Q68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T68" s="11" t="str">
+      <c r="T68" s="11">
         <f>IF(OR($C68="",S68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S68,FIND("-",S68)-1),"")=AW68,IFERROR(--MID(S68,FIND("-",S68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(S68,FIND("-",S68)-1),""))-(IFERROR(--MID(S68,FIND("-",S68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(S68,FIND("-",S68)-1),""))-(IFERROR(--MID(S68,FIND("-",S68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(S68,FIND("-",S68)-1),""))=(AW68))+2*((IFERROR(--MID(S68,FIND("-",S68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V68" s="11" t="str">
+      <c r="V68" s="11">
         <f>IF(OR($C68="",U68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U68,FIND("-",U68)-1),"")=AW68,IFERROR(--MID(U68,FIND("-",U68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(U68,FIND("-",U68)-1),""))-(IFERROR(--MID(U68,FIND("-",U68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(U68,FIND("-",U68)-1),""))-(IFERROR(--MID(U68,FIND("-",U68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(U68,FIND("-",U68)-1),""))=(AW68))+2*((IFERROR(--MID(U68,FIND("-",U68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X68" s="11" t="str">
+      <c r="X68" s="11">
         <f>IF(OR($C68="",W68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W68,FIND("-",W68)-1),"")=AW68,IFERROR(--MID(W68,FIND("-",W68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(W68,FIND("-",W68)-1),""))-(IFERROR(--MID(W68,FIND("-",W68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(W68,FIND("-",W68)-1),""))-(IFERROR(--MID(W68,FIND("-",W68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(W68,FIND("-",W68)-1),""))=(AW68))+2*((IFERROR(--MID(W68,FIND("-",W68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="Z68" s="11" t="str">
+      <c r="Z68" s="11">
         <f>IF(OR($C68="",Y68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y68,FIND("-",Y68)-1),"")=AW68,IFERROR(--MID(Y68,FIND("-",Y68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(Y68,FIND("-",Y68)-1),""))-(IFERROR(--MID(Y68,FIND("-",Y68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(Y68,FIND("-",Y68)-1),""))-(IFERROR(--MID(Y68,FIND("-",Y68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(Y68,FIND("-",Y68)-1),""))=(AW68))+2*((IFERROR(--MID(Y68,FIND("-",Y68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB68" s="11" t="str">
+      <c r="AB68" s="11">
         <f>IF(OR($C68="",AA68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA68,FIND("-",AA68)-1),"")=AW68,IFERROR(--MID(AA68,FIND("-",AA68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AA68,FIND("-",AA68)-1),""))-(IFERROR(--MID(AA68,FIND("-",AA68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AA68,FIND("-",AA68)-1),""))-(IFERROR(--MID(AA68,FIND("-",AA68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AA68,FIND("-",AA68)-1),""))=(AW68))+2*((IFERROR(--MID(AA68,FIND("-",AA68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD68" s="11" t="str">
+      <c r="AD68" s="11">
         <f>IF(OR($C68="",AC68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC68,FIND("-",AC68)-1),"")=AW68,IFERROR(--MID(AC68,FIND("-",AC68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AC68,FIND("-",AC68)-1),""))-(IFERROR(--MID(AC68,FIND("-",AC68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AC68,FIND("-",AC68)-1),""))-(IFERROR(--MID(AC68,FIND("-",AC68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AC68,FIND("-",AC68)-1),""))=(AW68))+2*((IFERROR(--MID(AC68,FIND("-",AC68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AE68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF68" s="11" t="str">
+      <c r="AF68" s="11">
         <f>IF(OR($C68="",AE68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE68,FIND("-",AE68)-1),"")=AW68,IFERROR(--MID(AE68,FIND("-",AE68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AE68,FIND("-",AE68)-1),""))-(IFERROR(--MID(AE68,FIND("-",AE68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AE68,FIND("-",AE68)-1),""))-(IFERROR(--MID(AE68,FIND("-",AE68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AE68,FIND("-",AE68)-1),""))=(AW68))+2*((IFERROR(--MID(AE68,FIND("-",AE68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH68" s="11" t="str">
+      <c r="AH68" s="11">
         <f>IF(OR($C68="",AG68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG68,FIND("-",AG68)-1),"")=AW68,IFERROR(--MID(AG68,FIND("-",AG68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AG68,FIND("-",AG68)-1),""))-(IFERROR(--MID(AG68,FIND("-",AG68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AG68,FIND("-",AG68)-1),""))-(IFERROR(--MID(AG68,FIND("-",AG68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AG68,FIND("-",AG68)-1),""))=(AW68))+2*((IFERROR(--MID(AG68,FIND("-",AG68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ68" s="11" t="str">
+      <c r="AJ68" s="11">
         <f>IF(OR($C68="",AI68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI68,FIND("-",AI68)-1),"")=AW68,IFERROR(--MID(AI68,FIND("-",AI68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AI68,FIND("-",AI68)-1),""))-(IFERROR(--MID(AI68,FIND("-",AI68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AI68,FIND("-",AI68)-1),""))-(IFERROR(--MID(AI68,FIND("-",AI68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AI68,FIND("-",AI68)-1),""))=(AW68))+2*((IFERROR(--MID(AI68,FIND("-",AI68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL68" s="11" t="str">
+      <c r="AL68" s="11">
         <f>IF(OR($C68="",AK68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK68,FIND("-",AK68)-1),"")=AW68,IFERROR(--MID(AK68,FIND("-",AK68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AK68,FIND("-",AK68)-1),""))-(IFERROR(--MID(AK68,FIND("-",AK68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AK68,FIND("-",AK68)-1),""))-(IFERROR(--MID(AK68,FIND("-",AK68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AK68,FIND("-",AK68)-1),""))=(AW68))+2*((IFERROR(--MID(AK68,FIND("-",AK68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN68" s="11" t="str">
+      <c r="AN68" s="11">
         <f>IF(OR($C68="",AM68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM68,FIND("-",AM68)-1),"")=AW68,IFERROR(--MID(AM68,FIND("-",AM68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AM68,FIND("-",AM68)-1),""))-(IFERROR(--MID(AM68,FIND("-",AM68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AM68,FIND("-",AM68)-1),""))-(IFERROR(--MID(AM68,FIND("-",AM68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AM68,FIND("-",AM68)-1),""))=(AW68))+2*((IFERROR(--MID(AM68,FIND("-",AM68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP68" s="11" t="str">
+      <c r="AP68" s="11">
         <f>IF(OR($C68="",AO68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO68,FIND("-",AO68)-1),"")=AW68,IFERROR(--MID(AO68,FIND("-",AO68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AO68,FIND("-",AO68)-1),""))-(IFERROR(--MID(AO68,FIND("-",AO68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AO68,FIND("-",AO68)-1),""))-(IFERROR(--MID(AO68,FIND("-",AO68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AO68,FIND("-",AO68)-1),""))=(AW68))+2*((IFERROR(--MID(AO68,FIND("-",AO68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ68" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AR68" s="11" t="str">
+      <c r="AR68" s="11">
         <f>IF(OR($C68="",AQ68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ68,FIND("-",AQ68)-1),"")=AW68,IFERROR(--MID(AQ68,FIND("-",AQ68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AQ68,FIND("-",AQ68)-1),""))-(IFERROR(--MID(AQ68,FIND("-",AQ68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AQ68,FIND("-",AQ68)-1),""))-(IFERROR(--MID(AQ68,FIND("-",AQ68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AQ68,FIND("-",AQ68)-1),""))=(AW68))+2*((IFERROR(--MID(AQ68,FIND("-",AQ68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AT68" s="11" t="str">
+      <c r="AT68" s="11">
         <f>IF(OR($C68="",AS68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS68,FIND("-",AS68)-1),"")=AW68,IFERROR(--MID(AS68,FIND("-",AS68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AS68,FIND("-",AS68)-1),""))-(IFERROR(--MID(AS68,FIND("-",AS68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AS68,FIND("-",AS68)-1),""))-(IFERROR(--MID(AS68,FIND("-",AS68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AS68,FIND("-",AS68)-1),""))=(AW68))+2*((IFERROR(--MID(AS68,FIND("-",AS68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AU68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AV68" s="11" t="str">
+      <c r="AV68" s="11">
         <f>IF(OR($C68="",AU68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU68,FIND("-",AU68)-1),"")=AW68,IFERROR(--MID(AU68,FIND("-",AU68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AU68,FIND("-",AU68)-1),""))-(IFERROR(--MID(AU68,FIND("-",AU68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AU68,FIND("-",AU68)-1),""))-(IFERROR(--MID(AU68,FIND("-",AU68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AU68,FIND("-",AU68)-1),""))=(AW68))+2*((IFERROR(--MID(AU68,FIND("-",AU68)+1,99),""))=(AX68))),""))</f>
-        <v/>
-      </c>
-      <c r="AW68" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW68" s="11">
         <f>IF($C68="","",IFERROR(--LEFT($C68,FIND("-",$C68)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX68" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX68" s="11">
         <f>IF($C68="","",IFERROR(--MID($C68,FIND("-",$C68)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -10833,171 +10833,173 @@
       <c r="B71" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="D71" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F71" s="11" t="str">
+      <c r="F71" s="11">
         <f>IF(OR($C71="",E71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E71,FIND("-",E71)-1),"")=AW71,IFERROR(--MID(E71,FIND("-",E71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(E71,FIND("-",E71)-1),""))-(IFERROR(--MID(E71,FIND("-",E71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(E71,FIND("-",E71)-1),""))-(IFERROR(--MID(E71,FIND("-",E71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(E71,FIND("-",E71)-1),""))=(AW71))+2*((IFERROR(--MID(E71,FIND("-",E71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H71" s="11" t="str">
+      <c r="H71" s="11">
         <f>IF(OR($C71="",G71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G71,FIND("-",G71)-1),"")=AW71,IFERROR(--MID(G71,FIND("-",G71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(G71,FIND("-",G71)-1),""))-(IFERROR(--MID(G71,FIND("-",G71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(G71,FIND("-",G71)-1),""))-(IFERROR(--MID(G71,FIND("-",G71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(G71,FIND("-",G71)-1),""))=(AW71))+2*((IFERROR(--MID(G71,FIND("-",G71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J71" s="11" t="str">
+      <c r="J71" s="11">
         <f>IF(OR($C71="",I71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I71,FIND("-",I71)-1),"")=AW71,IFERROR(--MID(I71,FIND("-",I71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(I71,FIND("-",I71)-1),""))-(IFERROR(--MID(I71,FIND("-",I71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(I71,FIND("-",I71)-1),""))-(IFERROR(--MID(I71,FIND("-",I71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(I71,FIND("-",I71)-1),""))=(AW71))+2*((IFERROR(--MID(I71,FIND("-",I71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K71" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L71" s="11" t="str">
+      <c r="L71" s="11">
         <f>IF(OR($C71="",K71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K71,FIND("-",K71)-1),"")=AW71,IFERROR(--MID(K71,FIND("-",K71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(K71,FIND("-",K71)-1),""))-(IFERROR(--MID(K71,FIND("-",K71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(K71,FIND("-",K71)-1),""))-(IFERROR(--MID(K71,FIND("-",K71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(K71,FIND("-",K71)-1),""))=(AW71))+2*((IFERROR(--MID(K71,FIND("-",K71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M71" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N71" s="11" t="str">
+      <c r="N71" s="11">
         <f>IF(OR($C71="",M71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M71,FIND("-",M71)-1),"")=AW71,IFERROR(--MID(M71,FIND("-",M71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(M71,FIND("-",M71)-1),""))-(IFERROR(--MID(M71,FIND("-",M71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(M71,FIND("-",M71)-1),""))-(IFERROR(--MID(M71,FIND("-",M71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(M71,FIND("-",M71)-1),""))=(AW71))+2*((IFERROR(--MID(M71,FIND("-",M71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P71" s="11" t="str">
+      <c r="P71" s="11">
         <f>IF(OR($C71="",O71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O71,FIND("-",O71)-1),"")=AW71,IFERROR(--MID(O71,FIND("-",O71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(O71,FIND("-",O71)-1),""))-(IFERROR(--MID(O71,FIND("-",O71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(O71,FIND("-",O71)-1),""))-(IFERROR(--MID(O71,FIND("-",O71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(O71,FIND("-",O71)-1),""))=(AW71))+2*((IFERROR(--MID(O71,FIND("-",O71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q71" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R71" s="11" t="str">
+      <c r="R71" s="11">
         <f>IF(OR($C71="",Q71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q71,FIND("-",Q71)-1),"")=AW71,IFERROR(--MID(Q71,FIND("-",Q71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(Q71,FIND("-",Q71)-1),""))-(IFERROR(--MID(Q71,FIND("-",Q71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(Q71,FIND("-",Q71)-1),""))-(IFERROR(--MID(Q71,FIND("-",Q71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(Q71,FIND("-",Q71)-1),""))=(AW71))+2*((IFERROR(--MID(Q71,FIND("-",Q71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S71" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T71" s="11" t="str">
+      <c r="T71" s="11">
         <f>IF(OR($C71="",S71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S71,FIND("-",S71)-1),"")=AW71,IFERROR(--MID(S71,FIND("-",S71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(S71,FIND("-",S71)-1),""))-(IFERROR(--MID(S71,FIND("-",S71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(S71,FIND("-",S71)-1),""))-(IFERROR(--MID(S71,FIND("-",S71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(S71,FIND("-",S71)-1),""))=(AW71))+2*((IFERROR(--MID(S71,FIND("-",S71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V71" s="11" t="str">
+      <c r="V71" s="11">
         <f>IF(OR($C71="",U71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U71,FIND("-",U71)-1),"")=AW71,IFERROR(--MID(U71,FIND("-",U71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(U71,FIND("-",U71)-1),""))-(IFERROR(--MID(U71,FIND("-",U71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(U71,FIND("-",U71)-1),""))-(IFERROR(--MID(U71,FIND("-",U71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(U71,FIND("-",U71)-1),""))=(AW71))+2*((IFERROR(--MID(U71,FIND("-",U71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X71" s="11" t="str">
+      <c r="X71" s="11">
         <f>IF(OR($C71="",W71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W71,FIND("-",W71)-1),"")=AW71,IFERROR(--MID(W71,FIND("-",W71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(W71,FIND("-",W71)-1),""))-(IFERROR(--MID(W71,FIND("-",W71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(W71,FIND("-",W71)-1),""))-(IFERROR(--MID(W71,FIND("-",W71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(W71,FIND("-",W71)-1),""))=(AW71))+2*((IFERROR(--MID(W71,FIND("-",W71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z71" s="11" t="str">
+      <c r="Z71" s="11">
         <f>IF(OR($C71="",Y71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y71,FIND("-",Y71)-1),"")=AW71,IFERROR(--MID(Y71,FIND("-",Y71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(Y71,FIND("-",Y71)-1),""))-(IFERROR(--MID(Y71,FIND("-",Y71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(Y71,FIND("-",Y71)-1),""))-(IFERROR(--MID(Y71,FIND("-",Y71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(Y71,FIND("-",Y71)-1),""))=(AW71))+2*((IFERROR(--MID(Y71,FIND("-",Y71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA71" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AB71" s="11" t="str">
+      <c r="AB71" s="11">
         <f>IF(OR($C71="",AA71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA71,FIND("-",AA71)-1),"")=AW71,IFERROR(--MID(AA71,FIND("-",AA71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AA71,FIND("-",AA71)-1),""))-(IFERROR(--MID(AA71,FIND("-",AA71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AA71,FIND("-",AA71)-1),""))-(IFERROR(--MID(AA71,FIND("-",AA71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AA71,FIND("-",AA71)-1),""))=(AW71))+2*((IFERROR(--MID(AA71,FIND("-",AA71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC71" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD71" s="11" t="str">
+      <c r="AD71" s="11">
         <f>IF(OR($C71="",AC71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC71,FIND("-",AC71)-1),"")=AW71,IFERROR(--MID(AC71,FIND("-",AC71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AC71,FIND("-",AC71)-1),""))-(IFERROR(--MID(AC71,FIND("-",AC71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AC71,FIND("-",AC71)-1),""))-(IFERROR(--MID(AC71,FIND("-",AC71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AC71,FIND("-",AC71)-1),""))=(AW71))+2*((IFERROR(--MID(AC71,FIND("-",AC71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF71" s="11" t="str">
+      <c r="AF71" s="11">
         <f>IF(OR($C71="",AE71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE71,FIND("-",AE71)-1),"")=AW71,IFERROR(--MID(AE71,FIND("-",AE71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AE71,FIND("-",AE71)-1),""))-(IFERROR(--MID(AE71,FIND("-",AE71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AE71,FIND("-",AE71)-1),""))-(IFERROR(--MID(AE71,FIND("-",AE71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AE71,FIND("-",AE71)-1),""))=(AW71))+2*((IFERROR(--MID(AE71,FIND("-",AE71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AH71" s="11" t="str">
+      <c r="AH71" s="11">
         <f>IF(OR($C71="",AG71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG71,FIND("-",AG71)-1),"")=AW71,IFERROR(--MID(AG71,FIND("-",AG71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AG71,FIND("-",AG71)-1),""))-(IFERROR(--MID(AG71,FIND("-",AG71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AG71,FIND("-",AG71)-1),""))-(IFERROR(--MID(AG71,FIND("-",AG71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AG71,FIND("-",AG71)-1),""))=(AW71))+2*((IFERROR(--MID(AG71,FIND("-",AG71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI71" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ71" s="11" t="str">
+      <c r="AJ71" s="11">
         <f>IF(OR($C71="",AI71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI71,FIND("-",AI71)-1),"")=AW71,IFERROR(--MID(AI71,FIND("-",AI71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AI71,FIND("-",AI71)-1),""))-(IFERROR(--MID(AI71,FIND("-",AI71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AI71,FIND("-",AI71)-1),""))-(IFERROR(--MID(AI71,FIND("-",AI71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AI71,FIND("-",AI71)-1),""))=(AW71))+2*((IFERROR(--MID(AI71,FIND("-",AI71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK71" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL71" s="11" t="str">
+      <c r="AL71" s="11">
         <f>IF(OR($C71="",AK71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK71,FIND("-",AK71)-1),"")=AW71,IFERROR(--MID(AK71,FIND("-",AK71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AK71,FIND("-",AK71)-1),""))-(IFERROR(--MID(AK71,FIND("-",AK71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AK71,FIND("-",AK71)-1),""))-(IFERROR(--MID(AK71,FIND("-",AK71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AK71,FIND("-",AK71)-1),""))=(AW71))+2*((IFERROR(--MID(AK71,FIND("-",AK71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM71" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AN71" s="11" t="str">
+      <c r="AN71" s="11">
         <f>IF(OR($C71="",AM71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM71,FIND("-",AM71)-1),"")=AW71,IFERROR(--MID(AM71,FIND("-",AM71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AM71,FIND("-",AM71)-1),""))-(IFERROR(--MID(AM71,FIND("-",AM71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AM71,FIND("-",AM71)-1),""))-(IFERROR(--MID(AM71,FIND("-",AM71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AM71,FIND("-",AM71)-1),""))=(AW71))+2*((IFERROR(--MID(AM71,FIND("-",AM71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO71" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP71" s="11" t="str">
+      <c r="AP71" s="11">
         <f>IF(OR($C71="",AO71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO71,FIND("-",AO71)-1),"")=AW71,IFERROR(--MID(AO71,FIND("-",AO71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AO71,FIND("-",AO71)-1),""))-(IFERROR(--MID(AO71,FIND("-",AO71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AO71,FIND("-",AO71)-1),""))-(IFERROR(--MID(AO71,FIND("-",AO71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AO71,FIND("-",AO71)-1),""))=(AW71))+2*((IFERROR(--MID(AO71,FIND("-",AO71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ71" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR71" s="11" t="str">
+      <c r="AR71" s="11">
         <f>IF(OR($C71="",AQ71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ71,FIND("-",AQ71)-1),"")=AW71,IFERROR(--MID(AQ71,FIND("-",AQ71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AQ71,FIND("-",AQ71)-1),""))-(IFERROR(--MID(AQ71,FIND("-",AQ71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AQ71,FIND("-",AQ71)-1),""))-(IFERROR(--MID(AQ71,FIND("-",AQ71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AQ71,FIND("-",AQ71)-1),""))=(AW71))+2*((IFERROR(--MID(AQ71,FIND("-",AQ71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS71" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT71" s="11" t="str">
+      <c r="AT71" s="11">
         <f>IF(OR($C71="",AS71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS71,FIND("-",AS71)-1),"")=AW71,IFERROR(--MID(AS71,FIND("-",AS71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AS71,FIND("-",AS71)-1),""))-(IFERROR(--MID(AS71,FIND("-",AS71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AS71,FIND("-",AS71)-1),""))-(IFERROR(--MID(AS71,FIND("-",AS71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AS71,FIND("-",AS71)-1),""))=(AW71))+2*((IFERROR(--MID(AS71,FIND("-",AS71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU71" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV71" s="11" t="str">
+      <c r="AV71" s="11">
         <f>IF(OR($C71="",AU71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU71,FIND("-",AU71)-1),"")=AW71,IFERROR(--MID(AU71,FIND("-",AU71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AU71,FIND("-",AU71)-1),""))-(IFERROR(--MID(AU71,FIND("-",AU71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AU71,FIND("-",AU71)-1),""))-(IFERROR(--MID(AU71,FIND("-",AU71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AU71,FIND("-",AU71)-1),""))=(AW71))+2*((IFERROR(--MID(AU71,FIND("-",AU71)+1,99),""))=(AX71))),""))</f>
-        <v/>
-      </c>
-      <c r="AW71" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW71" s="11">
         <f>IF($C71="","",IFERROR(--LEFT($C71,FIND("-",$C71)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX71" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX71" s="11">
         <f>IF($C71="","",IFERROR(--MID($C71,FIND("-",$C71)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -11007,171 +11009,173 @@
       <c r="B72" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C72" s="10"/>
+      <c r="C72" s="10" t="s">
+        <v>37</v>
+      </c>
       <c r="D72" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F72" s="11" t="str">
+      <c r="F72" s="11">
         <f>IF(OR($C72="",E72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E72,FIND("-",E72)-1),"")=AW72,IFERROR(--MID(E72,FIND("-",E72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(E72,FIND("-",E72)-1),""))-(IFERROR(--MID(E72,FIND("-",E72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(E72,FIND("-",E72)-1),""))-(IFERROR(--MID(E72,FIND("-",E72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(E72,FIND("-",E72)-1),""))=(AW72))+2*((IFERROR(--MID(E72,FIND("-",E72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H72" s="11" t="str">
+      <c r="H72" s="11">
         <f>IF(OR($C72="",G72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G72,FIND("-",G72)-1),"")=AW72,IFERROR(--MID(G72,FIND("-",G72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(G72,FIND("-",G72)-1),""))-(IFERROR(--MID(G72,FIND("-",G72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(G72,FIND("-",G72)-1),""))-(IFERROR(--MID(G72,FIND("-",G72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(G72,FIND("-",G72)-1),""))=(AW72))+2*((IFERROR(--MID(G72,FIND("-",G72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I72" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J72" s="11" t="str">
+      <c r="J72" s="11">
         <f>IF(OR($C72="",I72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I72,FIND("-",I72)-1),"")=AW72,IFERROR(--MID(I72,FIND("-",I72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(I72,FIND("-",I72)-1),""))-(IFERROR(--MID(I72,FIND("-",I72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(I72,FIND("-",I72)-1),""))-(IFERROR(--MID(I72,FIND("-",I72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(I72,FIND("-",I72)-1),""))=(AW72))+2*((IFERROR(--MID(I72,FIND("-",I72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L72" s="11" t="str">
+      <c r="L72" s="11">
         <f>IF(OR($C72="",K72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K72,FIND("-",K72)-1),"")=AW72,IFERROR(--MID(K72,FIND("-",K72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(K72,FIND("-",K72)-1),""))-(IFERROR(--MID(K72,FIND("-",K72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(K72,FIND("-",K72)-1),""))-(IFERROR(--MID(K72,FIND("-",K72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(K72,FIND("-",K72)-1),""))=(AW72))+2*((IFERROR(--MID(K72,FIND("-",K72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M72" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N72" s="11" t="str">
+      <c r="N72" s="11">
         <f>IF(OR($C72="",M72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M72,FIND("-",M72)-1),"")=AW72,IFERROR(--MID(M72,FIND("-",M72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(M72,FIND("-",M72)-1),""))-(IFERROR(--MID(M72,FIND("-",M72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(M72,FIND("-",M72)-1),""))-(IFERROR(--MID(M72,FIND("-",M72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(M72,FIND("-",M72)-1),""))=(AW72))+2*((IFERROR(--MID(M72,FIND("-",M72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O72" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="P72" s="11" t="str">
+      <c r="P72" s="11">
         <f>IF(OR($C72="",O72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O72,FIND("-",O72)-1),"")=AW72,IFERROR(--MID(O72,FIND("-",O72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(O72,FIND("-",O72)-1),""))-(IFERROR(--MID(O72,FIND("-",O72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(O72,FIND("-",O72)-1),""))-(IFERROR(--MID(O72,FIND("-",O72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(O72,FIND("-",O72)-1),""))=(AW72))+2*((IFERROR(--MID(O72,FIND("-",O72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R72" s="11" t="str">
+      <c r="R72" s="11">
         <f>IF(OR($C72="",Q72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q72,FIND("-",Q72)-1),"")=AW72,IFERROR(--MID(Q72,FIND("-",Q72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(Q72,FIND("-",Q72)-1),""))-(IFERROR(--MID(Q72,FIND("-",Q72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(Q72,FIND("-",Q72)-1),""))-(IFERROR(--MID(Q72,FIND("-",Q72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(Q72,FIND("-",Q72)-1),""))=(AW72))+2*((IFERROR(--MID(Q72,FIND("-",Q72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S72" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T72" s="11" t="str">
+      <c r="T72" s="11">
         <f>IF(OR($C72="",S72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S72,FIND("-",S72)-1),"")=AW72,IFERROR(--MID(S72,FIND("-",S72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(S72,FIND("-",S72)-1),""))-(IFERROR(--MID(S72,FIND("-",S72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(S72,FIND("-",S72)-1),""))-(IFERROR(--MID(S72,FIND("-",S72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(S72,FIND("-",S72)-1),""))=(AW72))+2*((IFERROR(--MID(S72,FIND("-",S72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="V72" s="11" t="str">
+      <c r="V72" s="11">
         <f>IF(OR($C72="",U72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U72,FIND("-",U72)-1),"")=AW72,IFERROR(--MID(U72,FIND("-",U72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(U72,FIND("-",U72)-1),""))-(IFERROR(--MID(U72,FIND("-",U72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(U72,FIND("-",U72)-1),""))-(IFERROR(--MID(U72,FIND("-",U72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(U72,FIND("-",U72)-1),""))=(AW72))+2*((IFERROR(--MID(U72,FIND("-",U72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W72" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="X72" s="11" t="str">
+      <c r="X72" s="11">
         <f>IF(OR($C72="",W72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W72,FIND("-",W72)-1),"")=AW72,IFERROR(--MID(W72,FIND("-",W72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(W72,FIND("-",W72)-1),""))-(IFERROR(--MID(W72,FIND("-",W72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(W72,FIND("-",W72)-1),""))-(IFERROR(--MID(W72,FIND("-",W72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(W72,FIND("-",W72)-1),""))=(AW72))+2*((IFERROR(--MID(W72,FIND("-",W72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y72" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="Z72" s="11" t="str">
+      <c r="Z72" s="11">
         <f>IF(OR($C72="",Y72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y72,FIND("-",Y72)-1),"")=AW72,IFERROR(--MID(Y72,FIND("-",Y72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(Y72,FIND("-",Y72)-1),""))-(IFERROR(--MID(Y72,FIND("-",Y72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(Y72,FIND("-",Y72)-1),""))-(IFERROR(--MID(Y72,FIND("-",Y72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(Y72,FIND("-",Y72)-1),""))=(AW72))+2*((IFERROR(--MID(Y72,FIND("-",Y72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA72" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AB72" s="11" t="str">
+      <c r="AB72" s="11">
         <f>IF(OR($C72="",AA72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA72,FIND("-",AA72)-1),"")=AW72,IFERROR(--MID(AA72,FIND("-",AA72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AA72,FIND("-",AA72)-1),""))-(IFERROR(--MID(AA72,FIND("-",AA72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AA72,FIND("-",AA72)-1),""))-(IFERROR(--MID(AA72,FIND("-",AA72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AA72,FIND("-",AA72)-1),""))=(AW72))+2*((IFERROR(--MID(AA72,FIND("-",AA72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC72" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD72" s="11" t="str">
+      <c r="AD72" s="11">
         <f>IF(OR($C72="",AC72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC72,FIND("-",AC72)-1),"")=AW72,IFERROR(--MID(AC72,FIND("-",AC72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AC72,FIND("-",AC72)-1),""))-(IFERROR(--MID(AC72,FIND("-",AC72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AC72,FIND("-",AC72)-1),""))-(IFERROR(--MID(AC72,FIND("-",AC72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AC72,FIND("-",AC72)-1),""))=(AW72))+2*((IFERROR(--MID(AC72,FIND("-",AC72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE72" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF72" s="11" t="str">
+      <c r="AF72" s="11">
         <f>IF(OR($C72="",AE72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE72,FIND("-",AE72)-1),"")=AW72,IFERROR(--MID(AE72,FIND("-",AE72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AE72,FIND("-",AE72)-1),""))-(IFERROR(--MID(AE72,FIND("-",AE72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AE72,FIND("-",AE72)-1),""))-(IFERROR(--MID(AE72,FIND("-",AE72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AE72,FIND("-",AE72)-1),""))=(AW72))+2*((IFERROR(--MID(AE72,FIND("-",AE72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG72" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH72" s="11" t="str">
+      <c r="AH72" s="11">
         <f>IF(OR($C72="",AG72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG72,FIND("-",AG72)-1),"")=AW72,IFERROR(--MID(AG72,FIND("-",AG72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AG72,FIND("-",AG72)-1),""))-(IFERROR(--MID(AG72,FIND("-",AG72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AG72,FIND("-",AG72)-1),""))-(IFERROR(--MID(AG72,FIND("-",AG72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AG72,FIND("-",AG72)-1),""))=(AW72))+2*((IFERROR(--MID(AG72,FIND("-",AG72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI72" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AJ72" s="11" t="str">
+      <c r="AJ72" s="11">
         <f>IF(OR($C72="",AI72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI72,FIND("-",AI72)-1),"")=AW72,IFERROR(--MID(AI72,FIND("-",AI72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AI72,FIND("-",AI72)-1),""))-(IFERROR(--MID(AI72,FIND("-",AI72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AI72,FIND("-",AI72)-1),""))-(IFERROR(--MID(AI72,FIND("-",AI72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AI72,FIND("-",AI72)-1),""))=(AW72))+2*((IFERROR(--MID(AI72,FIND("-",AI72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK72" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL72" s="11" t="str">
+      <c r="AL72" s="11">
         <f>IF(OR($C72="",AK72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK72,FIND("-",AK72)-1),"")=AW72,IFERROR(--MID(AK72,FIND("-",AK72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AK72,FIND("-",AK72)-1),""))-(IFERROR(--MID(AK72,FIND("-",AK72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AK72,FIND("-",AK72)-1),""))-(IFERROR(--MID(AK72,FIND("-",AK72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AK72,FIND("-",AK72)-1),""))=(AW72))+2*((IFERROR(--MID(AK72,FIND("-",AK72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM72" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AN72" s="11" t="str">
+      <c r="AN72" s="11">
         <f>IF(OR($C72="",AM72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM72,FIND("-",AM72)-1),"")=AW72,IFERROR(--MID(AM72,FIND("-",AM72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AM72,FIND("-",AM72)-1),""))-(IFERROR(--MID(AM72,FIND("-",AM72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AM72,FIND("-",AM72)-1),""))-(IFERROR(--MID(AM72,FIND("-",AM72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AM72,FIND("-",AM72)-1),""))=(AW72))+2*((IFERROR(--MID(AM72,FIND("-",AM72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO72" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AP72" s="11" t="str">
+      <c r="AP72" s="11">
         <f>IF(OR($C72="",AO72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO72,FIND("-",AO72)-1),"")=AW72,IFERROR(--MID(AO72,FIND("-",AO72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AO72,FIND("-",AO72)-1),""))-(IFERROR(--MID(AO72,FIND("-",AO72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AO72,FIND("-",AO72)-1),""))-(IFERROR(--MID(AO72,FIND("-",AO72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AO72,FIND("-",AO72)-1),""))=(AW72))+2*((IFERROR(--MID(AO72,FIND("-",AO72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR72" s="11" t="str">
+      <c r="AR72" s="11">
         <f>IF(OR($C72="",AQ72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ72,FIND("-",AQ72)-1),"")=AW72,IFERROR(--MID(AQ72,FIND("-",AQ72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AQ72,FIND("-",AQ72)-1),""))-(IFERROR(--MID(AQ72,FIND("-",AQ72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AQ72,FIND("-",AQ72)-1),""))-(IFERROR(--MID(AQ72,FIND("-",AQ72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AQ72,FIND("-",AQ72)-1),""))=(AW72))+2*((IFERROR(--MID(AQ72,FIND("-",AQ72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT72" s="11" t="str">
+      <c r="AT72" s="11">
         <f>IF(OR($C72="",AS72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS72,FIND("-",AS72)-1),"")=AW72,IFERROR(--MID(AS72,FIND("-",AS72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AS72,FIND("-",AS72)-1),""))-(IFERROR(--MID(AS72,FIND("-",AS72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AS72,FIND("-",AS72)-1),""))-(IFERROR(--MID(AS72,FIND("-",AS72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AS72,FIND("-",AS72)-1),""))=(AW72))+2*((IFERROR(--MID(AS72,FIND("-",AS72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU72" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV72" s="11" t="str">
+      <c r="AV72" s="11">
         <f>IF(OR($C72="",AU72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU72,FIND("-",AU72)-1),"")=AW72,IFERROR(--MID(AU72,FIND("-",AU72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AU72,FIND("-",AU72)-1),""))-(IFERROR(--MID(AU72,FIND("-",AU72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AU72,FIND("-",AU72)-1),""))-(IFERROR(--MID(AU72,FIND("-",AU72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AU72,FIND("-",AU72)-1),""))=(AW72))+2*((IFERROR(--MID(AU72,FIND("-",AU72)+1,99),""))=(AX72))),""))</f>
-        <v/>
-      </c>
-      <c r="AW72" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW72" s="11">
         <f>IF($C72="","",IFERROR(--LEFT($C72,FIND("-",$C72)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX72" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX72" s="11">
         <f>IF($C72="","",IFERROR(--MID($C72,FIND("-",$C72)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26567,20 +26571,20 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C3" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>192</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>213</v>
       </c>
       <c r="D3" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26594,7 +26598,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26602,29 +26606,29 @@
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>185</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>209</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>185</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26633,42 +26637,42 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>184</v>
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>208</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>184</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>183</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>208</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>183</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26682,7 +26686,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!U17</f>
@@ -26690,29 +26694,29 @@
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>177</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>177</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>203</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>177</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26726,7 +26730,7 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -26734,51 +26738,51 @@
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>175</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>175</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>201</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>175</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>174</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>201</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>174</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26787,20 +26791,20 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>168</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>200</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>168</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26809,26 +26813,26 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>167</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>189</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -26836,7 +26840,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -26844,7 +26848,7 @@
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26858,7 +26862,7 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!AU17</f>
@@ -26866,7 +26870,7 @@
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>161</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26880,7 +26884,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!AU18</f>
@@ -26888,7 +26892,7 @@
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>161</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26902,7 +26906,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!M17</f>
@@ -26910,7 +26914,7 @@
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26924,7 +26928,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26932,7 +26936,7 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>153</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26946,7 +26950,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26954,7 +26958,7 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>142</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26968,7 +26972,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!S17</f>
@@ -26976,7 +26980,7 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26990,7 +26994,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26998,7 +27002,7 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -27012,7 +27016,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -27020,7 +27024,7 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -27034,7 +27038,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -27042,7 +27046,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -27637,16 +27641,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1525" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3EBA5CC-668D-49F9-89ED-3789A591FD9F}"/>
+  <xr:revisionPtr revIDLastSave="1530" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA62429A-A1A3-4E1F-999A-02E7090D390D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1349,21 +1349,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1731,22 +1731,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1826,11 +1826,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="44"/>
+      <c r="AT1" s="39"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="44"/>
+      <c r="AV1" s="39"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1839,9 +1839,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="43"/>
+      <c r="A2" s="41"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1986,53 +1986,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -11185,171 +11185,173 @@
       <c r="B73" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="D73" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F73" s="11" t="str">
+      <c r="F73" s="11">
         <f>IF(OR($C73="",E73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E73,FIND("-",E73)-1),"")=AW73,IFERROR(--MID(E73,FIND("-",E73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(E73,FIND("-",E73)-1),""))-(IFERROR(--MID(E73,FIND("-",E73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(E73,FIND("-",E73)-1),""))-(IFERROR(--MID(E73,FIND("-",E73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(E73,FIND("-",E73)-1),""))=(AW73))+2*((IFERROR(--MID(E73,FIND("-",E73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H73" s="11" t="str">
+      <c r="H73" s="11">
         <f>IF(OR($C73="",G73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G73,FIND("-",G73)-1),"")=AW73,IFERROR(--MID(G73,FIND("-",G73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(G73,FIND("-",G73)-1),""))-(IFERROR(--MID(G73,FIND("-",G73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(G73,FIND("-",G73)-1),""))-(IFERROR(--MID(G73,FIND("-",G73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(G73,FIND("-",G73)-1),""))=(AW73))+2*((IFERROR(--MID(G73,FIND("-",G73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I73" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J73" s="11" t="str">
+      <c r="J73" s="11">
         <f>IF(OR($C73="",I73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I73,FIND("-",I73)-1),"")=AW73,IFERROR(--MID(I73,FIND("-",I73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(I73,FIND("-",I73)-1),""))-(IFERROR(--MID(I73,FIND("-",I73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(I73,FIND("-",I73)-1),""))-(IFERROR(--MID(I73,FIND("-",I73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(I73,FIND("-",I73)-1),""))=(AW73))+2*((IFERROR(--MID(I73,FIND("-",I73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L73" s="11" t="str">
+      <c r="L73" s="11">
         <f>IF(OR($C73="",K73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K73,FIND("-",K73)-1),"")=AW73,IFERROR(--MID(K73,FIND("-",K73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(K73,FIND("-",K73)-1),""))-(IFERROR(--MID(K73,FIND("-",K73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(K73,FIND("-",K73)-1),""))-(IFERROR(--MID(K73,FIND("-",K73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(K73,FIND("-",K73)-1),""))=(AW73))+2*((IFERROR(--MID(K73,FIND("-",K73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N73" s="11" t="str">
+      <c r="N73" s="11">
         <f>IF(OR($C73="",M73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M73,FIND("-",M73)-1),"")=AW73,IFERROR(--MID(M73,FIND("-",M73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(M73,FIND("-",M73)-1),""))-(IFERROR(--MID(M73,FIND("-",M73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(M73,FIND("-",M73)-1),""))-(IFERROR(--MID(M73,FIND("-",M73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(M73,FIND("-",M73)-1),""))=(AW73))+2*((IFERROR(--MID(M73,FIND("-",M73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P73" s="11" t="str">
+      <c r="P73" s="11">
         <f>IF(OR($C73="",O73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O73,FIND("-",O73)-1),"")=AW73,IFERROR(--MID(O73,FIND("-",O73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(O73,FIND("-",O73)-1),""))-(IFERROR(--MID(O73,FIND("-",O73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(O73,FIND("-",O73)-1),""))-(IFERROR(--MID(O73,FIND("-",O73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(O73,FIND("-",O73)-1),""))=(AW73))+2*((IFERROR(--MID(O73,FIND("-",O73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q73" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="R73" s="11" t="str">
+      <c r="R73" s="11">
         <f>IF(OR($C73="",Q73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q73,FIND("-",Q73)-1),"")=AW73,IFERROR(--MID(Q73,FIND("-",Q73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(Q73,FIND("-",Q73)-1),""))-(IFERROR(--MID(Q73,FIND("-",Q73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(Q73,FIND("-",Q73)-1),""))-(IFERROR(--MID(Q73,FIND("-",Q73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(Q73,FIND("-",Q73)-1),""))=(AW73))+2*((IFERROR(--MID(Q73,FIND("-",Q73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S73" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T73" s="11" t="str">
+      <c r="T73" s="11">
         <f>IF(OR($C73="",S73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S73,FIND("-",S73)-1),"")=AW73,IFERROR(--MID(S73,FIND("-",S73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(S73,FIND("-",S73)-1),""))-(IFERROR(--MID(S73,FIND("-",S73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(S73,FIND("-",S73)-1),""))-(IFERROR(--MID(S73,FIND("-",S73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(S73,FIND("-",S73)-1),""))=(AW73))+2*((IFERROR(--MID(S73,FIND("-",S73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="U73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V73" s="11" t="str">
+      <c r="V73" s="11">
         <f>IF(OR($C73="",U73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U73,FIND("-",U73)-1),"")=AW73,IFERROR(--MID(U73,FIND("-",U73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(U73,FIND("-",U73)-1),""))-(IFERROR(--MID(U73,FIND("-",U73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(U73,FIND("-",U73)-1),""))-(IFERROR(--MID(U73,FIND("-",U73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(U73,FIND("-",U73)-1),""))=(AW73))+2*((IFERROR(--MID(U73,FIND("-",U73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="X73" s="11" t="str">
+      <c r="X73" s="11">
         <f>IF(OR($C73="",W73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W73,FIND("-",W73)-1),"")=AW73,IFERROR(--MID(W73,FIND("-",W73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(W73,FIND("-",W73)-1),""))-(IFERROR(--MID(W73,FIND("-",W73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(W73,FIND("-",W73)-1),""))-(IFERROR(--MID(W73,FIND("-",W73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(W73,FIND("-",W73)-1),""))=(AW73))+2*((IFERROR(--MID(W73,FIND("-",W73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z73" s="11" t="str">
+      <c r="Z73" s="11">
         <f>IF(OR($C73="",Y73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y73,FIND("-",Y73)-1),"")=AW73,IFERROR(--MID(Y73,FIND("-",Y73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(Y73,FIND("-",Y73)-1),""))-(IFERROR(--MID(Y73,FIND("-",Y73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(Y73,FIND("-",Y73)-1),""))-(IFERROR(--MID(Y73,FIND("-",Y73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(Y73,FIND("-",Y73)-1),""))=(AW73))+2*((IFERROR(--MID(Y73,FIND("-",Y73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA73" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AB73" s="11" t="str">
+      <c r="AB73" s="11">
         <f>IF(OR($C73="",AA73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA73,FIND("-",AA73)-1),"")=AW73,IFERROR(--MID(AA73,FIND("-",AA73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AA73,FIND("-",AA73)-1),""))-(IFERROR(--MID(AA73,FIND("-",AA73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AA73,FIND("-",AA73)-1),""))-(IFERROR(--MID(AA73,FIND("-",AA73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AA73,FIND("-",AA73)-1),""))=(AW73))+2*((IFERROR(--MID(AA73,FIND("-",AA73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC73" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AD73" s="11" t="str">
+      <c r="AD73" s="11">
         <f>IF(OR($C73="",AC73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC73,FIND("-",AC73)-1),"")=AW73,IFERROR(--MID(AC73,FIND("-",AC73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AC73,FIND("-",AC73)-1),""))-(IFERROR(--MID(AC73,FIND("-",AC73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AC73,FIND("-",AC73)-1),""))-(IFERROR(--MID(AC73,FIND("-",AC73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AC73,FIND("-",AC73)-1),""))=(AW73))+2*((IFERROR(--MID(AC73,FIND("-",AC73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF73" s="11" t="str">
+      <c r="AF73" s="11">
         <f>IF(OR($C73="",AE73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE73,FIND("-",AE73)-1),"")=AW73,IFERROR(--MID(AE73,FIND("-",AE73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AE73,FIND("-",AE73)-1),""))-(IFERROR(--MID(AE73,FIND("-",AE73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AE73,FIND("-",AE73)-1),""))-(IFERROR(--MID(AE73,FIND("-",AE73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AE73,FIND("-",AE73)-1),""))=(AW73))+2*((IFERROR(--MID(AE73,FIND("-",AE73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH73" s="11" t="str">
+      <c r="AH73" s="11">
         <f>IF(OR($C73="",AG73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG73,FIND("-",AG73)-1),"")=AW73,IFERROR(--MID(AG73,FIND("-",AG73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AG73,FIND("-",AG73)-1),""))-(IFERROR(--MID(AG73,FIND("-",AG73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AG73,FIND("-",AG73)-1),""))-(IFERROR(--MID(AG73,FIND("-",AG73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AG73,FIND("-",AG73)-1),""))=(AW73))+2*((IFERROR(--MID(AG73,FIND("-",AG73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI73" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AJ73" s="11" t="str">
+      <c r="AJ73" s="11">
         <f>IF(OR($C73="",AI73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI73,FIND("-",AI73)-1),"")=AW73,IFERROR(--MID(AI73,FIND("-",AI73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AI73,FIND("-",AI73)-1),""))-(IFERROR(--MID(AI73,FIND("-",AI73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AI73,FIND("-",AI73)-1),""))-(IFERROR(--MID(AI73,FIND("-",AI73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AI73,FIND("-",AI73)-1),""))=(AW73))+2*((IFERROR(--MID(AI73,FIND("-",AI73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL73" s="11" t="str">
+      <c r="AL73" s="11">
         <f>IF(OR($C73="",AK73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK73,FIND("-",AK73)-1),"")=AW73,IFERROR(--MID(AK73,FIND("-",AK73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AK73,FIND("-",AK73)-1),""))-(IFERROR(--MID(AK73,FIND("-",AK73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AK73,FIND("-",AK73)-1),""))-(IFERROR(--MID(AK73,FIND("-",AK73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AK73,FIND("-",AK73)-1),""))=(AW73))+2*((IFERROR(--MID(AK73,FIND("-",AK73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AN73" s="11" t="str">
+      <c r="AN73" s="11">
         <f>IF(OR($C73="",AM73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM73,FIND("-",AM73)-1),"")=AW73,IFERROR(--MID(AM73,FIND("-",AM73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AM73,FIND("-",AM73)-1),""))-(IFERROR(--MID(AM73,FIND("-",AM73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AM73,FIND("-",AM73)-1),""))-(IFERROR(--MID(AM73,FIND("-",AM73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AM73,FIND("-",AM73)-1),""))=(AW73))+2*((IFERROR(--MID(AM73,FIND("-",AM73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP73" s="11" t="str">
+      <c r="AP73" s="11">
         <f>IF(OR($C73="",AO73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO73,FIND("-",AO73)-1),"")=AW73,IFERROR(--MID(AO73,FIND("-",AO73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AO73,FIND("-",AO73)-1),""))-(IFERROR(--MID(AO73,FIND("-",AO73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AO73,FIND("-",AO73)-1),""))-(IFERROR(--MID(AO73,FIND("-",AO73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AO73,FIND("-",AO73)-1),""))=(AW73))+2*((IFERROR(--MID(AO73,FIND("-",AO73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ73" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR73" s="11" t="str">
+      <c r="AR73" s="11">
         <f>IF(OR($C73="",AQ73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ73,FIND("-",AQ73)-1),"")=AW73,IFERROR(--MID(AQ73,FIND("-",AQ73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AQ73,FIND("-",AQ73)-1),""))-(IFERROR(--MID(AQ73,FIND("-",AQ73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AQ73,FIND("-",AQ73)-1),""))-(IFERROR(--MID(AQ73,FIND("-",AQ73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AQ73,FIND("-",AQ73)-1),""))=(AW73))+2*((IFERROR(--MID(AQ73,FIND("-",AQ73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS73" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT73" s="11" t="str">
+      <c r="AT73" s="11">
         <f>IF(OR($C73="",AS73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS73,FIND("-",AS73)-1),"")=AW73,IFERROR(--MID(AS73,FIND("-",AS73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AS73,FIND("-",AS73)-1),""))-(IFERROR(--MID(AS73,FIND("-",AS73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AS73,FIND("-",AS73)-1),""))-(IFERROR(--MID(AS73,FIND("-",AS73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AS73,FIND("-",AS73)-1),""))=(AW73))+2*((IFERROR(--MID(AS73,FIND("-",AS73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU73" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AV73" s="11" t="str">
+      <c r="AV73" s="11">
         <f>IF(OR($C73="",AU73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU73,FIND("-",AU73)-1),"")=AW73,IFERROR(--MID(AU73,FIND("-",AU73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AU73,FIND("-",AU73)-1),""))-(IFERROR(--MID(AU73,FIND("-",AU73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AU73,FIND("-",AU73)-1),""))-(IFERROR(--MID(AU73,FIND("-",AU73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AU73,FIND("-",AU73)-1),""))=(AW73))+2*((IFERROR(--MID(AU73,FIND("-",AU73)+1,99),""))=(AX73))),""))</f>
-        <v/>
-      </c>
-      <c r="AW73" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW73" s="11">
         <f>IF($C73="","",IFERROR(--LEFT($C73,FIND("-",$C73)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX73" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AX73" s="11">
         <f>IF($C73="","",IFERROR(--MID($C73,FIND("-",$C73)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -11359,171 +11361,173 @@
       <c r="B74" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="10"/>
+      <c r="C74" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D74" s="1" t="s">
         <v>104</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F74" s="11" t="str">
+      <c r="F74" s="11">
         <f>IF(OR($C74="",E74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E74,FIND("-",E74)-1),"")=AW74,IFERROR(--MID(E74,FIND("-",E74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(E74,FIND("-",E74)-1),""))-(IFERROR(--MID(E74,FIND("-",E74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(E74,FIND("-",E74)-1),""))-(IFERROR(--MID(E74,FIND("-",E74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(E74,FIND("-",E74)-1),""))=(AW74))+2*((IFERROR(--MID(E74,FIND("-",E74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="H74" s="11" t="str">
+      <c r="H74" s="11">
         <f>IF(OR($C74="",G74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G74,FIND("-",G74)-1),"")=AW74,IFERROR(--MID(G74,FIND("-",G74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(G74,FIND("-",G74)-1),""))-(IFERROR(--MID(G74,FIND("-",G74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(G74,FIND("-",G74)-1),""))-(IFERROR(--MID(G74,FIND("-",G74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(G74,FIND("-",G74)-1),""))=(AW74))+2*((IFERROR(--MID(G74,FIND("-",G74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J74" s="11" t="str">
+      <c r="J74" s="11">
         <f>IF(OR($C74="",I74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I74,FIND("-",I74)-1),"")=AW74,IFERROR(--MID(I74,FIND("-",I74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(I74,FIND("-",I74)-1),""))-(IFERROR(--MID(I74,FIND("-",I74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(I74,FIND("-",I74)-1),""))-(IFERROR(--MID(I74,FIND("-",I74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(I74,FIND("-",I74)-1),""))=(AW74))+2*((IFERROR(--MID(I74,FIND("-",I74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K74" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L74" s="11" t="str">
+      <c r="L74" s="11">
         <f>IF(OR($C74="",K74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K74,FIND("-",K74)-1),"")=AW74,IFERROR(--MID(K74,FIND("-",K74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(K74,FIND("-",K74)-1),""))-(IFERROR(--MID(K74,FIND("-",K74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(K74,FIND("-",K74)-1),""))-(IFERROR(--MID(K74,FIND("-",K74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(K74,FIND("-",K74)-1),""))=(AW74))+2*((IFERROR(--MID(K74,FIND("-",K74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M74" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N74" s="11" t="str">
+      <c r="N74" s="11">
         <f>IF(OR($C74="",M74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M74,FIND("-",M74)-1),"")=AW74,IFERROR(--MID(M74,FIND("-",M74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(M74,FIND("-",M74)-1),""))-(IFERROR(--MID(M74,FIND("-",M74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(M74,FIND("-",M74)-1),""))-(IFERROR(--MID(M74,FIND("-",M74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(M74,FIND("-",M74)-1),""))=(AW74))+2*((IFERROR(--MID(M74,FIND("-",M74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P74" s="11" t="str">
+      <c r="P74" s="11">
         <f>IF(OR($C74="",O74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O74,FIND("-",O74)-1),"")=AW74,IFERROR(--MID(O74,FIND("-",O74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(O74,FIND("-",O74)-1),""))-(IFERROR(--MID(O74,FIND("-",O74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(O74,FIND("-",O74)-1),""))-(IFERROR(--MID(O74,FIND("-",O74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(O74,FIND("-",O74)-1),""))=(AW74))+2*((IFERROR(--MID(O74,FIND("-",O74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q74" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="R74" s="11" t="str">
+      <c r="R74" s="11">
         <f>IF(OR($C74="",Q74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q74,FIND("-",Q74)-1),"")=AW74,IFERROR(--MID(Q74,FIND("-",Q74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(Q74,FIND("-",Q74)-1),""))-(IFERROR(--MID(Q74,FIND("-",Q74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(Q74,FIND("-",Q74)-1),""))-(IFERROR(--MID(Q74,FIND("-",Q74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(Q74,FIND("-",Q74)-1),""))=(AW74))+2*((IFERROR(--MID(Q74,FIND("-",Q74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S74" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T74" s="11" t="str">
+      <c r="T74" s="11">
         <f>IF(OR($C74="",S74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S74,FIND("-",S74)-1),"")=AW74,IFERROR(--MID(S74,FIND("-",S74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(S74,FIND("-",S74)-1),""))-(IFERROR(--MID(S74,FIND("-",S74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(S74,FIND("-",S74)-1),""))-(IFERROR(--MID(S74,FIND("-",S74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(S74,FIND("-",S74)-1),""))=(AW74))+2*((IFERROR(--MID(S74,FIND("-",S74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V74" s="11" t="str">
+      <c r="V74" s="11">
         <f>IF(OR($C74="",U74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U74,FIND("-",U74)-1),"")=AW74,IFERROR(--MID(U74,FIND("-",U74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(U74,FIND("-",U74)-1),""))-(IFERROR(--MID(U74,FIND("-",U74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(U74,FIND("-",U74)-1),""))-(IFERROR(--MID(U74,FIND("-",U74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(U74,FIND("-",U74)-1),""))=(AW74))+2*((IFERROR(--MID(U74,FIND("-",U74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X74" s="11" t="str">
+      <c r="X74" s="11">
         <f>IF(OR($C74="",W74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W74,FIND("-",W74)-1),"")=AW74,IFERROR(--MID(W74,FIND("-",W74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(W74,FIND("-",W74)-1),""))-(IFERROR(--MID(W74,FIND("-",W74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(W74,FIND("-",W74)-1),""))-(IFERROR(--MID(W74,FIND("-",W74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(W74,FIND("-",W74)-1),""))=(AW74))+2*((IFERROR(--MID(W74,FIND("-",W74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z74" s="11" t="str">
+      <c r="Z74" s="11">
         <f>IF(OR($C74="",Y74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y74,FIND("-",Y74)-1),"")=AW74,IFERROR(--MID(Y74,FIND("-",Y74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(Y74,FIND("-",Y74)-1),""))-(IFERROR(--MID(Y74,FIND("-",Y74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(Y74,FIND("-",Y74)-1),""))-(IFERROR(--MID(Y74,FIND("-",Y74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(Y74,FIND("-",Y74)-1),""))=(AW74))+2*((IFERROR(--MID(Y74,FIND("-",Y74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA74" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AB74" s="11" t="str">
+      <c r="AB74" s="11">
         <f>IF(OR($C74="",AA74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA74,FIND("-",AA74)-1),"")=AW74,IFERROR(--MID(AA74,FIND("-",AA74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AA74,FIND("-",AA74)-1),""))-(IFERROR(--MID(AA74,FIND("-",AA74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AA74,FIND("-",AA74)-1),""))-(IFERROR(--MID(AA74,FIND("-",AA74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AA74,FIND("-",AA74)-1),""))=(AW74))+2*((IFERROR(--MID(AA74,FIND("-",AA74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC74" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD74" s="11" t="str">
+      <c r="AD74" s="11">
         <f>IF(OR($C74="",AC74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC74,FIND("-",AC74)-1),"")=AW74,IFERROR(--MID(AC74,FIND("-",AC74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AC74,FIND("-",AC74)-1),""))-(IFERROR(--MID(AC74,FIND("-",AC74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AC74,FIND("-",AC74)-1),""))-(IFERROR(--MID(AC74,FIND("-",AC74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AC74,FIND("-",AC74)-1),""))=(AW74))+2*((IFERROR(--MID(AC74,FIND("-",AC74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF74" s="11" t="str">
+      <c r="AF74" s="11">
         <f>IF(OR($C74="",AE74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE74,FIND("-",AE74)-1),"")=AW74,IFERROR(--MID(AE74,FIND("-",AE74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AE74,FIND("-",AE74)-1),""))-(IFERROR(--MID(AE74,FIND("-",AE74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AE74,FIND("-",AE74)-1),""))-(IFERROR(--MID(AE74,FIND("-",AE74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AE74,FIND("-",AE74)-1),""))=(AW74))+2*((IFERROR(--MID(AE74,FIND("-",AE74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH74" s="11" t="str">
+      <c r="AH74" s="11">
         <f>IF(OR($C74="",AG74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG74,FIND("-",AG74)-1),"")=AW74,IFERROR(--MID(AG74,FIND("-",AG74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AG74,FIND("-",AG74)-1),""))-(IFERROR(--MID(AG74,FIND("-",AG74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AG74,FIND("-",AG74)-1),""))-(IFERROR(--MID(AG74,FIND("-",AG74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AG74,FIND("-",AG74)-1),""))=(AW74))+2*((IFERROR(--MID(AG74,FIND("-",AG74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI74" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ74" s="11" t="str">
+      <c r="AJ74" s="11">
         <f>IF(OR($C74="",AI74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI74,FIND("-",AI74)-1),"")=AW74,IFERROR(--MID(AI74,FIND("-",AI74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AI74,FIND("-",AI74)-1),""))-(IFERROR(--MID(AI74,FIND("-",AI74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AI74,FIND("-",AI74)-1),""))-(IFERROR(--MID(AI74,FIND("-",AI74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AI74,FIND("-",AI74)-1),""))=(AW74))+2*((IFERROR(--MID(AI74,FIND("-",AI74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK74" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AL74" s="11" t="str">
+      <c r="AL74" s="11">
         <f>IF(OR($C74="",AK74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK74,FIND("-",AK74)-1),"")=AW74,IFERROR(--MID(AK74,FIND("-",AK74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AK74,FIND("-",AK74)-1),""))-(IFERROR(--MID(AK74,FIND("-",AK74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AK74,FIND("-",AK74)-1),""))-(IFERROR(--MID(AK74,FIND("-",AK74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AK74,FIND("-",AK74)-1),""))=(AW74))+2*((IFERROR(--MID(AK74,FIND("-",AK74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM74" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AN74" s="11" t="str">
+      <c r="AN74" s="11">
         <f>IF(OR($C74="",AM74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM74,FIND("-",AM74)-1),"")=AW74,IFERROR(--MID(AM74,FIND("-",AM74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AM74,FIND("-",AM74)-1),""))-(IFERROR(--MID(AM74,FIND("-",AM74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AM74,FIND("-",AM74)-1),""))-(IFERROR(--MID(AM74,FIND("-",AM74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AM74,FIND("-",AM74)-1),""))=(AW74))+2*((IFERROR(--MID(AM74,FIND("-",AM74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP74" s="11" t="str">
+      <c r="AP74" s="11">
         <f>IF(OR($C74="",AO74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO74,FIND("-",AO74)-1),"")=AW74,IFERROR(--MID(AO74,FIND("-",AO74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AO74,FIND("-",AO74)-1),""))-(IFERROR(--MID(AO74,FIND("-",AO74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AO74,FIND("-",AO74)-1),""))-(IFERROR(--MID(AO74,FIND("-",AO74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AO74,FIND("-",AO74)-1),""))=(AW74))+2*((IFERROR(--MID(AO74,FIND("-",AO74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ74" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AR74" s="11" t="str">
+      <c r="AR74" s="11">
         <f>IF(OR($C74="",AQ74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ74,FIND("-",AQ74)-1),"")=AW74,IFERROR(--MID(AQ74,FIND("-",AQ74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AQ74,FIND("-",AQ74)-1),""))-(IFERROR(--MID(AQ74,FIND("-",AQ74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AQ74,FIND("-",AQ74)-1),""))-(IFERROR(--MID(AQ74,FIND("-",AQ74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AQ74,FIND("-",AQ74)-1),""))=(AW74))+2*((IFERROR(--MID(AQ74,FIND("-",AQ74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT74" s="11" t="str">
+      <c r="AT74" s="11">
         <f>IF(OR($C74="",AS74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS74,FIND("-",AS74)-1),"")=AW74,IFERROR(--MID(AS74,FIND("-",AS74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AS74,FIND("-",AS74)-1),""))-(IFERROR(--MID(AS74,FIND("-",AS74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AS74,FIND("-",AS74)-1),""))-(IFERROR(--MID(AS74,FIND("-",AS74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AS74,FIND("-",AS74)-1),""))=(AW74))+2*((IFERROR(--MID(AS74,FIND("-",AS74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV74" s="11" t="str">
+      <c r="AV74" s="11">
         <f>IF(OR($C74="",AU74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU74,FIND("-",AU74)-1),"")=AW74,IFERROR(--MID(AU74,FIND("-",AU74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AU74,FIND("-",AU74)-1),""))-(IFERROR(--MID(AU74,FIND("-",AU74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AU74,FIND("-",AU74)-1),""))-(IFERROR(--MID(AU74,FIND("-",AU74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AU74,FIND("-",AU74)-1),""))=(AW74))+2*((IFERROR(--MID(AU74,FIND("-",AU74)+1,99),""))=(AX74))),""))</f>
-        <v/>
-      </c>
-      <c r="AW74" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW74" s="11">
         <f>IF($C74="","",IFERROR(--LEFT($C74,FIND("-",$C74)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX74" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX74" s="11">
         <f>IF($C74="","",IFERROR(--MID($C74,FIND("-",$C74)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -11645,171 +11649,173 @@
       <c r="B77" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D77" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F77" s="11" t="str">
+      <c r="F77" s="11">
         <f>IF(OR($C77="",E77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E77,FIND("-",E77)-1),"")=AW77,IFERROR(--MID(E77,FIND("-",E77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(E77,FIND("-",E77)-1),""))-(IFERROR(--MID(E77,FIND("-",E77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(E77,FIND("-",E77)-1),""))-(IFERROR(--MID(E77,FIND("-",E77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(E77,FIND("-",E77)-1),""))=(AW77))+2*((IFERROR(--MID(E77,FIND("-",E77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H77" s="11" t="str">
+      <c r="H77" s="11">
         <f>IF(OR($C77="",G77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G77,FIND("-",G77)-1),"")=AW77,IFERROR(--MID(G77,FIND("-",G77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(G77,FIND("-",G77)-1),""))-(IFERROR(--MID(G77,FIND("-",G77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(G77,FIND("-",G77)-1),""))-(IFERROR(--MID(G77,FIND("-",G77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(G77,FIND("-",G77)-1),""))=(AW77))+2*((IFERROR(--MID(G77,FIND("-",G77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I77" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J77" s="11" t="str">
+      <c r="J77" s="11">
         <f>IF(OR($C77="",I77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I77,FIND("-",I77)-1),"")=AW77,IFERROR(--MID(I77,FIND("-",I77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(I77,FIND("-",I77)-1),""))-(IFERROR(--MID(I77,FIND("-",I77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(I77,FIND("-",I77)-1),""))-(IFERROR(--MID(I77,FIND("-",I77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(I77,FIND("-",I77)-1),""))=(AW77))+2*((IFERROR(--MID(I77,FIND("-",I77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L77" s="11" t="str">
+      <c r="L77" s="11">
         <f>IF(OR($C77="",K77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K77,FIND("-",K77)-1),"")=AW77,IFERROR(--MID(K77,FIND("-",K77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(K77,FIND("-",K77)-1),""))-(IFERROR(--MID(K77,FIND("-",K77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(K77,FIND("-",K77)-1),""))-(IFERROR(--MID(K77,FIND("-",K77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(K77,FIND("-",K77)-1),""))=(AW77))+2*((IFERROR(--MID(K77,FIND("-",K77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M77" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N77" s="11" t="str">
+      <c r="N77" s="11">
         <f>IF(OR($C77="",M77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M77,FIND("-",M77)-1),"")=AW77,IFERROR(--MID(M77,FIND("-",M77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(M77,FIND("-",M77)-1),""))-(IFERROR(--MID(M77,FIND("-",M77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(M77,FIND("-",M77)-1),""))-(IFERROR(--MID(M77,FIND("-",M77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(M77,FIND("-",M77)-1),""))=(AW77))+2*((IFERROR(--MID(M77,FIND("-",M77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="P77" s="11" t="str">
+      <c r="P77" s="11">
         <f>IF(OR($C77="",O77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O77,FIND("-",O77)-1),"")=AW77,IFERROR(--MID(O77,FIND("-",O77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(O77,FIND("-",O77)-1),""))-(IFERROR(--MID(O77,FIND("-",O77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(O77,FIND("-",O77)-1),""))-(IFERROR(--MID(O77,FIND("-",O77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(O77,FIND("-",O77)-1),""))=(AW77))+2*((IFERROR(--MID(O77,FIND("-",O77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q77" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="R77" s="11" t="str">
+      <c r="R77" s="11">
         <f>IF(OR($C77="",Q77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q77,FIND("-",Q77)-1),"")=AW77,IFERROR(--MID(Q77,FIND("-",Q77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(Q77,FIND("-",Q77)-1),""))-(IFERROR(--MID(Q77,FIND("-",Q77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(Q77,FIND("-",Q77)-1),""))-(IFERROR(--MID(Q77,FIND("-",Q77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(Q77,FIND("-",Q77)-1),""))=(AW77))+2*((IFERROR(--MID(Q77,FIND("-",Q77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S77" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T77" s="11" t="str">
+      <c r="T77" s="11">
         <f>IF(OR($C77="",S77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S77,FIND("-",S77)-1),"")=AW77,IFERROR(--MID(S77,FIND("-",S77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(S77,FIND("-",S77)-1),""))-(IFERROR(--MID(S77,FIND("-",S77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(S77,FIND("-",S77)-1),""))-(IFERROR(--MID(S77,FIND("-",S77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(S77,FIND("-",S77)-1),""))=(AW77))+2*((IFERROR(--MID(S77,FIND("-",S77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V77" s="11" t="str">
+      <c r="V77" s="11">
         <f>IF(OR($C77="",U77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U77,FIND("-",U77)-1),"")=AW77,IFERROR(--MID(U77,FIND("-",U77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(U77,FIND("-",U77)-1),""))-(IFERROR(--MID(U77,FIND("-",U77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(U77,FIND("-",U77)-1),""))-(IFERROR(--MID(U77,FIND("-",U77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(U77,FIND("-",U77)-1),""))=(AW77))+2*((IFERROR(--MID(U77,FIND("-",U77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X77" s="11" t="str">
+      <c r="X77" s="11">
         <f>IF(OR($C77="",W77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W77,FIND("-",W77)-1),"")=AW77,IFERROR(--MID(W77,FIND("-",W77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(W77,FIND("-",W77)-1),""))-(IFERROR(--MID(W77,FIND("-",W77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(W77,FIND("-",W77)-1),""))-(IFERROR(--MID(W77,FIND("-",W77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(W77,FIND("-",W77)-1),""))=(AW77))+2*((IFERROR(--MID(W77,FIND("-",W77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z77" s="11" t="str">
+      <c r="Z77" s="11">
         <f>IF(OR($C77="",Y77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y77,FIND("-",Y77)-1),"")=AW77,IFERROR(--MID(Y77,FIND("-",Y77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(Y77,FIND("-",Y77)-1),""))-(IFERROR(--MID(Y77,FIND("-",Y77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(Y77,FIND("-",Y77)-1),""))-(IFERROR(--MID(Y77,FIND("-",Y77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(Y77,FIND("-",Y77)-1),""))=(AW77))+2*((IFERROR(--MID(Y77,FIND("-",Y77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AB77" s="11" t="str">
+      <c r="AB77" s="11">
         <f>IF(OR($C77="",AA77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA77,FIND("-",AA77)-1),"")=AW77,IFERROR(--MID(AA77,FIND("-",AA77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AA77,FIND("-",AA77)-1),""))-(IFERROR(--MID(AA77,FIND("-",AA77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AA77,FIND("-",AA77)-1),""))-(IFERROR(--MID(AA77,FIND("-",AA77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AA77,FIND("-",AA77)-1),""))=(AW77))+2*((IFERROR(--MID(AA77,FIND("-",AA77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC77" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="AD77" s="11" t="str">
+      <c r="AD77" s="11">
         <f>IF(OR($C77="",AC77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC77,FIND("-",AC77)-1),"")=AW77,IFERROR(--MID(AC77,FIND("-",AC77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AC77,FIND("-",AC77)-1),""))-(IFERROR(--MID(AC77,FIND("-",AC77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AC77,FIND("-",AC77)-1),""))-(IFERROR(--MID(AC77,FIND("-",AC77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AC77,FIND("-",AC77)-1),""))=(AW77))+2*((IFERROR(--MID(AC77,FIND("-",AC77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF77" s="11" t="str">
+      <c r="AF77" s="11">
         <f>IF(OR($C77="",AE77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE77,FIND("-",AE77)-1),"")=AW77,IFERROR(--MID(AE77,FIND("-",AE77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AE77,FIND("-",AE77)-1),""))-(IFERROR(--MID(AE77,FIND("-",AE77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AE77,FIND("-",AE77)-1),""))-(IFERROR(--MID(AE77,FIND("-",AE77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AE77,FIND("-",AE77)-1),""))=(AW77))+2*((IFERROR(--MID(AE77,FIND("-",AE77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH77" s="11" t="str">
+      <c r="AH77" s="11">
         <f>IF(OR($C77="",AG77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG77,FIND("-",AG77)-1),"")=AW77,IFERROR(--MID(AG77,FIND("-",AG77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AG77,FIND("-",AG77)-1),""))-(IFERROR(--MID(AG77,FIND("-",AG77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AG77,FIND("-",AG77)-1),""))-(IFERROR(--MID(AG77,FIND("-",AG77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AG77,FIND("-",AG77)-1),""))=(AW77))+2*((IFERROR(--MID(AG77,FIND("-",AG77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI77" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AJ77" s="11" t="str">
+      <c r="AJ77" s="11">
         <f>IF(OR($C77="",AI77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI77,FIND("-",AI77)-1),"")=AW77,IFERROR(--MID(AI77,FIND("-",AI77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AI77,FIND("-",AI77)-1),""))-(IFERROR(--MID(AI77,FIND("-",AI77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AI77,FIND("-",AI77)-1),""))-(IFERROR(--MID(AI77,FIND("-",AI77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AI77,FIND("-",AI77)-1),""))=(AW77))+2*((IFERROR(--MID(AI77,FIND("-",AI77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL77" s="11" t="str">
+      <c r="AL77" s="11">
         <f>IF(OR($C77="",AK77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK77,FIND("-",AK77)-1),"")=AW77,IFERROR(--MID(AK77,FIND("-",AK77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AK77,FIND("-",AK77)-1),""))-(IFERROR(--MID(AK77,FIND("-",AK77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AK77,FIND("-",AK77)-1),""))-(IFERROR(--MID(AK77,FIND("-",AK77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AK77,FIND("-",AK77)-1),""))=(AW77))+2*((IFERROR(--MID(AK77,FIND("-",AK77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN77" s="11" t="str">
+      <c r="AN77" s="11">
         <f>IF(OR($C77="",AM77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM77,FIND("-",AM77)-1),"")=AW77,IFERROR(--MID(AM77,FIND("-",AM77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AM77,FIND("-",AM77)-1),""))-(IFERROR(--MID(AM77,FIND("-",AM77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AM77,FIND("-",AM77)-1),""))-(IFERROR(--MID(AM77,FIND("-",AM77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AM77,FIND("-",AM77)-1),""))=(AW77))+2*((IFERROR(--MID(AM77,FIND("-",AM77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO77" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AP77" s="11" t="str">
+      <c r="AP77" s="11">
         <f>IF(OR($C77="",AO77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO77,FIND("-",AO77)-1),"")=AW77,IFERROR(--MID(AO77,FIND("-",AO77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AO77,FIND("-",AO77)-1),""))-(IFERROR(--MID(AO77,FIND("-",AO77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AO77,FIND("-",AO77)-1),""))-(IFERROR(--MID(AO77,FIND("-",AO77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AO77,FIND("-",AO77)-1),""))=(AW77))+2*((IFERROR(--MID(AO77,FIND("-",AO77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ77" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR77" s="11" t="str">
+      <c r="AR77" s="11">
         <f>IF(OR($C77="",AQ77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ77,FIND("-",AQ77)-1),"")=AW77,IFERROR(--MID(AQ77,FIND("-",AQ77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AQ77,FIND("-",AQ77)-1),""))-(IFERROR(--MID(AQ77,FIND("-",AQ77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AQ77,FIND("-",AQ77)-1),""))-(IFERROR(--MID(AQ77,FIND("-",AQ77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AQ77,FIND("-",AQ77)-1),""))=(AW77))+2*((IFERROR(--MID(AQ77,FIND("-",AQ77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS77" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT77" s="11" t="str">
+      <c r="AT77" s="11">
         <f>IF(OR($C77="",AS77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS77,FIND("-",AS77)-1),"")=AW77,IFERROR(--MID(AS77,FIND("-",AS77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AS77,FIND("-",AS77)-1),""))-(IFERROR(--MID(AS77,FIND("-",AS77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AS77,FIND("-",AS77)-1),""))-(IFERROR(--MID(AS77,FIND("-",AS77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AS77,FIND("-",AS77)-1),""))=(AW77))+2*((IFERROR(--MID(AS77,FIND("-",AS77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU77" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV77" s="11" t="str">
+      <c r="AV77" s="11">
         <f>IF(OR($C77="",AU77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU77,FIND("-",AU77)-1),"")=AW77,IFERROR(--MID(AU77,FIND("-",AU77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AU77,FIND("-",AU77)-1),""))-(IFERROR(--MID(AU77,FIND("-",AU77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AU77,FIND("-",AU77)-1),""))-(IFERROR(--MID(AU77,FIND("-",AU77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AU77,FIND("-",AU77)-1),""))=(AW77))+2*((IFERROR(--MID(AU77,FIND("-",AU77)+1,99),""))=(AX77))),""))</f>
-        <v/>
-      </c>
-      <c r="AW77" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW77" s="11">
         <f>IF($C77="","",IFERROR(--LEFT($C77,FIND("-",$C77)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX77" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX77" s="11">
         <f>IF($C77="","",IFERROR(--MID($C77,FIND("-",$C77)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -11819,171 +11825,173 @@
       <c r="B78" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C78" s="10"/>
+      <c r="C78" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D78" s="1" t="s">
         <v>100</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F78" s="11" t="str">
+      <c r="F78" s="11">
         <f>IF(OR($C78="",E78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E78,FIND("-",E78)-1),"")=AW78,IFERROR(--MID(E78,FIND("-",E78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(E78,FIND("-",E78)-1),""))-(IFERROR(--MID(E78,FIND("-",E78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(E78,FIND("-",E78)-1),""))-(IFERROR(--MID(E78,FIND("-",E78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(E78,FIND("-",E78)-1),""))=(AW78))+2*((IFERROR(--MID(E78,FIND("-",E78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H78" s="11" t="str">
+      <c r="H78" s="11">
         <f>IF(OR($C78="",G78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G78,FIND("-",G78)-1),"")=AW78,IFERROR(--MID(G78,FIND("-",G78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(G78,FIND("-",G78)-1),""))-(IFERROR(--MID(G78,FIND("-",G78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(G78,FIND("-",G78)-1),""))-(IFERROR(--MID(G78,FIND("-",G78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(G78,FIND("-",G78)-1),""))=(AW78))+2*((IFERROR(--MID(G78,FIND("-",G78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J78" s="11" t="str">
+      <c r="J78" s="11">
         <f>IF(OR($C78="",I78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I78,FIND("-",I78)-1),"")=AW78,IFERROR(--MID(I78,FIND("-",I78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(I78,FIND("-",I78)-1),""))-(IFERROR(--MID(I78,FIND("-",I78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(I78,FIND("-",I78)-1),""))-(IFERROR(--MID(I78,FIND("-",I78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(I78,FIND("-",I78)-1),""))=(AW78))+2*((IFERROR(--MID(I78,FIND("-",I78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L78" s="11" t="str">
+      <c r="L78" s="11">
         <f>IF(OR($C78="",K78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K78,FIND("-",K78)-1),"")=AW78,IFERROR(--MID(K78,FIND("-",K78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(K78,FIND("-",K78)-1),""))-(IFERROR(--MID(K78,FIND("-",K78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(K78,FIND("-",K78)-1),""))-(IFERROR(--MID(K78,FIND("-",K78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(K78,FIND("-",K78)-1),""))=(AW78))+2*((IFERROR(--MID(K78,FIND("-",K78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M78" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="N78" s="11" t="str">
+      <c r="N78" s="11">
         <f>IF(OR($C78="",M78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M78,FIND("-",M78)-1),"")=AW78,IFERROR(--MID(M78,FIND("-",M78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(M78,FIND("-",M78)-1),""))-(IFERROR(--MID(M78,FIND("-",M78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(M78,FIND("-",M78)-1),""))-(IFERROR(--MID(M78,FIND("-",M78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(M78,FIND("-",M78)-1),""))=(AW78))+2*((IFERROR(--MID(M78,FIND("-",M78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O78" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P78" s="11" t="str">
+      <c r="P78" s="11">
         <f>IF(OR($C78="",O78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O78,FIND("-",O78)-1),"")=AW78,IFERROR(--MID(O78,FIND("-",O78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(O78,FIND("-",O78)-1),""))-(IFERROR(--MID(O78,FIND("-",O78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(O78,FIND("-",O78)-1),""))-(IFERROR(--MID(O78,FIND("-",O78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(O78,FIND("-",O78)-1),""))=(AW78))+2*((IFERROR(--MID(O78,FIND("-",O78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="R78" s="11" t="str">
+      <c r="R78" s="11">
         <f>IF(OR($C78="",Q78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q78,FIND("-",Q78)-1),"")=AW78,IFERROR(--MID(Q78,FIND("-",Q78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(Q78,FIND("-",Q78)-1),""))-(IFERROR(--MID(Q78,FIND("-",Q78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(Q78,FIND("-",Q78)-1),""))-(IFERROR(--MID(Q78,FIND("-",Q78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(Q78,FIND("-",Q78)-1),""))=(AW78))+2*((IFERROR(--MID(Q78,FIND("-",Q78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S78" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T78" s="11" t="str">
+      <c r="T78" s="11">
         <f>IF(OR($C78="",S78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S78,FIND("-",S78)-1),"")=AW78,IFERROR(--MID(S78,FIND("-",S78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(S78,FIND("-",S78)-1),""))-(IFERROR(--MID(S78,FIND("-",S78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(S78,FIND("-",S78)-1),""))-(IFERROR(--MID(S78,FIND("-",S78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(S78,FIND("-",S78)-1),""))=(AW78))+2*((IFERROR(--MID(S78,FIND("-",S78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V78" s="11" t="str">
+      <c r="V78" s="11">
         <f>IF(OR($C78="",U78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U78,FIND("-",U78)-1),"")=AW78,IFERROR(--MID(U78,FIND("-",U78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(U78,FIND("-",U78)-1),""))-(IFERROR(--MID(U78,FIND("-",U78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(U78,FIND("-",U78)-1),""))-(IFERROR(--MID(U78,FIND("-",U78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(U78,FIND("-",U78)-1),""))=(AW78))+2*((IFERROR(--MID(U78,FIND("-",U78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X78" s="11" t="str">
+      <c r="X78" s="11">
         <f>IF(OR($C78="",W78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W78,FIND("-",W78)-1),"")=AW78,IFERROR(--MID(W78,FIND("-",W78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(W78,FIND("-",W78)-1),""))-(IFERROR(--MID(W78,FIND("-",W78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(W78,FIND("-",W78)-1),""))-(IFERROR(--MID(W78,FIND("-",W78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(W78,FIND("-",W78)-1),""))=(AW78))+2*((IFERROR(--MID(W78,FIND("-",W78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y78" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z78" s="11" t="str">
+      <c r="Z78" s="11">
         <f>IF(OR($C78="",Y78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y78,FIND("-",Y78)-1),"")=AW78,IFERROR(--MID(Y78,FIND("-",Y78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(Y78,FIND("-",Y78)-1),""))-(IFERROR(--MID(Y78,FIND("-",Y78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(Y78,FIND("-",Y78)-1),""))-(IFERROR(--MID(Y78,FIND("-",Y78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(Y78,FIND("-",Y78)-1),""))=(AW78))+2*((IFERROR(--MID(Y78,FIND("-",Y78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA78" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB78" s="11" t="str">
+      <c r="AB78" s="11">
         <f>IF(OR($C78="",AA78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA78,FIND("-",AA78)-1),"")=AW78,IFERROR(--MID(AA78,FIND("-",AA78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AA78,FIND("-",AA78)-1),""))-(IFERROR(--MID(AA78,FIND("-",AA78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AA78,FIND("-",AA78)-1),""))-(IFERROR(--MID(AA78,FIND("-",AA78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AA78,FIND("-",AA78)-1),""))=(AW78))+2*((IFERROR(--MID(AA78,FIND("-",AA78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC78" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="AD78" s="11" t="str">
+      <c r="AD78" s="11">
         <f>IF(OR($C78="",AC78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC78,FIND("-",AC78)-1),"")=AW78,IFERROR(--MID(AC78,FIND("-",AC78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AC78,FIND("-",AC78)-1),""))-(IFERROR(--MID(AC78,FIND("-",AC78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AC78,FIND("-",AC78)-1),""))-(IFERROR(--MID(AC78,FIND("-",AC78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AC78,FIND("-",AC78)-1),""))=(AW78))+2*((IFERROR(--MID(AC78,FIND("-",AC78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF78" s="11" t="str">
+      <c r="AF78" s="11">
         <f>IF(OR($C78="",AE78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE78,FIND("-",AE78)-1),"")=AW78,IFERROR(--MID(AE78,FIND("-",AE78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AE78,FIND("-",AE78)-1),""))-(IFERROR(--MID(AE78,FIND("-",AE78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AE78,FIND("-",AE78)-1),""))-(IFERROR(--MID(AE78,FIND("-",AE78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AE78,FIND("-",AE78)-1),""))=(AW78))+2*((IFERROR(--MID(AE78,FIND("-",AE78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH78" s="11" t="str">
+      <c r="AH78" s="11">
         <f>IF(OR($C78="",AG78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG78,FIND("-",AG78)-1),"")=AW78,IFERROR(--MID(AG78,FIND("-",AG78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AG78,FIND("-",AG78)-1),""))-(IFERROR(--MID(AG78,FIND("-",AG78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AG78,FIND("-",AG78)-1),""))-(IFERROR(--MID(AG78,FIND("-",AG78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AG78,FIND("-",AG78)-1),""))=(AW78))+2*((IFERROR(--MID(AG78,FIND("-",AG78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI78" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ78" s="11" t="str">
+      <c r="AJ78" s="11">
         <f>IF(OR($C78="",AI78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI78,FIND("-",AI78)-1),"")=AW78,IFERROR(--MID(AI78,FIND("-",AI78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AI78,FIND("-",AI78)-1),""))-(IFERROR(--MID(AI78,FIND("-",AI78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AI78,FIND("-",AI78)-1),""))-(IFERROR(--MID(AI78,FIND("-",AI78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AI78,FIND("-",AI78)-1),""))=(AW78))+2*((IFERROR(--MID(AI78,FIND("-",AI78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL78" s="11" t="str">
+      <c r="AL78" s="11">
         <f>IF(OR($C78="",AK78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK78,FIND("-",AK78)-1),"")=AW78,IFERROR(--MID(AK78,FIND("-",AK78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AK78,FIND("-",AK78)-1),""))-(IFERROR(--MID(AK78,FIND("-",AK78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AK78,FIND("-",AK78)-1),""))-(IFERROR(--MID(AK78,FIND("-",AK78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AK78,FIND("-",AK78)-1),""))=(AW78))+2*((IFERROR(--MID(AK78,FIND("-",AK78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM78" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN78" s="11" t="str">
+      <c r="AN78" s="11">
         <f>IF(OR($C78="",AM78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM78,FIND("-",AM78)-1),"")=AW78,IFERROR(--MID(AM78,FIND("-",AM78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AM78,FIND("-",AM78)-1),""))-(IFERROR(--MID(AM78,FIND("-",AM78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AM78,FIND("-",AM78)-1),""))-(IFERROR(--MID(AM78,FIND("-",AM78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AM78,FIND("-",AM78)-1),""))=(AW78))+2*((IFERROR(--MID(AM78,FIND("-",AM78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP78" s="11" t="str">
+      <c r="AP78" s="11">
         <f>IF(OR($C78="",AO78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO78,FIND("-",AO78)-1),"")=AW78,IFERROR(--MID(AO78,FIND("-",AO78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AO78,FIND("-",AO78)-1),""))-(IFERROR(--MID(AO78,FIND("-",AO78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AO78,FIND("-",AO78)-1),""))-(IFERROR(--MID(AO78,FIND("-",AO78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AO78,FIND("-",AO78)-1),""))=(AW78))+2*((IFERROR(--MID(AO78,FIND("-",AO78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR78" s="11" t="str">
+      <c r="AR78" s="11">
         <f>IF(OR($C78="",AQ78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ78,FIND("-",AQ78)-1),"")=AW78,IFERROR(--MID(AQ78,FIND("-",AQ78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AQ78,FIND("-",AQ78)-1),""))-(IFERROR(--MID(AQ78,FIND("-",AQ78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AQ78,FIND("-",AQ78)-1),""))-(IFERROR(--MID(AQ78,FIND("-",AQ78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AQ78,FIND("-",AQ78)-1),""))=(AW78))+2*((IFERROR(--MID(AQ78,FIND("-",AQ78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS78" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT78" s="11" t="str">
+      <c r="AT78" s="11">
         <f>IF(OR($C78="",AS78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS78,FIND("-",AS78)-1),"")=AW78,IFERROR(--MID(AS78,FIND("-",AS78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AS78,FIND("-",AS78)-1),""))-(IFERROR(--MID(AS78,FIND("-",AS78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AS78,FIND("-",AS78)-1),""))-(IFERROR(--MID(AS78,FIND("-",AS78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AS78,FIND("-",AS78)-1),""))=(AW78))+2*((IFERROR(--MID(AS78,FIND("-",AS78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AU78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV78" s="11" t="str">
+      <c r="AV78" s="11">
         <f>IF(OR($C78="",AU78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU78,FIND("-",AU78)-1),"")=AW78,IFERROR(--MID(AU78,FIND("-",AU78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AU78,FIND("-",AU78)-1),""))-(IFERROR(--MID(AU78,FIND("-",AU78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AU78,FIND("-",AU78)-1),""))-(IFERROR(--MID(AU78,FIND("-",AU78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AU78,FIND("-",AU78)-1),""))=(AW78))+2*((IFERROR(--MID(AU78,FIND("-",AU78)+1,99),""))=(AX78))),""))</f>
-        <v/>
-      </c>
-      <c r="AW78" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW78" s="11">
         <f>IF($C78="","",IFERROR(--LEFT($C78,FIND("-",$C78)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX78" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX78" s="11">
         <f>IF($C78="","",IFERROR(--MID($C78,FIND("-",$C78)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -23712,6 +23720,60 @@
     <filterColumn colId="46" showButton="0"/>
   </autoFilter>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23728,60 +23790,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23948,12 +23956,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="44"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="44"/>
+      <c r="AU1" s="39"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
@@ -26497,6 +26505,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26508,17 +26527,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26576,7 +26584,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -26584,7 +26592,7 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>213</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26593,20 +26601,20 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>209</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>230</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26615,20 +26623,20 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>209</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>230</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26642,7 +26650,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26650,29 +26658,29 @@
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>208</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>227</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>208</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26681,20 +26689,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>204</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>225</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>204</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26703,42 +26711,42 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>203</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>224</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>202</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>224</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26747,20 +26755,20 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>201</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>223</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26769,20 +26777,20 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>201</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>223</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26791,20 +26799,20 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>200</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>219</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26818,7 +26826,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26826,7 +26834,7 @@
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26840,7 +26848,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -26848,7 +26856,7 @@
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26862,7 +26870,7 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!AU17</f>
@@ -26870,7 +26878,7 @@
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26884,7 +26892,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!AU18</f>
@@ -26892,7 +26900,7 @@
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26906,7 +26914,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!M17</f>
@@ -26914,7 +26922,7 @@
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>180</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26928,7 +26936,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26936,7 +26944,7 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26950,7 +26958,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26958,7 +26966,7 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26967,20 +26975,20 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>153</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>178</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>153</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26989,64 +26997,64 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>151</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>172</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>149</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>172</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="11">
         <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C24" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>149</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>160</v>
       </c>
       <c r="D24" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -27424,26 +27432,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27638,32 +27626,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27680,4 +27663,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1530" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA62429A-A1A3-4E1F-999A-02E7090D390D}"/>
+  <xr:revisionPtr revIDLastSave="1540" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEF60F4-95A2-42B0-B0C6-14325133CD3E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -12001,171 +12001,173 @@
       <c r="B79" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="D79" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F79" s="11" t="str">
+      <c r="F79" s="11">
         <f>IF(OR($C79="",E79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E79,FIND("-",E79)-1),"")=AW79,IFERROR(--MID(E79,FIND("-",E79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(E79,FIND("-",E79)-1),""))-(IFERROR(--MID(E79,FIND("-",E79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(E79,FIND("-",E79)-1),""))-(IFERROR(--MID(E79,FIND("-",E79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(E79,FIND("-",E79)-1),""))=(AW79))+2*((IFERROR(--MID(E79,FIND("-",E79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H79" s="11" t="str">
+      <c r="H79" s="11">
         <f>IF(OR($C79="",G79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G79,FIND("-",G79)-1),"")=AW79,IFERROR(--MID(G79,FIND("-",G79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(G79,FIND("-",G79)-1),""))-(IFERROR(--MID(G79,FIND("-",G79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(G79,FIND("-",G79)-1),""))-(IFERROR(--MID(G79,FIND("-",G79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(G79,FIND("-",G79)-1),""))=(AW79))+2*((IFERROR(--MID(G79,FIND("-",G79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I79" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J79" s="11" t="str">
+      <c r="J79" s="11">
         <f>IF(OR($C79="",I79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I79,FIND("-",I79)-1),"")=AW79,IFERROR(--MID(I79,FIND("-",I79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(I79,FIND("-",I79)-1),""))-(IFERROR(--MID(I79,FIND("-",I79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(I79,FIND("-",I79)-1),""))-(IFERROR(--MID(I79,FIND("-",I79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(I79,FIND("-",I79)-1),""))=(AW79))+2*((IFERROR(--MID(I79,FIND("-",I79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K79" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L79" s="11" t="str">
+      <c r="L79" s="11">
         <f>IF(OR($C79="",K79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K79,FIND("-",K79)-1),"")=AW79,IFERROR(--MID(K79,FIND("-",K79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(K79,FIND("-",K79)-1),""))-(IFERROR(--MID(K79,FIND("-",K79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(K79,FIND("-",K79)-1),""))-(IFERROR(--MID(K79,FIND("-",K79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(K79,FIND("-",K79)-1),""))=(AW79))+2*((IFERROR(--MID(K79,FIND("-",K79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N79" s="11" t="str">
+      <c r="N79" s="11">
         <f>IF(OR($C79="",M79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M79,FIND("-",M79)-1),"")=AW79,IFERROR(--MID(M79,FIND("-",M79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(M79,FIND("-",M79)-1),""))-(IFERROR(--MID(M79,FIND("-",M79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(M79,FIND("-",M79)-1),""))-(IFERROR(--MID(M79,FIND("-",M79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(M79,FIND("-",M79)-1),""))=(AW79))+2*((IFERROR(--MID(M79,FIND("-",M79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P79" s="11" t="str">
+      <c r="P79" s="11">
         <f>IF(OR($C79="",O79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O79,FIND("-",O79)-1),"")=AW79,IFERROR(--MID(O79,FIND("-",O79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(O79,FIND("-",O79)-1),""))-(IFERROR(--MID(O79,FIND("-",O79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(O79,FIND("-",O79)-1),""))-(IFERROR(--MID(O79,FIND("-",O79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(O79,FIND("-",O79)-1),""))=(AW79))+2*((IFERROR(--MID(O79,FIND("-",O79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q79" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R79" s="11" t="str">
+      <c r="R79" s="11">
         <f>IF(OR($C79="",Q79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q79,FIND("-",Q79)-1),"")=AW79,IFERROR(--MID(Q79,FIND("-",Q79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(Q79,FIND("-",Q79)-1),""))-(IFERROR(--MID(Q79,FIND("-",Q79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(Q79,FIND("-",Q79)-1),""))-(IFERROR(--MID(Q79,FIND("-",Q79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(Q79,FIND("-",Q79)-1),""))=(AW79))+2*((IFERROR(--MID(Q79,FIND("-",Q79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S79" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T79" s="11" t="str">
+      <c r="T79" s="11">
         <f>IF(OR($C79="",S79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S79,FIND("-",S79)-1),"")=AW79,IFERROR(--MID(S79,FIND("-",S79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(S79,FIND("-",S79)-1),""))-(IFERROR(--MID(S79,FIND("-",S79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(S79,FIND("-",S79)-1),""))-(IFERROR(--MID(S79,FIND("-",S79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(S79,FIND("-",S79)-1),""))=(AW79))+2*((IFERROR(--MID(S79,FIND("-",S79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V79" s="11" t="str">
+      <c r="V79" s="11">
         <f>IF(OR($C79="",U79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U79,FIND("-",U79)-1),"")=AW79,IFERROR(--MID(U79,FIND("-",U79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(U79,FIND("-",U79)-1),""))-(IFERROR(--MID(U79,FIND("-",U79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(U79,FIND("-",U79)-1),""))-(IFERROR(--MID(U79,FIND("-",U79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(U79,FIND("-",U79)-1),""))=(AW79))+2*((IFERROR(--MID(U79,FIND("-",U79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X79" s="11" t="str">
+      <c r="X79" s="11">
         <f>IF(OR($C79="",W79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W79,FIND("-",W79)-1),"")=AW79,IFERROR(--MID(W79,FIND("-",W79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(W79,FIND("-",W79)-1),""))-(IFERROR(--MID(W79,FIND("-",W79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(W79,FIND("-",W79)-1),""))-(IFERROR(--MID(W79,FIND("-",W79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(W79,FIND("-",W79)-1),""))=(AW79))+2*((IFERROR(--MID(W79,FIND("-",W79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z79" s="11" t="str">
+      <c r="Z79" s="11">
         <f>IF(OR($C79="",Y79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y79,FIND("-",Y79)-1),"")=AW79,IFERROR(--MID(Y79,FIND("-",Y79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(Y79,FIND("-",Y79)-1),""))-(IFERROR(--MID(Y79,FIND("-",Y79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(Y79,FIND("-",Y79)-1),""))-(IFERROR(--MID(Y79,FIND("-",Y79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(Y79,FIND("-",Y79)-1),""))=(AW79))+2*((IFERROR(--MID(Y79,FIND("-",Y79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AB79" s="11" t="str">
+      <c r="AB79" s="11">
         <f>IF(OR($C79="",AA79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA79,FIND("-",AA79)-1),"")=AW79,IFERROR(--MID(AA79,FIND("-",AA79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AA79,FIND("-",AA79)-1),""))-(IFERROR(--MID(AA79,FIND("-",AA79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AA79,FIND("-",AA79)-1),""))-(IFERROR(--MID(AA79,FIND("-",AA79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AA79,FIND("-",AA79)-1),""))=(AW79))+2*((IFERROR(--MID(AA79,FIND("-",AA79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC79" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="AD79" s="11" t="str">
+      <c r="AD79" s="11">
         <f>IF(OR($C79="",AC79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC79,FIND("-",AC79)-1),"")=AW79,IFERROR(--MID(AC79,FIND("-",AC79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AC79,FIND("-",AC79)-1),""))-(IFERROR(--MID(AC79,FIND("-",AC79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AC79,FIND("-",AC79)-1),""))-(IFERROR(--MID(AC79,FIND("-",AC79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AC79,FIND("-",AC79)-1),""))=(AW79))+2*((IFERROR(--MID(AC79,FIND("-",AC79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF79" s="11" t="str">
+      <c r="AF79" s="11">
         <f>IF(OR($C79="",AE79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE79,FIND("-",AE79)-1),"")=AW79,IFERROR(--MID(AE79,FIND("-",AE79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AE79,FIND("-",AE79)-1),""))-(IFERROR(--MID(AE79,FIND("-",AE79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AE79,FIND("-",AE79)-1),""))-(IFERROR(--MID(AE79,FIND("-",AE79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AE79,FIND("-",AE79)-1),""))=(AW79))+2*((IFERROR(--MID(AE79,FIND("-",AE79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG79" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH79" s="11" t="str">
+      <c r="AH79" s="11">
         <f>IF(OR($C79="",AG79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG79,FIND("-",AG79)-1),"")=AW79,IFERROR(--MID(AG79,FIND("-",AG79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AG79,FIND("-",AG79)-1),""))-(IFERROR(--MID(AG79,FIND("-",AG79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AG79,FIND("-",AG79)-1),""))-(IFERROR(--MID(AG79,FIND("-",AG79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AG79,FIND("-",AG79)-1),""))=(AW79))+2*((IFERROR(--MID(AG79,FIND("-",AG79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ79" s="11" t="str">
+      <c r="AJ79" s="11">
         <f>IF(OR($C79="",AI79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI79,FIND("-",AI79)-1),"")=AW79,IFERROR(--MID(AI79,FIND("-",AI79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AI79,FIND("-",AI79)-1),""))-(IFERROR(--MID(AI79,FIND("-",AI79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AI79,FIND("-",AI79)-1),""))-(IFERROR(--MID(AI79,FIND("-",AI79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AI79,FIND("-",AI79)-1),""))=(AW79))+2*((IFERROR(--MID(AI79,FIND("-",AI79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL79" s="11" t="str">
+      <c r="AL79" s="11">
         <f>IF(OR($C79="",AK79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK79,FIND("-",AK79)-1),"")=AW79,IFERROR(--MID(AK79,FIND("-",AK79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AK79,FIND("-",AK79)-1),""))-(IFERROR(--MID(AK79,FIND("-",AK79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AK79,FIND("-",AK79)-1),""))-(IFERROR(--MID(AK79,FIND("-",AK79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AK79,FIND("-",AK79)-1),""))=(AW79))+2*((IFERROR(--MID(AK79,FIND("-",AK79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM79" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AN79" s="11" t="str">
+      <c r="AN79" s="11">
         <f>IF(OR($C79="",AM79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM79,FIND("-",AM79)-1),"")=AW79,IFERROR(--MID(AM79,FIND("-",AM79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AM79,FIND("-",AM79)-1),""))-(IFERROR(--MID(AM79,FIND("-",AM79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AM79,FIND("-",AM79)-1),""))-(IFERROR(--MID(AM79,FIND("-",AM79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AM79,FIND("-",AM79)-1),""))=(AW79))+2*((IFERROR(--MID(AM79,FIND("-",AM79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AP79" s="11" t="str">
+      <c r="AP79" s="11">
         <f>IF(OR($C79="",AO79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO79,FIND("-",AO79)-1),"")=AW79,IFERROR(--MID(AO79,FIND("-",AO79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AO79,FIND("-",AO79)-1),""))-(IFERROR(--MID(AO79,FIND("-",AO79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AO79,FIND("-",AO79)-1),""))-(IFERROR(--MID(AO79,FIND("-",AO79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AO79,FIND("-",AO79)-1),""))=(AW79))+2*((IFERROR(--MID(AO79,FIND("-",AO79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ79" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR79" s="11" t="str">
+      <c r="AR79" s="11">
         <f>IF(OR($C79="",AQ79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ79,FIND("-",AQ79)-1),"")=AW79,IFERROR(--MID(AQ79,FIND("-",AQ79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AQ79,FIND("-",AQ79)-1),""))-(IFERROR(--MID(AQ79,FIND("-",AQ79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AQ79,FIND("-",AQ79)-1),""))-(IFERROR(--MID(AQ79,FIND("-",AQ79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AQ79,FIND("-",AQ79)-1),""))=(AW79))+2*((IFERROR(--MID(AQ79,FIND("-",AQ79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS79" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT79" s="11" t="str">
+      <c r="AT79" s="11">
         <f>IF(OR($C79="",AS79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS79,FIND("-",AS79)-1),"")=AW79,IFERROR(--MID(AS79,FIND("-",AS79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AS79,FIND("-",AS79)-1),""))-(IFERROR(--MID(AS79,FIND("-",AS79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AS79,FIND("-",AS79)-1),""))-(IFERROR(--MID(AS79,FIND("-",AS79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AS79,FIND("-",AS79)-1),""))=(AW79))+2*((IFERROR(--MID(AS79,FIND("-",AS79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AV79" s="11" t="str">
+      <c r="AV79" s="11">
         <f>IF(OR($C79="",AU79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU79,FIND("-",AU79)-1),"")=AW79,IFERROR(--MID(AU79,FIND("-",AU79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AU79,FIND("-",AU79)-1),""))-(IFERROR(--MID(AU79,FIND("-",AU79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AU79,FIND("-",AU79)-1),""))-(IFERROR(--MID(AU79,FIND("-",AU79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AU79,FIND("-",AU79)-1),""))=(AW79))+2*((IFERROR(--MID(AU79,FIND("-",AU79)+1,99),""))=(AX79))),""))</f>
-        <v/>
-      </c>
-      <c r="AW79" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW79" s="11">
         <f>IF($C79="","",IFERROR(--LEFT($C79,FIND("-",$C79)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX79" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX79" s="11">
         <f>IF($C79="","",IFERROR(--MID($C79,FIND("-",$C79)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -12175,171 +12177,173 @@
       <c r="B80" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="D80" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F80" s="11" t="str">
+      <c r="F80" s="11">
         <f>IF(OR($C80="",E80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E80,FIND("-",E80)-1),"")=AW80,IFERROR(--MID(E80,FIND("-",E80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(E80,FIND("-",E80)-1),""))-(IFERROR(--MID(E80,FIND("-",E80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(E80,FIND("-",E80)-1),""))-(IFERROR(--MID(E80,FIND("-",E80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(E80,FIND("-",E80)-1),""))=(AW80))+2*((IFERROR(--MID(E80,FIND("-",E80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H80" s="11" t="str">
+      <c r="H80" s="11">
         <f>IF(OR($C80="",G80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G80,FIND("-",G80)-1),"")=AW80,IFERROR(--MID(G80,FIND("-",G80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(G80,FIND("-",G80)-1),""))-(IFERROR(--MID(G80,FIND("-",G80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(G80,FIND("-",G80)-1),""))-(IFERROR(--MID(G80,FIND("-",G80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(G80,FIND("-",G80)-1),""))=(AW80))+2*((IFERROR(--MID(G80,FIND("-",G80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I80" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J80" s="11" t="str">
+      <c r="J80" s="11">
         <f>IF(OR($C80="",I80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I80,FIND("-",I80)-1),"")=AW80,IFERROR(--MID(I80,FIND("-",I80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(I80,FIND("-",I80)-1),""))-(IFERROR(--MID(I80,FIND("-",I80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(I80,FIND("-",I80)-1),""))-(IFERROR(--MID(I80,FIND("-",I80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(I80,FIND("-",I80)-1),""))=(AW80))+2*((IFERROR(--MID(I80,FIND("-",I80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L80" s="11" t="str">
+      <c r="L80" s="11">
         <f>IF(OR($C80="",K80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K80,FIND("-",K80)-1),"")=AW80,IFERROR(--MID(K80,FIND("-",K80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(K80,FIND("-",K80)-1),""))-(IFERROR(--MID(K80,FIND("-",K80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(K80,FIND("-",K80)-1),""))-(IFERROR(--MID(K80,FIND("-",K80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(K80,FIND("-",K80)-1),""))=(AW80))+2*((IFERROR(--MID(K80,FIND("-",K80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N80" s="11" t="str">
+      <c r="N80" s="11">
         <f>IF(OR($C80="",M80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M80,FIND("-",M80)-1),"")=AW80,IFERROR(--MID(M80,FIND("-",M80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(M80,FIND("-",M80)-1),""))-(IFERROR(--MID(M80,FIND("-",M80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(M80,FIND("-",M80)-1),""))-(IFERROR(--MID(M80,FIND("-",M80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(M80,FIND("-",M80)-1),""))=(AW80))+2*((IFERROR(--MID(M80,FIND("-",M80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P80" s="11" t="str">
+      <c r="P80" s="11">
         <f>IF(OR($C80="",O80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O80,FIND("-",O80)-1),"")=AW80,IFERROR(--MID(O80,FIND("-",O80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(O80,FIND("-",O80)-1),""))-(IFERROR(--MID(O80,FIND("-",O80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(O80,FIND("-",O80)-1),""))-(IFERROR(--MID(O80,FIND("-",O80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(O80,FIND("-",O80)-1),""))=(AW80))+2*((IFERROR(--MID(O80,FIND("-",O80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q80" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R80" s="11" t="str">
+      <c r="R80" s="11">
         <f>IF(OR($C80="",Q80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q80,FIND("-",Q80)-1),"")=AW80,IFERROR(--MID(Q80,FIND("-",Q80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(Q80,FIND("-",Q80)-1),""))-(IFERROR(--MID(Q80,FIND("-",Q80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(Q80,FIND("-",Q80)-1),""))-(IFERROR(--MID(Q80,FIND("-",Q80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(Q80,FIND("-",Q80)-1),""))=(AW80))+2*((IFERROR(--MID(Q80,FIND("-",Q80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T80" s="11" t="str">
+      <c r="T80" s="11">
         <f>IF(OR($C80="",S80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S80,FIND("-",S80)-1),"")=AW80,IFERROR(--MID(S80,FIND("-",S80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(S80,FIND("-",S80)-1),""))-(IFERROR(--MID(S80,FIND("-",S80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(S80,FIND("-",S80)-1),""))-(IFERROR(--MID(S80,FIND("-",S80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(S80,FIND("-",S80)-1),""))=(AW80))+2*((IFERROR(--MID(S80,FIND("-",S80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V80" s="11" t="str">
+      <c r="V80" s="11">
         <f>IF(OR($C80="",U80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U80,FIND("-",U80)-1),"")=AW80,IFERROR(--MID(U80,FIND("-",U80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(U80,FIND("-",U80)-1),""))-(IFERROR(--MID(U80,FIND("-",U80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(U80,FIND("-",U80)-1),""))-(IFERROR(--MID(U80,FIND("-",U80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(U80,FIND("-",U80)-1),""))=(AW80))+2*((IFERROR(--MID(U80,FIND("-",U80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W80" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X80" s="11" t="str">
+      <c r="X80" s="11">
         <f>IF(OR($C80="",W80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W80,FIND("-",W80)-1),"")=AW80,IFERROR(--MID(W80,FIND("-",W80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(W80,FIND("-",W80)-1),""))-(IFERROR(--MID(W80,FIND("-",W80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(W80,FIND("-",W80)-1),""))-(IFERROR(--MID(W80,FIND("-",W80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(W80,FIND("-",W80)-1),""))=(AW80))+2*((IFERROR(--MID(W80,FIND("-",W80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y80" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z80" s="11" t="str">
+      <c r="Z80" s="11">
         <f>IF(OR($C80="",Y80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y80,FIND("-",Y80)-1),"")=AW80,IFERROR(--MID(Y80,FIND("-",Y80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(Y80,FIND("-",Y80)-1),""))-(IFERROR(--MID(Y80,FIND("-",Y80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(Y80,FIND("-",Y80)-1),""))-(IFERROR(--MID(Y80,FIND("-",Y80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(Y80,FIND("-",Y80)-1),""))=(AW80))+2*((IFERROR(--MID(Y80,FIND("-",Y80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA80" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB80" s="11" t="str">
+      <c r="AB80" s="11">
         <f>IF(OR($C80="",AA80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA80,FIND("-",AA80)-1),"")=AW80,IFERROR(--MID(AA80,FIND("-",AA80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AA80,FIND("-",AA80)-1),""))-(IFERROR(--MID(AA80,FIND("-",AA80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AA80,FIND("-",AA80)-1),""))-(IFERROR(--MID(AA80,FIND("-",AA80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AA80,FIND("-",AA80)-1),""))=(AW80))+2*((IFERROR(--MID(AA80,FIND("-",AA80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC80" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="AD80" s="11" t="str">
+      <c r="AD80" s="11">
         <f>IF(OR($C80="",AC80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC80,FIND("-",AC80)-1),"")=AW80,IFERROR(--MID(AC80,FIND("-",AC80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AC80,FIND("-",AC80)-1),""))-(IFERROR(--MID(AC80,FIND("-",AC80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AC80,FIND("-",AC80)-1),""))-(IFERROR(--MID(AC80,FIND("-",AC80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AC80,FIND("-",AC80)-1),""))=(AW80))+2*((IFERROR(--MID(AC80,FIND("-",AC80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AE80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF80" s="11" t="str">
+      <c r="AF80" s="11">
         <f>IF(OR($C80="",AE80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE80,FIND("-",AE80)-1),"")=AW80,IFERROR(--MID(AE80,FIND("-",AE80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AE80,FIND("-",AE80)-1),""))-(IFERROR(--MID(AE80,FIND("-",AE80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AE80,FIND("-",AE80)-1),""))-(IFERROR(--MID(AE80,FIND("-",AE80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AE80,FIND("-",AE80)-1),""))=(AW80))+2*((IFERROR(--MID(AE80,FIND("-",AE80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG80" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH80" s="11" t="str">
+      <c r="AH80" s="11">
         <f>IF(OR($C80="",AG80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG80,FIND("-",AG80)-1),"")=AW80,IFERROR(--MID(AG80,FIND("-",AG80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AG80,FIND("-",AG80)-1),""))-(IFERROR(--MID(AG80,FIND("-",AG80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AG80,FIND("-",AG80)-1),""))-(IFERROR(--MID(AG80,FIND("-",AG80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AG80,FIND("-",AG80)-1),""))=(AW80))+2*((IFERROR(--MID(AG80,FIND("-",AG80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ80" s="11" t="str">
+      <c r="AJ80" s="11">
         <f>IF(OR($C80="",AI80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI80,FIND("-",AI80)-1),"")=AW80,IFERROR(--MID(AI80,FIND("-",AI80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AI80,FIND("-",AI80)-1),""))-(IFERROR(--MID(AI80,FIND("-",AI80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AI80,FIND("-",AI80)-1),""))-(IFERROR(--MID(AI80,FIND("-",AI80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AI80,FIND("-",AI80)-1),""))=(AW80))+2*((IFERROR(--MID(AI80,FIND("-",AI80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK80" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL80" s="11" t="str">
+      <c r="AL80" s="11">
         <f>IF(OR($C80="",AK80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK80,FIND("-",AK80)-1),"")=AW80,IFERROR(--MID(AK80,FIND("-",AK80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AK80,FIND("-",AK80)-1),""))-(IFERROR(--MID(AK80,FIND("-",AK80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AK80,FIND("-",AK80)-1),""))-(IFERROR(--MID(AK80,FIND("-",AK80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AK80,FIND("-",AK80)-1),""))=(AW80))+2*((IFERROR(--MID(AK80,FIND("-",AK80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN80" s="11" t="str">
+      <c r="AN80" s="11">
         <f>IF(OR($C80="",AM80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM80,FIND("-",AM80)-1),"")=AW80,IFERROR(--MID(AM80,FIND("-",AM80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AM80,FIND("-",AM80)-1),""))-(IFERROR(--MID(AM80,FIND("-",AM80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AM80,FIND("-",AM80)-1),""))-(IFERROR(--MID(AM80,FIND("-",AM80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AM80,FIND("-",AM80)-1),""))=(AW80))+2*((IFERROR(--MID(AM80,FIND("-",AM80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP80" s="11" t="str">
+      <c r="AP80" s="11">
         <f>IF(OR($C80="",AO80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO80,FIND("-",AO80)-1),"")=AW80,IFERROR(--MID(AO80,FIND("-",AO80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AO80,FIND("-",AO80)-1),""))-(IFERROR(--MID(AO80,FIND("-",AO80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AO80,FIND("-",AO80)-1),""))-(IFERROR(--MID(AO80,FIND("-",AO80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AO80,FIND("-",AO80)-1),""))=(AW80))+2*((IFERROR(--MID(AO80,FIND("-",AO80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ80" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AR80" s="11" t="str">
+      <c r="AR80" s="11">
         <f>IF(OR($C80="",AQ80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ80,FIND("-",AQ80)-1),"")=AW80,IFERROR(--MID(AQ80,FIND("-",AQ80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AQ80,FIND("-",AQ80)-1),""))-(IFERROR(--MID(AQ80,FIND("-",AQ80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AQ80,FIND("-",AQ80)-1),""))-(IFERROR(--MID(AQ80,FIND("-",AQ80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AQ80,FIND("-",AQ80)-1),""))=(AW80))+2*((IFERROR(--MID(AQ80,FIND("-",AQ80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS80" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AT80" s="11" t="str">
+      <c r="AT80" s="11">
         <f>IF(OR($C80="",AS80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS80,FIND("-",AS80)-1),"")=AW80,IFERROR(--MID(AS80,FIND("-",AS80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AS80,FIND("-",AS80)-1),""))-(IFERROR(--MID(AS80,FIND("-",AS80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AS80,FIND("-",AS80)-1),""))-(IFERROR(--MID(AS80,FIND("-",AS80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AS80,FIND("-",AS80)-1),""))=(AW80))+2*((IFERROR(--MID(AS80,FIND("-",AS80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU80" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV80" s="11" t="str">
+      <c r="AV80" s="11">
         <f>IF(OR($C80="",AU80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU80,FIND("-",AU80)-1),"")=AW80,IFERROR(--MID(AU80,FIND("-",AU80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AU80,FIND("-",AU80)-1),""))-(IFERROR(--MID(AU80,FIND("-",AU80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AU80,FIND("-",AU80)-1),""))-(IFERROR(--MID(AU80,FIND("-",AU80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AU80,FIND("-",AU80)-1),""))=(AW80))+2*((IFERROR(--MID(AU80,FIND("-",AU80)+1,99),""))=(AX80))),""))</f>
-        <v/>
-      </c>
-      <c r="AW80" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW80" s="11">
         <f>IF($C80="","",IFERROR(--LEFT($C80,FIND("-",$C80)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX80" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX80" s="11">
         <f>IF($C80="","",IFERROR(--MID($C80,FIND("-",$C80)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -12461,171 +12465,173 @@
       <c r="B83" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="D83" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F83" s="11" t="str">
+      <c r="F83" s="11">
         <f t="shared" ref="F83:F88" si="6">IF(OR($C83="",E83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E83,FIND("-",E83)-1),"")=AW83,IFERROR(--MID(E83,FIND("-",E83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(E83,FIND("-",E83)-1),""))-(IFERROR(--MID(E83,FIND("-",E83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(E83,FIND("-",E83)-1),""))-(IFERROR(--MID(E83,FIND("-",E83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(E83,FIND("-",E83)-1),""))=(AW83))+2*((IFERROR(--MID(E83,FIND("-",E83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H83" s="11" t="str">
+      <c r="H83" s="11">
         <f t="shared" ref="H83:H88" si="7">IF(OR($C83="",G83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G83,FIND("-",G83)-1),"")=AW83,IFERROR(--MID(G83,FIND("-",G83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(G83,FIND("-",G83)-1),""))-(IFERROR(--MID(G83,FIND("-",G83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(G83,FIND("-",G83)-1),""))-(IFERROR(--MID(G83,FIND("-",G83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(G83,FIND("-",G83)-1),""))=(AW83))+2*((IFERROR(--MID(G83,FIND("-",G83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J83" s="11" t="str">
+      <c r="J83" s="11">
         <f t="shared" ref="J83:J88" si="8">IF(OR($C83="",I83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I83,FIND("-",I83)-1),"")=AW83,IFERROR(--MID(I83,FIND("-",I83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(I83,FIND("-",I83)-1),""))-(IFERROR(--MID(I83,FIND("-",I83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(I83,FIND("-",I83)-1),""))-(IFERROR(--MID(I83,FIND("-",I83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(I83,FIND("-",I83)-1),""))=(AW83))+2*((IFERROR(--MID(I83,FIND("-",I83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L83" s="11" t="str">
+      <c r="L83" s="11">
         <f t="shared" ref="L83:L88" si="9">IF(OR($C83="",K83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K83,FIND("-",K83)-1),"")=AW83,IFERROR(--MID(K83,FIND("-",K83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(K83,FIND("-",K83)-1),""))-(IFERROR(--MID(K83,FIND("-",K83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(K83,FIND("-",K83)-1),""))-(IFERROR(--MID(K83,FIND("-",K83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(K83,FIND("-",K83)-1),""))=(AW83))+2*((IFERROR(--MID(K83,FIND("-",K83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M83" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N83" s="11" t="str">
+      <c r="N83" s="11">
         <f t="shared" ref="N83:N88" si="10">IF(OR($C83="",M83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M83,FIND("-",M83)-1),"")=AW83,IFERROR(--MID(M83,FIND("-",M83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(M83,FIND("-",M83)-1),""))-(IFERROR(--MID(M83,FIND("-",M83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(M83,FIND("-",M83)-1),""))-(IFERROR(--MID(M83,FIND("-",M83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(M83,FIND("-",M83)-1),""))=(AW83))+2*((IFERROR(--MID(M83,FIND("-",M83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="P83" s="11" t="str">
+      <c r="P83" s="11">
         <f t="shared" ref="P83:P88" si="11">IF(OR($C83="",O83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O83,FIND("-",O83)-1),"")=AW83,IFERROR(--MID(O83,FIND("-",O83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(O83,FIND("-",O83)-1),""))-(IFERROR(--MID(O83,FIND("-",O83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(O83,FIND("-",O83)-1),""))-(IFERROR(--MID(O83,FIND("-",O83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(O83,FIND("-",O83)-1),""))=(AW83))+2*((IFERROR(--MID(O83,FIND("-",O83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q83" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R83" s="11" t="str">
+      <c r="R83" s="11">
         <f t="shared" ref="R83:R88" si="12">IF(OR($C83="",Q83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q83,FIND("-",Q83)-1),"")=AW83,IFERROR(--MID(Q83,FIND("-",Q83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(Q83,FIND("-",Q83)-1),""))-(IFERROR(--MID(Q83,FIND("-",Q83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(Q83,FIND("-",Q83)-1),""))-(IFERROR(--MID(Q83,FIND("-",Q83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(Q83,FIND("-",Q83)-1),""))=(AW83))+2*((IFERROR(--MID(Q83,FIND("-",Q83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S83" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="T83" s="11" t="str">
+      <c r="T83" s="11">
         <f t="shared" ref="T83:T88" si="13">IF(OR($C83="",S83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S83,FIND("-",S83)-1),"")=AW83,IFERROR(--MID(S83,FIND("-",S83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(S83,FIND("-",S83)-1),""))-(IFERROR(--MID(S83,FIND("-",S83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(S83,FIND("-",S83)-1),""))-(IFERROR(--MID(S83,FIND("-",S83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(S83,FIND("-",S83)-1),""))=(AW83))+2*((IFERROR(--MID(S83,FIND("-",S83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V83" s="11" t="str">
+      <c r="V83" s="11">
         <f t="shared" ref="V83:V88" si="14">IF(OR($C83="",U83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U83,FIND("-",U83)-1),"")=AW83,IFERROR(--MID(U83,FIND("-",U83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(U83,FIND("-",U83)-1),""))-(IFERROR(--MID(U83,FIND("-",U83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(U83,FIND("-",U83)-1),""))-(IFERROR(--MID(U83,FIND("-",U83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(U83,FIND("-",U83)-1),""))=(AW83))+2*((IFERROR(--MID(U83,FIND("-",U83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="X83" s="11" t="str">
+      <c r="X83" s="11">
         <f t="shared" ref="X83:X88" si="15">IF(OR($C83="",W83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W83,FIND("-",W83)-1),"")=AW83,IFERROR(--MID(W83,FIND("-",W83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(W83,FIND("-",W83)-1),""))-(IFERROR(--MID(W83,FIND("-",W83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(W83,FIND("-",W83)-1),""))-(IFERROR(--MID(W83,FIND("-",W83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(W83,FIND("-",W83)-1),""))=(AW83))+2*((IFERROR(--MID(W83,FIND("-",W83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z83" s="11" t="str">
+      <c r="Z83" s="11">
         <f t="shared" ref="Z83:Z88" si="16">IF(OR($C83="",Y83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y83,FIND("-",Y83)-1),"")=AW83,IFERROR(--MID(Y83,FIND("-",Y83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(Y83,FIND("-",Y83)-1),""))-(IFERROR(--MID(Y83,FIND("-",Y83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(Y83,FIND("-",Y83)-1),""))-(IFERROR(--MID(Y83,FIND("-",Y83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(Y83,FIND("-",Y83)-1),""))=(AW83))+2*((IFERROR(--MID(Y83,FIND("-",Y83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA83" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AB83" s="11" t="str">
+      <c r="AB83" s="11">
         <f t="shared" ref="AB83:AB88" si="17">IF(OR($C83="",AA83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA83,FIND("-",AA83)-1),"")=AW83,IFERROR(--MID(AA83,FIND("-",AA83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AA83,FIND("-",AA83)-1),""))-(IFERROR(--MID(AA83,FIND("-",AA83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AA83,FIND("-",AA83)-1),""))-(IFERROR(--MID(AA83,FIND("-",AA83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AA83,FIND("-",AA83)-1),""))=(AW83))+2*((IFERROR(--MID(AA83,FIND("-",AA83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC83" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="AD83" s="11" t="str">
+      <c r="AD83" s="11">
         <f t="shared" ref="AD83:AD88" si="18">IF(OR($C83="",AC83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC83,FIND("-",AC83)-1),"")=AW83,IFERROR(--MID(AC83,FIND("-",AC83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AC83,FIND("-",AC83)-1),""))-(IFERROR(--MID(AC83,FIND("-",AC83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AC83,FIND("-",AC83)-1),""))-(IFERROR(--MID(AC83,FIND("-",AC83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AC83,FIND("-",AC83)-1),""))=(AW83))+2*((IFERROR(--MID(AC83,FIND("-",AC83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF83" s="11" t="str">
+      <c r="AF83" s="11">
         <f t="shared" ref="AF83:AF88" si="19">IF(OR($C83="",AE83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE83,FIND("-",AE83)-1),"")=AW83,IFERROR(--MID(AE83,FIND("-",AE83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AE83,FIND("-",AE83)-1),""))-(IFERROR(--MID(AE83,FIND("-",AE83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AE83,FIND("-",AE83)-1),""))-(IFERROR(--MID(AE83,FIND("-",AE83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AE83,FIND("-",AE83)-1),""))=(AW83))+2*((IFERROR(--MID(AE83,FIND("-",AE83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH83" s="11" t="str">
+      <c r="AH83" s="11">
         <f t="shared" ref="AH83:AH88" si="20">IF(OR($C83="",AG83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG83,FIND("-",AG83)-1),"")=AW83,IFERROR(--MID(AG83,FIND("-",AG83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AG83,FIND("-",AG83)-1),""))-(IFERROR(--MID(AG83,FIND("-",AG83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AG83,FIND("-",AG83)-1),""))-(IFERROR(--MID(AG83,FIND("-",AG83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AG83,FIND("-",AG83)-1),""))=(AW83))+2*((IFERROR(--MID(AG83,FIND("-",AG83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI83" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AJ83" s="11" t="str">
+      <c r="AJ83" s="11">
         <f t="shared" ref="AJ83:AJ88" si="21">IF(OR($C83="",AI83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI83,FIND("-",AI83)-1),"")=AW83,IFERROR(--MID(AI83,FIND("-",AI83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AI83,FIND("-",AI83)-1),""))-(IFERROR(--MID(AI83,FIND("-",AI83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AI83,FIND("-",AI83)-1),""))-(IFERROR(--MID(AI83,FIND("-",AI83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AI83,FIND("-",AI83)-1),""))=(AW83))+2*((IFERROR(--MID(AI83,FIND("-",AI83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL83" s="11" t="str">
+      <c r="AL83" s="11">
         <f t="shared" ref="AL83:AL88" si="22">IF(OR($C83="",AK83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK83,FIND("-",AK83)-1),"")=AW83,IFERROR(--MID(AK83,FIND("-",AK83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AK83,FIND("-",AK83)-1),""))-(IFERROR(--MID(AK83,FIND("-",AK83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AK83,FIND("-",AK83)-1),""))-(IFERROR(--MID(AK83,FIND("-",AK83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AK83,FIND("-",AK83)-1),""))=(AW83))+2*((IFERROR(--MID(AK83,FIND("-",AK83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AN83" s="11" t="str">
+      <c r="AN83" s="11">
         <f t="shared" ref="AN83:AN88" si="23">IF(OR($C83="",AM83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM83,FIND("-",AM83)-1),"")=AW83,IFERROR(--MID(AM83,FIND("-",AM83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AM83,FIND("-",AM83)-1),""))-(IFERROR(--MID(AM83,FIND("-",AM83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AM83,FIND("-",AM83)-1),""))-(IFERROR(--MID(AM83,FIND("-",AM83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AM83,FIND("-",AM83)-1),""))=(AW83))+2*((IFERROR(--MID(AM83,FIND("-",AM83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO83" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AP83" s="11" t="str">
+      <c r="AP83" s="11">
         <f t="shared" ref="AP83:AP88" si="24">IF(OR($C83="",AO83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO83,FIND("-",AO83)-1),"")=AW83,IFERROR(--MID(AO83,FIND("-",AO83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AO83,FIND("-",AO83)-1),""))-(IFERROR(--MID(AO83,FIND("-",AO83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AO83,FIND("-",AO83)-1),""))-(IFERROR(--MID(AO83,FIND("-",AO83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AO83,FIND("-",AO83)-1),""))=(AW83))+2*((IFERROR(--MID(AO83,FIND("-",AO83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ83" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR83" s="11" t="str">
+      <c r="AR83" s="11">
         <f t="shared" ref="AR83:AR89" si="25">IF(OR($C83="",AQ83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ83,FIND("-",AQ83)-1),"")=AW83,IFERROR(--MID(AQ83,FIND("-",AQ83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AQ83,FIND("-",AQ83)-1),""))-(IFERROR(--MID(AQ83,FIND("-",AQ83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AQ83,FIND("-",AQ83)-1),""))-(IFERROR(--MID(AQ83,FIND("-",AQ83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AQ83,FIND("-",AQ83)-1),""))=(AW83))+2*((IFERROR(--MID(AQ83,FIND("-",AQ83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS83" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="AT83" s="11" t="str">
+      <c r="AT83" s="11">
         <f t="shared" ref="AT83:AT89" si="26">IF(OR($C83="",AS83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS83,FIND("-",AS83)-1),"")=AW83,IFERROR(--MID(AS83,FIND("-",AS83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AS83,FIND("-",AS83)-1),""))-(IFERROR(--MID(AS83,FIND("-",AS83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AS83,FIND("-",AS83)-1),""))-(IFERROR(--MID(AS83,FIND("-",AS83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AS83,FIND("-",AS83)-1),""))=(AW83))+2*((IFERROR(--MID(AS83,FIND("-",AS83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU83" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AV83" s="11" t="str">
+      <c r="AV83" s="11">
         <f t="shared" ref="AV83:AV88" si="27">IF(OR($C83="",AU83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU83,FIND("-",AU83)-1),"")=AW83,IFERROR(--MID(AU83,FIND("-",AU83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AU83,FIND("-",AU83)-1),""))-(IFERROR(--MID(AU83,FIND("-",AU83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AU83,FIND("-",AU83)-1),""))-(IFERROR(--MID(AU83,FIND("-",AU83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AU83,FIND("-",AU83)-1),""))=(AW83))+2*((IFERROR(--MID(AU83,FIND("-",AU83)+1,99),""))=(AX83))),""))</f>
-        <v/>
-      </c>
-      <c r="AW83" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW83" s="11">
         <f t="shared" ref="AW83:AW88" si="28">IF($C83="","",IFERROR(--LEFT($C83,FIND("-",$C83)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX83" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX83" s="11">
         <f t="shared" ref="AX83:AX88" si="29">IF($C83="","",IFERROR(--MID($C83,FIND("-",$C83)+1,99),""))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -12635,171 +12641,173 @@
       <c r="B84" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C84" s="10"/>
+      <c r="C84" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="D84" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F84" s="11" t="str">
+      <c r="F84" s="11">
         <f t="shared" si="6"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H84" s="11" t="str">
+      <c r="H84" s="11">
         <f t="shared" si="7"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J84" s="11" t="str">
+      <c r="J84" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K84" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="L84" s="11" t="str">
+      <c r="L84" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N84" s="11" t="str">
+      <c r="N84" s="11">
         <f t="shared" si="10"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P84" s="11" t="str">
+      <c r="P84" s="11">
         <f t="shared" si="11"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q84" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="R84" s="11" t="str">
+      <c r="R84" s="11">
         <f t="shared" si="12"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S84" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T84" s="11" t="str">
+      <c r="T84" s="11">
         <f t="shared" si="13"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V84" s="11" t="str">
+      <c r="V84" s="11">
         <f t="shared" si="14"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X84" s="11" t="str">
+      <c r="X84" s="11">
         <f t="shared" si="15"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z84" s="11" t="str">
+      <c r="Z84" s="11">
         <f t="shared" si="16"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB84" s="11" t="str">
+      <c r="AB84" s="11">
         <f t="shared" si="17"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC84" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="AD84" s="11" t="str">
+      <c r="AD84" s="11">
         <f t="shared" si="18"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF84" s="11" t="str">
+      <c r="AF84" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH84" s="11" t="str">
+      <c r="AH84" s="11">
         <f t="shared" si="20"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ84" s="11" t="str">
+      <c r="AJ84" s="11">
         <f t="shared" si="21"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL84" s="11" t="str">
+      <c r="AL84" s="11">
         <f t="shared" si="22"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM84" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN84" s="11" t="str">
+      <c r="AN84" s="11">
         <f t="shared" si="23"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP84" s="11" t="str">
+      <c r="AP84" s="11">
         <f t="shared" si="24"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ84" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR84" s="11" t="str">
+      <c r="AR84" s="11">
         <f t="shared" si="25"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT84" s="11" t="str">
+      <c r="AT84" s="11">
         <f t="shared" si="26"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV84" s="11" t="str">
+      <c r="AV84" s="11">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="AW84" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW84" s="11">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AX84" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX84" s="11">
         <f t="shared" si="29"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -12809,171 +12817,173 @@
       <c r="B85" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="D85" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F85" s="11" t="str">
+      <c r="F85" s="11">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H85" s="11" t="str">
+      <c r="H85" s="11">
         <f t="shared" si="7"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J85" s="11" t="str">
+      <c r="J85" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K85" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="L85" s="11" t="str">
+      <c r="L85" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N85" s="11" t="str">
+      <c r="N85" s="11">
         <f t="shared" si="10"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P85" s="11" t="str">
+      <c r="P85" s="11">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q85" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R85" s="11" t="str">
+      <c r="R85" s="11">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S85" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="T85" s="11" t="str">
+      <c r="T85" s="11">
         <f t="shared" si="13"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="U85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="V85" s="11" t="str">
+      <c r="V85" s="11">
         <f t="shared" si="14"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="W85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="X85" s="11" t="str">
+      <c r="X85" s="11">
         <f t="shared" si="15"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z85" s="11" t="str">
+      <c r="Z85" s="11">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB85" s="11" t="str">
+      <c r="AB85" s="11">
         <f t="shared" si="17"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC85" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="AD85" s="11" t="str">
+      <c r="AD85" s="11">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF85" s="11" t="str">
+      <c r="AF85" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH85" s="11" t="str">
+      <c r="AH85" s="11">
         <f t="shared" si="20"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI85" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AJ85" s="11" t="str">
+      <c r="AJ85" s="11">
         <f t="shared" si="21"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL85" s="11" t="str">
+      <c r="AL85" s="11">
         <f t="shared" si="22"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AN85" s="11" t="str">
+      <c r="AN85" s="11">
         <f t="shared" si="23"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO85" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AP85" s="11" t="str">
+      <c r="AP85" s="11">
         <f t="shared" si="24"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ85" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR85" s="11" t="str">
+      <c r="AR85" s="11">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT85" s="11" t="str">
+      <c r="AT85" s="11">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU85" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AV85" s="11" t="str">
+      <c r="AV85" s="11">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="AW85" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW85" s="11">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AX85" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX85" s="11">
         <f t="shared" si="29"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -12983,171 +12993,173 @@
       <c r="B86" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="10"/>
+      <c r="C86" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D86" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F86" s="11" t="str">
+      <c r="F86" s="11">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H86" s="11" t="str">
+      <c r="H86" s="11">
         <f t="shared" si="7"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I86" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="J86" s="11" t="str">
+      <c r="J86" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K86" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L86" s="11" t="str">
+      <c r="L86" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N86" s="11" t="str">
+      <c r="N86" s="11">
         <f t="shared" si="10"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O86" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="P86" s="11" t="str">
+      <c r="P86" s="11">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q86" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R86" s="11" t="str">
+      <c r="R86" s="11">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T86" s="11" t="str">
+      <c r="T86" s="11">
         <f t="shared" si="13"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U86" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="V86" s="11" t="str">
+      <c r="V86" s="11">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W86" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="X86" s="11" t="str">
+      <c r="X86" s="11">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y86" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z86" s="11" t="str">
+      <c r="Z86" s="11">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB86" s="11" t="str">
+      <c r="AB86" s="11">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC86" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="AD86" s="11" t="str">
+      <c r="AD86" s="11">
         <f t="shared" si="18"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF86" s="11" t="str">
+      <c r="AF86" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG86" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AH86" s="11" t="str">
+      <c r="AH86" s="11">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ86" s="11" t="str">
+      <c r="AJ86" s="11">
         <f t="shared" si="21"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AL86" s="11" t="str">
+      <c r="AL86" s="11">
         <f t="shared" si="22"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM86" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN86" s="11" t="str">
+      <c r="AN86" s="11">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP86" s="11" t="str">
+      <c r="AP86" s="11">
         <f t="shared" si="24"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR86" s="11" t="str">
+      <c r="AR86" s="11">
         <f t="shared" si="25"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT86" s="11" t="str">
+      <c r="AT86" s="11">
         <f t="shared" si="26"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU86" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AV86" s="11" t="str">
+      <c r="AV86" s="11">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="AW86" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW86" s="11">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AX86" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX86" s="11">
         <f t="shared" si="29"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26584,7 +26596,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -26592,7 +26604,7 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>236</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26601,26 +26613,26 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>230</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>262</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>230</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
@@ -26628,7 +26640,7 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!I17</f>
@@ -26636,7 +26648,7 @@
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>230</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26650,7 +26662,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26658,7 +26670,7 @@
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>229</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26667,20 +26679,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>227</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>258</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>227</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26689,20 +26701,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>225</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>256</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>225</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26711,20 +26723,20 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>224</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>255</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>224</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26733,20 +26745,20 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>224</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>255</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>224</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26760,7 +26772,7 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26768,29 +26780,29 @@
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>223</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>223</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>242</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>223</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26799,20 +26811,20 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>219</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>241</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>219</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26821,42 +26833,42 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>210</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>239</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>210</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>210</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>234</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>210</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26865,64 +26877,64 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>204</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>232</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>204</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>204</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>230</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>204</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>203</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>230</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>203</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26936,7 +26948,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26944,7 +26956,7 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>186</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26953,20 +26965,20 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C20" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>182</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>198</v>
       </c>
       <c r="D20" s="11">
-        <f>Bonus_beheer!K17</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26975,20 +26987,20 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>178</v>
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
+        <v>194</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -27002,7 +27014,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -27010,7 +27022,7 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -27024,7 +27036,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -27032,7 +27044,7 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -27046,7 +27058,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!S17</f>
@@ -27054,7 +27066,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>160</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -27676,16 +27688,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1540" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEF60F4-95A2-42B0-B0C6-14325133CD3E}"/>
+  <xr:revisionPtr revIDLastSave="1546" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25645308-D081-4AF4-8DA0-D56BC8EF4BDA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1349,21 +1349,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1731,22 +1731,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40" t="s">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="40" t="s">
+      <c r="C1" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="44"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1826,11 +1826,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="39"/>
+      <c r="AT1" s="44"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="39"/>
+      <c r="AV1" s="44"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1839,9 +1839,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="41"/>
+      <c r="A2" s="43"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1986,53 +1986,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="40"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -13169,171 +13169,173 @@
       <c r="B87" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="10" t="s">
+        <v>48</v>
+      </c>
       <c r="D87" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F87" s="11" t="str">
+      <c r="F87" s="11">
         <f t="shared" si="6"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H87" s="11" t="str">
+      <c r="H87" s="11">
         <f t="shared" si="7"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I87" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="J87" s="11" t="str">
+      <c r="J87" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L87" s="11" t="str">
+      <c r="L87" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M87" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N87" s="11" t="str">
+      <c r="N87" s="11">
         <f t="shared" si="10"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="P87" s="11" t="str">
+      <c r="P87" s="11">
         <f t="shared" si="11"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q87" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R87" s="11" t="str">
+      <c r="R87" s="11">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S87" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T87" s="11" t="str">
+      <c r="T87" s="11">
         <f t="shared" si="13"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U87" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V87" s="11" t="str">
+      <c r="V87" s="11">
         <f t="shared" si="14"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W87" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X87" s="11" t="str">
+      <c r="X87" s="11">
         <f t="shared" si="15"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Y87" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="Z87" s="11" t="str">
+      <c r="Z87" s="11">
         <f t="shared" si="16"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA87" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AB87" s="11" t="str">
+      <c r="AB87" s="11">
         <f t="shared" si="17"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC87" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="AD87" s="11" t="str">
+      <c r="AD87" s="11">
         <f t="shared" si="18"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE87" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF87" s="11" t="str">
+      <c r="AF87" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG87" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH87" s="11" t="str">
+      <c r="AH87" s="11">
         <f t="shared" si="20"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI87" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AJ87" s="11" t="str">
+      <c r="AJ87" s="11">
         <f t="shared" si="21"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK87" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL87" s="11" t="str">
+      <c r="AL87" s="11">
         <f t="shared" si="22"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM87" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN87" s="11" t="str">
+      <c r="AN87" s="11">
         <f t="shared" si="23"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO87" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AP87" s="11" t="str">
+      <c r="AP87" s="11">
         <f t="shared" si="24"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ87" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AR87" s="11" t="str">
+      <c r="AR87" s="11">
         <f t="shared" si="25"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS87" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT87" s="11" t="str">
+      <c r="AT87" s="11">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU87" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AV87" s="11" t="str">
+      <c r="AV87" s="11">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="AW87" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW87" s="11">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AX87" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX87" s="11">
         <f t="shared" si="29"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -13343,171 +13345,173 @@
       <c r="B88" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="10"/>
+      <c r="C88" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="D88" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F88" s="11" t="str">
+      <c r="F88" s="11">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H88" s="11" t="str">
+      <c r="H88" s="11">
         <f t="shared" si="7"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I88" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J88" s="11" t="str">
+      <c r="J88" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K88" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="L88" s="11" t="str">
+      <c r="L88" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M88" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N88" s="11" t="str">
+      <c r="N88" s="11">
         <f t="shared" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O88" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P88" s="11" t="str">
+      <c r="P88" s="11">
         <f t="shared" si="11"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q88" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="R88" s="11" t="str">
+      <c r="R88" s="11">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S88" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="T88" s="11" t="str">
+      <c r="T88" s="11">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V88" s="11" t="str">
+      <c r="V88" s="11">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W88" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X88" s="11" t="str">
+      <c r="X88" s="11">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y88" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z88" s="11" t="str">
+      <c r="Z88" s="11">
         <f t="shared" si="16"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA88" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AB88" s="11" t="str">
+      <c r="AB88" s="11">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC88" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="AD88" s="11" t="str">
+      <c r="AD88" s="11">
         <f t="shared" si="18"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE88" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AF88" s="11" t="str">
+      <c r="AF88" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG88" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH88" s="11" t="str">
+      <c r="AH88" s="11">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI88" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="AJ88" s="11" t="str">
+      <c r="AJ88" s="11">
         <f t="shared" si="21"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK88" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL88" s="11" t="str">
+      <c r="AL88" s="11">
         <f t="shared" si="22"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM88" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AN88" s="11" t="str">
+      <c r="AN88" s="11">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO88" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP88" s="11" t="str">
+      <c r="AP88" s="11">
         <f t="shared" si="24"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ88" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR88" s="11" t="str">
+      <c r="AR88" s="11">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS88" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AT88" s="11" t="str">
+      <c r="AT88" s="11">
         <f t="shared" si="26"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU88" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AV88" s="11" t="str">
+      <c r="AV88" s="11">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="AW88" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW88" s="11">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AX88" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX88" s="11">
         <f t="shared" si="29"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -13629,171 +13633,173 @@
       <c r="B91" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D91" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F91" s="11" t="str">
+      <c r="F91" s="11">
         <f t="shared" ref="F91:F96" si="30">IF(OR($C91="",E91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E91,FIND("-",E91)-1),"")=AW91,IFERROR(--MID(E91,FIND("-",E91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(E91,FIND("-",E91)-1),""))-(IFERROR(--MID(E91,FIND("-",E91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(E91,FIND("-",E91)-1),""))-(IFERROR(--MID(E91,FIND("-",E91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(E91,FIND("-",E91)-1),""))=(AW91))+2*((IFERROR(--MID(E91,FIND("-",E91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H91" s="11" t="str">
+      <c r="H91" s="11">
         <f t="shared" ref="H91:H96" si="31">IF(OR($C91="",G91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G91,FIND("-",G91)-1),"")=AW91,IFERROR(--MID(G91,FIND("-",G91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(G91,FIND("-",G91)-1),""))-(IFERROR(--MID(G91,FIND("-",G91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(G91,FIND("-",G91)-1),""))-(IFERROR(--MID(G91,FIND("-",G91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(G91,FIND("-",G91)-1),""))=(AW91))+2*((IFERROR(--MID(G91,FIND("-",G91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I91" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="J91" s="11" t="str">
+      <c r="J91" s="11">
         <f t="shared" ref="J91:J96" si="32">IF(OR($C91="",I91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I91,FIND("-",I91)-1),"")=AW91,IFERROR(--MID(I91,FIND("-",I91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(I91,FIND("-",I91)-1),""))-(IFERROR(--MID(I91,FIND("-",I91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(I91,FIND("-",I91)-1),""))-(IFERROR(--MID(I91,FIND("-",I91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(I91,FIND("-",I91)-1),""))=(AW91))+2*((IFERROR(--MID(I91,FIND("-",I91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="L91" s="11" t="str">
+      <c r="L91" s="11">
         <f t="shared" ref="L91:L96" si="33">IF(OR($C91="",K91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K91,FIND("-",K91)-1),"")=AW91,IFERROR(--MID(K91,FIND("-",K91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(K91,FIND("-",K91)-1),""))-(IFERROR(--MID(K91,FIND("-",K91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(K91,FIND("-",K91)-1),""))-(IFERROR(--MID(K91,FIND("-",K91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(K91,FIND("-",K91)-1),""))=(AW91))+2*((IFERROR(--MID(K91,FIND("-",K91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M91" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N91" s="11" t="str">
+      <c r="N91" s="11">
         <f t="shared" ref="N91:N96" si="34">IF(OR($C91="",M91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M91,FIND("-",M91)-1),"")=AW91,IFERROR(--MID(M91,FIND("-",M91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(M91,FIND("-",M91)-1),""))-(IFERROR(--MID(M91,FIND("-",M91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(M91,FIND("-",M91)-1),""))-(IFERROR(--MID(M91,FIND("-",M91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(M91,FIND("-",M91)-1),""))=(AW91))+2*((IFERROR(--MID(M91,FIND("-",M91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="P91" s="11" t="str">
+      <c r="P91" s="11">
         <f t="shared" ref="P91:P96" si="35">IF(OR($C91="",O91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O91,FIND("-",O91)-1),"")=AW91,IFERROR(--MID(O91,FIND("-",O91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(O91,FIND("-",O91)-1),""))-(IFERROR(--MID(O91,FIND("-",O91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(O91,FIND("-",O91)-1),""))-(IFERROR(--MID(O91,FIND("-",O91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(O91,FIND("-",O91)-1),""))=(AW91))+2*((IFERROR(--MID(O91,FIND("-",O91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q91" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="R91" s="11" t="str">
+      <c r="R91" s="11">
         <f t="shared" ref="R91:R96" si="36">IF(OR($C91="",Q91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q91,FIND("-",Q91)-1),"")=AW91,IFERROR(--MID(Q91,FIND("-",Q91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(Q91,FIND("-",Q91)-1),""))-(IFERROR(--MID(Q91,FIND("-",Q91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(Q91,FIND("-",Q91)-1),""))-(IFERROR(--MID(Q91,FIND("-",Q91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(Q91,FIND("-",Q91)-1),""))=(AW91))+2*((IFERROR(--MID(Q91,FIND("-",Q91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S91" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T91" s="11" t="str">
+      <c r="T91" s="11">
         <f t="shared" ref="T91:T96" si="37">IF(OR($C91="",S91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S91,FIND("-",S91)-1),"")=AW91,IFERROR(--MID(S91,FIND("-",S91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(S91,FIND("-",S91)-1),""))-(IFERROR(--MID(S91,FIND("-",S91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(S91,FIND("-",S91)-1),""))-(IFERROR(--MID(S91,FIND("-",S91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(S91,FIND("-",S91)-1),""))=(AW91))+2*((IFERROR(--MID(S91,FIND("-",S91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V91" s="11" t="str">
+      <c r="V91" s="11">
         <f t="shared" ref="V91:V96" si="38">IF(OR($C91="",U91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U91,FIND("-",U91)-1),"")=AW91,IFERROR(--MID(U91,FIND("-",U91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(U91,FIND("-",U91)-1),""))-(IFERROR(--MID(U91,FIND("-",U91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(U91,FIND("-",U91)-1),""))-(IFERROR(--MID(U91,FIND("-",U91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(U91,FIND("-",U91)-1),""))=(AW91))+2*((IFERROR(--MID(U91,FIND("-",U91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X91" s="11" t="str">
+      <c r="X91" s="11">
         <f t="shared" ref="X91:X96" si="39">IF(OR($C91="",W91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W91,FIND("-",W91)-1),"")=AW91,IFERROR(--MID(W91,FIND("-",W91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(W91,FIND("-",W91)-1),""))-(IFERROR(--MID(W91,FIND("-",W91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(W91,FIND("-",W91)-1),""))-(IFERROR(--MID(W91,FIND("-",W91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(W91,FIND("-",W91)-1),""))=(AW91))+2*((IFERROR(--MID(W91,FIND("-",W91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Y91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z91" s="11" t="str">
+      <c r="Z91" s="11">
         <f t="shared" ref="Z91:Z96" si="40">IF(OR($C91="",Y91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y91,FIND("-",Y91)-1),"")=AW91,IFERROR(--MID(Y91,FIND("-",Y91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(Y91,FIND("-",Y91)-1),""))-(IFERROR(--MID(Y91,FIND("-",Y91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(Y91,FIND("-",Y91)-1),""))-(IFERROR(--MID(Y91,FIND("-",Y91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(Y91,FIND("-",Y91)-1),""))=(AW91))+2*((IFERROR(--MID(Y91,FIND("-",Y91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AB91" s="11" t="str">
+      <c r="AB91" s="11">
         <f t="shared" ref="AB91:AB96" si="41">IF(OR($C91="",AA91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA91,FIND("-",AA91)-1),"")=AW91,IFERROR(--MID(AA91,FIND("-",AA91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AA91,FIND("-",AA91)-1),""))-(IFERROR(--MID(AA91,FIND("-",AA91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AA91,FIND("-",AA91)-1),""))-(IFERROR(--MID(AA91,FIND("-",AA91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AA91,FIND("-",AA91)-1),""))=(AW91))+2*((IFERROR(--MID(AA91,FIND("-",AA91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC91" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="AD91" s="11" t="str">
+      <c r="AD91" s="11">
         <f t="shared" ref="AD91:AD96" si="42">IF(OR($C91="",AC91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC91,FIND("-",AC91)-1),"")=AW91,IFERROR(--MID(AC91,FIND("-",AC91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AC91,FIND("-",AC91)-1),""))-(IFERROR(--MID(AC91,FIND("-",AC91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AC91,FIND("-",AC91)-1),""))-(IFERROR(--MID(AC91,FIND("-",AC91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AC91,FIND("-",AC91)-1),""))=(AW91))+2*((IFERROR(--MID(AC91,FIND("-",AC91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF91" s="11" t="str">
+      <c r="AF91" s="11">
         <f t="shared" ref="AF91:AF96" si="43">IF(OR($C91="",AE91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE91,FIND("-",AE91)-1),"")=AW91,IFERROR(--MID(AE91,FIND("-",AE91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AE91,FIND("-",AE91)-1),""))-(IFERROR(--MID(AE91,FIND("-",AE91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AE91,FIND("-",AE91)-1),""))-(IFERROR(--MID(AE91,FIND("-",AE91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AE91,FIND("-",AE91)-1),""))=(AW91))+2*((IFERROR(--MID(AE91,FIND("-",AE91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG91" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH91" s="11" t="str">
+      <c r="AH91" s="11">
         <f t="shared" ref="AH91:AH96" si="44">IF(OR($C91="",AG91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG91,FIND("-",AG91)-1),"")=AW91,IFERROR(--MID(AG91,FIND("-",AG91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AG91,FIND("-",AG91)-1),""))-(IFERROR(--MID(AG91,FIND("-",AG91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AG91,FIND("-",AG91)-1),""))-(IFERROR(--MID(AG91,FIND("-",AG91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AG91,FIND("-",AG91)-1),""))=(AW91))+2*((IFERROR(--MID(AG91,FIND("-",AG91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI91" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AJ91" s="11" t="str">
+      <c r="AJ91" s="11">
         <f t="shared" ref="AJ91:AJ96" si="45">IF(OR($C91="",AI91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI91,FIND("-",AI91)-1),"")=AW91,IFERROR(--MID(AI91,FIND("-",AI91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AI91,FIND("-",AI91)-1),""))-(IFERROR(--MID(AI91,FIND("-",AI91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AI91,FIND("-",AI91)-1),""))-(IFERROR(--MID(AI91,FIND("-",AI91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AI91,FIND("-",AI91)-1),""))=(AW91))+2*((IFERROR(--MID(AI91,FIND("-",AI91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK91" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL91" s="11" t="str">
+      <c r="AL91" s="11">
         <f t="shared" ref="AL91:AL96" si="46">IF(OR($C91="",AK91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK91,FIND("-",AK91)-1),"")=AW91,IFERROR(--MID(AK91,FIND("-",AK91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AK91,FIND("-",AK91)-1),""))-(IFERROR(--MID(AK91,FIND("-",AK91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AK91,FIND("-",AK91)-1),""))-(IFERROR(--MID(AK91,FIND("-",AK91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AK91,FIND("-",AK91)-1),""))=(AW91))+2*((IFERROR(--MID(AK91,FIND("-",AK91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN91" s="11" t="str">
+      <c r="AN91" s="11">
         <f t="shared" ref="AN91:AN96" si="47">IF(OR($C91="",AM91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM91,FIND("-",AM91)-1),"")=AW91,IFERROR(--MID(AM91,FIND("-",AM91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AM91,FIND("-",AM91)-1),""))-(IFERROR(--MID(AM91,FIND("-",AM91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AM91,FIND("-",AM91)-1),""))-(IFERROR(--MID(AM91,FIND("-",AM91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AM91,FIND("-",AM91)-1),""))=(AW91))+2*((IFERROR(--MID(AM91,FIND("-",AM91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO91" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AP91" s="11" t="str">
+      <c r="AP91" s="11">
         <f t="shared" ref="AP91:AP96" si="48">IF(OR($C91="",AO91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO91,FIND("-",AO91)-1),"")=AW91,IFERROR(--MID(AO91,FIND("-",AO91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AO91,FIND("-",AO91)-1),""))-(IFERROR(--MID(AO91,FIND("-",AO91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AO91,FIND("-",AO91)-1),""))-(IFERROR(--MID(AO91,FIND("-",AO91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AO91,FIND("-",AO91)-1),""))=(AW91))+2*((IFERROR(--MID(AO91,FIND("-",AO91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ91" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR91" s="11" t="str">
+      <c r="AR91" s="11">
         <f t="shared" ref="AR91:AR97" si="49">IF(OR($C91="",AQ91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ91,FIND("-",AQ91)-1),"")=AW91,IFERROR(--MID(AQ91,FIND("-",AQ91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AQ91,FIND("-",AQ91)-1),""))-(IFERROR(--MID(AQ91,FIND("-",AQ91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AQ91,FIND("-",AQ91)-1),""))-(IFERROR(--MID(AQ91,FIND("-",AQ91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AQ91,FIND("-",AQ91)-1),""))=(AW91))+2*((IFERROR(--MID(AQ91,FIND("-",AQ91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS91" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT91" s="11" t="str">
+      <c r="AT91" s="11">
         <f t="shared" ref="AT91:AT97" si="50">IF(OR($C91="",AS91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS91,FIND("-",AS91)-1),"")=AW91,IFERROR(--MID(AS91,FIND("-",AS91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AS91,FIND("-",AS91)-1),""))-(IFERROR(--MID(AS91,FIND("-",AS91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AS91,FIND("-",AS91)-1),""))-(IFERROR(--MID(AS91,FIND("-",AS91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AS91,FIND("-",AS91)-1),""))=(AW91))+2*((IFERROR(--MID(AS91,FIND("-",AS91)+1,99),""))=(AX91))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AV91" s="11" t="str">
+      <c r="AV91" s="11">
         <f t="shared" ref="AV91:AV96" si="51">IF(OR($C91="",AU91=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU91,FIND("-",AU91)-1),"")=AW91,IFERROR(--MID(AU91,FIND("-",AU91)+1,99),"")=AX91),10,5*(SIGN((IFERROR(--LEFT(AU91,FIND("-",AU91)-1),""))-(IFERROR(--MID(AU91,FIND("-",AU91)+1,99),"")))=SIGN((AW91)-(AX91)))+2*(((IFERROR(--LEFT(AU91,FIND("-",AU91)-1),""))-(IFERROR(--MID(AU91,FIND("-",AU91)+1,99),"")))=((AW91)-(AX91)))+2*((IFERROR(--LEFT(AU91,FIND("-",AU91)-1),""))=(AW91))+2*((IFERROR(--MID(AU91,FIND("-",AU91)+1,99),""))=(AX91))),""))</f>
-        <v/>
-      </c>
-      <c r="AW91" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW91" s="11">
         <f t="shared" ref="AW91:AW96" si="52">IF($C91="","",IFERROR(--LEFT($C91,FIND("-",$C91)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX91" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX91" s="11">
         <f t="shared" ref="AX91:AX96" si="53">IF($C91="","",IFERROR(--MID($C91,FIND("-",$C91)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -13803,171 +13809,173 @@
       <c r="B92" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C92" s="10"/>
+      <c r="C92" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="D92" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F92" s="11" t="str">
+      <c r="F92" s="11">
         <f t="shared" si="30"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H92" s="11" t="str">
+      <c r="H92" s="11">
         <f t="shared" si="31"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I92" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J92" s="11" t="str">
+      <c r="J92" s="11">
         <f t="shared" si="32"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K92" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="L92" s="11" t="str">
+      <c r="L92" s="11">
         <f t="shared" si="33"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M92" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="N92" s="11" t="str">
+      <c r="N92" s="11">
         <f t="shared" si="34"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O92" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="P92" s="11" t="str">
+      <c r="P92" s="11">
         <f t="shared" si="35"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q92" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="R92" s="11" t="str">
+      <c r="R92" s="11">
         <f t="shared" si="36"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S92" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="T92" s="11" t="str">
+      <c r="T92" s="11">
         <f t="shared" si="37"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V92" s="11" t="str">
+      <c r="V92" s="11">
         <f t="shared" si="38"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X92" s="11" t="str">
+      <c r="X92" s="11">
         <f t="shared" si="39"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z92" s="11" t="str">
+      <c r="Z92" s="11">
         <f t="shared" si="40"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA92" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="AB92" s="11" t="str">
+      <c r="AB92" s="11">
         <f t="shared" si="41"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC92" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="AD92" s="11" t="str">
+      <c r="AD92" s="11">
         <f t="shared" si="42"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF92" s="11" t="str">
+      <c r="AF92" s="11">
         <f t="shared" si="43"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH92" s="11" t="str">
+      <c r="AH92" s="11">
         <f t="shared" si="44"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AJ92" s="11" t="str">
+      <c r="AJ92" s="11">
         <f t="shared" si="45"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL92" s="11" t="str">
+      <c r="AL92" s="11">
         <f t="shared" si="46"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN92" s="11" t="str">
+      <c r="AN92" s="11">
         <f t="shared" si="47"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AP92" s="11" t="str">
+      <c r="AP92" s="11">
         <f t="shared" si="48"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ92" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR92" s="11" t="str">
+      <c r="AR92" s="11">
         <f t="shared" si="49"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AT92" s="11" t="str">
+      <c r="AT92" s="11">
         <f t="shared" si="50"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU92" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AV92" s="11" t="str">
+      <c r="AV92" s="11">
         <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="AW92" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW92" s="11">
         <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="AX92" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX92" s="11">
         <f t="shared" si="53"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -13977,171 +13985,173 @@
       <c r="B93" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="D93" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F93" s="11" t="str">
+      <c r="F93" s="11">
         <f t="shared" si="30"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H93" s="11" t="str">
+      <c r="H93" s="11">
         <f t="shared" si="31"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I93" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J93" s="11" t="str">
+      <c r="J93" s="11">
         <f t="shared" si="32"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L93" s="11" t="str">
+      <c r="L93" s="11">
         <f t="shared" si="33"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M93" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N93" s="11" t="str">
+      <c r="N93" s="11">
         <f t="shared" si="34"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="P93" s="11" t="str">
+      <c r="P93" s="11">
         <f t="shared" si="35"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q93" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="R93" s="11" t="str">
+      <c r="R93" s="11">
         <f t="shared" si="36"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="S93" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="T93" s="11" t="str">
+      <c r="T93" s="11">
         <f t="shared" si="37"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U93" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V93" s="11" t="str">
+      <c r="V93" s="11">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W93" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="X93" s="11" t="str">
+      <c r="X93" s="11">
         <f t="shared" si="39"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y93" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z93" s="11" t="str">
+      <c r="Z93" s="11">
         <f t="shared" si="40"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA93" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AB93" s="11" t="str">
+      <c r="AB93" s="11">
         <f t="shared" si="41"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC93" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="AD93" s="11" t="str">
+      <c r="AD93" s="11">
         <f t="shared" si="42"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE93" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AF93" s="11" t="str">
+      <c r="AF93" s="11">
         <f t="shared" si="43"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG93" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AH93" s="11" t="str">
+      <c r="AH93" s="11">
         <f t="shared" si="44"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI93" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ93" s="11" t="str">
+      <c r="AJ93" s="11">
         <f t="shared" si="45"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK93" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL93" s="11" t="str">
+      <c r="AL93" s="11">
         <f t="shared" si="46"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM93" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN93" s="11" t="str">
+      <c r="AN93" s="11">
         <f t="shared" si="47"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO93" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP93" s="11" t="str">
+      <c r="AP93" s="11">
         <f t="shared" si="48"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ93" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR93" s="11" t="str">
+      <c r="AR93" s="11">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS93" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT93" s="11" t="str">
+      <c r="AT93" s="11">
         <f t="shared" si="50"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU93" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AV93" s="11" t="str">
+      <c r="AV93" s="11">
         <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="AW93" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW93" s="11">
         <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="AX93" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX93" s="11">
         <f t="shared" si="53"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -23732,6 +23742,60 @@
     <filterColumn colId="46" showButton="0"/>
   </autoFilter>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23748,60 +23812,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23968,12 +23978,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="39"/>
+      <c r="AS1" s="44"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="39"/>
+      <c r="AU1" s="44"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
@@ -26517,6 +26527,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26528,17 +26549,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26596,7 +26606,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -26604,29 +26614,29 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>271</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>262</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>289</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>262</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26635,20 +26645,20 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>261</v>
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>288</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>261</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26657,20 +26667,20 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>260</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>287</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>260</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26679,20 +26689,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>258</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>283</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>258</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26701,20 +26711,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>256</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>282</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>256</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26723,42 +26733,42 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>255</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>277</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>255</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>255</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>275</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>255</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26767,20 +26777,20 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>244</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>274</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>244</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26794,7 +26804,7 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!Y17</f>
@@ -26802,7 +26812,7 @@
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>242</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26811,20 +26821,20 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>241</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>266</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>241</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26833,20 +26843,20 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>239</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>263</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>239</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26855,42 +26865,42 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>234</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>256</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>232</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>256</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>232</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26899,42 +26909,42 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>230</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>252</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>230</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>248</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>230</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26948,7 +26958,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26956,7 +26966,7 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26970,7 +26980,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26978,7 +26988,7 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>198</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26992,7 +27002,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!K17</f>
@@ -27000,13 +27010,13 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
         <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -27014,7 +27024,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -27022,13 +27032,13 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>188</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -27036,7 +27046,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -27044,7 +27054,7 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>188</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -27058,7 +27068,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!S17</f>
@@ -27066,7 +27076,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>183</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -27639,15 +27649,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
@@ -27656,6 +27657,15 @@
     <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27678,26 +27688,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1546" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25645308-D081-4AF4-8DA0-D56BC8EF4BDA}"/>
+  <xr:revisionPtr revIDLastSave="1548" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AA6F4A3-5C2E-4996-A9EA-16D71BA36B61}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1349,21 +1349,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1731,22 +1731,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1826,11 +1826,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="44"/>
+      <c r="AT1" s="39"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="44"/>
+      <c r="AV1" s="39"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1839,9 +1839,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="43"/>
+      <c r="A2" s="41"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1986,53 +1986,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -14161,171 +14161,173 @@
       <c r="B94" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C94" s="10"/>
+      <c r="C94" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D94" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F94" s="11" t="str">
+      <c r="F94" s="11">
         <f t="shared" si="30"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G94" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H94" s="11" t="str">
+      <c r="H94" s="11">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I94" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J94" s="11" t="str">
+      <c r="J94" s="11">
         <f t="shared" si="32"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K94" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L94" s="11" t="str">
+      <c r="L94" s="11">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M94" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N94" s="11" t="str">
+      <c r="N94" s="11">
         <f t="shared" si="34"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O94" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P94" s="11" t="str">
+      <c r="P94" s="11">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q94" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R94" s="11" t="str">
+      <c r="R94" s="11">
         <f t="shared" si="36"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S94" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T94" s="11" t="str">
+      <c r="T94" s="11">
         <f t="shared" si="37"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="V94" s="11" t="str">
+      <c r="V94" s="11">
         <f t="shared" si="38"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W94" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X94" s="11" t="str">
+      <c r="X94" s="11">
         <f t="shared" si="39"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y94" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z94" s="11" t="str">
+      <c r="Z94" s="11">
         <f t="shared" si="40"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA94" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AB94" s="11" t="str">
+      <c r="AB94" s="11">
         <f t="shared" si="41"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC94" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="AD94" s="11" t="str">
+      <c r="AD94" s="11">
         <f t="shared" si="42"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE94" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF94" s="11" t="str">
+      <c r="AF94" s="11">
         <f t="shared" si="43"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG94" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH94" s="11" t="str">
+      <c r="AH94" s="11">
         <f t="shared" si="44"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI94" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AJ94" s="11" t="str">
+      <c r="AJ94" s="11">
         <f t="shared" si="45"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK94" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL94" s="11" t="str">
+      <c r="AL94" s="11">
         <f t="shared" si="46"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM94" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AN94" s="11" t="str">
+      <c r="AN94" s="11">
         <f t="shared" si="47"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO94" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP94" s="11" t="str">
+      <c r="AP94" s="11">
         <f t="shared" si="48"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ94" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AR94" s="11" t="str">
+      <c r="AR94" s="11">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS94" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT94" s="11" t="str">
+      <c r="AT94" s="11">
         <f t="shared" si="50"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU94" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV94" s="11" t="str">
+      <c r="AV94" s="11">
         <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="AW94" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW94" s="11">
         <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="AX94" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX94" s="11">
         <f t="shared" si="53"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -23742,6 +23744,60 @@
     <filterColumn colId="46" showButton="0"/>
   </autoFilter>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23758,60 +23814,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23978,12 +23980,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="44"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="44"/>
+      <c r="AU1" s="39"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
@@ -26527,6 +26529,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26538,17 +26551,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26601,64 +26603,64 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C3" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>289</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>294</v>
       </c>
       <c r="D3" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>289</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>291</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>288</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>291</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26667,20 +26669,20 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>287</v>
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>288</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26689,42 +26691,42 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>283</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>284</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>282</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>284</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26733,20 +26735,20 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>277</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>283</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26760,7 +26762,7 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26768,7 +26770,7 @@
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26782,7 +26784,7 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!AG17</f>
@@ -26790,29 +26792,29 @@
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>268</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>276</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26821,20 +26823,20 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>266</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>268</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26848,7 +26850,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26856,7 +26858,7 @@
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26958,7 +26960,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26966,7 +26968,7 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26980,7 +26982,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26988,7 +26990,7 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26997,20 +26999,20 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>212</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>219</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!K17</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -27019,37 +27021,37 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>212</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>219</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
         <v>212</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
@@ -27454,6 +27456,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27648,41 +27670,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27705,9 +27696,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1548" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AA6F4A3-5C2E-4996-A9EA-16D71BA36B61}"/>
+  <xr:revisionPtr revIDLastSave="1597" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A139B7E2-FCB6-47A2-AD89-7E91D04A02ED}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="299">
   <si>
     <t>Tijd</t>
   </si>
@@ -434,120 +434,24 @@
     <t>Zestiende finales</t>
   </si>
   <si>
-    <t>2A</t>
-  </si>
-  <si>
-    <t>2B</t>
-  </si>
-  <si>
     <t>maandag 29 juni 2026</t>
   </si>
   <si>
-    <t>1C</t>
-  </si>
-  <si>
-    <t>2F</t>
-  </si>
-  <si>
-    <t>1E</t>
-  </si>
-  <si>
-    <t>3ABCDF</t>
-  </si>
-  <si>
     <t>dinsdag 30 juni 2026</t>
   </si>
   <si>
-    <t>1F</t>
-  </si>
-  <si>
-    <t>2C</t>
-  </si>
-  <si>
-    <t>2E</t>
-  </si>
-  <si>
-    <t>2I</t>
-  </si>
-  <si>
-    <t>1I</t>
-  </si>
-  <si>
-    <t>3CDFGH</t>
-  </si>
-  <si>
     <t>woensdag 1 juli 2026</t>
   </si>
   <si>
-    <t>1A</t>
-  </si>
-  <si>
-    <t>3CEFHI</t>
-  </si>
-  <si>
-    <t>1L</t>
-  </si>
-  <si>
-    <t>3EHIJK</t>
-  </si>
-  <si>
-    <t>1G</t>
-  </si>
-  <si>
-    <t>3AEHIJ</t>
-  </si>
-  <si>
     <t>donderdag 2 juli 2026</t>
   </si>
   <si>
-    <t>1D</t>
-  </si>
-  <si>
-    <t>3BEFIJ</t>
-  </si>
-  <si>
-    <t>1H</t>
-  </si>
-  <si>
-    <t>2J</t>
-  </si>
-  <si>
     <t>vrijdag 3 juli 2026</t>
   </si>
   <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>2L</t>
-  </si>
-  <si>
-    <t>1B</t>
-  </si>
-  <si>
-    <t>3EFGIJ</t>
-  </si>
-  <si>
-    <t>2D</t>
-  </si>
-  <si>
-    <t>2G</t>
-  </si>
-  <si>
     <t>zaterdag 4 juli 2026</t>
   </si>
   <si>
-    <t>1J</t>
-  </si>
-  <si>
-    <t>2H</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>3DEIJL</t>
-  </si>
-  <si>
     <t>Achtste finales</t>
   </si>
   <si>
@@ -1035,6 +939,9 @@
   </si>
   <si>
     <t>7-1</t>
+  </si>
+  <si>
+    <t>Maroko</t>
   </si>
 </sst>
 </file>
@@ -1677,60 +1584,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" customWidth="1"/>
-    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.54296875" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.54296875" customWidth="1"/>
-    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.54296875" customWidth="1"/>
-    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.54296875" customWidth="1"/>
-    <col min="21" max="21" width="12.54296875" customWidth="1"/>
-    <col min="22" max="22" width="8.54296875" customWidth="1"/>
-    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.54296875" customWidth="1"/>
-    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.54296875" customWidth="1"/>
-    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.54296875" customWidth="1"/>
-    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.54296875" customWidth="1"/>
-    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.54296875" customWidth="1"/>
-    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.54296875" customWidth="1"/>
-    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.54296875" customWidth="1"/>
-    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.54296875" customWidth="1"/>
-    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.54296875" customWidth="1"/>
-    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.54296875" customWidth="1"/>
-    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.54296875" customWidth="1"/>
-    <col min="45" max="45" width="15.7265625" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.54296875" customWidth="1"/>
-    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.5703125" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.5703125" customWidth="1"/>
+    <col min="25" max="25" width="12.5703125" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.5703125" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.5703125" customWidth="1"/>
+    <col min="29" max="29" width="12.5703125" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.5703125" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.5703125" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.5703125" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.5703125" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.5703125" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.5703125" customWidth="1"/>
+    <col min="41" max="41" width="15.5703125" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.5703125" customWidth="1"/>
+    <col min="43" max="43" width="15.5703125" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.5703125" customWidth="1"/>
+    <col min="45" max="45" width="15.7109375" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.5703125" customWidth="1"/>
+    <col min="47" max="47" width="15.5703125" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.5703125" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -1824,7 +1731,7 @@
       </c>
       <c r="AR1" s="36"/>
       <c r="AS1" s="37" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
       <c r="AT1" s="39"/>
       <c r="AU1" s="37" t="s">
@@ -1838,7 +1745,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="41"/>
       <c r="B2" s="42"/>
       <c r="C2" s="41"/>
@@ -1982,7 +1889,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
@@ -2036,7 +1943,7 @@
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
@@ -2090,7 +1997,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2266,7 +2173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2324,7 +2231,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -2378,7 +2285,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2554,7 +2461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2730,7 +2637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2788,7 +2695,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
@@ -2842,7 +2749,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3018,7 +2925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3194,7 +3101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3252,7 +3159,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
@@ -3306,7 +3213,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3482,7 +3389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3658,7 +3565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3834,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -3842,7 +3749,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>70</v>
@@ -4010,7 +3917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4186,7 +4093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4244,7 +4151,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
@@ -4298,7 +4205,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4474,7 +4381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4650,7 +4557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4826,7 +4733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -5002,7 +4909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5060,7 +4967,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
@@ -5114,7 +5021,7 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5290,7 +5197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5466,7 +5373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5642,7 +5549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5700,7 +5607,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
@@ -5754,7 +5661,7 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5930,7 +5837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6106,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6282,7 +6189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6458,7 +6365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6634,7 +6541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6692,7 +6599,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
@@ -6746,7 +6653,7 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6922,7 +6829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7098,7 +7005,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43